--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Control de fotos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Control de fotos'!$A$7:$I$992</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Control de fotos'!$A$7:$I$997</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -220,8 +220,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ControlFotosCodigoDia" displayName="ControlFotosCodigoDia" ref="A7:I992" headerRowCount="1">
-  <autoFilter ref="A7:I992"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ControlFotosCodigoDia" displayName="ControlFotosCodigoDia" ref="A7:I997" headerRowCount="1">
+  <autoFilter ref="A7:I997"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ESTADO FOTO"/>
     <tableColumn id="2" name="CÓDIGO DÍA"/>
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I992"/>
+  <dimension ref="A1:I997"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -575,17 +575,17 @@
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <f>COUNTA(B8:B992)</f>
+        <f>COUNTA(B8:B997)</f>
         <v/>
       </c>
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="3">
-        <f>COUNTIF(A8:A992,"CON FOTO")</f>
+        <f>COUNTIF(A8:A997,"CON FOTO")</f>
         <v/>
       </c>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3">
-        <f>COUNTIF(A8:A992,"FALTA FOTO")</f>
+        <f>COUNTIF(A8:A997,"FALTA FOTO")</f>
         <v/>
       </c>
       <c r="F4" s="3" t="n"/>
@@ -29306,17 +29306,17 @@
       </c>
       <c r="B827" s="7" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="C827" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11174779</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>Sp26NEBlack</t>
+          <t>Wt26CCGl16Red</t>
         </is>
       </c>
       <c r="E827" t="inlineStr">
@@ -29341,17 +29341,17 @@
       </c>
       <c r="B828" s="7" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="C828" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11174804</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>Sp26NECrossB</t>
+          <t>Wt26BTLStanley</t>
         </is>
       </c>
       <c r="E828" t="inlineStr">
@@ -29376,17 +29376,17 @@
       </c>
       <c r="B829" s="7" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>16543</t>
         </is>
       </c>
       <c r="C829" s="7" t="inlineStr">
         <is>
-          <t>11174779</t>
+          <t>11174795</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>Wt26CCGl16Red</t>
+          <t>Wt26CC24Spinner</t>
         </is>
       </c>
       <c r="E829" t="inlineStr">
@@ -29411,17 +29411,17 @@
       </c>
       <c r="B830" s="7" t="inlineStr">
         <is>
-          <t>16541</t>
+          <t>16544</t>
         </is>
       </c>
       <c r="C830" s="7" t="inlineStr">
         <is>
-          <t>11174804</t>
+          <t>11177277</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>Wt26BTLStanley</t>
+          <t>Wt26CC24Choco</t>
         </is>
       </c>
       <c r="E830" t="inlineStr">
@@ -29446,17 +29446,17 @@
       </c>
       <c r="B831" s="7" t="inlineStr">
         <is>
-          <t>16543</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="C831" s="7" t="inlineStr">
         <is>
-          <t>11174795</t>
+          <t>11174808</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
         <is>
-          <t>Wt26CC24Spinner</t>
+          <t>Wt26SSCC24Grad</t>
         </is>
       </c>
       <c r="E831" t="inlineStr">
@@ -29481,17 +29481,17 @@
       </c>
       <c r="B832" s="7" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>16546</t>
         </is>
       </c>
       <c r="C832" s="7" t="inlineStr">
         <is>
-          <t>11177277</t>
+          <t>11174811</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>Wt26CC24Choco</t>
+          <t>Wt26SS30Jac</t>
         </is>
       </c>
       <c r="E832" t="inlineStr">
@@ -29516,17 +29516,17 @@
       </c>
       <c r="B833" s="7" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>16547</t>
         </is>
       </c>
       <c r="C833" s="7" t="inlineStr">
         <is>
-          <t>11174808</t>
+          <t>11177274</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>Wt26SSCC24Grad</t>
+          <t>Wt26SSCC24Win</t>
         </is>
       </c>
       <c r="E833" t="inlineStr">
@@ -29551,17 +29551,17 @@
       </c>
       <c r="B834" s="7" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16548</t>
         </is>
       </c>
       <c r="C834" s="7" t="inlineStr">
         <is>
-          <t>11174811</t>
+          <t>11174801</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>Wt26SS30Jac</t>
+          <t>Wt26SSBTL20SV</t>
         </is>
       </c>
       <c r="E834" t="inlineStr">
@@ -29586,17 +29586,17 @@
       </c>
       <c r="B835" s="7" t="inlineStr">
         <is>
-          <t>16547</t>
+          <t>16549</t>
         </is>
       </c>
       <c r="C835" s="7" t="inlineStr">
         <is>
-          <t>11177274</t>
+          <t>11174803</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>Wt26SSCC24Win</t>
+          <t>Wt262PkStanley</t>
         </is>
       </c>
       <c r="E835" t="inlineStr">
@@ -29621,17 +29621,17 @@
       </c>
       <c r="B836" s="7" t="inlineStr">
         <is>
-          <t>16548</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="C836" s="7" t="inlineStr">
         <is>
-          <t>11174801</t>
+          <t>11174776</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>Wt26SSBTL20SV</t>
+          <t>Wt26Mug14Bow</t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
@@ -29656,17 +29656,17 @@
       </c>
       <c r="B837" s="7" t="inlineStr">
         <is>
-          <t>16549</t>
+          <t>16551</t>
         </is>
       </c>
       <c r="C837" s="7" t="inlineStr">
         <is>
-          <t>11174803</t>
+          <t>11174775</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>Wt262PkStanley</t>
+          <t>Wt26Dw12Jac</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
@@ -29691,17 +29691,17 @@
       </c>
       <c r="B838" s="7" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>16552</t>
         </is>
       </c>
       <c r="C838" s="7" t="inlineStr">
         <is>
-          <t>11174776</t>
+          <t>11174798</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>Wt26Mug14Bow</t>
+          <t>Wt26SS16Green</t>
         </is>
       </c>
       <c r="E838" t="inlineStr">
@@ -29726,17 +29726,17 @@
       </c>
       <c r="B839" s="7" t="inlineStr">
         <is>
-          <t>16551</t>
+          <t>16553</t>
         </is>
       </c>
       <c r="C839" s="7" t="inlineStr">
         <is>
-          <t>11174775</t>
+          <t>11174800</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>Wt26Dw12Jac</t>
+          <t>Wt26BTL20Gr</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
@@ -29761,17 +29761,17 @@
       </c>
       <c r="B840" s="7" t="inlineStr">
         <is>
-          <t>16552</t>
+          <t>16554</t>
         </is>
       </c>
       <c r="C840" s="7" t="inlineStr">
         <is>
-          <t>11174798</t>
+          <t>11174807</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>Wt26SS16Green</t>
+          <t>Wt26SS16Choco</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
@@ -29796,17 +29796,17 @@
       </c>
       <c r="B841" s="7" t="inlineStr">
         <is>
-          <t>16553</t>
+          <t>16555</t>
         </is>
       </c>
       <c r="C841" s="7" t="inlineStr">
         <is>
-          <t>11174800</t>
+          <t>11174810</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>Wt26BTL20Gr</t>
+          <t>Wt26Canteen</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
@@ -29831,17 +29831,17 @@
       </c>
       <c r="B842" s="7" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>16556</t>
         </is>
       </c>
       <c r="C842" s="7" t="inlineStr">
         <is>
-          <t>11174807</t>
+          <t>11174799</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>Wt26SS16Choco</t>
+          <t>Wt26SSCC16Grad</t>
         </is>
       </c>
       <c r="E842" t="inlineStr">
@@ -29866,17 +29866,17 @@
       </c>
       <c r="B843" s="7" t="inlineStr">
         <is>
-          <t>16555</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="C843" s="7" t="inlineStr">
         <is>
-          <t>11174810</t>
+          <t>11174806</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>Wt26Canteen</t>
+          <t>Wt26SSCC16Jac</t>
         </is>
       </c>
       <c r="E843" t="inlineStr">
@@ -29901,17 +29901,17 @@
       </c>
       <c r="B844" s="7" t="inlineStr">
         <is>
-          <t>16556</t>
+          <t>16558</t>
         </is>
       </c>
       <c r="C844" s="7" t="inlineStr">
         <is>
-          <t>11174799</t>
+          <t>11177275</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>Wt26SSCC16Grad</t>
+          <t>Wt26SS20SV</t>
         </is>
       </c>
       <c r="E844" t="inlineStr">
@@ -29936,17 +29936,17 @@
       </c>
       <c r="B845" s="7" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>16559</t>
         </is>
       </c>
       <c r="C845" s="7" t="inlineStr">
         <is>
-          <t>11174806</t>
+          <t>11177276</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>Wt26SSCC16Jac</t>
+          <t>Wt26SS20Jac</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
@@ -29971,17 +29971,17 @@
       </c>
       <c r="B846" s="7" t="inlineStr">
         <is>
-          <t>16558</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="C846" s="7" t="inlineStr">
         <is>
-          <t>11177275</t>
+          <t>11174791</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>Wt26SS20SV</t>
+          <t>Wt26ReusSV</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
@@ -30006,17 +30006,17 @@
       </c>
       <c r="B847" s="7" t="inlineStr">
         <is>
-          <t>16559</t>
+          <t>16573</t>
         </is>
       </c>
       <c r="C847" s="7" t="inlineStr">
         <is>
-          <t>11177276</t>
+          <t>11175037</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>Wt26SS20Jac</t>
+          <t>Wt26Tu16Charm</t>
         </is>
       </c>
       <c r="E847" t="inlineStr">
@@ -30041,17 +30041,17 @@
       </c>
       <c r="B848" s="7" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="C848" s="7" t="inlineStr">
         <is>
-          <t>11174791</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>Wt26ReusSV</t>
+          <t>Xm25ReuElev</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
@@ -30076,17 +30076,17 @@
       </c>
       <c r="B849" s="7" t="inlineStr">
         <is>
-          <t>16573</t>
+          <t>16589</t>
         </is>
       </c>
       <c r="C849" s="7" t="inlineStr">
         <is>
-          <t>11175037</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>Wt26Tu16Charm</t>
+          <t>Xm25ReuMike</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
@@ -30111,7 +30111,7 @@
       </c>
       <c r="B850" s="7" t="inlineStr">
         <is>
-          <t>16588</t>
+          <t>16590</t>
         </is>
       </c>
       <c r="C850" s="7" t="inlineStr">
@@ -30121,7 +30121,7 @@
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>Xm25ReuElev</t>
+          <t>Xm25Reus16ST</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
@@ -30146,7 +30146,7 @@
       </c>
       <c r="B851" s="7" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>16591</t>
         </is>
       </c>
       <c r="C851" s="7" t="inlineStr">
@@ -30156,7 +30156,7 @@
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>Xm25ReuMike</t>
+          <t>Xm25Reu24CCST</t>
         </is>
       </c>
       <c r="E851" t="inlineStr">
@@ -30181,7 +30181,7 @@
       </c>
       <c r="B852" s="7" t="inlineStr">
         <is>
-          <t>16590</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="C852" s="7" t="inlineStr">
@@ -30191,7 +30191,7 @@
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>Xm25Reus16ST</t>
+          <t>Xm25Reu2Hol</t>
         </is>
       </c>
       <c r="E852" t="inlineStr">
@@ -30216,7 +30216,7 @@
       </c>
       <c r="B853" s="7" t="inlineStr">
         <is>
-          <t>16591</t>
+          <t>16603</t>
         </is>
       </c>
       <c r="C853" s="7" t="inlineStr">
@@ -30226,7 +30226,7 @@
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>Xm25Reu24CCST</t>
+          <t>Xm25Reu1Hol</t>
         </is>
       </c>
       <c r="E853" t="inlineStr">
@@ -30251,17 +30251,17 @@
       </c>
       <c r="B854" s="7" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>16607</t>
         </is>
       </c>
       <c r="C854" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11177964</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>Xm25Reu2Hol</t>
+          <t>Sp26WTBLSS16Cher</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
@@ -30286,17 +30286,17 @@
       </c>
       <c r="B855" s="7" t="inlineStr">
         <is>
-          <t>16603</t>
+          <t>16608</t>
         </is>
       </c>
       <c r="C855" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11176612</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>Xm25Reu1Hol</t>
+          <t>Wt26CC15Blue</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
@@ -30321,17 +30321,17 @@
       </c>
       <c r="B856" s="7" t="inlineStr">
         <is>
-          <t>16607</t>
+          <t>16609</t>
         </is>
       </c>
       <c r="C856" s="7" t="inlineStr">
         <is>
-          <t>11177964</t>
+          <t>11176610</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>Sp26WTBLSS16Cher</t>
+          <t>Wt26TuSS16Duck</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
@@ -30356,17 +30356,17 @@
       </c>
       <c r="B857" s="7" t="inlineStr">
         <is>
-          <t>16608</t>
+          <t>16610</t>
         </is>
       </c>
       <c r="C857" s="7" t="inlineStr">
         <is>
-          <t>11176612</t>
+          <t>11179880</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>Wt26CC15Blue</t>
+          <t>SII26SS16Resort</t>
         </is>
       </c>
       <c r="E857" t="inlineStr">
@@ -30391,17 +30391,17 @@
       </c>
       <c r="B858" s="7" t="inlineStr">
         <is>
-          <t>16609</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="C858" s="7" t="inlineStr">
         <is>
-          <t>11176610</t>
+          <t>11177937</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>Wt26TuSS16Duck</t>
+          <t>Sp26CCup16Cherry</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
@@ -30426,17 +30426,17 @@
       </c>
       <c r="B859" s="7" t="inlineStr">
         <is>
-          <t>16610</t>
+          <t>16613</t>
         </is>
       </c>
       <c r="C859" s="7" t="inlineStr">
         <is>
-          <t>11179880</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
         <is>
-          <t>SII26SS16Resort</t>
+          <t>Xm25StopDermo</t>
         </is>
       </c>
       <c r="E859" t="inlineStr">
@@ -30461,17 +30461,17 @@
       </c>
       <c r="B860" s="7" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>16614</t>
         </is>
       </c>
       <c r="C860" s="7" t="inlineStr">
         <is>
-          <t>11177937</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
         <is>
-          <t>Sp26CCup16Cherry</t>
+          <t>Xm25StopHopp</t>
         </is>
       </c>
       <c r="E860" t="inlineStr">
@@ -30496,17 +30496,17 @@
       </c>
       <c r="B861" s="7" t="inlineStr">
         <is>
-          <t>16613</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="C861" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11176708</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>Xm25StopDermo</t>
+          <t>Wt26GlassCC16</t>
         </is>
       </c>
       <c r="E861" t="inlineStr">
@@ -30531,17 +30531,17 @@
       </c>
       <c r="B862" s="7" t="inlineStr">
         <is>
-          <t>16614</t>
+          <t>16659</t>
         </is>
       </c>
       <c r="C862" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11176714</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>Xm25StopHopp</t>
+          <t>Wt26SS16Vac</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
@@ -30566,17 +30566,17 @@
       </c>
       <c r="B863" s="7" t="inlineStr">
         <is>
-          <t>16658</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="C863" s="7" t="inlineStr">
         <is>
-          <t>11176708</t>
+          <t>11176719</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>Wt26GlassCC16</t>
+          <t>Wt26SSCC24CarryL</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
@@ -30601,17 +30601,17 @@
       </c>
       <c r="B864" s="7" t="inlineStr">
         <is>
-          <t>16659</t>
+          <t>16661</t>
         </is>
       </c>
       <c r="C864" s="7" t="inlineStr">
         <is>
-          <t>11176714</t>
+          <t>11176720</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>Wt26SS16Vac</t>
+          <t>Wt26SSCC30Togo</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
@@ -30636,17 +30636,17 @@
       </c>
       <c r="B865" s="7" t="inlineStr">
         <is>
-          <t>16660</t>
+          <t>16662</t>
         </is>
       </c>
       <c r="C865" s="7" t="inlineStr">
         <is>
-          <t>11176719</t>
+          <t>11176721</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>Wt26SSCC24CarryL</t>
+          <t>Sp26Stan30Purp</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
@@ -30671,17 +30671,17 @@
       </c>
       <c r="B866" s="7" t="inlineStr">
         <is>
-          <t>16661</t>
+          <t>16663</t>
         </is>
       </c>
       <c r="C866" s="7" t="inlineStr">
         <is>
-          <t>11176720</t>
+          <t>11176699</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>Wt26SSCC30Togo</t>
+          <t>Sp26Mug14Rabbit</t>
         </is>
       </c>
       <c r="E866" t="inlineStr">
@@ -30706,17 +30706,17 @@
       </c>
       <c r="B867" s="7" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>16665</t>
         </is>
       </c>
       <c r="C867" s="7" t="inlineStr">
         <is>
-          <t>11176721</t>
+          <t>11176701</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>Sp26Stan30Purp</t>
+          <t>Sp26CC216Rabbit</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
@@ -30741,17 +30741,17 @@
       </c>
       <c r="B868" s="7" t="inlineStr">
         <is>
-          <t>16663</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C868" s="7" t="inlineStr">
         <is>
-          <t>11176699</t>
+          <t>11176702</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>Sp26Mug14Rabbit</t>
+          <t>Sp26Tu20Blue</t>
         </is>
       </c>
       <c r="E868" t="inlineStr">
@@ -30776,17 +30776,17 @@
       </c>
       <c r="B869" s="7" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="C869" s="7" t="inlineStr">
         <is>
-          <t>11176710</t>
+          <t>11176715</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>Sp26CC24Dome</t>
+          <t>Sp26SS16Rabbit</t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
@@ -30811,17 +30811,17 @@
       </c>
       <c r="B870" s="7" t="inlineStr">
         <is>
-          <t>16665</t>
+          <t>16669</t>
         </is>
       </c>
       <c r="C870" s="7" t="inlineStr">
         <is>
-          <t>11176701</t>
+          <t>11176711</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>Sp26CC216Rabbit</t>
+          <t>Sp26Gl18Mottled</t>
         </is>
       </c>
       <c r="E870" t="inlineStr">
@@ -30846,17 +30846,17 @@
       </c>
       <c r="B871" s="7" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="C871" s="7" t="inlineStr">
         <is>
-          <t>11176702</t>
+          <t>11176700</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
         <is>
-          <t>Sp26Tu20Blue</t>
+          <t>Sp26Tz14GlassC</t>
         </is>
       </c>
       <c r="E871" t="inlineStr">
@@ -30881,17 +30881,17 @@
       </c>
       <c r="B872" s="7" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>16671</t>
         </is>
       </c>
       <c r="C872" s="7" t="inlineStr">
         <is>
-          <t>11176715</t>
+          <t>11176717</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>Sp26SS16Rabbit</t>
+          <t>Sp26SS12Pink</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
@@ -30916,17 +30916,17 @@
       </c>
       <c r="B873" s="7" t="inlineStr">
         <is>
-          <t>16669</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="C873" s="7" t="inlineStr">
         <is>
-          <t>11176711</t>
+          <t>11176724</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>Sp26Gl18Mottled</t>
+          <t>Sp26CookieJP</t>
         </is>
       </c>
       <c r="E873" t="inlineStr">
@@ -30951,17 +30951,17 @@
       </c>
       <c r="B874" s="7" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>16673</t>
         </is>
       </c>
       <c r="C874" s="7" t="inlineStr">
         <is>
-          <t>11176700</t>
+          <t>11176703</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
         <is>
-          <t>Sp26Tz14GlassC</t>
+          <t>Sp26Tu16Cherry</t>
         </is>
       </c>
       <c r="E874" t="inlineStr">
@@ -30986,17 +30986,17 @@
       </c>
       <c r="B875" s="7" t="inlineStr">
         <is>
-          <t>16671</t>
+          <t>16674</t>
         </is>
       </c>
       <c r="C875" s="7" t="inlineStr">
         <is>
-          <t>11176717</t>
+          <t>11176704</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
         <is>
-          <t>Sp26SS12Pink</t>
+          <t>Sp26CC16Prism</t>
         </is>
       </c>
       <c r="E875" t="inlineStr">
@@ -31021,17 +31021,17 @@
       </c>
       <c r="B876" s="7" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="C876" s="7" t="inlineStr">
         <is>
-          <t>11176724</t>
+          <t>11176722</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>Sp26CookieJP</t>
+          <t>Sp26SSCC24Cherry</t>
         </is>
       </c>
       <c r="E876" t="inlineStr">
@@ -31056,17 +31056,17 @@
       </c>
       <c r="B877" s="7" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="C877" s="7" t="inlineStr">
         <is>
-          <t>11176703</t>
+          <t>11176718</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>Sp26Tu16Cherry</t>
+          <t>Sp26SS16Cherry</t>
         </is>
       </c>
       <c r="E877" t="inlineStr">
@@ -31091,17 +31091,17 @@
       </c>
       <c r="B878" s="7" t="inlineStr">
         <is>
-          <t>16674</t>
+          <t>16677</t>
         </is>
       </c>
       <c r="C878" s="7" t="inlineStr">
         <is>
-          <t>11176704</t>
+          <t>11176723</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>Sp26CC16Prism</t>
+          <t>Sp26SSVac40Cherr</t>
         </is>
       </c>
       <c r="E878" t="inlineStr">
@@ -31126,17 +31126,17 @@
       </c>
       <c r="B879" s="7" t="inlineStr">
         <is>
-          <t>16675</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="C879" s="7" t="inlineStr">
         <is>
-          <t>11176722</t>
+          <t>11176705</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>Sp26SSCC24Cherry</t>
+          <t>Sp26ReusTierra</t>
         </is>
       </c>
       <c r="E879" t="inlineStr">
@@ -31161,17 +31161,17 @@
       </c>
       <c r="B880" s="7" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>16679</t>
         </is>
       </c>
       <c r="C880" s="7" t="inlineStr">
         <is>
-          <t>11176718</t>
+          <t>11176712</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>Sp26SS16Cherry</t>
+          <t>Sp26CCReusTierra</t>
         </is>
       </c>
       <c r="E880" t="inlineStr">
@@ -31196,17 +31196,17 @@
       </c>
       <c r="B881" s="7" t="inlineStr">
         <is>
-          <t>16677</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="C881" s="7" t="inlineStr">
         <is>
-          <t>11176723</t>
+          <t>11177607</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>Sp26SSVac40Cherr</t>
+          <t>Wt26ReusSiren</t>
         </is>
       </c>
       <c r="E881" t="inlineStr">
@@ -31231,17 +31231,17 @@
       </c>
       <c r="B882" s="7" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="C882" s="7" t="inlineStr">
         <is>
-          <t>11176705</t>
+          <t>11176586</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
         <is>
-          <t>Sp26ReusTierra</t>
+          <t>SII26SSCC20Pony</t>
         </is>
       </c>
       <c r="E882" t="inlineStr">
@@ -31266,17 +31266,17 @@
       </c>
       <c r="B883" s="7" t="inlineStr">
         <is>
-          <t>16679</t>
+          <t>16720</t>
         </is>
       </c>
       <c r="C883" s="7" t="inlineStr">
         <is>
-          <t>11176712</t>
+          <t>11176587</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
         <is>
-          <t>Sp26CCReusTierra</t>
+          <t>SII26SSCC16Pony</t>
         </is>
       </c>
       <c r="E883" t="inlineStr">
@@ -31301,17 +31301,17 @@
       </c>
       <c r="B884" s="7" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="C884" s="7" t="inlineStr">
         <is>
-          <t>11177607</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
         <is>
-          <t>Wt26ReusSiren</t>
+          <t>Sp26SS16Under</t>
         </is>
       </c>
       <c r="E884" t="inlineStr">
@@ -31336,17 +31336,17 @@
       </c>
       <c r="B885" s="7" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>16729</t>
         </is>
       </c>
       <c r="C885" s="7" t="inlineStr">
         <is>
-          <t>11176586</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
         <is>
-          <t>SII26SSCC20Pony</t>
+          <t>Wt26ReusBear</t>
         </is>
       </c>
       <c r="E885" t="inlineStr">
@@ -31371,17 +31371,17 @@
       </c>
       <c r="B886" s="7" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="C886" s="7" t="inlineStr">
         <is>
-          <t>11176587</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
         <is>
-          <t>SII26SSCC16Pony</t>
+          <t>Wt26VasoPistache</t>
         </is>
       </c>
       <c r="E886" t="inlineStr">
@@ -31406,7 +31406,7 @@
       </c>
       <c r="B887" s="7" t="inlineStr">
         <is>
-          <t>16721</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="C887" s="7" t="inlineStr">
@@ -31416,7 +31416,7 @@
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>Sp26SS16Under</t>
+          <t>Wt26VasoFresa</t>
         </is>
       </c>
       <c r="E887" t="inlineStr">
@@ -31441,7 +31441,7 @@
       </c>
       <c r="B888" s="7" t="inlineStr">
         <is>
-          <t>16729</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="C888" s="7" t="inlineStr">
@@ -31451,7 +31451,7 @@
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>Wt26ReusBear</t>
+          <t>Wt26VasoJacaran</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
@@ -31476,7 +31476,7 @@
       </c>
       <c r="B889" s="7" t="inlineStr">
         <is>
-          <t>16769</t>
+          <t>16775</t>
         </is>
       </c>
       <c r="C889" s="7" t="inlineStr">
@@ -31486,7 +31486,7 @@
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>Wt26VasoPistache</t>
+          <t>Wt26LlaveroSV</t>
         </is>
       </c>
       <c r="E889" t="inlineStr">
@@ -31511,17 +31511,17 @@
       </c>
       <c r="B890" s="7" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="C890" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11179885</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>Wt26VasoFresa</t>
+          <t>SII26BTL20Resort</t>
         </is>
       </c>
       <c r="E890" t="inlineStr">
@@ -31546,17 +31546,17 @@
       </c>
       <c r="B891" s="7" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>16779</t>
         </is>
       </c>
       <c r="C891" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11176592</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
         <is>
-          <t>Wt26VasoJacaran</t>
+          <t>SII26SSTu12Pony</t>
         </is>
       </c>
       <c r="E891" t="inlineStr">
@@ -31581,7 +31581,7 @@
       </c>
       <c r="B892" s="7" t="inlineStr">
         <is>
-          <t>16775</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="C892" s="7" t="inlineStr">
@@ -31591,7 +31591,7 @@
       </c>
       <c r="D892" t="inlineStr">
         <is>
-          <t>Wt26LlaveroSV</t>
+          <t>Sp26WTBL19Under</t>
         </is>
       </c>
       <c r="E892" t="inlineStr">
@@ -31616,17 +31616,17 @@
       </c>
       <c r="B893" s="7" t="inlineStr">
         <is>
-          <t>16777</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="C893" s="7" t="inlineStr">
         <is>
-          <t>11179885</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
         <is>
-          <t>SII26BTL20Resort</t>
+          <t>Sp26Tu20Blossom</t>
         </is>
       </c>
       <c r="E893" t="inlineStr">
@@ -31651,17 +31651,17 @@
       </c>
       <c r="B894" s="7" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="C894" s="7" t="inlineStr">
         <is>
-          <t>11176592</t>
+          <t>11176597</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>SII26SSTu12Pony</t>
+          <t>SII26BearPony</t>
         </is>
       </c>
       <c r="E894" t="inlineStr">
@@ -31686,17 +31686,17 @@
       </c>
       <c r="B895" s="7" t="inlineStr">
         <is>
-          <t>16780</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="C895" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1176593</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>Sp26WTBL19Under</t>
+          <t>SII26BTL16Pony</t>
         </is>
       </c>
       <c r="E895" t="inlineStr">
@@ -31721,17 +31721,17 @@
       </c>
       <c r="B896" s="7" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="C896" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178952</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>Sp26Tu20Blossom</t>
+          <t>WC26SSCC24Grad</t>
         </is>
       </c>
       <c r="E896" t="inlineStr">
@@ -31756,17 +31756,17 @@
       </c>
       <c r="B897" s="7" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="C897" s="7" t="inlineStr">
         <is>
-          <t>11176597</t>
+          <t>11178953</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>SII26BearPony</t>
+          <t>Sp26SSCC24Oran</t>
         </is>
       </c>
       <c r="E897" t="inlineStr">
@@ -31791,17 +31791,17 @@
       </c>
       <c r="B898" s="7" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="C898" s="7" t="inlineStr">
         <is>
-          <t>1176593</t>
+          <t>11178954</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
         <is>
-          <t>SII26BTL16Pony</t>
+          <t>Sp26SSCC24CarryC</t>
         </is>
       </c>
       <c r="E898" t="inlineStr">
@@ -31826,17 +31826,17 @@
       </c>
       <c r="B899" s="7" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>16878</t>
         </is>
       </c>
       <c r="C899" s="7" t="inlineStr">
         <is>
-          <t>11178952</t>
+          <t>11178921</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>WC26SSCC24Grad</t>
+          <t>Sp26Tu16Orange</t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
@@ -31861,17 +31861,17 @@
       </c>
       <c r="B900" s="7" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="C900" s="7" t="inlineStr">
         <is>
-          <t>11178953</t>
+          <t>11178922</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>Sp26SSCC24Oran</t>
+          <t>WC26Tu16Flower</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
@@ -31896,17 +31896,17 @@
       </c>
       <c r="B901" s="7" t="inlineStr">
         <is>
-          <t>16877</t>
+          <t>16880</t>
         </is>
       </c>
       <c r="C901" s="7" t="inlineStr">
         <is>
-          <t>11178954</t>
+          <t>11178928</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>Sp26SSCC24CarryC</t>
+          <t>WC26CC24Road</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
@@ -31931,17 +31931,17 @@
       </c>
       <c r="B902" s="7" t="inlineStr">
         <is>
-          <t>16878</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="C902" s="7" t="inlineStr">
         <is>
-          <t>11178921</t>
+          <t>11178930</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>Sp26Tu16Orange</t>
+          <t>WC26CC24Pride</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
@@ -31966,17 +31966,17 @@
       </c>
       <c r="B903" s="7" t="inlineStr">
         <is>
-          <t>16879</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="C903" s="7" t="inlineStr">
         <is>
-          <t>11178922</t>
+          <t>11178964</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>WC26Tu16Flower</t>
+          <t>Sp26KeychainOr</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
@@ -32001,17 +32001,17 @@
       </c>
       <c r="B904" s="7" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="C904" s="7" t="inlineStr">
         <is>
-          <t>11178928</t>
+          <t>11178934</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>WC26CC24Road</t>
+          <t>SII26CC24GID</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
@@ -32036,17 +32036,17 @@
       </c>
       <c r="B905" s="7" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="C905" s="7" t="inlineStr">
         <is>
-          <t>11178930</t>
+          <t>11179003</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>WC26CC24Pride</t>
+          <t>Sp26CC24Teach</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
@@ -32071,17 +32071,17 @@
       </c>
       <c r="B906" s="7" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>16896</t>
         </is>
       </c>
       <c r="C906" s="7" t="inlineStr">
         <is>
-          <t>11178964</t>
+          <t>11178970</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>Sp26KeychainOr</t>
+          <t>Sp26SSCC16Band</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
@@ -32106,17 +32106,17 @@
       </c>
       <c r="B907" s="7" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>16897</t>
         </is>
       </c>
       <c r="C907" s="7" t="inlineStr">
         <is>
-          <t>11178934</t>
+          <t>11178959</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>SII26CC24GID</t>
+          <t>WC26CCSS24Puffy</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
@@ -32141,17 +32141,17 @@
       </c>
       <c r="B908" s="7" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>16898</t>
         </is>
       </c>
       <c r="C908" s="7" t="inlineStr">
         <is>
-          <t>11179003</t>
+          <t>11178938</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>Sp26CC24Teach</t>
+          <t>Sp26Tu16Mom</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
@@ -32176,17 +32176,17 @@
       </c>
       <c r="B909" s="7" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="C909" s="7" t="inlineStr">
         <is>
-          <t>11178970</t>
+          <t>11179004</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>Sp26SSCC16Band</t>
+          <t>Sp26Tu16Teach</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
@@ -32211,17 +32211,17 @@
       </c>
       <c r="B910" s="7" t="inlineStr">
         <is>
-          <t>16897</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="C910" s="7" t="inlineStr">
         <is>
-          <t>11178959</t>
+          <t>11178941</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>WC26CCSS24Puffy</t>
+          <t>SII26SS16Studded</t>
         </is>
       </c>
       <c r="E910" t="inlineStr">
@@ -32246,17 +32246,17 @@
       </c>
       <c r="B911" s="7" t="inlineStr">
         <is>
-          <t>16898</t>
+          <t>16901</t>
         </is>
       </c>
       <c r="C911" s="7" t="inlineStr">
         <is>
-          <t>11178938</t>
+          <t>11178937</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>Sp26Tu16Mom</t>
+          <t>WC26Mug12Stan</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
@@ -32281,17 +32281,17 @@
       </c>
       <c r="B912" s="7" t="inlineStr">
         <is>
-          <t>16899</t>
+          <t>16902</t>
         </is>
       </c>
       <c r="C912" s="7" t="inlineStr">
         <is>
-          <t>11179004</t>
+          <t>11178920</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>Sp26Tu16Teach</t>
+          <t>WC26Tu20Yellow</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
@@ -32316,17 +32316,17 @@
       </c>
       <c r="B913" s="7" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="C913" s="7" t="inlineStr">
         <is>
-          <t>11178941</t>
+          <t>11178926</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>SII26SS16Studded</t>
+          <t>Sp26CC24Or</t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
@@ -32351,17 +32351,17 @@
       </c>
       <c r="B914" s="7" t="inlineStr">
         <is>
-          <t>16901</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="C914" s="7" t="inlineStr">
         <is>
-          <t>11178937</t>
+          <t>11178965</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>WC26Mug12Stan</t>
+          <t>WC26ToteRoad</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
@@ -32386,17 +32386,17 @@
       </c>
       <c r="B915" s="7" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="C915" s="7" t="inlineStr">
         <is>
-          <t>11178920</t>
+          <t>11178966</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>WC26Tu20Yellow</t>
+          <t>WC26TotePride</t>
         </is>
       </c>
       <c r="E915" t="inlineStr">
@@ -32421,17 +32421,17 @@
       </c>
       <c r="B916" s="7" t="inlineStr">
         <is>
-          <t>16903</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="C916" s="7" t="inlineStr">
         <is>
-          <t>11178926</t>
+          <t>11179005</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>Sp26CC24Or</t>
+          <t>WC26SS30Pride</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
@@ -32456,17 +32456,17 @@
       </c>
       <c r="B917" s="7" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="C917" s="7" t="inlineStr">
         <is>
-          <t>11178965</t>
+          <t>11187369</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>WC26ToteRoad</t>
+          <t>WC26BearWC</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
@@ -32491,17 +32491,17 @@
       </c>
       <c r="B918" s="7" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>16909</t>
         </is>
       </c>
       <c r="C918" s="7" t="inlineStr">
         <is>
-          <t>11178966</t>
+          <t>11178944</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>WC26TotePride</t>
+          <t>WC26SS20BTL</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
@@ -32526,17 +32526,17 @@
       </c>
       <c r="B919" s="7" t="inlineStr">
         <is>
-          <t>16906</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="C919" s="7" t="inlineStr">
         <is>
-          <t>11179005</t>
+          <t>11178969</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>WC26SS30Pride</t>
+          <t>WC26SS16Pink</t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
@@ -32561,17 +32561,17 @@
       </c>
       <c r="B920" s="7" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>16911</t>
         </is>
       </c>
       <c r="C920" s="7" t="inlineStr">
         <is>
-          <t>11187369</t>
+          <t>11178971</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>WC26BearWC</t>
+          <t>WC26SS16Charm</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
@@ -32596,17 +32596,17 @@
       </c>
       <c r="B921" s="7" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>16912</t>
         </is>
       </c>
       <c r="C921" s="7" t="inlineStr">
         <is>
-          <t>11178944</t>
+          <t>11178949</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>WC26SS20BTL</t>
+          <t>WC26SS20Pull</t>
         </is>
       </c>
       <c r="E921" t="inlineStr">
@@ -32631,17 +32631,17 @@
       </c>
       <c r="B922" s="7" t="inlineStr">
         <is>
-          <t>16910</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="C922" s="7" t="inlineStr">
         <is>
-          <t>11178969</t>
+          <t>11178946</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>WC26SS16Pink</t>
+          <t>WC26SS20Twist</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
@@ -32666,17 +32666,17 @@
       </c>
       <c r="B923" s="7" t="inlineStr">
         <is>
-          <t>16911</t>
+          <t>16914</t>
         </is>
       </c>
       <c r="C923" s="7" t="inlineStr">
         <is>
-          <t>11178971</t>
+          <t>11178947</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>WC26SS16Charm</t>
+          <t>Sp26StanQuen20</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
@@ -32701,17 +32701,17 @@
       </c>
       <c r="B924" s="7" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>16915</t>
         </is>
       </c>
       <c r="C924" s="7" t="inlineStr">
         <is>
-          <t>11178949</t>
+          <t>11178948</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>WC26SS20Pull</t>
+          <t>WC26StanHand20</t>
         </is>
       </c>
       <c r="E924" t="inlineStr">
@@ -32736,17 +32736,17 @@
       </c>
       <c r="B925" s="7" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>16916</t>
         </is>
       </c>
       <c r="C925" s="7" t="inlineStr">
         <is>
-          <t>11178946</t>
+          <t>11178956</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>WC26SS20Twist</t>
+          <t>SII26Quencher30P</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
@@ -32771,17 +32771,17 @@
       </c>
       <c r="B926" s="7" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="C926" s="7" t="inlineStr">
         <is>
-          <t>11178947</t>
+          <t>11178972</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>Sp26StanQuen20</t>
+          <t>Sp26Vac16Stan</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
@@ -32806,17 +32806,17 @@
       </c>
       <c r="B927" s="7" t="inlineStr">
         <is>
-          <t>16915</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="C927" s="7" t="inlineStr">
         <is>
-          <t>11178948</t>
+          <t>11178943</t>
         </is>
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>WC26StanHand20</t>
+          <t>Sp26SS20Orange</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
@@ -32841,17 +32841,17 @@
       </c>
       <c r="B928" s="7" t="inlineStr">
         <is>
-          <t>16916</t>
+          <t>16919</t>
         </is>
       </c>
       <c r="C928" s="7" t="inlineStr">
         <is>
-          <t>11178956</t>
+          <t>11178957</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>SII26Quencher30P</t>
+          <t>WC26StanQuen30</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
@@ -32876,17 +32876,17 @@
       </c>
       <c r="B929" s="7" t="inlineStr">
         <is>
-          <t>16917</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="C929" s="7" t="inlineStr">
         <is>
-          <t>11178972</t>
+          <t>11178935</t>
         </is>
       </c>
       <c r="D929" t="inlineStr">
         <is>
-          <t>Sp26Vac16Stan</t>
+          <t>SII26Tu10Gam</t>
         </is>
       </c>
       <c r="E929" t="inlineStr">
@@ -32911,17 +32911,17 @@
       </c>
       <c r="B930" s="7" t="inlineStr">
         <is>
-          <t>16918</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="C930" s="7" t="inlineStr">
         <is>
-          <t>11178943</t>
+          <t>11178917</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t>Sp26SS20Orange</t>
+          <t>WC26DW12Oran</t>
         </is>
       </c>
       <c r="E930" t="inlineStr">
@@ -32946,17 +32946,17 @@
       </c>
       <c r="B931" s="7" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>16923</t>
         </is>
       </c>
       <c r="C931" s="7" t="inlineStr">
         <is>
-          <t>11178957</t>
+          <t>11178918</t>
         </is>
       </c>
       <c r="D931" t="inlineStr">
         <is>
-          <t>WC26StanQuen30</t>
+          <t>WC26Gl20Silicone</t>
         </is>
       </c>
       <c r="E931" t="inlineStr">
@@ -32981,17 +32981,17 @@
       </c>
       <c r="B932" s="7" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>16924</t>
         </is>
       </c>
       <c r="C932" s="7" t="inlineStr">
         <is>
-          <t>11178935</t>
+          <t>11178945</t>
         </is>
       </c>
       <c r="D932" t="inlineStr">
         <is>
-          <t>SII26Tu10Gam</t>
+          <t>WC26Stan20IceF</t>
         </is>
       </c>
       <c r="E932" t="inlineStr">
@@ -33016,17 +33016,17 @@
       </c>
       <c r="B933" s="7" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="C933" s="7" t="inlineStr">
         <is>
-          <t>11178917</t>
+          <t>11178973</t>
         </is>
       </c>
       <c r="D933" t="inlineStr">
         <is>
-          <t>WC26DW12Oran</t>
+          <t>WC26SS16Lid</t>
         </is>
       </c>
       <c r="E933" t="inlineStr">
@@ -33051,17 +33051,17 @@
       </c>
       <c r="B934" s="7" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="C934" s="7" t="inlineStr">
         <is>
-          <t>11178919</t>
+          <t>11187370</t>
         </is>
       </c>
       <c r="D934" t="inlineStr">
         <is>
-          <t>Sp26Mug14Mom</t>
+          <t>WC26SS16Black</t>
         </is>
       </c>
       <c r="E934" t="inlineStr">
@@ -33086,17 +33086,17 @@
       </c>
       <c r="B935" s="7" t="inlineStr">
         <is>
-          <t>16923</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="C935" s="7" t="inlineStr">
         <is>
-          <t>11178918</t>
+          <t>11187372</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
         <is>
-          <t>WC26Gl20Silicone</t>
+          <t>WC26Tu24DW</t>
         </is>
       </c>
       <c r="E935" t="inlineStr">
@@ -33121,17 +33121,13 @@
       </c>
       <c r="B936" s="7" t="inlineStr">
         <is>
-          <t>16924</t>
-        </is>
-      </c>
-      <c r="C936" s="7" t="inlineStr">
-        <is>
-          <t>11178945</t>
-        </is>
-      </c>
+          <t>16971</t>
+        </is>
+      </c>
+      <c r="C936" s="7" t="inlineStr"/>
       <c r="D936" t="inlineStr">
         <is>
-          <t>WC26Stan20IceF</t>
+          <t>WC26BearMex</t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
@@ -33156,17 +33152,17 @@
       </c>
       <c r="B937" s="7" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>16978</t>
         </is>
       </c>
       <c r="C937" s="7" t="inlineStr">
         <is>
-          <t>11178973</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>WC26SS16Lid</t>
+          <t>WC26LlaveroB</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
@@ -33186,12 +33182,12 @@
     <row r="938" ht="24" customHeight="1">
       <c r="A938" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B938" s="7" t="inlineStr">
         <is>
-          <t>16955</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="C938" s="7" t="inlineStr">
@@ -33201,7 +33197,7 @@
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>WC26NESBX</t>
+          <t>Sp26NEBlack</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
@@ -33214,29 +33210,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G938" t="inlineStr"/>
-      <c r="H938" t="inlineStr"/>
-      <c r="I938" t="inlineStr"/>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>lote-01/16531.jpeg</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="939" ht="24" customHeight="1">
       <c r="A939" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B939" s="7" t="inlineStr">
         <is>
-          <t>16958</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="C939" s="7" t="inlineStr">
         <is>
-          <t>11187370</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
         <is>
-          <t>WC26SS16Black</t>
+          <t>Sp26NECrossB</t>
         </is>
       </c>
       <c r="E939" t="inlineStr">
@@ -33249,29 +33257,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G939" t="inlineStr"/>
-      <c r="H939" t="inlineStr"/>
-      <c r="I939" t="inlineStr"/>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>lote-01/16532.jpeg</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="940" ht="24" customHeight="1">
       <c r="A940" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B940" s="7" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="C940" s="7" t="inlineStr">
         <is>
-          <t>11187372</t>
+          <t>11170187</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
         <is>
-          <t>WC26Tu24DW</t>
+          <t>ToteBag MxPais</t>
         </is>
       </c>
       <c r="E940" t="inlineStr">
@@ -33284,25 +33304,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G940" t="inlineStr"/>
-      <c r="H940" t="inlineStr"/>
-      <c r="I940" t="inlineStr"/>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>lote-01/011170187.jpeg</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="941" ht="24" customHeight="1">
       <c r="A941" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B941" s="7" t="inlineStr">
         <is>
-          <t>16971</t>
-        </is>
-      </c>
-      <c r="C941" s="7" t="inlineStr"/>
+          <t>16643</t>
+        </is>
+      </c>
+      <c r="C941" s="7" t="inlineStr">
+        <is>
+          <t>11170102</t>
+        </is>
+      </c>
       <c r="D941" t="inlineStr">
         <is>
-          <t>WC26BearMex</t>
+          <t>DiscoveryCDMX</t>
         </is>
       </c>
       <c r="E941" t="inlineStr">
@@ -33315,29 +33351,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G941" t="inlineStr"/>
-      <c r="H941" t="inlineStr"/>
-      <c r="I941" t="inlineStr"/>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>lote-01/011170102.jpeg</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="942" ht="24" customHeight="1">
       <c r="A942" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B942" s="7" t="inlineStr">
         <is>
-          <t>16978</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="C942" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11176710</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t>WC26LlaveroB</t>
+          <t>Sp26CC24Dome</t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
@@ -33350,9 +33398,21 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G942" t="inlineStr"/>
-      <c r="H942" t="inlineStr"/>
-      <c r="I942" t="inlineStr"/>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>lote-01/011176710.jpeg</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="943" ht="24" customHeight="1">
       <c r="A943" t="inlineStr">
@@ -33362,17 +33422,17 @@
       </c>
       <c r="B943" s="7" t="inlineStr">
         <is>
-          <t>16995</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="C943" s="7" t="inlineStr">
         <is>
-          <t>11186650</t>
+          <t>11170174</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
         <is>
-          <t>SII26SS16Pleat</t>
+          <t>DiscCC24MxPais</t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
@@ -33387,7 +33447,7 @@
       </c>
       <c r="G943" t="inlineStr">
         <is>
-          <t>lote-01/11186650.jpg</t>
+          <t>lote-01/011170174.jpeg</t>
         </is>
       </c>
       <c r="H943" t="inlineStr">
@@ -33409,17 +33469,17 @@
       </c>
       <c r="B944" s="7" t="inlineStr">
         <is>
-          <t>16997</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="C944" s="7" t="inlineStr">
         <is>
-          <t>11186646</t>
+          <t>11170147</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t>SII26SS12Charm</t>
+          <t>Disc2ozMxPais</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
@@ -33434,7 +33494,7 @@
       </c>
       <c r="G944" t="inlineStr">
         <is>
-          <t>lote-01/11186646.jpg</t>
+          <t>lote-01/011170147.jpeg</t>
         </is>
       </c>
       <c r="H944" t="inlineStr">
@@ -33456,17 +33516,17 @@
       </c>
       <c r="B945" s="7" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="C945" s="7" t="inlineStr">
         <is>
-          <t>11186658</t>
+          <t>11170149</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>SII26SS20Hand</t>
+          <t>Disc2ozCDMX</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
@@ -33481,7 +33541,7 @@
       </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t>lote-01/11186658.jpg</t>
+          <t>lote-01/011170149.jpeg</t>
         </is>
       </c>
       <c r="H945" t="inlineStr">
@@ -33503,17 +33563,17 @@
       </c>
       <c r="B946" s="7" t="inlineStr">
         <is>
-          <t>16999</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="C946" s="7" t="inlineStr">
         <is>
-          <t>11186659</t>
+          <t>11178919</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>SII26BTLSS20</t>
+          <t>Sp26Mug14Mom</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
@@ -33528,7 +33588,7 @@
       </c>
       <c r="G946" t="inlineStr">
         <is>
-          <t>lote-01/11186659.jpg</t>
+          <t>lote-01/011178919.jpeg</t>
         </is>
       </c>
       <c r="H946" t="inlineStr">
@@ -33545,12 +33605,12 @@
     <row r="947" ht="24" customHeight="1">
       <c r="A947" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B947" s="7" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>16955</t>
         </is>
       </c>
       <c r="C947" s="7" t="inlineStr">
@@ -33560,7 +33620,7 @@
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>ESS Chemex 15oz</t>
+          <t>WC26NESBX</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
@@ -33570,32 +33630,44 @@
       </c>
       <c r="F947" t="inlineStr">
         <is>
-          <t>SECUNDARIO</t>
-        </is>
-      </c>
-      <c r="G947" t="inlineStr"/>
-      <c r="H947" t="inlineStr"/>
-      <c r="I947" t="inlineStr"/>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>lote-01/16955.jpeg</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="948" ht="24" customHeight="1">
       <c r="A948" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B948" s="7" t="inlineStr">
         <is>
-          <t>12480</t>
+          <t>16995</t>
         </is>
       </c>
       <c r="C948" s="7" t="inlineStr">
         <is>
-          <t>11103799</t>
+          <t>11186650</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
         <is>
-          <t>12480 Cafetera Green CJ/1 PZA</t>
+          <t>SII26SS16Pleat</t>
         </is>
       </c>
       <c r="E948" t="inlineStr">
@@ -33605,32 +33677,44 @@
       </c>
       <c r="F948" t="inlineStr">
         <is>
-          <t>SECUNDARIO</t>
-        </is>
-      </c>
-      <c r="G948" t="inlineStr"/>
-      <c r="H948" t="inlineStr"/>
-      <c r="I948" t="inlineStr"/>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>lote-01/11186650.jpg</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="949" ht="24" customHeight="1">
       <c r="A949" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B949" s="7" t="inlineStr">
         <is>
-          <t>12642</t>
+          <t>16997</t>
         </is>
       </c>
       <c r="C949" s="7" t="inlineStr">
         <is>
-          <t>11090466</t>
+          <t>11186646</t>
         </is>
       </c>
       <c r="D949" t="inlineStr">
         <is>
-          <t>CAFETERA BLACK TRITAN BEAKER 8TZ</t>
+          <t>SII26SS12Charm</t>
         </is>
       </c>
       <c r="E949" t="inlineStr">
@@ -33640,32 +33724,44 @@
       </c>
       <c r="F949" t="inlineStr">
         <is>
-          <t>SECUNDARIO</t>
-        </is>
-      </c>
-      <c r="G949" t="inlineStr"/>
-      <c r="H949" t="inlineStr"/>
-      <c r="I949" t="inlineStr"/>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>lote-01/11186646.jpg</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="950" ht="24" customHeight="1">
       <c r="A950" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B950" s="7" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="C950" s="7" t="inlineStr">
         <is>
-          <t>11129870</t>
+          <t>11186658</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
         <is>
-          <t>COR23 SSCC24 Sir</t>
+          <t>SII26SS20Hand</t>
         </is>
       </c>
       <c r="E950" t="inlineStr">
@@ -33675,32 +33771,44 @@
       </c>
       <c r="F950" t="inlineStr">
         <is>
-          <t>SECUNDARIO</t>
-        </is>
-      </c>
-      <c r="G950" t="inlineStr"/>
-      <c r="H950" t="inlineStr"/>
-      <c r="I950" t="inlineStr"/>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>lote-01/11186658.jpg</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="951" ht="24" customHeight="1">
       <c r="A951" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B951" s="7" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="C951" s="7" t="inlineStr">
         <is>
-          <t>11129720</t>
+          <t>11186659</t>
         </is>
       </c>
       <c r="D951" t="inlineStr">
         <is>
-          <t>COR23 CC16 TinST</t>
+          <t>SII26BTLSS20</t>
         </is>
       </c>
       <c r="E951" t="inlineStr">
@@ -33710,12 +33818,24 @@
       </c>
       <c r="F951" t="inlineStr">
         <is>
-          <t>SECUNDARIO</t>
-        </is>
-      </c>
-      <c r="G951" t="inlineStr"/>
-      <c r="H951" t="inlineStr"/>
-      <c r="I951" t="inlineStr"/>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>lote-01/11186659.jpg</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="952" ht="24" customHeight="1">
       <c r="A952" t="inlineStr">
@@ -33725,17 +33845,17 @@
       </c>
       <c r="B952" s="7" t="inlineStr">
         <is>
-          <t>14781</t>
+          <t>9616</t>
         </is>
       </c>
       <c r="C952" s="7" t="inlineStr">
         <is>
-          <t>11129821</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D952" t="inlineStr">
         <is>
-          <t>COR23CC16 irid</t>
+          <t>ESS Chemex 15oz</t>
         </is>
       </c>
       <c r="E952" t="inlineStr">
@@ -33760,17 +33880,17 @@
       </c>
       <c r="B953" s="7" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>12480</t>
         </is>
       </c>
       <c r="C953" s="7" t="inlineStr">
         <is>
-          <t>11129797</t>
+          <t>11103799</t>
         </is>
       </c>
       <c r="D953" t="inlineStr">
         <is>
-          <t>COR23 CC16 Shell</t>
+          <t>12480 Cafetera Green CJ/1 PZA</t>
         </is>
       </c>
       <c r="E953" t="inlineStr">
@@ -33795,17 +33915,17 @@
       </c>
       <c r="B954" s="7" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>12642</t>
         </is>
       </c>
       <c r="C954" s="7" t="inlineStr">
         <is>
-          <t>11129846</t>
+          <t>11090466</t>
         </is>
       </c>
       <c r="D954" t="inlineStr">
         <is>
-          <t>COR23 KeyR TinST</t>
+          <t>CAFETERA BLACK TRITAN BEAKER 8TZ</t>
         </is>
       </c>
       <c r="E954" t="inlineStr">
@@ -33830,17 +33950,17 @@
       </c>
       <c r="B955" s="7" t="inlineStr">
         <is>
-          <t>14919</t>
+          <t>14779</t>
         </is>
       </c>
       <c r="C955" s="7" t="inlineStr">
         <is>
-          <t>11141068</t>
+          <t>11129870</t>
         </is>
       </c>
       <c r="D955" t="inlineStr">
         <is>
-          <t>COR23 Tu16 Siren</t>
+          <t>COR23 SSCC24 Sir</t>
         </is>
       </c>
       <c r="E955" t="inlineStr">
@@ -33865,17 +33985,17 @@
       </c>
       <c r="B956" s="7" t="inlineStr">
         <is>
-          <t>15996</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="C956" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11129720</t>
         </is>
       </c>
       <c r="D956" t="inlineStr">
         <is>
-          <t>COR25CoffeeBean</t>
+          <t>COR23 CC16 TinST</t>
         </is>
       </c>
       <c r="E956" t="inlineStr">
@@ -33900,17 +34020,17 @@
       </c>
       <c r="B957" s="7" t="inlineStr">
         <is>
-          <t>16121</t>
+          <t>14781</t>
         </is>
       </c>
       <c r="C957" s="7" t="inlineStr">
         <is>
-          <t>11164269</t>
+          <t>11129821</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
         <is>
-          <t>SI25Tu16Charm</t>
+          <t>COR23CC16 irid</t>
         </is>
       </c>
       <c r="E957" t="inlineStr">
@@ -33935,17 +34055,17 @@
       </c>
       <c r="B958" s="7" t="inlineStr">
         <is>
-          <t>16127</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="C958" s="7" t="inlineStr">
         <is>
-          <t>11164289</t>
+          <t>11129797</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
         <is>
-          <t>Fl25SSTu16B</t>
+          <t>COR23 CC16 Shell</t>
         </is>
       </c>
       <c r="E958" t="inlineStr">
@@ -33970,17 +34090,17 @@
       </c>
       <c r="B959" s="7" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="C959" s="7" t="inlineStr">
         <is>
-          <t>11164299</t>
+          <t>11129846</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
         <is>
-          <t>SI25SS20Zoo</t>
+          <t>COR23 KeyR TinST</t>
         </is>
       </c>
       <c r="E959" t="inlineStr">
@@ -34005,17 +34125,17 @@
       </c>
       <c r="B960" s="7" t="inlineStr">
         <is>
-          <t>16148</t>
+          <t>14919</t>
         </is>
       </c>
       <c r="C960" s="7" t="inlineStr">
         <is>
-          <t>11164315</t>
+          <t>11141068</t>
         </is>
       </c>
       <c r="D960" t="inlineStr">
         <is>
-          <t>SII25Iceflow30</t>
+          <t>COR23 Tu16 Siren</t>
         </is>
       </c>
       <c r="E960" t="inlineStr">
@@ -34040,17 +34160,17 @@
       </c>
       <c r="B961" s="7" t="inlineStr">
         <is>
-          <t>16153</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="C961" s="7" t="inlineStr">
         <is>
-          <t>11164278</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D961" t="inlineStr">
         <is>
-          <t>SI25BTL24Zoo</t>
+          <t>COR25CoffeeBean</t>
         </is>
       </c>
       <c r="E961" t="inlineStr">
@@ -34075,17 +34195,17 @@
       </c>
       <c r="B962" s="7" t="inlineStr">
         <is>
-          <t>16158</t>
+          <t>16121</t>
         </is>
       </c>
       <c r="C962" s="7" t="inlineStr">
         <is>
-          <t>11164260</t>
+          <t>11164269</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
         <is>
-          <t>Fl25Mug14Bar</t>
+          <t>SI25Tu16Charm</t>
         </is>
       </c>
       <c r="E962" t="inlineStr">
@@ -34110,17 +34230,17 @@
       </c>
       <c r="B963" s="7" t="inlineStr">
         <is>
-          <t>16159</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="C963" s="7" t="inlineStr">
         <is>
-          <t>11164261</t>
+          <t>11164289</t>
         </is>
       </c>
       <c r="D963" t="inlineStr">
         <is>
-          <t>SI25Tz14Eleph</t>
+          <t>Fl25SSTu16B</t>
         </is>
       </c>
       <c r="E963" t="inlineStr">
@@ -34145,17 +34265,17 @@
       </c>
       <c r="B964" s="7" t="inlineStr">
         <is>
-          <t>16160</t>
+          <t>16130</t>
         </is>
       </c>
       <c r="C964" s="7" t="inlineStr">
         <is>
-          <t>11164262</t>
+          <t>11164299</t>
         </is>
       </c>
       <c r="D964" t="inlineStr">
         <is>
-          <t>SI25Mug14Mothers</t>
+          <t>SI25SS20Zoo</t>
         </is>
       </c>
       <c r="E964" t="inlineStr">
@@ -34180,17 +34300,17 @@
       </c>
       <c r="B965" s="7" t="inlineStr">
         <is>
-          <t>16161</t>
+          <t>16148</t>
         </is>
       </c>
       <c r="C965" s="7" t="inlineStr">
         <is>
-          <t>11164263</t>
+          <t>11164315</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
         <is>
-          <t>SI25DW12Mothers</t>
+          <t>SII25Iceflow30</t>
         </is>
       </c>
       <c r="E965" t="inlineStr">
@@ -34215,17 +34335,17 @@
       </c>
       <c r="B966" s="7" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>16153</t>
         </is>
       </c>
       <c r="C966" s="7" t="inlineStr">
         <is>
-          <t>11164291</t>
+          <t>11164278</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>SII25SS16Pearl</t>
+          <t>SI25BTL24Zoo</t>
         </is>
       </c>
       <c r="E966" t="inlineStr">
@@ -34250,17 +34370,17 @@
       </c>
       <c r="B967" s="7" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>16158</t>
         </is>
       </c>
       <c r="C967" s="7" t="inlineStr">
         <is>
-          <t>11164296</t>
+          <t>11164260</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
         <is>
-          <t>Fl25Tu20Silicon</t>
+          <t>Fl25Mug14Bar</t>
         </is>
       </c>
       <c r="E967" t="inlineStr">
@@ -34285,17 +34405,17 @@
       </c>
       <c r="B968" s="7" t="inlineStr">
         <is>
-          <t>16169</t>
+          <t>16159</t>
         </is>
       </c>
       <c r="C968" s="7" t="inlineStr">
         <is>
-          <t>11164301</t>
+          <t>11164261</t>
         </is>
       </c>
       <c r="D968" t="inlineStr">
         <is>
-          <t>SI25SSBTLZoo</t>
+          <t>SI25Tz14Eleph</t>
         </is>
       </c>
       <c r="E968" t="inlineStr">
@@ -34320,17 +34440,17 @@
       </c>
       <c r="B969" s="7" t="inlineStr">
         <is>
-          <t>16173</t>
+          <t>16160</t>
         </is>
       </c>
       <c r="C969" s="7" t="inlineStr">
         <is>
-          <t>11164308</t>
+          <t>11164262</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
         <is>
-          <t>SII25StanOrange</t>
+          <t>SI25Mug14Mothers</t>
         </is>
       </c>
       <c r="E969" t="inlineStr">
@@ -34355,17 +34475,17 @@
       </c>
       <c r="B970" s="7" t="inlineStr">
         <is>
-          <t>16177</t>
+          <t>16161</t>
         </is>
       </c>
       <c r="C970" s="7" t="inlineStr">
         <is>
-          <t>11164318</t>
+          <t>11164263</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
         <is>
-          <t>SII25KeyChain</t>
+          <t>SI25DW12Mothers</t>
         </is>
       </c>
       <c r="E970" t="inlineStr">
@@ -34390,17 +34510,17 @@
       </c>
       <c r="B971" s="7" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>16166</t>
         </is>
       </c>
       <c r="C971" s="7" t="inlineStr">
         <is>
-          <t>11167151</t>
+          <t>11164291</t>
         </is>
       </c>
       <c r="D971" t="inlineStr">
         <is>
-          <t>SII25CC24FRLenco</t>
+          <t>SII25SS16Pearl</t>
         </is>
       </c>
       <c r="E971" t="inlineStr">
@@ -34425,17 +34545,17 @@
       </c>
       <c r="B972" s="7" t="inlineStr">
         <is>
-          <t>16183</t>
+          <t>16167</t>
         </is>
       </c>
       <c r="C972" s="7" t="inlineStr">
         <is>
-          <t>11167153</t>
+          <t>11164296</t>
         </is>
       </c>
       <c r="D972" t="inlineStr">
         <is>
-          <t>SII25BTL20FarmR</t>
+          <t>Fl25Tu20Silicon</t>
         </is>
       </c>
       <c r="E972" t="inlineStr">
@@ -34460,17 +34580,17 @@
       </c>
       <c r="B973" s="7" t="inlineStr">
         <is>
-          <t>16184</t>
+          <t>16169</t>
         </is>
       </c>
       <c r="C973" s="7" t="inlineStr">
         <is>
-          <t>11167154</t>
+          <t>11164301</t>
         </is>
       </c>
       <c r="D973" t="inlineStr">
         <is>
-          <t>SII25Mug14FarmR</t>
+          <t>SI25SSBTLZoo</t>
         </is>
       </c>
       <c r="E973" t="inlineStr">
@@ -34495,17 +34615,17 @@
       </c>
       <c r="B974" s="7" t="inlineStr">
         <is>
-          <t>16225</t>
+          <t>16173</t>
         </is>
       </c>
       <c r="C974" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11164308</t>
         </is>
       </c>
       <c r="D974" t="inlineStr">
         <is>
-          <t>Fl25ReusDDM</t>
+          <t>SII25StanOrange</t>
         </is>
       </c>
       <c r="E974" t="inlineStr">
@@ -34530,17 +34650,17 @@
       </c>
       <c r="B975" s="7" t="inlineStr">
         <is>
-          <t>16259</t>
+          <t>16177</t>
         </is>
       </c>
       <c r="C975" s="7" t="inlineStr">
         <is>
-          <t>11171525</t>
+          <t>11164318</t>
         </is>
       </c>
       <c r="D975" t="inlineStr">
         <is>
-          <t>SII25CCDomeBday</t>
+          <t>SII25KeyChain</t>
         </is>
       </c>
       <c r="E975" t="inlineStr">
@@ -34565,17 +34685,17 @@
       </c>
       <c r="B976" s="7" t="inlineStr">
         <is>
-          <t>16260</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="C976" s="7" t="inlineStr">
         <is>
-          <t>11171526</t>
+          <t>11167151</t>
         </is>
       </c>
       <c r="D976" t="inlineStr">
         <is>
-          <t>SII25CCLlavero</t>
+          <t>SII25CC24FRLenco</t>
         </is>
       </c>
       <c r="E976" t="inlineStr">
@@ -34600,17 +34720,17 @@
       </c>
       <c r="B977" s="7" t="inlineStr">
         <is>
-          <t>16289</t>
+          <t>16183</t>
         </is>
       </c>
       <c r="C977" s="7" t="inlineStr">
         <is>
-          <t>11169485</t>
+          <t>11167153</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
         <is>
-          <t>Fl25PPFood</t>
+          <t>SII25BTL20FarmR</t>
         </is>
       </c>
       <c r="E977" t="inlineStr">
@@ -34635,17 +34755,17 @@
       </c>
       <c r="B978" s="7" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="C978" s="7" t="inlineStr">
         <is>
-          <t>11169422</t>
+          <t>11167154</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
         <is>
-          <t>Fl25Mug14Bear</t>
+          <t>SII25Mug14FarmR</t>
         </is>
       </c>
       <c r="E978" t="inlineStr">
@@ -34670,17 +34790,17 @@
       </c>
       <c r="B979" s="7" t="inlineStr">
         <is>
-          <t>16316</t>
+          <t>16225</t>
         </is>
       </c>
       <c r="C979" s="7" t="inlineStr">
         <is>
-          <t>11169425</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t>Fl25Mug14Calav</t>
+          <t>Fl25ReusDDM</t>
         </is>
       </c>
       <c r="E979" t="inlineStr">
@@ -34705,17 +34825,17 @@
       </c>
       <c r="B980" s="7" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>16259</t>
         </is>
       </c>
       <c r="C980" s="7" t="inlineStr">
         <is>
-          <t>11169480</t>
+          <t>11171525</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t>Fl25StanIceF</t>
+          <t>SII25CCDomeBday</t>
         </is>
       </c>
       <c r="E980" t="inlineStr">
@@ -34740,17 +34860,17 @@
       </c>
       <c r="B981" s="7" t="inlineStr">
         <is>
-          <t>16325</t>
+          <t>16260</t>
         </is>
       </c>
       <c r="C981" s="7" t="inlineStr">
         <is>
-          <t>11169484</t>
+          <t>11171526</t>
         </is>
       </c>
       <c r="D981" t="inlineStr">
         <is>
-          <t>Fl25CookieJar</t>
+          <t>SII25CCLlavero</t>
         </is>
       </c>
       <c r="E981" t="inlineStr">
@@ -34775,17 +34895,17 @@
       </c>
       <c r="B982" s="7" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>16289</t>
         </is>
       </c>
       <c r="C982" s="7" t="inlineStr">
         <is>
-          <t>Dinámica especial</t>
+          <t>11169485</t>
         </is>
       </c>
       <c r="D982" t="inlineStr">
         <is>
-          <t>SII25ReusPSL</t>
+          <t>Fl25PPFood</t>
         </is>
       </c>
       <c r="E982" t="inlineStr">
@@ -34810,17 +34930,17 @@
       </c>
       <c r="B983" s="7" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="C983" s="7" t="inlineStr">
         <is>
-          <t>11173272</t>
+          <t>11169422</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
         <is>
-          <t>Xm25Tu12Lux</t>
+          <t>Fl25Mug14Bear</t>
         </is>
       </c>
       <c r="E983" t="inlineStr">
@@ -34845,17 +34965,17 @@
       </c>
       <c r="B984" s="7" t="inlineStr">
         <is>
-          <t>16460</t>
+          <t>16316</t>
         </is>
       </c>
       <c r="C984" s="7" t="inlineStr">
         <is>
-          <t>11172987</t>
+          <t>11169425</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
         <is>
-          <t>Xm25SS16Knit</t>
+          <t>Fl25Mug14Calav</t>
         </is>
       </c>
       <c r="E984" t="inlineStr">
@@ -34880,17 +35000,17 @@
       </c>
       <c r="B985" s="7" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>16324</t>
         </is>
       </c>
       <c r="C985" s="7" t="inlineStr">
         <is>
-          <t>11173043</t>
+          <t>11169480</t>
         </is>
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t>Xm25GlassBear</t>
+          <t>Fl25StanIceF</t>
         </is>
       </c>
       <c r="E985" t="inlineStr">
@@ -34915,17 +35035,17 @@
       </c>
       <c r="B986" s="7" t="inlineStr">
         <is>
-          <t>16542</t>
+          <t>16325</t>
         </is>
       </c>
       <c r="C986" s="7" t="inlineStr">
         <is>
-          <t>11174790</t>
+          <t>11169484</t>
         </is>
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t>Wt26Tu16Green</t>
+          <t>Fl25CookieJar</t>
         </is>
       </c>
       <c r="E986" t="inlineStr">
@@ -34950,17 +35070,17 @@
       </c>
       <c r="B987" s="7" t="inlineStr">
         <is>
-          <t>16668</t>
+          <t>16415</t>
         </is>
       </c>
       <c r="C987" s="7" t="inlineStr">
         <is>
-          <t>11176716</t>
+          <t>Dinámica especial</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t>Sp26StanYellow20</t>
+          <t>SII25ReusPSL</t>
         </is>
       </c>
       <c r="E987" t="inlineStr">
@@ -34985,17 +35105,17 @@
       </c>
       <c r="B988" s="7" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="C988" s="7" t="inlineStr">
         <is>
-          <t>11178933</t>
+          <t>11173272</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
         <is>
-          <t>SII25CC24Gamer</t>
+          <t>Xm25Tu12Lux</t>
         </is>
       </c>
       <c r="E988" t="inlineStr">
@@ -35020,13 +35140,17 @@
       </c>
       <c r="B989" s="7" t="inlineStr">
         <is>
-          <t>16977</t>
-        </is>
-      </c>
-      <c r="C989" s="7" t="inlineStr"/>
+          <t>16460</t>
+        </is>
+      </c>
+      <c r="C989" s="7" t="inlineStr">
+        <is>
+          <t>11172987</t>
+        </is>
+      </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>IMÁN MÉXICO</t>
+          <t>Xm25SS16Knit</t>
         </is>
       </c>
       <c r="E989" t="inlineStr">
@@ -35046,18 +35170,22 @@
     <row r="990" ht="24" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>CON FOTO</t>
+          <t>FALTA FOTO</t>
         </is>
       </c>
       <c r="B990" s="7" t="inlineStr">
         <is>
-          <t>17359</t>
-        </is>
-      </c>
-      <c r="C990" s="7" t="inlineStr"/>
+          <t>16477</t>
+        </is>
+      </c>
+      <c r="C990" s="7" t="inlineStr">
+        <is>
+          <t>11173043</t>
+        </is>
+      </c>
       <c r="D990" t="inlineStr">
         <is>
-          <t>SII26GlCCColor</t>
+          <t>Xm25GlassBear</t>
         </is>
       </c>
       <c r="E990" t="inlineStr">
@@ -35070,37 +35198,29 @@
           <t>SECUNDARIO</t>
         </is>
       </c>
-      <c r="G990" t="inlineStr">
-        <is>
-          <t>lote-01/17359.jpg</t>
-        </is>
-      </c>
-      <c r="H990" t="inlineStr">
-        <is>
-          <t>lote-01</t>
-        </is>
-      </c>
-      <c r="I990" t="inlineStr">
-        <is>
-          <t>codigoDia</t>
-        </is>
-      </c>
+      <c r="G990" t="inlineStr"/>
+      <c r="H990" t="inlineStr"/>
+      <c r="I990" t="inlineStr"/>
     </row>
     <row r="991" ht="24" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>CON FOTO</t>
+          <t>FALTA FOTO</t>
         </is>
       </c>
       <c r="B991" s="7" t="inlineStr">
         <is>
-          <t>17360</t>
-        </is>
-      </c>
-      <c r="C991" s="7" t="inlineStr"/>
+          <t>16542</t>
+        </is>
+      </c>
+      <c r="C991" s="7" t="inlineStr">
+        <is>
+          <t>11174790</t>
+        </is>
+      </c>
       <c r="D991" t="inlineStr">
         <is>
-          <t>SII26GlCCColor</t>
+          <t>Wt26Tu16Green</t>
         </is>
       </c>
       <c r="E991" t="inlineStr">
@@ -35113,72 +35233,247 @@
           <t>SECUNDARIO</t>
         </is>
       </c>
-      <c r="G991" t="inlineStr">
-        <is>
-          <t>lote-01/17360.jpg</t>
-        </is>
-      </c>
-      <c r="H991" t="inlineStr">
-        <is>
-          <t>lote-01</t>
-        </is>
-      </c>
-      <c r="I991" t="inlineStr">
-        <is>
-          <t>codigoDia</t>
-        </is>
-      </c>
+      <c r="G991" t="inlineStr"/>
+      <c r="H991" t="inlineStr"/>
+      <c r="I991" t="inlineStr"/>
     </row>
     <row r="992" ht="24" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
+          <t>FALTA FOTO</t>
+        </is>
+      </c>
+      <c r="B992" s="7" t="inlineStr">
+        <is>
+          <t>16668</t>
+        </is>
+      </c>
+      <c r="C992" s="7" t="inlineStr">
+        <is>
+          <t>11176716</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>Sp26StanYellow20</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>SECUNDARIO</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr"/>
+      <c r="H992" t="inlineStr"/>
+      <c r="I992" t="inlineStr"/>
+    </row>
+    <row r="993" ht="24" customHeight="1">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>FALTA FOTO</t>
+        </is>
+      </c>
+      <c r="B993" s="7" t="inlineStr">
+        <is>
+          <t>16881</t>
+        </is>
+      </c>
+      <c r="C993" s="7" t="inlineStr">
+        <is>
+          <t>11178933</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>SII25CC24Gamer</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>SECUNDARIO</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr"/>
+      <c r="H993" t="inlineStr"/>
+      <c r="I993" t="inlineStr"/>
+    </row>
+    <row r="994" ht="24" customHeight="1">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>FALTA FOTO</t>
+        </is>
+      </c>
+      <c r="B994" s="7" t="inlineStr">
+        <is>
+          <t>16977</t>
+        </is>
+      </c>
+      <c r="C994" s="7" t="inlineStr"/>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>IMÁN MÉXICO</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>SECUNDARIO</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr"/>
+      <c r="H994" t="inlineStr"/>
+      <c r="I994" t="inlineStr"/>
+    </row>
+    <row r="995" ht="24" customHeight="1">
+      <c r="A995" t="inlineStr">
+        <is>
           <t>CON FOTO</t>
         </is>
       </c>
-      <c r="B992" s="7" t="inlineStr">
+      <c r="B995" s="7" t="inlineStr">
+        <is>
+          <t>17359</t>
+        </is>
+      </c>
+      <c r="C995" s="7" t="inlineStr"/>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>SII26GlCCColor</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>SECUNDARIO</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>lote-01/17359.jpg</t>
+        </is>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
+    </row>
+    <row r="996" ht="24" customHeight="1">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>CON FOTO</t>
+        </is>
+      </c>
+      <c r="B996" s="7" t="inlineStr">
+        <is>
+          <t>17360</t>
+        </is>
+      </c>
+      <c r="C996" s="7" t="inlineStr"/>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>SII26GlCCColor</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>SECUNDARIO</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>lote-01/17360.jpg</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
+    </row>
+    <row r="997" ht="24" customHeight="1">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>CON FOTO</t>
+        </is>
+      </c>
+      <c r="B997" s="7" t="inlineStr">
         <is>
           <t>17362</t>
         </is>
       </c>
-      <c r="C992" s="7" t="inlineStr"/>
-      <c r="D992" t="inlineStr">
+      <c r="C997" s="7" t="inlineStr"/>
+      <c r="D997" t="inlineStr">
         <is>
           <t>SII26GlCCColor</t>
         </is>
       </c>
-      <c r="E992" t="inlineStr">
+      <c r="E997" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F992" t="inlineStr">
+      <c r="F997" t="inlineStr">
         <is>
           <t>SECUNDARIO</t>
         </is>
       </c>
-      <c r="G992" t="inlineStr">
+      <c r="G997" t="inlineStr">
         <is>
           <t>lote-01/17362.jpg</t>
         </is>
       </c>
-      <c r="H992" t="inlineStr">
+      <c r="H997" t="inlineStr">
         <is>
           <t>lote-01</t>
         </is>
       </c>
-      <c r="I992" t="inlineStr">
+      <c r="I997" t="inlineStr">
         <is>
           <t>codigoDia</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:I992"/>
+  <autoFilter ref="A7:I997"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A6:I6"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:A992">
+  <conditionalFormatting sqref="A8:A997">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>A8="CON FOTO"</formula>
     </cfRule>

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -31861,17 +31861,17 @@
       </c>
       <c r="B900" s="7" t="inlineStr">
         <is>
-          <t>16879</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="C900" s="7" t="inlineStr">
         <is>
-          <t>11178922</t>
+          <t>11178964</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>WC26Tu16Flower</t>
+          <t>Sp26KeychainOr</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
@@ -31896,17 +31896,17 @@
       </c>
       <c r="B901" s="7" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="C901" s="7" t="inlineStr">
         <is>
-          <t>11178928</t>
+          <t>11178934</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>WC26CC24Road</t>
+          <t>SII26CC24GID</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
@@ -31931,17 +31931,17 @@
       </c>
       <c r="B902" s="7" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="C902" s="7" t="inlineStr">
         <is>
-          <t>11178930</t>
+          <t>11179003</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>WC26CC24Pride</t>
+          <t>Sp26CC24Teach</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
@@ -31966,17 +31966,17 @@
       </c>
       <c r="B903" s="7" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>16896</t>
         </is>
       </c>
       <c r="C903" s="7" t="inlineStr">
         <is>
-          <t>11178964</t>
+          <t>11178970</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>Sp26KeychainOr</t>
+          <t>Sp26SSCC16Band</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
@@ -32001,17 +32001,17 @@
       </c>
       <c r="B904" s="7" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>16897</t>
         </is>
       </c>
       <c r="C904" s="7" t="inlineStr">
         <is>
-          <t>11178934</t>
+          <t>11178959</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>SII26CC24GID</t>
+          <t>WC26CCSS24Puffy</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
@@ -32036,17 +32036,17 @@
       </c>
       <c r="B905" s="7" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="C905" s="7" t="inlineStr">
         <is>
-          <t>11179003</t>
+          <t>11179004</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>Sp26CC24Teach</t>
+          <t>Sp26Tu16Teach</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
@@ -32071,17 +32071,17 @@
       </c>
       <c r="B906" s="7" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>16902</t>
         </is>
       </c>
       <c r="C906" s="7" t="inlineStr">
         <is>
-          <t>11178970</t>
+          <t>11178920</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>Sp26SSCC16Band</t>
+          <t>WC26Tu20Yellow</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
@@ -32106,17 +32106,17 @@
       </c>
       <c r="B907" s="7" t="inlineStr">
         <is>
-          <t>16897</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="C907" s="7" t="inlineStr">
         <is>
-          <t>11178959</t>
+          <t>11178926</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>WC26CCSS24Puffy</t>
+          <t>Sp26CC24Or</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
@@ -32141,17 +32141,17 @@
       </c>
       <c r="B908" s="7" t="inlineStr">
         <is>
-          <t>16898</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="C908" s="7" t="inlineStr">
         <is>
-          <t>11178938</t>
+          <t>11178965</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>Sp26Tu16Mom</t>
+          <t>WC26ToteRoad</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
@@ -32176,17 +32176,17 @@
       </c>
       <c r="B909" s="7" t="inlineStr">
         <is>
-          <t>16899</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="C909" s="7" t="inlineStr">
         <is>
-          <t>11179004</t>
+          <t>11178966</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>Sp26Tu16Teach</t>
+          <t>WC26TotePride</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
@@ -32211,17 +32211,17 @@
       </c>
       <c r="B910" s="7" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="C910" s="7" t="inlineStr">
         <is>
-          <t>11178941</t>
+          <t>11179005</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>SII26SS16Studded</t>
+          <t>WC26SS30Pride</t>
         </is>
       </c>
       <c r="E910" t="inlineStr">
@@ -32246,17 +32246,17 @@
       </c>
       <c r="B911" s="7" t="inlineStr">
         <is>
-          <t>16901</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="C911" s="7" t="inlineStr">
         <is>
-          <t>11178937</t>
+          <t>11187369</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>WC26Mug12Stan</t>
+          <t>WC26BearWC</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
@@ -32281,17 +32281,17 @@
       </c>
       <c r="B912" s="7" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>16909</t>
         </is>
       </c>
       <c r="C912" s="7" t="inlineStr">
         <is>
-          <t>11178920</t>
+          <t>11178944</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>WC26Tu20Yellow</t>
+          <t>WC26SS20BTL</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
@@ -32316,17 +32316,17 @@
       </c>
       <c r="B913" s="7" t="inlineStr">
         <is>
-          <t>16903</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="C913" s="7" t="inlineStr">
         <is>
-          <t>11178926</t>
+          <t>11178969</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>Sp26CC24Or</t>
+          <t>WC26SS16Pink</t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
@@ -32351,17 +32351,17 @@
       </c>
       <c r="B914" s="7" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>16911</t>
         </is>
       </c>
       <c r="C914" s="7" t="inlineStr">
         <is>
-          <t>11178965</t>
+          <t>11178971</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>WC26ToteRoad</t>
+          <t>WC26SS16Charm</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
@@ -32386,17 +32386,17 @@
       </c>
       <c r="B915" s="7" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>16912</t>
         </is>
       </c>
       <c r="C915" s="7" t="inlineStr">
         <is>
-          <t>11178966</t>
+          <t>11178949</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>WC26TotePride</t>
+          <t>WC26SS20Pull</t>
         </is>
       </c>
       <c r="E915" t="inlineStr">
@@ -32421,17 +32421,17 @@
       </c>
       <c r="B916" s="7" t="inlineStr">
         <is>
-          <t>16906</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="C916" s="7" t="inlineStr">
         <is>
-          <t>11179005</t>
+          <t>11178946</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>WC26SS30Pride</t>
+          <t>WC26SS20Twist</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
@@ -32456,17 +32456,17 @@
       </c>
       <c r="B917" s="7" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>16914</t>
         </is>
       </c>
       <c r="C917" s="7" t="inlineStr">
         <is>
-          <t>11187369</t>
+          <t>11178947</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>WC26BearWC</t>
+          <t>Sp26StanQuen20</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
@@ -32491,17 +32491,17 @@
       </c>
       <c r="B918" s="7" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>16915</t>
         </is>
       </c>
       <c r="C918" s="7" t="inlineStr">
         <is>
-          <t>11178944</t>
+          <t>11178948</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>WC26SS20BTL</t>
+          <t>WC26StanHand20</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
@@ -32526,17 +32526,17 @@
       </c>
       <c r="B919" s="7" t="inlineStr">
         <is>
-          <t>16910</t>
+          <t>16916</t>
         </is>
       </c>
       <c r="C919" s="7" t="inlineStr">
         <is>
-          <t>11178969</t>
+          <t>11178956</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>WC26SS16Pink</t>
+          <t>SII26Quencher30P</t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
@@ -32561,17 +32561,17 @@
       </c>
       <c r="B920" s="7" t="inlineStr">
         <is>
-          <t>16911</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="C920" s="7" t="inlineStr">
         <is>
-          <t>11178971</t>
+          <t>11178972</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>WC26SS16Charm</t>
+          <t>Sp26Vac16Stan</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
@@ -32596,17 +32596,17 @@
       </c>
       <c r="B921" s="7" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>16919</t>
         </is>
       </c>
       <c r="C921" s="7" t="inlineStr">
         <is>
-          <t>11178949</t>
+          <t>11178957</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>WC26SS20Pull</t>
+          <t>WC26StanQuen30</t>
         </is>
       </c>
       <c r="E921" t="inlineStr">
@@ -32631,17 +32631,17 @@
       </c>
       <c r="B922" s="7" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="C922" s="7" t="inlineStr">
         <is>
-          <t>11178946</t>
+          <t>11178917</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>WC26SS20Twist</t>
+          <t>WC26DW12Oran</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
@@ -32666,17 +32666,17 @@
       </c>
       <c r="B923" s="7" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>16923</t>
         </is>
       </c>
       <c r="C923" s="7" t="inlineStr">
         <is>
-          <t>11178947</t>
+          <t>11178918</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>Sp26StanQuen20</t>
+          <t>WC26Gl20Silicone</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
@@ -32701,17 +32701,17 @@
       </c>
       <c r="B924" s="7" t="inlineStr">
         <is>
-          <t>16915</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="C924" s="7" t="inlineStr">
         <is>
-          <t>11178948</t>
+          <t>11178973</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>WC26StanHand20</t>
+          <t>WC26SS16Lid</t>
         </is>
       </c>
       <c r="E924" t="inlineStr">
@@ -32736,17 +32736,17 @@
       </c>
       <c r="B925" s="7" t="inlineStr">
         <is>
-          <t>16916</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="C925" s="7" t="inlineStr">
         <is>
-          <t>11178956</t>
+          <t>11187370</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>SII26Quencher30P</t>
+          <t>WC26SS16Black</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
@@ -32771,17 +32771,17 @@
       </c>
       <c r="B926" s="7" t="inlineStr">
         <is>
-          <t>16917</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="C926" s="7" t="inlineStr">
         <is>
-          <t>11178972</t>
+          <t>11187372</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>Sp26Vac16Stan</t>
+          <t>WC26Tu24DW</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
@@ -32806,17 +32806,13 @@
       </c>
       <c r="B927" s="7" t="inlineStr">
         <is>
-          <t>16918</t>
-        </is>
-      </c>
-      <c r="C927" s="7" t="inlineStr">
-        <is>
-          <t>11178943</t>
-        </is>
-      </c>
+          <t>16971</t>
+        </is>
+      </c>
+      <c r="C927" s="7" t="inlineStr"/>
       <c r="D927" t="inlineStr">
         <is>
-          <t>Sp26SS20Orange</t>
+          <t>WC26BearMex</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
@@ -32841,17 +32837,17 @@
       </c>
       <c r="B928" s="7" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>16978</t>
         </is>
       </c>
       <c r="C928" s="7" t="inlineStr">
         <is>
-          <t>11178957</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>WC26StanQuen30</t>
+          <t>WC26LlaveroB</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
@@ -32871,22 +32867,22 @@
     <row r="929" ht="24" customHeight="1">
       <c r="A929" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B929" s="7" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="C929" s="7" t="inlineStr">
         <is>
-          <t>11178935</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D929" t="inlineStr">
         <is>
-          <t>SII26Tu10Gam</t>
+          <t>Sp26NEBlack</t>
         </is>
       </c>
       <c r="E929" t="inlineStr">
@@ -32899,29 +32895,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G929" t="inlineStr"/>
-      <c r="H929" t="inlineStr"/>
-      <c r="I929" t="inlineStr"/>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>lote-01/16531.jpeg</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="930" ht="24" customHeight="1">
       <c r="A930" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B930" s="7" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="C930" s="7" t="inlineStr">
         <is>
-          <t>11178917</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t>WC26DW12Oran</t>
+          <t>Sp26NECrossB</t>
         </is>
       </c>
       <c r="E930" t="inlineStr">
@@ -32934,29 +32942,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G930" t="inlineStr"/>
-      <c r="H930" t="inlineStr"/>
-      <c r="I930" t="inlineStr"/>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>lote-01/16532.jpeg</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="931" ht="24" customHeight="1">
       <c r="A931" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B931" s="7" t="inlineStr">
         <is>
-          <t>16923</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="C931" s="7" t="inlineStr">
         <is>
-          <t>11178918</t>
+          <t>11170187</t>
         </is>
       </c>
       <c r="D931" t="inlineStr">
         <is>
-          <t>WC26Gl20Silicone</t>
+          <t>ToteBag MxPais</t>
         </is>
       </c>
       <c r="E931" t="inlineStr">
@@ -32969,29 +32989,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G931" t="inlineStr"/>
-      <c r="H931" t="inlineStr"/>
-      <c r="I931" t="inlineStr"/>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>lote-01/011170187.jpeg</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="932" ht="24" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B932" s="7" t="inlineStr">
         <is>
-          <t>16924</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="C932" s="7" t="inlineStr">
         <is>
-          <t>11178945</t>
+          <t>11170102</t>
         </is>
       </c>
       <c r="D932" t="inlineStr">
         <is>
-          <t>WC26Stan20IceF</t>
+          <t>DiscoveryCDMX</t>
         </is>
       </c>
       <c r="E932" t="inlineStr">
@@ -33004,29 +33036,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G932" t="inlineStr"/>
-      <c r="H932" t="inlineStr"/>
-      <c r="I932" t="inlineStr"/>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>lote-01/011170102.jpeg</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="933" ht="24" customHeight="1">
       <c r="A933" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B933" s="7" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="C933" s="7" t="inlineStr">
         <is>
-          <t>11178973</t>
+          <t>11176710</t>
         </is>
       </c>
       <c r="D933" t="inlineStr">
         <is>
-          <t>WC26SS16Lid</t>
+          <t>Sp26CC24Dome</t>
         </is>
       </c>
       <c r="E933" t="inlineStr">
@@ -33039,29 +33083,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G933" t="inlineStr"/>
-      <c r="H933" t="inlineStr"/>
-      <c r="I933" t="inlineStr"/>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>lote-01/011176710.jpeg</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="934" ht="24" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B934" s="7" t="inlineStr">
         <is>
-          <t>16958</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="C934" s="7" t="inlineStr">
         <is>
-          <t>11187370</t>
+          <t>11170174</t>
         </is>
       </c>
       <c r="D934" t="inlineStr">
         <is>
-          <t>WC26SS16Black</t>
+          <t>DiscCC24MxPais</t>
         </is>
       </c>
       <c r="E934" t="inlineStr">
@@ -33074,29 +33130,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G934" t="inlineStr"/>
-      <c r="H934" t="inlineStr"/>
-      <c r="I934" t="inlineStr"/>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>lote-01/011170174.jpeg</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="935" ht="24" customHeight="1">
       <c r="A935" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B935" s="7" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="C935" s="7" t="inlineStr">
         <is>
-          <t>11187372</t>
+          <t>11170147</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
         <is>
-          <t>WC26Tu24DW</t>
+          <t>Disc2ozMxPais</t>
         </is>
       </c>
       <c r="E935" t="inlineStr">
@@ -33109,25 +33177,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G935" t="inlineStr"/>
-      <c r="H935" t="inlineStr"/>
-      <c r="I935" t="inlineStr"/>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>lote-01/011170147.jpeg</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="936" ht="24" customHeight="1">
       <c r="A936" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B936" s="7" t="inlineStr">
         <is>
-          <t>16971</t>
-        </is>
-      </c>
-      <c r="C936" s="7" t="inlineStr"/>
+          <t>16689</t>
+        </is>
+      </c>
+      <c r="C936" s="7" t="inlineStr">
+        <is>
+          <t>11170149</t>
+        </is>
+      </c>
       <c r="D936" t="inlineStr">
         <is>
-          <t>WC26BearMex</t>
+          <t>Disc2ozCDMX</t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
@@ -33140,29 +33224,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G936" t="inlineStr"/>
-      <c r="H936" t="inlineStr"/>
-      <c r="I936" t="inlineStr"/>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>lote-01/011170149.jpeg</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="937" ht="24" customHeight="1">
       <c r="A937" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B937" s="7" t="inlineStr">
         <is>
-          <t>16978</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="C937" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178922</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>WC26LlaveroB</t>
+          <t>WC26Tu16Flower</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
@@ -33175,9 +33271,21 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G937" t="inlineStr"/>
-      <c r="H937" t="inlineStr"/>
-      <c r="I937" t="inlineStr"/>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>lote-01/011178922.jpeg</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="938" ht="24" customHeight="1">
       <c r="A938" t="inlineStr">
@@ -33187,17 +33295,17 @@
       </c>
       <c r="B938" s="7" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>16880</t>
         </is>
       </c>
       <c r="C938" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178928</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>Sp26NEBlack</t>
+          <t>WC26CC24Road</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
@@ -33212,7 +33320,7 @@
       </c>
       <c r="G938" t="inlineStr">
         <is>
-          <t>lote-01/16531.jpeg</t>
+          <t>lote-01/011178928.jpeg</t>
         </is>
       </c>
       <c r="H938" t="inlineStr">
@@ -33222,7 +33330,7 @@
       </c>
       <c r="I938" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -33234,17 +33342,17 @@
       </c>
       <c r="B939" s="7" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="C939" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178930</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
         <is>
-          <t>Sp26NECrossB</t>
+          <t>WC26CC24Pride</t>
         </is>
       </c>
       <c r="E939" t="inlineStr">
@@ -33259,7 +33367,7 @@
       </c>
       <c r="G939" t="inlineStr">
         <is>
-          <t>lote-01/16532.jpeg</t>
+          <t>lote-01/011178930.jpeg</t>
         </is>
       </c>
       <c r="H939" t="inlineStr">
@@ -33269,7 +33377,7 @@
       </c>
       <c r="I939" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -33281,17 +33389,17 @@
       </c>
       <c r="B940" s="7" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>16898</t>
         </is>
       </c>
       <c r="C940" s="7" t="inlineStr">
         <is>
-          <t>11170187</t>
+          <t>11178938</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
         <is>
-          <t>ToteBag MxPais</t>
+          <t>Sp26Tu16Mom</t>
         </is>
       </c>
       <c r="E940" t="inlineStr">
@@ -33306,7 +33414,7 @@
       </c>
       <c r="G940" t="inlineStr">
         <is>
-          <t>lote-01/011170187.jpeg</t>
+          <t>lote-01/011178938.jpeg</t>
         </is>
       </c>
       <c r="H940" t="inlineStr">
@@ -33328,17 +33436,17 @@
       </c>
       <c r="B941" s="7" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="C941" s="7" t="inlineStr">
         <is>
-          <t>11170102</t>
+          <t>11178941</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
         <is>
-          <t>DiscoveryCDMX</t>
+          <t>SII26SS16Studded</t>
         </is>
       </c>
       <c r="E941" t="inlineStr">
@@ -33353,7 +33461,7 @@
       </c>
       <c r="G941" t="inlineStr">
         <is>
-          <t>lote-01/011170102.jpeg</t>
+          <t>lote-01/011178941.jpeg</t>
         </is>
       </c>
       <c r="H941" t="inlineStr">
@@ -33375,17 +33483,17 @@
       </c>
       <c r="B942" s="7" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>16901</t>
         </is>
       </c>
       <c r="C942" s="7" t="inlineStr">
         <is>
-          <t>11176710</t>
+          <t>11178937</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t>Sp26CC24Dome</t>
+          <t>WC26Mug12Stan</t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
@@ -33400,7 +33508,7 @@
       </c>
       <c r="G942" t="inlineStr">
         <is>
-          <t>lote-01/011176710.jpeg</t>
+          <t>lote-01/011178937.jpeg</t>
         </is>
       </c>
       <c r="H942" t="inlineStr">
@@ -33422,17 +33530,17 @@
       </c>
       <c r="B943" s="7" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="C943" s="7" t="inlineStr">
         <is>
-          <t>11170174</t>
+          <t>11178943</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
         <is>
-          <t>DiscCC24MxPais</t>
+          <t>Sp26SS20Orange</t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
@@ -33447,7 +33555,7 @@
       </c>
       <c r="G943" t="inlineStr">
         <is>
-          <t>lote-01/011170174.jpeg</t>
+          <t>lote-01/011178943.jpeg</t>
         </is>
       </c>
       <c r="H943" t="inlineStr">
@@ -33469,17 +33577,17 @@
       </c>
       <c r="B944" s="7" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="C944" s="7" t="inlineStr">
         <is>
-          <t>11170147</t>
+          <t>11178935</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t>Disc2ozMxPais</t>
+          <t>SII26Tu10Gam</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
@@ -33494,7 +33602,7 @@
       </c>
       <c r="G944" t="inlineStr">
         <is>
-          <t>lote-01/011170147.jpeg</t>
+          <t>lote-01/011178935.jpeg</t>
         </is>
       </c>
       <c r="H944" t="inlineStr">
@@ -33516,17 +33624,17 @@
       </c>
       <c r="B945" s="7" t="inlineStr">
         <is>
-          <t>16689</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="C945" s="7" t="inlineStr">
         <is>
-          <t>11170149</t>
+          <t>11178919</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>Disc2ozCDMX</t>
+          <t>Sp26Mug14Mom</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
@@ -33541,7 +33649,7 @@
       </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t>lote-01/011170149.jpeg</t>
+          <t>lote-01/011178919.jpeg</t>
         </is>
       </c>
       <c r="H945" t="inlineStr">
@@ -33563,17 +33671,17 @@
       </c>
       <c r="B946" s="7" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>16924</t>
         </is>
       </c>
       <c r="C946" s="7" t="inlineStr">
         <is>
-          <t>11178919</t>
+          <t>11178945</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>Sp26Mug14Mom</t>
+          <t>WC26Stan20IceF</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
@@ -33588,7 +33696,7 @@
       </c>
       <c r="G946" t="inlineStr">
         <is>
-          <t>lote-01/011178919.jpeg</t>
+          <t>lote-01/011178945.jpeg</t>
         </is>
       </c>
       <c r="H946" t="inlineStr">
@@ -35280,17 +35388,13 @@
       </c>
       <c r="B993" s="7" t="inlineStr">
         <is>
-          <t>16881</t>
-        </is>
-      </c>
-      <c r="C993" s="7" t="inlineStr">
-        <is>
-          <t>11178933</t>
-        </is>
-      </c>
+          <t>16977</t>
+        </is>
+      </c>
+      <c r="C993" s="7" t="inlineStr"/>
       <c r="D993" t="inlineStr">
         <is>
-          <t>SII25CC24Gamer</t>
+          <t>IMÁN MÉXICO</t>
         </is>
       </c>
       <c r="E993" t="inlineStr">
@@ -35310,18 +35414,22 @@
     <row r="994" ht="24" customHeight="1">
       <c r="A994" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B994" s="7" t="inlineStr">
         <is>
-          <t>16977</t>
-        </is>
-      </c>
-      <c r="C994" s="7" t="inlineStr"/>
+          <t>16881</t>
+        </is>
+      </c>
+      <c r="C994" s="7" t="inlineStr">
+        <is>
+          <t>11178933</t>
+        </is>
+      </c>
       <c r="D994" t="inlineStr">
         <is>
-          <t>IMÁN MÉXICO</t>
+          <t>SII25CC24Gamer</t>
         </is>
       </c>
       <c r="E994" t="inlineStr">
@@ -35334,9 +35442,21 @@
           <t>SECUNDARIO</t>
         </is>
       </c>
-      <c r="G994" t="inlineStr"/>
-      <c r="H994" t="inlineStr"/>
-      <c r="I994" t="inlineStr"/>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>lote-01/011178933.jpeg</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="995" ht="24" customHeight="1">
       <c r="A995" t="inlineStr">

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -31721,17 +31721,17 @@
       </c>
       <c r="B896" s="7" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="C896" s="7" t="inlineStr">
         <is>
-          <t>11178952</t>
+          <t>11178953</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>WC26SSCC24Grad</t>
+          <t>Sp26SSCC24Oran</t>
         </is>
       </c>
       <c r="E896" t="inlineStr">
@@ -31756,17 +31756,17 @@
       </c>
       <c r="B897" s="7" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="C897" s="7" t="inlineStr">
         <is>
-          <t>11178953</t>
+          <t>11178954</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>Sp26SSCC24Oran</t>
+          <t>Sp26SSCC24CarryC</t>
         </is>
       </c>
       <c r="E897" t="inlineStr">
@@ -31791,17 +31791,17 @@
       </c>
       <c r="B898" s="7" t="inlineStr">
         <is>
-          <t>16877</t>
+          <t>16878</t>
         </is>
       </c>
       <c r="C898" s="7" t="inlineStr">
         <is>
-          <t>11178954</t>
+          <t>11178921</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
         <is>
-          <t>Sp26SSCC24CarryC</t>
+          <t>Sp26Tu16Orange</t>
         </is>
       </c>
       <c r="E898" t="inlineStr">
@@ -31826,17 +31826,17 @@
       </c>
       <c r="B899" s="7" t="inlineStr">
         <is>
-          <t>16878</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="C899" s="7" t="inlineStr">
         <is>
-          <t>11178921</t>
+          <t>11178964</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>Sp26Tu16Orange</t>
+          <t>Sp26KeychainOr</t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
@@ -31861,17 +31861,17 @@
       </c>
       <c r="B900" s="7" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="C900" s="7" t="inlineStr">
         <is>
-          <t>11178964</t>
+          <t>11178934</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>Sp26KeychainOr</t>
+          <t>SII26CC24GID</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
@@ -31896,17 +31896,17 @@
       </c>
       <c r="B901" s="7" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="C901" s="7" t="inlineStr">
         <is>
-          <t>11178934</t>
+          <t>11179003</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>SII26CC24GID</t>
+          <t>Sp26CC24Teach</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
@@ -31931,17 +31931,17 @@
       </c>
       <c r="B902" s="7" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>16896</t>
         </is>
       </c>
       <c r="C902" s="7" t="inlineStr">
         <is>
-          <t>11179003</t>
+          <t>11178970</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>Sp26CC24Teach</t>
+          <t>Sp26SSCC16Band</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
@@ -31966,17 +31966,17 @@
       </c>
       <c r="B903" s="7" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="C903" s="7" t="inlineStr">
         <is>
-          <t>11178970</t>
+          <t>11179004</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>Sp26SSCC16Band</t>
+          <t>Sp26Tu16Teach</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
@@ -32001,17 +32001,17 @@
       </c>
       <c r="B904" s="7" t="inlineStr">
         <is>
-          <t>16897</t>
+          <t>16902</t>
         </is>
       </c>
       <c r="C904" s="7" t="inlineStr">
         <is>
-          <t>11178959</t>
+          <t>11178920</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>WC26CCSS24Puffy</t>
+          <t>WC26Tu20Yellow</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
@@ -32036,17 +32036,17 @@
       </c>
       <c r="B905" s="7" t="inlineStr">
         <is>
-          <t>16899</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="C905" s="7" t="inlineStr">
         <is>
-          <t>11179004</t>
+          <t>11178926</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>Sp26Tu16Teach</t>
+          <t>Sp26CC24Or</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
@@ -32071,17 +32071,17 @@
       </c>
       <c r="B906" s="7" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="C906" s="7" t="inlineStr">
         <is>
-          <t>11178920</t>
+          <t>11178965</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>WC26Tu20Yellow</t>
+          <t>WC26ToteRoad</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
@@ -32106,17 +32106,17 @@
       </c>
       <c r="B907" s="7" t="inlineStr">
         <is>
-          <t>16903</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="C907" s="7" t="inlineStr">
         <is>
-          <t>11178926</t>
+          <t>11178966</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>Sp26CC24Or</t>
+          <t>WC26TotePride</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
@@ -32141,17 +32141,17 @@
       </c>
       <c r="B908" s="7" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="C908" s="7" t="inlineStr">
         <is>
-          <t>11178965</t>
+          <t>11187369</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>WC26ToteRoad</t>
+          <t>WC26BearWC</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
@@ -32176,17 +32176,17 @@
       </c>
       <c r="B909" s="7" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>16909</t>
         </is>
       </c>
       <c r="C909" s="7" t="inlineStr">
         <is>
-          <t>11178966</t>
+          <t>11178944</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>WC26TotePride</t>
+          <t>WC26SS20BTL</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
@@ -32211,17 +32211,17 @@
       </c>
       <c r="B910" s="7" t="inlineStr">
         <is>
-          <t>16906</t>
+          <t>16912</t>
         </is>
       </c>
       <c r="C910" s="7" t="inlineStr">
         <is>
-          <t>11179005</t>
+          <t>11178949</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>WC26SS30Pride</t>
+          <t>WC26SS20Pull</t>
         </is>
       </c>
       <c r="E910" t="inlineStr">
@@ -32246,17 +32246,17 @@
       </c>
       <c r="B911" s="7" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>16914</t>
         </is>
       </c>
       <c r="C911" s="7" t="inlineStr">
         <is>
-          <t>11187369</t>
+          <t>11178947</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>WC26BearWC</t>
+          <t>Sp26StanQuen20</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
@@ -32281,17 +32281,17 @@
       </c>
       <c r="B912" s="7" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="C912" s="7" t="inlineStr">
         <is>
-          <t>11178944</t>
+          <t>11178972</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>WC26SS20BTL</t>
+          <t>Sp26Vac16Stan</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
@@ -32316,17 +32316,17 @@
       </c>
       <c r="B913" s="7" t="inlineStr">
         <is>
-          <t>16910</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="C913" s="7" t="inlineStr">
         <is>
-          <t>11178969</t>
+          <t>11178917</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>WC26SS16Pink</t>
+          <t>WC26DW12Oran</t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
@@ -32351,17 +32351,17 @@
       </c>
       <c r="B914" s="7" t="inlineStr">
         <is>
-          <t>16911</t>
+          <t>16923</t>
         </is>
       </c>
       <c r="C914" s="7" t="inlineStr">
         <is>
-          <t>11178971</t>
+          <t>11178918</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>WC26SS16Charm</t>
+          <t>WC26Gl20Silicone</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
@@ -32386,17 +32386,17 @@
       </c>
       <c r="B915" s="7" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="C915" s="7" t="inlineStr">
         <is>
-          <t>11178949</t>
+          <t>11187370</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>WC26SS20Pull</t>
+          <t>WC26SS16Black</t>
         </is>
       </c>
       <c r="E915" t="inlineStr">
@@ -32421,17 +32421,17 @@
       </c>
       <c r="B916" s="7" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="C916" s="7" t="inlineStr">
         <is>
-          <t>11178946</t>
+          <t>11187372</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>WC26SS20Twist</t>
+          <t>WC26Tu24DW</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
@@ -32456,17 +32456,13 @@
       </c>
       <c r="B917" s="7" t="inlineStr">
         <is>
-          <t>16914</t>
-        </is>
-      </c>
-      <c r="C917" s="7" t="inlineStr">
-        <is>
-          <t>11178947</t>
-        </is>
-      </c>
+          <t>16971</t>
+        </is>
+      </c>
+      <c r="C917" s="7" t="inlineStr"/>
       <c r="D917" t="inlineStr">
         <is>
-          <t>Sp26StanQuen20</t>
+          <t>WC26BearMex</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
@@ -32491,17 +32487,17 @@
       </c>
       <c r="B918" s="7" t="inlineStr">
         <is>
-          <t>16915</t>
+          <t>16978</t>
         </is>
       </c>
       <c r="C918" s="7" t="inlineStr">
         <is>
-          <t>11178948</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>WC26StanHand20</t>
+          <t>WC26LlaveroB</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
@@ -32521,22 +32517,22 @@
     <row r="919" ht="24" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B919" s="7" t="inlineStr">
         <is>
-          <t>16916</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="C919" s="7" t="inlineStr">
         <is>
-          <t>11178956</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>SII26Quencher30P</t>
+          <t>Sp26NEBlack</t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
@@ -32549,29 +32545,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G919" t="inlineStr"/>
-      <c r="H919" t="inlineStr"/>
-      <c r="I919" t="inlineStr"/>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>lote-01/16531.jpeg</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="920" ht="24" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B920" s="7" t="inlineStr">
         <is>
-          <t>16917</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="C920" s="7" t="inlineStr">
         <is>
-          <t>11178972</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>Sp26Vac16Stan</t>
+          <t>Sp26NECrossB</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
@@ -32584,29 +32592,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G920" t="inlineStr"/>
-      <c r="H920" t="inlineStr"/>
-      <c r="I920" t="inlineStr"/>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>lote-01/16532.jpeg</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="921" ht="24" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B921" s="7" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="C921" s="7" t="inlineStr">
         <is>
-          <t>11178957</t>
+          <t>11170187</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>WC26StanQuen30</t>
+          <t>ToteBag MxPais</t>
         </is>
       </c>
       <c r="E921" t="inlineStr">
@@ -32619,29 +32639,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G921" t="inlineStr"/>
-      <c r="H921" t="inlineStr"/>
-      <c r="I921" t="inlineStr"/>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>lote-01/011170187.jpeg</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="922" ht="24" customHeight="1">
       <c r="A922" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B922" s="7" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="C922" s="7" t="inlineStr">
         <is>
-          <t>11178917</t>
+          <t>11170102</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>WC26DW12Oran</t>
+          <t>DiscoveryCDMX</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
@@ -32654,29 +32686,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G922" t="inlineStr"/>
-      <c r="H922" t="inlineStr"/>
-      <c r="I922" t="inlineStr"/>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>lote-01/011170102.jpeg</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="923" ht="24" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B923" s="7" t="inlineStr">
         <is>
-          <t>16923</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="C923" s="7" t="inlineStr">
         <is>
-          <t>11178918</t>
+          <t>11176710</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>WC26Gl20Silicone</t>
+          <t>Sp26CC24Dome</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
@@ -32689,29 +32733,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G923" t="inlineStr"/>
-      <c r="H923" t="inlineStr"/>
-      <c r="I923" t="inlineStr"/>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>lote-01/011176710.jpeg</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="924" ht="24" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B924" s="7" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="C924" s="7" t="inlineStr">
         <is>
-          <t>11178973</t>
+          <t>11170174</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>WC26SS16Lid</t>
+          <t>DiscCC24MxPais</t>
         </is>
       </c>
       <c r="E924" t="inlineStr">
@@ -32724,29 +32780,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G924" t="inlineStr"/>
-      <c r="H924" t="inlineStr"/>
-      <c r="I924" t="inlineStr"/>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>lote-01/011170174.jpeg</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="925" ht="24" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B925" s="7" t="inlineStr">
         <is>
-          <t>16958</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="C925" s="7" t="inlineStr">
         <is>
-          <t>11187370</t>
+          <t>11170147</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>WC26SS16Black</t>
+          <t>Disc2ozMxPais</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
@@ -32759,29 +32827,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G925" t="inlineStr"/>
-      <c r="H925" t="inlineStr"/>
-      <c r="I925" t="inlineStr"/>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>lote-01/011170147.jpeg</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="926" ht="24" customHeight="1">
       <c r="A926" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B926" s="7" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="C926" s="7" t="inlineStr">
         <is>
-          <t>11187372</t>
+          <t>11170149</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>WC26Tu24DW</t>
+          <t>Disc2ozCDMX</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
@@ -32794,25 +32874,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G926" t="inlineStr"/>
-      <c r="H926" t="inlineStr"/>
-      <c r="I926" t="inlineStr"/>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>lote-01/011170149.jpeg</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="927" ht="24" customHeight="1">
       <c r="A927" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B927" s="7" t="inlineStr">
         <is>
-          <t>16971</t>
-        </is>
-      </c>
-      <c r="C927" s="7" t="inlineStr"/>
+          <t>16875</t>
+        </is>
+      </c>
+      <c r="C927" s="7" t="inlineStr">
+        <is>
+          <t>11178952</t>
+        </is>
+      </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>WC26BearMex</t>
+          <t>WC26SSCC24Grad</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
@@ -32825,29 +32921,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G927" t="inlineStr"/>
-      <c r="H927" t="inlineStr"/>
-      <c r="I927" t="inlineStr"/>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>lote-01/011178952.jpeg</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="928" ht="24" customHeight="1">
       <c r="A928" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B928" s="7" t="inlineStr">
         <is>
-          <t>16978</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="C928" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178922</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>WC26LlaveroB</t>
+          <t>WC26Tu16Flower</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
@@ -32860,9 +32968,21 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G928" t="inlineStr"/>
-      <c r="H928" t="inlineStr"/>
-      <c r="I928" t="inlineStr"/>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>lote-01/011178922.jpeg</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="929" ht="24" customHeight="1">
       <c r="A929" t="inlineStr">
@@ -32872,17 +32992,17 @@
       </c>
       <c r="B929" s="7" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>16880</t>
         </is>
       </c>
       <c r="C929" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178928</t>
         </is>
       </c>
       <c r="D929" t="inlineStr">
         <is>
-          <t>Sp26NEBlack</t>
+          <t>WC26CC24Road</t>
         </is>
       </c>
       <c r="E929" t="inlineStr">
@@ -32897,7 +33017,7 @@
       </c>
       <c r="G929" t="inlineStr">
         <is>
-          <t>lote-01/16531.jpeg</t>
+          <t>lote-01/011178928.jpeg</t>
         </is>
       </c>
       <c r="H929" t="inlineStr">
@@ -32907,7 +33027,7 @@
       </c>
       <c r="I929" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -32919,17 +33039,17 @@
       </c>
       <c r="B930" s="7" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="C930" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178930</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t>Sp26NECrossB</t>
+          <t>WC26CC24Pride</t>
         </is>
       </c>
       <c r="E930" t="inlineStr">
@@ -32944,7 +33064,7 @@
       </c>
       <c r="G930" t="inlineStr">
         <is>
-          <t>lote-01/16532.jpeg</t>
+          <t>lote-01/011178930.jpeg</t>
         </is>
       </c>
       <c r="H930" t="inlineStr">
@@ -32954,7 +33074,7 @@
       </c>
       <c r="I930" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -32966,17 +33086,17 @@
       </c>
       <c r="B931" s="7" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>16897</t>
         </is>
       </c>
       <c r="C931" s="7" t="inlineStr">
         <is>
-          <t>11170187</t>
+          <t>11178959</t>
         </is>
       </c>
       <c r="D931" t="inlineStr">
         <is>
-          <t>ToteBag MxPais</t>
+          <t>WC26CCSS24Puffy</t>
         </is>
       </c>
       <c r="E931" t="inlineStr">
@@ -32991,7 +33111,7 @@
       </c>
       <c r="G931" t="inlineStr">
         <is>
-          <t>lote-01/011170187.jpeg</t>
+          <t>lote-01/011178959.jpeg</t>
         </is>
       </c>
       <c r="H931" t="inlineStr">
@@ -33013,17 +33133,17 @@
       </c>
       <c r="B932" s="7" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>16898</t>
         </is>
       </c>
       <c r="C932" s="7" t="inlineStr">
         <is>
-          <t>11170102</t>
+          <t>11178938</t>
         </is>
       </c>
       <c r="D932" t="inlineStr">
         <is>
-          <t>DiscoveryCDMX</t>
+          <t>Sp26Tu16Mom</t>
         </is>
       </c>
       <c r="E932" t="inlineStr">
@@ -33038,7 +33158,7 @@
       </c>
       <c r="G932" t="inlineStr">
         <is>
-          <t>lote-01/011170102.jpeg</t>
+          <t>lote-01/011178938.jpeg</t>
         </is>
       </c>
       <c r="H932" t="inlineStr">
@@ -33060,17 +33180,17 @@
       </c>
       <c r="B933" s="7" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="C933" s="7" t="inlineStr">
         <is>
-          <t>11176710</t>
+          <t>11178941</t>
         </is>
       </c>
       <c r="D933" t="inlineStr">
         <is>
-          <t>Sp26CC24Dome</t>
+          <t>SII26SS16Studded</t>
         </is>
       </c>
       <c r="E933" t="inlineStr">
@@ -33085,7 +33205,7 @@
       </c>
       <c r="G933" t="inlineStr">
         <is>
-          <t>lote-01/011176710.jpeg</t>
+          <t>lote-01/011178941.jpeg</t>
         </is>
       </c>
       <c r="H933" t="inlineStr">
@@ -33107,17 +33227,17 @@
       </c>
       <c r="B934" s="7" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>16901</t>
         </is>
       </c>
       <c r="C934" s="7" t="inlineStr">
         <is>
-          <t>11170174</t>
+          <t>11178937</t>
         </is>
       </c>
       <c r="D934" t="inlineStr">
         <is>
-          <t>DiscCC24MxPais</t>
+          <t>WC26Mug12Stan</t>
         </is>
       </c>
       <c r="E934" t="inlineStr">
@@ -33132,7 +33252,7 @@
       </c>
       <c r="G934" t="inlineStr">
         <is>
-          <t>lote-01/011170174.jpeg</t>
+          <t>lote-01/011178937.jpeg</t>
         </is>
       </c>
       <c r="H934" t="inlineStr">
@@ -33154,17 +33274,17 @@
       </c>
       <c r="B935" s="7" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="C935" s="7" t="inlineStr">
         <is>
-          <t>11170147</t>
+          <t>11179005</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
         <is>
-          <t>Disc2ozMxPais</t>
+          <t>WC26SS30Pride</t>
         </is>
       </c>
       <c r="E935" t="inlineStr">
@@ -33179,7 +33299,7 @@
       </c>
       <c r="G935" t="inlineStr">
         <is>
-          <t>lote-01/011170147.jpeg</t>
+          <t>lote-01/011179005.jpeg</t>
         </is>
       </c>
       <c r="H935" t="inlineStr">
@@ -33201,17 +33321,17 @@
       </c>
       <c r="B936" s="7" t="inlineStr">
         <is>
-          <t>16689</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="C936" s="7" t="inlineStr">
         <is>
-          <t>11170149</t>
+          <t>11178969</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
         <is>
-          <t>Disc2ozCDMX</t>
+          <t>WC26SS16Pink</t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
@@ -33226,7 +33346,7 @@
       </c>
       <c r="G936" t="inlineStr">
         <is>
-          <t>lote-01/011170149.jpeg</t>
+          <t>lote-01/011178969.jpeg</t>
         </is>
       </c>
       <c r="H936" t="inlineStr">
@@ -33248,17 +33368,17 @@
       </c>
       <c r="B937" s="7" t="inlineStr">
         <is>
-          <t>16879</t>
+          <t>16911</t>
         </is>
       </c>
       <c r="C937" s="7" t="inlineStr">
         <is>
-          <t>11178922</t>
+          <t>11178971</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>WC26Tu16Flower</t>
+          <t>WC26SS16Charm</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
@@ -33273,7 +33393,7 @@
       </c>
       <c r="G937" t="inlineStr">
         <is>
-          <t>lote-01/011178922.jpeg</t>
+          <t>lote-01/011178971.jpeg</t>
         </is>
       </c>
       <c r="H937" t="inlineStr">
@@ -33295,17 +33415,17 @@
       </c>
       <c r="B938" s="7" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="C938" s="7" t="inlineStr">
         <is>
-          <t>11178928</t>
+          <t>11178946</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>WC26CC24Road</t>
+          <t>WC26SS20Twist</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
@@ -33320,7 +33440,7 @@
       </c>
       <c r="G938" t="inlineStr">
         <is>
-          <t>lote-01/011178928.jpeg</t>
+          <t>lote-01/011178946.jpg</t>
         </is>
       </c>
       <c r="H938" t="inlineStr">
@@ -33342,17 +33462,17 @@
       </c>
       <c r="B939" s="7" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16915</t>
         </is>
       </c>
       <c r="C939" s="7" t="inlineStr">
         <is>
-          <t>11178930</t>
+          <t>11178948</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
         <is>
-          <t>WC26CC24Pride</t>
+          <t>WC26StanHand20</t>
         </is>
       </c>
       <c r="E939" t="inlineStr">
@@ -33367,7 +33487,7 @@
       </c>
       <c r="G939" t="inlineStr">
         <is>
-          <t>lote-01/011178930.jpeg</t>
+          <t>lote-01/011178948.jpeg</t>
         </is>
       </c>
       <c r="H939" t="inlineStr">
@@ -33389,17 +33509,17 @@
       </c>
       <c r="B940" s="7" t="inlineStr">
         <is>
-          <t>16898</t>
+          <t>16916</t>
         </is>
       </c>
       <c r="C940" s="7" t="inlineStr">
         <is>
-          <t>11178938</t>
+          <t>11178956</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
         <is>
-          <t>Sp26Tu16Mom</t>
+          <t>SII26Quencher30P</t>
         </is>
       </c>
       <c r="E940" t="inlineStr">
@@ -33414,7 +33534,7 @@
       </c>
       <c r="G940" t="inlineStr">
         <is>
-          <t>lote-01/011178938.jpeg</t>
+          <t>lote-01/011178956.jpeg</t>
         </is>
       </c>
       <c r="H940" t="inlineStr">
@@ -33436,17 +33556,17 @@
       </c>
       <c r="B941" s="7" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="C941" s="7" t="inlineStr">
         <is>
-          <t>11178941</t>
+          <t>11178943</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
         <is>
-          <t>SII26SS16Studded</t>
+          <t>Sp26SS20Orange</t>
         </is>
       </c>
       <c r="E941" t="inlineStr">
@@ -33461,7 +33581,7 @@
       </c>
       <c r="G941" t="inlineStr">
         <is>
-          <t>lote-01/011178941.jpeg</t>
+          <t>lote-01/011178943.jpeg</t>
         </is>
       </c>
       <c r="H941" t="inlineStr">
@@ -33483,17 +33603,17 @@
       </c>
       <c r="B942" s="7" t="inlineStr">
         <is>
-          <t>16901</t>
+          <t>16919</t>
         </is>
       </c>
       <c r="C942" s="7" t="inlineStr">
         <is>
-          <t>11178937</t>
+          <t>11178957</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t>WC26Mug12Stan</t>
+          <t>WC26StanQuen30</t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
@@ -33508,7 +33628,7 @@
       </c>
       <c r="G942" t="inlineStr">
         <is>
-          <t>lote-01/011178937.jpeg</t>
+          <t>lote-01/011178957_1.jpg</t>
         </is>
       </c>
       <c r="H942" t="inlineStr">
@@ -33530,17 +33650,17 @@
       </c>
       <c r="B943" s="7" t="inlineStr">
         <is>
-          <t>16918</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="C943" s="7" t="inlineStr">
         <is>
-          <t>11178943</t>
+          <t>11178935</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
         <is>
-          <t>Sp26SS20Orange</t>
+          <t>SII26Tu10Gam</t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
@@ -33555,7 +33675,7 @@
       </c>
       <c r="G943" t="inlineStr">
         <is>
-          <t>lote-01/011178943.jpeg</t>
+          <t>lote-01/011178935.jpeg</t>
         </is>
       </c>
       <c r="H943" t="inlineStr">
@@ -33577,17 +33697,17 @@
       </c>
       <c r="B944" s="7" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="C944" s="7" t="inlineStr">
         <is>
-          <t>11178935</t>
+          <t>11178919</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t>SII26Tu10Gam</t>
+          <t>Sp26Mug14Mom</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
@@ -33602,7 +33722,7 @@
       </c>
       <c r="G944" t="inlineStr">
         <is>
-          <t>lote-01/011178935.jpeg</t>
+          <t>lote-01/011178919.jpeg</t>
         </is>
       </c>
       <c r="H944" t="inlineStr">
@@ -33624,17 +33744,17 @@
       </c>
       <c r="B945" s="7" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>16924</t>
         </is>
       </c>
       <c r="C945" s="7" t="inlineStr">
         <is>
-          <t>11178919</t>
+          <t>11178945</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>Sp26Mug14Mom</t>
+          <t>WC26Stan20IceF</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
@@ -33649,7 +33769,7 @@
       </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t>lote-01/011178919.jpeg</t>
+          <t>lote-01/011178945.jpeg</t>
         </is>
       </c>
       <c r="H945" t="inlineStr">
@@ -33671,17 +33791,17 @@
       </c>
       <c r="B946" s="7" t="inlineStr">
         <is>
-          <t>16924</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="C946" s="7" t="inlineStr">
         <is>
-          <t>11178945</t>
+          <t>11178973</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>WC26Stan20IceF</t>
+          <t>WC26SS16Lid</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
@@ -33696,7 +33816,7 @@
       </c>
       <c r="G946" t="inlineStr">
         <is>
-          <t>lote-01/011178945.jpeg</t>
+          <t>lote-01/011178973.jpg</t>
         </is>
       </c>
       <c r="H946" t="inlineStr">

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -33910,7 +33910,7 @@
       </c>
       <c r="G948" t="inlineStr">
         <is>
-          <t>lote-01/11186650.jpg</t>
+          <t>lote-01/011186650.jpeg</t>
         </is>
       </c>
       <c r="H948" t="inlineStr">
@@ -33957,7 +33957,7 @@
       </c>
       <c r="G949" t="inlineStr">
         <is>
-          <t>lote-01/11186646.jpg</t>
+          <t>lote-01/011186646.jpeg</t>
         </is>
       </c>
       <c r="H949" t="inlineStr">
@@ -34004,7 +34004,7 @@
       </c>
       <c r="G950" t="inlineStr">
         <is>
-          <t>lote-01/11186658.jpg</t>
+          <t>lote-01/011186658.jpeg</t>
         </is>
       </c>
       <c r="H950" t="inlineStr">
@@ -34051,7 +34051,7 @@
       </c>
       <c r="G951" t="inlineStr">
         <is>
-          <t>lote-01/11186659.jpg</t>
+          <t>lote-01/011186659.jpeg</t>
         </is>
       </c>
       <c r="H951" t="inlineStr">
@@ -35586,7 +35586,7 @@
       </c>
       <c r="B995" s="7" t="inlineStr">
         <is>
-          <t>17359</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="C995" s="7" t="inlineStr"/>
@@ -35607,7 +35607,7 @@
       </c>
       <c r="G995" t="inlineStr">
         <is>
-          <t>lote-01/17359.jpg</t>
+          <t>lote-01/017357.jpeg</t>
         </is>
       </c>
       <c r="H995" t="inlineStr">
@@ -35629,7 +35629,7 @@
       </c>
       <c r="B996" s="7" t="inlineStr">
         <is>
-          <t>17360</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="C996" s="7" t="inlineStr"/>
@@ -35650,7 +35650,7 @@
       </c>
       <c r="G996" t="inlineStr">
         <is>
-          <t>lote-01/17360.jpg</t>
+          <t>lote-01/017358.jpeg</t>
         </is>
       </c>
       <c r="H996" t="inlineStr">
@@ -35672,7 +35672,7 @@
       </c>
       <c r="B997" s="7" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="C997" s="7" t="inlineStr"/>
@@ -35693,7 +35693,7 @@
       </c>
       <c r="G997" t="inlineStr">
         <is>
-          <t>lote-01/17362.jpg</t>
+          <t>lote-01/017359.jpeg</t>
         </is>
       </c>
       <c r="H997" t="inlineStr">

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -19965,17 +19965,17 @@
       </c>
       <c r="B560" s="7" t="inlineStr">
         <is>
-          <t>15857</t>
+          <t>15858</t>
         </is>
       </c>
       <c r="C560" s="7" t="inlineStr">
         <is>
-          <t>11157547</t>
+          <t>11157551</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>CCup Acero SBX Genérico</t>
+          <t>Tumb acero SBX Genérico</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -20000,17 +20000,17 @@
       </c>
       <c r="B561" s="7" t="inlineStr">
         <is>
-          <t>15858</t>
+          <t>15874</t>
         </is>
       </c>
       <c r="C561" s="7" t="inlineStr">
         <is>
-          <t>11157551</t>
+          <t>11161838</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>Tumb acero SBX Genérico</t>
+          <t>CCupPlastic SBX Genérico</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
@@ -20035,17 +20035,17 @@
       </c>
       <c r="B562" s="7" t="inlineStr">
         <is>
-          <t>15874</t>
+          <t>15875</t>
         </is>
       </c>
       <c r="C562" s="7" t="inlineStr">
         <is>
-          <t>11161838</t>
+          <t>11161850</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>CCupPlastic SBX Genérico</t>
+          <t>Llavero SBX Genérico</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
@@ -20070,17 +20070,17 @@
       </c>
       <c r="B563" s="7" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>15876</t>
         </is>
       </c>
       <c r="C563" s="7" t="inlineStr">
         <is>
-          <t>11161850</t>
+          <t>11161839</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
+          <t>CCupPlastic SBX Genérico</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -20105,17 +20105,17 @@
       </c>
       <c r="B564" s="7" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>15877</t>
         </is>
       </c>
       <c r="C564" s="7" t="inlineStr">
         <is>
-          <t>11161839</t>
+          <t>11161846</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>CCupPlastic SBX Genérico</t>
+          <t>Tumb acero SBX Genérico</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
@@ -20140,17 +20140,17 @@
       </c>
       <c r="B565" s="7" t="inlineStr">
         <is>
-          <t>15877</t>
+          <t>15878</t>
         </is>
       </c>
       <c r="C565" s="7" t="inlineStr">
         <is>
-          <t>11161846</t>
+          <t>11161840</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>Tumb acero SBX Genérico</t>
+          <t>CCupPlastic SBX Genérico</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -20175,17 +20175,17 @@
       </c>
       <c r="B566" s="7" t="inlineStr">
         <is>
-          <t>15878</t>
+          <t>15879</t>
         </is>
       </c>
       <c r="C566" s="7" t="inlineStr">
         <is>
-          <t>11161840</t>
+          <t>11161851</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>CCupPlastic SBX Genérico</t>
+          <t>Llavero SBX Genérico</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
@@ -20210,17 +20210,17 @@
       </c>
       <c r="B567" s="7" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>15880</t>
         </is>
       </c>
       <c r="C567" s="7" t="inlineStr">
         <is>
-          <t>11161851</t>
+          <t>11161841</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
+          <t>CCupPlastic SBX Genérico</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -20245,17 +20245,17 @@
       </c>
       <c r="B568" s="7" t="inlineStr">
         <is>
-          <t>15880</t>
+          <t>15881</t>
         </is>
       </c>
       <c r="C568" s="7" t="inlineStr">
         <is>
-          <t>11161841</t>
+          <t>11161847</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>CCupPlastic SBX Genérico</t>
+          <t>Tumb acero SBX Genérico</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
@@ -20280,17 +20280,17 @@
       </c>
       <c r="B569" s="7" t="inlineStr">
         <is>
-          <t>15881</t>
+          <t>15882</t>
         </is>
       </c>
       <c r="C569" s="7" t="inlineStr">
         <is>
-          <t>11161847</t>
+          <t>11161842</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>Tumb acero SBX Genérico</t>
+          <t>CCupPlastic SBX Genérico</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
@@ -20315,17 +20315,17 @@
       </c>
       <c r="B570" s="7" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>15883</t>
         </is>
       </c>
       <c r="C570" s="7" t="inlineStr">
         <is>
-          <t>11161842</t>
+          <t>11161852</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>CCupPlastic SBX Genérico</t>
+          <t>Llavero SBX Genérico</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
@@ -20350,17 +20350,17 @@
       </c>
       <c r="B571" s="7" t="inlineStr">
         <is>
-          <t>15883</t>
+          <t>15884</t>
         </is>
       </c>
       <c r="C571" s="7" t="inlineStr">
         <is>
-          <t>11161852</t>
+          <t>11161843</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
+          <t>CCupPlastic SBX Genérico</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
@@ -20385,17 +20385,17 @@
       </c>
       <c r="B572" s="7" t="inlineStr">
         <is>
-          <t>15884</t>
+          <t>15885</t>
         </is>
       </c>
       <c r="C572" s="7" t="inlineStr">
         <is>
-          <t>11161843</t>
+          <t>11161848</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>CCupPlastic SBX Genérico</t>
+          <t>Tumb acero SBX Genérico</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -20420,17 +20420,17 @@
       </c>
       <c r="B573" s="7" t="inlineStr">
         <is>
-          <t>15885</t>
+          <t>15898</t>
         </is>
       </c>
       <c r="C573" s="7" t="inlineStr">
         <is>
-          <t>11161848</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>Tumb acero SBX Genérico</t>
+          <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -20455,17 +20455,17 @@
       </c>
       <c r="B574" s="7" t="inlineStr">
         <is>
-          <t>15898</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="C574" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11162617</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
+          <t>Tumb Plastic SBX Genérico</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -20490,17 +20490,17 @@
       </c>
       <c r="B575" s="7" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16056</t>
         </is>
       </c>
       <c r="C575" s="7" t="inlineStr">
         <is>
-          <t>11162617</t>
+          <t>11162629</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>Tumb Plastic SBX Genérico</t>
+          <t>Stanley SBX Genérico</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
@@ -20525,17 +20525,17 @@
       </c>
       <c r="B576" s="7" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>16061</t>
         </is>
       </c>
       <c r="C576" s="7" t="inlineStr">
         <is>
-          <t>11162629</t>
+          <t>11162624</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>Stanley SBX Genérico</t>
+          <t>Tumb acero SBX Genérico</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
@@ -20560,17 +20560,17 @@
       </c>
       <c r="B577" s="7" t="inlineStr">
         <is>
-          <t>16061</t>
+          <t>16062</t>
         </is>
       </c>
       <c r="C577" s="7" t="inlineStr">
         <is>
-          <t>11162624</t>
+          <t>11162625</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>Tumb acero SBX Genérico</t>
+          <t>CCup Acero SBX Genérico</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
@@ -20595,12 +20595,12 @@
       </c>
       <c r="B578" s="7" t="inlineStr">
         <is>
-          <t>16062</t>
+          <t>16063</t>
         </is>
       </c>
       <c r="C578" s="7" t="inlineStr">
         <is>
-          <t>11162625</t>
+          <t>11163280</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -20630,17 +20630,17 @@
       </c>
       <c r="B579" s="7" t="inlineStr">
         <is>
-          <t>16063</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="C579" s="7" t="inlineStr">
         <is>
-          <t>11163280</t>
+          <t>11162615</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>CCup Acero SBX Genérico</t>
+          <t>Tazas SBX Genérico</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
@@ -20665,12 +20665,12 @@
       </c>
       <c r="B580" s="7" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>16066</t>
         </is>
       </c>
       <c r="C580" s="7" t="inlineStr">
         <is>
-          <t>11162615</t>
+          <t>11162614</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -20700,17 +20700,17 @@
       </c>
       <c r="B581" s="7" t="inlineStr">
         <is>
-          <t>16066</t>
+          <t>16069</t>
         </is>
       </c>
       <c r="C581" s="7" t="inlineStr">
         <is>
-          <t>11162614</t>
+          <t>11162635</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>Tazas SBX Genérico</t>
+          <t>CCup Acero SBX Genérico</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
@@ -20735,17 +20735,17 @@
       </c>
       <c r="B582" s="7" t="inlineStr">
         <is>
-          <t>16069</t>
+          <t>16078</t>
         </is>
       </c>
       <c r="C582" s="7" t="inlineStr">
         <is>
-          <t>11162635</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>CCup Acero SBX Genérico</t>
+          <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
@@ -20770,7 +20770,7 @@
       </c>
       <c r="B583" s="7" t="inlineStr">
         <is>
-          <t>16078</t>
+          <t>16079</t>
         </is>
       </c>
       <c r="C583" s="7" t="inlineStr">
@@ -20780,7 +20780,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
+          <t>Stoppers SBX Genérico</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
@@ -20805,17 +20805,17 @@
       </c>
       <c r="B584" s="7" t="inlineStr">
         <is>
-          <t>16079</t>
+          <t>16089</t>
         </is>
       </c>
       <c r="C584" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11163285</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>Stoppers SBX Genérico</t>
+          <t>CCup Acero SBX Genérico</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -20840,17 +20840,17 @@
       </c>
       <c r="B585" s="7" t="inlineStr">
         <is>
-          <t>16089</t>
+          <t>16090</t>
         </is>
       </c>
       <c r="C585" s="7" t="inlineStr">
         <is>
-          <t>11163285</t>
+          <t>11163286</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>CCup Acero SBX Genérico</t>
+          <t>CCupPlastic SBX Genérico</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -20875,17 +20875,17 @@
       </c>
       <c r="B586" s="7" t="inlineStr">
         <is>
-          <t>16090</t>
+          <t>16091</t>
         </is>
       </c>
       <c r="C586" s="7" t="inlineStr">
         <is>
-          <t>11163286</t>
+          <t>11163287</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>CCupPlastic SBX Genérico</t>
+          <t>CCup Acero SBX Genérico</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
@@ -20910,12 +20910,12 @@
       </c>
       <c r="B587" s="7" t="inlineStr">
         <is>
-          <t>16091</t>
+          <t>16092</t>
         </is>
       </c>
       <c r="C587" s="7" t="inlineStr">
         <is>
-          <t>11163287</t>
+          <t>11163288</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -20945,17 +20945,17 @@
       </c>
       <c r="B588" s="7" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>16093</t>
         </is>
       </c>
       <c r="C588" s="7" t="inlineStr">
         <is>
-          <t>11163288</t>
+          <t>11163289</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>CCup Acero SBX Genérico</t>
+          <t>Tumb acero SBX Genérico</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -20980,17 +20980,17 @@
       </c>
       <c r="B589" s="7" t="inlineStr">
         <is>
-          <t>16093</t>
+          <t>16094</t>
         </is>
       </c>
       <c r="C589" s="7" t="inlineStr">
         <is>
-          <t>11163289</t>
+          <t>11163290</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>Tumb acero SBX Genérico</t>
+          <t>Tazas SBX Genérico</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
@@ -21015,17 +21015,17 @@
       </c>
       <c r="B590" s="7" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="C590" s="7" t="inlineStr">
         <is>
-          <t>11163290</t>
+          <t>11163293</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>Tazas SBX Genérico</t>
+          <t>Pines SBX Genérico</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
@@ -21050,12 +21050,12 @@
       </c>
       <c r="B591" s="7" t="inlineStr">
         <is>
-          <t>16097</t>
+          <t>16098</t>
         </is>
       </c>
       <c r="C591" s="7" t="inlineStr">
         <is>
-          <t>11163293</t>
+          <t>11163294</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -21085,12 +21085,12 @@
       </c>
       <c r="B592" s="7" t="inlineStr">
         <is>
-          <t>16098</t>
+          <t>16099</t>
         </is>
       </c>
       <c r="C592" s="7" t="inlineStr">
         <is>
-          <t>11163294</t>
+          <t>11163295</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -21120,17 +21120,17 @@
       </c>
       <c r="B593" s="7" t="inlineStr">
         <is>
-          <t>16099</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="C593" s="7" t="inlineStr">
         <is>
-          <t>11163295</t>
+          <t>11160762</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Pines SBX Genérico</t>
+          <t>CCup Acero SBX Genérico</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
@@ -21155,12 +21155,12 @@
       </c>
       <c r="B594" s="7" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="C594" s="7" t="inlineStr">
         <is>
-          <t>11160762</t>
+          <t>11160763</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
@@ -21190,17 +21190,17 @@
       </c>
       <c r="B595" s="7" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="C595" s="7" t="inlineStr">
         <is>
-          <t>11160763</t>
+          <t>11160764</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>CCup Acero SBX Genérico</t>
+          <t>CCupPlastic SBX Genérico</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
@@ -21225,17 +21225,17 @@
       </c>
       <c r="B596" s="7" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="C596" s="7" t="inlineStr">
         <is>
-          <t>11160764</t>
+          <t>11160765</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>CCupPlastic SBX Genérico</t>
+          <t>Tazas SBX Genérico</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
@@ -21260,17 +21260,17 @@
       </c>
       <c r="B597" s="7" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="C597" s="7" t="inlineStr">
         <is>
-          <t>11160765</t>
+          <t>11160766</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>Tazas SBX Genérico</t>
+          <t>Stanley SBX Genérico</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
@@ -21295,17 +21295,17 @@
       </c>
       <c r="B598" s="7" t="inlineStr">
         <is>
-          <t>16105</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="C598" s="7" t="inlineStr">
         <is>
-          <t>11160766</t>
+          <t>11160767</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>Stanley SBX Genérico</t>
+          <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
@@ -21330,17 +21330,17 @@
       </c>
       <c r="B599" s="7" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="C599" s="7" t="inlineStr">
         <is>
-          <t>11160767</t>
+          <t>11160768</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
+          <t>Tote bags SBX Genérico</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
@@ -21365,17 +21365,17 @@
       </c>
       <c r="B600" s="7" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="C600" s="7" t="inlineStr">
         <is>
-          <t>11160768</t>
+          <t>11160769</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Tote bags SBX Genérico</t>
+          <t>Llavero SBX Genérico</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
@@ -21395,22 +21395,22 @@
     <row r="601" ht="24" customHeight="1">
       <c r="A601" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B601" s="7" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>15857</t>
         </is>
       </c>
       <c r="C601" s="7" t="inlineStr">
         <is>
-          <t>11160769</t>
+          <t>11157547</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
+          <t>CCup Acero SBX Genérico</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
@@ -21423,9 +21423,21 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G601" t="inlineStr"/>
-      <c r="H601" t="inlineStr"/>
-      <c r="I601" t="inlineStr"/>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>lote-01/15857.jpeg</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="602" ht="24" customHeight="1">
       <c r="A602" t="inlineStr">
@@ -31861,17 +31873,17 @@
       </c>
       <c r="B900" s="7" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="C900" s="7" t="inlineStr">
         <is>
-          <t>11178934</t>
+          <t>11179003</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>SII26CC24GID</t>
+          <t>Sp26CC24Teach</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
@@ -31896,17 +31908,17 @@
       </c>
       <c r="B901" s="7" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>16896</t>
         </is>
       </c>
       <c r="C901" s="7" t="inlineStr">
         <is>
-          <t>11179003</t>
+          <t>11178970</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>Sp26CC24Teach</t>
+          <t>Sp26SSCC16Band</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
@@ -31931,17 +31943,17 @@
       </c>
       <c r="B902" s="7" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="C902" s="7" t="inlineStr">
         <is>
-          <t>11178970</t>
+          <t>11179004</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>Sp26SSCC16Band</t>
+          <t>Sp26Tu16Teach</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
@@ -31966,17 +31978,17 @@
       </c>
       <c r="B903" s="7" t="inlineStr">
         <is>
-          <t>16899</t>
+          <t>16902</t>
         </is>
       </c>
       <c r="C903" s="7" t="inlineStr">
         <is>
-          <t>11179004</t>
+          <t>11178920</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>Sp26Tu16Teach</t>
+          <t>WC26Tu20Yellow</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
@@ -32001,17 +32013,17 @@
       </c>
       <c r="B904" s="7" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="C904" s="7" t="inlineStr">
         <is>
-          <t>11178920</t>
+          <t>11178926</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>WC26Tu20Yellow</t>
+          <t>Sp26CC24Or</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
@@ -32036,17 +32048,17 @@
       </c>
       <c r="B905" s="7" t="inlineStr">
         <is>
-          <t>16903</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="C905" s="7" t="inlineStr">
         <is>
-          <t>11178926</t>
+          <t>11178965</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>Sp26CC24Or</t>
+          <t>WC26ToteRoad</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
@@ -32071,17 +32083,17 @@
       </c>
       <c r="B906" s="7" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="C906" s="7" t="inlineStr">
         <is>
-          <t>11178965</t>
+          <t>11178966</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>WC26ToteRoad</t>
+          <t>WC26TotePride</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
@@ -32106,17 +32118,17 @@
       </c>
       <c r="B907" s="7" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="C907" s="7" t="inlineStr">
         <is>
-          <t>11178966</t>
+          <t>11187369</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>WC26TotePride</t>
+          <t>WC26BearWC</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
@@ -32141,17 +32153,17 @@
       </c>
       <c r="B908" s="7" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>16909</t>
         </is>
       </c>
       <c r="C908" s="7" t="inlineStr">
         <is>
-          <t>11187369</t>
+          <t>11178944</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>WC26BearWC</t>
+          <t>WC26SS20BTL</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
@@ -32176,17 +32188,17 @@
       </c>
       <c r="B909" s="7" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>16912</t>
         </is>
       </c>
       <c r="C909" s="7" t="inlineStr">
         <is>
-          <t>11178944</t>
+          <t>11178949</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>WC26SS20BTL</t>
+          <t>WC26SS20Pull</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
@@ -32211,17 +32223,17 @@
       </c>
       <c r="B910" s="7" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>16914</t>
         </is>
       </c>
       <c r="C910" s="7" t="inlineStr">
         <is>
-          <t>11178949</t>
+          <t>11178947</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>WC26SS20Pull</t>
+          <t>Sp26StanQuen20</t>
         </is>
       </c>
       <c r="E910" t="inlineStr">
@@ -32246,17 +32258,17 @@
       </c>
       <c r="B911" s="7" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="C911" s="7" t="inlineStr">
         <is>
-          <t>11178947</t>
+          <t>11178972</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>Sp26StanQuen20</t>
+          <t>Sp26Vac16Stan</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
@@ -32281,17 +32293,17 @@
       </c>
       <c r="B912" s="7" t="inlineStr">
         <is>
-          <t>16917</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="C912" s="7" t="inlineStr">
         <is>
-          <t>11178972</t>
+          <t>11178917</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>Sp26Vac16Stan</t>
+          <t>WC26DW12Oran</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
@@ -32316,17 +32328,17 @@
       </c>
       <c r="B913" s="7" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="C913" s="7" t="inlineStr">
         <is>
-          <t>11178917</t>
+          <t>11187370</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>WC26DW12Oran</t>
+          <t>WC26SS16Black</t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
@@ -32351,17 +32363,17 @@
       </c>
       <c r="B914" s="7" t="inlineStr">
         <is>
-          <t>16923</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="C914" s="7" t="inlineStr">
         <is>
-          <t>11178918</t>
+          <t>11187372</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>WC26Gl20Silicone</t>
+          <t>WC26Tu24DW</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
@@ -32386,17 +32398,13 @@
       </c>
       <c r="B915" s="7" t="inlineStr">
         <is>
-          <t>16958</t>
-        </is>
-      </c>
-      <c r="C915" s="7" t="inlineStr">
-        <is>
-          <t>11187370</t>
-        </is>
-      </c>
+          <t>16971</t>
+        </is>
+      </c>
+      <c r="C915" s="7" t="inlineStr"/>
       <c r="D915" t="inlineStr">
         <is>
-          <t>WC26SS16Black</t>
+          <t>WC26BearMex</t>
         </is>
       </c>
       <c r="E915" t="inlineStr">
@@ -32421,17 +32429,17 @@
       </c>
       <c r="B916" s="7" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>16978</t>
         </is>
       </c>
       <c r="C916" s="7" t="inlineStr">
         <is>
-          <t>11187372</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>WC26Tu24DW</t>
+          <t>WC26LlaveroB</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
@@ -32451,18 +32459,22 @@
     <row r="917" ht="24" customHeight="1">
       <c r="A917" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B917" s="7" t="inlineStr">
         <is>
-          <t>16971</t>
-        </is>
-      </c>
-      <c r="C917" s="7" t="inlineStr"/>
+          <t>16531</t>
+        </is>
+      </c>
+      <c r="C917" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>WC26BearMex</t>
+          <t>Sp26NEBlack</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
@@ -32475,19 +32487,31 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G917" t="inlineStr"/>
-      <c r="H917" t="inlineStr"/>
-      <c r="I917" t="inlineStr"/>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>lote-01/16531.jpeg</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="918" ht="24" customHeight="1">
       <c r="A918" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B918" s="7" t="inlineStr">
         <is>
-          <t>16978</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="C918" s="7" t="inlineStr">
@@ -32497,7 +32521,7 @@
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>WC26LlaveroB</t>
+          <t>Sp26NECrossB</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
@@ -32510,9 +32534,21 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G918" t="inlineStr"/>
-      <c r="H918" t="inlineStr"/>
-      <c r="I918" t="inlineStr"/>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>lote-01/16532.jpeg</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="919" ht="24" customHeight="1">
       <c r="A919" t="inlineStr">
@@ -32522,17 +32558,17 @@
       </c>
       <c r="B919" s="7" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="C919" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11170187</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>Sp26NEBlack</t>
+          <t>ToteBag MxPais</t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
@@ -32547,7 +32583,7 @@
       </c>
       <c r="G919" t="inlineStr">
         <is>
-          <t>lote-01/16531.jpeg</t>
+          <t>lote-01/011170187.jpeg</t>
         </is>
       </c>
       <c r="H919" t="inlineStr">
@@ -32557,7 +32593,7 @@
       </c>
       <c r="I919" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -32569,17 +32605,17 @@
       </c>
       <c r="B920" s="7" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="C920" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11170102</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>Sp26NECrossB</t>
+          <t>DiscoveryCDMX</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
@@ -32594,7 +32630,7 @@
       </c>
       <c r="G920" t="inlineStr">
         <is>
-          <t>lote-01/16532.jpeg</t>
+          <t>lote-01/011170102.jpeg</t>
         </is>
       </c>
       <c r="H920" t="inlineStr">
@@ -32604,7 +32640,7 @@
       </c>
       <c r="I920" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -32616,17 +32652,17 @@
       </c>
       <c r="B921" s="7" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="C921" s="7" t="inlineStr">
         <is>
-          <t>11170187</t>
+          <t>11176710</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>ToteBag MxPais</t>
+          <t>Sp26CC24Dome</t>
         </is>
       </c>
       <c r="E921" t="inlineStr">
@@ -32641,7 +32677,7 @@
       </c>
       <c r="G921" t="inlineStr">
         <is>
-          <t>lote-01/011170187.jpeg</t>
+          <t>lote-01/011176710.jpeg</t>
         </is>
       </c>
       <c r="H921" t="inlineStr">
@@ -32663,17 +32699,17 @@
       </c>
       <c r="B922" s="7" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="C922" s="7" t="inlineStr">
         <is>
-          <t>11170102</t>
+          <t>11170174</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>DiscoveryCDMX</t>
+          <t>DiscCC24MxPais</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
@@ -32688,7 +32724,7 @@
       </c>
       <c r="G922" t="inlineStr">
         <is>
-          <t>lote-01/011170102.jpeg</t>
+          <t>lote-01/011170174.jpeg</t>
         </is>
       </c>
       <c r="H922" t="inlineStr">
@@ -32710,17 +32746,17 @@
       </c>
       <c r="B923" s="7" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="C923" s="7" t="inlineStr">
         <is>
-          <t>11176710</t>
+          <t>11170147</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>Sp26CC24Dome</t>
+          <t>Disc2ozMxPais</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
@@ -32735,7 +32771,7 @@
       </c>
       <c r="G923" t="inlineStr">
         <is>
-          <t>lote-01/011176710.jpeg</t>
+          <t>lote-01/011170147.jpeg</t>
         </is>
       </c>
       <c r="H923" t="inlineStr">
@@ -32757,17 +32793,17 @@
       </c>
       <c r="B924" s="7" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="C924" s="7" t="inlineStr">
         <is>
-          <t>11170174</t>
+          <t>11170149</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>DiscCC24MxPais</t>
+          <t>Disc2ozCDMX</t>
         </is>
       </c>
       <c r="E924" t="inlineStr">
@@ -32782,7 +32818,7 @@
       </c>
       <c r="G924" t="inlineStr">
         <is>
-          <t>lote-01/011170174.jpeg</t>
+          <t>lote-01/011170149.jpeg</t>
         </is>
       </c>
       <c r="H924" t="inlineStr">
@@ -32804,17 +32840,17 @@
       </c>
       <c r="B925" s="7" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="C925" s="7" t="inlineStr">
         <is>
-          <t>11170147</t>
+          <t>11178952</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>Disc2ozMxPais</t>
+          <t>WC26SSCC24Grad</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
@@ -32829,7 +32865,7 @@
       </c>
       <c r="G925" t="inlineStr">
         <is>
-          <t>lote-01/011170147.jpeg</t>
+          <t>lote-01/011178952.jpeg</t>
         </is>
       </c>
       <c r="H925" t="inlineStr">
@@ -32851,17 +32887,17 @@
       </c>
       <c r="B926" s="7" t="inlineStr">
         <is>
-          <t>16689</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="C926" s="7" t="inlineStr">
         <is>
-          <t>11170149</t>
+          <t>11178922</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>Disc2ozCDMX</t>
+          <t>WC26Tu16Flower</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
@@ -32876,7 +32912,7 @@
       </c>
       <c r="G926" t="inlineStr">
         <is>
-          <t>lote-01/011170149.jpeg</t>
+          <t>lote-01/011178922.jpeg</t>
         </is>
       </c>
       <c r="H926" t="inlineStr">
@@ -32898,17 +32934,17 @@
       </c>
       <c r="B927" s="7" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>16880</t>
         </is>
       </c>
       <c r="C927" s="7" t="inlineStr">
         <is>
-          <t>11178952</t>
+          <t>11178928</t>
         </is>
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>WC26SSCC24Grad</t>
+          <t>WC26CC24Road</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
@@ -32923,7 +32959,7 @@
       </c>
       <c r="G927" t="inlineStr">
         <is>
-          <t>lote-01/011178952.jpeg</t>
+          <t>lote-01/011178928.jpeg</t>
         </is>
       </c>
       <c r="H927" t="inlineStr">
@@ -32945,17 +32981,17 @@
       </c>
       <c r="B928" s="7" t="inlineStr">
         <is>
-          <t>16879</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="C928" s="7" t="inlineStr">
         <is>
-          <t>11178922</t>
+          <t>11178930</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>WC26Tu16Flower</t>
+          <t>WC26CC24Pride</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
@@ -32970,7 +33006,7 @@
       </c>
       <c r="G928" t="inlineStr">
         <is>
-          <t>lote-01/011178922.jpeg</t>
+          <t>lote-01/011178930.jpeg</t>
         </is>
       </c>
       <c r="H928" t="inlineStr">
@@ -32992,17 +33028,17 @@
       </c>
       <c r="B929" s="7" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="C929" s="7" t="inlineStr">
         <is>
-          <t>11178928</t>
+          <t>11178934</t>
         </is>
       </c>
       <c r="D929" t="inlineStr">
         <is>
-          <t>WC26CC24Road</t>
+          <t>SII26CC24GID</t>
         </is>
       </c>
       <c r="E929" t="inlineStr">
@@ -33017,7 +33053,7 @@
       </c>
       <c r="G929" t="inlineStr">
         <is>
-          <t>lote-01/011178928.jpeg</t>
+          <t>lote-01/16884.jpeg</t>
         </is>
       </c>
       <c r="H929" t="inlineStr">
@@ -33027,7 +33063,7 @@
       </c>
       <c r="I929" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -33039,17 +33075,17 @@
       </c>
       <c r="B930" s="7" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16897</t>
         </is>
       </c>
       <c r="C930" s="7" t="inlineStr">
         <is>
-          <t>11178930</t>
+          <t>11178959</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t>WC26CC24Pride</t>
+          <t>WC26CCSS24Puffy</t>
         </is>
       </c>
       <c r="E930" t="inlineStr">
@@ -33064,7 +33100,7 @@
       </c>
       <c r="G930" t="inlineStr">
         <is>
-          <t>lote-01/011178930.jpeg</t>
+          <t>lote-01/011178959.jpeg</t>
         </is>
       </c>
       <c r="H930" t="inlineStr">
@@ -33086,17 +33122,17 @@
       </c>
       <c r="B931" s="7" t="inlineStr">
         <is>
-          <t>16897</t>
+          <t>16898</t>
         </is>
       </c>
       <c r="C931" s="7" t="inlineStr">
         <is>
-          <t>11178959</t>
+          <t>11178938</t>
         </is>
       </c>
       <c r="D931" t="inlineStr">
         <is>
-          <t>WC26CCSS24Puffy</t>
+          <t>Sp26Tu16Mom</t>
         </is>
       </c>
       <c r="E931" t="inlineStr">
@@ -33111,7 +33147,7 @@
       </c>
       <c r="G931" t="inlineStr">
         <is>
-          <t>lote-01/011178959.jpeg</t>
+          <t>lote-01/011178938.jpeg</t>
         </is>
       </c>
       <c r="H931" t="inlineStr">
@@ -33133,17 +33169,17 @@
       </c>
       <c r="B932" s="7" t="inlineStr">
         <is>
-          <t>16898</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="C932" s="7" t="inlineStr">
         <is>
-          <t>11178938</t>
+          <t>11178941</t>
         </is>
       </c>
       <c r="D932" t="inlineStr">
         <is>
-          <t>Sp26Tu16Mom</t>
+          <t>SII26SS16Studded</t>
         </is>
       </c>
       <c r="E932" t="inlineStr">
@@ -33158,7 +33194,7 @@
       </c>
       <c r="G932" t="inlineStr">
         <is>
-          <t>lote-01/011178938.jpeg</t>
+          <t>lote-01/011178941.jpeg</t>
         </is>
       </c>
       <c r="H932" t="inlineStr">
@@ -33180,17 +33216,17 @@
       </c>
       <c r="B933" s="7" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>16901</t>
         </is>
       </c>
       <c r="C933" s="7" t="inlineStr">
         <is>
-          <t>11178941</t>
+          <t>11178937</t>
         </is>
       </c>
       <c r="D933" t="inlineStr">
         <is>
-          <t>SII26SS16Studded</t>
+          <t>WC26Mug12Stan</t>
         </is>
       </c>
       <c r="E933" t="inlineStr">
@@ -33205,7 +33241,7 @@
       </c>
       <c r="G933" t="inlineStr">
         <is>
-          <t>lote-01/011178941.jpeg</t>
+          <t>lote-01/011178937.jpeg</t>
         </is>
       </c>
       <c r="H933" t="inlineStr">
@@ -33227,17 +33263,17 @@
       </c>
       <c r="B934" s="7" t="inlineStr">
         <is>
-          <t>16901</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="C934" s="7" t="inlineStr">
         <is>
-          <t>11178937</t>
+          <t>11179005</t>
         </is>
       </c>
       <c r="D934" t="inlineStr">
         <is>
-          <t>WC26Mug12Stan</t>
+          <t>WC26SS30Pride</t>
         </is>
       </c>
       <c r="E934" t="inlineStr">
@@ -33252,7 +33288,7 @@
       </c>
       <c r="G934" t="inlineStr">
         <is>
-          <t>lote-01/011178937.jpeg</t>
+          <t>lote-01/011179005.jpeg</t>
         </is>
       </c>
       <c r="H934" t="inlineStr">
@@ -33274,17 +33310,17 @@
       </c>
       <c r="B935" s="7" t="inlineStr">
         <is>
-          <t>16906</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="C935" s="7" t="inlineStr">
         <is>
-          <t>11179005</t>
+          <t>11178969</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
         <is>
-          <t>WC26SS30Pride</t>
+          <t>WC26SS16Pink</t>
         </is>
       </c>
       <c r="E935" t="inlineStr">
@@ -33299,7 +33335,7 @@
       </c>
       <c r="G935" t="inlineStr">
         <is>
-          <t>lote-01/011179005.jpeg</t>
+          <t>lote-01/011178969.jpeg</t>
         </is>
       </c>
       <c r="H935" t="inlineStr">
@@ -33321,17 +33357,17 @@
       </c>
       <c r="B936" s="7" t="inlineStr">
         <is>
-          <t>16910</t>
+          <t>16911</t>
         </is>
       </c>
       <c r="C936" s="7" t="inlineStr">
         <is>
-          <t>11178969</t>
+          <t>11178971</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
         <is>
-          <t>WC26SS16Pink</t>
+          <t>WC26SS16Charm</t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
@@ -33346,7 +33382,7 @@
       </c>
       <c r="G936" t="inlineStr">
         <is>
-          <t>lote-01/011178969.jpeg</t>
+          <t>lote-01/011178971.jpeg</t>
         </is>
       </c>
       <c r="H936" t="inlineStr">
@@ -33368,17 +33404,17 @@
       </c>
       <c r="B937" s="7" t="inlineStr">
         <is>
-          <t>16911</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="C937" s="7" t="inlineStr">
         <is>
-          <t>11178971</t>
+          <t>11178946</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>WC26SS16Charm</t>
+          <t>WC26SS20Twist</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
@@ -33393,7 +33429,7 @@
       </c>
       <c r="G937" t="inlineStr">
         <is>
-          <t>lote-01/011178971.jpeg</t>
+          <t>lote-01/011178946.jpg</t>
         </is>
       </c>
       <c r="H937" t="inlineStr">
@@ -33415,17 +33451,17 @@
       </c>
       <c r="B938" s="7" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>16915</t>
         </is>
       </c>
       <c r="C938" s="7" t="inlineStr">
         <is>
-          <t>11178946</t>
+          <t>11178948</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>WC26SS20Twist</t>
+          <t>WC26StanHand20</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
@@ -33440,7 +33476,7 @@
       </c>
       <c r="G938" t="inlineStr">
         <is>
-          <t>lote-01/011178946.jpg</t>
+          <t>lote-01/011178948.jpeg</t>
         </is>
       </c>
       <c r="H938" t="inlineStr">
@@ -33462,17 +33498,17 @@
       </c>
       <c r="B939" s="7" t="inlineStr">
         <is>
-          <t>16915</t>
+          <t>16916</t>
         </is>
       </c>
       <c r="C939" s="7" t="inlineStr">
         <is>
-          <t>11178948</t>
+          <t>11178956</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
         <is>
-          <t>WC26StanHand20</t>
+          <t>SII26Quencher30P</t>
         </is>
       </c>
       <c r="E939" t="inlineStr">
@@ -33487,7 +33523,7 @@
       </c>
       <c r="G939" t="inlineStr">
         <is>
-          <t>lote-01/011178948.jpeg</t>
+          <t>lote-01/011178956.jpeg</t>
         </is>
       </c>
       <c r="H939" t="inlineStr">
@@ -33509,17 +33545,17 @@
       </c>
       <c r="B940" s="7" t="inlineStr">
         <is>
-          <t>16916</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="C940" s="7" t="inlineStr">
         <is>
-          <t>11178956</t>
+          <t>11178943</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
         <is>
-          <t>SII26Quencher30P</t>
+          <t>Sp26SS20Orange</t>
         </is>
       </c>
       <c r="E940" t="inlineStr">
@@ -33534,7 +33570,7 @@
       </c>
       <c r="G940" t="inlineStr">
         <is>
-          <t>lote-01/011178956.jpeg</t>
+          <t>lote-01/011178943.jpeg</t>
         </is>
       </c>
       <c r="H940" t="inlineStr">
@@ -33556,17 +33592,17 @@
       </c>
       <c r="B941" s="7" t="inlineStr">
         <is>
-          <t>16918</t>
+          <t>16919</t>
         </is>
       </c>
       <c r="C941" s="7" t="inlineStr">
         <is>
-          <t>11178943</t>
+          <t>11178957</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
         <is>
-          <t>Sp26SS20Orange</t>
+          <t>WC26StanQuen30</t>
         </is>
       </c>
       <c r="E941" t="inlineStr">
@@ -33581,7 +33617,7 @@
       </c>
       <c r="G941" t="inlineStr">
         <is>
-          <t>lote-01/011178943.jpeg</t>
+          <t>lote-01/011178957_1.jpg</t>
         </is>
       </c>
       <c r="H941" t="inlineStr">
@@ -33603,17 +33639,17 @@
       </c>
       <c r="B942" s="7" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="C942" s="7" t="inlineStr">
         <is>
-          <t>11178957</t>
+          <t>11178935</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t>WC26StanQuen30</t>
+          <t>SII26Tu10Gam</t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
@@ -33628,7 +33664,7 @@
       </c>
       <c r="G942" t="inlineStr">
         <is>
-          <t>lote-01/011178957_1.jpg</t>
+          <t>lote-01/011178935.jpeg</t>
         </is>
       </c>
       <c r="H942" t="inlineStr">
@@ -33650,17 +33686,17 @@
       </c>
       <c r="B943" s="7" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="C943" s="7" t="inlineStr">
         <is>
-          <t>11178935</t>
+          <t>11178919</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
         <is>
-          <t>SII26Tu10Gam</t>
+          <t>Sp26Mug14Mom</t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
@@ -33675,7 +33711,7 @@
       </c>
       <c r="G943" t="inlineStr">
         <is>
-          <t>lote-01/011178935.jpeg</t>
+          <t>lote-01/011178919.jpeg</t>
         </is>
       </c>
       <c r="H943" t="inlineStr">
@@ -33697,17 +33733,17 @@
       </c>
       <c r="B944" s="7" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>16923</t>
         </is>
       </c>
       <c r="C944" s="7" t="inlineStr">
         <is>
-          <t>11178919</t>
+          <t>11178918</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t>Sp26Mug14Mom</t>
+          <t>WC26Gl20Silicone</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
@@ -33722,7 +33758,7 @@
       </c>
       <c r="G944" t="inlineStr">
         <is>
-          <t>lote-01/011178919.jpeg</t>
+          <t>lote-01/16923.jpeg</t>
         </is>
       </c>
       <c r="H944" t="inlineStr">
@@ -33732,7 +33768,7 @@
       </c>
       <c r="I944" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Control de fotos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Control de fotos'!$A$7:$I$1081</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Control de fotos'!$A$7:$I$1082</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -220,8 +220,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ControlFotosCodigoDia" displayName="ControlFotosCodigoDia" ref="A7:I1081" headerRowCount="1">
-  <autoFilter ref="A7:I1081"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ControlFotosCodigoDia" displayName="ControlFotosCodigoDia" ref="A7:I1082" headerRowCount="1">
+  <autoFilter ref="A7:I1082"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ESTADO FOTO"/>
     <tableColumn id="2" name="CÓDIGO DÍA"/>
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1081"/>
+  <dimension ref="A1:I1082"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -575,17 +575,17 @@
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <f>COUNTA(B8:B1081)</f>
+        <f>COUNTA(B8:B1082)</f>
         <v/>
       </c>
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="3">
-        <f>COUNTIF(A8:A1081,"CON FOTO")</f>
+        <f>COUNTIF(A8:A1082,"CON FOTO")</f>
         <v/>
       </c>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3">
-        <f>COUNTIF(A8:A1081,"FALTA FOTO")</f>
+        <f>COUNTIF(A8:A1082,"FALTA FOTO")</f>
         <v/>
       </c>
       <c r="F4" s="3" t="n"/>
@@ -23788,13 +23788,13 @@
       </c>
       <c r="B669" s="7" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>11812</t>
         </is>
       </c>
       <c r="C669" s="7" t="inlineStr"/>
       <c r="D669" t="inlineStr">
         <is>
-          <t>ESS Reusable cup</t>
+          <t>Been There Merida 14 oz</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
@@ -23819,13 +23819,13 @@
       </c>
       <c r="B670" s="7" t="inlineStr">
         <is>
-          <t>11812</t>
+          <t>11830</t>
         </is>
       </c>
       <c r="C670" s="7" t="inlineStr"/>
       <c r="D670" t="inlineStr">
         <is>
-          <t>Been There Merida 14 oz</t>
+          <t>Been There Puerto Vallarta 14 oz</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
@@ -23850,13 +23850,13 @@
       </c>
       <c r="B671" s="7" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>11831</t>
         </is>
       </c>
       <c r="C671" s="7" t="inlineStr"/>
       <c r="D671" t="inlineStr">
         <is>
-          <t>Been There Puerto Vallarta 14 oz</t>
+          <t>Been There Cancun 14 oz</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
@@ -23881,13 +23881,13 @@
       </c>
       <c r="B672" s="7" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>11832</t>
         </is>
       </c>
       <c r="C672" s="7" t="inlineStr"/>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Been There Cancun 14 oz</t>
+          <t>Been There Guanajuato 14 oz</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
@@ -23912,13 +23912,13 @@
       </c>
       <c r="B673" s="7" t="inlineStr">
         <is>
-          <t>11832</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="C673" s="7" t="inlineStr"/>
       <c r="D673" t="inlineStr">
         <is>
-          <t>Been There Guanajuato 14 oz</t>
+          <t>Been There Tulum 14 oz</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
@@ -23943,13 +23943,13 @@
       </c>
       <c r="B674" s="7" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="C674" s="7" t="inlineStr"/>
       <c r="D674" t="inlineStr">
         <is>
-          <t>Been There Tulum 14 oz</t>
+          <t>Been There Mazatlan 14 oz</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
@@ -23974,13 +23974,17 @@
       </c>
       <c r="B675" s="7" t="inlineStr">
         <is>
-          <t>12096</t>
-        </is>
-      </c>
-      <c r="C675" s="7" t="inlineStr"/>
+          <t>12981</t>
+        </is>
+      </c>
+      <c r="C675" s="7" t="inlineStr">
+        <is>
+          <t>11115533</t>
+        </is>
+      </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Been There Mazatlan 14 oz</t>
+          <t>COR25 CC24Siren</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
@@ -24005,17 +24009,13 @@
       </c>
       <c r="B676" s="7" t="inlineStr">
         <is>
-          <t>12981</t>
-        </is>
-      </c>
-      <c r="C676" s="7" t="inlineStr">
-        <is>
-          <t>11115533</t>
-        </is>
-      </c>
+          <t>13694</t>
+        </is>
+      </c>
+      <c r="C676" s="7" t="inlineStr"/>
       <c r="D676" t="inlineStr">
         <is>
-          <t>COR25 CC24Siren</t>
+          <t>Filtros Chemex</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
@@ -24040,13 +24040,17 @@
       </c>
       <c r="B677" s="7" t="inlineStr">
         <is>
-          <t>13694</t>
-        </is>
-      </c>
-      <c r="C677" s="7" t="inlineStr"/>
+          <t>14882</t>
+        </is>
+      </c>
+      <c r="C677" s="7" t="inlineStr">
+        <is>
+          <t>11141066</t>
+        </is>
+      </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>Filtros Chemex</t>
+          <t>COR23 ReuHotCup</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
@@ -24071,17 +24075,17 @@
       </c>
       <c r="B678" s="7" t="inlineStr">
         <is>
-          <t>14882</t>
+          <t>14883</t>
         </is>
       </c>
       <c r="C678" s="7" t="inlineStr">
         <is>
-          <t>11141066</t>
+          <t>11141067</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>COR23 ReuHotCup</t>
+          <t>COR23 ReusCC16</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
@@ -24106,17 +24110,17 @@
       </c>
       <c r="B679" s="7" t="inlineStr">
         <is>
-          <t>14883</t>
+          <t>14884</t>
         </is>
       </c>
       <c r="C679" s="7" t="inlineStr">
         <is>
-          <t>11141067</t>
+          <t>11141089</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>COR23 ReusCC16</t>
+          <t>COR23 ReusCC24</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
@@ -24141,17 +24145,17 @@
       </c>
       <c r="B680" s="7" t="inlineStr">
         <is>
-          <t>14884</t>
+          <t>14885</t>
         </is>
       </c>
       <c r="C680" s="7" t="inlineStr">
         <is>
-          <t>11141089</t>
+          <t>11141050</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>COR23 ReusCC24</t>
+          <t>COR23 Tz14 Rain</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
@@ -24176,17 +24180,17 @@
       </c>
       <c r="B681" s="7" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>14886</t>
         </is>
       </c>
       <c r="C681" s="7" t="inlineStr">
         <is>
-          <t>11141050</t>
+          <t>11141051</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>COR23 Tz14 Rain</t>
+          <t>COR23 Tz14Green</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
@@ -24211,17 +24215,17 @@
       </c>
       <c r="B682" s="7" t="inlineStr">
         <is>
-          <t>14886</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="C682" s="7" t="inlineStr">
         <is>
-          <t>11141051</t>
+          <t>11141100</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>COR23 Tz14Green</t>
+          <t>COR23 GlCC18 Omb</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
@@ -24246,17 +24250,17 @@
       </c>
       <c r="B683" s="7" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14917</t>
         </is>
       </c>
       <c r="C683" s="7" t="inlineStr">
         <is>
-          <t>11141100</t>
+          <t>11141045</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>COR23 GlCC18 Omb</t>
+          <t>COR23 DW12 Green</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
@@ -24281,17 +24285,17 @@
       </c>
       <c r="B684" s="7" t="inlineStr">
         <is>
-          <t>14917</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="C684" s="7" t="inlineStr">
         <is>
-          <t>11141045</t>
+          <t>11141076</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>COR23 DW12 Green</t>
+          <t>COR23 Tu20STBlck</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
@@ -24316,17 +24320,17 @@
       </c>
       <c r="B685" s="7" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>14920</t>
         </is>
       </c>
       <c r="C685" s="7" t="inlineStr">
         <is>
-          <t>11141076</t>
+          <t>11141112</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>COR23 Tu20STBlck</t>
+          <t>COR23 SS16ToneB</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -24351,17 +24355,17 @@
       </c>
       <c r="B686" s="7" t="inlineStr">
         <is>
-          <t>14920</t>
+          <t>14921</t>
         </is>
       </c>
       <c r="C686" s="7" t="inlineStr">
         <is>
-          <t>11141112</t>
+          <t>11141115</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>COR23 SS16ToneB</t>
+          <t>COR23 SS16 ThruL</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
@@ -24386,17 +24390,17 @@
       </c>
       <c r="B687" s="7" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>14922</t>
         </is>
       </c>
       <c r="C687" s="7" t="inlineStr">
         <is>
-          <t>11141115</t>
+          <t>11141117</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>COR23 SS16 ThruL</t>
+          <t>COR23 SS20Copper</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
@@ -24421,17 +24425,17 @@
       </c>
       <c r="B688" s="7" t="inlineStr">
         <is>
-          <t>14922</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="C688" s="7" t="inlineStr">
         <is>
-          <t>11141117</t>
+          <t>11141127</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>COR23 SS20Copper</t>
+          <t>COR23 SS20StQuen</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
@@ -24456,17 +24460,17 @@
       </c>
       <c r="B689" s="7" t="inlineStr">
         <is>
-          <t>14923</t>
+          <t>14924</t>
         </is>
       </c>
       <c r="C689" s="7" t="inlineStr">
         <is>
-          <t>11141127</t>
+          <t>11141113</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>COR23 SS20StQuen</t>
+          <t>COR23 SS16StSwi</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
@@ -24491,17 +24495,17 @@
       </c>
       <c r="B690" s="7" t="inlineStr">
         <is>
-          <t>14924</t>
+          <t>14925</t>
         </is>
       </c>
       <c r="C690" s="7" t="inlineStr">
         <is>
-          <t>11141113</t>
+          <t>11141134</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>COR23 SS16StSwi</t>
+          <t>COR23 SS25StyBTL</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
@@ -24526,17 +24530,17 @@
       </c>
       <c r="B691" s="7" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>14926</t>
         </is>
       </c>
       <c r="C691" s="7" t="inlineStr">
         <is>
-          <t>11141134</t>
+          <t>11141189</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>COR23 SS25StyBTL</t>
+          <t>COR23 ToteBag</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
@@ -24561,17 +24565,17 @@
       </c>
       <c r="B692" s="7" t="inlineStr">
         <is>
-          <t>14926</t>
+          <t>14927</t>
         </is>
       </c>
       <c r="C692" s="7" t="inlineStr">
         <is>
-          <t>11141189</t>
+          <t>11141041</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>COR23 ToteBag</t>
+          <t>COR23 Pour Over</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
@@ -24596,17 +24600,17 @@
       </c>
       <c r="B693" s="7" t="inlineStr">
         <is>
-          <t>14927</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="C693" s="7" t="inlineStr">
         <is>
-          <t>11141041</t>
+          <t>11141095</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>COR23 Pour Over</t>
+          <t>COR23 Cold Brew</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
@@ -24631,17 +24635,17 @@
       </c>
       <c r="B694" s="7" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="C694" s="7" t="inlineStr">
         <is>
-          <t>11141095</t>
+          <t>11141040</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>COR23 Cold Brew</t>
+          <t>COR23 PrensaFran</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
@@ -24666,17 +24670,17 @@
       </c>
       <c r="B695" s="7" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t>15191</t>
         </is>
       </c>
       <c r="C695" s="7" t="inlineStr">
         <is>
-          <t>11141040</t>
+          <t>11144107</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>COR23 PrensaFran</t>
+          <t>COR23 CC24 Green</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
@@ -24701,17 +24705,17 @@
       </c>
       <c r="B696" s="7" t="inlineStr">
         <is>
-          <t>15191</t>
+          <t>15192</t>
         </is>
       </c>
       <c r="C696" s="7" t="inlineStr">
         <is>
-          <t>11144107</t>
+          <t>11144117</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>COR23 CC24 Green</t>
+          <t>COR23 Mug20 Stan</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
@@ -24736,17 +24740,13 @@
       </c>
       <c r="B697" s="7" t="inlineStr">
         <is>
-          <t>15192</t>
-        </is>
-      </c>
-      <c r="C697" s="7" t="inlineStr">
-        <is>
-          <t>11144117</t>
-        </is>
-      </c>
+          <t>15743</t>
+        </is>
+      </c>
+      <c r="C697" s="7" t="inlineStr"/>
       <c r="D697" t="inlineStr">
         <is>
-          <t>COR23 Mug20 Stan</t>
+          <t>ResSetCT3Pck</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
@@ -24771,13 +24771,13 @@
       </c>
       <c r="B698" s="7" t="inlineStr">
         <is>
-          <t>15743</t>
+          <t>15746</t>
         </is>
       </c>
       <c r="C698" s="7" t="inlineStr"/>
       <c r="D698" t="inlineStr">
         <is>
-          <t>ResSetCT3Pck</t>
+          <t>ResMug12SSCopper</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
@@ -24802,13 +24802,13 @@
       </c>
       <c r="B699" s="7" t="inlineStr">
         <is>
-          <t>15746</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="C699" s="7" t="inlineStr"/>
       <c r="D699" t="inlineStr">
         <is>
-          <t>ResMug12SSCopper</t>
+          <t>Res SS16GoldShin</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
@@ -24833,13 +24833,13 @@
       </c>
       <c r="B700" s="7" t="inlineStr">
         <is>
-          <t>15793</t>
+          <t>15794</t>
         </is>
       </c>
       <c r="C700" s="7" t="inlineStr"/>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Res SS16GoldShin</t>
+          <t>ResSS16BananaLea</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
@@ -24864,13 +24864,13 @@
       </c>
       <c r="B701" s="7" t="inlineStr">
         <is>
-          <t>15794</t>
+          <t>15886</t>
         </is>
       </c>
       <c r="C701" s="7" t="inlineStr"/>
       <c r="D701" t="inlineStr">
         <is>
-          <t>ResSS16BananaLea</t>
+          <t>BTTu16Mex</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
@@ -24895,13 +24895,17 @@
       </c>
       <c r="B702" s="7" t="inlineStr">
         <is>
-          <t>15886</t>
-        </is>
-      </c>
-      <c r="C702" s="7" t="inlineStr"/>
+          <t>15967</t>
+        </is>
+      </c>
+      <c r="C702" s="7" t="inlineStr">
+        <is>
+          <t>11161004</t>
+        </is>
+      </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>BTTu16Mex</t>
+          <t>Wt25CrarryingBag</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
@@ -24926,17 +24930,17 @@
       </c>
       <c r="B703" s="7" t="inlineStr">
         <is>
-          <t>15967</t>
+          <t>16052</t>
         </is>
       </c>
       <c r="C703" s="7" t="inlineStr">
         <is>
-          <t>11161004</t>
+          <t>11162618</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>Wt25CrarryingBag</t>
+          <t>SI25ReusTierra</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
@@ -24961,17 +24965,17 @@
       </c>
       <c r="B704" s="7" t="inlineStr">
         <is>
-          <t>16052</t>
+          <t>16053</t>
         </is>
       </c>
       <c r="C704" s="7" t="inlineStr">
         <is>
-          <t>11162618</t>
+          <t>11162640</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>SI25ReusTierra</t>
+          <t>SI25CCReusTierra</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
@@ -24996,17 +25000,17 @@
       </c>
       <c r="B705" s="7" t="inlineStr">
         <is>
-          <t>16053</t>
+          <t>16080</t>
         </is>
       </c>
       <c r="C705" s="7" t="inlineStr">
         <is>
-          <t>11162640</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>SI25CCReusTierra</t>
+          <t>SII25BdayStopper</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
@@ -25031,7 +25035,7 @@
       </c>
       <c r="B706" s="7" t="inlineStr">
         <is>
-          <t>16080</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="C706" s="7" t="inlineStr">
@@ -25041,7 +25045,7 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>SII25BdayStopper</t>
+          <t>SII25ClipBoyB</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
@@ -25066,7 +25070,7 @@
       </c>
       <c r="B707" s="7" t="inlineStr">
         <is>
-          <t>16081</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="C707" s="7" t="inlineStr">
@@ -25076,7 +25080,7 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>SII25ClipBoyB</t>
+          <t>SII25ClipGirlB</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
@@ -25101,17 +25105,17 @@
       </c>
       <c r="B708" s="7" t="inlineStr">
         <is>
-          <t>16082</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="C708" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11160779</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>SII25ClipGirlB</t>
+          <t>Sp25StopperP</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
@@ -25136,17 +25140,17 @@
       </c>
       <c r="B709" s="7" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="C709" s="7" t="inlineStr">
         <is>
-          <t>11160779</t>
+          <t>11164267</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>Sp25StopperP</t>
+          <t>SI25Tu20Swimm</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
@@ -25171,17 +25175,17 @@
       </c>
       <c r="B710" s="7" t="inlineStr">
         <is>
-          <t>16120</t>
+          <t>16122</t>
         </is>
       </c>
       <c r="C710" s="7" t="inlineStr">
         <is>
-          <t>11164267</t>
+          <t>11164270</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>SI25Tu20Swimm</t>
+          <t>SI25Tu20Zoo</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
@@ -25206,17 +25210,17 @@
       </c>
       <c r="B711" s="7" t="inlineStr">
         <is>
-          <t>16122</t>
+          <t>16123</t>
         </is>
       </c>
       <c r="C711" s="7" t="inlineStr">
         <is>
-          <t>11164270</t>
+          <t>11164277</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>SI25Tu20Zoo</t>
+          <t>SI25CC24Dome</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
@@ -25241,17 +25245,17 @@
       </c>
       <c r="B712" s="7" t="inlineStr">
         <is>
-          <t>16123</t>
+          <t>16124</t>
         </is>
       </c>
       <c r="C712" s="7" t="inlineStr">
         <is>
-          <t>11164277</t>
+          <t>11164280</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>SI25CC24Dome</t>
+          <t>SI25Reus24Teach</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
@@ -25276,17 +25280,17 @@
       </c>
       <c r="B713" s="7" t="inlineStr">
         <is>
-          <t>16124</t>
+          <t>16125</t>
         </is>
       </c>
       <c r="C713" s="7" t="inlineStr">
         <is>
-          <t>11164280</t>
+          <t>11164285</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>SI25Reus24Teach</t>
+          <t>SI25CC24Colors</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
@@ -25311,17 +25315,17 @@
       </c>
       <c r="B714" s="7" t="inlineStr">
         <is>
-          <t>16125</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="C714" s="7" t="inlineStr">
         <is>
-          <t>11164285</t>
+          <t>11164288</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>SI25CC24Colors</t>
+          <t>SII25Tu16Blue</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
@@ -25346,17 +25350,17 @@
       </c>
       <c r="B715" s="7" t="inlineStr">
         <is>
-          <t>16126</t>
+          <t>16128</t>
         </is>
       </c>
       <c r="C715" s="7" t="inlineStr">
         <is>
-          <t>11164288</t>
+          <t>11164292</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>SII25Tu16Blue</t>
+          <t>SI25SSDoodle</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
@@ -25381,17 +25385,17 @@
       </c>
       <c r="B716" s="7" t="inlineStr">
         <is>
-          <t>16128</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="C716" s="7" t="inlineStr">
         <is>
-          <t>11164292</t>
+          <t>11164293</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>SI25SSDoodle</t>
+          <t>SI25Tz14Glass</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
@@ -25416,17 +25420,17 @@
       </c>
       <c r="B717" s="7" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="C717" s="7" t="inlineStr">
         <is>
-          <t>11164293</t>
+          <t>11164305</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>SI25Tz14Glass</t>
+          <t>SII25SSCC24Green</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
@@ -25451,17 +25455,17 @@
       </c>
       <c r="B718" s="7" t="inlineStr">
         <is>
-          <t>16131</t>
+          <t>16149</t>
         </is>
       </c>
       <c r="C718" s="7" t="inlineStr">
         <is>
-          <t>11164305</t>
+          <t>11164265</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>SII25SSCC24Green</t>
+          <t>SI25Tu16Bubble</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
@@ -25486,17 +25490,17 @@
       </c>
       <c r="B719" s="7" t="inlineStr">
         <is>
-          <t>16149</t>
+          <t>16150</t>
         </is>
       </c>
       <c r="C719" s="7" t="inlineStr">
         <is>
-          <t>11164265</t>
+          <t>11164271</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>SI25Tu16Bubble</t>
+          <t>SI25SSCC24Paddle</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
@@ -25521,17 +25525,17 @@
       </c>
       <c r="B720" s="7" t="inlineStr">
         <is>
-          <t>16150</t>
+          <t>16151</t>
         </is>
       </c>
       <c r="C720" s="7" t="inlineStr">
         <is>
-          <t>11164271</t>
+          <t>11164272</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>SI25SSCC24Paddle</t>
+          <t>SI25CC24Fun</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
@@ -25556,17 +25560,17 @@
       </c>
       <c r="B721" s="7" t="inlineStr">
         <is>
-          <t>16151</t>
+          <t>16152</t>
         </is>
       </c>
       <c r="C721" s="7" t="inlineStr">
         <is>
-          <t>11164272</t>
+          <t>11164316</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>SI25CC24Fun</t>
+          <t>SI25KeyChainCC</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
@@ -25591,17 +25595,17 @@
       </c>
       <c r="B722" s="7" t="inlineStr">
         <is>
-          <t>16152</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="C722" s="7" t="inlineStr">
         <is>
-          <t>11164316</t>
+          <t>11164283</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>SI25KeyChainCC</t>
+          <t>SI25CC24Drinks</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
@@ -25626,17 +25630,17 @@
       </c>
       <c r="B723" s="7" t="inlineStr">
         <is>
-          <t>16154</t>
+          <t>16155</t>
         </is>
       </c>
       <c r="C723" s="7" t="inlineStr">
         <is>
-          <t>11164283</t>
+          <t>11164275</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>SI25CC24Drinks</t>
+          <t>SI25CC24Bling</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
@@ -25661,17 +25665,17 @@
       </c>
       <c r="B724" s="7" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>16156</t>
         </is>
       </c>
       <c r="C724" s="7" t="inlineStr">
         <is>
-          <t>11164275</t>
+          <t>11164258</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>SI25CC24Bling</t>
+          <t>SI25DW12Beach</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
@@ -25696,17 +25700,17 @@
       </c>
       <c r="B725" s="7" t="inlineStr">
         <is>
-          <t>16156</t>
+          <t>16157</t>
         </is>
       </c>
       <c r="C725" s="7" t="inlineStr">
         <is>
-          <t>11164258</t>
+          <t>11164259</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>SI25DW12Beach</t>
+          <t>SII25DW12Studded</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
@@ -25731,17 +25735,17 @@
       </c>
       <c r="B726" s="7" t="inlineStr">
         <is>
-          <t>16157</t>
+          <t>16162</t>
         </is>
       </c>
       <c r="C726" s="7" t="inlineStr">
         <is>
-          <t>11164259</t>
+          <t>11164264</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>SII25DW12Studded</t>
+          <t>SI25Mug12Teach</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
@@ -25766,17 +25770,17 @@
       </c>
       <c r="B727" s="7" t="inlineStr">
         <is>
-          <t>16162</t>
+          <t>16163</t>
         </is>
       </c>
       <c r="C727" s="7" t="inlineStr">
         <is>
-          <t>11164264</t>
+          <t>11164268</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>SI25Mug12Teach</t>
+          <t>SII25Tu20Soft</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
@@ -25801,17 +25805,17 @@
       </c>
       <c r="B728" s="7" t="inlineStr">
         <is>
-          <t>16163</t>
+          <t>16164</t>
         </is>
       </c>
       <c r="C728" s="7" t="inlineStr">
         <is>
-          <t>11164268</t>
+          <t>11164273</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>SII25Tu20Soft</t>
+          <t>SII25CC24Jeweled</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
@@ -25836,17 +25840,17 @@
       </c>
       <c r="B729" s="7" t="inlineStr">
         <is>
-          <t>16164</t>
+          <t>16165</t>
         </is>
       </c>
       <c r="C729" s="7" t="inlineStr">
         <is>
-          <t>11164273</t>
+          <t>11164281</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>SII25CC24Jeweled</t>
+          <t>SII25CC24B2S</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
@@ -25871,17 +25875,17 @@
       </c>
       <c r="B730" s="7" t="inlineStr">
         <is>
-          <t>16165</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="C730" s="7" t="inlineStr">
         <is>
-          <t>11164281</t>
+          <t>11164298</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>SII25CC24B2S</t>
+          <t>Fl25SS20Grad</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
@@ -25906,17 +25910,17 @@
       </c>
       <c r="B731" s="7" t="inlineStr">
         <is>
-          <t>16168</t>
+          <t>16170</t>
         </is>
       </c>
       <c r="C731" s="7" t="inlineStr">
         <is>
-          <t>11164298</t>
+          <t>11164302</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Fl25SS20Grad</t>
+          <t>SI25SSCC24Swimm</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
@@ -25941,17 +25945,17 @@
       </c>
       <c r="B732" s="7" t="inlineStr">
         <is>
-          <t>16170</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="C732" s="7" t="inlineStr">
         <is>
-          <t>11164302</t>
+          <t>11164303</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>SI25SSCC24Swimm</t>
+          <t>Fl25SS24Vac</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
@@ -25976,17 +25980,17 @@
       </c>
       <c r="B733" s="7" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>16172</t>
         </is>
       </c>
       <c r="C733" s="7" t="inlineStr">
         <is>
-          <t>11164303</t>
+          <t>11164306</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>Fl25SS24Vac</t>
+          <t>SI25Vac24Stanley</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
@@ -26011,17 +26015,17 @@
       </c>
       <c r="B734" s="7" t="inlineStr">
         <is>
-          <t>16172</t>
+          <t>16174</t>
         </is>
       </c>
       <c r="C734" s="7" t="inlineStr">
         <is>
-          <t>11164306</t>
+          <t>11164309</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>SI25Vac24Stanley</t>
+          <t>SII25Quencher30</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
@@ -26046,17 +26050,17 @@
       </c>
       <c r="B735" s="7" t="inlineStr">
         <is>
-          <t>16174</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="C735" s="7" t="inlineStr">
         <is>
-          <t>11164309</t>
+          <t>11164311</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>SII25Quencher30</t>
+          <t>SI25Quencher30</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
@@ -26081,17 +26085,17 @@
       </c>
       <c r="B736" s="7" t="inlineStr">
         <is>
-          <t>16175</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="C736" s="7" t="inlineStr">
         <is>
-          <t>11164311</t>
+          <t>11164312</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>SI25Quencher30</t>
+          <t>SI25SSCC24Father</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
@@ -26116,17 +26120,17 @@
       </c>
       <c r="B737" s="7" t="inlineStr">
         <is>
-          <t>16176</t>
+          <t>16178</t>
         </is>
       </c>
       <c r="C737" s="7" t="inlineStr">
         <is>
-          <t>11164312</t>
+          <t>11164319</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>SI25SSCC24Father</t>
+          <t>SI25KeychainZoo</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
@@ -26151,17 +26155,17 @@
       </c>
       <c r="B738" s="7" t="inlineStr">
         <is>
-          <t>16178</t>
+          <t>16179</t>
         </is>
       </c>
       <c r="C738" s="7" t="inlineStr">
         <is>
-          <t>11164319</t>
+          <t>11167149</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>SI25KeychainZoo</t>
+          <t>SII25SSCC24FRB</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
@@ -26186,17 +26190,17 @@
       </c>
       <c r="B739" s="7" t="inlineStr">
         <is>
-          <t>16179</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="C739" s="7" t="inlineStr">
         <is>
-          <t>11167149</t>
+          <t>11167150</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>SII25SSCC24FRB</t>
+          <t>SII25CC24FRBlue</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
@@ -26221,17 +26225,17 @@
       </c>
       <c r="B740" s="7" t="inlineStr">
         <is>
-          <t>16180</t>
+          <t>16182</t>
         </is>
       </c>
       <c r="C740" s="7" t="inlineStr">
         <is>
-          <t>11167150</t>
+          <t>11167152</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>SII25CC24FRBlue</t>
+          <t>SII25Tu16FarmR</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
@@ -26256,17 +26260,17 @@
       </c>
       <c r="B741" s="7" t="inlineStr">
         <is>
-          <t>16182</t>
+          <t>16246</t>
         </is>
       </c>
       <c r="C741" s="7" t="inlineStr">
         <is>
-          <t>11167152</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>SII25Tu16FarmR</t>
+          <t>Fl25SS20Siren</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
@@ -26291,17 +26295,17 @@
       </c>
       <c r="B742" s="7" t="inlineStr">
         <is>
-          <t>16246</t>
+          <t>16258</t>
         </is>
       </c>
       <c r="C742" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11171524</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>Fl25SS20Siren</t>
+          <t>SII25ReusColor</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
@@ -26326,17 +26330,17 @@
       </c>
       <c r="B743" s="7" t="inlineStr">
         <is>
-          <t>16258</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="C743" s="7" t="inlineStr">
         <is>
-          <t>11171524</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>SII25ReusColor</t>
+          <t>SI25ReusDelivery</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
@@ -26361,17 +26365,17 @@
       </c>
       <c r="B744" s="7" t="inlineStr">
         <is>
-          <t>16261</t>
+          <t>16264</t>
         </is>
       </c>
       <c r="C744" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11160967</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>SI25ReusDelivery</t>
+          <t>COR26PPBTL20S</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
@@ -26396,17 +26400,17 @@
       </c>
       <c r="B745" s="7" t="inlineStr">
         <is>
-          <t>16264</t>
+          <t>16265</t>
         </is>
       </c>
       <c r="C745" s="7" t="inlineStr">
         <is>
-          <t>11160967</t>
+          <t>11169482</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>COR26PPBTL20S</t>
+          <t>Fl25KeyChainD</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
@@ -26431,17 +26435,17 @@
       </c>
       <c r="B746" s="7" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>16266</t>
         </is>
       </c>
       <c r="C746" s="7" t="inlineStr">
         <is>
-          <t>11169482</t>
+          <t>11169450</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>Fl25KeyChainD</t>
+          <t>Fl25CC24StrawT</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
@@ -26466,17 +26470,17 @@
       </c>
       <c r="B747" s="7" t="inlineStr">
         <is>
-          <t>16266</t>
+          <t>16267</t>
         </is>
       </c>
       <c r="C747" s="7" t="inlineStr">
         <is>
-          <t>11169450</t>
+          <t>11162638</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>Fl25CC24StrawT</t>
+          <t>COR25SSCC24Black</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
@@ -26501,17 +26505,17 @@
       </c>
       <c r="B748" s="7" t="inlineStr">
         <is>
-          <t>16267</t>
+          <t>16268</t>
         </is>
       </c>
       <c r="C748" s="7" t="inlineStr">
         <is>
-          <t>11162638</t>
+          <t>11169473</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>COR25SSCC24Black</t>
+          <t>Fl25CCSS24Pearl</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
@@ -26536,17 +26540,17 @@
       </c>
       <c r="B749" s="7" t="inlineStr">
         <is>
-          <t>16268</t>
+          <t>16269</t>
         </is>
       </c>
       <c r="C749" s="7" t="inlineStr">
         <is>
-          <t>11169473</t>
+          <t>11169467</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>Fl25CCSS24Pearl</t>
+          <t>Fl25CCSS16Vac</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
@@ -26571,17 +26575,17 @@
       </c>
       <c r="B750" s="7" t="inlineStr">
         <is>
-          <t>16269</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="C750" s="7" t="inlineStr">
         <is>
-          <t>11169467</t>
+          <t>11169475</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>Fl25CCSS16Vac</t>
+          <t>Fl25SSCC24Anniv</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
@@ -26606,17 +26610,17 @@
       </c>
       <c r="B751" s="7" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>16272</t>
         </is>
       </c>
       <c r="C751" s="7" t="inlineStr">
         <is>
-          <t>11169475</t>
+          <t>11169453</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>Fl25SSCC24Anniv</t>
+          <t>Fl25SSMug12Rib</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
@@ -26641,17 +26645,17 @@
       </c>
       <c r="B752" s="7" t="inlineStr">
         <is>
-          <t>16272</t>
+          <t>16273</t>
         </is>
       </c>
       <c r="C752" s="7" t="inlineStr">
         <is>
-          <t>11169453</t>
+          <t>11169470</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>Fl25SSMug12Rib</t>
+          <t>Fl25Stanley16</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
@@ -26676,17 +26680,17 @@
       </c>
       <c r="B753" s="7" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16274</t>
         </is>
       </c>
       <c r="C753" s="7" t="inlineStr">
         <is>
-          <t>11169470</t>
+          <t>11169471</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>Fl25Stanley16</t>
+          <t>Fl25SS16Charm</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
@@ -26711,17 +26715,17 @@
       </c>
       <c r="B754" s="7" t="inlineStr">
         <is>
-          <t>16274</t>
+          <t>16275</t>
         </is>
       </c>
       <c r="C754" s="7" t="inlineStr">
         <is>
-          <t>11169471</t>
+          <t>11169454</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>Fl25SS16Charm</t>
+          <t>Fl25SSTu20Vac</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
@@ -26746,17 +26750,17 @@
       </c>
       <c r="B755" s="7" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>16276</t>
         </is>
       </c>
       <c r="C755" s="7" t="inlineStr">
         <is>
-          <t>11169454</t>
+          <t>11169464</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>Fl25SSTu20Vac</t>
+          <t>Fl25SSTu16Wave</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
@@ -26781,17 +26785,17 @@
       </c>
       <c r="B756" s="7" t="inlineStr">
         <is>
-          <t>16276</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="C756" s="7" t="inlineStr">
         <is>
-          <t>11169464</t>
+          <t>11169455</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>Fl25SSTu16Wave</t>
+          <t>Fl25SSBTL20</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
@@ -26816,17 +26820,17 @@
       </c>
       <c r="B757" s="7" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>16278</t>
         </is>
       </c>
       <c r="C757" s="7" t="inlineStr">
         <is>
-          <t>11169455</t>
+          <t>11169466</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>Fl25SSBTL20</t>
+          <t>Fl25StanPearl</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
@@ -26851,17 +26855,17 @@
       </c>
       <c r="B758" s="7" t="inlineStr">
         <is>
-          <t>16278</t>
+          <t>16279</t>
         </is>
       </c>
       <c r="C758" s="7" t="inlineStr">
         <is>
-          <t>11169466</t>
+          <t>11169456</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>Fl25StanPearl</t>
+          <t>Fl25SSTu20Anni</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
@@ -26886,17 +26890,17 @@
       </c>
       <c r="B759" s="7" t="inlineStr">
         <is>
-          <t>16279</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="C759" s="7" t="inlineStr">
         <is>
-          <t>11169456</t>
+          <t>11169460</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>Fl25SSTu20Anni</t>
+          <t>Fl25SSCC24Sust</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
@@ -26921,17 +26925,17 @@
       </c>
       <c r="B760" s="7" t="inlineStr">
         <is>
-          <t>16280</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="C760" s="7" t="inlineStr">
         <is>
-          <t>11169460</t>
+          <t>11160988</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>Fl25SSCC24Sust</t>
+          <t>COR25SS20STouch</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
@@ -26956,17 +26960,17 @@
       </c>
       <c r="B761" s="7" t="inlineStr">
         <is>
-          <t>16281</t>
+          <t>16282</t>
         </is>
       </c>
       <c r="C761" s="7" t="inlineStr">
         <is>
-          <t>11160988</t>
+          <t>11161002</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>COR25SS20STouch</t>
+          <t>COR25Stan30Black</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
@@ -26991,17 +26995,17 @@
       </c>
       <c r="B762" s="7" t="inlineStr">
         <is>
-          <t>16282</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="C762" s="7" t="inlineStr">
         <is>
-          <t>11161002</t>
+          <t>11161003</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>COR25Stan30Black</t>
+          <t>COR26Stan30White</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
@@ -27026,17 +27030,17 @@
       </c>
       <c r="B763" s="7" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>16284</t>
         </is>
       </c>
       <c r="C763" s="7" t="inlineStr">
         <is>
-          <t>11161003</t>
+          <t>11160991</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>COR26Stan30White</t>
+          <t>COR25SS16Sleeve</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
@@ -27061,17 +27065,17 @@
       </c>
       <c r="B764" s="7" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>16285</t>
         </is>
       </c>
       <c r="C764" s="7" t="inlineStr">
         <is>
-          <t>11160991</t>
+          <t>11160965</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>COR25SS16Sleeve</t>
+          <t>COR26Tu16Sust</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
@@ -27096,17 +27100,17 @@
       </c>
       <c r="B765" s="7" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>16286</t>
         </is>
       </c>
       <c r="C765" s="7" t="inlineStr">
         <is>
-          <t>11160965</t>
+          <t>11169436</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>COR26Tu16Sust</t>
+          <t>Fl25Tu16Sust</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
@@ -27131,17 +27135,17 @@
       </c>
       <c r="B766" s="7" t="inlineStr">
         <is>
-          <t>16286</t>
+          <t>16287</t>
         </is>
       </c>
       <c r="C766" s="7" t="inlineStr">
         <is>
-          <t>11169436</t>
+          <t>11169430</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>Fl25Tu16Sust</t>
+          <t>Fl25Tu16Charm</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
@@ -27166,17 +27170,17 @@
       </c>
       <c r="B767" s="7" t="inlineStr">
         <is>
-          <t>16287</t>
+          <t>16288</t>
         </is>
       </c>
       <c r="C767" s="7" t="inlineStr">
         <is>
-          <t>11169430</t>
+          <t>11170273</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>Fl25Tu16Charm</t>
+          <t>Fl25ReusCCEsp</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
@@ -27201,17 +27205,17 @@
       </c>
       <c r="B768" s="7" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="C768" s="7" t="inlineStr">
         <is>
-          <t>11170273</t>
+          <t>11169434</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>Fl25ReusCCEsp</t>
+          <t>Fl25Tu16DDM</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
@@ -27236,17 +27240,17 @@
       </c>
       <c r="B769" s="7" t="inlineStr">
         <is>
-          <t>16290</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="C769" s="7" t="inlineStr">
         <is>
-          <t>11169434</t>
+          <t>11169439</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>Fl25Tu16DDM</t>
+          <t>Fl25CC24Dome</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
@@ -27271,17 +27275,17 @@
       </c>
       <c r="B770" s="7" t="inlineStr">
         <is>
-          <t>16291</t>
+          <t>16292</t>
         </is>
       </c>
       <c r="C770" s="7" t="inlineStr">
         <is>
-          <t>11169439</t>
+          <t>11169432</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>Fl25CC24Dome</t>
+          <t>Fl25Tu16Anniv</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
@@ -27306,17 +27310,17 @@
       </c>
       <c r="B771" s="7" t="inlineStr">
         <is>
-          <t>16292</t>
+          <t>16293</t>
         </is>
       </c>
       <c r="C771" s="7" t="inlineStr">
         <is>
-          <t>11169432</t>
+          <t>11169435</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>Fl25Tu16Anniv</t>
+          <t>Fl25ReusPikeP</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
@@ -27341,17 +27345,17 @@
       </c>
       <c r="B772" s="7" t="inlineStr">
         <is>
-          <t>16293</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="C772" s="7" t="inlineStr">
         <is>
-          <t>11169435</t>
+          <t>11170275</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>Fl25ReusPikeP</t>
+          <t>Fl25ReusCCPikeP</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
@@ -27376,17 +27380,17 @@
       </c>
       <c r="B773" s="7" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="C773" s="7" t="inlineStr">
         <is>
-          <t>11170275</t>
+          <t>11170274</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>Fl25ReusCCPikeP</t>
+          <t>Fl25ReusEspresso</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
@@ -27411,17 +27415,17 @@
       </c>
       <c r="B774" s="7" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>16296</t>
         </is>
       </c>
       <c r="C774" s="7" t="inlineStr">
         <is>
-          <t>11170274</t>
+          <t>11169487</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>Fl25ReusEspresso</t>
+          <t>Fl25Pines</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
@@ -27446,17 +27450,17 @@
       </c>
       <c r="B775" s="7" t="inlineStr">
         <is>
-          <t>16296</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="C775" s="7" t="inlineStr">
         <is>
-          <t>11169487</t>
+          <t>11169491</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>Fl25Pines</t>
+          <t>Fl25PinesDDM</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
@@ -27481,17 +27485,17 @@
       </c>
       <c r="B776" s="7" t="inlineStr">
         <is>
-          <t>16297</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="C776" s="7" t="inlineStr">
         <is>
-          <t>11169491</t>
+          <t>11169429</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>Fl25PinesDDM</t>
+          <t>Fl25GlassCCSust</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
@@ -27516,17 +27520,17 @@
       </c>
       <c r="B777" s="7" t="inlineStr">
         <is>
-          <t>16298</t>
+          <t>16299</t>
         </is>
       </c>
       <c r="C777" s="7" t="inlineStr">
         <is>
-          <t>11169429</t>
+          <t>11160981</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>Fl25GlassCCSust</t>
+          <t>COR26Glass16Sus</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
@@ -27551,17 +27555,17 @@
       </c>
       <c r="B778" s="7" t="inlineStr">
         <is>
-          <t>16299</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="C778" s="7" t="inlineStr">
         <is>
-          <t>11160981</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>COR26Glass16Sus</t>
+          <t>Fl25GlassCC</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
@@ -27586,17 +27590,17 @@
       </c>
       <c r="B779" s="7" t="inlineStr">
         <is>
-          <t>16306</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="C779" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11160947</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>Fl25GlassCC</t>
+          <t>COR25DW12Prism</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
@@ -27621,17 +27625,17 @@
       </c>
       <c r="B780" s="7" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>16309</t>
         </is>
       </c>
       <c r="C780" s="7" t="inlineStr">
         <is>
-          <t>11160947</t>
+          <t>11160952</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>COR25DW12Prism</t>
+          <t>COR26Mug14Copper</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
@@ -27656,17 +27660,17 @@
       </c>
       <c r="B781" s="7" t="inlineStr">
         <is>
-          <t>16309</t>
+          <t>16310</t>
         </is>
       </c>
       <c r="C781" s="7" t="inlineStr">
         <is>
-          <t>11160952</t>
+          <t>11160955</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>COR26Mug14Copper</t>
+          <t>COR26Mug2Copper</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
@@ -27691,17 +27695,17 @@
       </c>
       <c r="B782" s="7" t="inlineStr">
         <is>
-          <t>16310</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="C782" s="7" t="inlineStr">
         <is>
-          <t>11160955</t>
+          <t>11160990</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>COR26Mug2Copper</t>
+          <t>COR26SSThruLid</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
@@ -27726,17 +27730,17 @@
       </c>
       <c r="B783" s="7" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="C783" s="7" t="inlineStr">
         <is>
-          <t>11160990</t>
+          <t>11160996</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>COR26SSThruLid</t>
+          <t>COR25StanIceflow</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
@@ -27761,17 +27765,17 @@
       </c>
       <c r="B784" s="7" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16315</t>
         </is>
       </c>
       <c r="C784" s="7" t="inlineStr">
         <is>
-          <t>11160995</t>
+          <t>11169423</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>COR26BTL20</t>
+          <t>Fl25DW12Luster</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
@@ -27796,17 +27800,17 @@
       </c>
       <c r="B785" s="7" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16317</t>
         </is>
       </c>
       <c r="C785" s="7" t="inlineStr">
         <is>
-          <t>11160996</t>
+          <t>11169426</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>COR25StanIceflow</t>
+          <t>Fl25Mug14Abrac</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
@@ -27831,17 +27835,17 @@
       </c>
       <c r="B786" s="7" t="inlineStr">
         <is>
-          <t>16315</t>
+          <t>16318</t>
         </is>
       </c>
       <c r="C786" s="7" t="inlineStr">
         <is>
-          <t>11169423</t>
+          <t>11169427</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>Fl25DW12Luster</t>
+          <t>Fl25Mug16Sust</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
@@ -27866,17 +27870,17 @@
       </c>
       <c r="B787" s="7" t="inlineStr">
         <is>
-          <t>16317</t>
+          <t>16319</t>
         </is>
       </c>
       <c r="C787" s="7" t="inlineStr">
         <is>
-          <t>11169426</t>
+          <t>11169447</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>Fl25Mug14Abrac</t>
+          <t>Fl25CC24DDM</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
@@ -27901,17 +27905,17 @@
       </c>
       <c r="B788" s="7" t="inlineStr">
         <is>
-          <t>16318</t>
+          <t>16320</t>
         </is>
       </c>
       <c r="C788" s="7" t="inlineStr">
         <is>
-          <t>11169427</t>
+          <t>11169458</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>Fl25Mug16Sust</t>
+          <t>Fl25SS20DDM</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
@@ -27936,17 +27940,17 @@
       </c>
       <c r="B789" s="7" t="inlineStr">
         <is>
-          <t>16319</t>
+          <t>16321</t>
         </is>
       </c>
       <c r="C789" s="7" t="inlineStr">
         <is>
-          <t>11169447</t>
+          <t>11169461</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>Fl25CC24DDM</t>
+          <t>Fl25SSTu12Sust</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
@@ -27971,17 +27975,17 @@
       </c>
       <c r="B790" s="7" t="inlineStr">
         <is>
-          <t>16320</t>
+          <t>16322</t>
         </is>
       </c>
       <c r="C790" s="7" t="inlineStr">
         <is>
-          <t>11169458</t>
+          <t>11169462</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>Fl25SS20DDM</t>
+          <t>Fl25SS16Studded</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
@@ -28006,17 +28010,17 @@
       </c>
       <c r="B791" s="7" t="inlineStr">
         <is>
-          <t>16321</t>
+          <t>16323</t>
         </is>
       </c>
       <c r="C791" s="7" t="inlineStr">
         <is>
-          <t>11169461</t>
+          <t>11169468</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>Fl25SSTu12Sust</t>
+          <t>Fl25SSCC16Purple</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
@@ -28041,17 +28045,17 @@
       </c>
       <c r="B792" s="7" t="inlineStr">
         <is>
-          <t>16322</t>
+          <t>16326</t>
         </is>
       </c>
       <c r="C792" s="7" t="inlineStr">
         <is>
-          <t>11169462</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>Fl25SS16Studded</t>
+          <t>Fl25MonTSC</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
@@ -28076,17 +28080,17 @@
       </c>
       <c r="B793" s="7" t="inlineStr">
         <is>
-          <t>16323</t>
+          <t>16327</t>
         </is>
       </c>
       <c r="C793" s="7" t="inlineStr">
         <is>
-          <t>11169468</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>Fl25SSCC16Purple</t>
+          <t>Fl25MonVXMC</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
@@ -28111,7 +28115,7 @@
       </c>
       <c r="B794" s="7" t="inlineStr">
         <is>
-          <t>16326</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="C794" s="7" t="inlineStr">
@@ -28121,7 +28125,7 @@
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>Fl25MonTSC</t>
+          <t>SII25LlaveroB2S</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
@@ -28146,7 +28150,7 @@
       </c>
       <c r="B795" s="7" t="inlineStr">
         <is>
-          <t>16327</t>
+          <t>16343</t>
         </is>
       </c>
       <c r="C795" s="7" t="inlineStr">
@@ -28156,7 +28160,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>Fl25MonVXMC</t>
+          <t>SII25ClipGirlB</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
@@ -28181,7 +28185,7 @@
       </c>
       <c r="B796" s="7" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>16344</t>
         </is>
       </c>
       <c r="C796" s="7" t="inlineStr">
@@ -28191,7 +28195,7 @@
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>SII25LlaveroB2S</t>
+          <t>SII25StrawLluvia</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
@@ -28216,7 +28220,7 @@
       </c>
       <c r="B797" s="7" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>16345</t>
         </is>
       </c>
       <c r="C797" s="7" t="inlineStr">
@@ -28226,7 +28230,7 @@
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>SII25ClipGirlB</t>
+          <t>SII25StopPSL</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
@@ -28251,7 +28255,7 @@
       </c>
       <c r="B798" s="7" t="inlineStr">
         <is>
-          <t>16344</t>
+          <t>16378</t>
         </is>
       </c>
       <c r="C798" s="7" t="inlineStr">
@@ -28261,7 +28265,7 @@
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>SII25StrawLluvia</t>
+          <t>COR25CircCup</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
@@ -28286,7 +28290,7 @@
       </c>
       <c r="B799" s="7" t="inlineStr">
         <is>
-          <t>16345</t>
+          <t>16416</t>
         </is>
       </c>
       <c r="C799" s="7" t="inlineStr">
@@ -28296,7 +28300,7 @@
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>SII25StopPSL</t>
+          <t>Fl25ReusCCBa</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
@@ -28321,7 +28325,7 @@
       </c>
       <c r="B800" s="7" t="inlineStr">
         <is>
-          <t>16378</t>
+          <t>16417</t>
         </is>
       </c>
       <c r="C800" s="7" t="inlineStr">
@@ -28331,7 +28335,7 @@
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>COR25CircCup</t>
+          <t>Fl25ReusBar</t>
         </is>
       </c>
       <c r="E800" t="inlineStr">
@@ -28356,17 +28360,17 @@
       </c>
       <c r="B801" s="7" t="inlineStr">
         <is>
-          <t>16416</t>
+          <t>16433</t>
         </is>
       </c>
       <c r="C801" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11173273</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>Fl25ReusCCBa</t>
+          <t>Xm25Tu12Hol</t>
         </is>
       </c>
       <c r="E801" t="inlineStr">
@@ -28391,17 +28395,17 @@
       </c>
       <c r="B802" s="7" t="inlineStr">
         <is>
-          <t>16417</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="C802" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11173046</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
         <is>
-          <t>Fl25ReusBar</t>
+          <t>Xm25CCGlass18</t>
         </is>
       </c>
       <c r="E802" t="inlineStr">
@@ -28426,17 +28430,17 @@
       </c>
       <c r="B803" s="7" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>16438</t>
         </is>
       </c>
       <c r="C803" s="7" t="inlineStr">
         <is>
-          <t>11173273</t>
+          <t>11173047</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>Xm25Tu12Hol</t>
+          <t>Xm25Tz14Glass</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
@@ -28461,17 +28465,17 @@
       </c>
       <c r="B804" s="7" t="inlineStr">
         <is>
-          <t>16437</t>
+          <t>16439</t>
         </is>
       </c>
       <c r="C804" s="7" t="inlineStr">
         <is>
-          <t>11173046</t>
+          <t>11172983</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>Xm25CCGlass18</t>
+          <t>Xm25Mug12Stan</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
@@ -28496,17 +28500,17 @@
       </c>
       <c r="B805" s="7" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>16440</t>
         </is>
       </c>
       <c r="C805" s="7" t="inlineStr">
         <is>
-          <t>11173047</t>
+          <t>11172998</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>Xm25Tz14Glass</t>
+          <t>Xm25SSCC24Topp</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
@@ -28531,17 +28535,17 @@
       </c>
       <c r="B806" s="7" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>16441</t>
         </is>
       </c>
       <c r="C806" s="7" t="inlineStr">
         <is>
-          <t>11172983</t>
+          <t>11173000</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>Xm25Mug12Stan</t>
+          <t>Xm25CC24House</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
@@ -28566,17 +28570,17 @@
       </c>
       <c r="B807" s="7" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>16442</t>
         </is>
       </c>
       <c r="C807" s="7" t="inlineStr">
         <is>
-          <t>11172998</t>
+          <t>11172996</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>Xm25SSCC24Topp</t>
+          <t>Xm25SSCC24R</t>
         </is>
       </c>
       <c r="E807" t="inlineStr">
@@ -28601,17 +28605,17 @@
       </c>
       <c r="B808" s="7" t="inlineStr">
         <is>
-          <t>16441</t>
+          <t>16443</t>
         </is>
       </c>
       <c r="C808" s="7" t="inlineStr">
         <is>
-          <t>11173000</t>
+          <t>11172994</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>Xm25CC24House</t>
+          <t>Xm25BTLStanley</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
@@ -28636,17 +28640,17 @@
       </c>
       <c r="B809" s="7" t="inlineStr">
         <is>
-          <t>16442</t>
+          <t>16444</t>
         </is>
       </c>
       <c r="C809" s="7" t="inlineStr">
         <is>
-          <t>11172996</t>
+          <t>11172855</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>Xm25SSCC24R</t>
+          <t>Xm25DW12Red</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
@@ -28671,17 +28675,17 @@
       </c>
       <c r="B810" s="7" t="inlineStr">
         <is>
-          <t>16443</t>
+          <t>16446</t>
         </is>
       </c>
       <c r="C810" s="7" t="inlineStr">
         <is>
-          <t>11172994</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>Xm25BTLStanley</t>
+          <t>Fl25MonederoAniv</t>
         </is>
       </c>
       <c r="E810" t="inlineStr">
@@ -28706,17 +28710,17 @@
       </c>
       <c r="B811" s="7" t="inlineStr">
         <is>
-          <t>16444</t>
+          <t>16453</t>
         </is>
       </c>
       <c r="C811" s="7" t="inlineStr">
         <is>
-          <t>11172855</t>
+          <t>11172962</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>Xm25DW12Red</t>
+          <t>Xm25Tu16Charm</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
@@ -28741,17 +28745,13 @@
       </c>
       <c r="B812" s="7" t="inlineStr">
         <is>
-          <t>16446</t>
-        </is>
-      </c>
-      <c r="C812" s="7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>16454</t>
+        </is>
+      </c>
+      <c r="C812" s="7" t="inlineStr"/>
       <c r="D812" t="inlineStr">
         <is>
-          <t>Fl25MonederoAniv</t>
+          <t>Xm25Give16CC</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
@@ -28776,17 +28776,17 @@
       </c>
       <c r="B813" s="7" t="inlineStr">
         <is>
-          <t>16453</t>
+          <t>16455</t>
         </is>
       </c>
       <c r="C813" s="7" t="inlineStr">
         <is>
-          <t>11172962</t>
+          <t>11172965</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>Xm25Tu16Charm</t>
+          <t>Xm25Tu16CPing</t>
         </is>
       </c>
       <c r="E813" t="inlineStr">
@@ -28811,13 +28811,17 @@
       </c>
       <c r="B814" s="7" t="inlineStr">
         <is>
-          <t>16454</t>
-        </is>
-      </c>
-      <c r="C814" s="7" t="inlineStr"/>
+          <t>16456</t>
+        </is>
+      </c>
+      <c r="C814" s="7" t="inlineStr">
+        <is>
+          <t>11172974</t>
+        </is>
+      </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>Xm25Give16CC</t>
+          <t>Xm25CC24Snow</t>
         </is>
       </c>
       <c r="E814" t="inlineStr">
@@ -28842,17 +28846,17 @@
       </c>
       <c r="B815" s="7" t="inlineStr">
         <is>
-          <t>16455</t>
+          <t>16457</t>
         </is>
       </c>
       <c r="C815" s="7" t="inlineStr">
         <is>
-          <t>11172965</t>
+          <t>11173031</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>Xm25Tu16CPing</t>
+          <t>Xm25Llavero</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
@@ -28877,17 +28881,17 @@
       </c>
       <c r="B816" s="7" t="inlineStr">
         <is>
-          <t>16456</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="C816" s="7" t="inlineStr">
         <is>
-          <t>11172974</t>
+          <t>11172984</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>Xm25CC24Snow</t>
+          <t>Xm25SS16DIam</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">
@@ -28912,17 +28916,17 @@
       </c>
       <c r="B817" s="7" t="inlineStr">
         <is>
-          <t>16457</t>
+          <t>16459</t>
         </is>
       </c>
       <c r="C817" s="7" t="inlineStr">
         <is>
-          <t>11173031</t>
+          <t>11172985</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>Xm25Llavero</t>
+          <t>Xm25SS16Green</t>
         </is>
       </c>
       <c r="E817" t="inlineStr">
@@ -28947,17 +28951,17 @@
       </c>
       <c r="B818" s="7" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="C818" s="7" t="inlineStr">
         <is>
-          <t>11172984</t>
+          <t>11172993</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>Xm25SS16DIam</t>
+          <t>Xm25TuStan20</t>
         </is>
       </c>
       <c r="E818" t="inlineStr">
@@ -28982,17 +28986,17 @@
       </c>
       <c r="B819" s="7" t="inlineStr">
         <is>
-          <t>16459</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="C819" s="7" t="inlineStr">
         <is>
-          <t>11172985</t>
+          <t>11172997</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>Xm25SS16Green</t>
+          <t>Xm25RedQuen30</t>
         </is>
       </c>
       <c r="E819" t="inlineStr">
@@ -29017,17 +29021,17 @@
       </c>
       <c r="B820" s="7" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="C820" s="7" t="inlineStr">
         <is>
-          <t>11172993</t>
+          <t>11173001</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
         <is>
-          <t>Xm25TuStan20</t>
+          <t>Xm25Quencher30</t>
         </is>
       </c>
       <c r="E820" t="inlineStr">
@@ -29052,17 +29056,17 @@
       </c>
       <c r="B821" s="7" t="inlineStr">
         <is>
-          <t>16462</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="C821" s="7" t="inlineStr">
         <is>
-          <t>11172997</t>
+          <t>11172989</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>Xm25RedQuen30</t>
+          <t>Xm25StanVac16</t>
         </is>
       </c>
       <c r="E821" t="inlineStr">
@@ -29087,17 +29091,17 @@
       </c>
       <c r="B822" s="7" t="inlineStr">
         <is>
-          <t>16463</t>
+          <t>16465</t>
         </is>
       </c>
       <c r="C822" s="7" t="inlineStr">
         <is>
-          <t>11173001</t>
+          <t>11172990</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>Xm25Quencher30</t>
+          <t>Xm25StanCB16</t>
         </is>
       </c>
       <c r="E822" t="inlineStr">
@@ -29122,17 +29126,17 @@
       </c>
       <c r="B823" s="7" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16466</t>
         </is>
       </c>
       <c r="C823" s="7" t="inlineStr">
         <is>
-          <t>11172989</t>
+          <t>11172999</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
         <is>
-          <t>Xm25StanVac16</t>
+          <t>Xm25Quen30Lil</t>
         </is>
       </c>
       <c r="E823" t="inlineStr">
@@ -29157,17 +29161,17 @@
       </c>
       <c r="B824" s="7" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>16467</t>
         </is>
       </c>
       <c r="C824" s="7" t="inlineStr">
         <is>
-          <t>11172990</t>
+          <t>11172981</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
         <is>
-          <t>Xm25StanCB16</t>
+          <t>Xm25SS12Vac</t>
         </is>
       </c>
       <c r="E824" t="inlineStr">
@@ -29192,17 +29196,17 @@
       </c>
       <c r="B825" s="7" t="inlineStr">
         <is>
-          <t>16466</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="C825" s="7" t="inlineStr">
         <is>
-          <t>11172999</t>
+          <t>11172992</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>Xm25Quen30Lil</t>
+          <t>Xm25BTL20Twi</t>
         </is>
       </c>
       <c r="E825" t="inlineStr">
@@ -29227,17 +29231,17 @@
       </c>
       <c r="B826" s="7" t="inlineStr">
         <is>
-          <t>16467</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="C826" s="7" t="inlineStr">
         <is>
-          <t>11172981</t>
+          <t>11172988</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>Xm25SS12Vac</t>
+          <t>Xm25SS16Charm</t>
         </is>
       </c>
       <c r="E826" t="inlineStr">
@@ -29262,17 +29266,17 @@
       </c>
       <c r="B827" s="7" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="C827" s="7" t="inlineStr">
         <is>
-          <t>11172992</t>
+          <t>11172971</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>Xm25BTL20Twi</t>
+          <t>Xm25CC24Hol</t>
         </is>
       </c>
       <c r="E827" t="inlineStr">
@@ -29297,17 +29301,13 @@
       </c>
       <c r="B828" s="7" t="inlineStr">
         <is>
-          <t>16469</t>
-        </is>
-      </c>
-      <c r="C828" s="7" t="inlineStr">
-        <is>
-          <t>11172988</t>
-        </is>
-      </c>
+          <t>16471</t>
+        </is>
+      </c>
+      <c r="C828" s="7" t="inlineStr"/>
       <c r="D828" t="inlineStr">
         <is>
-          <t>Xm25SS16Charm</t>
+          <t>Xm25Give16Hot</t>
         </is>
       </c>
       <c r="E828" t="inlineStr">
@@ -29332,17 +29332,17 @@
       </c>
       <c r="B829" s="7" t="inlineStr">
         <is>
-          <t>16470</t>
+          <t>16472</t>
         </is>
       </c>
       <c r="C829" s="7" t="inlineStr">
         <is>
-          <t>11172971</t>
+          <t>11172975</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>Xm25CC24Hol</t>
+          <t>Xm25BTL24Magn</t>
         </is>
       </c>
       <c r="E829" t="inlineStr">
@@ -29367,13 +29367,17 @@
       </c>
       <c r="B830" s="7" t="inlineStr">
         <is>
-          <t>16471</t>
-        </is>
-      </c>
-      <c r="C830" s="7" t="inlineStr"/>
+          <t>16473</t>
+        </is>
+      </c>
+      <c r="C830" s="7" t="inlineStr">
+        <is>
+          <t>11172967</t>
+        </is>
+      </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>Xm25Give16Hot</t>
+          <t>Xm25Tu16Bow</t>
         </is>
       </c>
       <c r="E830" t="inlineStr">
@@ -29398,17 +29402,17 @@
       </c>
       <c r="B831" s="7" t="inlineStr">
         <is>
-          <t>16472</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="C831" s="7" t="inlineStr">
         <is>
-          <t>11172975</t>
+          <t>11172857</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
         <is>
-          <t>Xm25BTL24Magn</t>
+          <t>Xm25MugPinguin</t>
         </is>
       </c>
       <c r="E831" t="inlineStr">
@@ -29433,17 +29437,17 @@
       </c>
       <c r="B832" s="7" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>16475</t>
         </is>
       </c>
       <c r="C832" s="7" t="inlineStr">
         <is>
-          <t>11172967</t>
+          <t>11172859</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>Xm25Tu16Bow</t>
+          <t>Xm25Mug12House</t>
         </is>
       </c>
       <c r="E832" t="inlineStr">
@@ -29468,17 +29472,17 @@
       </c>
       <c r="B833" s="7" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>16476</t>
         </is>
       </c>
       <c r="C833" s="7" t="inlineStr">
         <is>
-          <t>11172857</t>
+          <t>11172986</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>Xm25MugPinguin</t>
+          <t>Xm25SS16Peng</t>
         </is>
       </c>
       <c r="E833" t="inlineStr">
@@ -29503,17 +29507,17 @@
       </c>
       <c r="B834" s="7" t="inlineStr">
         <is>
-          <t>16475</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="C834" s="7" t="inlineStr">
         <is>
-          <t>11172859</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>Xm25Mug12House</t>
+          <t>Fl25StopperBar</t>
         </is>
       </c>
       <c r="E834" t="inlineStr">
@@ -29538,17 +29542,17 @@
       </c>
       <c r="B835" s="7" t="inlineStr">
         <is>
-          <t>16476</t>
+          <t>16489</t>
         </is>
       </c>
       <c r="C835" s="7" t="inlineStr">
         <is>
-          <t>11172986</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>Xm25SS16Peng</t>
+          <t>Fl25StrawBar</t>
         </is>
       </c>
       <c r="E835" t="inlineStr">
@@ -29573,7 +29577,7 @@
       </c>
       <c r="B836" s="7" t="inlineStr">
         <is>
-          <t>16488</t>
+          <t>16490</t>
         </is>
       </c>
       <c r="C836" s="7" t="inlineStr">
@@ -29583,7 +29587,7 @@
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>Fl25StopperBar</t>
+          <t>Fl25Manga</t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
@@ -29608,7 +29612,7 @@
       </c>
       <c r="B837" s="7" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="C837" s="7" t="inlineStr">
@@ -29618,7 +29622,7 @@
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>Fl25StrawBar</t>
+          <t>Fl25Llavero</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
@@ -29643,7 +29647,7 @@
       </c>
       <c r="B838" s="7" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>16502</t>
         </is>
       </c>
       <c r="C838" s="7" t="inlineStr">
@@ -29653,7 +29657,7 @@
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>Fl25Manga</t>
+          <t>Xm25Tag</t>
         </is>
       </c>
       <c r="E838" t="inlineStr">
@@ -29678,7 +29682,7 @@
       </c>
       <c r="B839" s="7" t="inlineStr">
         <is>
-          <t>16500</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="C839" s="7" t="inlineStr">
@@ -29688,7 +29692,7 @@
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>Fl25Llavero</t>
+          <t>Xm25Stopper</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
@@ -29713,17 +29717,17 @@
       </c>
       <c r="B840" s="7" t="inlineStr">
         <is>
-          <t>16502</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="C840" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11174779</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>Xm25Tag</t>
+          <t>Wt26CCGl16Red</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
@@ -29748,17 +29752,17 @@
       </c>
       <c r="B841" s="7" t="inlineStr">
         <is>
-          <t>16503</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="C841" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11174804</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>Xm25Stopper</t>
+          <t>Wt26BTLStanley</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
@@ -29783,17 +29787,17 @@
       </c>
       <c r="B842" s="7" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>16543</t>
         </is>
       </c>
       <c r="C842" s="7" t="inlineStr">
         <is>
-          <t>11174779</t>
+          <t>11174795</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>Wt26CCGl16Red</t>
+          <t>Wt26CC24Spinner</t>
         </is>
       </c>
       <c r="E842" t="inlineStr">
@@ -29818,17 +29822,17 @@
       </c>
       <c r="B843" s="7" t="inlineStr">
         <is>
-          <t>16541</t>
+          <t>16544</t>
         </is>
       </c>
       <c r="C843" s="7" t="inlineStr">
         <is>
-          <t>11174804</t>
+          <t>11177277</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>Wt26BTLStanley</t>
+          <t>Wt26CC24Choco</t>
         </is>
       </c>
       <c r="E843" t="inlineStr">
@@ -29853,17 +29857,17 @@
       </c>
       <c r="B844" s="7" t="inlineStr">
         <is>
-          <t>16543</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="C844" s="7" t="inlineStr">
         <is>
-          <t>11174795</t>
+          <t>11174808</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>Wt26CC24Spinner</t>
+          <t>Wt26SSCC24Grad</t>
         </is>
       </c>
       <c r="E844" t="inlineStr">
@@ -29888,17 +29892,17 @@
       </c>
       <c r="B845" s="7" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>16546</t>
         </is>
       </c>
       <c r="C845" s="7" t="inlineStr">
         <is>
-          <t>11177277</t>
+          <t>11174811</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>Wt26CC24Choco</t>
+          <t>Wt26SS30Jac</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
@@ -29923,17 +29927,17 @@
       </c>
       <c r="B846" s="7" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>16547</t>
         </is>
       </c>
       <c r="C846" s="7" t="inlineStr">
         <is>
-          <t>11174808</t>
+          <t>11177274</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>Wt26SSCC24Grad</t>
+          <t>Wt26SSCC24Win</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
@@ -29958,17 +29962,17 @@
       </c>
       <c r="B847" s="7" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16548</t>
         </is>
       </c>
       <c r="C847" s="7" t="inlineStr">
         <is>
-          <t>11174811</t>
+          <t>11174801</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>Wt26SS30Jac</t>
+          <t>Wt26SSBTL20SV</t>
         </is>
       </c>
       <c r="E847" t="inlineStr">
@@ -29993,17 +29997,17 @@
       </c>
       <c r="B848" s="7" t="inlineStr">
         <is>
-          <t>16547</t>
+          <t>16549</t>
         </is>
       </c>
       <c r="C848" s="7" t="inlineStr">
         <is>
-          <t>11177274</t>
+          <t>11174803</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>Wt26SSCC24Win</t>
+          <t>Wt262PkStanley</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
@@ -30028,17 +30032,17 @@
       </c>
       <c r="B849" s="7" t="inlineStr">
         <is>
-          <t>16548</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="C849" s="7" t="inlineStr">
         <is>
-          <t>11174801</t>
+          <t>11174776</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>Wt26SSBTL20SV</t>
+          <t>Wt26Mug14Bow</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
@@ -30063,17 +30067,17 @@
       </c>
       <c r="B850" s="7" t="inlineStr">
         <is>
-          <t>16549</t>
+          <t>16551</t>
         </is>
       </c>
       <c r="C850" s="7" t="inlineStr">
         <is>
-          <t>11174803</t>
+          <t>11174775</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>Wt262PkStanley</t>
+          <t>Wt26Dw12Jac</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
@@ -30098,17 +30102,17 @@
       </c>
       <c r="B851" s="7" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>16552</t>
         </is>
       </c>
       <c r="C851" s="7" t="inlineStr">
         <is>
-          <t>11174776</t>
+          <t>11174798</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>Wt26Mug14Bow</t>
+          <t>Wt26SS16Green</t>
         </is>
       </c>
       <c r="E851" t="inlineStr">
@@ -30133,17 +30137,17 @@
       </c>
       <c r="B852" s="7" t="inlineStr">
         <is>
-          <t>16551</t>
+          <t>16553</t>
         </is>
       </c>
       <c r="C852" s="7" t="inlineStr">
         <is>
-          <t>11174775</t>
+          <t>11174800</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>Wt26Dw12Jac</t>
+          <t>Wt26BTL20Gr</t>
         </is>
       </c>
       <c r="E852" t="inlineStr">
@@ -30168,17 +30172,17 @@
       </c>
       <c r="B853" s="7" t="inlineStr">
         <is>
-          <t>16552</t>
+          <t>16554</t>
         </is>
       </c>
       <c r="C853" s="7" t="inlineStr">
         <is>
-          <t>11174798</t>
+          <t>11174807</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>Wt26SS16Green</t>
+          <t>Wt26SS16Choco</t>
         </is>
       </c>
       <c r="E853" t="inlineStr">
@@ -30203,17 +30207,17 @@
       </c>
       <c r="B854" s="7" t="inlineStr">
         <is>
-          <t>16553</t>
+          <t>16555</t>
         </is>
       </c>
       <c r="C854" s="7" t="inlineStr">
         <is>
-          <t>11174800</t>
+          <t>11174810</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>Wt26BTL20Gr</t>
+          <t>Wt26Canteen</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
@@ -30238,17 +30242,17 @@
       </c>
       <c r="B855" s="7" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>16556</t>
         </is>
       </c>
       <c r="C855" s="7" t="inlineStr">
         <is>
-          <t>11174807</t>
+          <t>11174799</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>Wt26SS16Choco</t>
+          <t>Wt26SSCC16Grad</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
@@ -30273,17 +30277,17 @@
       </c>
       <c r="B856" s="7" t="inlineStr">
         <is>
-          <t>16555</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="C856" s="7" t="inlineStr">
         <is>
-          <t>11174810</t>
+          <t>11174806</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>Wt26Canteen</t>
+          <t>Wt26SSCC16Jac</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
@@ -30308,17 +30312,17 @@
       </c>
       <c r="B857" s="7" t="inlineStr">
         <is>
-          <t>16556</t>
+          <t>16558</t>
         </is>
       </c>
       <c r="C857" s="7" t="inlineStr">
         <is>
-          <t>11174799</t>
+          <t>11177275</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>Wt26SSCC16Grad</t>
+          <t>Wt26SS20SV</t>
         </is>
       </c>
       <c r="E857" t="inlineStr">
@@ -30343,17 +30347,17 @@
       </c>
       <c r="B858" s="7" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>16559</t>
         </is>
       </c>
       <c r="C858" s="7" t="inlineStr">
         <is>
-          <t>11174806</t>
+          <t>11177276</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>Wt26SSCC16Jac</t>
+          <t>Wt26SS20Jac</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
@@ -30378,17 +30382,13 @@
       </c>
       <c r="B859" s="7" t="inlineStr">
         <is>
-          <t>16558</t>
-        </is>
-      </c>
-      <c r="C859" s="7" t="inlineStr">
-        <is>
-          <t>11177275</t>
-        </is>
-      </c>
+          <t>16566</t>
+        </is>
+      </c>
+      <c r="C859" s="7" t="inlineStr"/>
       <c r="D859" t="inlineStr">
         <is>
-          <t>Wt26SS20SV</t>
+          <t>BearHugger</t>
         </is>
       </c>
       <c r="E859" t="inlineStr">
@@ -30413,17 +30413,17 @@
       </c>
       <c r="B860" s="7" t="inlineStr">
         <is>
-          <t>16559</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="C860" s="7" t="inlineStr">
         <is>
-          <t>11177276</t>
+          <t>11174791</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
         <is>
-          <t>Wt26SS20Jac</t>
+          <t>Wt26ReusSV</t>
         </is>
       </c>
       <c r="E860" t="inlineStr">
@@ -30448,13 +30448,17 @@
       </c>
       <c r="B861" s="7" t="inlineStr">
         <is>
-          <t>16566</t>
-        </is>
-      </c>
-      <c r="C861" s="7" t="inlineStr"/>
+          <t>16573</t>
+        </is>
+      </c>
+      <c r="C861" s="7" t="inlineStr">
+        <is>
+          <t>11175037</t>
+        </is>
+      </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>BearHugger</t>
+          <t>Wt26Tu16Charm</t>
         </is>
       </c>
       <c r="E861" t="inlineStr">
@@ -30479,17 +30483,17 @@
       </c>
       <c r="B862" s="7" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="C862" s="7" t="inlineStr">
         <is>
-          <t>11174791</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>Wt26ReusSV</t>
+          <t>Xm25ReuElev</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
@@ -30514,17 +30518,17 @@
       </c>
       <c r="B863" s="7" t="inlineStr">
         <is>
-          <t>16573</t>
+          <t>16589</t>
         </is>
       </c>
       <c r="C863" s="7" t="inlineStr">
         <is>
-          <t>11175037</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>Wt26Tu16Charm</t>
+          <t>Xm25ReuMike</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
@@ -30549,7 +30553,7 @@
       </c>
       <c r="B864" s="7" t="inlineStr">
         <is>
-          <t>16588</t>
+          <t>16590</t>
         </is>
       </c>
       <c r="C864" s="7" t="inlineStr">
@@ -30559,7 +30563,7 @@
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>Xm25ReuElev</t>
+          <t>Xm25Reus16ST</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
@@ -30584,7 +30588,7 @@
       </c>
       <c r="B865" s="7" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>16591</t>
         </is>
       </c>
       <c r="C865" s="7" t="inlineStr">
@@ -30594,7 +30598,7 @@
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>Xm25ReuMike</t>
+          <t>Xm25Reu24CCST</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
@@ -30619,7 +30623,7 @@
       </c>
       <c r="B866" s="7" t="inlineStr">
         <is>
-          <t>16590</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="C866" s="7" t="inlineStr">
@@ -30629,7 +30633,7 @@
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>Xm25Reus16ST</t>
+          <t>Xm25Reu2Hol</t>
         </is>
       </c>
       <c r="E866" t="inlineStr">
@@ -30654,7 +30658,7 @@
       </c>
       <c r="B867" s="7" t="inlineStr">
         <is>
-          <t>16591</t>
+          <t>16603</t>
         </is>
       </c>
       <c r="C867" s="7" t="inlineStr">
@@ -30664,7 +30668,7 @@
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>Xm25Reu24CCST</t>
+          <t>Xm25Reu1Hol</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
@@ -30689,17 +30693,17 @@
       </c>
       <c r="B868" s="7" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>16607</t>
         </is>
       </c>
       <c r="C868" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11177964</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>Xm25Reu2Hol</t>
+          <t>Sp26WTBLSS16Cher</t>
         </is>
       </c>
       <c r="E868" t="inlineStr">
@@ -30724,17 +30728,17 @@
       </c>
       <c r="B869" s="7" t="inlineStr">
         <is>
-          <t>16603</t>
+          <t>16608</t>
         </is>
       </c>
       <c r="C869" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11176612</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>Xm25Reu1Hol</t>
+          <t>Wt26CC15Blue</t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
@@ -30759,17 +30763,17 @@
       </c>
       <c r="B870" s="7" t="inlineStr">
         <is>
-          <t>16607</t>
+          <t>16609</t>
         </is>
       </c>
       <c r="C870" s="7" t="inlineStr">
         <is>
-          <t>11177964</t>
+          <t>11176610</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>Sp26WTBLSS16Cher</t>
+          <t>Wt26TuSS16Duck</t>
         </is>
       </c>
       <c r="E870" t="inlineStr">
@@ -30794,17 +30798,17 @@
       </c>
       <c r="B871" s="7" t="inlineStr">
         <is>
-          <t>16608</t>
+          <t>16610</t>
         </is>
       </c>
       <c r="C871" s="7" t="inlineStr">
         <is>
-          <t>11176612</t>
+          <t>11179880</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
         <is>
-          <t>Wt26CC15Blue</t>
+          <t>SII26SS16Resort</t>
         </is>
       </c>
       <c r="E871" t="inlineStr">
@@ -30829,17 +30833,17 @@
       </c>
       <c r="B872" s="7" t="inlineStr">
         <is>
-          <t>16609</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="C872" s="7" t="inlineStr">
         <is>
-          <t>11176610</t>
+          <t>11177937</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>Wt26TuSS16Duck</t>
+          <t>Sp26CCup16Cherry</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
@@ -30864,17 +30868,17 @@
       </c>
       <c r="B873" s="7" t="inlineStr">
         <is>
-          <t>16610</t>
+          <t>16613</t>
         </is>
       </c>
       <c r="C873" s="7" t="inlineStr">
         <is>
-          <t>11179880</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>SII26SS16Resort</t>
+          <t>Xm25StopDermo</t>
         </is>
       </c>
       <c r="E873" t="inlineStr">
@@ -30899,17 +30903,17 @@
       </c>
       <c r="B874" s="7" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>16614</t>
         </is>
       </c>
       <c r="C874" s="7" t="inlineStr">
         <is>
-          <t>11177937</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
         <is>
-          <t>Sp26CCup16Cherry</t>
+          <t>Xm25StopHopp</t>
         </is>
       </c>
       <c r="E874" t="inlineStr">
@@ -30934,17 +30938,17 @@
       </c>
       <c r="B875" s="7" t="inlineStr">
         <is>
-          <t>16613</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="C875" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11176708</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
         <is>
-          <t>Xm25StopDermo</t>
+          <t>Wt26GlassCC16</t>
         </is>
       </c>
       <c r="E875" t="inlineStr">
@@ -30969,17 +30973,17 @@
       </c>
       <c r="B876" s="7" t="inlineStr">
         <is>
-          <t>16614</t>
+          <t>16659</t>
         </is>
       </c>
       <c r="C876" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11176714</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>Xm25StopHopp</t>
+          <t>Wt26SS16Vac</t>
         </is>
       </c>
       <c r="E876" t="inlineStr">
@@ -31004,17 +31008,17 @@
       </c>
       <c r="B877" s="7" t="inlineStr">
         <is>
-          <t>16658</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="C877" s="7" t="inlineStr">
         <is>
-          <t>11176708</t>
+          <t>11176719</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>Wt26GlassCC16</t>
+          <t>Wt26SSCC24CarryL</t>
         </is>
       </c>
       <c r="E877" t="inlineStr">
@@ -31039,17 +31043,17 @@
       </c>
       <c r="B878" s="7" t="inlineStr">
         <is>
-          <t>16659</t>
+          <t>16661</t>
         </is>
       </c>
       <c r="C878" s="7" t="inlineStr">
         <is>
-          <t>11176714</t>
+          <t>11176720</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>Wt26SS16Vac</t>
+          <t>Wt26SSCC30Togo</t>
         </is>
       </c>
       <c r="E878" t="inlineStr">
@@ -31074,17 +31078,17 @@
       </c>
       <c r="B879" s="7" t="inlineStr">
         <is>
-          <t>16660</t>
+          <t>16662</t>
         </is>
       </c>
       <c r="C879" s="7" t="inlineStr">
         <is>
-          <t>11176719</t>
+          <t>11176721</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>Wt26SSCC24CarryL</t>
+          <t>Sp26Stan30Purp</t>
         </is>
       </c>
       <c r="E879" t="inlineStr">
@@ -31109,17 +31113,17 @@
       </c>
       <c r="B880" s="7" t="inlineStr">
         <is>
-          <t>16661</t>
+          <t>16663</t>
         </is>
       </c>
       <c r="C880" s="7" t="inlineStr">
         <is>
-          <t>11176720</t>
+          <t>11176699</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>Wt26SSCC30Togo</t>
+          <t>Sp26Mug14Rabbit</t>
         </is>
       </c>
       <c r="E880" t="inlineStr">
@@ -31144,17 +31148,17 @@
       </c>
       <c r="B881" s="7" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>16665</t>
         </is>
       </c>
       <c r="C881" s="7" t="inlineStr">
         <is>
-          <t>11176721</t>
+          <t>11176701</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>Sp26Stan30Purp</t>
+          <t>Sp26CC216Rabbit</t>
         </is>
       </c>
       <c r="E881" t="inlineStr">
@@ -31179,17 +31183,17 @@
       </c>
       <c r="B882" s="7" t="inlineStr">
         <is>
-          <t>16663</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C882" s="7" t="inlineStr">
         <is>
-          <t>11176699</t>
+          <t>11176702</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
         <is>
-          <t>Sp26Mug14Rabbit</t>
+          <t>Sp26Tu20Blue</t>
         </is>
       </c>
       <c r="E882" t="inlineStr">
@@ -31214,17 +31218,17 @@
       </c>
       <c r="B883" s="7" t="inlineStr">
         <is>
-          <t>16665</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="C883" s="7" t="inlineStr">
         <is>
-          <t>11176701</t>
+          <t>11176715</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
         <is>
-          <t>Sp26CC216Rabbit</t>
+          <t>Sp26SS16Rabbit</t>
         </is>
       </c>
       <c r="E883" t="inlineStr">
@@ -31249,17 +31253,17 @@
       </c>
       <c r="B884" s="7" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>16669</t>
         </is>
       </c>
       <c r="C884" s="7" t="inlineStr">
         <is>
-          <t>11176702</t>
+          <t>11176711</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
         <is>
-          <t>Sp26Tu20Blue</t>
+          <t>Sp26Gl18Mottled</t>
         </is>
       </c>
       <c r="E884" t="inlineStr">
@@ -31284,17 +31288,17 @@
       </c>
       <c r="B885" s="7" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="C885" s="7" t="inlineStr">
         <is>
-          <t>11176715</t>
+          <t>11176700</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
         <is>
-          <t>Sp26SS16Rabbit</t>
+          <t>Sp26Tz14GlassC</t>
         </is>
       </c>
       <c r="E885" t="inlineStr">
@@ -31319,17 +31323,17 @@
       </c>
       <c r="B886" s="7" t="inlineStr">
         <is>
-          <t>16669</t>
+          <t>16671</t>
         </is>
       </c>
       <c r="C886" s="7" t="inlineStr">
         <is>
-          <t>11176711</t>
+          <t>11176717</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
         <is>
-          <t>Sp26Gl18Mottled</t>
+          <t>Sp26SS12Pink</t>
         </is>
       </c>
       <c r="E886" t="inlineStr">
@@ -31354,17 +31358,17 @@
       </c>
       <c r="B887" s="7" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="C887" s="7" t="inlineStr">
         <is>
-          <t>11176700</t>
+          <t>11176724</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>Sp26Tz14GlassC</t>
+          <t>Sp26CookieJP</t>
         </is>
       </c>
       <c r="E887" t="inlineStr">
@@ -31389,17 +31393,17 @@
       </c>
       <c r="B888" s="7" t="inlineStr">
         <is>
-          <t>16671</t>
+          <t>16673</t>
         </is>
       </c>
       <c r="C888" s="7" t="inlineStr">
         <is>
-          <t>11176717</t>
+          <t>11176703</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>Sp26SS12Pink</t>
+          <t>Sp26Tu16Cherry</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
@@ -31424,17 +31428,17 @@
       </c>
       <c r="B889" s="7" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>16674</t>
         </is>
       </c>
       <c r="C889" s="7" t="inlineStr">
         <is>
-          <t>11176724</t>
+          <t>11176704</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>Sp26CookieJP</t>
+          <t>Sp26CC16Prism</t>
         </is>
       </c>
       <c r="E889" t="inlineStr">
@@ -31459,17 +31463,17 @@
       </c>
       <c r="B890" s="7" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="C890" s="7" t="inlineStr">
         <is>
-          <t>11176703</t>
+          <t>11176722</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>Sp26Tu16Cherry</t>
+          <t>Sp26SSCC24Cherry</t>
         </is>
       </c>
       <c r="E890" t="inlineStr">
@@ -31494,17 +31498,17 @@
       </c>
       <c r="B891" s="7" t="inlineStr">
         <is>
-          <t>16674</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="C891" s="7" t="inlineStr">
         <is>
-          <t>11176704</t>
+          <t>11176718</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
         <is>
-          <t>Sp26CC16Prism</t>
+          <t>Sp26SS16Cherry</t>
         </is>
       </c>
       <c r="E891" t="inlineStr">
@@ -31529,17 +31533,17 @@
       </c>
       <c r="B892" s="7" t="inlineStr">
         <is>
-          <t>16675</t>
+          <t>16677</t>
         </is>
       </c>
       <c r="C892" s="7" t="inlineStr">
         <is>
-          <t>11176722</t>
+          <t>11176723</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
         <is>
-          <t>Sp26SSCC24Cherry</t>
+          <t>Sp26SSVac40Cherr</t>
         </is>
       </c>
       <c r="E892" t="inlineStr">
@@ -31564,17 +31568,17 @@
       </c>
       <c r="B893" s="7" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="C893" s="7" t="inlineStr">
         <is>
-          <t>11176718</t>
+          <t>11176705</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
         <is>
-          <t>Sp26SS16Cherry</t>
+          <t>Sp26ReusTierra</t>
         </is>
       </c>
       <c r="E893" t="inlineStr">
@@ -31599,17 +31603,17 @@
       </c>
       <c r="B894" s="7" t="inlineStr">
         <is>
-          <t>16677</t>
+          <t>16679</t>
         </is>
       </c>
       <c r="C894" s="7" t="inlineStr">
         <is>
-          <t>11176723</t>
+          <t>11176712</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>Sp26SSVac40Cherr</t>
+          <t>Sp26CCReusTierra</t>
         </is>
       </c>
       <c r="E894" t="inlineStr">
@@ -31634,17 +31638,17 @@
       </c>
       <c r="B895" s="7" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="C895" s="7" t="inlineStr">
         <is>
-          <t>11176705</t>
+          <t>11177607</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>Sp26ReusTierra</t>
+          <t>Wt26ReusSiren</t>
         </is>
       </c>
       <c r="E895" t="inlineStr">
@@ -31669,17 +31673,17 @@
       </c>
       <c r="B896" s="7" t="inlineStr">
         <is>
-          <t>16679</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="C896" s="7" t="inlineStr">
         <is>
-          <t>11176712</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>Sp26CCReusTierra</t>
+          <t>Sp26SS16Under</t>
         </is>
       </c>
       <c r="E896" t="inlineStr">
@@ -31704,17 +31708,13 @@
       </c>
       <c r="B897" s="7" t="inlineStr">
         <is>
-          <t>16680</t>
-        </is>
-      </c>
-      <c r="C897" s="7" t="inlineStr">
-        <is>
-          <t>11177607</t>
-        </is>
-      </c>
+          <t>16722</t>
+        </is>
+      </c>
+      <c r="C897" s="7" t="inlineStr"/>
       <c r="D897" t="inlineStr">
         <is>
-          <t>Wt26ReusSiren</t>
+          <t>BearHuggerSpring</t>
         </is>
       </c>
       <c r="E897" t="inlineStr">
@@ -31739,17 +31739,17 @@
       </c>
       <c r="B898" s="7" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>16729</t>
         </is>
       </c>
       <c r="C898" s="7" t="inlineStr">
         <is>
-          <t>11176586</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
         <is>
-          <t>SII26SSCC20Pony</t>
+          <t>Wt26ReusBear</t>
         </is>
       </c>
       <c r="E898" t="inlineStr">
@@ -31774,17 +31774,17 @@
       </c>
       <c r="B899" s="7" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="C899" s="7" t="inlineStr">
         <is>
-          <t>11176587</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>SII26SSCC16Pony</t>
+          <t>Wt26VasoPistache</t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
@@ -31809,7 +31809,7 @@
       </c>
       <c r="B900" s="7" t="inlineStr">
         <is>
-          <t>16721</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="C900" s="7" t="inlineStr">
@@ -31819,7 +31819,7 @@
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>Sp26SS16Under</t>
+          <t>Wt26VasoFresa</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
@@ -31844,13 +31844,17 @@
       </c>
       <c r="B901" s="7" t="inlineStr">
         <is>
-          <t>16722</t>
-        </is>
-      </c>
-      <c r="C901" s="7" t="inlineStr"/>
+          <t>16771</t>
+        </is>
+      </c>
+      <c r="C901" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>BearHuggerSpring</t>
+          <t>Wt26VasoJacaran</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
@@ -31875,7 +31879,7 @@
       </c>
       <c r="B902" s="7" t="inlineStr">
         <is>
-          <t>16729</t>
+          <t>16775</t>
         </is>
       </c>
       <c r="C902" s="7" t="inlineStr">
@@ -31885,7 +31889,7 @@
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>Wt26ReusBear</t>
+          <t>Wt26LlaveroSV</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
@@ -31910,17 +31914,17 @@
       </c>
       <c r="B903" s="7" t="inlineStr">
         <is>
-          <t>16769</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="C903" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11179885</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>Wt26VasoPistache</t>
+          <t>SII26BTL20Resort</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
@@ -31945,17 +31949,17 @@
       </c>
       <c r="B904" s="7" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>16779</t>
         </is>
       </c>
       <c r="C904" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11176592</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>Wt26VasoFresa</t>
+          <t>SII26SSTu12Pony</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
@@ -31980,7 +31984,7 @@
       </c>
       <c r="B905" s="7" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="C905" s="7" t="inlineStr">
@@ -31990,7 +31994,7 @@
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>Wt26VasoJacaran</t>
+          <t>Sp26WTBL19Under</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
@@ -32015,7 +32019,7 @@
       </c>
       <c r="B906" s="7" t="inlineStr">
         <is>
-          <t>16775</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="C906" s="7" t="inlineStr">
@@ -32025,7 +32029,7 @@
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>Wt26LlaveroSV</t>
+          <t>Sp26Tu20Blossom</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
@@ -32050,17 +32054,17 @@
       </c>
       <c r="B907" s="7" t="inlineStr">
         <is>
-          <t>16777</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="C907" s="7" t="inlineStr">
         <is>
-          <t>11179885</t>
+          <t>11176597</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>SII26BTL20Resort</t>
+          <t>SII26BearPony</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
@@ -32085,17 +32089,17 @@
       </c>
       <c r="B908" s="7" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="C908" s="7" t="inlineStr">
         <is>
-          <t>11176592</t>
+          <t>1176593</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>SII26SSTu12Pony</t>
+          <t>SII26BTL16Pony</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
@@ -32120,17 +32124,13 @@
       </c>
       <c r="B909" s="7" t="inlineStr">
         <is>
-          <t>16780</t>
-        </is>
-      </c>
-      <c r="C909" s="7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>16828</t>
+        </is>
+      </c>
+      <c r="C909" s="7" t="inlineStr"/>
       <c r="D909" t="inlineStr">
         <is>
-          <t>Sp26WTBL19Under</t>
+          <t>BearHugWorldCup</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
@@ -32155,17 +32155,17 @@
       </c>
       <c r="B910" s="7" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="C910" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178953</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>Sp26Tu20Blossom</t>
+          <t>Sp26SSCC24Oran</t>
         </is>
       </c>
       <c r="E910" t="inlineStr">
@@ -32190,17 +32190,17 @@
       </c>
       <c r="B911" s="7" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="C911" s="7" t="inlineStr">
         <is>
-          <t>11176597</t>
+          <t>11178954</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>SII26BearPony</t>
+          <t>Sp26SSCC24CarryC</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
@@ -32225,17 +32225,17 @@
       </c>
       <c r="B912" s="7" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>16878</t>
         </is>
       </c>
       <c r="C912" s="7" t="inlineStr">
         <is>
-          <t>1176593</t>
+          <t>11178921</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>SII26BTL16Pony</t>
+          <t>Sp26Tu16Orange</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
@@ -32260,13 +32260,17 @@
       </c>
       <c r="B913" s="7" t="inlineStr">
         <is>
-          <t>16828</t>
-        </is>
-      </c>
-      <c r="C913" s="7" t="inlineStr"/>
+          <t>16883</t>
+        </is>
+      </c>
+      <c r="C913" s="7" t="inlineStr">
+        <is>
+          <t>11178964</t>
+        </is>
+      </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>BearHugWorldCup</t>
+          <t>Sp26KeychainOr</t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
@@ -32291,17 +32295,17 @@
       </c>
       <c r="B914" s="7" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="C914" s="7" t="inlineStr">
         <is>
-          <t>11178953</t>
+          <t>11179003</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>Sp26SSCC24Oran</t>
+          <t>Sp26CC24Teach</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
@@ -32326,17 +32330,17 @@
       </c>
       <c r="B915" s="7" t="inlineStr">
         <is>
-          <t>16877</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="C915" s="7" t="inlineStr">
         <is>
-          <t>11178954</t>
+          <t>11179004</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>Sp26SSCC24CarryC</t>
+          <t>Sp26Tu16Teach</t>
         </is>
       </c>
       <c r="E915" t="inlineStr">
@@ -32361,17 +32365,17 @@
       </c>
       <c r="B916" s="7" t="inlineStr">
         <is>
-          <t>16878</t>
+          <t>16902</t>
         </is>
       </c>
       <c r="C916" s="7" t="inlineStr">
         <is>
-          <t>11178921</t>
+          <t>11178920</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>Sp26Tu16Orange</t>
+          <t>WC26Tu20Yellow</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
@@ -32396,17 +32400,17 @@
       </c>
       <c r="B917" s="7" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="C917" s="7" t="inlineStr">
         <is>
-          <t>11178964</t>
+          <t>11178926</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>Sp26KeychainOr</t>
+          <t>Sp26CC24Or</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
@@ -32431,17 +32435,17 @@
       </c>
       <c r="B918" s="7" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="C918" s="7" t="inlineStr">
         <is>
-          <t>11179003</t>
+          <t>11178965</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>Sp26CC24Teach</t>
+          <t>WC26ToteRoad</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
@@ -32466,17 +32470,17 @@
       </c>
       <c r="B919" s="7" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="C919" s="7" t="inlineStr">
         <is>
-          <t>11178970</t>
+          <t>11178966</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>Sp26SSCC16Band</t>
+          <t>WC26TotePride</t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
@@ -32501,17 +32505,17 @@
       </c>
       <c r="B920" s="7" t="inlineStr">
         <is>
-          <t>16899</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="C920" s="7" t="inlineStr">
         <is>
-          <t>11179004</t>
+          <t>11187369</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>Sp26Tu16Teach</t>
+          <t>WC26BearWC</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
@@ -32536,17 +32540,17 @@
       </c>
       <c r="B921" s="7" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>16909</t>
         </is>
       </c>
       <c r="C921" s="7" t="inlineStr">
         <is>
-          <t>11178920</t>
+          <t>11178944</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>WC26Tu20Yellow</t>
+          <t>WC26SS20BTL</t>
         </is>
       </c>
       <c r="E921" t="inlineStr">
@@ -32571,17 +32575,17 @@
       </c>
       <c r="B922" s="7" t="inlineStr">
         <is>
-          <t>16903</t>
+          <t>16912</t>
         </is>
       </c>
       <c r="C922" s="7" t="inlineStr">
         <is>
-          <t>11178926</t>
+          <t>11178949</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>Sp26CC24Or</t>
+          <t>WC26SS20Pull</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
@@ -32606,17 +32610,17 @@
       </c>
       <c r="B923" s="7" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>16914</t>
         </is>
       </c>
       <c r="C923" s="7" t="inlineStr">
         <is>
-          <t>11178965</t>
+          <t>11178947</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>WC26ToteRoad</t>
+          <t>Sp26StanQuen20</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
@@ -32641,17 +32645,17 @@
       </c>
       <c r="B924" s="7" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="C924" s="7" t="inlineStr">
         <is>
-          <t>11178966</t>
+          <t>11178972</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>WC26TotePride</t>
+          <t>Sp26Vac16Stan</t>
         </is>
       </c>
       <c r="E924" t="inlineStr">
@@ -32676,17 +32680,17 @@
       </c>
       <c r="B925" s="7" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="C925" s="7" t="inlineStr">
         <is>
-          <t>11187369</t>
+          <t>11178917</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>WC26BearWC</t>
+          <t>WC26DW12Oran</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
@@ -32711,17 +32715,17 @@
       </c>
       <c r="B926" s="7" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="C926" s="7" t="inlineStr">
         <is>
-          <t>11178944</t>
+          <t>11187370</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>WC26SS20BTL</t>
+          <t>WC26SS16Black</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
@@ -32746,17 +32750,13 @@
       </c>
       <c r="B927" s="7" t="inlineStr">
         <is>
-          <t>16912</t>
-        </is>
-      </c>
-      <c r="C927" s="7" t="inlineStr">
-        <is>
-          <t>11178949</t>
-        </is>
-      </c>
+          <t>16971</t>
+        </is>
+      </c>
+      <c r="C927" s="7" t="inlineStr"/>
       <c r="D927" t="inlineStr">
         <is>
-          <t>WC26SS20Pull</t>
+          <t>WC26BearMex</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
@@ -32781,17 +32781,17 @@
       </c>
       <c r="B928" s="7" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>16978</t>
         </is>
       </c>
       <c r="C928" s="7" t="inlineStr">
         <is>
-          <t>11178947</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>Sp26StanQuen20</t>
+          <t>WC26LlaveroB</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
@@ -32816,17 +32816,13 @@
       </c>
       <c r="B929" s="7" t="inlineStr">
         <is>
-          <t>16917</t>
-        </is>
-      </c>
-      <c r="C929" s="7" t="inlineStr">
-        <is>
-          <t>11178972</t>
-        </is>
-      </c>
+          <t>16989</t>
+        </is>
+      </c>
+      <c r="C929" s="7" t="inlineStr"/>
       <c r="D929" t="inlineStr">
         <is>
-          <t>Sp26Vac16Stan</t>
+          <t>SII26SS12Aniv</t>
         </is>
       </c>
       <c r="E929" t="inlineStr">
@@ -32851,17 +32847,13 @@
       </c>
       <c r="B930" s="7" t="inlineStr">
         <is>
-          <t>16921</t>
-        </is>
-      </c>
-      <c r="C930" s="7" t="inlineStr">
-        <is>
-          <t>11178917</t>
-        </is>
-      </c>
+          <t>17298</t>
+        </is>
+      </c>
+      <c r="C930" s="7" t="inlineStr"/>
       <c r="D930" t="inlineStr">
         <is>
-          <t>WC26DW12Oran</t>
+          <t>SII26SSBTL12Aniv</t>
         </is>
       </c>
       <c r="E930" t="inlineStr">
@@ -32886,17 +32878,13 @@
       </c>
       <c r="B931" s="7" t="inlineStr">
         <is>
-          <t>16958</t>
-        </is>
-      </c>
-      <c r="C931" s="7" t="inlineStr">
-        <is>
-          <t>11187370</t>
-        </is>
-      </c>
+          <t>17299</t>
+        </is>
+      </c>
+      <c r="C931" s="7" t="inlineStr"/>
       <c r="D931" t="inlineStr">
         <is>
-          <t>WC26SS16Black</t>
+          <t>SII26Mug14Aniv</t>
         </is>
       </c>
       <c r="E931" t="inlineStr">
@@ -32921,17 +32909,13 @@
       </c>
       <c r="B932" s="7" t="inlineStr">
         <is>
-          <t>16959</t>
-        </is>
-      </c>
-      <c r="C932" s="7" t="inlineStr">
-        <is>
-          <t>11187372</t>
-        </is>
-      </c>
+          <t>17307</t>
+        </is>
+      </c>
+      <c r="C932" s="7" t="inlineStr"/>
       <c r="D932" t="inlineStr">
         <is>
-          <t>WC26Tu24DW</t>
+          <t>SII26Doodle16</t>
         </is>
       </c>
       <c r="E932" t="inlineStr">
@@ -32956,13 +32940,13 @@
       </c>
       <c r="B933" s="7" t="inlineStr">
         <is>
-          <t>16971</t>
+          <t>52206</t>
         </is>
       </c>
       <c r="C933" s="7" t="inlineStr"/>
       <c r="D933" t="inlineStr">
         <is>
-          <t>WC26BearMex</t>
+          <t>Vaso Rewards</t>
         </is>
       </c>
       <c r="E933" t="inlineStr">
@@ -32987,17 +32971,13 @@
       </c>
       <c r="B934" s="7" t="inlineStr">
         <is>
-          <t>16978</t>
-        </is>
-      </c>
-      <c r="C934" s="7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>53500</t>
+        </is>
+      </c>
+      <c r="C934" s="7" t="inlineStr"/>
       <c r="D934" t="inlineStr">
         <is>
-          <t>WC26LlaveroB</t>
+          <t>ResSS16TGradient</t>
         </is>
       </c>
       <c r="E934" t="inlineStr">
@@ -33022,13 +33002,13 @@
       </c>
       <c r="B935" s="7" t="inlineStr">
         <is>
-          <t>16989</t>
+          <t>53834</t>
         </is>
       </c>
       <c r="C935" s="7" t="inlineStr"/>
       <c r="D935" t="inlineStr">
         <is>
-          <t>SII26SS12Aniv</t>
+          <t>Tazas SBX Genérico</t>
         </is>
       </c>
       <c r="E935" t="inlineStr">
@@ -33053,13 +33033,13 @@
       </c>
       <c r="B936" s="7" t="inlineStr">
         <is>
-          <t>17298</t>
+          <t>53835</t>
         </is>
       </c>
       <c r="C936" s="7" t="inlineStr"/>
       <c r="D936" t="inlineStr">
         <is>
-          <t>SII26SSBTL12Aniv</t>
+          <t>CCupPlastic SBX Genérico</t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
@@ -33084,13 +33064,13 @@
       </c>
       <c r="B937" s="7" t="inlineStr">
         <is>
-          <t>17299</t>
+          <t>53836</t>
         </is>
       </c>
       <c r="C937" s="7" t="inlineStr"/>
       <c r="D937" t="inlineStr">
         <is>
-          <t>SII26Mug14Aniv</t>
+          <t>CCup Acero SBX Genérico</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
@@ -33115,13 +33095,13 @@
       </c>
       <c r="B938" s="7" t="inlineStr">
         <is>
-          <t>17307</t>
+          <t>53837</t>
         </is>
       </c>
       <c r="C938" s="7" t="inlineStr"/>
       <c r="D938" t="inlineStr">
         <is>
-          <t>SII26Doodle16</t>
+          <t>Tumb acero SBX Genérico</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
@@ -33146,13 +33126,13 @@
       </c>
       <c r="B939" s="7" t="inlineStr">
         <is>
-          <t>52206</t>
+          <t>53838</t>
         </is>
       </c>
       <c r="C939" s="7" t="inlineStr"/>
       <c r="D939" t="inlineStr">
         <is>
-          <t>Vaso Rewards</t>
+          <t>Tumb Plastic SBX Genérico</t>
         </is>
       </c>
       <c r="E939" t="inlineStr">
@@ -33177,13 +33157,13 @@
       </c>
       <c r="B940" s="7" t="inlineStr">
         <is>
-          <t>53500</t>
+          <t>53839</t>
         </is>
       </c>
       <c r="C940" s="7" t="inlineStr"/>
       <c r="D940" t="inlineStr">
         <is>
-          <t>ResSS16TGradient</t>
+          <t>Stanley SBX Genérico</t>
         </is>
       </c>
       <c r="E940" t="inlineStr">
@@ -33208,13 +33188,13 @@
       </c>
       <c r="B941" s="7" t="inlineStr">
         <is>
-          <t>53834</t>
+          <t>53840</t>
         </is>
       </c>
       <c r="C941" s="7" t="inlineStr"/>
       <c r="D941" t="inlineStr">
         <is>
-          <t>Tazas SBX Genérico</t>
+          <t>Llavero SBX Genérico</t>
         </is>
       </c>
       <c r="E941" t="inlineStr">
@@ -33239,13 +33219,13 @@
       </c>
       <c r="B942" s="7" t="inlineStr">
         <is>
-          <t>53835</t>
+          <t>53841</t>
         </is>
       </c>
       <c r="C942" s="7" t="inlineStr"/>
       <c r="D942" t="inlineStr">
         <is>
-          <t>CCupPlastic SBX Genérico</t>
+          <t>Stoppers SBX Genérico</t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
@@ -33270,13 +33250,13 @@
       </c>
       <c r="B943" s="7" t="inlineStr">
         <is>
-          <t>53836</t>
+          <t>53842</t>
         </is>
       </c>
       <c r="C943" s="7" t="inlineStr"/>
       <c r="D943" t="inlineStr">
         <is>
-          <t>CCup Acero SBX Genérico</t>
+          <t>Tote bags SBX Genérico</t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
@@ -33301,13 +33281,13 @@
       </c>
       <c r="B944" s="7" t="inlineStr">
         <is>
-          <t>53837</t>
+          <t>53843</t>
         </is>
       </c>
       <c r="C944" s="7" t="inlineStr"/>
       <c r="D944" t="inlineStr">
         <is>
-          <t>Tumb acero SBX Genérico</t>
+          <t>Pines SBX Genérico</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
@@ -33332,13 +33312,13 @@
       </c>
       <c r="B945" s="7" t="inlineStr">
         <is>
-          <t>53838</t>
+          <t>53844</t>
         </is>
       </c>
       <c r="C945" s="7" t="inlineStr"/>
       <c r="D945" t="inlineStr">
         <is>
-          <t>Tumb Plastic SBX Genérico</t>
+          <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
@@ -33363,13 +33343,13 @@
       </c>
       <c r="B946" s="7" t="inlineStr">
         <is>
-          <t>53839</t>
+          <t>53845</t>
         </is>
       </c>
       <c r="C946" s="7" t="inlineStr"/>
       <c r="D946" t="inlineStr">
         <is>
-          <t>Stanley SBX Genérico</t>
+          <t>Set Reusa SBX Genérico</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
@@ -33394,13 +33374,13 @@
       </c>
       <c r="B947" s="7" t="inlineStr">
         <is>
-          <t>53840</t>
+          <t>53949</t>
         </is>
       </c>
       <c r="C947" s="7" t="inlineStr"/>
       <c r="D947" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
+          <t>Xm25Tu12Hol</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
@@ -33425,13 +33405,13 @@
       </c>
       <c r="B948" s="7" t="inlineStr">
         <is>
-          <t>53841</t>
+          <t>53951</t>
         </is>
       </c>
       <c r="C948" s="7" t="inlineStr"/>
       <c r="D948" t="inlineStr">
         <is>
-          <t>Stoppers SBX Genérico</t>
+          <t>Xm25StopDermo</t>
         </is>
       </c>
       <c r="E948" t="inlineStr">
@@ -33456,13 +33436,13 @@
       </c>
       <c r="B949" s="7" t="inlineStr">
         <is>
-          <t>53842</t>
+          <t>53952</t>
         </is>
       </c>
       <c r="C949" s="7" t="inlineStr"/>
       <c r="D949" t="inlineStr">
         <is>
-          <t>Tote bags SBX Genérico</t>
+          <t>Xm25StopMike</t>
         </is>
       </c>
       <c r="E949" t="inlineStr">
@@ -33487,13 +33467,13 @@
       </c>
       <c r="B950" s="7" t="inlineStr">
         <is>
-          <t>53843</t>
+          <t>53953</t>
         </is>
       </c>
       <c r="C950" s="7" t="inlineStr"/>
       <c r="D950" t="inlineStr">
         <is>
-          <t>Pines SBX Genérico</t>
+          <t>Xm25StopDust</t>
         </is>
       </c>
       <c r="E950" t="inlineStr">
@@ -33518,13 +33498,13 @@
       </c>
       <c r="B951" s="7" t="inlineStr">
         <is>
-          <t>53844</t>
+          <t>53958</t>
         </is>
       </c>
       <c r="C951" s="7" t="inlineStr"/>
       <c r="D951" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
+          <t>Xm25Reu1Hol</t>
         </is>
       </c>
       <c r="E951" t="inlineStr">
@@ -33549,13 +33529,13 @@
       </c>
       <c r="B952" s="7" t="inlineStr">
         <is>
-          <t>53845</t>
+          <t>53959</t>
         </is>
       </c>
       <c r="C952" s="7" t="inlineStr"/>
       <c r="D952" t="inlineStr">
         <is>
-          <t>Set Reusa SBX Genérico</t>
+          <t>Xm25Reu2Hol</t>
         </is>
       </c>
       <c r="E952" t="inlineStr">
@@ -33580,13 +33560,13 @@
       </c>
       <c r="B953" s="7" t="inlineStr">
         <is>
-          <t>53949</t>
+          <t>53962</t>
         </is>
       </c>
       <c r="C953" s="7" t="inlineStr"/>
       <c r="D953" t="inlineStr">
         <is>
-          <t>Xm25Tu12Hol</t>
+          <t>Xm25Tag</t>
         </is>
       </c>
       <c r="E953" t="inlineStr">
@@ -33611,13 +33591,13 @@
       </c>
       <c r="B954" s="7" t="inlineStr">
         <is>
-          <t>53951</t>
+          <t>53965</t>
         </is>
       </c>
       <c r="C954" s="7" t="inlineStr"/>
       <c r="D954" t="inlineStr">
         <is>
-          <t>Xm25StopDermo</t>
+          <t>Xm25StopWill</t>
         </is>
       </c>
       <c r="E954" t="inlineStr">
@@ -33642,13 +33622,13 @@
       </c>
       <c r="B955" s="7" t="inlineStr">
         <is>
-          <t>53952</t>
+          <t>53966</t>
         </is>
       </c>
       <c r="C955" s="7" t="inlineStr"/>
       <c r="D955" t="inlineStr">
         <is>
-          <t>Xm25StopMike</t>
+          <t>Xm25StopMax</t>
         </is>
       </c>
       <c r="E955" t="inlineStr">
@@ -33673,13 +33653,13 @@
       </c>
       <c r="B956" s="7" t="inlineStr">
         <is>
-          <t>53953</t>
+          <t>53967</t>
         </is>
       </c>
       <c r="C956" s="7" t="inlineStr"/>
       <c r="D956" t="inlineStr">
         <is>
-          <t>Xm25StopDust</t>
+          <t>Xm25StopHopp</t>
         </is>
       </c>
       <c r="E956" t="inlineStr">
@@ -33704,13 +33684,13 @@
       </c>
       <c r="B957" s="7" t="inlineStr">
         <is>
-          <t>53958</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="C957" s="7" t="inlineStr"/>
       <c r="D957" t="inlineStr">
         <is>
-          <t>Xm25Reu1Hol</t>
+          <t>Sp26BlindBox</t>
         </is>
       </c>
       <c r="E957" t="inlineStr">
@@ -33735,13 +33715,13 @@
       </c>
       <c r="B958" s="7" t="inlineStr">
         <is>
-          <t>53959</t>
+          <t>54192</t>
         </is>
       </c>
       <c r="C958" s="7" t="inlineStr"/>
       <c r="D958" t="inlineStr">
         <is>
-          <t>Xm25Reu2Hol</t>
+          <t>SII26GICCColor</t>
         </is>
       </c>
       <c r="E958" t="inlineStr">
@@ -33766,13 +33746,13 @@
       </c>
       <c r="B959" s="7" t="inlineStr">
         <is>
-          <t>53962</t>
+          <t>54201</t>
         </is>
       </c>
       <c r="C959" s="7" t="inlineStr"/>
       <c r="D959" t="inlineStr">
         <is>
-          <t>Xm25Tag</t>
+          <t>SII26CC24Rain</t>
         </is>
       </c>
       <c r="E959" t="inlineStr">
@@ -33797,13 +33777,13 @@
       </c>
       <c r="B960" s="7" t="inlineStr">
         <is>
-          <t>53965</t>
+          <t>54213</t>
         </is>
       </c>
       <c r="C960" s="7" t="inlineStr"/>
       <c r="D960" t="inlineStr">
         <is>
-          <t>Xm25StopWill</t>
+          <t>WC26Reus</t>
         </is>
       </c>
       <c r="E960" t="inlineStr">
@@ -33823,18 +33803,18 @@
     <row r="961" ht="24" customHeight="1">
       <c r="A961" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B961" s="7" t="inlineStr">
         <is>
-          <t>53966</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="C961" s="7" t="inlineStr"/>
       <c r="D961" t="inlineStr">
         <is>
-          <t>Xm25StopMax</t>
+          <t>ESS Reusable cup</t>
         </is>
       </c>
       <c r="E961" t="inlineStr">
@@ -33847,25 +33827,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G961" t="inlineStr"/>
-      <c r="H961" t="inlineStr"/>
-      <c r="I961" t="inlineStr"/>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>lote-01/11372.jpeg</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="962" ht="24" customHeight="1">
       <c r="A962" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B962" s="7" t="inlineStr">
         <is>
-          <t>53967</t>
-        </is>
-      </c>
-      <c r="C962" s="7" t="inlineStr"/>
+          <t>16312</t>
+        </is>
+      </c>
+      <c r="C962" s="7" t="inlineStr">
+        <is>
+          <t>11160995</t>
+        </is>
+      </c>
       <c r="D962" t="inlineStr">
         <is>
-          <t>Xm25StopHopp</t>
+          <t>COR26BTL20</t>
         </is>
       </c>
       <c r="E962" t="inlineStr">
@@ -33878,25 +33874,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G962" t="inlineStr"/>
-      <c r="H962" t="inlineStr"/>
-      <c r="I962" t="inlineStr"/>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>lote-01/16312.jpeg</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="963" ht="24" customHeight="1">
       <c r="A963" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B963" s="7" t="inlineStr">
         <is>
-          <t>54112</t>
-        </is>
-      </c>
-      <c r="C963" s="7" t="inlineStr"/>
+          <t>16531</t>
+        </is>
+      </c>
+      <c r="C963" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="D963" t="inlineStr">
         <is>
-          <t>Sp26BlindBox</t>
+          <t>Sp26NEBlack</t>
         </is>
       </c>
       <c r="E963" t="inlineStr">
@@ -33909,25 +33921,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G963" t="inlineStr"/>
-      <c r="H963" t="inlineStr"/>
-      <c r="I963" t="inlineStr"/>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>lote-01/16531.jpeg</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="964" ht="24" customHeight="1">
       <c r="A964" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B964" s="7" t="inlineStr">
         <is>
-          <t>54192</t>
-        </is>
-      </c>
-      <c r="C964" s="7" t="inlineStr"/>
+          <t>16532</t>
+        </is>
+      </c>
+      <c r="C964" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="D964" t="inlineStr">
         <is>
-          <t>SII26GICCColor</t>
+          <t>Sp26NECrossB</t>
         </is>
       </c>
       <c r="E964" t="inlineStr">
@@ -33940,25 +33968,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G964" t="inlineStr"/>
-      <c r="H964" t="inlineStr"/>
-      <c r="I964" t="inlineStr"/>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>lote-01/16532.jpeg</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="965" ht="24" customHeight="1">
       <c r="A965" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B965" s="7" t="inlineStr">
         <is>
-          <t>54201</t>
-        </is>
-      </c>
-      <c r="C965" s="7" t="inlineStr"/>
+          <t>16601</t>
+        </is>
+      </c>
+      <c r="C965" s="7" t="inlineStr">
+        <is>
+          <t>11170187</t>
+        </is>
+      </c>
       <c r="D965" t="inlineStr">
         <is>
-          <t>SII26CC24Rain</t>
+          <t>ToteBag MxPais</t>
         </is>
       </c>
       <c r="E965" t="inlineStr">
@@ -33971,25 +34015,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G965" t="inlineStr"/>
-      <c r="H965" t="inlineStr"/>
-      <c r="I965" t="inlineStr"/>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>lote-01/011170187.jpeg</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="966" ht="24" customHeight="1">
       <c r="A966" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B966" s="7" t="inlineStr">
         <is>
-          <t>54213</t>
-        </is>
-      </c>
-      <c r="C966" s="7" t="inlineStr"/>
+          <t>16643</t>
+        </is>
+      </c>
+      <c r="C966" s="7" t="inlineStr">
+        <is>
+          <t>11170102</t>
+        </is>
+      </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>WC26Reus</t>
+          <t>DiscoveryCDMX</t>
         </is>
       </c>
       <c r="E966" t="inlineStr">
@@ -34002,9 +34062,21 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G966" t="inlineStr"/>
-      <c r="H966" t="inlineStr"/>
-      <c r="I966" t="inlineStr"/>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>lote-01/011170102.jpeg</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="967" ht="24" customHeight="1">
       <c r="A967" t="inlineStr">
@@ -34014,17 +34086,17 @@
       </c>
       <c r="B967" s="7" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="C967" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11176710</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
         <is>
-          <t>Sp26NEBlack</t>
+          <t>Sp26CC24Dome</t>
         </is>
       </c>
       <c r="E967" t="inlineStr">
@@ -34039,7 +34111,7 @@
       </c>
       <c r="G967" t="inlineStr">
         <is>
-          <t>lote-01/16531.jpeg</t>
+          <t>lote-01/011176710.jpeg</t>
         </is>
       </c>
       <c r="H967" t="inlineStr">
@@ -34049,7 +34121,7 @@
       </c>
       <c r="I967" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -34061,17 +34133,17 @@
       </c>
       <c r="B968" s="7" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="C968" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11170174</t>
         </is>
       </c>
       <c r="D968" t="inlineStr">
         <is>
-          <t>Sp26NECrossB</t>
+          <t>DiscCC24MxPais</t>
         </is>
       </c>
       <c r="E968" t="inlineStr">
@@ -34086,7 +34158,7 @@
       </c>
       <c r="G968" t="inlineStr">
         <is>
-          <t>lote-01/16532.jpeg</t>
+          <t>lote-01/011170174.jpeg</t>
         </is>
       </c>
       <c r="H968" t="inlineStr">
@@ -34096,7 +34168,7 @@
       </c>
       <c r="I968" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -34108,17 +34180,17 @@
       </c>
       <c r="B969" s="7" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="C969" s="7" t="inlineStr">
         <is>
-          <t>11170187</t>
+          <t>11170158</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
         <is>
-          <t>ToteBag MxPais</t>
+          <t>Disc2ozChiapas</t>
         </is>
       </c>
       <c r="E969" t="inlineStr">
@@ -34133,7 +34205,7 @@
       </c>
       <c r="G969" t="inlineStr">
         <is>
-          <t>lote-01/011170187.jpeg</t>
+          <t>lote-01/011170158.jpeg</t>
         </is>
       </c>
       <c r="H969" t="inlineStr">
@@ -34155,17 +34227,17 @@
       </c>
       <c r="B970" s="7" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="C970" s="7" t="inlineStr">
         <is>
-          <t>11170102</t>
+          <t>11170147</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
         <is>
-          <t>DiscoveryCDMX</t>
+          <t>Disc2ozMxPais</t>
         </is>
       </c>
       <c r="E970" t="inlineStr">
@@ -34180,7 +34252,7 @@
       </c>
       <c r="G970" t="inlineStr">
         <is>
-          <t>lote-01/011170102.jpeg</t>
+          <t>lote-01/011170147.jpeg</t>
         </is>
       </c>
       <c r="H970" t="inlineStr">
@@ -34202,17 +34274,17 @@
       </c>
       <c r="B971" s="7" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="C971" s="7" t="inlineStr">
         <is>
-          <t>11176710</t>
+          <t>11170149</t>
         </is>
       </c>
       <c r="D971" t="inlineStr">
         <is>
-          <t>Sp26CC24Dome</t>
+          <t>Disc2ozCDMX</t>
         </is>
       </c>
       <c r="E971" t="inlineStr">
@@ -34227,7 +34299,7 @@
       </c>
       <c r="G971" t="inlineStr">
         <is>
-          <t>lote-01/011176710.jpeg</t>
+          <t>lote-01/011170149.jpeg</t>
         </is>
       </c>
       <c r="H971" t="inlineStr">
@@ -34249,17 +34321,17 @@
       </c>
       <c r="B972" s="7" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="C972" s="7" t="inlineStr">
         <is>
-          <t>11170174</t>
+          <t>11176586</t>
         </is>
       </c>
       <c r="D972" t="inlineStr">
         <is>
-          <t>DiscCC24MxPais</t>
+          <t>SII26SSCC20Pony</t>
         </is>
       </c>
       <c r="E972" t="inlineStr">
@@ -34274,7 +34346,7 @@
       </c>
       <c r="G972" t="inlineStr">
         <is>
-          <t>lote-01/011170174.jpeg</t>
+          <t>lote-01/16719.jpeg</t>
         </is>
       </c>
       <c r="H972" t="inlineStr">
@@ -34284,7 +34356,7 @@
       </c>
       <c r="I972" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -34296,17 +34368,17 @@
       </c>
       <c r="B973" s="7" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>16720</t>
         </is>
       </c>
       <c r="C973" s="7" t="inlineStr">
         <is>
-          <t>11170147</t>
+          <t>11176587</t>
         </is>
       </c>
       <c r="D973" t="inlineStr">
         <is>
-          <t>Disc2ozMxPais</t>
+          <t>SII26SSCC16Pony</t>
         </is>
       </c>
       <c r="E973" t="inlineStr">
@@ -34321,7 +34393,7 @@
       </c>
       <c r="G973" t="inlineStr">
         <is>
-          <t>lote-01/011170147.jpeg</t>
+          <t>lote-01/16720.jpeg</t>
         </is>
       </c>
       <c r="H973" t="inlineStr">
@@ -34331,7 +34403,7 @@
       </c>
       <c r="I973" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -34343,17 +34415,17 @@
       </c>
       <c r="B974" s="7" t="inlineStr">
         <is>
-          <t>16689</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="C974" s="7" t="inlineStr">
         <is>
-          <t>11170149</t>
+          <t>11178952</t>
         </is>
       </c>
       <c r="D974" t="inlineStr">
         <is>
-          <t>Disc2ozCDMX</t>
+          <t>WC26SSCC24Grad</t>
         </is>
       </c>
       <c r="E974" t="inlineStr">
@@ -34368,7 +34440,7 @@
       </c>
       <c r="G974" t="inlineStr">
         <is>
-          <t>lote-01/011170149.jpeg</t>
+          <t>lote-01/011178952.jpeg</t>
         </is>
       </c>
       <c r="H974" t="inlineStr">
@@ -34390,17 +34462,17 @@
       </c>
       <c r="B975" s="7" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="C975" s="7" t="inlineStr">
         <is>
-          <t>11178952</t>
+          <t>11178922</t>
         </is>
       </c>
       <c r="D975" t="inlineStr">
         <is>
-          <t>WC26SSCC24Grad</t>
+          <t>WC26Tu16Flower</t>
         </is>
       </c>
       <c r="E975" t="inlineStr">
@@ -34415,7 +34487,7 @@
       </c>
       <c r="G975" t="inlineStr">
         <is>
-          <t>lote-01/011178952.jpeg</t>
+          <t>lote-01/011178922.jpeg</t>
         </is>
       </c>
       <c r="H975" t="inlineStr">
@@ -34437,17 +34509,17 @@
       </c>
       <c r="B976" s="7" t="inlineStr">
         <is>
-          <t>16879</t>
+          <t>16880</t>
         </is>
       </c>
       <c r="C976" s="7" t="inlineStr">
         <is>
-          <t>11178922</t>
+          <t>11178928</t>
         </is>
       </c>
       <c r="D976" t="inlineStr">
         <is>
-          <t>WC26Tu16Flower</t>
+          <t>WC26CC24Road</t>
         </is>
       </c>
       <c r="E976" t="inlineStr">
@@ -34462,7 +34534,7 @@
       </c>
       <c r="G976" t="inlineStr">
         <is>
-          <t>lote-01/011178922.jpeg</t>
+          <t>lote-01/011178928.jpeg</t>
         </is>
       </c>
       <c r="H976" t="inlineStr">
@@ -34484,17 +34556,17 @@
       </c>
       <c r="B977" s="7" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="C977" s="7" t="inlineStr">
         <is>
-          <t>11178928</t>
+          <t>11178930</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
         <is>
-          <t>WC26CC24Road</t>
+          <t>WC26CC24Pride</t>
         </is>
       </c>
       <c r="E977" t="inlineStr">
@@ -34509,7 +34581,7 @@
       </c>
       <c r="G977" t="inlineStr">
         <is>
-          <t>lote-01/011178928.jpeg</t>
+          <t>lote-01/011178930.jpeg</t>
         </is>
       </c>
       <c r="H977" t="inlineStr">
@@ -34531,17 +34603,17 @@
       </c>
       <c r="B978" s="7" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="C978" s="7" t="inlineStr">
         <is>
-          <t>11178930</t>
+          <t>11178934</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
         <is>
-          <t>WC26CC24Pride</t>
+          <t>SII26CC24GID</t>
         </is>
       </c>
       <c r="E978" t="inlineStr">
@@ -34556,7 +34628,7 @@
       </c>
       <c r="G978" t="inlineStr">
         <is>
-          <t>lote-01/011178930.jpeg</t>
+          <t>lote-01/16884.jpeg</t>
         </is>
       </c>
       <c r="H978" t="inlineStr">
@@ -34566,7 +34638,7 @@
       </c>
       <c r="I978" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -34578,17 +34650,17 @@
       </c>
       <c r="B979" s="7" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>16896</t>
         </is>
       </c>
       <c r="C979" s="7" t="inlineStr">
         <is>
-          <t>11178934</t>
+          <t>11178970</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t>SII26CC24GID</t>
+          <t>Sp26SSCC16Band</t>
         </is>
       </c>
       <c r="E979" t="inlineStr">
@@ -34603,7 +34675,7 @@
       </c>
       <c r="G979" t="inlineStr">
         <is>
-          <t>lote-01/16884.jpeg</t>
+          <t>lote-01/16896.jpeg</t>
         </is>
       </c>
       <c r="H979" t="inlineStr">
@@ -35471,17 +35543,17 @@
       </c>
       <c r="B998" s="7" t="inlineStr">
         <is>
-          <t>16995</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="C998" s="7" t="inlineStr">
         <is>
-          <t>11186650</t>
+          <t>11187372</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
         <is>
-          <t>SII26SS16Pleat</t>
+          <t>WC26Tu24DW</t>
         </is>
       </c>
       <c r="E998" t="inlineStr">
@@ -35496,7 +35568,7 @@
       </c>
       <c r="G998" t="inlineStr">
         <is>
-          <t>lote-01/011186650.jpeg</t>
+          <t>lote-01/16959.jpeg</t>
         </is>
       </c>
       <c r="H998" t="inlineStr">
@@ -35506,7 +35578,7 @@
       </c>
       <c r="I998" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -35518,17 +35590,17 @@
       </c>
       <c r="B999" s="7" t="inlineStr">
         <is>
-          <t>16997</t>
+          <t>16995</t>
         </is>
       </c>
       <c r="C999" s="7" t="inlineStr">
         <is>
-          <t>11186646</t>
+          <t>11186650</t>
         </is>
       </c>
       <c r="D999" t="inlineStr">
         <is>
-          <t>SII26SS12Charm</t>
+          <t>SII26SS16Pleat</t>
         </is>
       </c>
       <c r="E999" t="inlineStr">
@@ -35543,7 +35615,7 @@
       </c>
       <c r="G999" t="inlineStr">
         <is>
-          <t>lote-01/011186646.jpeg</t>
+          <t>lote-01/011186650.jpeg</t>
         </is>
       </c>
       <c r="H999" t="inlineStr">
@@ -35565,17 +35637,17 @@
       </c>
       <c r="B1000" s="7" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>16997</t>
         </is>
       </c>
       <c r="C1000" s="7" t="inlineStr">
         <is>
-          <t>11186658</t>
+          <t>11186646</t>
         </is>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>SII26SS20Hand</t>
+          <t>SII26SS12Charm</t>
         </is>
       </c>
       <c r="E1000" t="inlineStr">
@@ -35590,7 +35662,7 @@
       </c>
       <c r="G1000" t="inlineStr">
         <is>
-          <t>lote-01/011186658.jpeg</t>
+          <t>lote-01/011186646.jpeg</t>
         </is>
       </c>
       <c r="H1000" t="inlineStr">
@@ -35612,17 +35684,17 @@
       </c>
       <c r="B1001" s="7" t="inlineStr">
         <is>
-          <t>16999</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="C1001" s="7" t="inlineStr">
         <is>
-          <t>11186659</t>
+          <t>11186658</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
-          <t>SII26BTLSS20</t>
+          <t>SII26SS20Hand</t>
         </is>
       </c>
       <c r="E1001" t="inlineStr">
@@ -35637,7 +35709,7 @@
       </c>
       <c r="G1001" t="inlineStr">
         <is>
-          <t>lote-01/011186659.jpeg</t>
+          <t>lote-01/011186658.jpeg</t>
         </is>
       </c>
       <c r="H1001" t="inlineStr">
@@ -35654,22 +35726,22 @@
     <row r="1002" ht="24" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B1002" s="7" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="C1002" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11186659</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>ESS Chemex 15oz</t>
+          <t>SII26BTLSS20</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
@@ -35679,12 +35751,24 @@
       </c>
       <c r="F1002" t="inlineStr">
         <is>
-          <t>SECUNDARIO</t>
-        </is>
-      </c>
-      <c r="G1002" t="inlineStr"/>
-      <c r="H1002" t="inlineStr"/>
-      <c r="I1002" t="inlineStr"/>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>lote-01/011186659.jpeg</t>
+        </is>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>skuIntl</t>
+        </is>
+      </c>
     </row>
     <row r="1003" ht="24" customHeight="1">
       <c r="A1003" t="inlineStr">
@@ -35694,13 +35778,17 @@
       </c>
       <c r="B1003" s="7" t="inlineStr">
         <is>
-          <t>11652</t>
-        </is>
-      </c>
-      <c r="C1003" s="7" t="inlineStr"/>
+          <t>9616</t>
+        </is>
+      </c>
+      <c r="C1003" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>ResSS12Mercury</t>
+          <t>ESS Chemex 15oz</t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
@@ -35725,13 +35813,13 @@
       </c>
       <c r="B1004" s="7" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>11652</t>
         </is>
       </c>
       <c r="C1004" s="7" t="inlineStr"/>
       <c r="D1004" t="inlineStr">
         <is>
-          <t>Been There Mexico City 14 oz</t>
+          <t>ResSS12Mercury</t>
         </is>
       </c>
       <c r="E1004" t="inlineStr">
@@ -35756,13 +35844,13 @@
       </c>
       <c r="B1005" s="7" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="C1005" s="7" t="inlineStr"/>
       <c r="D1005" t="inlineStr">
         <is>
-          <t>Been There Mexico 14 oz</t>
+          <t>Been There Mexico City 14 oz</t>
         </is>
       </c>
       <c r="E1005" t="inlineStr">
@@ -35787,13 +35875,13 @@
       </c>
       <c r="B1006" s="7" t="inlineStr">
         <is>
-          <t>11811</t>
+          <t>11810</t>
         </is>
       </c>
       <c r="C1006" s="7" t="inlineStr"/>
       <c r="D1006" t="inlineStr">
         <is>
-          <t>Been There Los Cabos 14 oz</t>
+          <t>Been There Mexico 14 oz</t>
         </is>
       </c>
       <c r="E1006" t="inlineStr">
@@ -35818,13 +35906,13 @@
       </c>
       <c r="B1007" s="7" t="inlineStr">
         <is>
-          <t>11813</t>
+          <t>11811</t>
         </is>
       </c>
       <c r="C1007" s="7" t="inlineStr"/>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>Been There Veracruz 14 oz</t>
+          <t>Been There Los Cabos 14 oz</t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
@@ -35849,13 +35937,13 @@
       </c>
       <c r="B1008" s="7" t="inlineStr">
         <is>
-          <t>11814</t>
+          <t>11813</t>
         </is>
       </c>
       <c r="C1008" s="7" t="inlineStr"/>
       <c r="D1008" t="inlineStr">
         <is>
-          <t>Been There Ensenada 14 oz</t>
+          <t>Been There Veracruz 14 oz</t>
         </is>
       </c>
       <c r="E1008" t="inlineStr">
@@ -35880,13 +35968,13 @@
       </c>
       <c r="B1009" s="7" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>11814</t>
         </is>
       </c>
       <c r="C1009" s="7" t="inlineStr"/>
       <c r="D1009" t="inlineStr">
         <is>
-          <t>Been There Acapulco 14 oz</t>
+          <t>Been There Ensenada 14 oz</t>
         </is>
       </c>
       <c r="E1009" t="inlineStr">
@@ -35911,13 +35999,13 @@
       </c>
       <c r="B1010" s="7" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>11827</t>
         </is>
       </c>
       <c r="C1010" s="7" t="inlineStr"/>
       <c r="D1010" t="inlineStr">
         <is>
-          <t>Been There Playa del Carmen 14oz</t>
+          <t>Been There Acapulco 14 oz</t>
         </is>
       </c>
       <c r="E1010" t="inlineStr">
@@ -35942,13 +36030,13 @@
       </c>
       <c r="B1011" s="7" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="C1011" s="7" t="inlineStr"/>
       <c r="D1011" t="inlineStr">
         <is>
-          <t>Been There Cozumen 14 oz</t>
+          <t>Been There Playa del Carmen 14oz</t>
         </is>
       </c>
       <c r="E1011" t="inlineStr">
@@ -35973,13 +36061,13 @@
       </c>
       <c r="B1012" s="7" t="inlineStr">
         <is>
-          <t>11861</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="C1012" s="7" t="inlineStr"/>
       <c r="D1012" t="inlineStr">
         <is>
-          <t>Been There Leon 14 oz</t>
+          <t>Been There Cozumen 14 oz</t>
         </is>
       </c>
       <c r="E1012" t="inlineStr">
@@ -36004,13 +36092,13 @@
       </c>
       <c r="B1013" s="7" t="inlineStr">
         <is>
-          <t>11862</t>
+          <t>11861</t>
         </is>
       </c>
       <c r="C1013" s="7" t="inlineStr"/>
       <c r="D1013" t="inlineStr">
         <is>
-          <t>Been There Queretaro 14 oz</t>
+          <t>Been There Leon 14 oz</t>
         </is>
       </c>
       <c r="E1013" t="inlineStr">
@@ -36035,13 +36123,13 @@
       </c>
       <c r="B1014" s="7" t="inlineStr">
         <is>
-          <t>11863</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="C1014" s="7" t="inlineStr"/>
       <c r="D1014" t="inlineStr">
         <is>
-          <t>Been There San Miguel 14 oz</t>
+          <t>Been There Queretaro 14 oz</t>
         </is>
       </c>
       <c r="E1014" t="inlineStr">
@@ -36066,13 +36154,13 @@
       </c>
       <c r="B1015" s="7" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>11863</t>
         </is>
       </c>
       <c r="C1015" s="7" t="inlineStr"/>
       <c r="D1015" t="inlineStr">
         <is>
-          <t>Been There Puebla 14 oz</t>
+          <t>Been There San Miguel 14 oz</t>
         </is>
       </c>
       <c r="E1015" t="inlineStr">
@@ -36097,13 +36185,13 @@
       </c>
       <c r="B1016" s="7" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="C1016" s="7" t="inlineStr"/>
       <c r="D1016" t="inlineStr">
         <is>
-          <t>Been There Guadalajara 14 oz</t>
+          <t>Been There Puebla 14 oz</t>
         </is>
       </c>
       <c r="E1016" t="inlineStr">
@@ -36128,13 +36216,13 @@
       </c>
       <c r="B1017" s="7" t="inlineStr">
         <is>
-          <t>11968</t>
+          <t>11865</t>
         </is>
       </c>
       <c r="C1017" s="7" t="inlineStr"/>
       <c r="D1017" t="inlineStr">
         <is>
-          <t>Been There Villahermosa 14 oz</t>
+          <t>Been There Guadalajara 14 oz</t>
         </is>
       </c>
       <c r="E1017" t="inlineStr">
@@ -36159,13 +36247,13 @@
       </c>
       <c r="B1018" s="7" t="inlineStr">
         <is>
-          <t>11969</t>
+          <t>11968</t>
         </is>
       </c>
       <c r="C1018" s="7" t="inlineStr"/>
       <c r="D1018" t="inlineStr">
         <is>
-          <t>Been There Morelia 14 oz</t>
+          <t>Been There Villahermosa 14 oz</t>
         </is>
       </c>
       <c r="E1018" t="inlineStr">
@@ -36190,13 +36278,13 @@
       </c>
       <c r="B1019" s="7" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>11969</t>
         </is>
       </c>
       <c r="C1019" s="7" t="inlineStr"/>
       <c r="D1019" t="inlineStr">
         <is>
-          <t>Been There Monterrey 14 oz</t>
+          <t>Been There Morelia 14 oz</t>
         </is>
       </c>
       <c r="E1019" t="inlineStr">
@@ -36221,13 +36309,13 @@
       </c>
       <c r="B1020" s="7" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>11970</t>
         </is>
       </c>
       <c r="C1020" s="7" t="inlineStr"/>
       <c r="D1020" t="inlineStr">
         <is>
-          <t>Been There Chihuahua 14 oz</t>
+          <t>Been There Monterrey 14 oz</t>
         </is>
       </c>
       <c r="E1020" t="inlineStr">
@@ -36252,13 +36340,13 @@
       </c>
       <c r="B1021" s="7" t="inlineStr">
         <is>
-          <t>12090</t>
+          <t>12089</t>
         </is>
       </c>
       <c r="C1021" s="7" t="inlineStr"/>
       <c r="D1021" t="inlineStr">
         <is>
-          <t>Been There Zacatecas 14 oz</t>
+          <t>Been There Chihuahua 14 oz</t>
         </is>
       </c>
       <c r="E1021" t="inlineStr">
@@ -36283,13 +36371,13 @@
       </c>
       <c r="B1022" s="7" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>12090</t>
         </is>
       </c>
       <c r="C1022" s="7" t="inlineStr"/>
       <c r="D1022" t="inlineStr">
         <is>
-          <t>Been There Oaxaca 14 oz</t>
+          <t>Been There Zacatecas 14 oz</t>
         </is>
       </c>
       <c r="E1022" t="inlineStr">
@@ -36314,13 +36402,13 @@
       </c>
       <c r="B1023" s="7" t="inlineStr">
         <is>
-          <t>12095</t>
+          <t>12094</t>
         </is>
       </c>
       <c r="C1023" s="7" t="inlineStr"/>
       <c r="D1023" t="inlineStr">
         <is>
-          <t>Been There Tuxtla Gutierre 14 oz</t>
+          <t>Been There Oaxaca 14 oz</t>
         </is>
       </c>
       <c r="E1023" t="inlineStr">
@@ -36345,17 +36433,13 @@
       </c>
       <c r="B1024" s="7" t="inlineStr">
         <is>
-          <t>12480</t>
-        </is>
-      </c>
-      <c r="C1024" s="7" t="inlineStr">
-        <is>
-          <t>11103799</t>
-        </is>
-      </c>
+          <t>12095</t>
+        </is>
+      </c>
+      <c r="C1024" s="7" t="inlineStr"/>
       <c r="D1024" t="inlineStr">
         <is>
-          <t>12480 Cafetera Green CJ/1 PZA</t>
+          <t>Been There Tuxtla Gutierre 14 oz</t>
         </is>
       </c>
       <c r="E1024" t="inlineStr">
@@ -36380,17 +36464,17 @@
       </c>
       <c r="B1025" s="7" t="inlineStr">
         <is>
-          <t>12642</t>
+          <t>12480</t>
         </is>
       </c>
       <c r="C1025" s="7" t="inlineStr">
         <is>
-          <t>11090466</t>
+          <t>11103799</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
-          <t>CAFETERA BLACK TRITAN BEAKER 8TZ</t>
+          <t>12480 Cafetera Green CJ/1 PZA</t>
         </is>
       </c>
       <c r="E1025" t="inlineStr">
@@ -36415,17 +36499,17 @@
       </c>
       <c r="B1026" s="7" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>12642</t>
         </is>
       </c>
       <c r="C1026" s="7" t="inlineStr">
         <is>
-          <t>11129870</t>
+          <t>11090466</t>
         </is>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
-          <t>COR23 SSCC24 Sir</t>
+          <t>CAFETERA BLACK TRITAN BEAKER 8TZ</t>
         </is>
       </c>
       <c r="E1026" t="inlineStr">
@@ -36450,17 +36534,17 @@
       </c>
       <c r="B1027" s="7" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>14779</t>
         </is>
       </c>
       <c r="C1027" s="7" t="inlineStr">
         <is>
-          <t>11129720</t>
+          <t>11129870</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t>COR23 CC16 TinST</t>
+          <t>COR23 SSCC24 Sir</t>
         </is>
       </c>
       <c r="E1027" t="inlineStr">
@@ -36485,17 +36569,17 @@
       </c>
       <c r="B1028" s="7" t="inlineStr">
         <is>
-          <t>14781</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="C1028" s="7" t="inlineStr">
         <is>
-          <t>11129821</t>
+          <t>11129720</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
-          <t>COR23CC16 irid</t>
+          <t>COR23 CC16 TinST</t>
         </is>
       </c>
       <c r="E1028" t="inlineStr">
@@ -36520,17 +36604,17 @@
       </c>
       <c r="B1029" s="7" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>14781</t>
         </is>
       </c>
       <c r="C1029" s="7" t="inlineStr">
         <is>
-          <t>11129797</t>
+          <t>11129821</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
-          <t>COR23 CC16 Shell</t>
+          <t>COR23CC16 irid</t>
         </is>
       </c>
       <c r="E1029" t="inlineStr">
@@ -36555,17 +36639,17 @@
       </c>
       <c r="B1030" s="7" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="C1030" s="7" t="inlineStr">
         <is>
-          <t>11129846</t>
+          <t>11129797</t>
         </is>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
-          <t>COR23 KeyR TinST</t>
+          <t>COR23 CC16 Shell</t>
         </is>
       </c>
       <c r="E1030" t="inlineStr">
@@ -36590,17 +36674,17 @@
       </c>
       <c r="B1031" s="7" t="inlineStr">
         <is>
-          <t>14919</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="C1031" s="7" t="inlineStr">
         <is>
-          <t>11141068</t>
+          <t>11129846</t>
         </is>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
-          <t>COR23 Tu16 Siren</t>
+          <t>COR23 KeyR TinST</t>
         </is>
       </c>
       <c r="E1031" t="inlineStr">
@@ -36625,13 +36709,17 @@
       </c>
       <c r="B1032" s="7" t="inlineStr">
         <is>
-          <t>15791</t>
-        </is>
-      </c>
-      <c r="C1032" s="7" t="inlineStr"/>
+          <t>14919</t>
+        </is>
+      </c>
+      <c r="C1032" s="7" t="inlineStr">
+        <is>
+          <t>11141068</t>
+        </is>
+      </c>
       <c r="D1032" t="inlineStr">
         <is>
-          <t>Res SS16GoldLeaf</t>
+          <t>COR23 Tu16 Siren</t>
         </is>
       </c>
       <c r="E1032" t="inlineStr">
@@ -36656,13 +36744,13 @@
       </c>
       <c r="B1033" s="7" t="inlineStr">
         <is>
-          <t>15792</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="C1033" s="7" t="inlineStr"/>
       <c r="D1033" t="inlineStr">
         <is>
-          <t>Res SS16TuBlack</t>
+          <t>Res SS16GoldLeaf</t>
         </is>
       </c>
       <c r="E1033" t="inlineStr">
@@ -36687,17 +36775,13 @@
       </c>
       <c r="B1034" s="7" t="inlineStr">
         <is>
-          <t>15996</t>
-        </is>
-      </c>
-      <c r="C1034" s="7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>15792</t>
+        </is>
+      </c>
+      <c r="C1034" s="7" t="inlineStr"/>
       <c r="D1034" t="inlineStr">
         <is>
-          <t>COR25CoffeeBean</t>
+          <t>Res SS16TuBlack</t>
         </is>
       </c>
       <c r="E1034" t="inlineStr">
@@ -36722,17 +36806,17 @@
       </c>
       <c r="B1035" s="7" t="inlineStr">
         <is>
-          <t>16121</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="C1035" s="7" t="inlineStr">
         <is>
-          <t>11164269</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
-          <t>SI25Tu16Charm</t>
+          <t>COR25CoffeeBean</t>
         </is>
       </c>
       <c r="E1035" t="inlineStr">
@@ -36757,17 +36841,17 @@
       </c>
       <c r="B1036" s="7" t="inlineStr">
         <is>
-          <t>16127</t>
+          <t>16121</t>
         </is>
       </c>
       <c r="C1036" s="7" t="inlineStr">
         <is>
-          <t>11164289</t>
+          <t>11164269</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
-          <t>Fl25SSTu16B</t>
+          <t>SI25Tu16Charm</t>
         </is>
       </c>
       <c r="E1036" t="inlineStr">
@@ -36792,17 +36876,17 @@
       </c>
       <c r="B1037" s="7" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="C1037" s="7" t="inlineStr">
         <is>
-          <t>11164299</t>
+          <t>11164289</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
-          <t>SI25SS20Zoo</t>
+          <t>Fl25SSTu16B</t>
         </is>
       </c>
       <c r="E1037" t="inlineStr">
@@ -36827,17 +36911,17 @@
       </c>
       <c r="B1038" s="7" t="inlineStr">
         <is>
-          <t>16148</t>
+          <t>16130</t>
         </is>
       </c>
       <c r="C1038" s="7" t="inlineStr">
         <is>
-          <t>11164315</t>
+          <t>11164299</t>
         </is>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
-          <t>SII25Iceflow30</t>
+          <t>SI25SS20Zoo</t>
         </is>
       </c>
       <c r="E1038" t="inlineStr">
@@ -36862,17 +36946,17 @@
       </c>
       <c r="B1039" s="7" t="inlineStr">
         <is>
-          <t>16153</t>
+          <t>16148</t>
         </is>
       </c>
       <c r="C1039" s="7" t="inlineStr">
         <is>
-          <t>11164278</t>
+          <t>11164315</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
-          <t>SI25BTL24Zoo</t>
+          <t>SII25Iceflow30</t>
         </is>
       </c>
       <c r="E1039" t="inlineStr">
@@ -36897,17 +36981,17 @@
       </c>
       <c r="B1040" s="7" t="inlineStr">
         <is>
-          <t>16158</t>
+          <t>16153</t>
         </is>
       </c>
       <c r="C1040" s="7" t="inlineStr">
         <is>
-          <t>11164260</t>
+          <t>11164278</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
-          <t>Fl25Mug14Bar</t>
+          <t>SI25BTL24Zoo</t>
         </is>
       </c>
       <c r="E1040" t="inlineStr">
@@ -36932,17 +37016,17 @@
       </c>
       <c r="B1041" s="7" t="inlineStr">
         <is>
-          <t>16159</t>
+          <t>16158</t>
         </is>
       </c>
       <c r="C1041" s="7" t="inlineStr">
         <is>
-          <t>11164261</t>
+          <t>11164260</t>
         </is>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
-          <t>SI25Tz14Eleph</t>
+          <t>Fl25Mug14Bar</t>
         </is>
       </c>
       <c r="E1041" t="inlineStr">
@@ -36967,17 +37051,17 @@
       </c>
       <c r="B1042" s="7" t="inlineStr">
         <is>
-          <t>16160</t>
+          <t>16159</t>
         </is>
       </c>
       <c r="C1042" s="7" t="inlineStr">
         <is>
-          <t>11164262</t>
+          <t>11164261</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
-          <t>SI25Mug14Mothers</t>
+          <t>SI25Tz14Eleph</t>
         </is>
       </c>
       <c r="E1042" t="inlineStr">
@@ -37002,17 +37086,17 @@
       </c>
       <c r="B1043" s="7" t="inlineStr">
         <is>
-          <t>16161</t>
+          <t>16160</t>
         </is>
       </c>
       <c r="C1043" s="7" t="inlineStr">
         <is>
-          <t>11164263</t>
+          <t>11164262</t>
         </is>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
-          <t>SI25DW12Mothers</t>
+          <t>SI25Mug14Mothers</t>
         </is>
       </c>
       <c r="E1043" t="inlineStr">
@@ -37037,17 +37121,17 @@
       </c>
       <c r="B1044" s="7" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>16161</t>
         </is>
       </c>
       <c r="C1044" s="7" t="inlineStr">
         <is>
-          <t>11164291</t>
+          <t>11164263</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
-          <t>SII25SS16Pearl</t>
+          <t>SI25DW12Mothers</t>
         </is>
       </c>
       <c r="E1044" t="inlineStr">
@@ -37072,17 +37156,17 @@
       </c>
       <c r="B1045" s="7" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>16166</t>
         </is>
       </c>
       <c r="C1045" s="7" t="inlineStr">
         <is>
-          <t>11164296</t>
+          <t>11164291</t>
         </is>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
-          <t>Fl25Tu20Silicon</t>
+          <t>SII25SS16Pearl</t>
         </is>
       </c>
       <c r="E1045" t="inlineStr">
@@ -37107,17 +37191,17 @@
       </c>
       <c r="B1046" s="7" t="inlineStr">
         <is>
-          <t>16169</t>
+          <t>16167</t>
         </is>
       </c>
       <c r="C1046" s="7" t="inlineStr">
         <is>
-          <t>11164301</t>
+          <t>11164296</t>
         </is>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
-          <t>SI25SSBTLZoo</t>
+          <t>Fl25Tu20Silicon</t>
         </is>
       </c>
       <c r="E1046" t="inlineStr">
@@ -37142,17 +37226,17 @@
       </c>
       <c r="B1047" s="7" t="inlineStr">
         <is>
-          <t>16173</t>
+          <t>16169</t>
         </is>
       </c>
       <c r="C1047" s="7" t="inlineStr">
         <is>
-          <t>11164308</t>
+          <t>11164301</t>
         </is>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
-          <t>SII25StanOrange</t>
+          <t>SI25SSBTLZoo</t>
         </is>
       </c>
       <c r="E1047" t="inlineStr">
@@ -37177,17 +37261,17 @@
       </c>
       <c r="B1048" s="7" t="inlineStr">
         <is>
-          <t>16177</t>
+          <t>16173</t>
         </is>
       </c>
       <c r="C1048" s="7" t="inlineStr">
         <is>
-          <t>11164318</t>
+          <t>11164308</t>
         </is>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
-          <t>SII25KeyChain</t>
+          <t>SII25StanOrange</t>
         </is>
       </c>
       <c r="E1048" t="inlineStr">
@@ -37212,17 +37296,17 @@
       </c>
       <c r="B1049" s="7" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>16177</t>
         </is>
       </c>
       <c r="C1049" s="7" t="inlineStr">
         <is>
-          <t>11167151</t>
+          <t>11164318</t>
         </is>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
-          <t>SII25CC24FRLenco</t>
+          <t>SII25KeyChain</t>
         </is>
       </c>
       <c r="E1049" t="inlineStr">
@@ -37247,17 +37331,17 @@
       </c>
       <c r="B1050" s="7" t="inlineStr">
         <is>
-          <t>16183</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="C1050" s="7" t="inlineStr">
         <is>
-          <t>11167153</t>
+          <t>11167151</t>
         </is>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
-          <t>SII25BTL20FarmR</t>
+          <t>SII25CC24FRLenco</t>
         </is>
       </c>
       <c r="E1050" t="inlineStr">
@@ -37282,17 +37366,17 @@
       </c>
       <c r="B1051" s="7" t="inlineStr">
         <is>
-          <t>16184</t>
+          <t>16183</t>
         </is>
       </c>
       <c r="C1051" s="7" t="inlineStr">
         <is>
-          <t>11167154</t>
+          <t>11167153</t>
         </is>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
-          <t>SII25Mug14FarmR</t>
+          <t>SII25BTL20FarmR</t>
         </is>
       </c>
       <c r="E1051" t="inlineStr">
@@ -37317,17 +37401,17 @@
       </c>
       <c r="B1052" s="7" t="inlineStr">
         <is>
-          <t>16225</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="C1052" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11167154</t>
         </is>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
-          <t>Fl25ReusDDM</t>
+          <t>SII25Mug14FarmR</t>
         </is>
       </c>
       <c r="E1052" t="inlineStr">
@@ -37352,17 +37436,17 @@
       </c>
       <c r="B1053" s="7" t="inlineStr">
         <is>
-          <t>16259</t>
+          <t>16225</t>
         </is>
       </c>
       <c r="C1053" s="7" t="inlineStr">
         <is>
-          <t>11171525</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
-          <t>SII25CCDomeBday</t>
+          <t>Fl25ReusDDM</t>
         </is>
       </c>
       <c r="E1053" t="inlineStr">
@@ -37387,17 +37471,17 @@
       </c>
       <c r="B1054" s="7" t="inlineStr">
         <is>
-          <t>16260</t>
+          <t>16259</t>
         </is>
       </c>
       <c r="C1054" s="7" t="inlineStr">
         <is>
-          <t>11171526</t>
+          <t>11171525</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
-          <t>SII25CCLlavero</t>
+          <t>SII25CCDomeBday</t>
         </is>
       </c>
       <c r="E1054" t="inlineStr">
@@ -37422,17 +37506,17 @@
       </c>
       <c r="B1055" s="7" t="inlineStr">
         <is>
-          <t>16289</t>
+          <t>16260</t>
         </is>
       </c>
       <c r="C1055" s="7" t="inlineStr">
         <is>
-          <t>11169485</t>
+          <t>11171526</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
-          <t>Fl25PPFood</t>
+          <t>SII25CCLlavero</t>
         </is>
       </c>
       <c r="E1055" t="inlineStr">
@@ -37457,17 +37541,17 @@
       </c>
       <c r="B1056" s="7" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16289</t>
         </is>
       </c>
       <c r="C1056" s="7" t="inlineStr">
         <is>
-          <t>11169422</t>
+          <t>11169485</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
-          <t>Fl25Mug14Bear</t>
+          <t>Fl25PPFood</t>
         </is>
       </c>
       <c r="E1056" t="inlineStr">
@@ -37492,17 +37576,17 @@
       </c>
       <c r="B1057" s="7" t="inlineStr">
         <is>
-          <t>16316</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="C1057" s="7" t="inlineStr">
         <is>
-          <t>11169425</t>
+          <t>11169422</t>
         </is>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
-          <t>Fl25Mug14Calav</t>
+          <t>Fl25Mug14Bear</t>
         </is>
       </c>
       <c r="E1057" t="inlineStr">
@@ -37527,17 +37611,17 @@
       </c>
       <c r="B1058" s="7" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>16316</t>
         </is>
       </c>
       <c r="C1058" s="7" t="inlineStr">
         <is>
-          <t>11169480</t>
+          <t>11169425</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
-          <t>Fl25StanIceF</t>
+          <t>Fl25Mug14Calav</t>
         </is>
       </c>
       <c r="E1058" t="inlineStr">
@@ -37562,17 +37646,17 @@
       </c>
       <c r="B1059" s="7" t="inlineStr">
         <is>
-          <t>16325</t>
+          <t>16324</t>
         </is>
       </c>
       <c r="C1059" s="7" t="inlineStr">
         <is>
-          <t>11169484</t>
+          <t>11169480</t>
         </is>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
-          <t>Fl25CookieJar</t>
+          <t>Fl25StanIceF</t>
         </is>
       </c>
       <c r="E1059" t="inlineStr">
@@ -37597,17 +37681,17 @@
       </c>
       <c r="B1060" s="7" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>16325</t>
         </is>
       </c>
       <c r="C1060" s="7" t="inlineStr">
         <is>
-          <t>Dinámica especial</t>
+          <t>11169484</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
-          <t>SII25ReusPSL</t>
+          <t>Fl25CookieJar</t>
         </is>
       </c>
       <c r="E1060" t="inlineStr">
@@ -37632,17 +37716,17 @@
       </c>
       <c r="B1061" s="7" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>16415</t>
         </is>
       </c>
       <c r="C1061" s="7" t="inlineStr">
         <is>
-          <t>11173272</t>
+          <t>Dinámica especial</t>
         </is>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
-          <t>Xm25Tu12Lux</t>
+          <t>SII25ReusPSL</t>
         </is>
       </c>
       <c r="E1061" t="inlineStr">
@@ -37667,17 +37751,17 @@
       </c>
       <c r="B1062" s="7" t="inlineStr">
         <is>
-          <t>16460</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="C1062" s="7" t="inlineStr">
         <is>
-          <t>11172987</t>
+          <t>11173272</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
-          <t>Xm25SS16Knit</t>
+          <t>Xm25Tu12Lux</t>
         </is>
       </c>
       <c r="E1062" t="inlineStr">
@@ -37702,17 +37786,17 @@
       </c>
       <c r="B1063" s="7" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>16460</t>
         </is>
       </c>
       <c r="C1063" s="7" t="inlineStr">
         <is>
-          <t>11173043</t>
+          <t>11172987</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
-          <t>Xm25GlassBear</t>
+          <t>Xm25SS16Knit</t>
         </is>
       </c>
       <c r="E1063" t="inlineStr">
@@ -37737,13 +37821,17 @@
       </c>
       <c r="B1064" s="7" t="inlineStr">
         <is>
-          <t>16501</t>
-        </is>
-      </c>
-      <c r="C1064" s="7" t="inlineStr"/>
+          <t>16477</t>
+        </is>
+      </c>
+      <c r="C1064" s="7" t="inlineStr">
+        <is>
+          <t>11173043</t>
+        </is>
+      </c>
       <c r="D1064" t="inlineStr">
         <is>
-          <t>Xm25LlaveroBB</t>
+          <t>Xm25GlassBear</t>
         </is>
       </c>
       <c r="E1064" t="inlineStr">
@@ -37768,17 +37856,13 @@
       </c>
       <c r="B1065" s="7" t="inlineStr">
         <is>
-          <t>16542</t>
-        </is>
-      </c>
-      <c r="C1065" s="7" t="inlineStr">
-        <is>
-          <t>11174790</t>
-        </is>
-      </c>
+          <t>16501</t>
+        </is>
+      </c>
+      <c r="C1065" s="7" t="inlineStr"/>
       <c r="D1065" t="inlineStr">
         <is>
-          <t>Wt26Tu16Green</t>
+          <t>Xm25LlaveroBB</t>
         </is>
       </c>
       <c r="E1065" t="inlineStr">
@@ -37803,17 +37887,17 @@
       </c>
       <c r="B1066" s="7" t="inlineStr">
         <is>
-          <t>16668</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="C1066" s="7" t="inlineStr">
         <is>
-          <t>11176716</t>
+          <t>11174790</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
-          <t>Sp26StanYellow20</t>
+          <t>Wt26Tu16Green</t>
         </is>
       </c>
       <c r="E1066" t="inlineStr">
@@ -37838,13 +37922,17 @@
       </c>
       <c r="B1067" s="7" t="inlineStr">
         <is>
-          <t>16977</t>
-        </is>
-      </c>
-      <c r="C1067" s="7" t="inlineStr"/>
+          <t>16668</t>
+        </is>
+      </c>
+      <c r="C1067" s="7" t="inlineStr">
+        <is>
+          <t>11176716</t>
+        </is>
+      </c>
       <c r="D1067" t="inlineStr">
         <is>
-          <t>IMÁN MÉXICO</t>
+          <t>Sp26StanYellow20</t>
         </is>
       </c>
       <c r="E1067" t="inlineStr">
@@ -38226,13 +38314,13 @@
       </c>
       <c r="B1079" s="7" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>16977</t>
         </is>
       </c>
       <c r="C1079" s="7" t="inlineStr"/>
       <c r="D1079" t="inlineStr">
         <is>
-          <t>SII26GlCCColor</t>
+          <t>IMÁN MÉXICO</t>
         </is>
       </c>
       <c r="E1079" t="inlineStr">
@@ -38247,7 +38335,7 @@
       </c>
       <c r="G1079" t="inlineStr">
         <is>
-          <t>lote-01/017357.jpeg</t>
+          <t>lote-01/16977.jpeg</t>
         </is>
       </c>
       <c r="H1079" t="inlineStr">
@@ -38269,7 +38357,7 @@
       </c>
       <c r="B1080" s="7" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="C1080" s="7" t="inlineStr"/>
@@ -38290,7 +38378,7 @@
       </c>
       <c r="G1080" t="inlineStr">
         <is>
-          <t>lote-01/017358.jpeg</t>
+          <t>lote-01/017357.jpeg</t>
         </is>
       </c>
       <c r="H1080" t="inlineStr">
@@ -38312,7 +38400,7 @@
       </c>
       <c r="B1081" s="7" t="inlineStr">
         <is>
-          <t>17359</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="C1081" s="7" t="inlineStr"/>
@@ -38333,27 +38421,70 @@
       </c>
       <c r="G1081" t="inlineStr">
         <is>
+          <t>lote-01/017358.jpeg</t>
+        </is>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082" ht="24" customHeight="1">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>CON FOTO</t>
+        </is>
+      </c>
+      <c r="B1082" s="7" t="inlineStr">
+        <is>
+          <t>17359</t>
+        </is>
+      </c>
+      <c r="C1082" s="7" t="inlineStr"/>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>SII26GlCCColor</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>SECUNDARIO</t>
+        </is>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
           <t>lote-01/017359.jpeg</t>
         </is>
       </c>
-      <c r="H1081" t="inlineStr">
+      <c r="H1082" t="inlineStr">
         <is>
           <t>lote-01</t>
         </is>
       </c>
-      <c r="I1081" t="inlineStr">
+      <c r="I1082" t="inlineStr">
         <is>
           <t>codigoDia</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:I1081"/>
+  <autoFilter ref="A7:I1082"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A6:I6"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:A1081">
+  <conditionalFormatting sqref="A8:A1082">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>A8="CON FOTO"</formula>
     </cfRule>

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -20735,7 +20735,7 @@
       </c>
       <c r="B582" s="7" t="inlineStr">
         <is>
-          <t>16078</t>
+          <t>16079</t>
         </is>
       </c>
       <c r="C582" s="7" t="inlineStr">
@@ -20745,7 +20745,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
+          <t>Stoppers SBX Genérico</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
@@ -20770,17 +20770,17 @@
       </c>
       <c r="B583" s="7" t="inlineStr">
         <is>
-          <t>16079</t>
+          <t>16089</t>
         </is>
       </c>
       <c r="C583" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11163285</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>Stoppers SBX Genérico</t>
+          <t>CCup Acero SBX Genérico</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
@@ -20805,17 +20805,17 @@
       </c>
       <c r="B584" s="7" t="inlineStr">
         <is>
-          <t>16089</t>
+          <t>16090</t>
         </is>
       </c>
       <c r="C584" s="7" t="inlineStr">
         <is>
-          <t>11163285</t>
+          <t>11163286</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>CCup Acero SBX Genérico</t>
+          <t>CCupPlastic SBX Genérico</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -20840,17 +20840,17 @@
       </c>
       <c r="B585" s="7" t="inlineStr">
         <is>
-          <t>16090</t>
+          <t>16091</t>
         </is>
       </c>
       <c r="C585" s="7" t="inlineStr">
         <is>
-          <t>11163286</t>
+          <t>11163287</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>CCupPlastic SBX Genérico</t>
+          <t>CCup Acero SBX Genérico</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -20875,12 +20875,12 @@
       </c>
       <c r="B586" s="7" t="inlineStr">
         <is>
-          <t>16091</t>
+          <t>16092</t>
         </is>
       </c>
       <c r="C586" s="7" t="inlineStr">
         <is>
-          <t>11163287</t>
+          <t>11163288</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -20910,17 +20910,17 @@
       </c>
       <c r="B587" s="7" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>16093</t>
         </is>
       </c>
       <c r="C587" s="7" t="inlineStr">
         <is>
-          <t>11163288</t>
+          <t>11163289</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>CCup Acero SBX Genérico</t>
+          <t>Tumb acero SBX Genérico</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -20945,17 +20945,17 @@
       </c>
       <c r="B588" s="7" t="inlineStr">
         <is>
-          <t>16093</t>
+          <t>16094</t>
         </is>
       </c>
       <c r="C588" s="7" t="inlineStr">
         <is>
-          <t>11163289</t>
+          <t>11163290</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>Tumb acero SBX Genérico</t>
+          <t>Tazas SBX Genérico</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -20980,17 +20980,17 @@
       </c>
       <c r="B589" s="7" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="C589" s="7" t="inlineStr">
         <is>
-          <t>11163290</t>
+          <t>11163293</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>Tazas SBX Genérico</t>
+          <t>Pines SBX Genérico</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
@@ -21015,12 +21015,12 @@
       </c>
       <c r="B590" s="7" t="inlineStr">
         <is>
-          <t>16097</t>
+          <t>16098</t>
         </is>
       </c>
       <c r="C590" s="7" t="inlineStr">
         <is>
-          <t>11163293</t>
+          <t>11163294</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -21050,12 +21050,12 @@
       </c>
       <c r="B591" s="7" t="inlineStr">
         <is>
-          <t>16098</t>
+          <t>16099</t>
         </is>
       </c>
       <c r="C591" s="7" t="inlineStr">
         <is>
-          <t>11163294</t>
+          <t>11163295</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -21085,17 +21085,17 @@
       </c>
       <c r="B592" s="7" t="inlineStr">
         <is>
-          <t>16099</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="C592" s="7" t="inlineStr">
         <is>
-          <t>11163295</t>
+          <t>11160762</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>Pines SBX Genérico</t>
+          <t>CCup Acero SBX Genérico</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
@@ -21120,12 +21120,12 @@
       </c>
       <c r="B593" s="7" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="C593" s="7" t="inlineStr">
         <is>
-          <t>11160762</t>
+          <t>11160763</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -21155,17 +21155,17 @@
       </c>
       <c r="B594" s="7" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="C594" s="7" t="inlineStr">
         <is>
-          <t>11160763</t>
+          <t>11160764</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>CCup Acero SBX Genérico</t>
+          <t>CCupPlastic SBX Genérico</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -21190,17 +21190,17 @@
       </c>
       <c r="B595" s="7" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="C595" s="7" t="inlineStr">
         <is>
-          <t>11160764</t>
+          <t>11160765</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>CCupPlastic SBX Genérico</t>
+          <t>Tazas SBX Genérico</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
@@ -21225,17 +21225,17 @@
       </c>
       <c r="B596" s="7" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="C596" s="7" t="inlineStr">
         <is>
-          <t>11160765</t>
+          <t>11160766</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>Tazas SBX Genérico</t>
+          <t>Stanley SBX Genérico</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
@@ -21260,17 +21260,17 @@
       </c>
       <c r="B597" s="7" t="inlineStr">
         <is>
-          <t>16105</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="C597" s="7" t="inlineStr">
         <is>
-          <t>11160766</t>
+          <t>11160767</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>Stanley SBX Genérico</t>
+          <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
@@ -21295,17 +21295,17 @@
       </c>
       <c r="B598" s="7" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="C598" s="7" t="inlineStr">
         <is>
-          <t>11160767</t>
+          <t>11160768</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
+          <t>Tote bags SBX Genérico</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
@@ -21330,17 +21330,17 @@
       </c>
       <c r="B599" s="7" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="C599" s="7" t="inlineStr">
         <is>
-          <t>11160768</t>
+          <t>11160769</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Tote bags SBX Genérico</t>
+          <t>Llavero SBX Genérico</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
@@ -21360,22 +21360,22 @@
     <row r="600" ht="24" customHeight="1">
       <c r="A600" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B600" s="7" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>15857</t>
         </is>
       </c>
       <c r="C600" s="7" t="inlineStr">
         <is>
-          <t>11160769</t>
+          <t>11157547</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
+          <t>CCup Acero SBX Genérico</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
@@ -21388,9 +21388,21 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G600" t="inlineStr"/>
-      <c r="H600" t="inlineStr"/>
-      <c r="I600" t="inlineStr"/>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>lote-01/15857.jpeg</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="601" ht="24" customHeight="1">
       <c r="A601" t="inlineStr">
@@ -21400,17 +21412,17 @@
       </c>
       <c r="B601" s="7" t="inlineStr">
         <is>
-          <t>15857</t>
+          <t>16078</t>
         </is>
       </c>
       <c r="C601" s="7" t="inlineStr">
         <is>
-          <t>11157547</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>CCup Acero SBX Genérico</t>
+          <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
@@ -21425,7 +21437,7 @@
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>lote-01/15857.jpeg</t>
+          <t>lote-01/16078.jpeg</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -24145,17 +24157,17 @@
       </c>
       <c r="B680" s="7" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>14886</t>
         </is>
       </c>
       <c r="C680" s="7" t="inlineStr">
         <is>
-          <t>11141050</t>
+          <t>11141051</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>COR23 Tz14 Rain</t>
+          <t>COR23 Tz14Green</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
@@ -24180,17 +24192,17 @@
       </c>
       <c r="B681" s="7" t="inlineStr">
         <is>
-          <t>14886</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="C681" s="7" t="inlineStr">
         <is>
-          <t>11141051</t>
+          <t>11141100</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>COR23 Tz14Green</t>
+          <t>COR23 GlCC18 Omb</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
@@ -24215,17 +24227,17 @@
       </c>
       <c r="B682" s="7" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14917</t>
         </is>
       </c>
       <c r="C682" s="7" t="inlineStr">
         <is>
-          <t>11141100</t>
+          <t>11141045</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>COR23 GlCC18 Omb</t>
+          <t>COR23 DW12 Green</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
@@ -24250,17 +24262,17 @@
       </c>
       <c r="B683" s="7" t="inlineStr">
         <is>
-          <t>14917</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="C683" s="7" t="inlineStr">
         <is>
-          <t>11141045</t>
+          <t>11141076</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>COR23 DW12 Green</t>
+          <t>COR23 Tu20STBlck</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
@@ -24285,17 +24297,17 @@
       </c>
       <c r="B684" s="7" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>14920</t>
         </is>
       </c>
       <c r="C684" s="7" t="inlineStr">
         <is>
-          <t>11141076</t>
+          <t>11141112</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>COR23 Tu20STBlck</t>
+          <t>COR23 SS16ToneB</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
@@ -24320,17 +24332,17 @@
       </c>
       <c r="B685" s="7" t="inlineStr">
         <is>
-          <t>14920</t>
+          <t>14921</t>
         </is>
       </c>
       <c r="C685" s="7" t="inlineStr">
         <is>
-          <t>11141112</t>
+          <t>11141115</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>COR23 SS16ToneB</t>
+          <t>COR23 SS16 ThruL</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -24355,17 +24367,17 @@
       </c>
       <c r="B686" s="7" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>14922</t>
         </is>
       </c>
       <c r="C686" s="7" t="inlineStr">
         <is>
-          <t>11141115</t>
+          <t>11141117</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>COR23 SS16 ThruL</t>
+          <t>COR23 SS20Copper</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
@@ -24390,17 +24402,17 @@
       </c>
       <c r="B687" s="7" t="inlineStr">
         <is>
-          <t>14922</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="C687" s="7" t="inlineStr">
         <is>
-          <t>11141117</t>
+          <t>11141127</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>COR23 SS20Copper</t>
+          <t>COR23 SS20StQuen</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
@@ -24425,17 +24437,17 @@
       </c>
       <c r="B688" s="7" t="inlineStr">
         <is>
-          <t>14923</t>
+          <t>14924</t>
         </is>
       </c>
       <c r="C688" s="7" t="inlineStr">
         <is>
-          <t>11141127</t>
+          <t>11141113</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>COR23 SS20StQuen</t>
+          <t>COR23 SS16StSwi</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
@@ -24460,17 +24472,17 @@
       </c>
       <c r="B689" s="7" t="inlineStr">
         <is>
-          <t>14924</t>
+          <t>14925</t>
         </is>
       </c>
       <c r="C689" s="7" t="inlineStr">
         <is>
-          <t>11141113</t>
+          <t>11141134</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>COR23 SS16StSwi</t>
+          <t>COR23 SS25StyBTL</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
@@ -24495,17 +24507,17 @@
       </c>
       <c r="B690" s="7" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>14926</t>
         </is>
       </c>
       <c r="C690" s="7" t="inlineStr">
         <is>
-          <t>11141134</t>
+          <t>11141189</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>COR23 SS25StyBTL</t>
+          <t>COR23 ToteBag</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
@@ -24530,17 +24542,17 @@
       </c>
       <c r="B691" s="7" t="inlineStr">
         <is>
-          <t>14926</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="C691" s="7" t="inlineStr">
         <is>
-          <t>11141189</t>
+          <t>11141040</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>COR23 ToteBag</t>
+          <t>COR23 PrensaFran</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
@@ -24565,17 +24577,17 @@
       </c>
       <c r="B692" s="7" t="inlineStr">
         <is>
-          <t>14927</t>
+          <t>15191</t>
         </is>
       </c>
       <c r="C692" s="7" t="inlineStr">
         <is>
-          <t>11141041</t>
+          <t>11144107</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>COR23 Pour Over</t>
+          <t>COR23 CC24 Green</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
@@ -24600,17 +24612,17 @@
       </c>
       <c r="B693" s="7" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>15192</t>
         </is>
       </c>
       <c r="C693" s="7" t="inlineStr">
         <is>
-          <t>11141095</t>
+          <t>11144117</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>COR23 Cold Brew</t>
+          <t>COR23 Mug20 Stan</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
@@ -24635,17 +24647,13 @@
       </c>
       <c r="B694" s="7" t="inlineStr">
         <is>
-          <t>14929</t>
-        </is>
-      </c>
-      <c r="C694" s="7" t="inlineStr">
-        <is>
-          <t>11141040</t>
-        </is>
-      </c>
+          <t>15743</t>
+        </is>
+      </c>
+      <c r="C694" s="7" t="inlineStr"/>
       <c r="D694" t="inlineStr">
         <is>
-          <t>COR23 PrensaFran</t>
+          <t>ResSetCT3Pck</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
@@ -24670,17 +24678,13 @@
       </c>
       <c r="B695" s="7" t="inlineStr">
         <is>
-          <t>15191</t>
-        </is>
-      </c>
-      <c r="C695" s="7" t="inlineStr">
-        <is>
-          <t>11144107</t>
-        </is>
-      </c>
+          <t>15746</t>
+        </is>
+      </c>
+      <c r="C695" s="7" t="inlineStr"/>
       <c r="D695" t="inlineStr">
         <is>
-          <t>COR23 CC24 Green</t>
+          <t>ResMug12SSCopper</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
@@ -24705,17 +24709,13 @@
       </c>
       <c r="B696" s="7" t="inlineStr">
         <is>
-          <t>15192</t>
-        </is>
-      </c>
-      <c r="C696" s="7" t="inlineStr">
-        <is>
-          <t>11144117</t>
-        </is>
-      </c>
+          <t>15793</t>
+        </is>
+      </c>
+      <c r="C696" s="7" t="inlineStr"/>
       <c r="D696" t="inlineStr">
         <is>
-          <t>COR23 Mug20 Stan</t>
+          <t>Res SS16GoldShin</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
@@ -24740,13 +24740,13 @@
       </c>
       <c r="B697" s="7" t="inlineStr">
         <is>
-          <t>15743</t>
+          <t>15794</t>
         </is>
       </c>
       <c r="C697" s="7" t="inlineStr"/>
       <c r="D697" t="inlineStr">
         <is>
-          <t>ResSetCT3Pck</t>
+          <t>ResSS16BananaLea</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
@@ -24771,13 +24771,13 @@
       </c>
       <c r="B698" s="7" t="inlineStr">
         <is>
-          <t>15746</t>
+          <t>15886</t>
         </is>
       </c>
       <c r="C698" s="7" t="inlineStr"/>
       <c r="D698" t="inlineStr">
         <is>
-          <t>ResMug12SSCopper</t>
+          <t>BTTu16Mex</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
@@ -24802,13 +24802,17 @@
       </c>
       <c r="B699" s="7" t="inlineStr">
         <is>
-          <t>15793</t>
-        </is>
-      </c>
-      <c r="C699" s="7" t="inlineStr"/>
+          <t>15967</t>
+        </is>
+      </c>
+      <c r="C699" s="7" t="inlineStr">
+        <is>
+          <t>11161004</t>
+        </is>
+      </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Res SS16GoldShin</t>
+          <t>Wt25CrarryingBag</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
@@ -24833,13 +24837,17 @@
       </c>
       <c r="B700" s="7" t="inlineStr">
         <is>
-          <t>15794</t>
-        </is>
-      </c>
-      <c r="C700" s="7" t="inlineStr"/>
+          <t>16052</t>
+        </is>
+      </c>
+      <c r="C700" s="7" t="inlineStr">
+        <is>
+          <t>11162618</t>
+        </is>
+      </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>ResSS16BananaLea</t>
+          <t>SI25ReusTierra</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
@@ -24864,13 +24872,17 @@
       </c>
       <c r="B701" s="7" t="inlineStr">
         <is>
-          <t>15886</t>
-        </is>
-      </c>
-      <c r="C701" s="7" t="inlineStr"/>
+          <t>16053</t>
+        </is>
+      </c>
+      <c r="C701" s="7" t="inlineStr">
+        <is>
+          <t>11162640</t>
+        </is>
+      </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>BTTu16Mex</t>
+          <t>SI25CCReusTierra</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
@@ -24895,17 +24907,17 @@
       </c>
       <c r="B702" s="7" t="inlineStr">
         <is>
-          <t>15967</t>
+          <t>16080</t>
         </is>
       </c>
       <c r="C702" s="7" t="inlineStr">
         <is>
-          <t>11161004</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>Wt25CrarryingBag</t>
+          <t>SII25BdayStopper</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
@@ -24930,17 +24942,17 @@
       </c>
       <c r="B703" s="7" t="inlineStr">
         <is>
-          <t>16052</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="C703" s="7" t="inlineStr">
         <is>
-          <t>11162618</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>SI25ReusTierra</t>
+          <t>SII25ClipBoyB</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
@@ -24965,17 +24977,17 @@
       </c>
       <c r="B704" s="7" t="inlineStr">
         <is>
-          <t>16053</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="C704" s="7" t="inlineStr">
         <is>
-          <t>11162640</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>SI25CCReusTierra</t>
+          <t>SII25ClipGirlB</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
@@ -25000,17 +25012,17 @@
       </c>
       <c r="B705" s="7" t="inlineStr">
         <is>
-          <t>16080</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="C705" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11160779</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>SII25BdayStopper</t>
+          <t>Sp25StopperP</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
@@ -25035,17 +25047,17 @@
       </c>
       <c r="B706" s="7" t="inlineStr">
         <is>
-          <t>16081</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="C706" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11164267</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>SII25ClipBoyB</t>
+          <t>SI25Tu20Swimm</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
@@ -25070,17 +25082,17 @@
       </c>
       <c r="B707" s="7" t="inlineStr">
         <is>
-          <t>16082</t>
+          <t>16122</t>
         </is>
       </c>
       <c r="C707" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11164270</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>SII25ClipGirlB</t>
+          <t>SI25Tu20Zoo</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
@@ -25105,17 +25117,17 @@
       </c>
       <c r="B708" s="7" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>16123</t>
         </is>
       </c>
       <c r="C708" s="7" t="inlineStr">
         <is>
-          <t>11160779</t>
+          <t>11164277</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>Sp25StopperP</t>
+          <t>SI25CC24Dome</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
@@ -25140,17 +25152,17 @@
       </c>
       <c r="B709" s="7" t="inlineStr">
         <is>
-          <t>16120</t>
+          <t>16124</t>
         </is>
       </c>
       <c r="C709" s="7" t="inlineStr">
         <is>
-          <t>11164267</t>
+          <t>11164280</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>SI25Tu20Swimm</t>
+          <t>SI25Reus24Teach</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
@@ -25175,17 +25187,17 @@
       </c>
       <c r="B710" s="7" t="inlineStr">
         <is>
-          <t>16122</t>
+          <t>16125</t>
         </is>
       </c>
       <c r="C710" s="7" t="inlineStr">
         <is>
-          <t>11164270</t>
+          <t>11164285</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>SI25Tu20Zoo</t>
+          <t>SI25CC24Colors</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
@@ -25210,17 +25222,17 @@
       </c>
       <c r="B711" s="7" t="inlineStr">
         <is>
-          <t>16123</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="C711" s="7" t="inlineStr">
         <is>
-          <t>11164277</t>
+          <t>11164288</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>SI25CC24Dome</t>
+          <t>SII25Tu16Blue</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
@@ -25245,17 +25257,17 @@
       </c>
       <c r="B712" s="7" t="inlineStr">
         <is>
-          <t>16124</t>
+          <t>16128</t>
         </is>
       </c>
       <c r="C712" s="7" t="inlineStr">
         <is>
-          <t>11164280</t>
+          <t>11164292</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>SI25Reus24Teach</t>
+          <t>SI25SSDoodle</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
@@ -25280,17 +25292,17 @@
       </c>
       <c r="B713" s="7" t="inlineStr">
         <is>
-          <t>16125</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="C713" s="7" t="inlineStr">
         <is>
-          <t>11164285</t>
+          <t>11164293</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>SI25CC24Colors</t>
+          <t>SI25Tz14Glass</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
@@ -25315,17 +25327,17 @@
       </c>
       <c r="B714" s="7" t="inlineStr">
         <is>
-          <t>16126</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="C714" s="7" t="inlineStr">
         <is>
-          <t>11164288</t>
+          <t>11164305</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>SII25Tu16Blue</t>
+          <t>SII25SSCC24Green</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
@@ -25350,17 +25362,17 @@
       </c>
       <c r="B715" s="7" t="inlineStr">
         <is>
-          <t>16128</t>
+          <t>16149</t>
         </is>
       </c>
       <c r="C715" s="7" t="inlineStr">
         <is>
-          <t>11164292</t>
+          <t>11164265</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>SI25SSDoodle</t>
+          <t>SI25Tu16Bubble</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
@@ -25385,17 +25397,17 @@
       </c>
       <c r="B716" s="7" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>16150</t>
         </is>
       </c>
       <c r="C716" s="7" t="inlineStr">
         <is>
-          <t>11164293</t>
+          <t>11164271</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>SI25Tz14Glass</t>
+          <t>SI25SSCC24Paddle</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
@@ -25420,17 +25432,17 @@
       </c>
       <c r="B717" s="7" t="inlineStr">
         <is>
-          <t>16131</t>
+          <t>16151</t>
         </is>
       </c>
       <c r="C717" s="7" t="inlineStr">
         <is>
-          <t>11164305</t>
+          <t>11164272</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>SII25SSCC24Green</t>
+          <t>SI25CC24Fun</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
@@ -25455,17 +25467,17 @@
       </c>
       <c r="B718" s="7" t="inlineStr">
         <is>
-          <t>16149</t>
+          <t>16152</t>
         </is>
       </c>
       <c r="C718" s="7" t="inlineStr">
         <is>
-          <t>11164265</t>
+          <t>11164316</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>SI25Tu16Bubble</t>
+          <t>SI25KeyChainCC</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
@@ -25490,17 +25502,17 @@
       </c>
       <c r="B719" s="7" t="inlineStr">
         <is>
-          <t>16150</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="C719" s="7" t="inlineStr">
         <is>
-          <t>11164271</t>
+          <t>11164283</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>SI25SSCC24Paddle</t>
+          <t>SI25CC24Drinks</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
@@ -25525,17 +25537,17 @@
       </c>
       <c r="B720" s="7" t="inlineStr">
         <is>
-          <t>16151</t>
+          <t>16155</t>
         </is>
       </c>
       <c r="C720" s="7" t="inlineStr">
         <is>
-          <t>11164272</t>
+          <t>11164275</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>SI25CC24Fun</t>
+          <t>SI25CC24Bling</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
@@ -25560,17 +25572,17 @@
       </c>
       <c r="B721" s="7" t="inlineStr">
         <is>
-          <t>16152</t>
+          <t>16156</t>
         </is>
       </c>
       <c r="C721" s="7" t="inlineStr">
         <is>
-          <t>11164316</t>
+          <t>11164258</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>SI25KeyChainCC</t>
+          <t>SI25DW12Beach</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
@@ -25595,17 +25607,17 @@
       </c>
       <c r="B722" s="7" t="inlineStr">
         <is>
-          <t>16154</t>
+          <t>16157</t>
         </is>
       </c>
       <c r="C722" s="7" t="inlineStr">
         <is>
-          <t>11164283</t>
+          <t>11164259</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>SI25CC24Drinks</t>
+          <t>SII25DW12Studded</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
@@ -25630,17 +25642,17 @@
       </c>
       <c r="B723" s="7" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>16162</t>
         </is>
       </c>
       <c r="C723" s="7" t="inlineStr">
         <is>
-          <t>11164275</t>
+          <t>11164264</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>SI25CC24Bling</t>
+          <t>SI25Mug12Teach</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
@@ -25665,17 +25677,17 @@
       </c>
       <c r="B724" s="7" t="inlineStr">
         <is>
-          <t>16156</t>
+          <t>16163</t>
         </is>
       </c>
       <c r="C724" s="7" t="inlineStr">
         <is>
-          <t>11164258</t>
+          <t>11164268</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>SI25DW12Beach</t>
+          <t>SII25Tu20Soft</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
@@ -25700,17 +25712,17 @@
       </c>
       <c r="B725" s="7" t="inlineStr">
         <is>
-          <t>16157</t>
+          <t>16164</t>
         </is>
       </c>
       <c r="C725" s="7" t="inlineStr">
         <is>
-          <t>11164259</t>
+          <t>11164273</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>SII25DW12Studded</t>
+          <t>SII25CC24Jeweled</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
@@ -25735,17 +25747,17 @@
       </c>
       <c r="B726" s="7" t="inlineStr">
         <is>
-          <t>16162</t>
+          <t>16165</t>
         </is>
       </c>
       <c r="C726" s="7" t="inlineStr">
         <is>
-          <t>11164264</t>
+          <t>11164281</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>SI25Mug12Teach</t>
+          <t>SII25CC24B2S</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
@@ -25770,17 +25782,17 @@
       </c>
       <c r="B727" s="7" t="inlineStr">
         <is>
-          <t>16163</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="C727" s="7" t="inlineStr">
         <is>
-          <t>11164268</t>
+          <t>11164298</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>SII25Tu20Soft</t>
+          <t>Fl25SS20Grad</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
@@ -25805,17 +25817,17 @@
       </c>
       <c r="B728" s="7" t="inlineStr">
         <is>
-          <t>16164</t>
+          <t>16170</t>
         </is>
       </c>
       <c r="C728" s="7" t="inlineStr">
         <is>
-          <t>11164273</t>
+          <t>11164302</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>SII25CC24Jeweled</t>
+          <t>SI25SSCC24Swimm</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
@@ -25840,17 +25852,17 @@
       </c>
       <c r="B729" s="7" t="inlineStr">
         <is>
-          <t>16165</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="C729" s="7" t="inlineStr">
         <is>
-          <t>11164281</t>
+          <t>11164303</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>SII25CC24B2S</t>
+          <t>Fl25SS24Vac</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
@@ -25875,17 +25887,17 @@
       </c>
       <c r="B730" s="7" t="inlineStr">
         <is>
-          <t>16168</t>
+          <t>16172</t>
         </is>
       </c>
       <c r="C730" s="7" t="inlineStr">
         <is>
-          <t>11164298</t>
+          <t>11164306</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>Fl25SS20Grad</t>
+          <t>SI25Vac24Stanley</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
@@ -25910,17 +25922,17 @@
       </c>
       <c r="B731" s="7" t="inlineStr">
         <is>
-          <t>16170</t>
+          <t>16174</t>
         </is>
       </c>
       <c r="C731" s="7" t="inlineStr">
         <is>
-          <t>11164302</t>
+          <t>11164309</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>SI25SSCC24Swimm</t>
+          <t>SII25Quencher30</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
@@ -25945,17 +25957,17 @@
       </c>
       <c r="B732" s="7" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="C732" s="7" t="inlineStr">
         <is>
-          <t>11164303</t>
+          <t>11164311</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>Fl25SS24Vac</t>
+          <t>SI25Quencher30</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
@@ -25980,17 +25992,17 @@
       </c>
       <c r="B733" s="7" t="inlineStr">
         <is>
-          <t>16172</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="C733" s="7" t="inlineStr">
         <is>
-          <t>11164306</t>
+          <t>11164312</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>SI25Vac24Stanley</t>
+          <t>SI25SSCC24Father</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
@@ -26015,17 +26027,17 @@
       </c>
       <c r="B734" s="7" t="inlineStr">
         <is>
-          <t>16174</t>
+          <t>16178</t>
         </is>
       </c>
       <c r="C734" s="7" t="inlineStr">
         <is>
-          <t>11164309</t>
+          <t>11164319</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>SII25Quencher30</t>
+          <t>SI25KeychainZoo</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
@@ -26050,17 +26062,17 @@
       </c>
       <c r="B735" s="7" t="inlineStr">
         <is>
-          <t>16175</t>
+          <t>16179</t>
         </is>
       </c>
       <c r="C735" s="7" t="inlineStr">
         <is>
-          <t>11164311</t>
+          <t>11167149</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>SI25Quencher30</t>
+          <t>SII25SSCC24FRB</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
@@ -26085,17 +26097,17 @@
       </c>
       <c r="B736" s="7" t="inlineStr">
         <is>
-          <t>16176</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="C736" s="7" t="inlineStr">
         <is>
-          <t>11164312</t>
+          <t>11167150</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>SI25SSCC24Father</t>
+          <t>SII25CC24FRBlue</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
@@ -26120,17 +26132,17 @@
       </c>
       <c r="B737" s="7" t="inlineStr">
         <is>
-          <t>16178</t>
+          <t>16182</t>
         </is>
       </c>
       <c r="C737" s="7" t="inlineStr">
         <is>
-          <t>11164319</t>
+          <t>11167152</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>SI25KeychainZoo</t>
+          <t>SII25Tu16FarmR</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
@@ -26155,17 +26167,17 @@
       </c>
       <c r="B738" s="7" t="inlineStr">
         <is>
-          <t>16179</t>
+          <t>16246</t>
         </is>
       </c>
       <c r="C738" s="7" t="inlineStr">
         <is>
-          <t>11167149</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>SII25SSCC24FRB</t>
+          <t>Fl25SS20Siren</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
@@ -26190,17 +26202,17 @@
       </c>
       <c r="B739" s="7" t="inlineStr">
         <is>
-          <t>16180</t>
+          <t>16258</t>
         </is>
       </c>
       <c r="C739" s="7" t="inlineStr">
         <is>
-          <t>11167150</t>
+          <t>11171524</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>SII25CC24FRBlue</t>
+          <t>SII25ReusColor</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
@@ -26225,17 +26237,17 @@
       </c>
       <c r="B740" s="7" t="inlineStr">
         <is>
-          <t>16182</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="C740" s="7" t="inlineStr">
         <is>
-          <t>11167152</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>SII25Tu16FarmR</t>
+          <t>SI25ReusDelivery</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
@@ -26260,17 +26272,17 @@
       </c>
       <c r="B741" s="7" t="inlineStr">
         <is>
-          <t>16246</t>
+          <t>16264</t>
         </is>
       </c>
       <c r="C741" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11160967</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>Fl25SS20Siren</t>
+          <t>COR26PPBTL20S</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
@@ -26295,17 +26307,17 @@
       </c>
       <c r="B742" s="7" t="inlineStr">
         <is>
-          <t>16258</t>
+          <t>16265</t>
         </is>
       </c>
       <c r="C742" s="7" t="inlineStr">
         <is>
-          <t>11171524</t>
+          <t>11169482</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>SII25ReusColor</t>
+          <t>Fl25KeyChainD</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
@@ -26330,17 +26342,17 @@
       </c>
       <c r="B743" s="7" t="inlineStr">
         <is>
-          <t>16261</t>
+          <t>16266</t>
         </is>
       </c>
       <c r="C743" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11169450</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>SI25ReusDelivery</t>
+          <t>Fl25CC24StrawT</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
@@ -26365,17 +26377,17 @@
       </c>
       <c r="B744" s="7" t="inlineStr">
         <is>
-          <t>16264</t>
+          <t>16267</t>
         </is>
       </c>
       <c r="C744" s="7" t="inlineStr">
         <is>
-          <t>11160967</t>
+          <t>11162638</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>COR26PPBTL20S</t>
+          <t>COR25SSCC24Black</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
@@ -26400,17 +26412,17 @@
       </c>
       <c r="B745" s="7" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>16268</t>
         </is>
       </c>
       <c r="C745" s="7" t="inlineStr">
         <is>
-          <t>11169482</t>
+          <t>11169473</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>Fl25KeyChainD</t>
+          <t>Fl25CCSS24Pearl</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
@@ -26435,17 +26447,17 @@
       </c>
       <c r="B746" s="7" t="inlineStr">
         <is>
-          <t>16266</t>
+          <t>16269</t>
         </is>
       </c>
       <c r="C746" s="7" t="inlineStr">
         <is>
-          <t>11169450</t>
+          <t>11169467</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>Fl25CC24StrawT</t>
+          <t>Fl25CCSS16Vac</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
@@ -26470,17 +26482,17 @@
       </c>
       <c r="B747" s="7" t="inlineStr">
         <is>
-          <t>16267</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="C747" s="7" t="inlineStr">
         <is>
-          <t>11162638</t>
+          <t>11169475</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>COR25SSCC24Black</t>
+          <t>Fl25SSCC24Anniv</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
@@ -26505,17 +26517,17 @@
       </c>
       <c r="B748" s="7" t="inlineStr">
         <is>
-          <t>16268</t>
+          <t>16272</t>
         </is>
       </c>
       <c r="C748" s="7" t="inlineStr">
         <is>
-          <t>11169473</t>
+          <t>11169453</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>Fl25CCSS24Pearl</t>
+          <t>Fl25SSMug12Rib</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
@@ -26540,17 +26552,17 @@
       </c>
       <c r="B749" s="7" t="inlineStr">
         <is>
-          <t>16269</t>
+          <t>16273</t>
         </is>
       </c>
       <c r="C749" s="7" t="inlineStr">
         <is>
-          <t>11169467</t>
+          <t>11169470</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>Fl25CCSS16Vac</t>
+          <t>Fl25Stanley16</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
@@ -26575,17 +26587,17 @@
       </c>
       <c r="B750" s="7" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>16274</t>
         </is>
       </c>
       <c r="C750" s="7" t="inlineStr">
         <is>
-          <t>11169475</t>
+          <t>11169471</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>Fl25SSCC24Anniv</t>
+          <t>Fl25SS16Charm</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
@@ -26610,17 +26622,17 @@
       </c>
       <c r="B751" s="7" t="inlineStr">
         <is>
-          <t>16272</t>
+          <t>16275</t>
         </is>
       </c>
       <c r="C751" s="7" t="inlineStr">
         <is>
-          <t>11169453</t>
+          <t>11169454</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>Fl25SSMug12Rib</t>
+          <t>Fl25SSTu20Vac</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
@@ -26645,17 +26657,17 @@
       </c>
       <c r="B752" s="7" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16276</t>
         </is>
       </c>
       <c r="C752" s="7" t="inlineStr">
         <is>
-          <t>11169470</t>
+          <t>11169464</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>Fl25Stanley16</t>
+          <t>Fl25SSTu16Wave</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
@@ -26680,17 +26692,17 @@
       </c>
       <c r="B753" s="7" t="inlineStr">
         <is>
-          <t>16274</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="C753" s="7" t="inlineStr">
         <is>
-          <t>11169471</t>
+          <t>11169455</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>Fl25SS16Charm</t>
+          <t>Fl25SSBTL20</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
@@ -26715,17 +26727,17 @@
       </c>
       <c r="B754" s="7" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>16278</t>
         </is>
       </c>
       <c r="C754" s="7" t="inlineStr">
         <is>
-          <t>11169454</t>
+          <t>11169466</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>Fl25SSTu20Vac</t>
+          <t>Fl25StanPearl</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
@@ -26750,17 +26762,17 @@
       </c>
       <c r="B755" s="7" t="inlineStr">
         <is>
-          <t>16276</t>
+          <t>16279</t>
         </is>
       </c>
       <c r="C755" s="7" t="inlineStr">
         <is>
-          <t>11169464</t>
+          <t>11169456</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>Fl25SSTu16Wave</t>
+          <t>Fl25SSTu20Anni</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
@@ -26785,17 +26797,17 @@
       </c>
       <c r="B756" s="7" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="C756" s="7" t="inlineStr">
         <is>
-          <t>11169455</t>
+          <t>11169460</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>Fl25SSBTL20</t>
+          <t>Fl25SSCC24Sust</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
@@ -26820,17 +26832,17 @@
       </c>
       <c r="B757" s="7" t="inlineStr">
         <is>
-          <t>16278</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="C757" s="7" t="inlineStr">
         <is>
-          <t>11169466</t>
+          <t>11160988</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>Fl25StanPearl</t>
+          <t>COR25SS20STouch</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
@@ -26855,17 +26867,17 @@
       </c>
       <c r="B758" s="7" t="inlineStr">
         <is>
-          <t>16279</t>
+          <t>16282</t>
         </is>
       </c>
       <c r="C758" s="7" t="inlineStr">
         <is>
-          <t>11169456</t>
+          <t>11161002</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>Fl25SSTu20Anni</t>
+          <t>COR25Stan30Black</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
@@ -26890,17 +26902,17 @@
       </c>
       <c r="B759" s="7" t="inlineStr">
         <is>
-          <t>16280</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="C759" s="7" t="inlineStr">
         <is>
-          <t>11169460</t>
+          <t>11161003</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>Fl25SSCC24Sust</t>
+          <t>COR26Stan30White</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
@@ -26925,17 +26937,17 @@
       </c>
       <c r="B760" s="7" t="inlineStr">
         <is>
-          <t>16281</t>
+          <t>16284</t>
         </is>
       </c>
       <c r="C760" s="7" t="inlineStr">
         <is>
-          <t>11160988</t>
+          <t>11160991</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>COR25SS20STouch</t>
+          <t>COR25SS16Sleeve</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
@@ -26960,17 +26972,17 @@
       </c>
       <c r="B761" s="7" t="inlineStr">
         <is>
-          <t>16282</t>
+          <t>16285</t>
         </is>
       </c>
       <c r="C761" s="7" t="inlineStr">
         <is>
-          <t>11161002</t>
+          <t>11160965</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>COR25Stan30Black</t>
+          <t>COR26Tu16Sust</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
@@ -26995,17 +27007,17 @@
       </c>
       <c r="B762" s="7" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>16286</t>
         </is>
       </c>
       <c r="C762" s="7" t="inlineStr">
         <is>
-          <t>11161003</t>
+          <t>11169436</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>COR26Stan30White</t>
+          <t>Fl25Tu16Sust</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
@@ -27030,17 +27042,17 @@
       </c>
       <c r="B763" s="7" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>16287</t>
         </is>
       </c>
       <c r="C763" s="7" t="inlineStr">
         <is>
-          <t>11160991</t>
+          <t>11169430</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>COR25SS16Sleeve</t>
+          <t>Fl25Tu16Charm</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
@@ -27065,17 +27077,17 @@
       </c>
       <c r="B764" s="7" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>16288</t>
         </is>
       </c>
       <c r="C764" s="7" t="inlineStr">
         <is>
-          <t>11160965</t>
+          <t>11170273</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>COR26Tu16Sust</t>
+          <t>Fl25ReusCCEsp</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
@@ -27100,17 +27112,17 @@
       </c>
       <c r="B765" s="7" t="inlineStr">
         <is>
-          <t>16286</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="C765" s="7" t="inlineStr">
         <is>
-          <t>11169436</t>
+          <t>11169434</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>Fl25Tu16Sust</t>
+          <t>Fl25Tu16DDM</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
@@ -27135,17 +27147,17 @@
       </c>
       <c r="B766" s="7" t="inlineStr">
         <is>
-          <t>16287</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="C766" s="7" t="inlineStr">
         <is>
-          <t>11169430</t>
+          <t>11169439</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>Fl25Tu16Charm</t>
+          <t>Fl25CC24Dome</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
@@ -27170,17 +27182,17 @@
       </c>
       <c r="B767" s="7" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>16292</t>
         </is>
       </c>
       <c r="C767" s="7" t="inlineStr">
         <is>
-          <t>11170273</t>
+          <t>11169432</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>Fl25ReusCCEsp</t>
+          <t>Fl25Tu16Anniv</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
@@ -27205,17 +27217,17 @@
       </c>
       <c r="B768" s="7" t="inlineStr">
         <is>
-          <t>16290</t>
+          <t>16293</t>
         </is>
       </c>
       <c r="C768" s="7" t="inlineStr">
         <is>
-          <t>11169434</t>
+          <t>11169435</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>Fl25Tu16DDM</t>
+          <t>Fl25ReusPikeP</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
@@ -27240,17 +27252,17 @@
       </c>
       <c r="B769" s="7" t="inlineStr">
         <is>
-          <t>16291</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="C769" s="7" t="inlineStr">
         <is>
-          <t>11169439</t>
+          <t>11170275</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>Fl25CC24Dome</t>
+          <t>Fl25ReusCCPikeP</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
@@ -27275,17 +27287,17 @@
       </c>
       <c r="B770" s="7" t="inlineStr">
         <is>
-          <t>16292</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="C770" s="7" t="inlineStr">
         <is>
-          <t>11169432</t>
+          <t>11170274</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>Fl25Tu16Anniv</t>
+          <t>Fl25ReusEspresso</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
@@ -27310,17 +27322,17 @@
       </c>
       <c r="B771" s="7" t="inlineStr">
         <is>
-          <t>16293</t>
+          <t>16296</t>
         </is>
       </c>
       <c r="C771" s="7" t="inlineStr">
         <is>
-          <t>11169435</t>
+          <t>11169487</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>Fl25ReusPikeP</t>
+          <t>Fl25Pines</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
@@ -27345,17 +27357,17 @@
       </c>
       <c r="B772" s="7" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="C772" s="7" t="inlineStr">
         <is>
-          <t>11170275</t>
+          <t>11169491</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>Fl25ReusCCPikeP</t>
+          <t>Fl25PinesDDM</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
@@ -27380,17 +27392,17 @@
       </c>
       <c r="B773" s="7" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="C773" s="7" t="inlineStr">
         <is>
-          <t>11170274</t>
+          <t>11169429</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>Fl25ReusEspresso</t>
+          <t>Fl25GlassCCSust</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
@@ -27415,17 +27427,17 @@
       </c>
       <c r="B774" s="7" t="inlineStr">
         <is>
-          <t>16296</t>
+          <t>16299</t>
         </is>
       </c>
       <c r="C774" s="7" t="inlineStr">
         <is>
-          <t>11169487</t>
+          <t>11160981</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>Fl25Pines</t>
+          <t>COR26Glass16Sus</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
@@ -27450,17 +27462,17 @@
       </c>
       <c r="B775" s="7" t="inlineStr">
         <is>
-          <t>16297</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="C775" s="7" t="inlineStr">
         <is>
-          <t>11169491</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>Fl25PinesDDM</t>
+          <t>Fl25GlassCC</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
@@ -27485,17 +27497,17 @@
       </c>
       <c r="B776" s="7" t="inlineStr">
         <is>
-          <t>16298</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="C776" s="7" t="inlineStr">
         <is>
-          <t>11169429</t>
+          <t>11160947</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>Fl25GlassCCSust</t>
+          <t>COR25DW12Prism</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
@@ -27520,17 +27532,17 @@
       </c>
       <c r="B777" s="7" t="inlineStr">
         <is>
-          <t>16299</t>
+          <t>16309</t>
         </is>
       </c>
       <c r="C777" s="7" t="inlineStr">
         <is>
-          <t>11160981</t>
+          <t>11160952</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>COR26Glass16Sus</t>
+          <t>COR26Mug14Copper</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
@@ -27555,17 +27567,17 @@
       </c>
       <c r="B778" s="7" t="inlineStr">
         <is>
-          <t>16306</t>
+          <t>16310</t>
         </is>
       </c>
       <c r="C778" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11160955</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>Fl25GlassCC</t>
+          <t>COR26Mug2Copper</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
@@ -27590,17 +27602,17 @@
       </c>
       <c r="B779" s="7" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="C779" s="7" t="inlineStr">
         <is>
-          <t>11160947</t>
+          <t>11160990</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>COR25DW12Prism</t>
+          <t>COR26SSThruLid</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
@@ -27625,17 +27637,17 @@
       </c>
       <c r="B780" s="7" t="inlineStr">
         <is>
-          <t>16309</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="C780" s="7" t="inlineStr">
         <is>
-          <t>11160952</t>
+          <t>11160996</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>COR26Mug14Copper</t>
+          <t>COR25StanIceflow</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
@@ -27660,17 +27672,17 @@
       </c>
       <c r="B781" s="7" t="inlineStr">
         <is>
-          <t>16310</t>
+          <t>16315</t>
         </is>
       </c>
       <c r="C781" s="7" t="inlineStr">
         <is>
-          <t>11160955</t>
+          <t>11169423</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>COR26Mug2Copper</t>
+          <t>Fl25DW12Luster</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
@@ -27695,17 +27707,17 @@
       </c>
       <c r="B782" s="7" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16317</t>
         </is>
       </c>
       <c r="C782" s="7" t="inlineStr">
         <is>
-          <t>11160990</t>
+          <t>11169426</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>COR26SSThruLid</t>
+          <t>Fl25Mug14Abrac</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
@@ -27730,17 +27742,17 @@
       </c>
       <c r="B783" s="7" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16318</t>
         </is>
       </c>
       <c r="C783" s="7" t="inlineStr">
         <is>
-          <t>11160996</t>
+          <t>11169427</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>COR25StanIceflow</t>
+          <t>Fl25Mug16Sust</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
@@ -27765,17 +27777,17 @@
       </c>
       <c r="B784" s="7" t="inlineStr">
         <is>
-          <t>16315</t>
+          <t>16319</t>
         </is>
       </c>
       <c r="C784" s="7" t="inlineStr">
         <is>
-          <t>11169423</t>
+          <t>11169447</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>Fl25DW12Luster</t>
+          <t>Fl25CC24DDM</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
@@ -27800,17 +27812,17 @@
       </c>
       <c r="B785" s="7" t="inlineStr">
         <is>
-          <t>16317</t>
+          <t>16320</t>
         </is>
       </c>
       <c r="C785" s="7" t="inlineStr">
         <is>
-          <t>11169426</t>
+          <t>11169458</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>Fl25Mug14Abrac</t>
+          <t>Fl25SS20DDM</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
@@ -27835,17 +27847,17 @@
       </c>
       <c r="B786" s="7" t="inlineStr">
         <is>
-          <t>16318</t>
+          <t>16321</t>
         </is>
       </c>
       <c r="C786" s="7" t="inlineStr">
         <is>
-          <t>11169427</t>
+          <t>11169461</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>Fl25Mug16Sust</t>
+          <t>Fl25SSTu12Sust</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
@@ -27870,17 +27882,17 @@
       </c>
       <c r="B787" s="7" t="inlineStr">
         <is>
-          <t>16319</t>
+          <t>16322</t>
         </is>
       </c>
       <c r="C787" s="7" t="inlineStr">
         <is>
-          <t>11169447</t>
+          <t>11169462</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>Fl25CC24DDM</t>
+          <t>Fl25SS16Studded</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
@@ -27905,17 +27917,17 @@
       </c>
       <c r="B788" s="7" t="inlineStr">
         <is>
-          <t>16320</t>
+          <t>16323</t>
         </is>
       </c>
       <c r="C788" s="7" t="inlineStr">
         <is>
-          <t>11169458</t>
+          <t>11169468</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>Fl25SS20DDM</t>
+          <t>Fl25SSCC16Purple</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
@@ -27940,17 +27952,17 @@
       </c>
       <c r="B789" s="7" t="inlineStr">
         <is>
-          <t>16321</t>
+          <t>16326</t>
         </is>
       </c>
       <c r="C789" s="7" t="inlineStr">
         <is>
-          <t>11169461</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>Fl25SSTu12Sust</t>
+          <t>Fl25MonTSC</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
@@ -27975,17 +27987,17 @@
       </c>
       <c r="B790" s="7" t="inlineStr">
         <is>
-          <t>16322</t>
+          <t>16327</t>
         </is>
       </c>
       <c r="C790" s="7" t="inlineStr">
         <is>
-          <t>11169462</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>Fl25SS16Studded</t>
+          <t>Fl25MonVXMC</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
@@ -28010,17 +28022,17 @@
       </c>
       <c r="B791" s="7" t="inlineStr">
         <is>
-          <t>16323</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="C791" s="7" t="inlineStr">
         <is>
-          <t>11169468</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>Fl25SSCC16Purple</t>
+          <t>SII25LlaveroB2S</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
@@ -28045,7 +28057,7 @@
       </c>
       <c r="B792" s="7" t="inlineStr">
         <is>
-          <t>16326</t>
+          <t>16343</t>
         </is>
       </c>
       <c r="C792" s="7" t="inlineStr">
@@ -28055,7 +28067,7 @@
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>Fl25MonTSC</t>
+          <t>SII25ClipGirlB</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
@@ -28080,7 +28092,7 @@
       </c>
       <c r="B793" s="7" t="inlineStr">
         <is>
-          <t>16327</t>
+          <t>16344</t>
         </is>
       </c>
       <c r="C793" s="7" t="inlineStr">
@@ -28090,7 +28102,7 @@
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>Fl25MonVXMC</t>
+          <t>SII25StrawLluvia</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
@@ -28115,7 +28127,7 @@
       </c>
       <c r="B794" s="7" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>16345</t>
         </is>
       </c>
       <c r="C794" s="7" t="inlineStr">
@@ -28125,7 +28137,7 @@
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>SII25LlaveroB2S</t>
+          <t>SII25StopPSL</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
@@ -28150,7 +28162,7 @@
       </c>
       <c r="B795" s="7" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>16378</t>
         </is>
       </c>
       <c r="C795" s="7" t="inlineStr">
@@ -28160,7 +28172,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>SII25ClipGirlB</t>
+          <t>COR25CircCup</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
@@ -28185,7 +28197,7 @@
       </c>
       <c r="B796" s="7" t="inlineStr">
         <is>
-          <t>16344</t>
+          <t>16416</t>
         </is>
       </c>
       <c r="C796" s="7" t="inlineStr">
@@ -28195,7 +28207,7 @@
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>SII25StrawLluvia</t>
+          <t>Fl25ReusCCBa</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
@@ -28220,7 +28232,7 @@
       </c>
       <c r="B797" s="7" t="inlineStr">
         <is>
-          <t>16345</t>
+          <t>16417</t>
         </is>
       </c>
       <c r="C797" s="7" t="inlineStr">
@@ -28230,7 +28242,7 @@
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>SII25StopPSL</t>
+          <t>Fl25ReusBar</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
@@ -28255,17 +28267,17 @@
       </c>
       <c r="B798" s="7" t="inlineStr">
         <is>
-          <t>16378</t>
+          <t>16433</t>
         </is>
       </c>
       <c r="C798" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11173273</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>COR25CircCup</t>
+          <t>Xm25Tu12Hol</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
@@ -28290,17 +28302,17 @@
       </c>
       <c r="B799" s="7" t="inlineStr">
         <is>
-          <t>16416</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="C799" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11173046</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>Fl25ReusCCBa</t>
+          <t>Xm25CCGlass18</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
@@ -28325,17 +28337,17 @@
       </c>
       <c r="B800" s="7" t="inlineStr">
         <is>
-          <t>16417</t>
+          <t>16438</t>
         </is>
       </c>
       <c r="C800" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11173047</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>Fl25ReusBar</t>
+          <t>Xm25Tz14Glass</t>
         </is>
       </c>
       <c r="E800" t="inlineStr">
@@ -28360,17 +28372,17 @@
       </c>
       <c r="B801" s="7" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>16439</t>
         </is>
       </c>
       <c r="C801" s="7" t="inlineStr">
         <is>
-          <t>11173273</t>
+          <t>11172983</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>Xm25Tu12Hol</t>
+          <t>Xm25Mug12Stan</t>
         </is>
       </c>
       <c r="E801" t="inlineStr">
@@ -28395,17 +28407,17 @@
       </c>
       <c r="B802" s="7" t="inlineStr">
         <is>
-          <t>16437</t>
+          <t>16440</t>
         </is>
       </c>
       <c r="C802" s="7" t="inlineStr">
         <is>
-          <t>11173046</t>
+          <t>11172998</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
         <is>
-          <t>Xm25CCGlass18</t>
+          <t>Xm25SSCC24Topp</t>
         </is>
       </c>
       <c r="E802" t="inlineStr">
@@ -28430,17 +28442,17 @@
       </c>
       <c r="B803" s="7" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>16441</t>
         </is>
       </c>
       <c r="C803" s="7" t="inlineStr">
         <is>
-          <t>11173047</t>
+          <t>11173000</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>Xm25Tz14Glass</t>
+          <t>Xm25CC24House</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
@@ -28465,17 +28477,17 @@
       </c>
       <c r="B804" s="7" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>16442</t>
         </is>
       </c>
       <c r="C804" s="7" t="inlineStr">
         <is>
-          <t>11172983</t>
+          <t>11172996</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>Xm25Mug12Stan</t>
+          <t>Xm25SSCC24R</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
@@ -28500,17 +28512,17 @@
       </c>
       <c r="B805" s="7" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>16443</t>
         </is>
       </c>
       <c r="C805" s="7" t="inlineStr">
         <is>
-          <t>11172998</t>
+          <t>11172994</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>Xm25SSCC24Topp</t>
+          <t>Xm25BTLStanley</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
@@ -28535,17 +28547,17 @@
       </c>
       <c r="B806" s="7" t="inlineStr">
         <is>
-          <t>16441</t>
+          <t>16444</t>
         </is>
       </c>
       <c r="C806" s="7" t="inlineStr">
         <is>
-          <t>11173000</t>
+          <t>11172855</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>Xm25CC24House</t>
+          <t>Xm25DW12Red</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
@@ -28570,17 +28582,17 @@
       </c>
       <c r="B807" s="7" t="inlineStr">
         <is>
-          <t>16442</t>
+          <t>16446</t>
         </is>
       </c>
       <c r="C807" s="7" t="inlineStr">
         <is>
-          <t>11172996</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>Xm25SSCC24R</t>
+          <t>Fl25MonederoAniv</t>
         </is>
       </c>
       <c r="E807" t="inlineStr">
@@ -28605,17 +28617,17 @@
       </c>
       <c r="B808" s="7" t="inlineStr">
         <is>
-          <t>16443</t>
+          <t>16453</t>
         </is>
       </c>
       <c r="C808" s="7" t="inlineStr">
         <is>
-          <t>11172994</t>
+          <t>11172962</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>Xm25BTLStanley</t>
+          <t>Xm25Tu16Charm</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
@@ -28640,17 +28652,13 @@
       </c>
       <c r="B809" s="7" t="inlineStr">
         <is>
-          <t>16444</t>
-        </is>
-      </c>
-      <c r="C809" s="7" t="inlineStr">
-        <is>
-          <t>11172855</t>
-        </is>
-      </c>
+          <t>16454</t>
+        </is>
+      </c>
+      <c r="C809" s="7" t="inlineStr"/>
       <c r="D809" t="inlineStr">
         <is>
-          <t>Xm25DW12Red</t>
+          <t>Xm25Give16CC</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
@@ -28675,17 +28683,17 @@
       </c>
       <c r="B810" s="7" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>16455</t>
         </is>
       </c>
       <c r="C810" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11172965</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>Fl25MonederoAniv</t>
+          <t>Xm25Tu16CPing</t>
         </is>
       </c>
       <c r="E810" t="inlineStr">
@@ -28710,17 +28718,17 @@
       </c>
       <c r="B811" s="7" t="inlineStr">
         <is>
-          <t>16453</t>
+          <t>16456</t>
         </is>
       </c>
       <c r="C811" s="7" t="inlineStr">
         <is>
-          <t>11172962</t>
+          <t>11172974</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>Xm25Tu16Charm</t>
+          <t>Xm25CC24Snow</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
@@ -28745,13 +28753,17 @@
       </c>
       <c r="B812" s="7" t="inlineStr">
         <is>
-          <t>16454</t>
-        </is>
-      </c>
-      <c r="C812" s="7" t="inlineStr"/>
+          <t>16457</t>
+        </is>
+      </c>
+      <c r="C812" s="7" t="inlineStr">
+        <is>
+          <t>11173031</t>
+        </is>
+      </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>Xm25Give16CC</t>
+          <t>Xm25Llavero</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
@@ -28776,17 +28788,17 @@
       </c>
       <c r="B813" s="7" t="inlineStr">
         <is>
-          <t>16455</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="C813" s="7" t="inlineStr">
         <is>
-          <t>11172965</t>
+          <t>11172984</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>Xm25Tu16CPing</t>
+          <t>Xm25SS16DIam</t>
         </is>
       </c>
       <c r="E813" t="inlineStr">
@@ -28811,17 +28823,17 @@
       </c>
       <c r="B814" s="7" t="inlineStr">
         <is>
-          <t>16456</t>
+          <t>16459</t>
         </is>
       </c>
       <c r="C814" s="7" t="inlineStr">
         <is>
-          <t>11172974</t>
+          <t>11172985</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>Xm25CC24Snow</t>
+          <t>Xm25SS16Green</t>
         </is>
       </c>
       <c r="E814" t="inlineStr">
@@ -28846,17 +28858,17 @@
       </c>
       <c r="B815" s="7" t="inlineStr">
         <is>
-          <t>16457</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="C815" s="7" t="inlineStr">
         <is>
-          <t>11173031</t>
+          <t>11172993</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>Xm25Llavero</t>
+          <t>Xm25TuStan20</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
@@ -28881,17 +28893,17 @@
       </c>
       <c r="B816" s="7" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="C816" s="7" t="inlineStr">
         <is>
-          <t>11172984</t>
+          <t>11172997</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>Xm25SS16DIam</t>
+          <t>Xm25RedQuen30</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">
@@ -28916,17 +28928,17 @@
       </c>
       <c r="B817" s="7" t="inlineStr">
         <is>
-          <t>16459</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="C817" s="7" t="inlineStr">
         <is>
-          <t>11172985</t>
+          <t>11173001</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>Xm25SS16Green</t>
+          <t>Xm25Quencher30</t>
         </is>
       </c>
       <c r="E817" t="inlineStr">
@@ -28951,17 +28963,17 @@
       </c>
       <c r="B818" s="7" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="C818" s="7" t="inlineStr">
         <is>
-          <t>11172993</t>
+          <t>11172989</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>Xm25TuStan20</t>
+          <t>Xm25StanVac16</t>
         </is>
       </c>
       <c r="E818" t="inlineStr">
@@ -28986,17 +28998,17 @@
       </c>
       <c r="B819" s="7" t="inlineStr">
         <is>
-          <t>16462</t>
+          <t>16465</t>
         </is>
       </c>
       <c r="C819" s="7" t="inlineStr">
         <is>
-          <t>11172997</t>
+          <t>11172990</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>Xm25RedQuen30</t>
+          <t>Xm25StanCB16</t>
         </is>
       </c>
       <c r="E819" t="inlineStr">
@@ -29021,17 +29033,17 @@
       </c>
       <c r="B820" s="7" t="inlineStr">
         <is>
-          <t>16463</t>
+          <t>16466</t>
         </is>
       </c>
       <c r="C820" s="7" t="inlineStr">
         <is>
-          <t>11173001</t>
+          <t>11172999</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
         <is>
-          <t>Xm25Quencher30</t>
+          <t>Xm25Quen30Lil</t>
         </is>
       </c>
       <c r="E820" t="inlineStr">
@@ -29056,17 +29068,17 @@
       </c>
       <c r="B821" s="7" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16467</t>
         </is>
       </c>
       <c r="C821" s="7" t="inlineStr">
         <is>
-          <t>11172989</t>
+          <t>11172981</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>Xm25StanVac16</t>
+          <t>Xm25SS12Vac</t>
         </is>
       </c>
       <c r="E821" t="inlineStr">
@@ -29091,17 +29103,17 @@
       </c>
       <c r="B822" s="7" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="C822" s="7" t="inlineStr">
         <is>
-          <t>11172990</t>
+          <t>11172992</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>Xm25StanCB16</t>
+          <t>Xm25BTL20Twi</t>
         </is>
       </c>
       <c r="E822" t="inlineStr">
@@ -29126,17 +29138,17 @@
       </c>
       <c r="B823" s="7" t="inlineStr">
         <is>
-          <t>16466</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="C823" s="7" t="inlineStr">
         <is>
-          <t>11172999</t>
+          <t>11172988</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
         <is>
-          <t>Xm25Quen30Lil</t>
+          <t>Xm25SS16Charm</t>
         </is>
       </c>
       <c r="E823" t="inlineStr">
@@ -29161,17 +29173,17 @@
       </c>
       <c r="B824" s="7" t="inlineStr">
         <is>
-          <t>16467</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="C824" s="7" t="inlineStr">
         <is>
-          <t>11172981</t>
+          <t>11172971</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
         <is>
-          <t>Xm25SS12Vac</t>
+          <t>Xm25CC24Hol</t>
         </is>
       </c>
       <c r="E824" t="inlineStr">
@@ -29196,17 +29208,13 @@
       </c>
       <c r="B825" s="7" t="inlineStr">
         <is>
-          <t>16468</t>
-        </is>
-      </c>
-      <c r="C825" s="7" t="inlineStr">
-        <is>
-          <t>11172992</t>
-        </is>
-      </c>
+          <t>16471</t>
+        </is>
+      </c>
+      <c r="C825" s="7" t="inlineStr"/>
       <c r="D825" t="inlineStr">
         <is>
-          <t>Xm25BTL20Twi</t>
+          <t>Xm25Give16Hot</t>
         </is>
       </c>
       <c r="E825" t="inlineStr">
@@ -29231,17 +29239,17 @@
       </c>
       <c r="B826" s="7" t="inlineStr">
         <is>
-          <t>16469</t>
+          <t>16472</t>
         </is>
       </c>
       <c r="C826" s="7" t="inlineStr">
         <is>
-          <t>11172988</t>
+          <t>11172975</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>Xm25SS16Charm</t>
+          <t>Xm25BTL24Magn</t>
         </is>
       </c>
       <c r="E826" t="inlineStr">
@@ -29266,17 +29274,17 @@
       </c>
       <c r="B827" s="7" t="inlineStr">
         <is>
-          <t>16470</t>
+          <t>16473</t>
         </is>
       </c>
       <c r="C827" s="7" t="inlineStr">
         <is>
-          <t>11172971</t>
+          <t>11172967</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>Xm25CC24Hol</t>
+          <t>Xm25Tu16Bow</t>
         </is>
       </c>
       <c r="E827" t="inlineStr">
@@ -29301,13 +29309,17 @@
       </c>
       <c r="B828" s="7" t="inlineStr">
         <is>
-          <t>16471</t>
-        </is>
-      </c>
-      <c r="C828" s="7" t="inlineStr"/>
+          <t>16474</t>
+        </is>
+      </c>
+      <c r="C828" s="7" t="inlineStr">
+        <is>
+          <t>11172857</t>
+        </is>
+      </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>Xm25Give16Hot</t>
+          <t>Xm25MugPinguin</t>
         </is>
       </c>
       <c r="E828" t="inlineStr">
@@ -29332,17 +29344,17 @@
       </c>
       <c r="B829" s="7" t="inlineStr">
         <is>
-          <t>16472</t>
+          <t>16475</t>
         </is>
       </c>
       <c r="C829" s="7" t="inlineStr">
         <is>
-          <t>11172975</t>
+          <t>11172859</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>Xm25BTL24Magn</t>
+          <t>Xm25Mug12House</t>
         </is>
       </c>
       <c r="E829" t="inlineStr">
@@ -29367,17 +29379,17 @@
       </c>
       <c r="B830" s="7" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>16476</t>
         </is>
       </c>
       <c r="C830" s="7" t="inlineStr">
         <is>
-          <t>11172967</t>
+          <t>11172986</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>Xm25Tu16Bow</t>
+          <t>Xm25SS16Peng</t>
         </is>
       </c>
       <c r="E830" t="inlineStr">
@@ -29402,17 +29414,17 @@
       </c>
       <c r="B831" s="7" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="C831" s="7" t="inlineStr">
         <is>
-          <t>11172857</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
         <is>
-          <t>Xm25MugPinguin</t>
+          <t>Fl25StopperBar</t>
         </is>
       </c>
       <c r="E831" t="inlineStr">
@@ -29437,17 +29449,17 @@
       </c>
       <c r="B832" s="7" t="inlineStr">
         <is>
-          <t>16475</t>
+          <t>16489</t>
         </is>
       </c>
       <c r="C832" s="7" t="inlineStr">
         <is>
-          <t>11172859</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>Xm25Mug12House</t>
+          <t>Fl25StrawBar</t>
         </is>
       </c>
       <c r="E832" t="inlineStr">
@@ -29472,17 +29484,17 @@
       </c>
       <c r="B833" s="7" t="inlineStr">
         <is>
-          <t>16476</t>
+          <t>16490</t>
         </is>
       </c>
       <c r="C833" s="7" t="inlineStr">
         <is>
-          <t>11172986</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>Xm25SS16Peng</t>
+          <t>Fl25Manga</t>
         </is>
       </c>
       <c r="E833" t="inlineStr">
@@ -29507,7 +29519,7 @@
       </c>
       <c r="B834" s="7" t="inlineStr">
         <is>
-          <t>16488</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="C834" s="7" t="inlineStr">
@@ -29517,7 +29529,7 @@
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>Fl25StopperBar</t>
+          <t>Fl25Llavero</t>
         </is>
       </c>
       <c r="E834" t="inlineStr">
@@ -29542,7 +29554,7 @@
       </c>
       <c r="B835" s="7" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>16502</t>
         </is>
       </c>
       <c r="C835" s="7" t="inlineStr">
@@ -29552,7 +29564,7 @@
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>Fl25StrawBar</t>
+          <t>Xm25Tag</t>
         </is>
       </c>
       <c r="E835" t="inlineStr">
@@ -29577,7 +29589,7 @@
       </c>
       <c r="B836" s="7" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="C836" s="7" t="inlineStr">
@@ -29587,7 +29599,7 @@
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>Fl25Manga</t>
+          <t>Xm25Stopper</t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
@@ -29612,17 +29624,17 @@
       </c>
       <c r="B837" s="7" t="inlineStr">
         <is>
-          <t>16500</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="C837" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11174779</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>Fl25Llavero</t>
+          <t>Wt26CCGl16Red</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
@@ -29647,17 +29659,17 @@
       </c>
       <c r="B838" s="7" t="inlineStr">
         <is>
-          <t>16502</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="C838" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11174804</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>Xm25Tag</t>
+          <t>Wt26BTLStanley</t>
         </is>
       </c>
       <c r="E838" t="inlineStr">
@@ -29682,17 +29694,17 @@
       </c>
       <c r="B839" s="7" t="inlineStr">
         <is>
-          <t>16503</t>
+          <t>16543</t>
         </is>
       </c>
       <c r="C839" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11174795</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>Xm25Stopper</t>
+          <t>Wt26CC24Spinner</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
@@ -29717,17 +29729,17 @@
       </c>
       <c r="B840" s="7" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>16544</t>
         </is>
       </c>
       <c r="C840" s="7" t="inlineStr">
         <is>
-          <t>11174779</t>
+          <t>11177277</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>Wt26CCGl16Red</t>
+          <t>Wt26CC24Choco</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
@@ -29752,17 +29764,17 @@
       </c>
       <c r="B841" s="7" t="inlineStr">
         <is>
-          <t>16541</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="C841" s="7" t="inlineStr">
         <is>
-          <t>11174804</t>
+          <t>11174808</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>Wt26BTLStanley</t>
+          <t>Wt26SSCC24Grad</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
@@ -29787,17 +29799,17 @@
       </c>
       <c r="B842" s="7" t="inlineStr">
         <is>
-          <t>16543</t>
+          <t>16546</t>
         </is>
       </c>
       <c r="C842" s="7" t="inlineStr">
         <is>
-          <t>11174795</t>
+          <t>11174811</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>Wt26CC24Spinner</t>
+          <t>Wt26SS30Jac</t>
         </is>
       </c>
       <c r="E842" t="inlineStr">
@@ -29822,17 +29834,17 @@
       </c>
       <c r="B843" s="7" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>16547</t>
         </is>
       </c>
       <c r="C843" s="7" t="inlineStr">
         <is>
-          <t>11177277</t>
+          <t>11177274</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>Wt26CC24Choco</t>
+          <t>Wt26SSCC24Win</t>
         </is>
       </c>
       <c r="E843" t="inlineStr">
@@ -29857,17 +29869,17 @@
       </c>
       <c r="B844" s="7" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>16548</t>
         </is>
       </c>
       <c r="C844" s="7" t="inlineStr">
         <is>
-          <t>11174808</t>
+          <t>11174801</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>Wt26SSCC24Grad</t>
+          <t>Wt26SSBTL20SV</t>
         </is>
       </c>
       <c r="E844" t="inlineStr">
@@ -29892,17 +29904,17 @@
       </c>
       <c r="B845" s="7" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16549</t>
         </is>
       </c>
       <c r="C845" s="7" t="inlineStr">
         <is>
-          <t>11174811</t>
+          <t>11174803</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>Wt26SS30Jac</t>
+          <t>Wt262PkStanley</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
@@ -29927,17 +29939,17 @@
       </c>
       <c r="B846" s="7" t="inlineStr">
         <is>
-          <t>16547</t>
+          <t>16551</t>
         </is>
       </c>
       <c r="C846" s="7" t="inlineStr">
         <is>
-          <t>11177274</t>
+          <t>11174775</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>Wt26SSCC24Win</t>
+          <t>Wt26Dw12Jac</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
@@ -29962,17 +29974,17 @@
       </c>
       <c r="B847" s="7" t="inlineStr">
         <is>
-          <t>16548</t>
+          <t>16552</t>
         </is>
       </c>
       <c r="C847" s="7" t="inlineStr">
         <is>
-          <t>11174801</t>
+          <t>11174798</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>Wt26SSBTL20SV</t>
+          <t>Wt26SS16Green</t>
         </is>
       </c>
       <c r="E847" t="inlineStr">
@@ -29997,17 +30009,17 @@
       </c>
       <c r="B848" s="7" t="inlineStr">
         <is>
-          <t>16549</t>
+          <t>16553</t>
         </is>
       </c>
       <c r="C848" s="7" t="inlineStr">
         <is>
-          <t>11174803</t>
+          <t>11174800</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>Wt262PkStanley</t>
+          <t>Wt26BTL20Gr</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
@@ -30032,17 +30044,17 @@
       </c>
       <c r="B849" s="7" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>16554</t>
         </is>
       </c>
       <c r="C849" s="7" t="inlineStr">
         <is>
-          <t>11174776</t>
+          <t>11174807</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>Wt26Mug14Bow</t>
+          <t>Wt26SS16Choco</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
@@ -30067,17 +30079,17 @@
       </c>
       <c r="B850" s="7" t="inlineStr">
         <is>
-          <t>16551</t>
+          <t>16555</t>
         </is>
       </c>
       <c r="C850" s="7" t="inlineStr">
         <is>
-          <t>11174775</t>
+          <t>11174810</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>Wt26Dw12Jac</t>
+          <t>Wt26Canteen</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
@@ -30102,17 +30114,17 @@
       </c>
       <c r="B851" s="7" t="inlineStr">
         <is>
-          <t>16552</t>
+          <t>16556</t>
         </is>
       </c>
       <c r="C851" s="7" t="inlineStr">
         <is>
-          <t>11174798</t>
+          <t>11174799</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>Wt26SS16Green</t>
+          <t>Wt26SSCC16Grad</t>
         </is>
       </c>
       <c r="E851" t="inlineStr">
@@ -30137,17 +30149,17 @@
       </c>
       <c r="B852" s="7" t="inlineStr">
         <is>
-          <t>16553</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="C852" s="7" t="inlineStr">
         <is>
-          <t>11174800</t>
+          <t>11174806</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>Wt26BTL20Gr</t>
+          <t>Wt26SSCC16Jac</t>
         </is>
       </c>
       <c r="E852" t="inlineStr">
@@ -30172,17 +30184,17 @@
       </c>
       <c r="B853" s="7" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>16558</t>
         </is>
       </c>
       <c r="C853" s="7" t="inlineStr">
         <is>
-          <t>11174807</t>
+          <t>11177275</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>Wt26SS16Choco</t>
+          <t>Wt26SS20SV</t>
         </is>
       </c>
       <c r="E853" t="inlineStr">
@@ -30207,17 +30219,17 @@
       </c>
       <c r="B854" s="7" t="inlineStr">
         <is>
-          <t>16555</t>
+          <t>16559</t>
         </is>
       </c>
       <c r="C854" s="7" t="inlineStr">
         <is>
-          <t>11174810</t>
+          <t>11177276</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>Wt26Canteen</t>
+          <t>Wt26SS20Jac</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
@@ -30242,17 +30254,13 @@
       </c>
       <c r="B855" s="7" t="inlineStr">
         <is>
-          <t>16556</t>
-        </is>
-      </c>
-      <c r="C855" s="7" t="inlineStr">
-        <is>
-          <t>11174799</t>
-        </is>
-      </c>
+          <t>16566</t>
+        </is>
+      </c>
+      <c r="C855" s="7" t="inlineStr"/>
       <c r="D855" t="inlineStr">
         <is>
-          <t>Wt26SSCC16Grad</t>
+          <t>BearHugger</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
@@ -30277,17 +30285,17 @@
       </c>
       <c r="B856" s="7" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="C856" s="7" t="inlineStr">
         <is>
-          <t>11174806</t>
+          <t>11174791</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>Wt26SSCC16Jac</t>
+          <t>Wt26ReusSV</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
@@ -30312,17 +30320,17 @@
       </c>
       <c r="B857" s="7" t="inlineStr">
         <is>
-          <t>16558</t>
+          <t>16573</t>
         </is>
       </c>
       <c r="C857" s="7" t="inlineStr">
         <is>
-          <t>11177275</t>
+          <t>11175037</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>Wt26SS20SV</t>
+          <t>Wt26Tu16Charm</t>
         </is>
       </c>
       <c r="E857" t="inlineStr">
@@ -30347,17 +30355,17 @@
       </c>
       <c r="B858" s="7" t="inlineStr">
         <is>
-          <t>16559</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="C858" s="7" t="inlineStr">
         <is>
-          <t>11177276</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>Wt26SS20Jac</t>
+          <t>Xm25ReuElev</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
@@ -30382,13 +30390,17 @@
       </c>
       <c r="B859" s="7" t="inlineStr">
         <is>
-          <t>16566</t>
-        </is>
-      </c>
-      <c r="C859" s="7" t="inlineStr"/>
+          <t>16589</t>
+        </is>
+      </c>
+      <c r="C859" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="D859" t="inlineStr">
         <is>
-          <t>BearHugger</t>
+          <t>Xm25ReuMike</t>
         </is>
       </c>
       <c r="E859" t="inlineStr">
@@ -30413,17 +30425,17 @@
       </c>
       <c r="B860" s="7" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>16590</t>
         </is>
       </c>
       <c r="C860" s="7" t="inlineStr">
         <is>
-          <t>11174791</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
         <is>
-          <t>Wt26ReusSV</t>
+          <t>Xm25Reus16ST</t>
         </is>
       </c>
       <c r="E860" t="inlineStr">
@@ -30448,17 +30460,17 @@
       </c>
       <c r="B861" s="7" t="inlineStr">
         <is>
-          <t>16573</t>
+          <t>16591</t>
         </is>
       </c>
       <c r="C861" s="7" t="inlineStr">
         <is>
-          <t>11175037</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>Wt26Tu16Charm</t>
+          <t>Xm25Reu24CCST</t>
         </is>
       </c>
       <c r="E861" t="inlineStr">
@@ -30483,7 +30495,7 @@
       </c>
       <c r="B862" s="7" t="inlineStr">
         <is>
-          <t>16588</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="C862" s="7" t="inlineStr">
@@ -30493,7 +30505,7 @@
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>Xm25ReuElev</t>
+          <t>Xm25Reu2Hol</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
@@ -30518,7 +30530,7 @@
       </c>
       <c r="B863" s="7" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>16603</t>
         </is>
       </c>
       <c r="C863" s="7" t="inlineStr">
@@ -30528,7 +30540,7 @@
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>Xm25ReuMike</t>
+          <t>Xm25Reu1Hol</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
@@ -30553,17 +30565,17 @@
       </c>
       <c r="B864" s="7" t="inlineStr">
         <is>
-          <t>16590</t>
+          <t>16607</t>
         </is>
       </c>
       <c r="C864" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11177964</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>Xm25Reus16ST</t>
+          <t>Sp26WTBLSS16Cher</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
@@ -30588,17 +30600,17 @@
       </c>
       <c r="B865" s="7" t="inlineStr">
         <is>
-          <t>16591</t>
+          <t>16608</t>
         </is>
       </c>
       <c r="C865" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11176612</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>Xm25Reu24CCST</t>
+          <t>Wt26CC15Blue</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
@@ -30623,17 +30635,17 @@
       </c>
       <c r="B866" s="7" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>16609</t>
         </is>
       </c>
       <c r="C866" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11176610</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>Xm25Reu2Hol</t>
+          <t>Wt26TuSS16Duck</t>
         </is>
       </c>
       <c r="E866" t="inlineStr">
@@ -30658,17 +30670,17 @@
       </c>
       <c r="B867" s="7" t="inlineStr">
         <is>
-          <t>16603</t>
+          <t>16610</t>
         </is>
       </c>
       <c r="C867" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11179880</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>Xm25Reu1Hol</t>
+          <t>SII26SS16Resort</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
@@ -30693,17 +30705,17 @@
       </c>
       <c r="B868" s="7" t="inlineStr">
         <is>
-          <t>16607</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="C868" s="7" t="inlineStr">
         <is>
-          <t>11177964</t>
+          <t>11177937</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>Sp26WTBLSS16Cher</t>
+          <t>Sp26CCup16Cherry</t>
         </is>
       </c>
       <c r="E868" t="inlineStr">
@@ -30728,17 +30740,17 @@
       </c>
       <c r="B869" s="7" t="inlineStr">
         <is>
-          <t>16608</t>
+          <t>16613</t>
         </is>
       </c>
       <c r="C869" s="7" t="inlineStr">
         <is>
-          <t>11176612</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>Wt26CC15Blue</t>
+          <t>Xm25StopDermo</t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
@@ -30763,17 +30775,17 @@
       </c>
       <c r="B870" s="7" t="inlineStr">
         <is>
-          <t>16609</t>
+          <t>16614</t>
         </is>
       </c>
       <c r="C870" s="7" t="inlineStr">
         <is>
-          <t>11176610</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>Wt26TuSS16Duck</t>
+          <t>Xm25StopHopp</t>
         </is>
       </c>
       <c r="E870" t="inlineStr">
@@ -30798,17 +30810,17 @@
       </c>
       <c r="B871" s="7" t="inlineStr">
         <is>
-          <t>16610</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="C871" s="7" t="inlineStr">
         <is>
-          <t>11179880</t>
+          <t>11176708</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
         <is>
-          <t>SII26SS16Resort</t>
+          <t>Wt26GlassCC16</t>
         </is>
       </c>
       <c r="E871" t="inlineStr">
@@ -30833,17 +30845,17 @@
       </c>
       <c r="B872" s="7" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>16659</t>
         </is>
       </c>
       <c r="C872" s="7" t="inlineStr">
         <is>
-          <t>11177937</t>
+          <t>11176714</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>Sp26CCup16Cherry</t>
+          <t>Wt26SS16Vac</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
@@ -30868,17 +30880,17 @@
       </c>
       <c r="B873" s="7" t="inlineStr">
         <is>
-          <t>16613</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="C873" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11176719</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>Xm25StopDermo</t>
+          <t>Wt26SSCC24CarryL</t>
         </is>
       </c>
       <c r="E873" t="inlineStr">
@@ -30903,17 +30915,17 @@
       </c>
       <c r="B874" s="7" t="inlineStr">
         <is>
-          <t>16614</t>
+          <t>16661</t>
         </is>
       </c>
       <c r="C874" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11176720</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
         <is>
-          <t>Xm25StopHopp</t>
+          <t>Wt26SSCC30Togo</t>
         </is>
       </c>
       <c r="E874" t="inlineStr">
@@ -30938,17 +30950,17 @@
       </c>
       <c r="B875" s="7" t="inlineStr">
         <is>
-          <t>16658</t>
+          <t>16662</t>
         </is>
       </c>
       <c r="C875" s="7" t="inlineStr">
         <is>
-          <t>11176708</t>
+          <t>11176721</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
         <is>
-          <t>Wt26GlassCC16</t>
+          <t>Sp26Stan30Purp</t>
         </is>
       </c>
       <c r="E875" t="inlineStr">
@@ -30973,17 +30985,17 @@
       </c>
       <c r="B876" s="7" t="inlineStr">
         <is>
-          <t>16659</t>
+          <t>16663</t>
         </is>
       </c>
       <c r="C876" s="7" t="inlineStr">
         <is>
-          <t>11176714</t>
+          <t>11176699</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>Wt26SS16Vac</t>
+          <t>Sp26Mug14Rabbit</t>
         </is>
       </c>
       <c r="E876" t="inlineStr">
@@ -31008,17 +31020,17 @@
       </c>
       <c r="B877" s="7" t="inlineStr">
         <is>
-          <t>16660</t>
+          <t>16665</t>
         </is>
       </c>
       <c r="C877" s="7" t="inlineStr">
         <is>
-          <t>11176719</t>
+          <t>11176701</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>Wt26SSCC24CarryL</t>
+          <t>Sp26CC216Rabbit</t>
         </is>
       </c>
       <c r="E877" t="inlineStr">
@@ -31043,17 +31055,17 @@
       </c>
       <c r="B878" s="7" t="inlineStr">
         <is>
-          <t>16661</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C878" s="7" t="inlineStr">
         <is>
-          <t>11176720</t>
+          <t>11176702</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>Wt26SSCC30Togo</t>
+          <t>Sp26Tu20Blue</t>
         </is>
       </c>
       <c r="E878" t="inlineStr">
@@ -31078,17 +31090,17 @@
       </c>
       <c r="B879" s="7" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="C879" s="7" t="inlineStr">
         <is>
-          <t>11176721</t>
+          <t>11176715</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>Sp26Stan30Purp</t>
+          <t>Sp26SS16Rabbit</t>
         </is>
       </c>
       <c r="E879" t="inlineStr">
@@ -31113,17 +31125,17 @@
       </c>
       <c r="B880" s="7" t="inlineStr">
         <is>
-          <t>16663</t>
+          <t>16669</t>
         </is>
       </c>
       <c r="C880" s="7" t="inlineStr">
         <is>
-          <t>11176699</t>
+          <t>11176711</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>Sp26Mug14Rabbit</t>
+          <t>Sp26Gl18Mottled</t>
         </is>
       </c>
       <c r="E880" t="inlineStr">
@@ -31148,17 +31160,17 @@
       </c>
       <c r="B881" s="7" t="inlineStr">
         <is>
-          <t>16665</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="C881" s="7" t="inlineStr">
         <is>
-          <t>11176701</t>
+          <t>11176700</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>Sp26CC216Rabbit</t>
+          <t>Sp26Tz14GlassC</t>
         </is>
       </c>
       <c r="E881" t="inlineStr">
@@ -31183,17 +31195,17 @@
       </c>
       <c r="B882" s="7" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>16671</t>
         </is>
       </c>
       <c r="C882" s="7" t="inlineStr">
         <is>
-          <t>11176702</t>
+          <t>11176717</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
         <is>
-          <t>Sp26Tu20Blue</t>
+          <t>Sp26SS12Pink</t>
         </is>
       </c>
       <c r="E882" t="inlineStr">
@@ -31218,17 +31230,17 @@
       </c>
       <c r="B883" s="7" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="C883" s="7" t="inlineStr">
         <is>
-          <t>11176715</t>
+          <t>11176724</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
         <is>
-          <t>Sp26SS16Rabbit</t>
+          <t>Sp26CookieJP</t>
         </is>
       </c>
       <c r="E883" t="inlineStr">
@@ -31253,17 +31265,17 @@
       </c>
       <c r="B884" s="7" t="inlineStr">
         <is>
-          <t>16669</t>
+          <t>16673</t>
         </is>
       </c>
       <c r="C884" s="7" t="inlineStr">
         <is>
-          <t>11176711</t>
+          <t>11176703</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
         <is>
-          <t>Sp26Gl18Mottled</t>
+          <t>Sp26Tu16Cherry</t>
         </is>
       </c>
       <c r="E884" t="inlineStr">
@@ -31288,17 +31300,17 @@
       </c>
       <c r="B885" s="7" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>16674</t>
         </is>
       </c>
       <c r="C885" s="7" t="inlineStr">
         <is>
-          <t>11176700</t>
+          <t>11176704</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
         <is>
-          <t>Sp26Tz14GlassC</t>
+          <t>Sp26CC16Prism</t>
         </is>
       </c>
       <c r="E885" t="inlineStr">
@@ -31323,17 +31335,17 @@
       </c>
       <c r="B886" s="7" t="inlineStr">
         <is>
-          <t>16671</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="C886" s="7" t="inlineStr">
         <is>
-          <t>11176717</t>
+          <t>11176722</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
         <is>
-          <t>Sp26SS12Pink</t>
+          <t>Sp26SSCC24Cherry</t>
         </is>
       </c>
       <c r="E886" t="inlineStr">
@@ -31358,17 +31370,17 @@
       </c>
       <c r="B887" s="7" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="C887" s="7" t="inlineStr">
         <is>
-          <t>11176724</t>
+          <t>11176718</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>Sp26CookieJP</t>
+          <t>Sp26SS16Cherry</t>
         </is>
       </c>
       <c r="E887" t="inlineStr">
@@ -31393,17 +31405,17 @@
       </c>
       <c r="B888" s="7" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>16677</t>
         </is>
       </c>
       <c r="C888" s="7" t="inlineStr">
         <is>
-          <t>11176703</t>
+          <t>11176723</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>Sp26Tu16Cherry</t>
+          <t>Sp26SSVac40Cherr</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
@@ -31428,17 +31440,17 @@
       </c>
       <c r="B889" s="7" t="inlineStr">
         <is>
-          <t>16674</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="C889" s="7" t="inlineStr">
         <is>
-          <t>11176704</t>
+          <t>11176705</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>Sp26CC16Prism</t>
+          <t>Sp26ReusTierra</t>
         </is>
       </c>
       <c r="E889" t="inlineStr">
@@ -31463,17 +31475,17 @@
       </c>
       <c r="B890" s="7" t="inlineStr">
         <is>
-          <t>16675</t>
+          <t>16679</t>
         </is>
       </c>
       <c r="C890" s="7" t="inlineStr">
         <is>
-          <t>11176722</t>
+          <t>11176712</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>Sp26SSCC24Cherry</t>
+          <t>Sp26CCReusTierra</t>
         </is>
       </c>
       <c r="E890" t="inlineStr">
@@ -31498,17 +31510,17 @@
       </c>
       <c r="B891" s="7" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="C891" s="7" t="inlineStr">
         <is>
-          <t>11176718</t>
+          <t>11177607</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
         <is>
-          <t>Sp26SS16Cherry</t>
+          <t>Wt26ReusSiren</t>
         </is>
       </c>
       <c r="E891" t="inlineStr">
@@ -31533,17 +31545,17 @@
       </c>
       <c r="B892" s="7" t="inlineStr">
         <is>
-          <t>16677</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="C892" s="7" t="inlineStr">
         <is>
-          <t>11176723</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
         <is>
-          <t>Sp26SSVac40Cherr</t>
+          <t>Sp26SS16Under</t>
         </is>
       </c>
       <c r="E892" t="inlineStr">
@@ -31568,17 +31580,13 @@
       </c>
       <c r="B893" s="7" t="inlineStr">
         <is>
-          <t>16678</t>
-        </is>
-      </c>
-      <c r="C893" s="7" t="inlineStr">
-        <is>
-          <t>11176705</t>
-        </is>
-      </c>
+          <t>16722</t>
+        </is>
+      </c>
+      <c r="C893" s="7" t="inlineStr"/>
       <c r="D893" t="inlineStr">
         <is>
-          <t>Sp26ReusTierra</t>
+          <t>BearHuggerSpring</t>
         </is>
       </c>
       <c r="E893" t="inlineStr">
@@ -31603,17 +31611,17 @@
       </c>
       <c r="B894" s="7" t="inlineStr">
         <is>
-          <t>16679</t>
+          <t>16729</t>
         </is>
       </c>
       <c r="C894" s="7" t="inlineStr">
         <is>
-          <t>11176712</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>Sp26CCReusTierra</t>
+          <t>Wt26ReusBear</t>
         </is>
       </c>
       <c r="E894" t="inlineStr">
@@ -31638,17 +31646,17 @@
       </c>
       <c r="B895" s="7" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="C895" s="7" t="inlineStr">
         <is>
-          <t>11177607</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>Wt26ReusSiren</t>
+          <t>Wt26VasoPistache</t>
         </is>
       </c>
       <c r="E895" t="inlineStr">
@@ -31673,7 +31681,7 @@
       </c>
       <c r="B896" s="7" t="inlineStr">
         <is>
-          <t>16721</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="C896" s="7" t="inlineStr">
@@ -31683,7 +31691,7 @@
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>Sp26SS16Under</t>
+          <t>Wt26VasoFresa</t>
         </is>
       </c>
       <c r="E896" t="inlineStr">
@@ -31708,13 +31716,17 @@
       </c>
       <c r="B897" s="7" t="inlineStr">
         <is>
-          <t>16722</t>
-        </is>
-      </c>
-      <c r="C897" s="7" t="inlineStr"/>
+          <t>16771</t>
+        </is>
+      </c>
+      <c r="C897" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>BearHuggerSpring</t>
+          <t>Wt26VasoJacaran</t>
         </is>
       </c>
       <c r="E897" t="inlineStr">
@@ -31739,7 +31751,7 @@
       </c>
       <c r="B898" s="7" t="inlineStr">
         <is>
-          <t>16729</t>
+          <t>16775</t>
         </is>
       </c>
       <c r="C898" s="7" t="inlineStr">
@@ -31749,7 +31761,7 @@
       </c>
       <c r="D898" t="inlineStr">
         <is>
-          <t>Wt26ReusBear</t>
+          <t>Wt26LlaveroSV</t>
         </is>
       </c>
       <c r="E898" t="inlineStr">
@@ -31774,17 +31786,17 @@
       </c>
       <c r="B899" s="7" t="inlineStr">
         <is>
-          <t>16769</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="C899" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11179885</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>Wt26VasoPistache</t>
+          <t>SII26BTL20Resort</t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
@@ -31809,17 +31821,17 @@
       </c>
       <c r="B900" s="7" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>16779</t>
         </is>
       </c>
       <c r="C900" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11176592</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>Wt26VasoFresa</t>
+          <t>SII26SSTu12Pony</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
@@ -31844,7 +31856,7 @@
       </c>
       <c r="B901" s="7" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="C901" s="7" t="inlineStr">
@@ -31854,7 +31866,7 @@
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>Wt26VasoJacaran</t>
+          <t>Sp26WTBL19Under</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
@@ -31879,7 +31891,7 @@
       </c>
       <c r="B902" s="7" t="inlineStr">
         <is>
-          <t>16775</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="C902" s="7" t="inlineStr">
@@ -31889,7 +31901,7 @@
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>Wt26LlaveroSV</t>
+          <t>Sp26Tu20Blossom</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
@@ -31914,17 +31926,17 @@
       </c>
       <c r="B903" s="7" t="inlineStr">
         <is>
-          <t>16777</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="C903" s="7" t="inlineStr">
         <is>
-          <t>11179885</t>
+          <t>11176597</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>SII26BTL20Resort</t>
+          <t>SII26BearPony</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
@@ -31949,17 +31961,17 @@
       </c>
       <c r="B904" s="7" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="C904" s="7" t="inlineStr">
         <is>
-          <t>11176592</t>
+          <t>1176593</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>SII26SSTu12Pony</t>
+          <t>SII26BTL16Pony</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
@@ -31984,17 +31996,13 @@
       </c>
       <c r="B905" s="7" t="inlineStr">
         <is>
-          <t>16780</t>
-        </is>
-      </c>
-      <c r="C905" s="7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>16828</t>
+        </is>
+      </c>
+      <c r="C905" s="7" t="inlineStr"/>
       <c r="D905" t="inlineStr">
         <is>
-          <t>Sp26WTBL19Under</t>
+          <t>BearHugWorldCup</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
@@ -32019,17 +32027,17 @@
       </c>
       <c r="B906" s="7" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="C906" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178953</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>Sp26Tu20Blossom</t>
+          <t>Sp26SSCC24Oran</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
@@ -32054,17 +32062,17 @@
       </c>
       <c r="B907" s="7" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16878</t>
         </is>
       </c>
       <c r="C907" s="7" t="inlineStr">
         <is>
-          <t>11176597</t>
+          <t>11178921</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>SII26BearPony</t>
+          <t>Sp26Tu16Orange</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
@@ -32089,17 +32097,17 @@
       </c>
       <c r="B908" s="7" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="C908" s="7" t="inlineStr">
         <is>
-          <t>1176593</t>
+          <t>11178964</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>SII26BTL16Pony</t>
+          <t>Sp26KeychainOr</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
@@ -32124,13 +32132,17 @@
       </c>
       <c r="B909" s="7" t="inlineStr">
         <is>
-          <t>16828</t>
-        </is>
-      </c>
-      <c r="C909" s="7" t="inlineStr"/>
+          <t>16885</t>
+        </is>
+      </c>
+      <c r="C909" s="7" t="inlineStr">
+        <is>
+          <t>11179003</t>
+        </is>
+      </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>BearHugWorldCup</t>
+          <t>Sp26CC24Teach</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
@@ -32155,17 +32167,17 @@
       </c>
       <c r="B910" s="7" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="C910" s="7" t="inlineStr">
         <is>
-          <t>11178953</t>
+          <t>11179004</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>Sp26SSCC24Oran</t>
+          <t>Sp26Tu16Teach</t>
         </is>
       </c>
       <c r="E910" t="inlineStr">
@@ -32190,17 +32202,17 @@
       </c>
       <c r="B911" s="7" t="inlineStr">
         <is>
-          <t>16877</t>
+          <t>16902</t>
         </is>
       </c>
       <c r="C911" s="7" t="inlineStr">
         <is>
-          <t>11178954</t>
+          <t>11178920</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>Sp26SSCC24CarryC</t>
+          <t>WC26Tu20Yellow</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
@@ -32225,17 +32237,17 @@
       </c>
       <c r="B912" s="7" t="inlineStr">
         <is>
-          <t>16878</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="C912" s="7" t="inlineStr">
         <is>
-          <t>11178921</t>
+          <t>11178926</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>Sp26Tu16Orange</t>
+          <t>Sp26CC24Or</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
@@ -32260,17 +32272,17 @@
       </c>
       <c r="B913" s="7" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="C913" s="7" t="inlineStr">
         <is>
-          <t>11178964</t>
+          <t>11178965</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>Sp26KeychainOr</t>
+          <t>WC26ToteRoad</t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
@@ -32295,17 +32307,17 @@
       </c>
       <c r="B914" s="7" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="C914" s="7" t="inlineStr">
         <is>
-          <t>11179003</t>
+          <t>11178966</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>Sp26CC24Teach</t>
+          <t>WC26TotePride</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
@@ -32330,17 +32342,17 @@
       </c>
       <c r="B915" s="7" t="inlineStr">
         <is>
-          <t>16899</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="C915" s="7" t="inlineStr">
         <is>
-          <t>11179004</t>
+          <t>11187369</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>Sp26Tu16Teach</t>
+          <t>WC26BearWC</t>
         </is>
       </c>
       <c r="E915" t="inlineStr">
@@ -32365,17 +32377,17 @@
       </c>
       <c r="B916" s="7" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>16909</t>
         </is>
       </c>
       <c r="C916" s="7" t="inlineStr">
         <is>
-          <t>11178920</t>
+          <t>11178944</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>WC26Tu20Yellow</t>
+          <t>WC26SS20BTL</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
@@ -32400,17 +32412,17 @@
       </c>
       <c r="B917" s="7" t="inlineStr">
         <is>
-          <t>16903</t>
+          <t>16912</t>
         </is>
       </c>
       <c r="C917" s="7" t="inlineStr">
         <is>
-          <t>11178926</t>
+          <t>11178949</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>Sp26CC24Or</t>
+          <t>WC26SS20Pull</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
@@ -32435,17 +32447,17 @@
       </c>
       <c r="B918" s="7" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>16914</t>
         </is>
       </c>
       <c r="C918" s="7" t="inlineStr">
         <is>
-          <t>11178965</t>
+          <t>11178947</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>WC26ToteRoad</t>
+          <t>Sp26StanQuen20</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
@@ -32470,17 +32482,17 @@
       </c>
       <c r="B919" s="7" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="C919" s="7" t="inlineStr">
         <is>
-          <t>11178966</t>
+          <t>11178972</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>WC26TotePride</t>
+          <t>Sp26Vac16Stan</t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
@@ -32505,17 +32517,17 @@
       </c>
       <c r="B920" s="7" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="C920" s="7" t="inlineStr">
         <is>
-          <t>11187369</t>
+          <t>11178917</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>WC26BearWC</t>
+          <t>WC26DW12Oran</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
@@ -32540,17 +32552,17 @@
       </c>
       <c r="B921" s="7" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="C921" s="7" t="inlineStr">
         <is>
-          <t>11178944</t>
+          <t>11187370</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>WC26SS20BTL</t>
+          <t>WC26SS16Black</t>
         </is>
       </c>
       <c r="E921" t="inlineStr">
@@ -32575,17 +32587,13 @@
       </c>
       <c r="B922" s="7" t="inlineStr">
         <is>
-          <t>16912</t>
-        </is>
-      </c>
-      <c r="C922" s="7" t="inlineStr">
-        <is>
-          <t>11178949</t>
-        </is>
-      </c>
+          <t>16971</t>
+        </is>
+      </c>
+      <c r="C922" s="7" t="inlineStr"/>
       <c r="D922" t="inlineStr">
         <is>
-          <t>WC26SS20Pull</t>
+          <t>WC26BearMex</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
@@ -32610,17 +32618,17 @@
       </c>
       <c r="B923" s="7" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>16978</t>
         </is>
       </c>
       <c r="C923" s="7" t="inlineStr">
         <is>
-          <t>11178947</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>Sp26StanQuen20</t>
+          <t>WC26LlaveroB</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
@@ -32645,17 +32653,13 @@
       </c>
       <c r="B924" s="7" t="inlineStr">
         <is>
-          <t>16917</t>
-        </is>
-      </c>
-      <c r="C924" s="7" t="inlineStr">
-        <is>
-          <t>11178972</t>
-        </is>
-      </c>
+          <t>16989</t>
+        </is>
+      </c>
+      <c r="C924" s="7" t="inlineStr"/>
       <c r="D924" t="inlineStr">
         <is>
-          <t>Sp26Vac16Stan</t>
+          <t>SII26SS12Aniv</t>
         </is>
       </c>
       <c r="E924" t="inlineStr">
@@ -32680,17 +32684,13 @@
       </c>
       <c r="B925" s="7" t="inlineStr">
         <is>
-          <t>16921</t>
-        </is>
-      </c>
-      <c r="C925" s="7" t="inlineStr">
-        <is>
-          <t>11178917</t>
-        </is>
-      </c>
+          <t>17298</t>
+        </is>
+      </c>
+      <c r="C925" s="7" t="inlineStr"/>
       <c r="D925" t="inlineStr">
         <is>
-          <t>WC26DW12Oran</t>
+          <t>SII26SSBTL12Aniv</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
@@ -32715,17 +32715,13 @@
       </c>
       <c r="B926" s="7" t="inlineStr">
         <is>
-          <t>16958</t>
-        </is>
-      </c>
-      <c r="C926" s="7" t="inlineStr">
-        <is>
-          <t>11187370</t>
-        </is>
-      </c>
+          <t>17299</t>
+        </is>
+      </c>
+      <c r="C926" s="7" t="inlineStr"/>
       <c r="D926" t="inlineStr">
         <is>
-          <t>WC26SS16Black</t>
+          <t>SII26Mug14Aniv</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
@@ -32750,13 +32746,13 @@
       </c>
       <c r="B927" s="7" t="inlineStr">
         <is>
-          <t>16971</t>
+          <t>17307</t>
         </is>
       </c>
       <c r="C927" s="7" t="inlineStr"/>
       <c r="D927" t="inlineStr">
         <is>
-          <t>WC26BearMex</t>
+          <t>SII26Doodle16</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
@@ -32781,17 +32777,13 @@
       </c>
       <c r="B928" s="7" t="inlineStr">
         <is>
-          <t>16978</t>
-        </is>
-      </c>
-      <c r="C928" s="7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>52206</t>
+        </is>
+      </c>
+      <c r="C928" s="7" t="inlineStr"/>
       <c r="D928" t="inlineStr">
         <is>
-          <t>WC26LlaveroB</t>
+          <t>Vaso Rewards</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
@@ -32816,13 +32808,13 @@
       </c>
       <c r="B929" s="7" t="inlineStr">
         <is>
-          <t>16989</t>
+          <t>53500</t>
         </is>
       </c>
       <c r="C929" s="7" t="inlineStr"/>
       <c r="D929" t="inlineStr">
         <is>
-          <t>SII26SS12Aniv</t>
+          <t>ResSS16TGradient</t>
         </is>
       </c>
       <c r="E929" t="inlineStr">
@@ -32847,13 +32839,13 @@
       </c>
       <c r="B930" s="7" t="inlineStr">
         <is>
-          <t>17298</t>
+          <t>53834</t>
         </is>
       </c>
       <c r="C930" s="7" t="inlineStr"/>
       <c r="D930" t="inlineStr">
         <is>
-          <t>SII26SSBTL12Aniv</t>
+          <t>Tazas SBX Genérico</t>
         </is>
       </c>
       <c r="E930" t="inlineStr">
@@ -32878,13 +32870,13 @@
       </c>
       <c r="B931" s="7" t="inlineStr">
         <is>
-          <t>17299</t>
+          <t>53835</t>
         </is>
       </c>
       <c r="C931" s="7" t="inlineStr"/>
       <c r="D931" t="inlineStr">
         <is>
-          <t>SII26Mug14Aniv</t>
+          <t>CCupPlastic SBX Genérico</t>
         </is>
       </c>
       <c r="E931" t="inlineStr">
@@ -32909,13 +32901,13 @@
       </c>
       <c r="B932" s="7" t="inlineStr">
         <is>
-          <t>17307</t>
+          <t>53836</t>
         </is>
       </c>
       <c r="C932" s="7" t="inlineStr"/>
       <c r="D932" t="inlineStr">
         <is>
-          <t>SII26Doodle16</t>
+          <t>CCup Acero SBX Genérico</t>
         </is>
       </c>
       <c r="E932" t="inlineStr">
@@ -32940,13 +32932,13 @@
       </c>
       <c r="B933" s="7" t="inlineStr">
         <is>
-          <t>52206</t>
+          <t>53837</t>
         </is>
       </c>
       <c r="C933" s="7" t="inlineStr"/>
       <c r="D933" t="inlineStr">
         <is>
-          <t>Vaso Rewards</t>
+          <t>Tumb acero SBX Genérico</t>
         </is>
       </c>
       <c r="E933" t="inlineStr">
@@ -32971,13 +32963,13 @@
       </c>
       <c r="B934" s="7" t="inlineStr">
         <is>
-          <t>53500</t>
+          <t>53838</t>
         </is>
       </c>
       <c r="C934" s="7" t="inlineStr"/>
       <c r="D934" t="inlineStr">
         <is>
-          <t>ResSS16TGradient</t>
+          <t>Tumb Plastic SBX Genérico</t>
         </is>
       </c>
       <c r="E934" t="inlineStr">
@@ -33002,13 +32994,13 @@
       </c>
       <c r="B935" s="7" t="inlineStr">
         <is>
-          <t>53834</t>
+          <t>53839</t>
         </is>
       </c>
       <c r="C935" s="7" t="inlineStr"/>
       <c r="D935" t="inlineStr">
         <is>
-          <t>Tazas SBX Genérico</t>
+          <t>Stanley SBX Genérico</t>
         </is>
       </c>
       <c r="E935" t="inlineStr">
@@ -33033,13 +33025,13 @@
       </c>
       <c r="B936" s="7" t="inlineStr">
         <is>
-          <t>53835</t>
+          <t>53840</t>
         </is>
       </c>
       <c r="C936" s="7" t="inlineStr"/>
       <c r="D936" t="inlineStr">
         <is>
-          <t>CCupPlastic SBX Genérico</t>
+          <t>Llavero SBX Genérico</t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
@@ -33064,13 +33056,13 @@
       </c>
       <c r="B937" s="7" t="inlineStr">
         <is>
-          <t>53836</t>
+          <t>53841</t>
         </is>
       </c>
       <c r="C937" s="7" t="inlineStr"/>
       <c r="D937" t="inlineStr">
         <is>
-          <t>CCup Acero SBX Genérico</t>
+          <t>Stoppers SBX Genérico</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
@@ -33095,13 +33087,13 @@
       </c>
       <c r="B938" s="7" t="inlineStr">
         <is>
-          <t>53837</t>
+          <t>53842</t>
         </is>
       </c>
       <c r="C938" s="7" t="inlineStr"/>
       <c r="D938" t="inlineStr">
         <is>
-          <t>Tumb acero SBX Genérico</t>
+          <t>Tote bags SBX Genérico</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
@@ -33126,13 +33118,13 @@
       </c>
       <c r="B939" s="7" t="inlineStr">
         <is>
-          <t>53838</t>
+          <t>53843</t>
         </is>
       </c>
       <c r="C939" s="7" t="inlineStr"/>
       <c r="D939" t="inlineStr">
         <is>
-          <t>Tumb Plastic SBX Genérico</t>
+          <t>Pines SBX Genérico</t>
         </is>
       </c>
       <c r="E939" t="inlineStr">
@@ -33157,13 +33149,13 @@
       </c>
       <c r="B940" s="7" t="inlineStr">
         <is>
-          <t>53839</t>
+          <t>53844</t>
         </is>
       </c>
       <c r="C940" s="7" t="inlineStr"/>
       <c r="D940" t="inlineStr">
         <is>
-          <t>Stanley SBX Genérico</t>
+          <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
       <c r="E940" t="inlineStr">
@@ -33188,13 +33180,13 @@
       </c>
       <c r="B941" s="7" t="inlineStr">
         <is>
-          <t>53840</t>
+          <t>53845</t>
         </is>
       </c>
       <c r="C941" s="7" t="inlineStr"/>
       <c r="D941" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
+          <t>Set Reusa SBX Genérico</t>
         </is>
       </c>
       <c r="E941" t="inlineStr">
@@ -33219,13 +33211,13 @@
       </c>
       <c r="B942" s="7" t="inlineStr">
         <is>
-          <t>53841</t>
+          <t>53949</t>
         </is>
       </c>
       <c r="C942" s="7" t="inlineStr"/>
       <c r="D942" t="inlineStr">
         <is>
-          <t>Stoppers SBX Genérico</t>
+          <t>Xm25Tu12Hol</t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
@@ -33250,13 +33242,13 @@
       </c>
       <c r="B943" s="7" t="inlineStr">
         <is>
-          <t>53842</t>
+          <t>53951</t>
         </is>
       </c>
       <c r="C943" s="7" t="inlineStr"/>
       <c r="D943" t="inlineStr">
         <is>
-          <t>Tote bags SBX Genérico</t>
+          <t>Xm25StopDermo</t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
@@ -33281,13 +33273,13 @@
       </c>
       <c r="B944" s="7" t="inlineStr">
         <is>
-          <t>53843</t>
+          <t>53952</t>
         </is>
       </c>
       <c r="C944" s="7" t="inlineStr"/>
       <c r="D944" t="inlineStr">
         <is>
-          <t>Pines SBX Genérico</t>
+          <t>Xm25StopMike</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
@@ -33312,13 +33304,13 @@
       </c>
       <c r="B945" s="7" t="inlineStr">
         <is>
-          <t>53844</t>
+          <t>53953</t>
         </is>
       </c>
       <c r="C945" s="7" t="inlineStr"/>
       <c r="D945" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
+          <t>Xm25StopDust</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
@@ -33343,13 +33335,13 @@
       </c>
       <c r="B946" s="7" t="inlineStr">
         <is>
-          <t>53845</t>
+          <t>53958</t>
         </is>
       </c>
       <c r="C946" s="7" t="inlineStr"/>
       <c r="D946" t="inlineStr">
         <is>
-          <t>Set Reusa SBX Genérico</t>
+          <t>Xm25Reu1Hol</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
@@ -33374,13 +33366,13 @@
       </c>
       <c r="B947" s="7" t="inlineStr">
         <is>
-          <t>53949</t>
+          <t>53959</t>
         </is>
       </c>
       <c r="C947" s="7" t="inlineStr"/>
       <c r="D947" t="inlineStr">
         <is>
-          <t>Xm25Tu12Hol</t>
+          <t>Xm25Reu2Hol</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
@@ -33405,13 +33397,13 @@
       </c>
       <c r="B948" s="7" t="inlineStr">
         <is>
-          <t>53951</t>
+          <t>53962</t>
         </is>
       </c>
       <c r="C948" s="7" t="inlineStr"/>
       <c r="D948" t="inlineStr">
         <is>
-          <t>Xm25StopDermo</t>
+          <t>Xm25Tag</t>
         </is>
       </c>
       <c r="E948" t="inlineStr">
@@ -33436,13 +33428,13 @@
       </c>
       <c r="B949" s="7" t="inlineStr">
         <is>
-          <t>53952</t>
+          <t>53965</t>
         </is>
       </c>
       <c r="C949" s="7" t="inlineStr"/>
       <c r="D949" t="inlineStr">
         <is>
-          <t>Xm25StopMike</t>
+          <t>Xm25StopWill</t>
         </is>
       </c>
       <c r="E949" t="inlineStr">
@@ -33467,13 +33459,13 @@
       </c>
       <c r="B950" s="7" t="inlineStr">
         <is>
-          <t>53953</t>
+          <t>53966</t>
         </is>
       </c>
       <c r="C950" s="7" t="inlineStr"/>
       <c r="D950" t="inlineStr">
         <is>
-          <t>Xm25StopDust</t>
+          <t>Xm25StopMax</t>
         </is>
       </c>
       <c r="E950" t="inlineStr">
@@ -33498,13 +33490,13 @@
       </c>
       <c r="B951" s="7" t="inlineStr">
         <is>
-          <t>53958</t>
+          <t>53967</t>
         </is>
       </c>
       <c r="C951" s="7" t="inlineStr"/>
       <c r="D951" t="inlineStr">
         <is>
-          <t>Xm25Reu1Hol</t>
+          <t>Xm25StopHopp</t>
         </is>
       </c>
       <c r="E951" t="inlineStr">
@@ -33529,13 +33521,13 @@
       </c>
       <c r="B952" s="7" t="inlineStr">
         <is>
-          <t>53959</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="C952" s="7" t="inlineStr"/>
       <c r="D952" t="inlineStr">
         <is>
-          <t>Xm25Reu2Hol</t>
+          <t>Sp26BlindBox</t>
         </is>
       </c>
       <c r="E952" t="inlineStr">
@@ -33560,13 +33552,13 @@
       </c>
       <c r="B953" s="7" t="inlineStr">
         <is>
-          <t>53962</t>
+          <t>54192</t>
         </is>
       </c>
       <c r="C953" s="7" t="inlineStr"/>
       <c r="D953" t="inlineStr">
         <is>
-          <t>Xm25Tag</t>
+          <t>SII26GICCColor</t>
         </is>
       </c>
       <c r="E953" t="inlineStr">
@@ -33591,13 +33583,13 @@
       </c>
       <c r="B954" s="7" t="inlineStr">
         <is>
-          <t>53965</t>
+          <t>54201</t>
         </is>
       </c>
       <c r="C954" s="7" t="inlineStr"/>
       <c r="D954" t="inlineStr">
         <is>
-          <t>Xm25StopWill</t>
+          <t>SII26CC24Rain</t>
         </is>
       </c>
       <c r="E954" t="inlineStr">
@@ -33622,13 +33614,13 @@
       </c>
       <c r="B955" s="7" t="inlineStr">
         <is>
-          <t>53966</t>
+          <t>54213</t>
         </is>
       </c>
       <c r="C955" s="7" t="inlineStr"/>
       <c r="D955" t="inlineStr">
         <is>
-          <t>Xm25StopMax</t>
+          <t>WC26Reus</t>
         </is>
       </c>
       <c r="E955" t="inlineStr">
@@ -33648,18 +33640,18 @@
     <row r="956" ht="24" customHeight="1">
       <c r="A956" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B956" s="7" t="inlineStr">
         <is>
-          <t>53967</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="C956" s="7" t="inlineStr"/>
       <c r="D956" t="inlineStr">
         <is>
-          <t>Xm25StopHopp</t>
+          <t>ESS Reusable cup</t>
         </is>
       </c>
       <c r="E956" t="inlineStr">
@@ -33672,25 +33664,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G956" t="inlineStr"/>
-      <c r="H956" t="inlineStr"/>
-      <c r="I956" t="inlineStr"/>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>lote-01/11372.jpeg</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="957" ht="24" customHeight="1">
       <c r="A957" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B957" s="7" t="inlineStr">
         <is>
-          <t>54112</t>
-        </is>
-      </c>
-      <c r="C957" s="7" t="inlineStr"/>
+          <t>14885</t>
+        </is>
+      </c>
+      <c r="C957" s="7" t="inlineStr">
+        <is>
+          <t>11141050</t>
+        </is>
+      </c>
       <c r="D957" t="inlineStr">
         <is>
-          <t>Sp26BlindBox</t>
+          <t>COR23 Tz14 Rain</t>
         </is>
       </c>
       <c r="E957" t="inlineStr">
@@ -33703,25 +33711,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G957" t="inlineStr"/>
-      <c r="H957" t="inlineStr"/>
-      <c r="I957" t="inlineStr"/>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>lote-01/14885.jpeg</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="958" ht="24" customHeight="1">
       <c r="A958" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B958" s="7" t="inlineStr">
         <is>
-          <t>54192</t>
-        </is>
-      </c>
-      <c r="C958" s="7" t="inlineStr"/>
+          <t>14927</t>
+        </is>
+      </c>
+      <c r="C958" s="7" t="inlineStr">
+        <is>
+          <t>11141041</t>
+        </is>
+      </c>
       <c r="D958" t="inlineStr">
         <is>
-          <t>SII26GICCColor</t>
+          <t>COR23 Pour Over</t>
         </is>
       </c>
       <c r="E958" t="inlineStr">
@@ -33734,25 +33758,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G958" t="inlineStr"/>
-      <c r="H958" t="inlineStr"/>
-      <c r="I958" t="inlineStr"/>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>lote-01/14927.jpeg</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="959" ht="24" customHeight="1">
       <c r="A959" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B959" s="7" t="inlineStr">
         <is>
-          <t>54201</t>
-        </is>
-      </c>
-      <c r="C959" s="7" t="inlineStr"/>
+          <t>14928</t>
+        </is>
+      </c>
+      <c r="C959" s="7" t="inlineStr">
+        <is>
+          <t>11141095</t>
+        </is>
+      </c>
       <c r="D959" t="inlineStr">
         <is>
-          <t>SII26CC24Rain</t>
+          <t>COR23 Cold Brew</t>
         </is>
       </c>
       <c r="E959" t="inlineStr">
@@ -33765,25 +33805,41 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G959" t="inlineStr"/>
-      <c r="H959" t="inlineStr"/>
-      <c r="I959" t="inlineStr"/>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>lote-01/14928.jpeg</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="960" ht="24" customHeight="1">
       <c r="A960" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B960" s="7" t="inlineStr">
         <is>
-          <t>54213</t>
-        </is>
-      </c>
-      <c r="C960" s="7" t="inlineStr"/>
+          <t>16312</t>
+        </is>
+      </c>
+      <c r="C960" s="7" t="inlineStr">
+        <is>
+          <t>11160995</t>
+        </is>
+      </c>
       <c r="D960" t="inlineStr">
         <is>
-          <t>WC26Reus</t>
+          <t>COR26BTL20</t>
         </is>
       </c>
       <c r="E960" t="inlineStr">
@@ -33796,9 +33852,21 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G960" t="inlineStr"/>
-      <c r="H960" t="inlineStr"/>
-      <c r="I960" t="inlineStr"/>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>lote-01/16312.jpeg</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="961" ht="24" customHeight="1">
       <c r="A961" t="inlineStr">
@@ -33808,13 +33876,17 @@
       </c>
       <c r="B961" s="7" t="inlineStr">
         <is>
-          <t>11372</t>
-        </is>
-      </c>
-      <c r="C961" s="7" t="inlineStr"/>
+          <t>16531</t>
+        </is>
+      </c>
+      <c r="C961" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="D961" t="inlineStr">
         <is>
-          <t>ESS Reusable cup</t>
+          <t>Sp26NEBlack</t>
         </is>
       </c>
       <c r="E961" t="inlineStr">
@@ -33829,7 +33901,7 @@
       </c>
       <c r="G961" t="inlineStr">
         <is>
-          <t>lote-01/11372.jpeg</t>
+          <t>lote-01/16531.jpeg</t>
         </is>
       </c>
       <c r="H961" t="inlineStr">
@@ -33851,17 +33923,17 @@
       </c>
       <c r="B962" s="7" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="C962" s="7" t="inlineStr">
         <is>
-          <t>11160995</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
         <is>
-          <t>COR26BTL20</t>
+          <t>Sp26NECrossB</t>
         </is>
       </c>
       <c r="E962" t="inlineStr">
@@ -33876,7 +33948,7 @@
       </c>
       <c r="G962" t="inlineStr">
         <is>
-          <t>lote-01/16312.jpeg</t>
+          <t>lote-01/16532.jpeg</t>
         </is>
       </c>
       <c r="H962" t="inlineStr">
@@ -33898,17 +33970,17 @@
       </c>
       <c r="B963" s="7" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="C963" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11174776</t>
         </is>
       </c>
       <c r="D963" t="inlineStr">
         <is>
-          <t>Sp26NEBlack</t>
+          <t>Wt26Mug14Bow</t>
         </is>
       </c>
       <c r="E963" t="inlineStr">
@@ -33923,7 +33995,7 @@
       </c>
       <c r="G963" t="inlineStr">
         <is>
-          <t>lote-01/16531.jpeg</t>
+          <t>lote-01/16550.jpeg</t>
         </is>
       </c>
       <c r="H963" t="inlineStr">
@@ -33945,17 +34017,17 @@
       </c>
       <c r="B964" s="7" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="C964" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11170187</t>
         </is>
       </c>
       <c r="D964" t="inlineStr">
         <is>
-          <t>Sp26NECrossB</t>
+          <t>ToteBag MxPais</t>
         </is>
       </c>
       <c r="E964" t="inlineStr">
@@ -33970,7 +34042,7 @@
       </c>
       <c r="G964" t="inlineStr">
         <is>
-          <t>lote-01/16532.jpeg</t>
+          <t>lote-01/011170187.jpeg</t>
         </is>
       </c>
       <c r="H964" t="inlineStr">
@@ -33980,7 +34052,7 @@
       </c>
       <c r="I964" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -33992,17 +34064,17 @@
       </c>
       <c r="B965" s="7" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="C965" s="7" t="inlineStr">
         <is>
-          <t>11170187</t>
+          <t>11170102</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
         <is>
-          <t>ToteBag MxPais</t>
+          <t>DiscoveryCDMX</t>
         </is>
       </c>
       <c r="E965" t="inlineStr">
@@ -34017,7 +34089,7 @@
       </c>
       <c r="G965" t="inlineStr">
         <is>
-          <t>lote-01/011170187.jpeg</t>
+          <t>lote-01/011170102.jpeg</t>
         </is>
       </c>
       <c r="H965" t="inlineStr">
@@ -34039,17 +34111,17 @@
       </c>
       <c r="B966" s="7" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="C966" s="7" t="inlineStr">
         <is>
-          <t>11170102</t>
+          <t>11176710</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>DiscoveryCDMX</t>
+          <t>Sp26CC24Dome</t>
         </is>
       </c>
       <c r="E966" t="inlineStr">
@@ -34064,7 +34136,7 @@
       </c>
       <c r="G966" t="inlineStr">
         <is>
-          <t>lote-01/011170102.jpeg</t>
+          <t>lote-01/011176710.jpeg</t>
         </is>
       </c>
       <c r="H966" t="inlineStr">
@@ -34086,17 +34158,17 @@
       </c>
       <c r="B967" s="7" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="C967" s="7" t="inlineStr">
         <is>
-          <t>11176710</t>
+          <t>11170174</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
         <is>
-          <t>Sp26CC24Dome</t>
+          <t>DiscCC24MxPais</t>
         </is>
       </c>
       <c r="E967" t="inlineStr">
@@ -34111,7 +34183,7 @@
       </c>
       <c r="G967" t="inlineStr">
         <is>
-          <t>lote-01/011176710.jpeg</t>
+          <t>lote-01/011170174.jpeg</t>
         </is>
       </c>
       <c r="H967" t="inlineStr">
@@ -34133,17 +34205,17 @@
       </c>
       <c r="B968" s="7" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="C968" s="7" t="inlineStr">
         <is>
-          <t>11170174</t>
+          <t>11170158</t>
         </is>
       </c>
       <c r="D968" t="inlineStr">
         <is>
-          <t>DiscCC24MxPais</t>
+          <t>Disc2ozChiapas</t>
         </is>
       </c>
       <c r="E968" t="inlineStr">
@@ -34158,7 +34230,7 @@
       </c>
       <c r="G968" t="inlineStr">
         <is>
-          <t>lote-01/011170174.jpeg</t>
+          <t>lote-01/011170158.jpeg</t>
         </is>
       </c>
       <c r="H968" t="inlineStr">
@@ -34180,17 +34252,17 @@
       </c>
       <c r="B969" s="7" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="C969" s="7" t="inlineStr">
         <is>
-          <t>11170158</t>
+          <t>11170147</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
         <is>
-          <t>Disc2ozChiapas</t>
+          <t>Disc2ozMxPais</t>
         </is>
       </c>
       <c r="E969" t="inlineStr">
@@ -34205,7 +34277,7 @@
       </c>
       <c r="G969" t="inlineStr">
         <is>
-          <t>lote-01/011170158.jpeg</t>
+          <t>lote-01/011170147.jpeg</t>
         </is>
       </c>
       <c r="H969" t="inlineStr">
@@ -34227,17 +34299,17 @@
       </c>
       <c r="B970" s="7" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="C970" s="7" t="inlineStr">
         <is>
-          <t>11170147</t>
+          <t>11170149</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
         <is>
-          <t>Disc2ozMxPais</t>
+          <t>Disc2ozCDMX</t>
         </is>
       </c>
       <c r="E970" t="inlineStr">
@@ -34252,7 +34324,7 @@
       </c>
       <c r="G970" t="inlineStr">
         <is>
-          <t>lote-01/011170147.jpeg</t>
+          <t>lote-01/011170149.jpeg</t>
         </is>
       </c>
       <c r="H970" t="inlineStr">
@@ -34274,17 +34346,17 @@
       </c>
       <c r="B971" s="7" t="inlineStr">
         <is>
-          <t>16689</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="C971" s="7" t="inlineStr">
         <is>
-          <t>11170149</t>
+          <t>11176586</t>
         </is>
       </c>
       <c r="D971" t="inlineStr">
         <is>
-          <t>Disc2ozCDMX</t>
+          <t>SII26SSCC20Pony</t>
         </is>
       </c>
       <c r="E971" t="inlineStr">
@@ -34299,7 +34371,7 @@
       </c>
       <c r="G971" t="inlineStr">
         <is>
-          <t>lote-01/011170149.jpeg</t>
+          <t>lote-01/16719.jpeg</t>
         </is>
       </c>
       <c r="H971" t="inlineStr">
@@ -34309,7 +34381,7 @@
       </c>
       <c r="I971" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -34321,17 +34393,17 @@
       </c>
       <c r="B972" s="7" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>16720</t>
         </is>
       </c>
       <c r="C972" s="7" t="inlineStr">
         <is>
-          <t>11176586</t>
+          <t>11176587</t>
         </is>
       </c>
       <c r="D972" t="inlineStr">
         <is>
-          <t>SII26SSCC20Pony</t>
+          <t>SII26SSCC16Pony</t>
         </is>
       </c>
       <c r="E972" t="inlineStr">
@@ -34346,7 +34418,7 @@
       </c>
       <c r="G972" t="inlineStr">
         <is>
-          <t>lote-01/16719.jpeg</t>
+          <t>lote-01/16720.jpeg</t>
         </is>
       </c>
       <c r="H972" t="inlineStr">
@@ -34368,17 +34440,17 @@
       </c>
       <c r="B973" s="7" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="C973" s="7" t="inlineStr">
         <is>
-          <t>11176587</t>
+          <t>11178952</t>
         </is>
       </c>
       <c r="D973" t="inlineStr">
         <is>
-          <t>SII26SSCC16Pony</t>
+          <t>WC26SSCC24Grad</t>
         </is>
       </c>
       <c r="E973" t="inlineStr">
@@ -34393,7 +34465,7 @@
       </c>
       <c r="G973" t="inlineStr">
         <is>
-          <t>lote-01/16720.jpeg</t>
+          <t>lote-01/011178952.jpeg</t>
         </is>
       </c>
       <c r="H973" t="inlineStr">
@@ -34403,7 +34475,7 @@
       </c>
       <c r="I973" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -34415,17 +34487,17 @@
       </c>
       <c r="B974" s="7" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="C974" s="7" t="inlineStr">
         <is>
-          <t>11178952</t>
+          <t>11178954</t>
         </is>
       </c>
       <c r="D974" t="inlineStr">
         <is>
-          <t>WC26SSCC24Grad</t>
+          <t>Sp26SSCC24CarryC</t>
         </is>
       </c>
       <c r="E974" t="inlineStr">
@@ -34440,7 +34512,7 @@
       </c>
       <c r="G974" t="inlineStr">
         <is>
-          <t>lote-01/011178952.jpeg</t>
+          <t>lote-01/16877.jpeg</t>
         </is>
       </c>
       <c r="H974" t="inlineStr">
@@ -34450,7 +34522,7 @@
       </c>
       <c r="I974" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -28162,7 +28162,7 @@
       </c>
       <c r="B795" s="7" t="inlineStr">
         <is>
-          <t>16378</t>
+          <t>16416</t>
         </is>
       </c>
       <c r="C795" s="7" t="inlineStr">
@@ -28172,7 +28172,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>COR25CircCup</t>
+          <t>Fl25ReusCCBa</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
@@ -28197,7 +28197,7 @@
       </c>
       <c r="B796" s="7" t="inlineStr">
         <is>
-          <t>16416</t>
+          <t>16417</t>
         </is>
       </c>
       <c r="C796" s="7" t="inlineStr">
@@ -28207,7 +28207,7 @@
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>Fl25ReusCCBa</t>
+          <t>Fl25ReusBar</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
@@ -28232,17 +28232,17 @@
       </c>
       <c r="B797" s="7" t="inlineStr">
         <is>
-          <t>16417</t>
+          <t>16433</t>
         </is>
       </c>
       <c r="C797" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11173273</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>Fl25ReusBar</t>
+          <t>Xm25Tu12Hol</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
@@ -28267,17 +28267,17 @@
       </c>
       <c r="B798" s="7" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="C798" s="7" t="inlineStr">
         <is>
-          <t>11173273</t>
+          <t>11173046</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>Xm25Tu12Hol</t>
+          <t>Xm25CCGlass18</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
@@ -28302,17 +28302,17 @@
       </c>
       <c r="B799" s="7" t="inlineStr">
         <is>
-          <t>16437</t>
+          <t>16438</t>
         </is>
       </c>
       <c r="C799" s="7" t="inlineStr">
         <is>
-          <t>11173046</t>
+          <t>11173047</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>Xm25CCGlass18</t>
+          <t>Xm25Tz14Glass</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
@@ -28337,17 +28337,17 @@
       </c>
       <c r="B800" s="7" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>16439</t>
         </is>
       </c>
       <c r="C800" s="7" t="inlineStr">
         <is>
-          <t>11173047</t>
+          <t>11172983</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>Xm25Tz14Glass</t>
+          <t>Xm25Mug12Stan</t>
         </is>
       </c>
       <c r="E800" t="inlineStr">
@@ -28372,17 +28372,17 @@
       </c>
       <c r="B801" s="7" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>16440</t>
         </is>
       </c>
       <c r="C801" s="7" t="inlineStr">
         <is>
-          <t>11172983</t>
+          <t>11172998</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>Xm25Mug12Stan</t>
+          <t>Xm25SSCC24Topp</t>
         </is>
       </c>
       <c r="E801" t="inlineStr">
@@ -28407,17 +28407,17 @@
       </c>
       <c r="B802" s="7" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>16441</t>
         </is>
       </c>
       <c r="C802" s="7" t="inlineStr">
         <is>
-          <t>11172998</t>
+          <t>11173000</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
         <is>
-          <t>Xm25SSCC24Topp</t>
+          <t>Xm25CC24House</t>
         </is>
       </c>
       <c r="E802" t="inlineStr">
@@ -28442,17 +28442,17 @@
       </c>
       <c r="B803" s="7" t="inlineStr">
         <is>
-          <t>16441</t>
+          <t>16442</t>
         </is>
       </c>
       <c r="C803" s="7" t="inlineStr">
         <is>
-          <t>11173000</t>
+          <t>11172996</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>Xm25CC24House</t>
+          <t>Xm25SSCC24R</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
@@ -28477,17 +28477,17 @@
       </c>
       <c r="B804" s="7" t="inlineStr">
         <is>
-          <t>16442</t>
+          <t>16443</t>
         </is>
       </c>
       <c r="C804" s="7" t="inlineStr">
         <is>
-          <t>11172996</t>
+          <t>11172994</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>Xm25SSCC24R</t>
+          <t>Xm25BTLStanley</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
@@ -28512,17 +28512,17 @@
       </c>
       <c r="B805" s="7" t="inlineStr">
         <is>
-          <t>16443</t>
+          <t>16444</t>
         </is>
       </c>
       <c r="C805" s="7" t="inlineStr">
         <is>
-          <t>11172994</t>
+          <t>11172855</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>Xm25BTLStanley</t>
+          <t>Xm25DW12Red</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
@@ -28547,17 +28547,17 @@
       </c>
       <c r="B806" s="7" t="inlineStr">
         <is>
-          <t>16444</t>
+          <t>16446</t>
         </is>
       </c>
       <c r="C806" s="7" t="inlineStr">
         <is>
-          <t>11172855</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>Xm25DW12Red</t>
+          <t>Fl25MonederoAniv</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
@@ -28582,17 +28582,17 @@
       </c>
       <c r="B807" s="7" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>16453</t>
         </is>
       </c>
       <c r="C807" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11172962</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>Fl25MonederoAniv</t>
+          <t>Xm25Tu16Charm</t>
         </is>
       </c>
       <c r="E807" t="inlineStr">
@@ -28617,17 +28617,13 @@
       </c>
       <c r="B808" s="7" t="inlineStr">
         <is>
-          <t>16453</t>
-        </is>
-      </c>
-      <c r="C808" s="7" t="inlineStr">
-        <is>
-          <t>11172962</t>
-        </is>
-      </c>
+          <t>16454</t>
+        </is>
+      </c>
+      <c r="C808" s="7" t="inlineStr"/>
       <c r="D808" t="inlineStr">
         <is>
-          <t>Xm25Tu16Charm</t>
+          <t>Xm25Give16CC</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
@@ -28652,13 +28648,17 @@
       </c>
       <c r="B809" s="7" t="inlineStr">
         <is>
-          <t>16454</t>
-        </is>
-      </c>
-      <c r="C809" s="7" t="inlineStr"/>
+          <t>16455</t>
+        </is>
+      </c>
+      <c r="C809" s="7" t="inlineStr">
+        <is>
+          <t>11172965</t>
+        </is>
+      </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>Xm25Give16CC</t>
+          <t>Xm25Tu16CPing</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
@@ -28683,17 +28683,17 @@
       </c>
       <c r="B810" s="7" t="inlineStr">
         <is>
-          <t>16455</t>
+          <t>16456</t>
         </is>
       </c>
       <c r="C810" s="7" t="inlineStr">
         <is>
-          <t>11172965</t>
+          <t>11172974</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>Xm25Tu16CPing</t>
+          <t>Xm25CC24Snow</t>
         </is>
       </c>
       <c r="E810" t="inlineStr">
@@ -28718,17 +28718,17 @@
       </c>
       <c r="B811" s="7" t="inlineStr">
         <is>
-          <t>16456</t>
+          <t>16457</t>
         </is>
       </c>
       <c r="C811" s="7" t="inlineStr">
         <is>
-          <t>11172974</t>
+          <t>11173031</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>Xm25CC24Snow</t>
+          <t>Xm25Llavero</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
@@ -28753,17 +28753,17 @@
       </c>
       <c r="B812" s="7" t="inlineStr">
         <is>
-          <t>16457</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="C812" s="7" t="inlineStr">
         <is>
-          <t>11173031</t>
+          <t>11172984</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>Xm25Llavero</t>
+          <t>Xm25SS16DIam</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
@@ -28788,17 +28788,17 @@
       </c>
       <c r="B813" s="7" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>16459</t>
         </is>
       </c>
       <c r="C813" s="7" t="inlineStr">
         <is>
-          <t>11172984</t>
+          <t>11172985</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>Xm25SS16DIam</t>
+          <t>Xm25SS16Green</t>
         </is>
       </c>
       <c r="E813" t="inlineStr">
@@ -28823,17 +28823,17 @@
       </c>
       <c r="B814" s="7" t="inlineStr">
         <is>
-          <t>16459</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="C814" s="7" t="inlineStr">
         <is>
-          <t>11172985</t>
+          <t>11172993</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>Xm25SS16Green</t>
+          <t>Xm25TuStan20</t>
         </is>
       </c>
       <c r="E814" t="inlineStr">
@@ -28858,17 +28858,17 @@
       </c>
       <c r="B815" s="7" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="C815" s="7" t="inlineStr">
         <is>
-          <t>11172993</t>
+          <t>11172997</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>Xm25TuStan20</t>
+          <t>Xm25RedQuen30</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
@@ -28893,17 +28893,17 @@
       </c>
       <c r="B816" s="7" t="inlineStr">
         <is>
-          <t>16462</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="C816" s="7" t="inlineStr">
         <is>
-          <t>11172997</t>
+          <t>11173001</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>Xm25RedQuen30</t>
+          <t>Xm25Quencher30</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">
@@ -28928,17 +28928,17 @@
       </c>
       <c r="B817" s="7" t="inlineStr">
         <is>
-          <t>16463</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="C817" s="7" t="inlineStr">
         <is>
-          <t>11173001</t>
+          <t>11172989</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>Xm25Quencher30</t>
+          <t>Xm25StanVac16</t>
         </is>
       </c>
       <c r="E817" t="inlineStr">
@@ -28963,17 +28963,17 @@
       </c>
       <c r="B818" s="7" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16465</t>
         </is>
       </c>
       <c r="C818" s="7" t="inlineStr">
         <is>
-          <t>11172989</t>
+          <t>11172990</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>Xm25StanVac16</t>
+          <t>Xm25StanCB16</t>
         </is>
       </c>
       <c r="E818" t="inlineStr">
@@ -28998,17 +28998,17 @@
       </c>
       <c r="B819" s="7" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>16466</t>
         </is>
       </c>
       <c r="C819" s="7" t="inlineStr">
         <is>
-          <t>11172990</t>
+          <t>11172999</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>Xm25StanCB16</t>
+          <t>Xm25Quen30Lil</t>
         </is>
       </c>
       <c r="E819" t="inlineStr">
@@ -29033,17 +29033,17 @@
       </c>
       <c r="B820" s="7" t="inlineStr">
         <is>
-          <t>16466</t>
+          <t>16467</t>
         </is>
       </c>
       <c r="C820" s="7" t="inlineStr">
         <is>
-          <t>11172999</t>
+          <t>11172981</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
         <is>
-          <t>Xm25Quen30Lil</t>
+          <t>Xm25SS12Vac</t>
         </is>
       </c>
       <c r="E820" t="inlineStr">
@@ -29068,17 +29068,17 @@
       </c>
       <c r="B821" s="7" t="inlineStr">
         <is>
-          <t>16467</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="C821" s="7" t="inlineStr">
         <is>
-          <t>11172981</t>
+          <t>11172992</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>Xm25SS12Vac</t>
+          <t>Xm25BTL20Twi</t>
         </is>
       </c>
       <c r="E821" t="inlineStr">
@@ -29103,17 +29103,17 @@
       </c>
       <c r="B822" s="7" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="C822" s="7" t="inlineStr">
         <is>
-          <t>11172992</t>
+          <t>11172988</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>Xm25BTL20Twi</t>
+          <t>Xm25SS16Charm</t>
         </is>
       </c>
       <c r="E822" t="inlineStr">
@@ -29138,17 +29138,17 @@
       </c>
       <c r="B823" s="7" t="inlineStr">
         <is>
-          <t>16469</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="C823" s="7" t="inlineStr">
         <is>
-          <t>11172988</t>
+          <t>11172971</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
         <is>
-          <t>Xm25SS16Charm</t>
+          <t>Xm25CC24Hol</t>
         </is>
       </c>
       <c r="E823" t="inlineStr">
@@ -29173,17 +29173,13 @@
       </c>
       <c r="B824" s="7" t="inlineStr">
         <is>
-          <t>16470</t>
-        </is>
-      </c>
-      <c r="C824" s="7" t="inlineStr">
-        <is>
-          <t>11172971</t>
-        </is>
-      </c>
+          <t>16471</t>
+        </is>
+      </c>
+      <c r="C824" s="7" t="inlineStr"/>
       <c r="D824" t="inlineStr">
         <is>
-          <t>Xm25CC24Hol</t>
+          <t>Xm25Give16Hot</t>
         </is>
       </c>
       <c r="E824" t="inlineStr">
@@ -29208,13 +29204,17 @@
       </c>
       <c r="B825" s="7" t="inlineStr">
         <is>
-          <t>16471</t>
-        </is>
-      </c>
-      <c r="C825" s="7" t="inlineStr"/>
+          <t>16472</t>
+        </is>
+      </c>
+      <c r="C825" s="7" t="inlineStr">
+        <is>
+          <t>11172975</t>
+        </is>
+      </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>Xm25Give16Hot</t>
+          <t>Xm25BTL24Magn</t>
         </is>
       </c>
       <c r="E825" t="inlineStr">
@@ -29239,17 +29239,17 @@
       </c>
       <c r="B826" s="7" t="inlineStr">
         <is>
-          <t>16472</t>
+          <t>16473</t>
         </is>
       </c>
       <c r="C826" s="7" t="inlineStr">
         <is>
-          <t>11172975</t>
+          <t>11172967</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>Xm25BTL24Magn</t>
+          <t>Xm25Tu16Bow</t>
         </is>
       </c>
       <c r="E826" t="inlineStr">
@@ -29274,17 +29274,17 @@
       </c>
       <c r="B827" s="7" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="C827" s="7" t="inlineStr">
         <is>
-          <t>11172967</t>
+          <t>11172857</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>Xm25Tu16Bow</t>
+          <t>Xm25MugPinguin</t>
         </is>
       </c>
       <c r="E827" t="inlineStr">
@@ -29309,17 +29309,17 @@
       </c>
       <c r="B828" s="7" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>16475</t>
         </is>
       </c>
       <c r="C828" s="7" t="inlineStr">
         <is>
-          <t>11172857</t>
+          <t>11172859</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>Xm25MugPinguin</t>
+          <t>Xm25Mug12House</t>
         </is>
       </c>
       <c r="E828" t="inlineStr">
@@ -29344,17 +29344,17 @@
       </c>
       <c r="B829" s="7" t="inlineStr">
         <is>
-          <t>16475</t>
+          <t>16476</t>
         </is>
       </c>
       <c r="C829" s="7" t="inlineStr">
         <is>
-          <t>11172859</t>
+          <t>11172986</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>Xm25Mug12House</t>
+          <t>Xm25SS16Peng</t>
         </is>
       </c>
       <c r="E829" t="inlineStr">
@@ -29379,17 +29379,17 @@
       </c>
       <c r="B830" s="7" t="inlineStr">
         <is>
-          <t>16476</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="C830" s="7" t="inlineStr">
         <is>
-          <t>11172986</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>Xm25SS16Peng</t>
+          <t>Fl25StopperBar</t>
         </is>
       </c>
       <c r="E830" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="B831" s="7" t="inlineStr">
         <is>
-          <t>16488</t>
+          <t>16489</t>
         </is>
       </c>
       <c r="C831" s="7" t="inlineStr">
@@ -29424,7 +29424,7 @@
       </c>
       <c r="D831" t="inlineStr">
         <is>
-          <t>Fl25StopperBar</t>
+          <t>Fl25StrawBar</t>
         </is>
       </c>
       <c r="E831" t="inlineStr">
@@ -29449,7 +29449,7 @@
       </c>
       <c r="B832" s="7" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>16490</t>
         </is>
       </c>
       <c r="C832" s="7" t="inlineStr">
@@ -29459,7 +29459,7 @@
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>Fl25StrawBar</t>
+          <t>Fl25Manga</t>
         </is>
       </c>
       <c r="E832" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="B833" s="7" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="C833" s="7" t="inlineStr">
@@ -29494,7 +29494,7 @@
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>Fl25Manga</t>
+          <t>Fl25Llavero</t>
         </is>
       </c>
       <c r="E833" t="inlineStr">
@@ -29519,7 +29519,7 @@
       </c>
       <c r="B834" s="7" t="inlineStr">
         <is>
-          <t>16500</t>
+          <t>16502</t>
         </is>
       </c>
       <c r="C834" s="7" t="inlineStr">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>Fl25Llavero</t>
+          <t>Xm25Tag</t>
         </is>
       </c>
       <c r="E834" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="B835" s="7" t="inlineStr">
         <is>
-          <t>16502</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="C835" s="7" t="inlineStr">
@@ -29564,7 +29564,7 @@
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>Xm25Tag</t>
+          <t>Xm25Stopper</t>
         </is>
       </c>
       <c r="E835" t="inlineStr">
@@ -29589,17 +29589,17 @@
       </c>
       <c r="B836" s="7" t="inlineStr">
         <is>
-          <t>16503</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="C836" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11174779</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>Xm25Stopper</t>
+          <t>Wt26CCGl16Red</t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
@@ -29624,17 +29624,17 @@
       </c>
       <c r="B837" s="7" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="C837" s="7" t="inlineStr">
         <is>
-          <t>11174779</t>
+          <t>11174804</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>Wt26CCGl16Red</t>
+          <t>Wt26BTLStanley</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
@@ -29659,17 +29659,17 @@
       </c>
       <c r="B838" s="7" t="inlineStr">
         <is>
-          <t>16541</t>
+          <t>16543</t>
         </is>
       </c>
       <c r="C838" s="7" t="inlineStr">
         <is>
-          <t>11174804</t>
+          <t>11174795</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>Wt26BTLStanley</t>
+          <t>Wt26CC24Spinner</t>
         </is>
       </c>
       <c r="E838" t="inlineStr">
@@ -29694,17 +29694,17 @@
       </c>
       <c r="B839" s="7" t="inlineStr">
         <is>
-          <t>16543</t>
+          <t>16544</t>
         </is>
       </c>
       <c r="C839" s="7" t="inlineStr">
         <is>
-          <t>11174795</t>
+          <t>11177277</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>Wt26CC24Spinner</t>
+          <t>Wt26CC24Choco</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
@@ -29729,17 +29729,17 @@
       </c>
       <c r="B840" s="7" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="C840" s="7" t="inlineStr">
         <is>
-          <t>11177277</t>
+          <t>11174808</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>Wt26CC24Choco</t>
+          <t>Wt26SSCC24Grad</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
@@ -29764,17 +29764,17 @@
       </c>
       <c r="B841" s="7" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>16546</t>
         </is>
       </c>
       <c r="C841" s="7" t="inlineStr">
         <is>
-          <t>11174808</t>
+          <t>11174811</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>Wt26SSCC24Grad</t>
+          <t>Wt26SS30Jac</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
@@ -29799,17 +29799,17 @@
       </c>
       <c r="B842" s="7" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16547</t>
         </is>
       </c>
       <c r="C842" s="7" t="inlineStr">
         <is>
-          <t>11174811</t>
+          <t>11177274</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>Wt26SS30Jac</t>
+          <t>Wt26SSCC24Win</t>
         </is>
       </c>
       <c r="E842" t="inlineStr">
@@ -29834,17 +29834,17 @@
       </c>
       <c r="B843" s="7" t="inlineStr">
         <is>
-          <t>16547</t>
+          <t>16548</t>
         </is>
       </c>
       <c r="C843" s="7" t="inlineStr">
         <is>
-          <t>11177274</t>
+          <t>11174801</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>Wt26SSCC24Win</t>
+          <t>Wt26SSBTL20SV</t>
         </is>
       </c>
       <c r="E843" t="inlineStr">
@@ -29869,17 +29869,17 @@
       </c>
       <c r="B844" s="7" t="inlineStr">
         <is>
-          <t>16548</t>
+          <t>16549</t>
         </is>
       </c>
       <c r="C844" s="7" t="inlineStr">
         <is>
-          <t>11174801</t>
+          <t>11174803</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>Wt26SSBTL20SV</t>
+          <t>Wt262PkStanley</t>
         </is>
       </c>
       <c r="E844" t="inlineStr">
@@ -29904,17 +29904,17 @@
       </c>
       <c r="B845" s="7" t="inlineStr">
         <is>
-          <t>16549</t>
+          <t>16551</t>
         </is>
       </c>
       <c r="C845" s="7" t="inlineStr">
         <is>
-          <t>11174803</t>
+          <t>11174775</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>Wt262PkStanley</t>
+          <t>Wt26Dw12Jac</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
@@ -29939,17 +29939,17 @@
       </c>
       <c r="B846" s="7" t="inlineStr">
         <is>
-          <t>16551</t>
+          <t>16552</t>
         </is>
       </c>
       <c r="C846" s="7" t="inlineStr">
         <is>
-          <t>11174775</t>
+          <t>11174798</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>Wt26Dw12Jac</t>
+          <t>Wt26SS16Green</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
@@ -29974,17 +29974,17 @@
       </c>
       <c r="B847" s="7" t="inlineStr">
         <is>
-          <t>16552</t>
+          <t>16553</t>
         </is>
       </c>
       <c r="C847" s="7" t="inlineStr">
         <is>
-          <t>11174798</t>
+          <t>11174800</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>Wt26SS16Green</t>
+          <t>Wt26BTL20Gr</t>
         </is>
       </c>
       <c r="E847" t="inlineStr">
@@ -30009,17 +30009,17 @@
       </c>
       <c r="B848" s="7" t="inlineStr">
         <is>
-          <t>16553</t>
+          <t>16554</t>
         </is>
       </c>
       <c r="C848" s="7" t="inlineStr">
         <is>
-          <t>11174800</t>
+          <t>11174807</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>Wt26BTL20Gr</t>
+          <t>Wt26SS16Choco</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
@@ -30044,17 +30044,17 @@
       </c>
       <c r="B849" s="7" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>16555</t>
         </is>
       </c>
       <c r="C849" s="7" t="inlineStr">
         <is>
-          <t>11174807</t>
+          <t>11174810</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>Wt26SS16Choco</t>
+          <t>Wt26Canteen</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
@@ -30079,17 +30079,17 @@
       </c>
       <c r="B850" s="7" t="inlineStr">
         <is>
-          <t>16555</t>
+          <t>16556</t>
         </is>
       </c>
       <c r="C850" s="7" t="inlineStr">
         <is>
-          <t>11174810</t>
+          <t>11174799</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>Wt26Canteen</t>
+          <t>Wt26SSCC16Grad</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
@@ -30114,17 +30114,17 @@
       </c>
       <c r="B851" s="7" t="inlineStr">
         <is>
-          <t>16556</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="C851" s="7" t="inlineStr">
         <is>
-          <t>11174799</t>
+          <t>11174806</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>Wt26SSCC16Grad</t>
+          <t>Wt26SSCC16Jac</t>
         </is>
       </c>
       <c r="E851" t="inlineStr">
@@ -30149,17 +30149,17 @@
       </c>
       <c r="B852" s="7" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>16558</t>
         </is>
       </c>
       <c r="C852" s="7" t="inlineStr">
         <is>
-          <t>11174806</t>
+          <t>11177275</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>Wt26SSCC16Jac</t>
+          <t>Wt26SS20SV</t>
         </is>
       </c>
       <c r="E852" t="inlineStr">
@@ -30184,17 +30184,17 @@
       </c>
       <c r="B853" s="7" t="inlineStr">
         <is>
-          <t>16558</t>
+          <t>16559</t>
         </is>
       </c>
       <c r="C853" s="7" t="inlineStr">
         <is>
-          <t>11177275</t>
+          <t>11177276</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>Wt26SS20SV</t>
+          <t>Wt26SS20Jac</t>
         </is>
       </c>
       <c r="E853" t="inlineStr">
@@ -30219,17 +30219,13 @@
       </c>
       <c r="B854" s="7" t="inlineStr">
         <is>
-          <t>16559</t>
-        </is>
-      </c>
-      <c r="C854" s="7" t="inlineStr">
-        <is>
-          <t>11177276</t>
-        </is>
-      </c>
+          <t>16566</t>
+        </is>
+      </c>
+      <c r="C854" s="7" t="inlineStr"/>
       <c r="D854" t="inlineStr">
         <is>
-          <t>Wt26SS20Jac</t>
+          <t>BearHugger</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
@@ -30254,13 +30250,17 @@
       </c>
       <c r="B855" s="7" t="inlineStr">
         <is>
-          <t>16566</t>
-        </is>
-      </c>
-      <c r="C855" s="7" t="inlineStr"/>
+          <t>16572</t>
+        </is>
+      </c>
+      <c r="C855" s="7" t="inlineStr">
+        <is>
+          <t>11174791</t>
+        </is>
+      </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>BearHugger</t>
+          <t>Wt26ReusSV</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
@@ -30285,17 +30285,17 @@
       </c>
       <c r="B856" s="7" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>16573</t>
         </is>
       </c>
       <c r="C856" s="7" t="inlineStr">
         <is>
-          <t>11174791</t>
+          <t>11175037</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>Wt26ReusSV</t>
+          <t>Wt26Tu16Charm</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
@@ -30320,17 +30320,17 @@
       </c>
       <c r="B857" s="7" t="inlineStr">
         <is>
-          <t>16573</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="C857" s="7" t="inlineStr">
         <is>
-          <t>11175037</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>Wt26Tu16Charm</t>
+          <t>Xm25ReuElev</t>
         </is>
       </c>
       <c r="E857" t="inlineStr">
@@ -30355,7 +30355,7 @@
       </c>
       <c r="B858" s="7" t="inlineStr">
         <is>
-          <t>16588</t>
+          <t>16589</t>
         </is>
       </c>
       <c r="C858" s="7" t="inlineStr">
@@ -30365,7 +30365,7 @@
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>Xm25ReuElev</t>
+          <t>Xm25ReuMike</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
@@ -30390,7 +30390,7 @@
       </c>
       <c r="B859" s="7" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>16590</t>
         </is>
       </c>
       <c r="C859" s="7" t="inlineStr">
@@ -30400,7 +30400,7 @@
       </c>
       <c r="D859" t="inlineStr">
         <is>
-          <t>Xm25ReuMike</t>
+          <t>Xm25Reus16ST</t>
         </is>
       </c>
       <c r="E859" t="inlineStr">
@@ -30425,7 +30425,7 @@
       </c>
       <c r="B860" s="7" t="inlineStr">
         <is>
-          <t>16590</t>
+          <t>16591</t>
         </is>
       </c>
       <c r="C860" s="7" t="inlineStr">
@@ -30435,7 +30435,7 @@
       </c>
       <c r="D860" t="inlineStr">
         <is>
-          <t>Xm25Reus16ST</t>
+          <t>Xm25Reu24CCST</t>
         </is>
       </c>
       <c r="E860" t="inlineStr">
@@ -30460,7 +30460,7 @@
       </c>
       <c r="B861" s="7" t="inlineStr">
         <is>
-          <t>16591</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="C861" s="7" t="inlineStr">
@@ -30470,7 +30470,7 @@
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>Xm25Reu24CCST</t>
+          <t>Xm25Reu2Hol</t>
         </is>
       </c>
       <c r="E861" t="inlineStr">
@@ -30495,7 +30495,7 @@
       </c>
       <c r="B862" s="7" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>16603</t>
         </is>
       </c>
       <c r="C862" s="7" t="inlineStr">
@@ -30505,7 +30505,7 @@
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>Xm25Reu2Hol</t>
+          <t>Xm25Reu1Hol</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
@@ -30530,17 +30530,17 @@
       </c>
       <c r="B863" s="7" t="inlineStr">
         <is>
-          <t>16603</t>
+          <t>16607</t>
         </is>
       </c>
       <c r="C863" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11177964</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>Xm25Reu1Hol</t>
+          <t>Sp26WTBLSS16Cher</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
@@ -30565,17 +30565,17 @@
       </c>
       <c r="B864" s="7" t="inlineStr">
         <is>
-          <t>16607</t>
+          <t>16608</t>
         </is>
       </c>
       <c r="C864" s="7" t="inlineStr">
         <is>
-          <t>11177964</t>
+          <t>11176612</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>Sp26WTBLSS16Cher</t>
+          <t>Wt26CC15Blue</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
@@ -30600,17 +30600,17 @@
       </c>
       <c r="B865" s="7" t="inlineStr">
         <is>
-          <t>16608</t>
+          <t>16609</t>
         </is>
       </c>
       <c r="C865" s="7" t="inlineStr">
         <is>
-          <t>11176612</t>
+          <t>11176610</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>Wt26CC15Blue</t>
+          <t>Wt26TuSS16Duck</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
@@ -30635,17 +30635,17 @@
       </c>
       <c r="B866" s="7" t="inlineStr">
         <is>
-          <t>16609</t>
+          <t>16610</t>
         </is>
       </c>
       <c r="C866" s="7" t="inlineStr">
         <is>
-          <t>11176610</t>
+          <t>11179880</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>Wt26TuSS16Duck</t>
+          <t>SII26SS16Resort</t>
         </is>
       </c>
       <c r="E866" t="inlineStr">
@@ -30670,17 +30670,17 @@
       </c>
       <c r="B867" s="7" t="inlineStr">
         <is>
-          <t>16610</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="C867" s="7" t="inlineStr">
         <is>
-          <t>11179880</t>
+          <t>11177937</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>SII26SS16Resort</t>
+          <t>Sp26CCup16Cherry</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
@@ -30705,17 +30705,17 @@
       </c>
       <c r="B868" s="7" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>16613</t>
         </is>
       </c>
       <c r="C868" s="7" t="inlineStr">
         <is>
-          <t>11177937</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>Sp26CCup16Cherry</t>
+          <t>Xm25StopDermo</t>
         </is>
       </c>
       <c r="E868" t="inlineStr">
@@ -30740,7 +30740,7 @@
       </c>
       <c r="B869" s="7" t="inlineStr">
         <is>
-          <t>16613</t>
+          <t>16614</t>
         </is>
       </c>
       <c r="C869" s="7" t="inlineStr">
@@ -30750,7 +30750,7 @@
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>Xm25StopDermo</t>
+          <t>Xm25StopHopp</t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
@@ -30775,17 +30775,17 @@
       </c>
       <c r="B870" s="7" t="inlineStr">
         <is>
-          <t>16614</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="C870" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11176708</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>Xm25StopHopp</t>
+          <t>Wt26GlassCC16</t>
         </is>
       </c>
       <c r="E870" t="inlineStr">
@@ -30810,17 +30810,17 @@
       </c>
       <c r="B871" s="7" t="inlineStr">
         <is>
-          <t>16658</t>
+          <t>16659</t>
         </is>
       </c>
       <c r="C871" s="7" t="inlineStr">
         <is>
-          <t>11176708</t>
+          <t>11176714</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
         <is>
-          <t>Wt26GlassCC16</t>
+          <t>Wt26SS16Vac</t>
         </is>
       </c>
       <c r="E871" t="inlineStr">
@@ -30845,17 +30845,17 @@
       </c>
       <c r="B872" s="7" t="inlineStr">
         <is>
-          <t>16659</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="C872" s="7" t="inlineStr">
         <is>
-          <t>11176714</t>
+          <t>11176719</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>Wt26SS16Vac</t>
+          <t>Wt26SSCC24CarryL</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
@@ -30880,17 +30880,17 @@
       </c>
       <c r="B873" s="7" t="inlineStr">
         <is>
-          <t>16660</t>
+          <t>16661</t>
         </is>
       </c>
       <c r="C873" s="7" t="inlineStr">
         <is>
-          <t>11176719</t>
+          <t>11176720</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>Wt26SSCC24CarryL</t>
+          <t>Wt26SSCC30Togo</t>
         </is>
       </c>
       <c r="E873" t="inlineStr">
@@ -30915,17 +30915,17 @@
       </c>
       <c r="B874" s="7" t="inlineStr">
         <is>
-          <t>16661</t>
+          <t>16662</t>
         </is>
       </c>
       <c r="C874" s="7" t="inlineStr">
         <is>
-          <t>11176720</t>
+          <t>11176721</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
         <is>
-          <t>Wt26SSCC30Togo</t>
+          <t>Sp26Stan30Purp</t>
         </is>
       </c>
       <c r="E874" t="inlineStr">
@@ -30950,17 +30950,17 @@
       </c>
       <c r="B875" s="7" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>16663</t>
         </is>
       </c>
       <c r="C875" s="7" t="inlineStr">
         <is>
-          <t>11176721</t>
+          <t>11176699</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
         <is>
-          <t>Sp26Stan30Purp</t>
+          <t>Sp26Mug14Rabbit</t>
         </is>
       </c>
       <c r="E875" t="inlineStr">
@@ -30985,17 +30985,17 @@
       </c>
       <c r="B876" s="7" t="inlineStr">
         <is>
-          <t>16663</t>
+          <t>16665</t>
         </is>
       </c>
       <c r="C876" s="7" t="inlineStr">
         <is>
-          <t>11176699</t>
+          <t>11176701</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>Sp26Mug14Rabbit</t>
+          <t>Sp26CC216Rabbit</t>
         </is>
       </c>
       <c r="E876" t="inlineStr">
@@ -31020,17 +31020,17 @@
       </c>
       <c r="B877" s="7" t="inlineStr">
         <is>
-          <t>16665</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C877" s="7" t="inlineStr">
         <is>
-          <t>11176701</t>
+          <t>11176702</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>Sp26CC216Rabbit</t>
+          <t>Sp26Tu20Blue</t>
         </is>
       </c>
       <c r="E877" t="inlineStr">
@@ -31055,17 +31055,17 @@
       </c>
       <c r="B878" s="7" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="C878" s="7" t="inlineStr">
         <is>
-          <t>11176702</t>
+          <t>11176715</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>Sp26Tu20Blue</t>
+          <t>Sp26SS16Rabbit</t>
         </is>
       </c>
       <c r="E878" t="inlineStr">
@@ -31090,17 +31090,17 @@
       </c>
       <c r="B879" s="7" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>16669</t>
         </is>
       </c>
       <c r="C879" s="7" t="inlineStr">
         <is>
-          <t>11176715</t>
+          <t>11176711</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>Sp26SS16Rabbit</t>
+          <t>Sp26Gl18Mottled</t>
         </is>
       </c>
       <c r="E879" t="inlineStr">
@@ -31125,17 +31125,17 @@
       </c>
       <c r="B880" s="7" t="inlineStr">
         <is>
-          <t>16669</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="C880" s="7" t="inlineStr">
         <is>
-          <t>11176711</t>
+          <t>11176700</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>Sp26Gl18Mottled</t>
+          <t>Sp26Tz14GlassC</t>
         </is>
       </c>
       <c r="E880" t="inlineStr">
@@ -31160,17 +31160,17 @@
       </c>
       <c r="B881" s="7" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>16671</t>
         </is>
       </c>
       <c r="C881" s="7" t="inlineStr">
         <is>
-          <t>11176700</t>
+          <t>11176717</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>Sp26Tz14GlassC</t>
+          <t>Sp26SS12Pink</t>
         </is>
       </c>
       <c r="E881" t="inlineStr">
@@ -31195,17 +31195,17 @@
       </c>
       <c r="B882" s="7" t="inlineStr">
         <is>
-          <t>16671</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="C882" s="7" t="inlineStr">
         <is>
-          <t>11176717</t>
+          <t>11176724</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
         <is>
-          <t>Sp26SS12Pink</t>
+          <t>Sp26CookieJP</t>
         </is>
       </c>
       <c r="E882" t="inlineStr">
@@ -31230,17 +31230,17 @@
       </c>
       <c r="B883" s="7" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>16673</t>
         </is>
       </c>
       <c r="C883" s="7" t="inlineStr">
         <is>
-          <t>11176724</t>
+          <t>11176703</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
         <is>
-          <t>Sp26CookieJP</t>
+          <t>Sp26Tu16Cherry</t>
         </is>
       </c>
       <c r="E883" t="inlineStr">
@@ -31265,17 +31265,17 @@
       </c>
       <c r="B884" s="7" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>16674</t>
         </is>
       </c>
       <c r="C884" s="7" t="inlineStr">
         <is>
-          <t>11176703</t>
+          <t>11176704</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
         <is>
-          <t>Sp26Tu16Cherry</t>
+          <t>Sp26CC16Prism</t>
         </is>
       </c>
       <c r="E884" t="inlineStr">
@@ -31300,17 +31300,17 @@
       </c>
       <c r="B885" s="7" t="inlineStr">
         <is>
-          <t>16674</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="C885" s="7" t="inlineStr">
         <is>
-          <t>11176704</t>
+          <t>11176722</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
         <is>
-          <t>Sp26CC16Prism</t>
+          <t>Sp26SSCC24Cherry</t>
         </is>
       </c>
       <c r="E885" t="inlineStr">
@@ -31335,17 +31335,17 @@
       </c>
       <c r="B886" s="7" t="inlineStr">
         <is>
-          <t>16675</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="C886" s="7" t="inlineStr">
         <is>
-          <t>11176722</t>
+          <t>11176718</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
         <is>
-          <t>Sp26SSCC24Cherry</t>
+          <t>Sp26SS16Cherry</t>
         </is>
       </c>
       <c r="E886" t="inlineStr">
@@ -31370,17 +31370,17 @@
       </c>
       <c r="B887" s="7" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>16677</t>
         </is>
       </c>
       <c r="C887" s="7" t="inlineStr">
         <is>
-          <t>11176718</t>
+          <t>11176723</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>Sp26SS16Cherry</t>
+          <t>Sp26SSVac40Cherr</t>
         </is>
       </c>
       <c r="E887" t="inlineStr">
@@ -31405,17 +31405,17 @@
       </c>
       <c r="B888" s="7" t="inlineStr">
         <is>
-          <t>16677</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="C888" s="7" t="inlineStr">
         <is>
-          <t>11176723</t>
+          <t>11176705</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>Sp26SSVac40Cherr</t>
+          <t>Sp26ReusTierra</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
@@ -31440,17 +31440,17 @@
       </c>
       <c r="B889" s="7" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16679</t>
         </is>
       </c>
       <c r="C889" s="7" t="inlineStr">
         <is>
-          <t>11176705</t>
+          <t>11176712</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>Sp26ReusTierra</t>
+          <t>Sp26CCReusTierra</t>
         </is>
       </c>
       <c r="E889" t="inlineStr">
@@ -31475,17 +31475,17 @@
       </c>
       <c r="B890" s="7" t="inlineStr">
         <is>
-          <t>16679</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="C890" s="7" t="inlineStr">
         <is>
-          <t>11176712</t>
+          <t>11177607</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>Sp26CCReusTierra</t>
+          <t>Wt26ReusSiren</t>
         </is>
       </c>
       <c r="E890" t="inlineStr">
@@ -31510,17 +31510,17 @@
       </c>
       <c r="B891" s="7" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="C891" s="7" t="inlineStr">
         <is>
-          <t>11177607</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
         <is>
-          <t>Wt26ReusSiren</t>
+          <t>Sp26SS16Under</t>
         </is>
       </c>
       <c r="E891" t="inlineStr">
@@ -31545,17 +31545,13 @@
       </c>
       <c r="B892" s="7" t="inlineStr">
         <is>
-          <t>16721</t>
-        </is>
-      </c>
-      <c r="C892" s="7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>16722</t>
+        </is>
+      </c>
+      <c r="C892" s="7" t="inlineStr"/>
       <c r="D892" t="inlineStr">
         <is>
-          <t>Sp26SS16Under</t>
+          <t>BearHuggerSpring</t>
         </is>
       </c>
       <c r="E892" t="inlineStr">
@@ -31580,13 +31576,17 @@
       </c>
       <c r="B893" s="7" t="inlineStr">
         <is>
-          <t>16722</t>
-        </is>
-      </c>
-      <c r="C893" s="7" t="inlineStr"/>
+          <t>16729</t>
+        </is>
+      </c>
+      <c r="C893" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="D893" t="inlineStr">
         <is>
-          <t>BearHuggerSpring</t>
+          <t>Wt26ReusBear</t>
         </is>
       </c>
       <c r="E893" t="inlineStr">
@@ -31611,7 +31611,7 @@
       </c>
       <c r="B894" s="7" t="inlineStr">
         <is>
-          <t>16729</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="C894" s="7" t="inlineStr">
@@ -31621,7 +31621,7 @@
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>Wt26ReusBear</t>
+          <t>Wt26VasoPistache</t>
         </is>
       </c>
       <c r="E894" t="inlineStr">
@@ -31646,7 +31646,7 @@
       </c>
       <c r="B895" s="7" t="inlineStr">
         <is>
-          <t>16769</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="C895" s="7" t="inlineStr">
@@ -31656,7 +31656,7 @@
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>Wt26VasoPistache</t>
+          <t>Wt26VasoFresa</t>
         </is>
       </c>
       <c r="E895" t="inlineStr">
@@ -31681,7 +31681,7 @@
       </c>
       <c r="B896" s="7" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="C896" s="7" t="inlineStr">
@@ -31691,7 +31691,7 @@
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>Wt26VasoFresa</t>
+          <t>Wt26VasoJacaran</t>
         </is>
       </c>
       <c r="E896" t="inlineStr">
@@ -31716,7 +31716,7 @@
       </c>
       <c r="B897" s="7" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>16775</t>
         </is>
       </c>
       <c r="C897" s="7" t="inlineStr">
@@ -31726,7 +31726,7 @@
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>Wt26VasoJacaran</t>
+          <t>Wt26LlaveroSV</t>
         </is>
       </c>
       <c r="E897" t="inlineStr">
@@ -31751,17 +31751,17 @@
       </c>
       <c r="B898" s="7" t="inlineStr">
         <is>
-          <t>16775</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="C898" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11179885</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
         <is>
-          <t>Wt26LlaveroSV</t>
+          <t>SII26BTL20Resort</t>
         </is>
       </c>
       <c r="E898" t="inlineStr">
@@ -31786,17 +31786,17 @@
       </c>
       <c r="B899" s="7" t="inlineStr">
         <is>
-          <t>16777</t>
+          <t>16779</t>
         </is>
       </c>
       <c r="C899" s="7" t="inlineStr">
         <is>
-          <t>11179885</t>
+          <t>11176592</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>SII26BTL20Resort</t>
+          <t>SII26SSTu12Pony</t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
@@ -31821,17 +31821,17 @@
       </c>
       <c r="B900" s="7" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="C900" s="7" t="inlineStr">
         <is>
-          <t>11176592</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>SII26SSTu12Pony</t>
+          <t>Sp26WTBL19Under</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
@@ -31856,7 +31856,7 @@
       </c>
       <c r="B901" s="7" t="inlineStr">
         <is>
-          <t>16780</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="C901" s="7" t="inlineStr">
@@ -31866,7 +31866,7 @@
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>Sp26WTBL19Under</t>
+          <t>Sp26Tu20Blossom</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
@@ -31891,17 +31891,17 @@
       </c>
       <c r="B902" s="7" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="C902" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11176597</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>Sp26Tu20Blossom</t>
+          <t>SII26BearPony</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
@@ -31926,17 +31926,17 @@
       </c>
       <c r="B903" s="7" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="C903" s="7" t="inlineStr">
         <is>
-          <t>11176597</t>
+          <t>1176593</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>SII26BearPony</t>
+          <t>SII26BTL16Pony</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
@@ -31961,17 +31961,13 @@
       </c>
       <c r="B904" s="7" t="inlineStr">
         <is>
-          <t>16793</t>
-        </is>
-      </c>
-      <c r="C904" s="7" t="inlineStr">
-        <is>
-          <t>1176593</t>
-        </is>
-      </c>
+          <t>16828</t>
+        </is>
+      </c>
+      <c r="C904" s="7" t="inlineStr"/>
       <c r="D904" t="inlineStr">
         <is>
-          <t>SII26BTL16Pony</t>
+          <t>BearHugWorldCup</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
@@ -31996,13 +31992,17 @@
       </c>
       <c r="B905" s="7" t="inlineStr">
         <is>
-          <t>16828</t>
-        </is>
-      </c>
-      <c r="C905" s="7" t="inlineStr"/>
+          <t>16876</t>
+        </is>
+      </c>
+      <c r="C905" s="7" t="inlineStr">
+        <is>
+          <t>11178953</t>
+        </is>
+      </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>BearHugWorldCup</t>
+          <t>Sp26SSCC24Oran</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
@@ -32027,17 +32027,17 @@
       </c>
       <c r="B906" s="7" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>16878</t>
         </is>
       </c>
       <c r="C906" s="7" t="inlineStr">
         <is>
-          <t>11178953</t>
+          <t>11178921</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>Sp26SSCC24Oran</t>
+          <t>Sp26Tu16Orange</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
@@ -32062,17 +32062,17 @@
       </c>
       <c r="B907" s="7" t="inlineStr">
         <is>
-          <t>16878</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="C907" s="7" t="inlineStr">
         <is>
-          <t>11178921</t>
+          <t>11178964</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>Sp26Tu16Orange</t>
+          <t>Sp26KeychainOr</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
@@ -32097,17 +32097,17 @@
       </c>
       <c r="B908" s="7" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="C908" s="7" t="inlineStr">
         <is>
-          <t>11178964</t>
+          <t>11179003</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>Sp26KeychainOr</t>
+          <t>Sp26CC24Teach</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
@@ -32132,17 +32132,17 @@
       </c>
       <c r="B909" s="7" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="C909" s="7" t="inlineStr">
         <is>
-          <t>11179003</t>
+          <t>11179004</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>Sp26CC24Teach</t>
+          <t>Sp26Tu16Teach</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
@@ -32167,17 +32167,17 @@
       </c>
       <c r="B910" s="7" t="inlineStr">
         <is>
-          <t>16899</t>
+          <t>16902</t>
         </is>
       </c>
       <c r="C910" s="7" t="inlineStr">
         <is>
-          <t>11179004</t>
+          <t>11178920</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>Sp26Tu16Teach</t>
+          <t>WC26Tu20Yellow</t>
         </is>
       </c>
       <c r="E910" t="inlineStr">
@@ -32202,17 +32202,17 @@
       </c>
       <c r="B911" s="7" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="C911" s="7" t="inlineStr">
         <is>
-          <t>11178920</t>
+          <t>11178926</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>WC26Tu20Yellow</t>
+          <t>Sp26CC24Or</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
@@ -32237,17 +32237,17 @@
       </c>
       <c r="B912" s="7" t="inlineStr">
         <is>
-          <t>16903</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="C912" s="7" t="inlineStr">
         <is>
-          <t>11178926</t>
+          <t>11178965</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>Sp26CC24Or</t>
+          <t>WC26ToteRoad</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
@@ -32272,17 +32272,17 @@
       </c>
       <c r="B913" s="7" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="C913" s="7" t="inlineStr">
         <is>
-          <t>11178965</t>
+          <t>11178966</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>WC26ToteRoad</t>
+          <t>WC26TotePride</t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
@@ -32307,17 +32307,17 @@
       </c>
       <c r="B914" s="7" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="C914" s="7" t="inlineStr">
         <is>
-          <t>11178966</t>
+          <t>11187369</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>WC26TotePride</t>
+          <t>WC26BearWC</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
@@ -32342,17 +32342,17 @@
       </c>
       <c r="B915" s="7" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>16909</t>
         </is>
       </c>
       <c r="C915" s="7" t="inlineStr">
         <is>
-          <t>11187369</t>
+          <t>11178944</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>WC26BearWC</t>
+          <t>WC26SS20BTL</t>
         </is>
       </c>
       <c r="E915" t="inlineStr">
@@ -32377,17 +32377,17 @@
       </c>
       <c r="B916" s="7" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>16912</t>
         </is>
       </c>
       <c r="C916" s="7" t="inlineStr">
         <is>
-          <t>11178944</t>
+          <t>11178949</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>WC26SS20BTL</t>
+          <t>WC26SS20Pull</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
@@ -32412,17 +32412,17 @@
       </c>
       <c r="B917" s="7" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>16914</t>
         </is>
       </c>
       <c r="C917" s="7" t="inlineStr">
         <is>
-          <t>11178949</t>
+          <t>11178947</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>WC26SS20Pull</t>
+          <t>Sp26StanQuen20</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
@@ -32447,17 +32447,17 @@
       </c>
       <c r="B918" s="7" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="C918" s="7" t="inlineStr">
         <is>
-          <t>11178947</t>
+          <t>11178972</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>Sp26StanQuen20</t>
+          <t>Sp26Vac16Stan</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
@@ -32482,17 +32482,17 @@
       </c>
       <c r="B919" s="7" t="inlineStr">
         <is>
-          <t>16917</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="C919" s="7" t="inlineStr">
         <is>
-          <t>11178972</t>
+          <t>11178917</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>Sp26Vac16Stan</t>
+          <t>WC26DW12Oran</t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
@@ -32517,17 +32517,17 @@
       </c>
       <c r="B920" s="7" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="C920" s="7" t="inlineStr">
         <is>
-          <t>11178917</t>
+          <t>11187370</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>WC26DW12Oran</t>
+          <t>WC26SS16Black</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
@@ -32552,17 +32552,13 @@
       </c>
       <c r="B921" s="7" t="inlineStr">
         <is>
-          <t>16958</t>
-        </is>
-      </c>
-      <c r="C921" s="7" t="inlineStr">
-        <is>
-          <t>11187370</t>
-        </is>
-      </c>
+          <t>16971</t>
+        </is>
+      </c>
+      <c r="C921" s="7" t="inlineStr"/>
       <c r="D921" t="inlineStr">
         <is>
-          <t>WC26SS16Black</t>
+          <t>WC26BearMex</t>
         </is>
       </c>
       <c r="E921" t="inlineStr">
@@ -32587,13 +32583,17 @@
       </c>
       <c r="B922" s="7" t="inlineStr">
         <is>
-          <t>16971</t>
-        </is>
-      </c>
-      <c r="C922" s="7" t="inlineStr"/>
+          <t>16978</t>
+        </is>
+      </c>
+      <c r="C922" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>WC26BearMex</t>
+          <t>WC26LlaveroB</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
@@ -32618,17 +32618,13 @@
       </c>
       <c r="B923" s="7" t="inlineStr">
         <is>
-          <t>16978</t>
-        </is>
-      </c>
-      <c r="C923" s="7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>16989</t>
+        </is>
+      </c>
+      <c r="C923" s="7" t="inlineStr"/>
       <c r="D923" t="inlineStr">
         <is>
-          <t>WC26LlaveroB</t>
+          <t>SII26SS12Aniv</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
@@ -32653,13 +32649,13 @@
       </c>
       <c r="B924" s="7" t="inlineStr">
         <is>
-          <t>16989</t>
+          <t>17298</t>
         </is>
       </c>
       <c r="C924" s="7" t="inlineStr"/>
       <c r="D924" t="inlineStr">
         <is>
-          <t>SII26SS12Aniv</t>
+          <t>SII26SSBTL12Aniv</t>
         </is>
       </c>
       <c r="E924" t="inlineStr">
@@ -32684,13 +32680,13 @@
       </c>
       <c r="B925" s="7" t="inlineStr">
         <is>
-          <t>17298</t>
+          <t>17299</t>
         </is>
       </c>
       <c r="C925" s="7" t="inlineStr"/>
       <c r="D925" t="inlineStr">
         <is>
-          <t>SII26SSBTL12Aniv</t>
+          <t>SII26Mug14Aniv</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
@@ -32715,13 +32711,13 @@
       </c>
       <c r="B926" s="7" t="inlineStr">
         <is>
-          <t>17299</t>
+          <t>17307</t>
         </is>
       </c>
       <c r="C926" s="7" t="inlineStr"/>
       <c r="D926" t="inlineStr">
         <is>
-          <t>SII26Mug14Aniv</t>
+          <t>SII26Doodle16</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
@@ -32746,13 +32742,13 @@
       </c>
       <c r="B927" s="7" t="inlineStr">
         <is>
-          <t>17307</t>
+          <t>52206</t>
         </is>
       </c>
       <c r="C927" s="7" t="inlineStr"/>
       <c r="D927" t="inlineStr">
         <is>
-          <t>SII26Doodle16</t>
+          <t>Vaso Rewards</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
@@ -32777,13 +32773,13 @@
       </c>
       <c r="B928" s="7" t="inlineStr">
         <is>
-          <t>52206</t>
+          <t>53500</t>
         </is>
       </c>
       <c r="C928" s="7" t="inlineStr"/>
       <c r="D928" t="inlineStr">
         <is>
-          <t>Vaso Rewards</t>
+          <t>ResSS16TGradient</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
@@ -32808,13 +32804,13 @@
       </c>
       <c r="B929" s="7" t="inlineStr">
         <is>
-          <t>53500</t>
+          <t>53834</t>
         </is>
       </c>
       <c r="C929" s="7" t="inlineStr"/>
       <c r="D929" t="inlineStr">
         <is>
-          <t>ResSS16TGradient</t>
+          <t>Tazas SBX Genérico</t>
         </is>
       </c>
       <c r="E929" t="inlineStr">
@@ -32839,13 +32835,13 @@
       </c>
       <c r="B930" s="7" t="inlineStr">
         <is>
-          <t>53834</t>
+          <t>53835</t>
         </is>
       </c>
       <c r="C930" s="7" t="inlineStr"/>
       <c r="D930" t="inlineStr">
         <is>
-          <t>Tazas SBX Genérico</t>
+          <t>CCupPlastic SBX Genérico</t>
         </is>
       </c>
       <c r="E930" t="inlineStr">
@@ -32870,13 +32866,13 @@
       </c>
       <c r="B931" s="7" t="inlineStr">
         <is>
-          <t>53835</t>
+          <t>53836</t>
         </is>
       </c>
       <c r="C931" s="7" t="inlineStr"/>
       <c r="D931" t="inlineStr">
         <is>
-          <t>CCupPlastic SBX Genérico</t>
+          <t>CCup Acero SBX Genérico</t>
         </is>
       </c>
       <c r="E931" t="inlineStr">
@@ -32901,13 +32897,13 @@
       </c>
       <c r="B932" s="7" t="inlineStr">
         <is>
-          <t>53836</t>
+          <t>53837</t>
         </is>
       </c>
       <c r="C932" s="7" t="inlineStr"/>
       <c r="D932" t="inlineStr">
         <is>
-          <t>CCup Acero SBX Genérico</t>
+          <t>Tumb acero SBX Genérico</t>
         </is>
       </c>
       <c r="E932" t="inlineStr">
@@ -32932,13 +32928,13 @@
       </c>
       <c r="B933" s="7" t="inlineStr">
         <is>
-          <t>53837</t>
+          <t>53838</t>
         </is>
       </c>
       <c r="C933" s="7" t="inlineStr"/>
       <c r="D933" t="inlineStr">
         <is>
-          <t>Tumb acero SBX Genérico</t>
+          <t>Tumb Plastic SBX Genérico</t>
         </is>
       </c>
       <c r="E933" t="inlineStr">
@@ -32963,13 +32959,13 @@
       </c>
       <c r="B934" s="7" t="inlineStr">
         <is>
-          <t>53838</t>
+          <t>53839</t>
         </is>
       </c>
       <c r="C934" s="7" t="inlineStr"/>
       <c r="D934" t="inlineStr">
         <is>
-          <t>Tumb Plastic SBX Genérico</t>
+          <t>Stanley SBX Genérico</t>
         </is>
       </c>
       <c r="E934" t="inlineStr">
@@ -32994,13 +32990,13 @@
       </c>
       <c r="B935" s="7" t="inlineStr">
         <is>
-          <t>53839</t>
+          <t>53840</t>
         </is>
       </c>
       <c r="C935" s="7" t="inlineStr"/>
       <c r="D935" t="inlineStr">
         <is>
-          <t>Stanley SBX Genérico</t>
+          <t>Llavero SBX Genérico</t>
         </is>
       </c>
       <c r="E935" t="inlineStr">
@@ -33025,13 +33021,13 @@
       </c>
       <c r="B936" s="7" t="inlineStr">
         <is>
-          <t>53840</t>
+          <t>53841</t>
         </is>
       </c>
       <c r="C936" s="7" t="inlineStr"/>
       <c r="D936" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
+          <t>Stoppers SBX Genérico</t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
@@ -33056,13 +33052,13 @@
       </c>
       <c r="B937" s="7" t="inlineStr">
         <is>
-          <t>53841</t>
+          <t>53842</t>
         </is>
       </c>
       <c r="C937" s="7" t="inlineStr"/>
       <c r="D937" t="inlineStr">
         <is>
-          <t>Stoppers SBX Genérico</t>
+          <t>Tote bags SBX Genérico</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
@@ -33087,13 +33083,13 @@
       </c>
       <c r="B938" s="7" t="inlineStr">
         <is>
-          <t>53842</t>
+          <t>53843</t>
         </is>
       </c>
       <c r="C938" s="7" t="inlineStr"/>
       <c r="D938" t="inlineStr">
         <is>
-          <t>Tote bags SBX Genérico</t>
+          <t>Pines SBX Genérico</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
@@ -33118,13 +33114,13 @@
       </c>
       <c r="B939" s="7" t="inlineStr">
         <is>
-          <t>53843</t>
+          <t>53844</t>
         </is>
       </c>
       <c r="C939" s="7" t="inlineStr"/>
       <c r="D939" t="inlineStr">
         <is>
-          <t>Pines SBX Genérico</t>
+          <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
       <c r="E939" t="inlineStr">
@@ -33149,13 +33145,13 @@
       </c>
       <c r="B940" s="7" t="inlineStr">
         <is>
-          <t>53844</t>
+          <t>53845</t>
         </is>
       </c>
       <c r="C940" s="7" t="inlineStr"/>
       <c r="D940" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
+          <t>Set Reusa SBX Genérico</t>
         </is>
       </c>
       <c r="E940" t="inlineStr">
@@ -33180,13 +33176,13 @@
       </c>
       <c r="B941" s="7" t="inlineStr">
         <is>
-          <t>53845</t>
+          <t>53949</t>
         </is>
       </c>
       <c r="C941" s="7" t="inlineStr"/>
       <c r="D941" t="inlineStr">
         <is>
-          <t>Set Reusa SBX Genérico</t>
+          <t>Xm25Tu12Hol</t>
         </is>
       </c>
       <c r="E941" t="inlineStr">
@@ -33211,13 +33207,13 @@
       </c>
       <c r="B942" s="7" t="inlineStr">
         <is>
-          <t>53949</t>
+          <t>53951</t>
         </is>
       </c>
       <c r="C942" s="7" t="inlineStr"/>
       <c r="D942" t="inlineStr">
         <is>
-          <t>Xm25Tu12Hol</t>
+          <t>Xm25StopDermo</t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
@@ -33242,13 +33238,13 @@
       </c>
       <c r="B943" s="7" t="inlineStr">
         <is>
-          <t>53951</t>
+          <t>53952</t>
         </is>
       </c>
       <c r="C943" s="7" t="inlineStr"/>
       <c r="D943" t="inlineStr">
         <is>
-          <t>Xm25StopDermo</t>
+          <t>Xm25StopMike</t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
@@ -33273,13 +33269,13 @@
       </c>
       <c r="B944" s="7" t="inlineStr">
         <is>
-          <t>53952</t>
+          <t>53953</t>
         </is>
       </c>
       <c r="C944" s="7" t="inlineStr"/>
       <c r="D944" t="inlineStr">
         <is>
-          <t>Xm25StopMike</t>
+          <t>Xm25StopDust</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
@@ -33304,13 +33300,13 @@
       </c>
       <c r="B945" s="7" t="inlineStr">
         <is>
-          <t>53953</t>
+          <t>53958</t>
         </is>
       </c>
       <c r="C945" s="7" t="inlineStr"/>
       <c r="D945" t="inlineStr">
         <is>
-          <t>Xm25StopDust</t>
+          <t>Xm25Reu1Hol</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
@@ -33335,13 +33331,13 @@
       </c>
       <c r="B946" s="7" t="inlineStr">
         <is>
-          <t>53958</t>
+          <t>53959</t>
         </is>
       </c>
       <c r="C946" s="7" t="inlineStr"/>
       <c r="D946" t="inlineStr">
         <is>
-          <t>Xm25Reu1Hol</t>
+          <t>Xm25Reu2Hol</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
@@ -33366,13 +33362,13 @@
       </c>
       <c r="B947" s="7" t="inlineStr">
         <is>
-          <t>53959</t>
+          <t>53962</t>
         </is>
       </c>
       <c r="C947" s="7" t="inlineStr"/>
       <c r="D947" t="inlineStr">
         <is>
-          <t>Xm25Reu2Hol</t>
+          <t>Xm25Tag</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
@@ -33397,13 +33393,13 @@
       </c>
       <c r="B948" s="7" t="inlineStr">
         <is>
-          <t>53962</t>
+          <t>53965</t>
         </is>
       </c>
       <c r="C948" s="7" t="inlineStr"/>
       <c r="D948" t="inlineStr">
         <is>
-          <t>Xm25Tag</t>
+          <t>Xm25StopWill</t>
         </is>
       </c>
       <c r="E948" t="inlineStr">
@@ -33428,13 +33424,13 @@
       </c>
       <c r="B949" s="7" t="inlineStr">
         <is>
-          <t>53965</t>
+          <t>53966</t>
         </is>
       </c>
       <c r="C949" s="7" t="inlineStr"/>
       <c r="D949" t="inlineStr">
         <is>
-          <t>Xm25StopWill</t>
+          <t>Xm25StopMax</t>
         </is>
       </c>
       <c r="E949" t="inlineStr">
@@ -33459,13 +33455,13 @@
       </c>
       <c r="B950" s="7" t="inlineStr">
         <is>
-          <t>53966</t>
+          <t>53967</t>
         </is>
       </c>
       <c r="C950" s="7" t="inlineStr"/>
       <c r="D950" t="inlineStr">
         <is>
-          <t>Xm25StopMax</t>
+          <t>Xm25StopHopp</t>
         </is>
       </c>
       <c r="E950" t="inlineStr">
@@ -33490,13 +33486,13 @@
       </c>
       <c r="B951" s="7" t="inlineStr">
         <is>
-          <t>53967</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="C951" s="7" t="inlineStr"/>
       <c r="D951" t="inlineStr">
         <is>
-          <t>Xm25StopHopp</t>
+          <t>Sp26BlindBox</t>
         </is>
       </c>
       <c r="E951" t="inlineStr">
@@ -33521,13 +33517,13 @@
       </c>
       <c r="B952" s="7" t="inlineStr">
         <is>
-          <t>54112</t>
+          <t>54192</t>
         </is>
       </c>
       <c r="C952" s="7" t="inlineStr"/>
       <c r="D952" t="inlineStr">
         <is>
-          <t>Sp26BlindBox</t>
+          <t>SII26GICCColor</t>
         </is>
       </c>
       <c r="E952" t="inlineStr">
@@ -33552,13 +33548,13 @@
       </c>
       <c r="B953" s="7" t="inlineStr">
         <is>
-          <t>54192</t>
+          <t>54201</t>
         </is>
       </c>
       <c r="C953" s="7" t="inlineStr"/>
       <c r="D953" t="inlineStr">
         <is>
-          <t>SII26GICCColor</t>
+          <t>SII26CC24Rain</t>
         </is>
       </c>
       <c r="E953" t="inlineStr">
@@ -33583,13 +33579,13 @@
       </c>
       <c r="B954" s="7" t="inlineStr">
         <is>
-          <t>54201</t>
+          <t>54213</t>
         </is>
       </c>
       <c r="C954" s="7" t="inlineStr"/>
       <c r="D954" t="inlineStr">
         <is>
-          <t>SII26CC24Rain</t>
+          <t>WC26Reus</t>
         </is>
       </c>
       <c r="E954" t="inlineStr">
@@ -33609,18 +33605,18 @@
     <row r="955" ht="24" customHeight="1">
       <c r="A955" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B955" s="7" t="inlineStr">
         <is>
-          <t>54213</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="C955" s="7" t="inlineStr"/>
       <c r="D955" t="inlineStr">
         <is>
-          <t>WC26Reus</t>
+          <t>ESS Reusable cup</t>
         </is>
       </c>
       <c r="E955" t="inlineStr">
@@ -33633,9 +33629,21 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="G955" t="inlineStr"/>
-      <c r="H955" t="inlineStr"/>
-      <c r="I955" t="inlineStr"/>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>lote-01/11372.jpeg</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="956" ht="24" customHeight="1">
       <c r="A956" t="inlineStr">
@@ -33645,13 +33653,17 @@
       </c>
       <c r="B956" s="7" t="inlineStr">
         <is>
-          <t>11372</t>
-        </is>
-      </c>
-      <c r="C956" s="7" t="inlineStr"/>
+          <t>14885</t>
+        </is>
+      </c>
+      <c r="C956" s="7" t="inlineStr">
+        <is>
+          <t>11141050</t>
+        </is>
+      </c>
       <c r="D956" t="inlineStr">
         <is>
-          <t>ESS Reusable cup</t>
+          <t>COR23 Tz14 Rain</t>
         </is>
       </c>
       <c r="E956" t="inlineStr">
@@ -33666,7 +33678,7 @@
       </c>
       <c r="G956" t="inlineStr">
         <is>
-          <t>lote-01/11372.jpeg</t>
+          <t>lote-01/14885.jpeg</t>
         </is>
       </c>
       <c r="H956" t="inlineStr">
@@ -33688,17 +33700,17 @@
       </c>
       <c r="B957" s="7" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>14927</t>
         </is>
       </c>
       <c r="C957" s="7" t="inlineStr">
         <is>
-          <t>11141050</t>
+          <t>11141041</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
         <is>
-          <t>COR23 Tz14 Rain</t>
+          <t>COR23 Pour Over</t>
         </is>
       </c>
       <c r="E957" t="inlineStr">
@@ -33713,7 +33725,7 @@
       </c>
       <c r="G957" t="inlineStr">
         <is>
-          <t>lote-01/14885.jpeg</t>
+          <t>lote-01/14927.jpeg</t>
         </is>
       </c>
       <c r="H957" t="inlineStr">
@@ -33735,17 +33747,17 @@
       </c>
       <c r="B958" s="7" t="inlineStr">
         <is>
-          <t>14927</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="C958" s="7" t="inlineStr">
         <is>
-          <t>11141041</t>
+          <t>11141095</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
         <is>
-          <t>COR23 Pour Over</t>
+          <t>COR23 Cold Brew</t>
         </is>
       </c>
       <c r="E958" t="inlineStr">
@@ -33760,7 +33772,7 @@
       </c>
       <c r="G958" t="inlineStr">
         <is>
-          <t>lote-01/14927.jpeg</t>
+          <t>lote-01/14928.jpeg</t>
         </is>
       </c>
       <c r="H958" t="inlineStr">
@@ -33782,17 +33794,17 @@
       </c>
       <c r="B959" s="7" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="C959" s="7" t="inlineStr">
         <is>
-          <t>11141095</t>
+          <t>11160995</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
         <is>
-          <t>COR23 Cold Brew</t>
+          <t>COR26BTL20</t>
         </is>
       </c>
       <c r="E959" t="inlineStr">
@@ -33807,7 +33819,7 @@
       </c>
       <c r="G959" t="inlineStr">
         <is>
-          <t>lote-01/14928.jpeg</t>
+          <t>lote-01/16312.jpeg</t>
         </is>
       </c>
       <c r="H959" t="inlineStr">
@@ -33829,17 +33841,17 @@
       </c>
       <c r="B960" s="7" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16378</t>
         </is>
       </c>
       <c r="C960" s="7" t="inlineStr">
         <is>
-          <t>11160995</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D960" t="inlineStr">
         <is>
-          <t>COR26BTL20</t>
+          <t>COR25CircCup</t>
         </is>
       </c>
       <c r="E960" t="inlineStr">
@@ -33854,7 +33866,7 @@
       </c>
       <c r="G960" t="inlineStr">
         <is>
-          <t>lote-01/16312.jpeg</t>
+          <t>lote-01/16378.jpeg</t>
         </is>
       </c>
       <c r="H960" t="inlineStr">

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de fotos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Control de fotos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Control de fotos'!$A$7:$M$1155</definedName>

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -686,27 +686,27 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>27933</v>
+        <v>30824</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>16807</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>149317</t>
+          <t>153719</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ESS Reusable cup</t>
+          <t>Vaso Rewards</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>VASO/TAPA 16OZ REUSABLE CJ216PZAS</t>
+          <t>VASO/TAPA 16OZ REUSABLE REWARDS CJ52PZAS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -721,12 +721,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ESS Reusable cup</t>
+          <t>Vaso Rewards</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>lote-01/11372.jpeg</t>
+          <t>lote-01/16807.jpeg</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -747,31 +747,27 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>11460</v>
+        <v>27933</v>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>154180</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>11178935</t>
-        </is>
-      </c>
+          <t>149317</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SII26Tu10Gam</t>
+          <t>ESS Reusable cup</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>78935 C1P SM26 PLSTC TMBLR GMRS 10OZ</t>
+          <t>VASO/TAPA 16OZ REUSABLE CJ216PZAS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -786,12 +782,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>SII26Tu10Gam</t>
+          <t>ESS Reusable cup</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>lote-01/011178935.jpeg</t>
+          <t>lote-01/11372.jpeg</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -801,7 +797,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -812,36 +808,36 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>10598</v>
+        <v>11460</v>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>16078</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>149784</t>
+          <t>154180</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178935</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
+          <t>SII26Tu10Gam</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MANGA SILICON P/VASO CELEBRACION CJ25PZA</t>
+          <t>78935 C1P SM26 PLSTC TMBLR GMRS 10OZ</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -851,12 +847,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
+          <t>SII26Tu10Gam</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>lote-01/16078.jpeg</t>
+          <t>lote-01/011178935.jpeg</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -866,7 +862,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -877,36 +873,36 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>8628</v>
+        <v>10598</v>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>16910</t>
+          <t>16078</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>154170</t>
+          <t>149784</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>11178969</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>WC26SS16Pink</t>
+          <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>78969 C2P SM26 SS VAC TMBLR 16OZ</t>
+          <t>MANGA SILICON P/VASO CELEBRACION CJ25PZA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -916,12 +912,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>WC26SS16Pink</t>
+          <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>lote-01/011178969.jpeg</t>
+          <t>lote-01/16078.jpeg</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -931,7 +927,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -942,31 +938,31 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>8447</v>
+        <v>8628</v>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>154148</t>
+          <t>154170</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>11178930</t>
+          <t>11178969</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>WC26CC24Pride</t>
+          <t>WC26SS16Pink</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>78930 C2P SM26 PLSTC HTCLD CUP PRD 24OZ</t>
+          <t>78969 C2P SM26 SS VAC TMBLR 16OZ</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -981,12 +977,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>WC26CC24Pride</t>
+          <t>WC26SS16Pink</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>lote-01/011178930.jpeg</t>
+          <t>lote-01/011178969.jpeg</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1007,31 +1003,31 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>8390</v>
+        <v>8447</v>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>154146</t>
+          <t>154148</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>11178928</t>
+          <t>11178930</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WC26CC24Road</t>
+          <t>WC26CC24Pride</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>78928 C2P SM26 PLSTC HTCLD CUP 24OZ</t>
+          <t>78930 C2P SM26 PLSTC HTCLD CUP PRD 24OZ</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1046,12 +1042,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>WC26CC24Road</t>
+          <t>WC26CC24Pride</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>lote-01/011178928.jpeg</t>
+          <t>lote-01/011178930.jpeg</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1072,31 +1068,31 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>7842</v>
+        <v>8390</v>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>16880</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>154150</t>
+          <t>154146</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>11178934</t>
+          <t>11178928</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SII26CC24GID</t>
+          <t>WC26CC24Road</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>78934 C2P SM26 PLSTC CLDCP GID 24OZ</t>
+          <t>78928 C2P SM26 PLSTC HTCLD CUP 24OZ</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1111,12 +1107,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SII26CC24GID</t>
+          <t>WC26CC24Road</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>lote-01/16884.jpeg</t>
+          <t>lote-01/011178928.jpeg</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1126,7 +1122,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1133,31 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>7841</v>
+        <v>7842</v>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>16916</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>154176</t>
+          <t>154150</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>11178956</t>
+          <t>11178934</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SII26Quencher30P</t>
+          <t>SII26CC24GID</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>78956 C1P SM26 RCLD SS TMBLR STNLY 30OZ</t>
+          <t>78934 C2P SM26 PLSTC CLDCP GID 24OZ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1176,12 +1172,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>SII26Quencher30P</t>
+          <t>SII26CC24GID</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>lote-01/011178956.jpeg</t>
+          <t>lote-01/16884.jpeg</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1191,7 +1187,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -1202,31 +1198,31 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>7663</v>
+        <v>7841</v>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>16999</t>
+          <t>16916</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>156348</t>
+          <t>154176</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>11186659</t>
+          <t>11178956</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SII26BTLSS20</t>
+          <t>SII26Quencher30P</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>86659 C2P FL26 SS WTRBTL TWST SP 20OZ</t>
+          <t>78956 C1P SM26 RCLD SS TMBLR STNLY 30OZ</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1241,12 +1237,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>SII26BTLSS20</t>
+          <t>SII26Quencher30P</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>lote-01/011186659.jpeg</t>
+          <t>lote-01/011178956.jpeg</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1267,31 +1263,31 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>7661</v>
+        <v>7663</v>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>156347</t>
+          <t>156348</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>11186658</t>
+          <t>11186659</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SII26SS20Hand</t>
+          <t>SII26BTLSS20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>86658 C2P FL26 SS TMBLR PLL HNDL 20OZ</t>
+          <t>86659 C2P FL26 SS WTRBTL TWST SP 20OZ</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1306,12 +1302,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>SII26SS20Hand</t>
+          <t>SII26BTLSS20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>lote-01/011186658.jpeg</t>
+          <t>lote-01/011186659.jpeg</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1332,31 +1328,31 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>7458</v>
+        <v>7661</v>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>149515</t>
+          <t>156347</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>11141095</t>
+          <t>11186658</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>COR23 Cold Brew</t>
+          <t>SII26SS20Hand</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>41095 C1P CORE GLASS COLD BREW MAKER</t>
+          <t>86658 C2P FL26 SS TMBLR PLL HNDL 20OZ</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1371,12 +1367,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>COR23 Cold Brew</t>
+          <t>SII26SS20Hand</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>lote-01/14928.jpeg</t>
+          <t>lote-01/011186658.jpeg</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1386,7 +1382,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -1397,31 +1393,31 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>7448</v>
+        <v>7458</v>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>16997</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>156346</t>
+          <t>149515</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>11186646</t>
+          <t>11141095</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SII26SS12Charm</t>
+          <t>COR23 Cold Brew</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>86646 C2P FL26 SS TMBLR CHRM JOY 12OZ</t>
+          <t>41095 C1P CORE GLASS COLD BREW MAKER</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1436,12 +1432,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>SII26SS12Charm</t>
+          <t>COR23 Cold Brew</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>lote-01/011186646.jpeg</t>
+          <t>lote-01/14928.jpeg</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1451,7 +1447,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -1462,31 +1458,31 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>7404</v>
+        <v>7448</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>16906</t>
+          <t>16997</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>154167</t>
+          <t>156346</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>11179005</t>
+          <t>11186646</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>WC26SS30Pride</t>
+          <t>SII26SS12Charm</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>79005 C1P SM26 SS VAC COLD TO GO 30OZ</t>
+          <t>86646 C2P FL26 SS TMBLR CHRM JOY 12OZ</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1501,12 +1497,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>WC26SS30Pride</t>
+          <t>SII26SS12Charm</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>lote-01/011179005.jpeg</t>
+          <t>lote-01/011186646.jpeg</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1527,36 +1523,36 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>7384</v>
+        <v>7404</v>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>15857</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>149714</t>
+          <t>154167</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>11157547</t>
+          <t>11179005</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CCup Acero SBX Genérico</t>
+          <t>WC26SS30Pride</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>57547 C2P CORE SS CLDCP SFTC IVORY 24 OZ</t>
+          <t>79005 C1P SM26 SS VAC COLD TO GO 30OZ</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1566,12 +1562,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>CCup Acero SBX Genérico, SII26SSCC24White</t>
+          <t>WC26SS30Pride</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>lote-01/15857.jpeg</t>
+          <t>lote-01/011179005.jpeg</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1581,7 +1577,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -1592,36 +1588,36 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>7252</v>
+        <v>7384</v>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>14927</t>
+          <t>15857</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>149514</t>
+          <t>149714</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>11141041</t>
+          <t>11157547</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>COR23 Pour Over</t>
+          <t>CCup Acero SBX Genérico</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>41041 C1P CORE POUR OVER</t>
+          <t>57547 C2P CORE SS CLDCP SFTC IVORY 24 OZ</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1631,12 +1627,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>COR23 Pour Over</t>
+          <t>CCup Acero SBX Genérico, SII26SSCC24White</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>lote-01/14927.jpeg</t>
+          <t>lote-01/15857.jpeg</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1657,31 +1653,31 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>7232</v>
+        <v>7252</v>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>16901</t>
+          <t>14927</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>154162</t>
+          <t>149514</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>11178937</t>
+          <t>11141041</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>WC26Mug12Stan</t>
+          <t>COR23 Pour Over</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>78937 C1P SM26 VAC MUG STANLEY CAMP 12OZ</t>
+          <t>41041 C1P CORE POUR OVER</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1696,12 +1692,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>WC26Mug12Stan</t>
+          <t>COR23 Pour Over</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>lote-01/011178937.jpeg</t>
+          <t>lote-01/14927.jpeg</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1711,7 +1707,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -1722,31 +1718,31 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>7181</v>
+        <v>7232</v>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>16901</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>161734</t>
+          <t>154162</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>11178946</t>
+          <t>11178937</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>WC26SS20Twist</t>
+          <t>WC26Mug12Stan</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>78946 C2P SM26 SS VAC WTR BTL TWIST</t>
+          <t>78937 C1P SM26 VAC MUG STANLEY CAMP 12OZ</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1761,12 +1757,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>WC26SS20Twist</t>
+          <t>WC26Mug12Stan</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>lote-01/011178946.jpg</t>
+          <t>lote-01/011178937.jpeg</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1787,31 +1783,31 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>7145</v>
+        <v>7181</v>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>154185</t>
+          <t>161734</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>11178973</t>
+          <t>11178946</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>WC26SS16Lid</t>
+          <t>WC26SS20Twist</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>78973 C2P SM26 SS TMBLR DRNK THRLD 16OZ</t>
+          <t>78946 C2P SM26 SS VAC WTR BTL TWIST</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1826,12 +1822,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>WC26SS16Lid</t>
+          <t>WC26SS20Twist</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>lote-01/011178973.jpg</t>
+          <t>lote-01/011178946.jpg</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1852,31 +1848,31 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>6561</v>
+        <v>7145</v>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>154141</t>
+          <t>154185</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>11178952</t>
+          <t>11178973</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>WC26SSCC24Grad</t>
+          <t>WC26SS16Lid</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>78952 C2P SM26 SS VAC CLD CUP GRDNT 24OZ</t>
+          <t>78973 C2P SM26 SS TMBLR DRNK THRLD 16OZ</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1891,12 +1887,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>WC26SSCC24Grad</t>
+          <t>WC26SS16Lid</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>lote-01/011178952.jpeg</t>
+          <t>lote-01/011178973.jpg</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1917,31 +1913,31 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>6131</v>
+        <v>6561</v>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>16995</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>156344</t>
+          <t>154141</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>11186650</t>
+          <t>11178952</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SII26SS16Pleat</t>
+          <t>WC26SSCC24Grad</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>86650 C2P FL26 SS TMBLR PLTD 16OZ</t>
+          <t>78952 C2P SM26 SS VAC CLD CUP GRDNT 24OZ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1956,12 +1952,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>SII26SS16Pleat</t>
+          <t>WC26SSCC24Grad</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>lote-01/011186650.jpeg</t>
+          <t>lote-01/011178952.jpeg</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1982,31 +1978,31 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>5063</v>
+        <v>6131</v>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>16995</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>154161</t>
+          <t>156344</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>11178941</t>
+          <t>11186650</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SII26SS16Studded</t>
+          <t>SII26SS16Pleat</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>78941 C2P SM26 SS TMBLR THRLD STDED 16OZ</t>
+          <t>86650 C2P FL26 SS TMBLR PLTD 16OZ</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2021,12 +2017,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SII26SS16Studded</t>
+          <t>SII26SS16Pleat</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>lote-01/011178941.jpeg</t>
+          <t>lote-01/011186650.jpeg</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2047,31 +2043,31 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>4708</v>
+        <v>5063</v>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>16879</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>154145</t>
+          <t>154161</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>11178922</t>
+          <t>11178941</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WC26Tu16Flower</t>
+          <t>SII26SS16Studded</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>78922 C2P SM26 PLSTC TMBLR SWIRL 16OZ</t>
+          <t>78941 C2P SM26 SS TMBLR THRLD STDED 16OZ</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2086,12 +2082,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>WC26Tu16Flower</t>
+          <t>SII26SS16Studded</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>lote-01/011178922.jpeg</t>
+          <t>lote-01/011178941.jpeg</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2112,31 +2108,31 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>4549</v>
+        <v>4708</v>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>16923</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>154183</t>
+          <t>154145</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>11178918</t>
+          <t>11178922</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>WC26Gl20Silicone</t>
+          <t>WC26Tu16Flower</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>78918 C1P SM26 GLSS CDCP SLCN BOOT 20OZ</t>
+          <t>78922 C2P SM26 PLSTC TMBLR SWIRL 16OZ</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2151,12 +2147,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>WC26Gl20Silicone</t>
+          <t>WC26Tu16Flower</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>lote-01/16923.jpeg</t>
+          <t>lote-01/011178922.jpeg</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2166,7 +2162,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -2177,31 +2173,31 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>4493</v>
+        <v>4549</v>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>16911</t>
+          <t>16923</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>154171</t>
+          <t>154183</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>11178971</t>
+          <t>11178918</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>WC26SS16Charm</t>
+          <t>WC26Gl20Silicone</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>78971 C2P SM26 SS VAC TMBLR CHRM 16OZ</t>
+          <t>78918 C1P SM26 GLSS CDCP SLCN BOOT 20OZ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2216,12 +2212,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>WC26SS16Charm</t>
+          <t>WC26Gl20Silicone</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>lote-01/011178971.jpeg</t>
+          <t>lote-01/16923.jpeg</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2231,7 +2227,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -2242,31 +2238,31 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>4307</v>
+        <v>4493</v>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>16911</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>154157</t>
+          <t>154171</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>11178970</t>
+          <t>11178971</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sp26SSCC16Band</t>
+          <t>WC26SS16Charm</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>78970 C2P SM26 SS CDCP BND THR LD 16OZ</t>
+          <t>78971 C2P SM26 SS VAC TMBLR CHRM 16OZ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2281,12 +2277,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Sp26SSCC16Band</t>
+          <t>WC26SS16Charm</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>lote-01/16896.jpeg</t>
+          <t>lote-01/011178971.jpeg</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2296,7 +2292,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -2307,31 +2303,31 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>4192</v>
+        <v>4307</v>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>16896</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>150033</t>
+          <t>154157</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178970</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sp26NEBlack</t>
+          <t>Sp26SSCC16Band</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>KIT GORRA NEGRA Y BLANCA NE CJ8PZAS</t>
+          <t>78970 C2P SM26 SS CDCP BND THR LD 16OZ</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2346,12 +2342,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Sp26NEBlack, Sp26NEWhite</t>
+          <t>Sp26SSCC16Band</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>lote-01/16531.jpeg</t>
+          <t>lote-01/16896.jpeg</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2372,31 +2368,31 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>4002</v>
+        <v>4192</v>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>16918</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>154178</t>
+          <t>150033</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>11178943</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sp26SS20Orange</t>
+          <t>Sp26NEBlack</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>78943 C2P SM26 SS VAC WTR BTL SHLL 20OZ</t>
+          <t>KIT GORRA NEGRA Y BLANCA NE CJ8PZAS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2411,12 +2407,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Sp26SS20Orange</t>
+          <t>Sp26NEBlack, Sp26NEWhite</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>lote-01/011178943.jpeg</t>
+          <t>lote-01/16531.jpeg</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2426,7 +2422,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -2437,31 +2433,31 @@
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>3238</v>
+        <v>4002</v>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>16955</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>155959</t>
+          <t>154178</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178943</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>WC26NESBX</t>
+          <t>Sp26SS20Orange</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>GORRA BLANCA Y NEGRA NE SBX CJ10PZAS</t>
+          <t>78943 C2P SM26 SS VAC WTR BTL SHLL 20OZ</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2476,12 +2472,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>WC26NESBX, WC26NESiren</t>
+          <t>Sp26SS20Orange</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>lote-01/16955.jpeg</t>
+          <t>lote-01/011178943.jpeg</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2491,7 +2487,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -2502,31 +2498,31 @@
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>3017</v>
+        <v>3238</v>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>16898</t>
+          <t>16955</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>155959</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>11178938</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sp26Tu16Mom</t>
+          <t>WC26NESBX</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>78938 C1P SM26 SS TMBLR DODL IT MOM 16OZ</t>
+          <t>GORRA BLANCA Y NEGRA NE SBX CJ10PZAS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2541,12 +2537,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Sp26Tu16Mom</t>
+          <t>WC26NESBX, WC26NESiren</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>lote-01/011178938.jpeg</t>
+          <t>lote-01/16955.jpeg</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2556,7 +2552,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -2567,31 +2563,31 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>2803</v>
+        <v>3017</v>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>16915</t>
+          <t>16898</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>154175</t>
+          <t>154159</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>11178948</t>
+          <t>11178938</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>WC26StanHand20</t>
+          <t>Sp26Tu16Mom</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>78948 C1P SM26 RCLD SS TMBLR STNLY 20OZ</t>
+          <t>78938 C1P SM26 SS TMBLR DODL IT MOM 16OZ</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2606,12 +2602,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>WC26StanHand20</t>
+          <t>Sp26Tu16Mom</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>lote-01/011178948.jpeg</t>
+          <t>lote-01/011178938.jpeg</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2632,31 +2628,31 @@
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>2790</v>
+        <v>2803</v>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>16915</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>154179</t>
+          <t>154175</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>11178957</t>
+          <t>11178948</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>WC26StanQuen30</t>
+          <t>WC26StanHand20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>78957 C1P SM26 RCLD SS TMBLR STNLY 30OZ</t>
+          <t>78948 C1P SM26 RCLD SS TMBLR STNLY 20OZ</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2671,12 +2667,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>WC26StanQuen30</t>
+          <t>WC26StanHand20</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>lote-01/011178957_1.jpg</t>
+          <t>lote-01/011178948.jpeg</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2697,31 +2693,31 @@
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>2589</v>
+        <v>2790</v>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>16919</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>152611</t>
+          <t>154179</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>11170174</t>
+          <t>11178957</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DiscCC24MxPais</t>
+          <t>WC26StanQuen30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>70174 C2P DIS PLSTC CLCP MEXICO 24OZ</t>
+          <t>78957 C1P SM26 RCLD SS TMBLR STNLY 30OZ</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2736,12 +2732,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>DiscCC24MxPais</t>
+          <t>WC26StanQuen30</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>lote-01/011170174.jpeg</t>
+          <t>lote-01/011178957_1.jpg</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2762,31 +2758,31 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>2529</v>
+        <v>2589</v>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>16924</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>154184</t>
+          <t>152611</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>11178945</t>
+          <t>11170174</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>WC26Stan20IceF</t>
+          <t>DiscCC24MxPais</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>78945 C1P SM26 SS VAC TMBLR STNLY 20OZ</t>
+          <t>70174 C2P DIS PLSTC CLCP MEXICO 24OZ</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2801,12 +2797,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>WC26Stan20IceF</t>
+          <t>DiscCC24MxPais</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>lote-01/011178945.jpeg</t>
+          <t>lote-01/011170174.jpeg</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2827,31 +2823,31 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>2521</v>
+        <v>2529</v>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>16378</t>
+          <t>16924</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>149967</t>
+          <t>154184</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178945</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>COR25CircCup</t>
+          <t>WC26Stan20IceF</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>40848 C8P VASO REUS RECYCLED COFFEE 12OZ</t>
+          <t>78945 C1P SM26 SS VAC TMBLR STNLY 20OZ</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2866,12 +2862,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>COR25CircCup</t>
+          <t>WC26Stan20IceF</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>lote-01/16378.jpeg</t>
+          <t>lote-01/011178945.jpeg</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2881,7 +2877,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -2892,27 +2888,31 @@
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>2297</v>
+        <v>2521</v>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>16977</t>
+          <t>16378</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>155974</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr"/>
+          <t>149967</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>IMÁN MÉXICO</t>
+          <t>COR25CircCup</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>IMAN BEARISTA MEXICO CJ15PZAS</t>
+          <t>40848 C8P VASO REUS RECYCLED COFFEE 12OZ</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>ImánMexico</t>
+          <t>COR25CircCup</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>lote-01/16977.jpeg</t>
+          <t>lote-01/16378.jpeg</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2953,31 +2953,27 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>2034</v>
+        <v>2297</v>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>16877</t>
+          <t>16977</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>154143</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>11178954</t>
-        </is>
-      </c>
+          <t>155974</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sp26SSCC24CarryC</t>
+          <t>IMÁN MÉXICO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>78954 C1P SM26 SS VAC HTCLD CUP 24OZ</t>
+          <t>IMAN BEARISTA MEXICO CJ15PZAS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2992,12 +2988,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Sp26SSCC24CarryC</t>
+          <t>ImánMexico</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>lote-01/16877.jpeg</t>
+          <t>lote-01/16977.jpeg</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3018,31 +3014,31 @@
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>1973</v>
+        <v>2034</v>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>16897</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>154158</t>
+          <t>154143</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>11178959</t>
+          <t>11178954</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>WC26CCSS24Puffy</t>
+          <t>Sp26SSCC24CarryC</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>78959 C2P SM26 SS CDCP PFFY GRDNT 24OZ</t>
+          <t>78954 C1P SM26 SS VAC HTCLD CUP 24OZ</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3057,12 +3053,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>WC26CCSS24Puffy</t>
+          <t>Sp26SSCC24CarryC</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>lote-01/011178959.jpeg</t>
+          <t>lote-01/16877.jpeg</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3072,7 +3068,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -3083,31 +3079,31 @@
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>1358</v>
+        <v>1973</v>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>16897</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>150092</t>
+          <t>154158</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>11141050</t>
+          <t>11178959</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>COR23 Tz14 Rain</t>
+          <t>WC26CCSS24Puffy</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>41050 C2P CORE CERMC MUG RAINBOW 14OZ</t>
+          <t>78959 C2P SM26 SS CDCP PFFY GRDNT 24OZ</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3122,12 +3118,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>COR23 Tz14 Rain</t>
+          <t>WC26CCSS24Puffy</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>lote-01/14885.jpeg</t>
+          <t>lote-01/011178959.jpeg</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3137,7 +3133,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -3148,31 +3144,31 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>1294</v>
+        <v>1358</v>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>14885</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>152594</t>
+          <t>150092</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>11176710</t>
+          <t>11141050</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sp26CC24Dome</t>
+          <t>COR23 Tz14 Rain</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>76710 C2P SP26 PLSTC CDCP DMLD 24OZ</t>
+          <t>41050 C2P CORE CERMC MUG RAINBOW 14OZ</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3187,12 +3183,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Sp26CC24Dome</t>
+          <t>COR23 Tz14 Rain</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>lote-01/011176710.jpeg</t>
+          <t>lote-01/14885.jpeg</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3202,7 +3198,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -3213,31 +3209,31 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>1208</v>
+        <v>1294</v>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>149939</t>
+          <t>152594</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>11160995</t>
+          <t>11176710</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>COR26BTL20</t>
+          <t>Sp26CC24Dome</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>60995 C2P CORE SS WTR BTL BEIGE 20OZ</t>
+          <t>76710 C2P SP26 PLSTC CDCP DMLD 24OZ</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3252,12 +3248,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>COR26BTL20</t>
+          <t>Sp26CC24Dome</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>lote-01/16312.jpeg</t>
+          <t>lote-01/011176710.jpeg</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3267,7 +3263,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -3278,31 +3274,31 @@
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>152968</t>
+          <t>149939</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>11176587</t>
+          <t>11160995</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SII26SSCC16Pony</t>
+          <t>COR26BTL20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>76587 C1P WN26 CCUP SS PONY 16OZ</t>
+          <t>60995 C2P CORE SS WTR BTL BEIGE 20OZ</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3317,12 +3313,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>SII26SSCC16Pony</t>
+          <t>COR26BTL20</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>lote-01/16720.jpeg</t>
+          <t>lote-01/16312.jpeg</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3343,31 +3339,31 @@
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>1180</v>
+        <v>1205</v>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>16720</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>154182</t>
+          <t>152968</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>11178919</t>
+          <t>11176587</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sp26Mug14Mom</t>
+          <t>SII26SSCC16Pony</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>78919 C2P SM26 STN MOM MUG 14OZ</t>
+          <t>76587 C1P WN26 CCUP SS PONY 16OZ</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3382,12 +3378,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Sp26Mug14Mom</t>
+          <t>SII26SSCC16Pony</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>lote-01/011178919.jpeg</t>
+          <t>lote-01/16720.jpeg</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3397,7 +3393,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -3408,31 +3404,31 @@
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>1097</v>
+        <v>1180</v>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>152967</t>
+          <t>154182</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>11176586</t>
+          <t>11178919</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SII26SSCC20Pony</t>
+          <t>Sp26Mug14Mom</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>76586 C1P WN26 CCUP SS PONIES 20OZ</t>
+          <t>78919 C2P SM26 STN MOM MUG 14OZ</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3447,12 +3443,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>SII26SSCC20Pony</t>
+          <t>Sp26Mug14Mom</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>lote-01/16719.jpeg</t>
+          <t>lote-01/011178919.jpeg</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3462,7 +3458,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -3473,31 +3469,31 @@
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>854</v>
+        <v>1097</v>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>152618</t>
+          <t>152967</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>11170147</t>
+          <t>11176586</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Disc2ozMxPais</t>
+          <t>SII26SSCC20Pony</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>70147 C4P DIS STN MUG MEXICO 2OZ</t>
+          <t>76586 C1P WN26 CCUP SS PONIES 20OZ</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3512,12 +3508,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Disc2ozMxPais</t>
+          <t>SII26SSCC20Pony</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>lote-01/011170147.jpeg</t>
+          <t>lote-01/16719.jpeg</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3527,7 +3523,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -3538,31 +3534,31 @@
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>732</v>
+        <v>854</v>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>150047</t>
+          <t>152618</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>11174776</t>
+          <t>11170147</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wt26Mug14Bow</t>
+          <t>Disc2ozMxPais</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>74776 C2P W26 STN MUG BOW 14OZ</t>
+          <t>70147 C4P DIS STN MUG MEXICO 2OZ</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3577,12 +3573,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Wt26Mug14Bow</t>
+          <t>Disc2ozMxPais</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>lote-01/16550.jpeg</t>
+          <t>lote-01/011170147.jpeg</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3592,7 +3588,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -3603,31 +3599,31 @@
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>150034</t>
+          <t>150047</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11174776</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sp26NELlavero</t>
+          <t>Wt26Mug14Bow</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>KIT POUCH Y LLAVERO NE CJ4PZAS</t>
+          <t>74776 C2P W26 STN MUG BOW 14OZ</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3642,12 +3638,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Sp26NECrossB, Sp26NELlavero</t>
+          <t>Wt26Mug14Bow</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>lote-01/16532.jpeg</t>
+          <t>lote-01/16550.jpeg</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3668,31 +3664,31 @@
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>576</v>
+        <v>725</v>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>152573</t>
+          <t>150034</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>11170102</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>DiscoveryCDMX</t>
+          <t>Sp26NELlavero</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>70102 C4P DIS STN MUG CDMX 14OZ</t>
+          <t>KIT POUCH Y LLAVERO NE CJ4PZAS</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3707,12 +3703,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>DiscoveryCDMX</t>
+          <t>Sp26NECrossB, Sp26NELlavero</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>lote-01/011170102.jpeg</t>
+          <t>lote-01/16532.jpeg</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3722,7 +3718,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -3733,31 +3729,31 @@
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>315</v>
+        <v>576</v>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>152541</t>
+          <t>152573</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>11170187</t>
+          <t>11170102</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ToteBag MxPais</t>
+          <t>DiscoveryCDMX</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>70187 P2P TOTE BAG MEXICO</t>
+          <t>70102 C4P DIS STN MUG CDMX 14OZ</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3772,12 +3768,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>ToteBag MxPais</t>
+          <t>DiscoveryCDMX</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>lote-01/011170187.jpeg</t>
+          <t>lote-01/011170102.jpeg</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3798,31 +3794,31 @@
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>16689</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>152619</t>
+          <t>152541</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>11170149</t>
+          <t>11170187</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Disc2ozCDMX</t>
+          <t>ToteBag MxPais</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>70149 C4P DIS STN MUG CDMX 2OZ</t>
+          <t>70187 P2P TOTE BAG MEXICO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3837,12 +3833,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Disc2ozCDMX</t>
+          <t>ToteBag MxPais</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>lote-01/011170149.jpeg</t>
+          <t>lote-01/011170187.jpeg</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3863,31 +3859,31 @@
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>53</v>
+        <v>278</v>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>152614</t>
+          <t>152619</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>11170158</t>
+          <t>11170149</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Disc2ozChiapas</t>
+          <t>Disc2ozCDMX</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>70158 C4P DIS STN MUG CHIAPAS 2OZ</t>
+          <t>70149 C4P DIS STN MUG CDMX 2OZ</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3902,12 +3898,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Disc2ozChiapas</t>
+          <t>Disc2ozCDMX</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>lote-01/011170158.jpeg</t>
+          <t>lote-01/011170149.jpeg</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3928,31 +3924,31 @@
         </is>
       </c>
       <c r="B58" s="7" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>155961</t>
+          <t>152614</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>11187372</t>
+          <t>11170158</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>WC26Tu24DW</t>
+          <t>Disc2ozChiapas</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>87372 C2P WC26 PLSTC CDCP FOOTBALL 24OZ</t>
+          <t>70158 C4P DIS STN MUG CHIAPAS 2OZ</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3967,12 +3963,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>WC26Tu24DW</t>
+          <t>Disc2ozChiapas</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>lote-01/16959.jpeg</t>
+          <t>lote-01/011170158.jpeg</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3982,7 +3978,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -3993,31 +3989,31 @@
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>154147</t>
+          <t>155961</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>11178933</t>
+          <t>11187372</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SII25CC24Gamer</t>
+          <t>WC26Tu24DW</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>78933 C2P SM26 PLSTC CLDCP GMR CHRM 24OZ</t>
+          <t>87372 C2P WC26 PLSTC CDCP FOOTBALL 24OZ</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4027,13 +4023,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SECUNDARIO</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>WC26Tu24DW</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>lote-01/011178933.jpeg</t>
+          <t>lote-01/16959.jpeg</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -4058,23 +4058,27 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>159943</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr"/>
+          <t>154147</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>11178933</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SII26GlCCColor</t>
+          <t>SII25CC24Gamer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>VASO VDR SODA TRANSP SBX 470ML CJ1PZA</t>
+          <t>78933 C2P SM26 PLSTC CLDCP GMR CHRM 24OZ</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4090,7 +4094,7 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>lote-01/017357.jpeg</t>
+          <t>lote-01/011178933.jpeg</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4100,7 +4104,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -4115,12 +4119,12 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>159944</t>
+          <t>159943</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr"/>
@@ -4131,7 +4135,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>VASO VDR SODA NARANJA SBX 470ML CJ1PZA</t>
+          <t>VASO VDR SODA TRANSP SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4147,7 +4151,7 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>lote-01/017358.jpeg</t>
+          <t>lote-01/017357.jpeg</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4172,12 +4176,12 @@
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>17359</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>159945</t>
+          <t>159944</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr"/>
@@ -4188,7 +4192,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>VASO VDR SODA ROJO SBX 470ML CJ1PZA</t>
+          <t>VASO VDR SODA NARANJA SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4204,7 +4208,7 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>lote-01/017359.jpeg</t>
+          <t>lote-01/017358.jpeg</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4221,25 +4225,33 @@
     <row r="63" ht="24" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>30824</v>
+        <v>0</v>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>52206</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr"/>
+          <t>17359</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>159945</t>
+        </is>
+      </c>
       <c r="E63" s="8" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vaso Rewards</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>SII26GlCCColor</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>VASO VDR SODA ROJO SBX 470ML CJ1PZA</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>NO</t>
@@ -4247,17 +4259,25 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ACTIVO</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Vaso Rewards</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
+          <t>SECUNDARIO</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>lote-01/017359.jpeg</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="24" customHeight="1">
       <c r="A64" t="inlineStr">

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -3144,31 +3144,31 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>1358</v>
+        <v>1508</v>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>16610</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>150092</t>
+          <t>152547</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>11141050</t>
+          <t>11179880</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>COR23 Tz14 Rain</t>
+          <t>SII26SS16Resort</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>41050 C2P CORE CERMC MUG RAINBOW 14OZ</t>
+          <t>79880 C1P SS TBLR BEARISTA RESORT 16OZ</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>COR23 Tz14 Rain</t>
+          <t>SII26SS16Resort</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>lote-01/14885.jpeg</t>
+          <t>lote-01/16610.jpeg</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3209,31 +3209,31 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>1294</v>
+        <v>1358</v>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>14885</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>152594</t>
+          <t>150092</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>11176710</t>
+          <t>11141050</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sp26CC24Dome</t>
+          <t>COR23 Tz14 Rain</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>76710 C2P SP26 PLSTC CDCP DMLD 24OZ</t>
+          <t>41050 C2P CORE CERMC MUG RAINBOW 14OZ</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3248,12 +3248,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Sp26CC24Dome</t>
+          <t>COR23 Tz14 Rain</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>lote-01/011176710.jpeg</t>
+          <t>lote-01/14885.jpeg</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -3274,31 +3274,31 @@
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>1208</v>
+        <v>1294</v>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>149939</t>
+          <t>152594</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>11160995</t>
+          <t>11176710</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>COR26BTL20</t>
+          <t>Sp26CC24Dome</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>60995 C2P CORE SS WTR BTL BEIGE 20OZ</t>
+          <t>76710 C2P SP26 PLSTC CDCP DMLD 24OZ</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>COR26BTL20</t>
+          <t>Sp26CC24Dome</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>lote-01/16312.jpeg</t>
+          <t>lote-01/011176710.jpeg</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -3339,31 +3339,31 @@
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>1205</v>
+        <v>1243</v>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>152968</t>
+          <t>154120</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>11176587</t>
+          <t>11179885</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SII26SSCC16Pony</t>
+          <t>SII26BTL20Resort</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>76587 C1P WN26 CCUP SS PONY 16OZ</t>
+          <t>79885 C2P SM126 WTBL BEAR RB 20OZ</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>SII26SSCC16Pony</t>
+          <t>SII26BTL20Resort</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>lote-01/16720.jpeg</t>
+          <t>lote-01/16777.jpeg</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3404,31 +3404,31 @@
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>1180</v>
+        <v>1208</v>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>154182</t>
+          <t>149939</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>11178919</t>
+          <t>11160995</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sp26Mug14Mom</t>
+          <t>COR26BTL20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>78919 C2P SM26 STN MOM MUG 14OZ</t>
+          <t>60995 C2P CORE SS WTR BTL BEIGE 20OZ</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Sp26Mug14Mom</t>
+          <t>COR26BTL20</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>lote-01/011178919.jpeg</t>
+          <t>lote-01/16312.jpeg</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -3469,31 +3469,31 @@
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>1097</v>
+        <v>1205</v>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>16720</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>152967</t>
+          <t>152968</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>11176586</t>
+          <t>11176587</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SII26SSCC20Pony</t>
+          <t>SII26SSCC16Pony</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>76586 C1P WN26 CCUP SS PONIES 20OZ</t>
+          <t>76587 C1P WN26 CCUP SS PONY 16OZ</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>SII26SSCC20Pony</t>
+          <t>SII26SSCC16Pony</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>lote-01/16719.jpeg</t>
+          <t>lote-01/16720.jpeg</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3534,31 +3534,31 @@
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>854</v>
+        <v>1180</v>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>152618</t>
+          <t>154182</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>11170147</t>
+          <t>11178919</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Disc2ozMxPais</t>
+          <t>Sp26Mug14Mom</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>70147 C4P DIS STN MUG MEXICO 2OZ</t>
+          <t>78919 C2P SM26 STN MOM MUG 14OZ</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3573,12 +3573,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Disc2ozMxPais</t>
+          <t>Sp26Mug14Mom</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>lote-01/011170147.jpeg</t>
+          <t>lote-01/011178919.jpeg</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3599,31 +3599,31 @@
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>732</v>
+        <v>1097</v>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>150047</t>
+          <t>152967</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>11174776</t>
+          <t>11176586</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wt26Mug14Bow</t>
+          <t>SII26SSCC20Pony</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>74776 C2P W26 STN MUG BOW 14OZ</t>
+          <t>76586 C1P WN26 CCUP SS PONIES 20OZ</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Wt26Mug14Bow</t>
+          <t>SII26SSCC20Pony</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>lote-01/16550.jpeg</t>
+          <t>lote-01/16719.jpeg</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3664,31 +3664,31 @@
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>725</v>
+        <v>854</v>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>150034</t>
+          <t>152618</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11170147</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sp26NELlavero</t>
+          <t>Disc2ozMxPais</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>KIT POUCH Y LLAVERO NE CJ4PZAS</t>
+          <t>70147 C4P DIS STN MUG MEXICO 2OZ</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Sp26NECrossB, Sp26NELlavero</t>
+          <t>Disc2ozMxPais</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>lote-01/16532.jpeg</t>
+          <t>lote-01/011170147.jpeg</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -3729,31 +3729,31 @@
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>576</v>
+        <v>732</v>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>152573</t>
+          <t>150047</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>11170102</t>
+          <t>11174776</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>DiscoveryCDMX</t>
+          <t>Wt26Mug14Bow</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>70102 C4P DIS STN MUG CDMX 14OZ</t>
+          <t>74776 C2P W26 STN MUG BOW 14OZ</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>DiscoveryCDMX</t>
+          <t>Wt26Mug14Bow</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>lote-01/011170102.jpeg</t>
+          <t>lote-01/16550.jpeg</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -3794,31 +3794,31 @@
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>315</v>
+        <v>725</v>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>152541</t>
+          <t>150034</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>11170187</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ToteBag MxPais</t>
+          <t>Sp26NELlavero</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>70187 P2P TOTE BAG MEXICO</t>
+          <t>KIT POUCH Y LLAVERO NE CJ4PZAS</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>ToteBag MxPais</t>
+          <t>Sp26NECrossB, Sp26NELlavero</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>lote-01/011170187.jpeg</t>
+          <t>lote-01/16532.jpeg</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -3859,31 +3859,31 @@
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>278</v>
+        <v>576</v>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>16689</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>152619</t>
+          <t>152573</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>11170149</t>
+          <t>11170102</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Disc2ozCDMX</t>
+          <t>DiscoveryCDMX</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>70149 C4P DIS STN MUG CDMX 2OZ</t>
+          <t>70102 C4P DIS STN MUG CDMX 14OZ</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Disc2ozCDMX</t>
+          <t>DiscoveryCDMX</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>lote-01/011170149.jpeg</t>
+          <t>lote-01/011170102.jpeg</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3924,31 +3924,31 @@
         </is>
       </c>
       <c r="B58" s="7" t="n">
-        <v>53</v>
+        <v>315</v>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>152614</t>
+          <t>152541</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>11170158</t>
+          <t>11170187</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Disc2ozChiapas</t>
+          <t>ToteBag MxPais</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>70158 C4P DIS STN MUG CHIAPAS 2OZ</t>
+          <t>70187 P2P TOTE BAG MEXICO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Disc2ozChiapas</t>
+          <t>ToteBag MxPais</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>lote-01/011170158.jpeg</t>
+          <t>lote-01/011170187.jpeg</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3989,31 +3989,31 @@
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>47</v>
+        <v>278</v>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>155961</t>
+          <t>152619</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>11187372</t>
+          <t>11170149</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>WC26Tu24DW</t>
+          <t>Disc2ozCDMX</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>87372 C2P WC26 PLSTC CDCP FOOTBALL 24OZ</t>
+          <t>70149 C4P DIS STN MUG CDMX 2OZ</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4028,12 +4028,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>WC26Tu24DW</t>
+          <t>Disc2ozCDMX</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>lote-01/16959.jpeg</t>
+          <t>lote-01/011170149.jpeg</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -4054,31 +4054,31 @@
         </is>
       </c>
       <c r="B60" s="7" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>154147</t>
+          <t>152614</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>11178933</t>
+          <t>11170158</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SII25CC24Gamer</t>
+          <t>Disc2ozChiapas</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>78933 C2P SM26 PLSTC CLDCP GMR CHRM 24OZ</t>
+          <t>70158 C4P DIS STN MUG CHIAPAS 2OZ</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4088,13 +4088,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SECUNDARIO</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Disc2ozChiapas</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>lote-01/011178933.jpeg</t>
+          <t>lote-01/011170158.jpeg</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4115,27 +4119,31 @@
         </is>
       </c>
       <c r="B61" s="7" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>159943</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr"/>
+          <t>155961</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>11187372</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SII26GlCCColor</t>
+          <t>WC26Tu24DW</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>VASO VDR SODA TRANSP SBX 470ML CJ1PZA</t>
+          <t>87372 C2P WC26 PLSTC CDCP FOOTBALL 24OZ</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4145,13 +4153,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SECUNDARIO</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>WC26Tu24DW</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>lote-01/017357.jpeg</t>
+          <t>lote-01/16959.jpeg</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4176,23 +4188,27 @@
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>159944</t>
-        </is>
-      </c>
-      <c r="E62" s="8" t="inlineStr"/>
+          <t>154147</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>11178933</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SII26GlCCColor</t>
+          <t>SII25CC24Gamer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>VASO VDR SODA NARANJA SBX 470ML CJ1PZA</t>
+          <t>78933 C2P SM26 PLSTC CLDCP GMR CHRM 24OZ</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4208,7 +4224,7 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>lote-01/017358.jpeg</t>
+          <t>lote-01/011178933.jpeg</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4218,7 +4234,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -4233,12 +4249,12 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>17359</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>159945</t>
+          <t>159943</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr"/>
@@ -4249,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>VASO VDR SODA ROJO SBX 470ML CJ1PZA</t>
+          <t>VASO VDR SODA TRANSP SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4265,7 +4281,7 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>lote-01/017359.jpeg</t>
+          <t>lote-01/017357.jpeg</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4282,104 +4298,116 @@
     <row r="64" ht="24" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B64" s="7" t="n">
-        <v>12340</v>
+        <v>0</v>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>15146</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>149531</t>
-        </is>
-      </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>159944</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stoppers SBX Genérico</t>
+          <t>SII26GlCCColor</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>TAPON P/VASO SOFT PVC C/DISENO CJ50PZAS</t>
+          <t>VASO VDR SODA NARANJA SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>ACTIVO</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Stoppers SBX Genérico</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+          <t>SECUNDARIO</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>lote-01/017358.jpeg</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B65" s="7" t="n">
-        <v>12340</v>
+        <v>0</v>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>150402</t>
+          <t>159945</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stoppers SBX Genérico</t>
+          <t>SII26GlCCColor</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>TAPON P/POPOTE SILICONA CJ100PZAS</t>
+          <t>VASO VDR SODA ROJO SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ACTIVO</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Stoppers SBX Genérico</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
+          <t>SECUNDARIO</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>lote-01/017359.jpeg</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" t="inlineStr">
@@ -4392,12 +4420,12 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>15146</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>149624</t>
+          <t>149531</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
@@ -4412,7 +4440,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>MANGA SILICON P/VASO CJ50PZAS</t>
+          <t>TAPON P/VASO SOFT PVC C/DISENO CJ50PZAS</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4445,19 +4473,15 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>15606</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>149625</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>150402</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>Stoppers SBX Genérico</t>
@@ -4465,7 +4489,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>TAPON P/POPOTE SILICONA CJ/50PZAS</t>
+          <t>TAPON P/POPOTE SILICONA CJ100PZAS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4498,12 +4522,12 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>15777</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>149681</t>
+          <t>149624</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
@@ -4518,7 +4542,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>PULSERA SILICON (11VERD/10NEG) CJ21PZAS</t>
+          <t>MANGA SILICON P/VASO CJ50PZAS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4551,12 +4575,12 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>15783</t>
+          <t>15606</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>149686</t>
+          <t>149625</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -4571,7 +4595,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>TAPON P/POPOTE SILICONA VXMC CJ50PZAS</t>
+          <t>TAPON P/POPOTE SILICONA CJ/50PZAS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4604,12 +4628,12 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>16079</t>
+          <t>15777</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>149785</t>
+          <t>149681</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
@@ -4624,7 +4648,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>TAPON SILICON P/POPOTE CELEB CJ25PZAS</t>
+          <t>PULSERA SILICON (11VERD/10NEG) CJ21PZAS</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4657,17 +4681,29 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>14527</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr"/>
-      <c r="E71" s="8" t="inlineStr"/>
+          <t>15783</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>149686</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>Stoppers SBX Genérico</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>TAPON P/POPOTE SILICONA VXMC CJ50PZAS</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>SÍ</t>
@@ -4698,20 +4734,32 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>53841</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr"/>
-      <c r="E72" s="8" t="inlineStr"/>
+          <t>16079</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>149785</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
           <t>Stoppers SBX Genérico</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>TAPON SILICON P/POPOTE CELEB CJ25PZAS</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4735,33 +4783,21 @@
         </is>
       </c>
       <c r="B73" s="7" t="n">
-        <v>10598</v>
+        <v>12340</v>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>15898</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>149735</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>14527</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr"/>
+      <c r="E73" s="8" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>KIT NAVIDENO CJ25KITS4PZAS</t>
-        </is>
-      </c>
+          <t>Stoppers SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>SÍ</t>
@@ -4774,7 +4810,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
+          <t>Stoppers SBX Genérico</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4788,36 +4824,24 @@
         </is>
       </c>
       <c r="B74" s="7" t="n">
-        <v>10598</v>
+        <v>12340</v>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>16106</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>149809</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>11160767</t>
-        </is>
-      </c>
+          <t>53841</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr"/>
+      <c r="E74" s="8" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>60767 C40P PNTS25 JOE KIND CUP SLEEVE</t>
-        </is>
-      </c>
+          <t>Stoppers SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4827,7 +4851,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
+          <t>Stoppers SBX Genérico</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4845,12 +4869,12 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>16077</t>
+          <t>15898</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>149783</t>
+          <t>149735</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -4865,12 +4889,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>TAPA P/STANLEY EASTER CJ5PZAS</t>
+          <t>KIT NAVIDENO CJ25KITS4PZAS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4898,13 +4922,17 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>12319</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr"/>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>149809</t>
+        </is>
+      </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>11101964</t>
+          <t>11160767</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4912,7 +4940,11 @@
           <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>60767 C40P PNTS25 JOE KIND CUP SLEEVE</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>SÍ</t>
@@ -4943,13 +4975,17 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>12395</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr"/>
+          <t>16077</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>149783</t>
+        </is>
+      </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>11101961</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4957,10 +4993,14 @@
           <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>TAPA P/STANLEY EASTER CJ5PZAS</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4988,13 +5028,13 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>12471</t>
+          <t>12319</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr"/>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>11091707</t>
+          <t>11101964</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5033,13 +5073,13 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr"/>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>11103794</t>
+          <t>11101961</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5078,13 +5118,13 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>12580</t>
+          <t>12471</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr"/>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>11109996</t>
+          <t>11091707</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5123,13 +5163,13 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>12581</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr"/>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>11109997</t>
+          <t>11103794</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5168,13 +5208,13 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr"/>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>11111777</t>
+          <t>11109996</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5213,13 +5253,13 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>12746</t>
+          <t>12581</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr"/>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>11113480</t>
+          <t>11109997</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5258,13 +5298,13 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>12920</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr"/>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>11117024</t>
+          <t>11111777</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5303,13 +5343,13 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>13458</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr"/>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>11121555</t>
+          <t>11113480</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5348,13 +5388,13 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>13851</t>
+          <t>12920</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr"/>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>11125966</t>
+          <t>11117024</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5393,13 +5433,13 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>13458</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr"/>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>11117063</t>
+          <t>11121555</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5438,13 +5478,13 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>13851</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr"/>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>11130716</t>
+          <t>11125966</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5483,13 +5523,13 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>15167</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr"/>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>11146257</t>
+          <t>11117063</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5528,13 +5568,13 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>15168</t>
+          <t>14342</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr"/>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>11146258</t>
+          <t>11130716</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5573,11 +5613,15 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>53844</t>
+          <t>15167</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr"/>
-      <c r="E91" s="8" t="inlineStr"/>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>11146257</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
           <t>Lifestyle SBX Genérico</t>
@@ -5586,7 +5630,7 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5610,36 +5654,28 @@
         </is>
       </c>
       <c r="B92" s="7" t="n">
-        <v>7551</v>
+        <v>10598</v>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>14886</t>
-        </is>
-      </c>
-      <c r="D92" s="8" t="inlineStr">
-        <is>
-          <t>149513</t>
-        </is>
-      </c>
+          <t>15168</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr"/>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>11141051</t>
+          <t>11146258</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>COR23 Tz14Green</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>41051 C2P CORE MUG DARK GREEN SIREN 14OZ</t>
-        </is>
-      </c>
+          <t>Lifestyle SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5649,7 +5685,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>COR23 Tz14Green</t>
+          <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -5663,33 +5699,21 @@
         </is>
       </c>
       <c r="B93" s="7" t="n">
-        <v>7513</v>
+        <v>10598</v>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>16903</t>
-        </is>
-      </c>
-      <c r="D93" s="8" t="inlineStr">
-        <is>
-          <t>154164</t>
-        </is>
-      </c>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t>11178926</t>
-        </is>
-      </c>
+          <t>53844</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr"/>
+      <c r="E93" s="8" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sp26CC24Or</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>78926 C2P SM26 PLSTC CDCP DOME LID 24OZ</t>
-        </is>
-      </c>
+          <t>Lifestyle SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>NO</t>
@@ -5702,7 +5726,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Sp26CC24Or</t>
+          <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -5716,36 +5740,36 @@
         </is>
       </c>
       <c r="B94" s="7" t="n">
-        <v>6944</v>
+        <v>7551</v>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>15128</t>
+          <t>14886</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>150104</t>
+          <t>149513</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11141051</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
+          <t>COR23 Tz14Green</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>LLAVERO OSO BEARISTA CJ50PZAS</t>
+          <t>41051 C2P CORE MUG DARK GREEN SIREN 14OZ</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5755,7 +5779,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
+          <t>COR23 Tz14Green</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -5769,36 +5793,36 @@
         </is>
       </c>
       <c r="B95" s="7" t="n">
-        <v>6944</v>
+        <v>7513</v>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>15163</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>149534</t>
+          <t>154164</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>11146255</t>
+          <t>11178926</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
+          <t>Sp26CC24Or</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>46255 P4P XM23 ORNAMENT METALLIC RED</t>
+          <t>78926 C2P SM26 PLSTC CDCP DOME LID 24OZ</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5808,7 +5832,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
+          <t>Sp26CC24Or</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -5826,17 +5850,17 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>149589</t>
+          <t>150104</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>11150774</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5846,7 +5870,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>50774 P4P S24 CLD CUP KEY CHAIN PLEATED</t>
+          <t>LLAVERO OSO BEARISTA CJ50PZAS</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5879,17 +5903,17 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>15513</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>149594</t>
+          <t>149534</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>11150776</t>
+          <t>11146255</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5899,7 +5923,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>50776 P4P S24 CLD CUP KEY CHAIN PRISM</t>
+          <t>46255 P4P XM23 ORNAMENT METALLIC RED</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5932,17 +5956,17 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>15526</t>
+          <t>15508</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>149606</t>
+          <t>149589</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>11150777</t>
+          <t>11150774</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5952,7 +5976,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>50777 P4P S24 COLD CUP KEY CHAIN BLING</t>
+          <t>50774 P4P S24 CLD CUP KEY CHAIN PLEATED</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5985,17 +6009,17 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>15513</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>149658</t>
+          <t>149594</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>11154026</t>
+          <t>11150776</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6005,7 +6029,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>54026 P4P F24 COLD CUP KEYCHAIN BLACK</t>
+          <t>50776 P4P S24 CLD CUP KEY CHAIN PRISM</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6038,17 +6062,17 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>15812</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>149699</t>
+          <t>149606</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>11157554</t>
+          <t>11150777</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6058,7 +6082,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>57554 P4P XM24 COLD CUP KEYCHAIN GREEN</t>
+          <t>50777 P4P S24 COLD CUP KEY CHAIN BLING</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6091,17 +6115,17 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>15842</t>
+          <t>15715</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>149706</t>
+          <t>149658</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>11157557</t>
+          <t>11154026</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6111,7 +6135,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>57557 P4P XM24 KEYCHAIN PLUG HOLIDAY</t>
+          <t>54026 P4P F24 COLD CUP KEYCHAIN BLACK</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6144,17 +6168,17 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>15812</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>149722</t>
+          <t>149699</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>11161850</t>
+          <t>11157554</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6164,7 +6188,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>61850 P4P WCK24 CLD CUP PRISM PVD GLINDA</t>
+          <t>57554 P4P XM24 COLD CUP KEYCHAIN GREEN</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6197,17 +6221,17 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>15842</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>149726</t>
+          <t>149706</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>11161851</t>
+          <t>11157557</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6217,7 +6241,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>61851 P4P WCK24 CLD CUP PLEATED ELPHABA</t>
+          <t>57557 P4P XM24 KEYCHAIN PLUG HOLIDAY</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6250,17 +6274,17 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>15883</t>
+          <t>15875</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>149730</t>
+          <t>149722</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>11161852</t>
+          <t>11161850</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6270,7 +6294,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>61852 P4P WCK24 CLD CUP GEMSTONE</t>
+          <t>61850 P4P WCK24 CLD CUP PRISM PVD GLINDA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6303,17 +6327,17 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>15879</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>149811</t>
+          <t>149726</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>11160769</t>
+          <t>11161851</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6323,7 +6347,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>60769 C16P PNTS25 KEYCHAIN JOE KIND</t>
+          <t>61851 P4P WCK24 CLD CUP PLEATED ELPHABA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6356,17 +6380,17 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>15883</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>150156</t>
+          <t>149730</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11161852</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6376,12 +6400,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>LLAVERO OSO BEARISTA ANO SERP CJ50PZAS</t>
+          <t>61852 P4P WCK24 CLD CUP GEMSTONE</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6409,17 +6433,17 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>15998</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>149752</t>
+          <t>149811</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11160769</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6429,12 +6453,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>LLAVERO OSO BEARISTA SAN VALENT CJ50PZAS</t>
+          <t>60769 C16P PNTS25 KEYCHAIN JOE KIND</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6462,13 +6486,17 @@
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>12980</t>
-        </is>
-      </c>
-      <c r="D108" s="8" t="inlineStr"/>
+          <t>15997</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t>150156</t>
+        </is>
+      </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>11118190</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6476,10 +6504,14 @@
           <t>Llavero SBX Genérico</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>LLAVERO OSO BEARISTA ANO SERP CJ50PZAS</t>
+        </is>
+      </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6507,20 +6539,32 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>14323</t>
-        </is>
-      </c>
-      <c r="D109" s="8" t="inlineStr"/>
-      <c r="E109" s="8" t="inlineStr"/>
+          <t>15998</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>149752</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>Llavero SBX Genérico</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>LLAVERO OSO BEARISTA SAN VALENT CJ50PZAS</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6548,13 +6592,13 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr"/>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>11141138</t>
+          <t>11118190</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6593,15 +6637,11 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>14323</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr"/>
-      <c r="E111" s="8" t="inlineStr">
-        <is>
-          <t>11144122</t>
-        </is>
-      </c>
+      <c r="E111" s="8" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>Llavero SBX Genérico</t>
@@ -6638,13 +6678,13 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>15368</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr"/>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>11147801</t>
+          <t>11141138</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6683,13 +6723,13 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>15784</t>
+          <t>15070</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr"/>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11144122</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6728,11 +6768,15 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>53840</t>
+          <t>15368</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr"/>
-      <c r="E114" s="8" t="inlineStr"/>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t>11147801</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr">
         <is>
           <t>Llavero SBX Genérico</t>
@@ -6741,7 +6785,7 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6765,36 +6809,28 @@
         </is>
       </c>
       <c r="B115" s="7" t="n">
-        <v>6932</v>
+        <v>6944</v>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>16178</t>
-        </is>
-      </c>
-      <c r="D115" s="8" t="inlineStr">
-        <is>
-          <t>149865</t>
-        </is>
-      </c>
+          <t>15784</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr"/>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>11164319</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SI25KeychainZoo</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>64319 P4P S25 SLCN KEYCHAIN BEAR GIRAFFE</t>
-        </is>
-      </c>
+          <t>Llavero SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6804,7 +6840,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>SI25KeychainZoo</t>
+          <t>Llavero SBX Genérico</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -6818,29 +6854,21 @@
         </is>
       </c>
       <c r="B116" s="7" t="n">
-        <v>4686</v>
+        <v>6944</v>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>17307</t>
-        </is>
-      </c>
-      <c r="D116" s="8" t="inlineStr">
-        <is>
-          <t>156359</t>
-        </is>
-      </c>
+          <t>53840</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr"/>
       <c r="E116" s="8" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SII26Doodle16</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>86651 C1P FL26 SS TMBLR DDLE IT 16OZ</t>
-        </is>
-      </c>
+          <t>Llavero SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
           <t>NO</t>
@@ -6853,7 +6881,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>SII26Doodle16</t>
+          <t>Llavero SBX Genérico</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -6867,31 +6895,31 @@
         </is>
       </c>
       <c r="B117" s="7" t="n">
-        <v>4195</v>
+        <v>6932</v>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>14926</t>
+          <t>16178</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>150102</t>
+          <t>149865</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>11141189</t>
+          <t>11164319</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>COR23 ToteBag</t>
+          <t>SI25KeychainZoo</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>41189 C2P CORE PLSTC REUS TOTE WFOLDABL</t>
+          <t>64319 P4P S25 SLCN KEYCHAIN BEAR GIRAFFE</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6906,7 +6934,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>COR23 ToteBag</t>
+          <t>SI25KeychainZoo</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -6920,31 +6948,27 @@
         </is>
       </c>
       <c r="B118" s="7" t="n">
-        <v>4168</v>
+        <v>4686</v>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>17307</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>152610</t>
-        </is>
-      </c>
-      <c r="E118" s="8" t="inlineStr">
-        <is>
-          <t>11177607</t>
-        </is>
-      </c>
+          <t>156359</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Wt26ReusSiren</t>
+          <t>SII26Doodle16</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>77607 P20P SP26 PLSTC RSBCLCP WMN 24OZ</t>
+          <t>86651 C1P FL26 SS TMBLR DDLE IT 16OZ</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -6959,7 +6983,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Wt26ReusSiren</t>
+          <t>SII26Doodle16</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -6973,31 +6997,31 @@
         </is>
       </c>
       <c r="B119" s="7" t="n">
-        <v>3964</v>
+        <v>4195</v>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>16917</t>
+          <t>14926</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>154177</t>
+          <t>150102</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>11178972</t>
+          <t>11141189</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sp26Vac16Stan</t>
+          <t>COR23 ToteBag</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>78972 C1P SM26 RCLD SS TMBLR STNLY 16OZ</t>
+          <t>41189 C2P CORE PLSTC REUS TOTE WFOLDABL</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7012,7 +7036,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Sp26Vac16Stan</t>
+          <t>COR23 ToteBag</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7026,27 +7050,31 @@
         </is>
       </c>
       <c r="B120" s="7" t="n">
-        <v>3769</v>
+        <v>4168</v>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>13694</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>150353</t>
-        </is>
-      </c>
-      <c r="E120" s="8" t="inlineStr"/>
+          <t>152610</t>
+        </is>
+      </c>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t>11177607</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Filtros Chemex</t>
+          <t>Wt26ReusSiren</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>FILTROS CUADRADOS CHEMEX CJ100PZAS</t>
+          <t>77607 P20P SP26 PLSTC RSBCLCP WMN 24OZ</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7061,7 +7089,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Filtros Chemex</t>
+          <t>Wt26ReusSiren</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7075,31 +7103,31 @@
         </is>
       </c>
       <c r="B121" s="7" t="n">
-        <v>3486</v>
+        <v>3964</v>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>154181</t>
+          <t>154177</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>11178917</t>
+          <t>11178972</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>WC26DW12Oran</t>
+          <t>Sp26Vac16Stan</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>78917 C1P SM26 STN DW TMBLR TWST 12OZ</t>
+          <t>78972 C1P SM26 RCLD SS TMBLR STNLY 16OZ</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7114,7 +7142,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>WC26Dw12Oran</t>
+          <t>Sp26Vac16Stan</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7128,31 +7156,27 @@
         </is>
       </c>
       <c r="B122" s="7" t="n">
-        <v>3068</v>
+        <v>3769</v>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>13694</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>154169</t>
-        </is>
-      </c>
-      <c r="E122" s="8" t="inlineStr">
-        <is>
-          <t>11178944</t>
-        </is>
-      </c>
+          <t>150353</t>
+        </is>
+      </c>
+      <c r="E122" s="8" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>WC26SS20BTL</t>
+          <t>Filtros Chemex</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>78944 C2P SM26 SS VAC WTR BTL 20OZ</t>
+          <t>FILTROS CUADRADOS CHEMEX CJ100PZAS</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7167,7 +7191,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>WC26SS20BTL</t>
+          <t>Filtros Chemex</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7181,31 +7205,31 @@
         </is>
       </c>
       <c r="B123" s="7" t="n">
-        <v>2785</v>
+        <v>3486</v>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>154149</t>
+          <t>154181</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>11178964</t>
+          <t>11178917</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sp26KeychainOr</t>
+          <t>WC26DW12Oran</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>78964 C4P SM26 PLSTC CLDCP DMLD KEYCHAIN</t>
+          <t>78917 C1P SM26 STN DW TMBLR TWST 12OZ</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7220,7 +7244,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Sp26KeychainOr</t>
+          <t>WC26Dw12Oran</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7234,31 +7258,31 @@
         </is>
       </c>
       <c r="B124" s="7" t="n">
-        <v>2665</v>
+        <v>3068</v>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>16080</t>
+          <t>16909</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>149786</t>
+          <t>154169</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178944</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SII25BdayStopper</t>
+          <t>WC26SS20BTL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>TAPON SILICON P/POPOTE CUMPLE CJ50PZAS</t>
+          <t>78944 C2P SM26 SS VAC WTR BTL 20OZ</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7273,7 +7297,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>SII25BdayStopper</t>
+          <t>WC26SS20BTL</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -7287,31 +7311,31 @@
         </is>
       </c>
       <c r="B125" s="7" t="n">
-        <v>2591</v>
+        <v>2785</v>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>152973</t>
+          <t>154149</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178964</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Wt26VasoJacaran</t>
+          <t>Sp26KeychainOr</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>VASO 470ML MORADO ALUMINIO OSO CJ25PZAS</t>
+          <t>78964 C4P SM26 PLSTC CLDCP DMLD KEYCHAIN</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -7326,7 +7350,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Wt26VasoJacaran</t>
+          <t>Sp26KeychainOr</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -7340,31 +7364,31 @@
         </is>
       </c>
       <c r="B126" s="7" t="n">
-        <v>2575</v>
+        <v>2665</v>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>16080</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>154142</t>
+          <t>149786</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>11178953</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sp26SSCC24Oran</t>
+          <t>SII25BdayStopper</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>78953 C2P SM26 SS VAC CLD CUP 24OZ</t>
+          <t>TAPON SILICON P/POPOTE CUMPLE CJ50PZAS</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -7379,7 +7403,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Sp26SSCC24Oran</t>
+          <t>SII25BdayStopper</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -7393,31 +7417,31 @@
         </is>
       </c>
       <c r="B127" s="7" t="n">
-        <v>2262</v>
+        <v>2591</v>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>154151</t>
+          <t>152973</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>11179003</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sp26CC24Teach</t>
+          <t>Wt26VasoJacaran</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>79003 C2P SM26 PLSTC CLDCP 24OZ</t>
+          <t>VASO 470ML MORADO ALUMINIO OSO CJ25PZAS</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -7432,7 +7456,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Sp26CC24Teach</t>
+          <t>Wt26VasoJacaran</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -7446,27 +7470,31 @@
         </is>
       </c>
       <c r="B128" s="7" t="n">
-        <v>2254</v>
+        <v>2575</v>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>17298</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>156350</t>
-        </is>
-      </c>
-      <c r="E128" s="8" t="inlineStr"/>
+          <t>154142</t>
+        </is>
+      </c>
+      <c r="E128" s="8" t="inlineStr">
+        <is>
+          <t>11178953</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SII26SSBTL12Aniv</t>
+          <t>Sp26SSCC24Oran</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>86647 C1P FL26 SS WTRBTL ANNVRSRY 12OZ</t>
+          <t>78953 C2P SM26 SS VAC CLD CUP 24OZ</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -7481,7 +7509,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>SII26SSBTL12Aniv</t>
+          <t>Sp26SSCC24Oran</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -7495,21 +7523,33 @@
         </is>
       </c>
       <c r="B129" s="7" t="n">
-        <v>2080</v>
+        <v>2262</v>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>54213</t>
-        </is>
-      </c>
-      <c r="D129" s="8" t="inlineStr"/>
-      <c r="E129" s="8" t="inlineStr"/>
+          <t>16885</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="inlineStr">
+        <is>
+          <t>154151</t>
+        </is>
+      </c>
+      <c r="E129" s="8" t="inlineStr">
+        <is>
+          <t>11179003</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>WC26Reus</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr"/>
+          <t>Sp26CC24Teach</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>79003 C2P SM26 PLSTC CLDCP 24OZ</t>
+        </is>
+      </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7522,7 +7562,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>WC26Reus</t>
+          <t>Sp26CC24Teach</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -7536,31 +7576,27 @@
         </is>
       </c>
       <c r="B130" s="7" t="n">
-        <v>1977</v>
+        <v>2254</v>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>16082</t>
+          <t>17298</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>149788</t>
-        </is>
-      </c>
-      <c r="E130" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>156350</t>
+        </is>
+      </c>
+      <c r="E130" s="8" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SII25ClipGirlB</t>
+          <t>SII26SSBTL12Aniv</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>CLIP P/TAZA SUMMER 2 CJ25PZAS</t>
+          <t>86647 C1P FL26 SS WTRBTL ANNVRSRY 12OZ</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -7575,7 +7611,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>SII25ClipGirlB</t>
+          <t>SII26SSBTL12Aniv</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -7589,33 +7625,21 @@
         </is>
       </c>
       <c r="B131" s="7" t="n">
-        <v>1977</v>
+        <v>2080</v>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>16343</t>
-        </is>
-      </c>
-      <c r="D131" s="8" t="inlineStr">
-        <is>
-          <t>149957</t>
-        </is>
-      </c>
-      <c r="E131" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>54213</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="inlineStr"/>
+      <c r="E131" s="8" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SII25ClipGirlB</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>LLAVERO ALOHA CJ50PZAS</t>
-        </is>
-      </c>
+          <t>WC26Reus</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7628,7 +7652,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>SII25ClipGirlB</t>
+          <t>WC26Reus</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -7642,27 +7666,31 @@
         </is>
       </c>
       <c r="B132" s="7" t="n">
-        <v>1832</v>
+        <v>1977</v>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>16989</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>156338</t>
-        </is>
-      </c>
-      <c r="E132" s="8" t="inlineStr"/>
+          <t>149788</t>
+        </is>
+      </c>
+      <c r="E132" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SII26SS12Aniv</t>
+          <t>SII25ClipGirlB</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>86648 C2P FL26 SS TMBLR ANVRSRY 12OZ</t>
+          <t>CLIP P/TAZA SUMMER 2 CJ25PZAS</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -7677,7 +7705,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>SII26SS12Aniv</t>
+          <t>SII25ClipGirlB</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -7691,31 +7719,31 @@
         </is>
       </c>
       <c r="B133" s="7" t="n">
-        <v>1803</v>
+        <v>1977</v>
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>16343</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>150060</t>
+          <t>149957</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>11174791</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Wt26ReusSV</t>
+          <t>SII25ClipGirlB</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>74791 P20P W26 PLS REUSE HTCP LD 16OZ</t>
+          <t>LLAVERO ALOHA CJ50PZAS</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -7730,7 +7758,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Wt26ReusSV</t>
+          <t>SII25ClipGirlB</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -7744,31 +7772,27 @@
         </is>
       </c>
       <c r="B134" s="7" t="n">
-        <v>1793</v>
+        <v>1832</v>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t>16989</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>149516</t>
-        </is>
-      </c>
-      <c r="E134" s="8" t="inlineStr">
-        <is>
-          <t>11141040</t>
-        </is>
-      </c>
+          <t>156338</t>
+        </is>
+      </c>
+      <c r="E134" s="8" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>COR23 PrensaFran</t>
+          <t>SII26SS12Aniv</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>41040 C1P CORE COFFEE PRESS 34OZ</t>
+          <t>86648 C2P FL26 SS TMBLR ANVRSRY 12OZ</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -7783,7 +7807,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>COR23 PrensaFran</t>
+          <t>SII26SS12Aniv</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -7797,31 +7821,31 @@
         </is>
       </c>
       <c r="B135" s="7" t="n">
-        <v>1766</v>
+        <v>1803</v>
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>154166</t>
+          <t>150060</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>11178966</t>
+          <t>11174791</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>WC26TotePride</t>
+          <t>Wt26ReusSV</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>78966 P2P SM26 CANVAS TOTE BAG PRIDE</t>
+          <t>74791 P20P W26 PLS REUSE HTCP LD 16OZ</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -7836,7 +7860,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>WC26TotePride</t>
+          <t>Wt26ReusSV</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -7850,31 +7874,31 @@
         </is>
       </c>
       <c r="B136" s="7" t="n">
-        <v>1764</v>
+        <v>1793</v>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>154174</t>
+          <t>149516</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>11178947</t>
+          <t>11141040</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sp26StanQuen20</t>
+          <t>COR23 PrensaFran</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>78947 C1P SM26 RCLD SS TMBLR STNLY 20OZ</t>
+          <t>41040 C1P CORE COFFEE PRESS 34OZ</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -7889,7 +7913,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Sp26StanQuen20</t>
+          <t>COR23 PrensaFran</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -7903,31 +7927,31 @@
         </is>
       </c>
       <c r="B137" s="7" t="n">
-        <v>1744</v>
+        <v>1766</v>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>15191</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>150106</t>
+          <t>154166</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>11144107</t>
+          <t>11178966</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>COR23 CC24 Green</t>
+          <t>WC26TotePride</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>44107 C2P CORE COLD CUP SOFT TOUCH 24OZ</t>
+          <t>78966 P2P SM26 CANVAS TOTE BAG PRIDE</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -7942,7 +7966,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>COR23 CC24 Green</t>
+          <t>WC26TotePride</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -7956,31 +7980,31 @@
         </is>
       </c>
       <c r="B138" s="7" t="n">
-        <v>1719</v>
+        <v>1764</v>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>16914</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>154165</t>
+          <t>154174</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>11178965</t>
+          <t>11178947</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>WC26ToteRoad</t>
+          <t>Sp26StanQuen20</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>78965 P2P SM26 CANVAS TOTE BAG SEASIDE</t>
+          <t>78947 C1P SM26 RCLD SS TMBLR STNLY 20OZ</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -7995,7 +8019,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>WC26ToteRoad</t>
+          <t>Sp26StanQuen20</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8009,31 +8033,31 @@
         </is>
       </c>
       <c r="B139" s="7" t="n">
-        <v>1657</v>
+        <v>1744</v>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>16682</t>
+          <t>15191</t>
         </is>
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>152612</t>
+          <t>150106</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>11170184</t>
+          <t>11144107</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>DiscSS20MxPais</t>
+          <t>COR23 CC24 Green</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>70184 C2P DIS SS VAC TBLR MEXICO 16OZ</t>
+          <t>44107 C2P CORE COLD CUP SOFT TOUCH 24OZ</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8048,7 +8072,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>DiscSS20MxPais</t>
+          <t>COR23 CC24 Green</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8062,31 +8086,31 @@
         </is>
       </c>
       <c r="B140" s="7" t="n">
-        <v>1637</v>
+        <v>1719</v>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>152972</t>
+          <t>154165</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178965</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Wt26VasoFresa</t>
+          <t>WC26ToteRoad</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>VASO 470ML ROSA ALUMINIO FRESA CJ25PZAS</t>
+          <t>78965 P2P SM26 CANVAS TOTE BAG SEASIDE</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8101,7 +8125,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Wt26VasoFresa</t>
+          <t>WC26ToteRoad</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8115,31 +8139,31 @@
         </is>
       </c>
       <c r="B141" s="7" t="n">
-        <v>1538</v>
+        <v>1657</v>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>16264</t>
+          <t>16682</t>
         </is>
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>149896</t>
+          <t>152612</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>11160967</t>
+          <t>11170184</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>COR26PPBTL20S</t>
+          <t>DiscSS20MxPais</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>60967 C2P CORE RECYCL WTR BTL BEIGE 24OZ</t>
+          <t>70184 C2P DIS SS VAC TBLR MEXICO 16OZ</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -8154,7 +8178,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>COR26PPBTL20S</t>
+          <t>DiscSS20MxPais</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -8168,31 +8192,31 @@
         </is>
       </c>
       <c r="B142" s="7" t="n">
-        <v>1508</v>
+        <v>1637</v>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>16610</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>152547</t>
+          <t>152972</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>11179880</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>SII26SS16Resort</t>
+          <t>Wt26VasoFresa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>79880 C1P SS TBLR BEARISTA RESORT 16OZ</t>
+          <t>VASO 470ML ROSA ALUMINIO FRESA CJ25PZAS</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -8207,7 +8231,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>SII26SS16Resort</t>
+          <t>Wt26VasoFresa</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -8221,27 +8245,31 @@
         </is>
       </c>
       <c r="B143" s="7" t="n">
-        <v>1481</v>
+        <v>1538</v>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>16722</t>
+          <t>16264</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>152970</t>
-        </is>
-      </c>
-      <c r="E143" s="8" t="inlineStr"/>
+          <t>149896</t>
+        </is>
+      </c>
+      <c r="E143" s="8" t="inlineStr">
+        <is>
+          <t>11160967</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>BearHuggerSpring</t>
+          <t>COR26PPBTL20S</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>OSO PELUCHE PASCUA CJ32PZAS</t>
+          <t>60967 C2P CORE RECYCL WTR BTL BEIGE 24OZ</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -8256,7 +8284,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>BearHuggerSpring</t>
+          <t>COR26PPBTL20S</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -8270,31 +8298,27 @@
         </is>
       </c>
       <c r="B144" s="7" t="n">
-        <v>1429</v>
+        <v>1481</v>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>152602</t>
-        </is>
-      </c>
-      <c r="E144" s="8" t="inlineStr">
-        <is>
-          <t>11176724</t>
-        </is>
-      </c>
+          <t>152970</t>
+        </is>
+      </c>
+      <c r="E144" s="8" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Sp26CookieJP</t>
+          <t>BearHuggerSpring</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>76724 C1P SP26 STN COOKIE JAR LUSTER</t>
+          <t>OSO PELUCHE PASCUA CJ32PZAS</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -8309,7 +8333,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Sp26CookieJP</t>
+          <t>BearHuggerSpring</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -8323,31 +8347,31 @@
         </is>
       </c>
       <c r="B145" s="7" t="n">
-        <v>1403</v>
+        <v>1429</v>
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>154122</t>
+          <t>152602</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>11176592</t>
+          <t>11176724</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>SII26SSTu12Pony</t>
+          <t>Sp26CookieJP</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>76592 C1P WIN TBLR PONNIES 12OZ</t>
+          <t>76724 C1P SP26 STN COOKIE JAR LUSTER</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -8362,7 +8386,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>SII26SSTu12Pony</t>
+          <t>Sp26CookieJP</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -8376,31 +8400,31 @@
         </is>
       </c>
       <c r="B146" s="7" t="n">
-        <v>1311</v>
+        <v>1403</v>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>16779</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>154127</t>
+          <t>154122</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>1176593</t>
+          <t>11176592</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SII26BTL16Pony</t>
+          <t>SII26SSTu12Pony</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>76593 C1P W26 WTBL SS PONY AND FLWR 16OZ</t>
+          <t>76592 C1P WIN TBLR PONNIES 12OZ</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -8415,7 +8439,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>SII26BTL16Pony</t>
+          <t>SII26SSTu12Pony</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -8429,21 +8453,33 @@
         </is>
       </c>
       <c r="B147" s="7" t="n">
-        <v>1300</v>
+        <v>1311</v>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>54192</t>
-        </is>
-      </c>
-      <c r="D147" s="8" t="inlineStr"/>
-      <c r="E147" s="8" t="inlineStr"/>
+          <t>16793</t>
+        </is>
+      </c>
+      <c r="D147" s="8" t="inlineStr">
+        <is>
+          <t>154127</t>
+        </is>
+      </c>
+      <c r="E147" s="8" t="inlineStr">
+        <is>
+          <t>1176593</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SII26GICCColor</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr"/>
+          <t>SII26BTL16Pony</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>76593 C1P W26 WTBL SS PONY AND FLWR 16OZ</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8456,7 +8492,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>SII26GICCColor</t>
+          <t>SII26BTL16Pony</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -8470,29 +8506,21 @@
         </is>
       </c>
       <c r="B148" s="7" t="n">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>17299</t>
-        </is>
-      </c>
-      <c r="D148" s="8" t="inlineStr">
-        <is>
-          <t>156351</t>
-        </is>
-      </c>
+          <t>54192</t>
+        </is>
+      </c>
+      <c r="D148" s="8" t="inlineStr"/>
       <c r="E148" s="8" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SII26Mug14Aniv</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>86632 C2P FL26 STN MUG SCALIE 14OZ</t>
-        </is>
-      </c>
+          <t>SII26GICCColor</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8505,7 +8533,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>SII26Mug14Aniv</t>
+          <t>SII26GICCColor</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -8519,31 +8547,27 @@
         </is>
       </c>
       <c r="B149" s="7" t="n">
-        <v>1277</v>
+        <v>1298</v>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>16081</t>
+          <t>17299</t>
         </is>
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>149787</t>
-        </is>
-      </c>
-      <c r="E149" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>156351</t>
+        </is>
+      </c>
+      <c r="E149" s="8" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SII25ClipBoyB</t>
+          <t>SII26Mug14Aniv</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>CLIP P/TAZA SUMMER 1 CJ25PZAS</t>
+          <t>86632 C2P FL26 STN MUG SCALIE 14OZ</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -8558,7 +8582,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>SII25ClipBoyB</t>
+          <t>SII26Mug14Aniv</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -8572,16 +8596,16 @@
         </is>
       </c>
       <c r="B150" s="7" t="n">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>16502</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>150023</t>
+          <t>149787</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
@@ -8591,12 +8615,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Xm25Tag</t>
+          <t>SII25ClipBoyB</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>TAG MALETA OSO CJ25PZAS</t>
+          <t>CLIP P/TAZA SUMMER 1 CJ25PZAS</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -8611,7 +8635,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Xm25Tag</t>
+          <t>SII25ClipBoyB</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -8629,17 +8653,29 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>53962</t>
-        </is>
-      </c>
-      <c r="D151" s="8" t="inlineStr"/>
-      <c r="E151" s="8" t="inlineStr"/>
+          <t>16502</t>
+        </is>
+      </c>
+      <c r="D151" s="8" t="inlineStr">
+        <is>
+          <t>150023</t>
+        </is>
+      </c>
+      <c r="E151" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F151" t="inlineStr">
         <is>
           <t>Xm25Tag</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>TAG MALETA OSO CJ25PZAS</t>
+        </is>
+      </c>
       <c r="H151" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8666,33 +8702,21 @@
         </is>
       </c>
       <c r="B152" s="7" t="n">
-        <v>1254</v>
+        <v>1276</v>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>16642</t>
-        </is>
-      </c>
-      <c r="D152" s="8" t="inlineStr">
-        <is>
-          <t>152572</t>
-        </is>
-      </c>
-      <c r="E152" s="8" t="inlineStr">
-        <is>
-          <t>11170100</t>
-        </is>
-      </c>
+          <t>53962</t>
+        </is>
+      </c>
+      <c r="D152" s="8" t="inlineStr"/>
+      <c r="E152" s="8" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>DiscoveryMxPaís</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>70100 C4P DIS STN MUG MEXICO 14OZ</t>
-        </is>
-      </c>
+          <t>Xm25Tag</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8705,7 +8729,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>DiscoveryMxPais</t>
+          <t>Xm25Tag</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -8719,31 +8743,31 @@
         </is>
       </c>
       <c r="B153" s="7" t="n">
-        <v>1243</v>
+        <v>1254</v>
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>16777</t>
+          <t>16642</t>
         </is>
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>154120</t>
+          <t>152572</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>11179885</t>
+          <t>11170100</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>SII26BTL20Resort</t>
+          <t>DiscoveryMxPaís</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>79885 C2P SM126 WTBL BEAR RB 20OZ</t>
+          <t>70100 C4P DIS STN MUG MEXICO 14OZ</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -8758,7 +8782,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>SII26BTL20Resort</t>
+          <t>DiscoveryMxPais</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -3144,31 +3144,27 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>2034</v>
+        <v>2254</v>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>16877</t>
+          <t>17298</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>154143</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>11178954</t>
-        </is>
-      </c>
+          <t>156350</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sp26SSCC24CarryC</t>
+          <t>SII26SSBTL12Aniv</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>78954 C1P SM26 SS VAC HTCLD CUP 24OZ</t>
+          <t>86647 C1P FL26 SS WTRBTL ANNVRSRY 12OZ</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3183,12 +3179,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Sp26SSCC24CarryC</t>
+          <t>SII26SSBTL12Aniv</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>lote-01/16877.jpeg</t>
+          <t>lote-01/17298.jpeg</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3209,31 +3205,31 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>1973</v>
+        <v>2034</v>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>16897</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>154158</t>
+          <t>154143</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>11178959</t>
+          <t>11178954</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>WC26CCSS24Puffy</t>
+          <t>Sp26SSCC24CarryC</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>78959 C2P SM26 SS CDCP PFFY GRDNT 24OZ</t>
+          <t>78954 C1P SM26 SS VAC HTCLD CUP 24OZ</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3248,12 +3244,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>WC26CCSS24Puffy</t>
+          <t>Sp26SSCC24CarryC</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>lote-01/011178959.jpeg</t>
+          <t>lote-01/16877.jpeg</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3263,7 +3259,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -3274,31 +3270,31 @@
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>1764</v>
+        <v>1973</v>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>16897</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>154174</t>
+          <t>154158</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>11178947</t>
+          <t>11178959</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sp26StanQuen20</t>
+          <t>WC26CCSS24Puffy</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>78947 C1P SM26 RCLD SS TMBLR STNLY 20OZ</t>
+          <t>78959 C2P SM26 SS CDCP PFFY GRDNT 24OZ</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3313,12 +3309,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Sp26StanQuen20</t>
+          <t>WC26CCSS24Puffy</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>lote-01/16914.jpeg</t>
+          <t>lote-01/011178959.jpeg</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3328,7 +3324,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -3339,31 +3335,27 @@
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>1508</v>
+        <v>1832</v>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>16610</t>
+          <t>16989</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>152547</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>11179880</t>
-        </is>
-      </c>
+          <t>156338</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SII26SS16Resort</t>
+          <t>SII26SS12Aniv</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>79880 C1P SS TBLR BEARISTA RESORT 16OZ</t>
+          <t>86648 C2P FL26 SS TMBLR ANVRSRY 12OZ</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3378,12 +3370,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>SII26SS16Resort</t>
+          <t>SII26SS12Aniv</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>lote-01/16610.jpeg</t>
+          <t>lote-01/16989.jpeg</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3404,31 +3396,31 @@
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>1358</v>
+        <v>1764</v>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>16914</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>150092</t>
+          <t>154174</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>11141050</t>
+          <t>11178947</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>COR23 Tz14 Rain</t>
+          <t>Sp26StanQuen20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>41050 C2P CORE CERMC MUG RAINBOW 14OZ</t>
+          <t>78947 C1P SM26 RCLD SS TMBLR STNLY 20OZ</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3443,12 +3435,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>COR23 Tz14 Rain</t>
+          <t>Sp26StanQuen20</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>lote-01/14885.jpeg</t>
+          <t>lote-01/16914.jpeg</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3469,31 +3461,31 @@
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>1294</v>
+        <v>1508</v>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>16610</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>152594</t>
+          <t>152547</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>11176710</t>
+          <t>11179880</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sp26CC24Dome</t>
+          <t>SII26SS16Resort</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>76710 C2P SP26 PLSTC CDCP DMLD 24OZ</t>
+          <t>79880 C1P SS TBLR BEARISTA RESORT 16OZ</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3508,12 +3500,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Sp26CC24Dome</t>
+          <t>SII26SS16Resort</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>lote-01/011176710.jpeg</t>
+          <t>lote-01/16610.jpeg</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3523,7 +3515,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -3534,31 +3526,31 @@
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>1243</v>
+        <v>1358</v>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>16777</t>
+          <t>14885</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>154120</t>
+          <t>150092</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>11179885</t>
+          <t>11141050</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SII26BTL20Resort</t>
+          <t>COR23 Tz14 Rain</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>79885 C2P SM126 WTBL BEAR RB 20OZ</t>
+          <t>41050 C2P CORE CERMC MUG RAINBOW 14OZ</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3573,12 +3565,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>SII26BTL20Resort</t>
+          <t>COR23 Tz14 Rain</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>lote-01/16777.jpeg</t>
+          <t>lote-01/14885.jpeg</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3599,31 +3591,27 @@
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>1208</v>
+        <v>1298</v>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>16125</t>
+          <t>17299</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>149823</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>11164285</t>
-        </is>
-      </c>
+          <t>156351</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SI25CC24Colors</t>
+          <t>SII26Mug14Aniv</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>64285 C2P S25 CLD CUP COLORED WAVES 24OZ</t>
+          <t>86632 C2P FL26 STN MUG SCALIE 14OZ</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3638,12 +3626,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>SI25CC24Colors</t>
+          <t>SII26Mug14Aniv</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>lote-01/16125.jpeg</t>
+          <t>lote-01/17299.jpeg</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3664,31 +3652,31 @@
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>1208</v>
+        <v>1294</v>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>149939</t>
+          <t>152594</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>11160995</t>
+          <t>11176710</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>COR26BTL20</t>
+          <t>Sp26CC24Dome</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>60995 C2P CORE SS WTR BTL BEIGE 20OZ</t>
+          <t>76710 C2P SP26 PLSTC CDCP DMLD 24OZ</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3703,12 +3691,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>COR26BTL20</t>
+          <t>Sp26CC24Dome</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>lote-01/16312.jpeg</t>
+          <t>lote-01/011176710.jpeg</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3718,7 +3706,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -3729,31 +3717,31 @@
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>1205</v>
+        <v>1243</v>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>152968</t>
+          <t>154120</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>11176587</t>
+          <t>11179885</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SII26SSCC16Pony</t>
+          <t>SII26BTL20Resort</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>76587 C1P WN26 CCUP SS PONY 16OZ</t>
+          <t>79885 C2P SM126 WTBL BEAR RB 20OZ</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3768,12 +3756,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>SII26SSCC16Pony</t>
+          <t>SII26BTL20Resort</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>lote-01/16720.jpeg</t>
+          <t>lote-01/16777.jpeg</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3794,31 +3782,31 @@
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>1180</v>
+        <v>1208</v>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>16125</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>154182</t>
+          <t>149823</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>11178919</t>
+          <t>11164285</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sp26Mug14Mom</t>
+          <t>SI25CC24Colors</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>78919 C2P SM26 STN MOM MUG 14OZ</t>
+          <t>64285 C2P S25 CLD CUP COLORED WAVES 24OZ</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3833,12 +3821,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Sp26Mug14Mom</t>
+          <t>SI25CC24Colors</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>lote-01/011178919.jpeg</t>
+          <t>lote-01/16125.jpeg</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3848,7 +3836,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -3859,31 +3847,31 @@
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>1097</v>
+        <v>1208</v>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>152967</t>
+          <t>149939</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>11176586</t>
+          <t>11160995</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SII26SSCC20Pony</t>
+          <t>COR26BTL20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>76586 C1P WN26 CCUP SS PONIES 20OZ</t>
+          <t>60995 C2P CORE SS WTR BTL BEIGE 20OZ</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3898,12 +3886,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>SII26SSCC20Pony</t>
+          <t>COR26BTL20</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>lote-01/16719.jpeg</t>
+          <t>lote-01/16312.jpeg</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3924,31 +3912,31 @@
         </is>
       </c>
       <c r="B58" s="7" t="n">
-        <v>939</v>
+        <v>1205</v>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>16720</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>149978</t>
+          <t>152968</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>11173047</t>
+          <t>11176587</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Xm25Tz14Glass</t>
+          <t>SII26SSCC16Pony</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>73047 C2P XM25 GLASS MUG HOL RIBBON 14OZ</t>
+          <t>76587 C1P WN26 CCUP SS PONY 16OZ</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3963,12 +3951,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Xm25Tz14Glass</t>
+          <t>SII26SSCC16Pony</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>lote-01/16438.jpeg</t>
+          <t>lote-01/16720.jpeg</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3989,31 +3977,31 @@
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>854</v>
+        <v>1180</v>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>152618</t>
+          <t>154182</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>11170147</t>
+          <t>11178919</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Disc2ozMxPais</t>
+          <t>Sp26Mug14Mom</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>70147 C4P DIS STN MUG MEXICO 2OZ</t>
+          <t>78919 C2P SM26 STN MOM MUG 14OZ</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4028,12 +4016,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Disc2ozMxPais</t>
+          <t>Sp26Mug14Mom</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>lote-01/011170147.jpeg</t>
+          <t>lote-01/011178919.jpeg</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4054,31 +4042,31 @@
         </is>
       </c>
       <c r="B60" s="7" t="n">
-        <v>732</v>
+        <v>1097</v>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>150047</t>
+          <t>152967</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>11174776</t>
+          <t>11176586</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Wt26Mug14Bow</t>
+          <t>SII26SSCC20Pony</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>74776 C2P W26 STN MUG BOW 14OZ</t>
+          <t>76586 C1P WN26 CCUP SS PONIES 20OZ</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4093,12 +4081,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Wt26Mug14Bow</t>
+          <t>SII26SSCC20Pony</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>lote-01/16550.jpeg</t>
+          <t>lote-01/16719.jpeg</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4119,31 +4107,31 @@
         </is>
       </c>
       <c r="B61" s="7" t="n">
-        <v>725</v>
+        <v>939</v>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>16438</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>150034</t>
+          <t>149978</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11173047</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sp26NELlavero</t>
+          <t>Xm25Tz14Glass</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>KIT POUCH Y LLAVERO NE CJ4PZAS</t>
+          <t>73047 C2P XM25 GLASS MUG HOL RIBBON 14OZ</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4158,12 +4146,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Sp26NECrossB, Sp26NELlavero</t>
+          <t>Xm25Tz14Glass</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>lote-01/16532.jpeg</t>
+          <t>lote-01/16438.jpeg</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4184,31 +4172,31 @@
         </is>
       </c>
       <c r="B62" s="7" t="n">
-        <v>576</v>
+        <v>854</v>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>152573</t>
+          <t>152618</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>11170102</t>
+          <t>11170147</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>DiscoveryCDMX</t>
+          <t>Disc2ozMxPais</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>70102 C4P DIS STN MUG CDMX 14OZ</t>
+          <t>70147 C4P DIS STN MUG MEXICO 2OZ</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4223,12 +4211,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>DiscoveryCDMX</t>
+          <t>Disc2ozMxPais</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>lote-01/011170102.jpeg</t>
+          <t>lote-01/011170147.jpeg</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4249,31 +4237,31 @@
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>315</v>
+        <v>732</v>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>152541</t>
+          <t>150047</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>11170187</t>
+          <t>11174776</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ToteBag MxPais</t>
+          <t>Wt26Mug14Bow</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>70187 P2P TOTE BAG MEXICO</t>
+          <t>74776 C2P W26 STN MUG BOW 14OZ</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4288,12 +4276,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>ToteBag MxPais</t>
+          <t>Wt26Mug14Bow</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>lote-01/011170187.jpeg</t>
+          <t>lote-01/16550.jpeg</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4303,7 +4291,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -4314,31 +4302,31 @@
         </is>
       </c>
       <c r="B64" s="7" t="n">
-        <v>278</v>
+        <v>725</v>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>16689</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>152619</t>
+          <t>150034</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>11170149</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Disc2ozCDMX</t>
+          <t>Sp26NELlavero</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>70149 C4P DIS STN MUG CDMX 2OZ</t>
+          <t>KIT POUCH Y LLAVERO NE CJ4PZAS</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4353,12 +4341,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Disc2ozCDMX</t>
+          <t>Sp26NECrossB, Sp26NELlavero</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>lote-01/011170149.jpeg</t>
+          <t>lote-01/16532.jpeg</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4368,7 +4356,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -4379,31 +4367,31 @@
         </is>
       </c>
       <c r="B65" s="7" t="n">
-        <v>88</v>
+        <v>576</v>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>149915</t>
+          <t>152573</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>11160991</t>
+          <t>11170102</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>COR25SS16Sleeve</t>
+          <t>DiscoveryCDMX</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>60991 C2P CORE RECYCLD SS SLEEVE SI 16OZ</t>
+          <t>70102 C4P DIS STN MUG CDMX 14OZ</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4418,12 +4406,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>COR25SS16Sleeve</t>
+          <t>DiscoveryCDMX</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>lote-01/16284.jpeg</t>
+          <t>lote-01/011170102.jpeg</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4433,7 +4421,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -4444,31 +4432,31 @@
         </is>
       </c>
       <c r="B66" s="7" t="n">
-        <v>73</v>
+        <v>315</v>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>149827</t>
+          <t>152541</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>11164293</t>
+          <t>11170187</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SI25Tz14Glass</t>
+          <t>ToteBag MxPais</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>64293 C2P S25 GLASS MUG SAFARI 14OZ</t>
+          <t>70187 P2P TOTE BAG MEXICO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4483,12 +4471,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>SI25Tz14Glass</t>
+          <t>ToteBag MxPais</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>lote-01/16129.jpeg</t>
+          <t>lote-01/011170187.jpeg</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4498,7 +4486,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -4509,31 +4497,31 @@
         </is>
       </c>
       <c r="B67" s="7" t="n">
-        <v>53</v>
+        <v>278</v>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>152614</t>
+          <t>152619</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>11170158</t>
+          <t>11170149</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Disc2ozChiapas</t>
+          <t>Disc2ozCDMX</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>70158 C4P DIS STN MUG CHIAPAS 2OZ</t>
+          <t>70149 C4P DIS STN MUG CDMX 2OZ</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4548,12 +4536,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Disc2ozChiapas</t>
+          <t>Disc2ozCDMX</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>lote-01/011170158.jpeg</t>
+          <t>lote-01/011170149.jpeg</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4574,31 +4562,31 @@
         </is>
       </c>
       <c r="B68" s="7" t="n">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>16284</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>155961</t>
+          <t>149915</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>11187372</t>
+          <t>11160991</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>WC26Tu24DW</t>
+          <t>COR25SS16Sleeve</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>87372 C2P WC26 PLSTC CDCP FOOTBALL 24OZ</t>
+          <t>60991 C2P CORE RECYCLD SS SLEEVE SI 16OZ</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4613,12 +4601,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>WC26Tu24DW</t>
+          <t>COR25SS16Sleeve</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>lote-01/16959.jpeg</t>
+          <t>lote-01/16284.jpeg</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4639,31 +4627,31 @@
         </is>
       </c>
       <c r="B69" s="7" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>154147</t>
+          <t>149827</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>11178933</t>
+          <t>11164293</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SII25CC24Gamer</t>
+          <t>SI25Tz14Glass</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>78933 C2P SM26 PLSTC CLDCP GMR CHRM 24OZ</t>
+          <t>64293 C2P S25 GLASS MUG SAFARI 14OZ</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4673,13 +4661,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SECUNDARIO</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr"/>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>SI25Tz14Glass</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>lote-01/011178933.jpeg</t>
+          <t>lote-01/16129.jpeg</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4689,7 +4681,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -4700,27 +4692,31 @@
         </is>
       </c>
       <c r="B70" s="7" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>159943</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr"/>
+          <t>152614</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>11170158</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SII26GlCCColor</t>
+          <t>Disc2ozChiapas</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>VASO VDR SODA TRANSP SBX 470ML CJ1PZA</t>
+          <t>70158 C4P DIS STN MUG CHIAPAS 2OZ</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4730,13 +4726,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>SECUNDARIO</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr"/>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Disc2ozChiapas</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>lote-01/017357.jpeg</t>
+          <t>lote-01/011170158.jpeg</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -4757,27 +4757,31 @@
         </is>
       </c>
       <c r="B71" s="7" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>159944</t>
-        </is>
-      </c>
-      <c r="E71" s="8" t="inlineStr"/>
+          <t>155961</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>11187372</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SII26GlCCColor</t>
+          <t>WC26Tu24DW</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>VASO VDR SODA NARANJA SBX 470ML CJ1PZA</t>
+          <t>87372 C2P WC26 PLSTC CDCP FOOTBALL 24OZ</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4787,13 +4791,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SECUNDARIO</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>WC26Tu24DW</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>lote-01/017358.jpeg</t>
+          <t>lote-01/16959.jpeg</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4818,23 +4826,27 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>17359</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>159945</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="inlineStr"/>
+          <t>154147</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>11178933</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SII26GlCCColor</t>
+          <t>SII25CC24Gamer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>VASO VDR SODA ROJO SBX 470ML CJ1PZA</t>
+          <t>78933 C2P SM26 PLSTC CLDCP GMR CHRM 24OZ</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4850,7 +4862,7 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>lote-01/017359.jpeg</t>
+          <t>lote-01/011178933.jpeg</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4860,164 +4872,180 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B73" s="7" t="n">
-        <v>12340</v>
+        <v>0</v>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>15146</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>149531</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>159943</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stoppers SBX Genérico</t>
+          <t>SII26GlCCColor</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>TAPON P/VASO SOFT PVC C/DISENO CJ50PZAS</t>
+          <t>VASO VDR SODA TRANSP SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ACTIVO</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Stoppers SBX Genérico</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
+          <t>SECUNDARIO</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>lote-01/017357.jpeg</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B74" s="7" t="n">
-        <v>12340</v>
+        <v>0</v>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>150402</t>
+          <t>159944</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stoppers SBX Genérico</t>
+          <t>SII26GlCCColor</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>TAPON P/POPOTE SILICONA CJ100PZAS</t>
+          <t>VASO VDR SODA NARANJA SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ACTIVO</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Stoppers SBX Genérico</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
+          <t>SECUNDARIO</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>lote-01/017358.jpeg</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="24" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B75" s="7" t="n">
-        <v>12340</v>
+        <v>0</v>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>149624</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>159945</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stoppers SBX Genérico</t>
+          <t>SII26GlCCColor</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>MANGA SILICON P/VASO CJ50PZAS</t>
+          <t>VASO VDR SODA ROJO SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ACTIVO</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Stoppers SBX Genérico</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
+          <t>SECUNDARIO</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>lote-01/017359.jpeg</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="24" customHeight="1">
       <c r="A76" t="inlineStr">
@@ -5030,12 +5058,12 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>15606</t>
+          <t>15146</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>149625</t>
+          <t>149531</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
@@ -5050,7 +5078,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>TAPON P/POPOTE SILICONA CJ/50PZAS</t>
+          <t>TAPON P/VASO SOFT PVC C/DISENO CJ50PZAS</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5083,19 +5111,15 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>15777</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>149681</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>150402</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>Stoppers SBX Genérico</t>
@@ -5103,7 +5127,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>PULSERA SILICON (11VERD/10NEG) CJ21PZAS</t>
+          <t>TAPON P/POPOTE SILICONA CJ100PZAS</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5136,12 +5160,12 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>15783</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>149686</t>
+          <t>149624</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -5156,7 +5180,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>TAPON P/POPOTE SILICONA VXMC CJ50PZAS</t>
+          <t>MANGA SILICON P/VASO CJ50PZAS</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5189,12 +5213,12 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>16079</t>
+          <t>15606</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>149785</t>
+          <t>149625</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -5209,7 +5233,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>TAPON SILICON P/POPOTE CELEB CJ25PZAS</t>
+          <t>TAPON P/POPOTE SILICONA CJ/50PZAS</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5242,17 +5266,29 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>14527</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="inlineStr"/>
-      <c r="E80" s="8" t="inlineStr"/>
+          <t>15777</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>149681</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>Stoppers SBX Genérico</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>PULSERA SILICON (11VERD/10NEG) CJ21PZAS</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>SÍ</t>
@@ -5283,20 +5319,32 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>53841</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="inlineStr"/>
-      <c r="E81" s="8" t="inlineStr"/>
+          <t>15783</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>149686</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>Stoppers SBX Genérico</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>TAPON P/POPOTE SILICONA VXMC CJ50PZAS</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5320,16 +5368,16 @@
         </is>
       </c>
       <c r="B82" s="7" t="n">
-        <v>10598</v>
+        <v>12340</v>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>15898</t>
+          <t>16079</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>149735</t>
+          <t>149785</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
@@ -5339,12 +5387,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
+          <t>Stoppers SBX Genérico</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>KIT NAVIDENO CJ25KITS4PZAS</t>
+          <t>TAPON SILICON P/POPOTE CELEB CJ25PZAS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5359,7 +5407,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
+          <t>Stoppers SBX Genérico</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5373,33 +5421,21 @@
         </is>
       </c>
       <c r="B83" s="7" t="n">
-        <v>10598</v>
+        <v>12340</v>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>16106</t>
-        </is>
-      </c>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t>149809</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t>11160767</t>
-        </is>
-      </c>
+          <t>14527</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr"/>
+      <c r="E83" s="8" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>60767 C40P PNTS25 JOE KIND CUP SLEEVE</t>
-        </is>
-      </c>
+          <t>Stoppers SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>SÍ</t>
@@ -5412,7 +5448,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
+          <t>Stoppers SBX Genérico</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5426,33 +5462,21 @@
         </is>
       </c>
       <c r="B84" s="7" t="n">
-        <v>10598</v>
+        <v>12340</v>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>16077</t>
-        </is>
-      </c>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t>149783</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>53841</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr"/>
+      <c r="E84" s="8" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>TAPA P/STANLEY EASTER CJ5PZAS</t>
-        </is>
-      </c>
+          <t>Stoppers SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>NO</t>
@@ -5465,7 +5489,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
+          <t>Stoppers SBX Genérico</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5483,13 +5507,17 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>12319</t>
-        </is>
-      </c>
-      <c r="D85" s="8" t="inlineStr"/>
+          <t>15898</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>149735</t>
+        </is>
+      </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>11101964</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5497,7 +5525,11 @@
           <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>KIT NAVIDENO CJ25KITS4PZAS</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>SÍ</t>
@@ -5528,13 +5560,17 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>12395</t>
-        </is>
-      </c>
-      <c r="D86" s="8" t="inlineStr"/>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>149809</t>
+        </is>
+      </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>11101961</t>
+          <t>11160767</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5542,7 +5578,11 @@
           <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>60767 C40P PNTS25 JOE KIND CUP SLEEVE</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>SÍ</t>
@@ -5573,13 +5613,17 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>12471</t>
-        </is>
-      </c>
-      <c r="D87" s="8" t="inlineStr"/>
+          <t>16077</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>149783</t>
+        </is>
+      </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>11091707</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5587,10 +5631,14 @@
           <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>TAPA P/STANLEY EASTER CJ5PZAS</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5618,13 +5666,13 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>12319</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr"/>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>11103794</t>
+          <t>11101964</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5663,13 +5711,13 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>12580</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr"/>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>11109996</t>
+          <t>11101961</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5708,13 +5756,13 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>12581</t>
+          <t>12471</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr"/>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>11109997</t>
+          <t>11091707</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5753,13 +5801,13 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr"/>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>11111777</t>
+          <t>11103794</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5798,13 +5846,13 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>12746</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr"/>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>11113480</t>
+          <t>11109996</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5843,13 +5891,13 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>12920</t>
+          <t>12581</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr"/>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>11117024</t>
+          <t>11109997</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5888,13 +5936,13 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>13458</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr"/>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>11121555</t>
+          <t>11111777</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5933,13 +5981,13 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>13851</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr"/>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>11125966</t>
+          <t>11113480</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5978,13 +6026,13 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>12920</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr"/>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>11117063</t>
+          <t>11117024</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6023,13 +6071,13 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>13458</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr"/>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>11130716</t>
+          <t>11121555</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6068,13 +6116,13 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>15167</t>
+          <t>13851</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr"/>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>11146257</t>
+          <t>11125966</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6113,13 +6161,13 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>15168</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr"/>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>11146258</t>
+          <t>11117063</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6158,11 +6206,15 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>53844</t>
+          <t>14342</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr"/>
-      <c r="E100" s="8" t="inlineStr"/>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>11130716</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr">
         <is>
           <t>Lifestyle SBX Genérico</t>
@@ -6171,7 +6223,7 @@
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6195,36 +6247,28 @@
         </is>
       </c>
       <c r="B101" s="7" t="n">
-        <v>7513</v>
+        <v>10598</v>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>16903</t>
-        </is>
-      </c>
-      <c r="D101" s="8" t="inlineStr">
-        <is>
-          <t>154164</t>
-        </is>
-      </c>
+          <t>15167</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr"/>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>11178926</t>
+          <t>11146257</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sp26CC24Or</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>78926 C2P SM26 PLSTC CDCP DOME LID 24OZ</t>
-        </is>
-      </c>
+          <t>Lifestyle SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6234,7 +6278,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Sp26CC24Or</t>
+          <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6248,33 +6292,25 @@
         </is>
       </c>
       <c r="B102" s="7" t="n">
-        <v>6944</v>
+        <v>10598</v>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>15128</t>
-        </is>
-      </c>
-      <c r="D102" s="8" t="inlineStr">
-        <is>
-          <t>150104</t>
-        </is>
-      </c>
+          <t>15168</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr"/>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11146258</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>LLAVERO OSO BEARISTA CJ50PZAS</t>
-        </is>
-      </c>
+          <t>Lifestyle SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>SÍ</t>
@@ -6287,7 +6323,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
+          <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6301,36 +6337,24 @@
         </is>
       </c>
       <c r="B103" s="7" t="n">
-        <v>6944</v>
+        <v>10598</v>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>15163</t>
-        </is>
-      </c>
-      <c r="D103" s="8" t="inlineStr">
-        <is>
-          <t>149534</t>
-        </is>
-      </c>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t>11146255</t>
-        </is>
-      </c>
+          <t>53844</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr"/>
+      <c r="E103" s="8" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>46255 P4P XM23 ORNAMENT METALLIC RED</t>
-        </is>
-      </c>
+          <t>Lifestyle SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6340,7 +6364,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
+          <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6354,36 +6378,36 @@
         </is>
       </c>
       <c r="B104" s="7" t="n">
-        <v>6944</v>
+        <v>7513</v>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>149589</t>
+          <t>154164</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>11150774</t>
+          <t>11178926</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
+          <t>Sp26CC24Or</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>50774 P4P S24 CLD CUP KEY CHAIN PLEATED</t>
+          <t>78926 C2P SM26 PLSTC CDCP DOME LID 24OZ</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6393,7 +6417,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
+          <t>Sp26CC24Or</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6411,17 +6435,17 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>15513</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>149594</t>
+          <t>150104</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>11150776</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6431,7 +6455,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>50776 P4P S24 CLD CUP KEY CHAIN PRISM</t>
+          <t>LLAVERO OSO BEARISTA CJ50PZAS</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6464,17 +6488,17 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>15526</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>149606</t>
+          <t>149534</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>11150777</t>
+          <t>11146255</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6484,7 +6508,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>50777 P4P S24 COLD CUP KEY CHAIN BLING</t>
+          <t>46255 P4P XM23 ORNAMENT METALLIC RED</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6517,17 +6541,17 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>15508</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>149658</t>
+          <t>149589</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>11154026</t>
+          <t>11150774</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6537,7 +6561,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>54026 P4P F24 COLD CUP KEYCHAIN BLACK</t>
+          <t>50774 P4P S24 CLD CUP KEY CHAIN PLEATED</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6570,17 +6594,17 @@
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>15812</t>
+          <t>15513</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>149699</t>
+          <t>149594</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>11157554</t>
+          <t>11150776</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6590,7 +6614,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>57554 P4P XM24 COLD CUP KEYCHAIN GREEN</t>
+          <t>50776 P4P S24 CLD CUP KEY CHAIN PRISM</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -6623,17 +6647,17 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>15842</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>149706</t>
+          <t>149606</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>11157557</t>
+          <t>11150777</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6643,7 +6667,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>57557 P4P XM24 KEYCHAIN PLUG HOLIDAY</t>
+          <t>50777 P4P S24 COLD CUP KEY CHAIN BLING</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -6676,17 +6700,17 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>15715</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>149722</t>
+          <t>149658</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>11161850</t>
+          <t>11154026</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6696,7 +6720,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>61850 P4P WCK24 CLD CUP PRISM PVD GLINDA</t>
+          <t>54026 P4P F24 COLD CUP KEYCHAIN BLACK</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -6729,17 +6753,17 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>15812</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>149726</t>
+          <t>149699</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>11161851</t>
+          <t>11157554</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6749,7 +6773,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>61851 P4P WCK24 CLD CUP PLEATED ELPHABA</t>
+          <t>57554 P4P XM24 COLD CUP KEYCHAIN GREEN</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -6782,17 +6806,17 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>15883</t>
+          <t>15842</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>149730</t>
+          <t>149706</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>11161852</t>
+          <t>11157557</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6802,7 +6826,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>61852 P4P WCK24 CLD CUP GEMSTONE</t>
+          <t>57557 P4P XM24 KEYCHAIN PLUG HOLIDAY</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -6835,17 +6859,17 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>15875</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>149811</t>
+          <t>149722</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>11160769</t>
+          <t>11161850</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6855,7 +6879,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>60769 C16P PNTS25 KEYCHAIN JOE KIND</t>
+          <t>61850 P4P WCK24 CLD CUP PRISM PVD GLINDA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -6888,17 +6912,17 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>15879</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>150156</t>
+          <t>149726</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11161851</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6908,12 +6932,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>LLAVERO OSO BEARISTA ANO SERP CJ50PZAS</t>
+          <t>61851 P4P WCK24 CLD CUP PLEATED ELPHABA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6941,17 +6965,17 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>15998</t>
+          <t>15883</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>149752</t>
+          <t>149730</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11161852</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6961,12 +6985,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>LLAVERO OSO BEARISTA SAN VALENT CJ50PZAS</t>
+          <t>61852 P4P WCK24 CLD CUP GEMSTONE</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6994,13 +7018,17 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>12980</t>
-        </is>
-      </c>
-      <c r="D116" s="8" t="inlineStr"/>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t>149811</t>
+        </is>
+      </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>11118190</t>
+          <t>11160769</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7008,7 +7036,11 @@
           <t>Llavero SBX Genérico</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>60769 C16P PNTS25 KEYCHAIN JOE KIND</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>SÍ</t>
@@ -7039,20 +7071,32 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>14323</t>
-        </is>
-      </c>
-      <c r="D117" s="8" t="inlineStr"/>
-      <c r="E117" s="8" t="inlineStr"/>
+          <t>15997</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t>150156</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
           <t>Llavero SBX Genérico</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>LLAVERO OSO BEARISTA ANO SERP CJ50PZAS</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7080,13 +7124,17 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>14837</t>
-        </is>
-      </c>
-      <c r="D118" s="8" t="inlineStr"/>
+          <t>15998</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr">
+        <is>
+          <t>149752</t>
+        </is>
+      </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>11141138</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -7094,10 +7142,14 @@
           <t>Llavero SBX Genérico</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>LLAVERO OSO BEARISTA SAN VALENT CJ50PZAS</t>
+        </is>
+      </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7125,13 +7177,13 @@
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr"/>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>11144122</t>
+          <t>11118190</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7170,15 +7222,11 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>15368</t>
+          <t>14323</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr"/>
-      <c r="E120" s="8" t="inlineStr">
-        <is>
-          <t>11147801</t>
-        </is>
-      </c>
+      <c r="E120" s="8" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>Llavero SBX Genérico</t>
@@ -7215,13 +7263,13 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>15784</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr"/>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11141138</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -7260,11 +7308,15 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>53840</t>
+          <t>15070</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr"/>
-      <c r="E122" s="8" t="inlineStr"/>
+      <c r="E122" s="8" t="inlineStr">
+        <is>
+          <t>11144122</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr">
         <is>
           <t>Llavero SBX Genérico</t>
@@ -7273,7 +7325,7 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7297,36 +7349,28 @@
         </is>
       </c>
       <c r="B123" s="7" t="n">
-        <v>6932</v>
+        <v>6944</v>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>16178</t>
-        </is>
-      </c>
-      <c r="D123" s="8" t="inlineStr">
-        <is>
-          <t>149865</t>
-        </is>
-      </c>
+          <t>15368</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="inlineStr"/>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>11164319</t>
+          <t>11147801</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SI25KeychainZoo</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>64319 P4P S25 SLCN KEYCHAIN BEAR GIRAFFE</t>
-        </is>
-      </c>
+          <t>Llavero SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7336,7 +7380,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>SI25KeychainZoo</t>
+          <t>Llavero SBX Genérico</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7350,32 +7394,28 @@
         </is>
       </c>
       <c r="B124" s="7" t="n">
-        <v>4686</v>
+        <v>6944</v>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>17307</t>
-        </is>
-      </c>
-      <c r="D124" s="8" t="inlineStr">
-        <is>
-          <t>156359</t>
-        </is>
-      </c>
-      <c r="E124" s="8" t="inlineStr"/>
+          <t>15784</t>
+        </is>
+      </c>
+      <c r="D124" s="8" t="inlineStr"/>
+      <c r="E124" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SII26Doodle16</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>86651 C1P FL26 SS TMBLR DDLE IT 16OZ</t>
-        </is>
-      </c>
+          <t>Llavero SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7385,7 +7425,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>SII26Doodle16</t>
+          <t>Llavero SBX Genérico</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -7399,33 +7439,21 @@
         </is>
       </c>
       <c r="B125" s="7" t="n">
-        <v>4168</v>
+        <v>6944</v>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>16680</t>
-        </is>
-      </c>
-      <c r="D125" s="8" t="inlineStr">
-        <is>
-          <t>152610</t>
-        </is>
-      </c>
-      <c r="E125" s="8" t="inlineStr">
-        <is>
-          <t>11177607</t>
-        </is>
-      </c>
+          <t>53840</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="inlineStr"/>
+      <c r="E125" s="8" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Wt26ReusSiren</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>77607 P20P SP26 PLSTC RSBCLCP WMN 24OZ</t>
-        </is>
-      </c>
+          <t>Llavero SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7438,7 +7466,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Wt26ReusSiren</t>
+          <t>Llavero SBX Genérico</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -7452,31 +7480,31 @@
         </is>
       </c>
       <c r="B126" s="7" t="n">
-        <v>3964</v>
+        <v>6932</v>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>16917</t>
+          <t>16178</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>154177</t>
+          <t>149865</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>11178972</t>
+          <t>11164319</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sp26Vac16Stan</t>
+          <t>SI25KeychainZoo</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>78972 C1P SM26 RCLD SS TMBLR STNLY 16OZ</t>
+          <t>64319 P4P S25 SLCN KEYCHAIN BEAR GIRAFFE</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -7491,7 +7519,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Sp26Vac16Stan</t>
+          <t>SI25KeychainZoo</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -7505,27 +7533,27 @@
         </is>
       </c>
       <c r="B127" s="7" t="n">
-        <v>3769</v>
+        <v>4686</v>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>13694</t>
+          <t>17307</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>150353</t>
+          <t>156359</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Filtros Chemex</t>
+          <t>SII26Doodle16</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>FILTROS CUADRADOS CHEMEX CJ100PZAS</t>
+          <t>86651 C1P FL26 SS TMBLR DDLE IT 16OZ</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -7540,7 +7568,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Filtros Chemex</t>
+          <t>SII26Doodle16</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -7554,31 +7582,31 @@
         </is>
       </c>
       <c r="B128" s="7" t="n">
-        <v>3486</v>
+        <v>4168</v>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>154181</t>
+          <t>152610</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>11178917</t>
+          <t>11177607</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>WC26DW12Oran</t>
+          <t>Wt26ReusSiren</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>78917 C1P SM26 STN DW TMBLR TWST 12OZ</t>
+          <t>77607 P20P SP26 PLSTC RSBCLCP WMN 24OZ</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -7593,7 +7621,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>WC26Dw12Oran</t>
+          <t>Wt26ReusSiren</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -7607,31 +7635,31 @@
         </is>
       </c>
       <c r="B129" s="7" t="n">
-        <v>3068</v>
+        <v>3964</v>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>154169</t>
+          <t>154177</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>11178944</t>
+          <t>11178972</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>WC26SS20BTL</t>
+          <t>Sp26Vac16Stan</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>78944 C2P SM26 SS VAC WTR BTL 20OZ</t>
+          <t>78972 C1P SM26 RCLD SS TMBLR STNLY 16OZ</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -7646,7 +7674,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>WC26SS20BTL</t>
+          <t>Sp26Vac16Stan</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -7660,31 +7688,27 @@
         </is>
       </c>
       <c r="B130" s="7" t="n">
-        <v>2785</v>
+        <v>3769</v>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>13694</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>154149</t>
-        </is>
-      </c>
-      <c r="E130" s="8" t="inlineStr">
-        <is>
-          <t>11178964</t>
-        </is>
-      </c>
+          <t>150353</t>
+        </is>
+      </c>
+      <c r="E130" s="8" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sp26KeychainOr</t>
+          <t>Filtros Chemex</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>78964 C4P SM26 PLSTC CLDCP DMLD KEYCHAIN</t>
+          <t>FILTROS CUADRADOS CHEMEX CJ100PZAS</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -7699,7 +7723,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Sp26KeychainOr</t>
+          <t>Filtros Chemex</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -7713,31 +7737,31 @@
         </is>
       </c>
       <c r="B131" s="7" t="n">
-        <v>2665</v>
+        <v>3486</v>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>16080</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>149786</t>
+          <t>154181</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178917</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SII25BdayStopper</t>
+          <t>WC26DW12Oran</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>TAPON SILICON P/POPOTE CUMPLE CJ50PZAS</t>
+          <t>78917 C1P SM26 STN DW TMBLR TWST 12OZ</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -7752,7 +7776,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>SII25BdayStopper</t>
+          <t>WC26Dw12Oran</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -7766,31 +7790,31 @@
         </is>
       </c>
       <c r="B132" s="7" t="n">
-        <v>2591</v>
+        <v>3068</v>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>16909</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>152973</t>
+          <t>154169</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178944</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Wt26VasoJacaran</t>
+          <t>WC26SS20BTL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>VASO 470ML MORADO ALUMINIO OSO CJ25PZAS</t>
+          <t>78944 C2P SM26 SS VAC WTR BTL 20OZ</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -7805,7 +7829,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Wt26VasoJacaran</t>
+          <t>WC26SS20BTL</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -7819,31 +7843,31 @@
         </is>
       </c>
       <c r="B133" s="7" t="n">
-        <v>2575</v>
+        <v>2785</v>
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>154142</t>
+          <t>154149</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>11178953</t>
+          <t>11178964</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sp26SSCC24Oran</t>
+          <t>Sp26KeychainOr</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>78953 C2P SM26 SS VAC CLD CUP 24OZ</t>
+          <t>78964 C4P SM26 PLSTC CLDCP DMLD KEYCHAIN</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -7858,7 +7882,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Sp26SSCC24Oran</t>
+          <t>Sp26KeychainOr</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -7872,31 +7896,31 @@
         </is>
       </c>
       <c r="B134" s="7" t="n">
-        <v>2262</v>
+        <v>2665</v>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>16080</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>154151</t>
+          <t>149786</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>11179003</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sp26CC24Teach</t>
+          <t>SII25BdayStopper</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>79003 C2P SM26 PLSTC CLDCP 24OZ</t>
+          <t>TAPON SILICON P/POPOTE CUMPLE CJ50PZAS</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -7911,7 +7935,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Sp26CC24Teach</t>
+          <t>SII25BdayStopper</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -7925,27 +7949,31 @@
         </is>
       </c>
       <c r="B135" s="7" t="n">
-        <v>2254</v>
+        <v>2591</v>
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>17298</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>156350</t>
-        </is>
-      </c>
-      <c r="E135" s="8" t="inlineStr"/>
+          <t>152973</t>
+        </is>
+      </c>
+      <c r="E135" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SII26SSBTL12Aniv</t>
+          <t>Wt26VasoJacaran</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>86647 C1P FL26 SS WTRBTL ANNVRSRY 12OZ</t>
+          <t>VASO 470ML MORADO ALUMINIO OSO CJ25PZAS</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -7960,7 +7988,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>SII26SSBTL12Aniv</t>
+          <t>Wt26VasoJacaran</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -7974,21 +8002,33 @@
         </is>
       </c>
       <c r="B136" s="7" t="n">
-        <v>2080</v>
+        <v>2575</v>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>54213</t>
-        </is>
-      </c>
-      <c r="D136" s="8" t="inlineStr"/>
-      <c r="E136" s="8" t="inlineStr"/>
+          <t>16876</t>
+        </is>
+      </c>
+      <c r="D136" s="8" t="inlineStr">
+        <is>
+          <t>154142</t>
+        </is>
+      </c>
+      <c r="E136" s="8" t="inlineStr">
+        <is>
+          <t>11178953</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>WC26Reus</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr"/>
+          <t>Sp26SSCC24Oran</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>78953 C2P SM26 SS VAC CLD CUP 24OZ</t>
+        </is>
+      </c>
       <c r="H136" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8001,7 +8041,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>WC26Reus</t>
+          <t>Sp26SSCC24Oran</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8015,31 +8055,31 @@
         </is>
       </c>
       <c r="B137" s="7" t="n">
-        <v>1977</v>
+        <v>2262</v>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>16082</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>149788</t>
+          <t>154151</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11179003</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SII25ClipGirlB</t>
+          <t>Sp26CC24Teach</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>CLIP P/TAZA SUMMER 2 CJ25PZAS</t>
+          <t>79003 C2P SM26 PLSTC CLDCP 24OZ</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8054,7 +8094,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>SII25ClipGirlB</t>
+          <t>Sp26CC24Teach</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8068,33 +8108,21 @@
         </is>
       </c>
       <c r="B138" s="7" t="n">
-        <v>1977</v>
+        <v>2080</v>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>16343</t>
-        </is>
-      </c>
-      <c r="D138" s="8" t="inlineStr">
-        <is>
-          <t>149957</t>
-        </is>
-      </c>
-      <c r="E138" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>54213</t>
+        </is>
+      </c>
+      <c r="D138" s="8" t="inlineStr"/>
+      <c r="E138" s="8" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SII25ClipGirlB</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>LLAVERO ALOHA CJ50PZAS</t>
-        </is>
-      </c>
+          <t>WC26Reus</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8107,7 +8135,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>SII25ClipGirlB</t>
+          <t>WC26Reus</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8121,27 +8149,31 @@
         </is>
       </c>
       <c r="B139" s="7" t="n">
-        <v>1832</v>
+        <v>1977</v>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>16989</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>156338</t>
-        </is>
-      </c>
-      <c r="E139" s="8" t="inlineStr"/>
+          <t>149788</t>
+        </is>
+      </c>
+      <c r="E139" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SII26SS12Aniv</t>
+          <t>SII25ClipGirlB</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>86648 C2P FL26 SS TMBLR ANVRSRY 12OZ</t>
+          <t>CLIP P/TAZA SUMMER 2 CJ25PZAS</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8156,7 +8188,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>SII26SS12Aniv</t>
+          <t>SII25ClipGirlB</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8170,31 +8202,31 @@
         </is>
       </c>
       <c r="B140" s="7" t="n">
-        <v>1803</v>
+        <v>1977</v>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>16343</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>150060</t>
+          <t>149957</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>11174791</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Wt26ReusSV</t>
+          <t>SII25ClipGirlB</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>74791 P20P W26 PLS REUSE HTCP LD 16OZ</t>
+          <t>LLAVERO ALOHA CJ50PZAS</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8209,7 +8241,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Wt26ReusSV</t>
+          <t>SII25ClipGirlB</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8223,31 +8255,31 @@
         </is>
       </c>
       <c r="B141" s="7" t="n">
-        <v>1793</v>
+        <v>1803</v>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>149516</t>
+          <t>150060</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>11141040</t>
+          <t>11174791</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>COR23 PrensaFran</t>
+          <t>Wt26ReusSV</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>41040 C1P CORE COFFEE PRESS 34OZ</t>
+          <t>74791 P20P W26 PLS REUSE HTCP LD 16OZ</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -8262,7 +8294,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>COR23 PrensaFran</t>
+          <t>Wt26ReusSV</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -8276,31 +8308,31 @@
         </is>
       </c>
       <c r="B142" s="7" t="n">
-        <v>1766</v>
+        <v>1793</v>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>154166</t>
+          <t>149516</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>11178966</t>
+          <t>11141040</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>WC26TotePride</t>
+          <t>COR23 PrensaFran</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>78966 P2P SM26 CANVAS TOTE BAG PRIDE</t>
+          <t>41040 C1P CORE COFFEE PRESS 34OZ</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -8315,7 +8347,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>WC26TotePride</t>
+          <t>COR23 PrensaFran</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -8329,31 +8361,31 @@
         </is>
       </c>
       <c r="B143" s="7" t="n">
-        <v>1744</v>
+        <v>1766</v>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>15191</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>150106</t>
+          <t>154166</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>11144107</t>
+          <t>11178966</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>COR23 CC24 Green</t>
+          <t>WC26TotePride</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>44107 C2P CORE COLD CUP SOFT TOUCH 24OZ</t>
+          <t>78966 P2P SM26 CANVAS TOTE BAG PRIDE</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -8368,7 +8400,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>COR23 CC24 Green</t>
+          <t>WC26TotePride</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -8382,31 +8414,31 @@
         </is>
       </c>
       <c r="B144" s="7" t="n">
-        <v>1719</v>
+        <v>1744</v>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>15191</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>154165</t>
+          <t>150106</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>11178965</t>
+          <t>11144107</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>WC26ToteRoad</t>
+          <t>COR23 CC24 Green</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>78965 P2P SM26 CANVAS TOTE BAG SEASIDE</t>
+          <t>44107 C2P CORE COLD CUP SOFT TOUCH 24OZ</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -8421,7 +8453,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>WC26ToteRoad</t>
+          <t>COR23 CC24 Green</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -8435,31 +8467,31 @@
         </is>
       </c>
       <c r="B145" s="7" t="n">
-        <v>1657</v>
+        <v>1719</v>
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>16682</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>152612</t>
+          <t>154165</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>11170184</t>
+          <t>11178965</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>DiscSS20MxPais</t>
+          <t>WC26ToteRoad</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>70184 C2P DIS SS VAC TBLR MEXICO 16OZ</t>
+          <t>78965 P2P SM26 CANVAS TOTE BAG SEASIDE</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -8474,7 +8506,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>DiscSS20MxPais</t>
+          <t>WC26ToteRoad</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -8488,31 +8520,31 @@
         </is>
       </c>
       <c r="B146" s="7" t="n">
-        <v>1637</v>
+        <v>1657</v>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>16682</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>152972</t>
+          <t>152612</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11170184</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Wt26VasoFresa</t>
+          <t>DiscSS20MxPais</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>VASO 470ML ROSA ALUMINIO FRESA CJ25PZAS</t>
+          <t>70184 C2P DIS SS VAC TBLR MEXICO 16OZ</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -8527,7 +8559,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Wt26VasoFresa</t>
+          <t>DiscSS20MxPais</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -8541,31 +8573,31 @@
         </is>
       </c>
       <c r="B147" s="7" t="n">
-        <v>1538</v>
+        <v>1637</v>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>16264</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>149896</t>
+          <t>152972</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>11160967</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>COR26PPBTL20S</t>
+          <t>Wt26VasoFresa</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>60967 C2P CORE RECYCL WTR BTL BEIGE 24OZ</t>
+          <t>VASO 470ML ROSA ALUMINIO FRESA CJ25PZAS</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -8580,7 +8612,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>COR26PPBTL20S</t>
+          <t>Wt26VasoFresa</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -8594,27 +8626,31 @@
         </is>
       </c>
       <c r="B148" s="7" t="n">
-        <v>1481</v>
+        <v>1538</v>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>16722</t>
+          <t>16264</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>152970</t>
-        </is>
-      </c>
-      <c r="E148" s="8" t="inlineStr"/>
+          <t>149896</t>
+        </is>
+      </c>
+      <c r="E148" s="8" t="inlineStr">
+        <is>
+          <t>11160967</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>BearHuggerSpring</t>
+          <t>COR26PPBTL20S</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>OSO PELUCHE PASCUA CJ32PZAS</t>
+          <t>60967 C2P CORE RECYCL WTR BTL BEIGE 24OZ</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -8629,7 +8665,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>BearHuggerSpring</t>
+          <t>COR26PPBTL20S</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -8643,31 +8679,27 @@
         </is>
       </c>
       <c r="B149" s="7" t="n">
-        <v>1429</v>
+        <v>1481</v>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>152602</t>
-        </is>
-      </c>
-      <c r="E149" s="8" t="inlineStr">
-        <is>
-          <t>11176724</t>
-        </is>
-      </c>
+          <t>152970</t>
+        </is>
+      </c>
+      <c r="E149" s="8" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Sp26CookieJP</t>
+          <t>BearHuggerSpring</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>76724 C1P SP26 STN COOKIE JAR LUSTER</t>
+          <t>OSO PELUCHE PASCUA CJ32PZAS</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -8682,7 +8714,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Sp26CookieJP</t>
+          <t>BearHuggerSpring</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -8696,31 +8728,31 @@
         </is>
       </c>
       <c r="B150" s="7" t="n">
-        <v>1403</v>
+        <v>1429</v>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>154122</t>
+          <t>152602</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>11176592</t>
+          <t>11176724</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SII26SSTu12Pony</t>
+          <t>Sp26CookieJP</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>76592 C1P WIN TBLR PONNIES 12OZ</t>
+          <t>76724 C1P SP26 STN COOKIE JAR LUSTER</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -8735,7 +8767,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>SII26SSTu12Pony</t>
+          <t>Sp26CookieJP</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -8749,31 +8781,31 @@
         </is>
       </c>
       <c r="B151" s="7" t="n">
-        <v>1311</v>
+        <v>1403</v>
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>16779</t>
         </is>
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>154127</t>
+          <t>154122</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>1176593</t>
+          <t>11176592</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SII26BTL16Pony</t>
+          <t>SII26SSTu12Pony</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>76593 C1P W26 WTBL SS PONY AND FLWR 16OZ</t>
+          <t>76592 C1P WIN TBLR PONNIES 12OZ</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -8788,7 +8820,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>SII26BTL16Pony</t>
+          <t>SII26SSTu12Pony</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -8802,21 +8834,33 @@
         </is>
       </c>
       <c r="B152" s="7" t="n">
-        <v>1300</v>
+        <v>1311</v>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>54192</t>
-        </is>
-      </c>
-      <c r="D152" s="8" t="inlineStr"/>
-      <c r="E152" s="8" t="inlineStr"/>
+          <t>16793</t>
+        </is>
+      </c>
+      <c r="D152" s="8" t="inlineStr">
+        <is>
+          <t>154127</t>
+        </is>
+      </c>
+      <c r="E152" s="8" t="inlineStr">
+        <is>
+          <t>1176593</t>
+        </is>
+      </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>SII26GICCColor</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr"/>
+          <t>SII26BTL16Pony</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>76593 C1P W26 WTBL SS PONY AND FLWR 16OZ</t>
+        </is>
+      </c>
       <c r="H152" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8829,7 +8873,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>SII26GICCColor</t>
+          <t>SII26BTL16Pony</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -8843,29 +8887,21 @@
         </is>
       </c>
       <c r="B153" s="7" t="n">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>17299</t>
-        </is>
-      </c>
-      <c r="D153" s="8" t="inlineStr">
-        <is>
-          <t>156351</t>
-        </is>
-      </c>
+          <t>54192</t>
+        </is>
+      </c>
+      <c r="D153" s="8" t="inlineStr"/>
       <c r="E153" s="8" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>SII26Mug14Aniv</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>86632 C2P FL26 STN MUG SCALIE 14OZ</t>
-        </is>
-      </c>
+          <t>SII26GICCColor</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8878,7 +8914,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>SII26Mug14Aniv</t>
+          <t>SII26GICCColor</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -3127,7 +3127,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>lote-01/011178957_1.jpg</t>
+          <t>lote-01/16919.jpeg</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -4867,31 +4867,31 @@
         </is>
       </c>
       <c r="B73" s="7" t="n">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>16902</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>152618</t>
+          <t>154163</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>11170147</t>
+          <t>11178920</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Disc2ozMxPais</t>
+          <t>WC26Tu20Yellow</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>70147 C4P DIS STN MUG MEXICO 2OZ</t>
+          <t>78920 C2P SM26 PLSTC TMBLR YLLOW 20OZ</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4906,12 +4906,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Disc2ozMxPais</t>
+          <t>WC26Tu20Yellow</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>lote-01/011170147.jpeg</t>
+          <t>lote-01/16902.jpeg</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -4932,31 +4932,31 @@
         </is>
       </c>
       <c r="B74" s="7" t="n">
-        <v>829</v>
+        <v>854</v>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>149938</t>
+          <t>152618</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>11160990</t>
+          <t>11170147</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>COR26SSThruLid</t>
+          <t>Disc2ozMxPais</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>60990 C2P CORE TMBLR DR TH ABS MAR 16 OZ</t>
+          <t>70147 C4P DIS STN MUG MEXICO 2OZ</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>COR26SSThruLid</t>
+          <t>Disc2ozMxPais</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>lote-01/16311.jpeg</t>
+          <t>lote-01/011170147.jpeg</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -4997,31 +4997,31 @@
         </is>
       </c>
       <c r="B75" s="7" t="n">
-        <v>732</v>
+        <v>829</v>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>150047</t>
+          <t>149938</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>11174776</t>
+          <t>11160990</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Wt26Mug14Bow</t>
+          <t>COR26SSThruLid</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>74776 C2P W26 STN MUG BOW 14OZ</t>
+          <t>60990 C2P CORE TMBLR DR TH ABS MAR 16 OZ</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Wt26Mug14Bow</t>
+          <t>COR26SSThruLid</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>lote-01/16550.jpeg</t>
+          <t>lote-01/16311.jpeg</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5062,31 +5062,31 @@
         </is>
       </c>
       <c r="B76" s="7" t="n">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>150034</t>
+          <t>150047</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11174776</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sp26NELlavero</t>
+          <t>Wt26Mug14Bow</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>KIT POUCH Y LLAVERO NE CJ4PZAS</t>
+          <t>74776 C2P W26 STN MUG BOW 14OZ</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Sp26NECrossB, Sp26NELlavero</t>
+          <t>Wt26Mug14Bow</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>lote-01/16532.jpeg</t>
+          <t>lote-01/16550.jpeg</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5127,31 +5127,31 @@
         </is>
       </c>
       <c r="B77" s="7" t="n">
-        <v>576</v>
+        <v>725</v>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>152573</t>
+          <t>150034</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>11170102</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>DiscoveryCDMX</t>
+          <t>Sp26NELlavero</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>70102 C4P DIS STN MUG CDMX 14OZ</t>
+          <t>KIT POUCH Y LLAVERO NE CJ4PZAS</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>DiscoveryCDMX</t>
+          <t>Sp26NECrossB, Sp26NELlavero</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>lote-01/011170102.jpeg</t>
+          <t>lote-01/16532.jpeg</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -5192,31 +5192,31 @@
         </is>
       </c>
       <c r="B78" s="7" t="n">
-        <v>315</v>
+        <v>576</v>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>152541</t>
+          <t>152573</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>11170187</t>
+          <t>11170102</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ToteBag MxPais</t>
+          <t>DiscoveryCDMX</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>70187 P2P TOTE BAG MEXICO</t>
+          <t>70102 C4P DIS STN MUG CDMX 14OZ</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>ToteBag MxPais</t>
+          <t>DiscoveryCDMX</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>lote-01/011170187.jpeg</t>
+          <t>lote-01/011170102.jpeg</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5257,31 +5257,31 @@
         </is>
       </c>
       <c r="B79" s="7" t="n">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>16689</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>152619</t>
+          <t>152541</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>11170149</t>
+          <t>11170187</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Disc2ozCDMX</t>
+          <t>ToteBag MxPais</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>70149 C4P DIS STN MUG CDMX 2OZ</t>
+          <t>70187 P2P TOTE BAG MEXICO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Disc2ozCDMX</t>
+          <t>ToteBag MxPais</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>lote-01/011170149.jpeg</t>
+          <t>lote-01/011170187.jpeg</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5322,31 +5322,31 @@
         </is>
       </c>
       <c r="B80" s="7" t="n">
-        <v>88</v>
+        <v>278</v>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>149915</t>
+          <t>152619</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>11160991</t>
+          <t>11170149</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>COR25SS16Sleeve</t>
+          <t>Disc2ozCDMX</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>60991 C2P CORE RECYCLD SS SLEEVE SI 16OZ</t>
+          <t>70149 C4P DIS STN MUG CDMX 2OZ</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>COR25SS16Sleeve</t>
+          <t>Disc2ozCDMX</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>lote-01/16284.jpeg</t>
+          <t>lote-01/011170149.jpeg</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -5387,31 +5387,31 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>16284</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>149827</t>
+          <t>149915</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>11164293</t>
+          <t>11160991</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SI25Tz14Glass</t>
+          <t>COR25SS16Sleeve</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>64293 C2P S25 GLASS MUG SAFARI 14OZ</t>
+          <t>60991 C2P CORE RECYCLD SS SLEEVE SI 16OZ</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>SI25Tz14Glass</t>
+          <t>COR25SS16Sleeve</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>lote-01/16129.jpeg</t>
+          <t>lote-01/16284.jpeg</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5452,31 +5452,31 @@
         </is>
       </c>
       <c r="B82" s="7" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>152614</t>
+          <t>149827</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>11170158</t>
+          <t>11164293</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Disc2ozChiapas</t>
+          <t>SI25Tz14Glass</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>70158 C4P DIS STN MUG CHIAPAS 2OZ</t>
+          <t>64293 C2P S25 GLASS MUG SAFARI 14OZ</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Disc2ozChiapas</t>
+          <t>SI25Tz14Glass</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>lote-01/011170158.jpeg</t>
+          <t>lote-01/16129.jpeg</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -5517,31 +5517,31 @@
         </is>
       </c>
       <c r="B83" s="7" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>155961</t>
+          <t>152614</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>11187372</t>
+          <t>11170158</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>WC26Tu24DW</t>
+          <t>Disc2ozChiapas</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>87372 C2P WC26 PLSTC CDCP FOOTBALL 24OZ</t>
+          <t>70158 C4P DIS STN MUG CHIAPAS 2OZ</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>WC26Tu24DW</t>
+          <t>Disc2ozChiapas</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>lote-01/16959.jpeg</t>
+          <t>lote-01/011170158.jpeg</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -5582,31 +5582,31 @@
         </is>
       </c>
       <c r="B84" s="7" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>150012</t>
+          <t>155961</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>11173043</t>
+          <t>11187372</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Xm25GlassBear</t>
+          <t>WC26Tu24DW</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>73043 C2P XM25 GLASS CLD BEARISTA 20OZ</t>
+          <t>87372 C2P WC26 PLSTC CDCP FOOTBALL 24OZ</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5616,13 +5616,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SECUNDARIO</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr"/>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>WC26Tu24DW</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>lote-01/16477.jpeg</t>
+          <t>lote-01/16959.jpeg</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5647,27 +5651,27 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16477</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>154147</t>
+          <t>150012</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>11178933</t>
+          <t>11173043</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>SII25CC24Gamer</t>
+          <t>Xm25GlassBear</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>78933 C2P SM26 PLSTC CLDCP GMR CHRM 24OZ</t>
+          <t>73043 C2P XM25 GLASS CLD BEARISTA 20OZ</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5683,7 +5687,7 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>lote-01/011178933.jpeg</t>
+          <t>lote-01/16477.jpeg</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5693,7 +5697,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -5708,23 +5712,27 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>16960</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>155962</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="inlineStr"/>
+          <t>154147</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>11178933</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>60979 C2P CORE PLSTC HTCDCP DCHRC 24OZ</t>
+          <t>SII25CC24Gamer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>60979 C2P CORE PLSTC HTCDCP DCHRC 24OZ</t>
+          <t>78933 C2P SM26 PLSTC CLDCP GMR CHRM 24OZ</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5740,7 +5748,7 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>lote-01/16960.jpeg</t>
+          <t>lote-01/011178933.jpeg</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5750,7 +5758,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>codigoDia</t>
+          <t>skuIntl</t>
         </is>
       </c>
     </row>
@@ -5765,23 +5773,23 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>16960</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>159943</t>
+          <t>155962</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>VASO VDR SODA TRANSP SBX 470ML CJ1PZA</t>
+          <t>60979 C2P CORE PLSTC HTCDCP DCHRC 24OZ</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>VASO VDR SODA TRANSP SBX 470ML CJ1PZA</t>
+          <t>60979 C2P CORE PLSTC HTCDCP DCHRC 24OZ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5797,7 +5805,7 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>lote-01/017357.jpeg</t>
+          <t>lote-01/16960.jpeg</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5822,23 +5830,23 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>159944</t>
+          <t>159943</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>VASO VDR SODA NARANJA SBX 470ML CJ1PZA</t>
+          <t>VASO VDR SODA TRANSP SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>VASO VDR SODA NARANJA SBX 470ML CJ1PZA</t>
+          <t>VASO VDR SODA TRANSP SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5854,7 +5862,7 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>lote-01/017358.jpeg</t>
+          <t>lote-01/017357.jpeg</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5879,23 +5887,23 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>17359</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>159945</t>
+          <t>159944</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>VASO VDR SODA ROJO SBX 470ML CJ1PZA</t>
+          <t>VASO VDR SODA NARANJA SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>VASO VDR SODA ROJO SBX 470ML CJ1PZA</t>
+          <t>VASO VDR SODA NARANJA SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5911,7 +5919,7 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>lote-01/017359.jpeg</t>
+          <t>lote-01/017358.jpeg</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5928,55 +5936,59 @@
     <row r="90" ht="24" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B90" s="7" t="n">
-        <v>12340</v>
+        <v>0</v>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>15146</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>149531</t>
-        </is>
-      </c>
-      <c r="E90" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>159945</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stoppers SBX Genérico</t>
+          <t>VASO VDR SODA ROJO SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>TAPON P/VASO SOFT PVC C/DISENO CJ50PZAS</t>
+          <t>VASO VDR SODA ROJO SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ACTIVO</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Stoppers SBX Genérico</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
+          <t>SECUNDARIO</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>lote-01/017359.jpeg</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="24" customHeight="1">
       <c r="A91" t="inlineStr">
@@ -5989,15 +6001,19 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>15146</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>150402</t>
-        </is>
-      </c>
-      <c r="E91" s="8" t="inlineStr"/>
+          <t>149531</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
           <t>Stoppers SBX Genérico</t>
@@ -6005,7 +6021,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>TAPON P/POPOTE SILICONA CJ100PZAS</t>
+          <t>TAPON P/VASO SOFT PVC C/DISENO CJ50PZAS</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6038,19 +6054,15 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>149624</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>150402</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>Stoppers SBX Genérico</t>
@@ -6058,7 +6070,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>MANGA SILICON P/VASO CJ50PZAS</t>
+          <t>TAPON P/POPOTE SILICONA CJ100PZAS</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6091,12 +6103,12 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>15606</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>149625</t>
+          <t>149624</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -6111,7 +6123,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>TAPON P/POPOTE SILICONA CJ/50PZAS</t>
+          <t>MANGA SILICON P/VASO CJ50PZAS</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6144,12 +6156,12 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>15777</t>
+          <t>15606</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>149681</t>
+          <t>149625</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
@@ -6164,7 +6176,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>PULSERA SILICON (11VERD/10NEG) CJ21PZAS</t>
+          <t>TAPON P/POPOTE SILICONA CJ/50PZAS</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6197,12 +6209,12 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>15783</t>
+          <t>15777</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>149686</t>
+          <t>149681</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -6217,7 +6229,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>TAPON P/POPOTE SILICONA VXMC CJ50PZAS</t>
+          <t>PULSERA SILICON (11VERD/10NEG) CJ21PZAS</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6250,12 +6262,12 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>16079</t>
+          <t>15783</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>149785</t>
+          <t>149686</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -6270,7 +6282,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>TAPON SILICON P/POPOTE CELEB CJ25PZAS</t>
+          <t>TAPON P/POPOTE SILICONA VXMC CJ50PZAS</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6303,17 +6315,29 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>14527</t>
-        </is>
-      </c>
-      <c r="D97" s="8" t="inlineStr"/>
-      <c r="E97" s="8" t="inlineStr"/>
+          <t>16079</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>149785</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr">
         <is>
           <t>Stoppers SBX Genérico</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>TAPON SILICON P/POPOTE CELEB CJ25PZAS</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>SÍ</t>
@@ -6344,7 +6368,7 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>53841</t>
+          <t>14527</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr"/>
@@ -6357,7 +6381,7 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6381,36 +6405,24 @@
         </is>
       </c>
       <c r="B99" s="7" t="n">
-        <v>10598</v>
+        <v>12340</v>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>15898</t>
-        </is>
-      </c>
-      <c r="D99" s="8" t="inlineStr">
-        <is>
-          <t>149735</t>
-        </is>
-      </c>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>53841</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr"/>
+      <c r="E99" s="8" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>KIT NAVIDENO CJ25KITS4PZAS</t>
-        </is>
-      </c>
+          <t>Stoppers SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6420,7 +6432,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
+          <t>Stoppers SBX Genérico</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6438,17 +6450,17 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>15898</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>149809</t>
+          <t>149735</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>11160767</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6458,7 +6470,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>60767 C40P PNTS25 JOE KIND CUP SLEEVE</t>
+          <t>KIT NAVIDENO CJ25KITS4PZAS</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6491,17 +6503,17 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>16077</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>149783</t>
+          <t>149809</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11160767</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6511,12 +6523,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>TAPA P/STANLEY EASTER CJ5PZAS</t>
+          <t>60767 C40P PNTS25 JOE KIND CUP SLEEVE</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6544,13 +6556,17 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>12319</t>
-        </is>
-      </c>
-      <c r="D102" s="8" t="inlineStr"/>
+          <t>16077</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>149783</t>
+        </is>
+      </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>11101964</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6558,10 +6574,14 @@
           <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>TAPA P/STANLEY EASTER CJ5PZAS</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6589,13 +6609,13 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>12395</t>
+          <t>12319</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr"/>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>11101961</t>
+          <t>11101964</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6634,13 +6654,13 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>12471</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr"/>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>11091707</t>
+          <t>11101961</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6679,13 +6699,13 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>12471</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr"/>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>11103794</t>
+          <t>11091707</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6724,13 +6744,13 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>12580</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr"/>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>11109996</t>
+          <t>11103794</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6769,13 +6789,13 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>12581</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr"/>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>11109997</t>
+          <t>11109996</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6814,13 +6834,13 @@
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12581</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr"/>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>11111777</t>
+          <t>11109997</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6859,13 +6879,13 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>12746</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr"/>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>11113480</t>
+          <t>11111777</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6904,13 +6924,13 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>12920</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr"/>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>11117024</t>
+          <t>11113480</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6949,13 +6969,13 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>13458</t>
+          <t>12920</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr"/>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>11121555</t>
+          <t>11117024</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6994,13 +7014,13 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>13851</t>
+          <t>13458</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr"/>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>11125966</t>
+          <t>11121555</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7039,13 +7059,13 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>13851</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr"/>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>11117063</t>
+          <t>11125966</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7084,13 +7104,13 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr"/>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>11130716</t>
+          <t>11117063</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7129,13 +7149,13 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>15167</t>
+          <t>14342</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr"/>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>11146257</t>
+          <t>11130716</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7174,13 +7194,13 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>15168</t>
+          <t>15167</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr"/>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>11146258</t>
+          <t>11146257</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7219,11 +7239,15 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>53844</t>
+          <t>15168</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr"/>
-      <c r="E117" s="8" t="inlineStr"/>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>11146258</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
           <t>Lifestyle SBX Genérico</t>
@@ -7232,7 +7256,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7256,36 +7280,24 @@
         </is>
       </c>
       <c r="B118" s="7" t="n">
-        <v>6944</v>
+        <v>10598</v>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>15128</t>
-        </is>
-      </c>
-      <c r="D118" s="8" t="inlineStr">
-        <is>
-          <t>150104</t>
-        </is>
-      </c>
-      <c r="E118" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>53844</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr"/>
+      <c r="E118" s="8" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>LLAVERO OSO BEARISTA CJ50PZAS</t>
-        </is>
-      </c>
+          <t>Lifestyle SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7295,7 +7307,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
+          <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7313,17 +7325,17 @@
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>15163</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>149534</t>
+          <t>150104</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>11146255</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7333,7 +7345,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>46255 P4P XM23 ORNAMENT METALLIC RED</t>
+          <t>LLAVERO OSO BEARISTA CJ50PZAS</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7366,17 +7378,17 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>149589</t>
+          <t>149534</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>11150774</t>
+          <t>11146255</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7386,7 +7398,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>50774 P4P S24 CLD CUP KEY CHAIN PLEATED</t>
+          <t>46255 P4P XM23 ORNAMENT METALLIC RED</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7419,17 +7431,17 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>15513</t>
+          <t>15508</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>149594</t>
+          <t>149589</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>11150776</t>
+          <t>11150774</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -7439,7 +7451,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>50776 P4P S24 CLD CUP KEY CHAIN PRISM</t>
+          <t>50774 P4P S24 CLD CUP KEY CHAIN PLEATED</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7472,17 +7484,17 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>15526</t>
+          <t>15513</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>149606</t>
+          <t>149594</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>11150777</t>
+          <t>11150776</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7492,7 +7504,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>50777 P4P S24 COLD CUP KEY CHAIN BLING</t>
+          <t>50776 P4P S24 CLD CUP KEY CHAIN PRISM</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7525,17 +7537,17 @@
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>149658</t>
+          <t>149606</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>11154026</t>
+          <t>11150777</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -7545,7 +7557,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>54026 P4P F24 COLD CUP KEYCHAIN BLACK</t>
+          <t>50777 P4P S24 COLD CUP KEY CHAIN BLING</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7578,17 +7590,17 @@
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>15812</t>
+          <t>15715</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>149699</t>
+          <t>149658</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>11157554</t>
+          <t>11154026</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -7598,7 +7610,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>57554 P4P XM24 COLD CUP KEYCHAIN GREEN</t>
+          <t>54026 P4P F24 COLD CUP KEYCHAIN BLACK</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7631,17 +7643,17 @@
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>15842</t>
+          <t>15812</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>149706</t>
+          <t>149699</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>11157557</t>
+          <t>11157554</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -7651,7 +7663,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>57557 P4P XM24 KEYCHAIN PLUG HOLIDAY</t>
+          <t>57554 P4P XM24 COLD CUP KEYCHAIN GREEN</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -7684,17 +7696,17 @@
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>15842</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>149722</t>
+          <t>149706</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>11161850</t>
+          <t>11157557</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -7704,7 +7716,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>61850 P4P WCK24 CLD CUP PRISM PVD GLINDA</t>
+          <t>57557 P4P XM24 KEYCHAIN PLUG HOLIDAY</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -7737,17 +7749,17 @@
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>15875</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>149726</t>
+          <t>149722</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>11161851</t>
+          <t>11161850</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -7757,7 +7769,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>61851 P4P WCK24 CLD CUP PLEATED ELPHABA</t>
+          <t>61850 P4P WCK24 CLD CUP PRISM PVD GLINDA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -7790,17 +7802,17 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>15883</t>
+          <t>15879</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>149730</t>
+          <t>149726</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>11161852</t>
+          <t>11161851</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7810,7 +7822,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>61852 P4P WCK24 CLD CUP GEMSTONE</t>
+          <t>61851 P4P WCK24 CLD CUP PLEATED ELPHABA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -7843,17 +7855,17 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>15883</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>149811</t>
+          <t>149730</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>11160769</t>
+          <t>11161852</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7863,7 +7875,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>60769 C16P PNTS25 KEYCHAIN JOE KIND</t>
+          <t>61852 P4P WCK24 CLD CUP GEMSTONE</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -7896,17 +7908,17 @@
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>150156</t>
+          <t>149811</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11160769</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -7916,12 +7928,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>LLAVERO OSO BEARISTA ANO SERP CJ50PZAS</t>
+          <t>60769 C16P PNTS25 KEYCHAIN JOE KIND</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7949,12 +7961,12 @@
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>15998</t>
+          <t>15997</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>149752</t>
+          <t>150156</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -7969,7 +7981,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>LLAVERO OSO BEARISTA SAN VALENT CJ50PZAS</t>
+          <t>LLAVERO OSO BEARISTA ANO SERP CJ50PZAS</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8002,13 +8014,17 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>12980</t>
-        </is>
-      </c>
-      <c r="D132" s="8" t="inlineStr"/>
+          <t>15998</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t>149752</t>
+        </is>
+      </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>11118190</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8016,10 +8032,14 @@
           <t>Llavero SBX Genérico</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>LLAVERO OSO BEARISTA SAN VALENT CJ50PZAS</t>
+        </is>
+      </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8047,11 +8067,15 @@
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>14323</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr"/>
-      <c r="E133" s="8" t="inlineStr"/>
+      <c r="E133" s="8" t="inlineStr">
+        <is>
+          <t>11118190</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
           <t>Llavero SBX Genérico</t>
@@ -8088,15 +8112,11 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>14323</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr"/>
-      <c r="E134" s="8" t="inlineStr">
-        <is>
-          <t>11141138</t>
-        </is>
-      </c>
+      <c r="E134" s="8" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>Llavero SBX Genérico</t>
@@ -8133,13 +8153,13 @@
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr"/>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>11144122</t>
+          <t>11141138</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8178,13 +8198,13 @@
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>15368</t>
+          <t>15070</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr"/>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>11147801</t>
+          <t>11144122</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8223,13 +8243,13 @@
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>15784</t>
+          <t>15368</t>
         </is>
       </c>
       <c r="D137" s="8" t="inlineStr"/>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11147801</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -8268,11 +8288,15 @@
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>53840</t>
+          <t>15784</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr"/>
-      <c r="E138" s="8" t="inlineStr"/>
+      <c r="E138" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr">
         <is>
           <t>Llavero SBX Genérico</t>
@@ -8281,7 +8305,7 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8305,33 +8329,21 @@
         </is>
       </c>
       <c r="B139" s="7" t="n">
-        <v>6932</v>
+        <v>6944</v>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>16178</t>
-        </is>
-      </c>
-      <c r="D139" s="8" t="inlineStr">
-        <is>
-          <t>149865</t>
-        </is>
-      </c>
-      <c r="E139" s="8" t="inlineStr">
-        <is>
-          <t>11164319</t>
-        </is>
-      </c>
+          <t>53840</t>
+        </is>
+      </c>
+      <c r="D139" s="8" t="inlineStr"/>
+      <c r="E139" s="8" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SI25KeychainZoo</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>64319 P4P S25 SLCN KEYCHAIN BEAR GIRAFFE</t>
-        </is>
-      </c>
+          <t>Llavero SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8344,7 +8356,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>SI25KeychainZoo</t>
+          <t>Llavero SBX Genérico</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8358,27 +8370,31 @@
         </is>
       </c>
       <c r="B140" s="7" t="n">
-        <v>4686</v>
+        <v>6932</v>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>17307</t>
+          <t>16178</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>156359</t>
-        </is>
-      </c>
-      <c r="E140" s="8" t="inlineStr"/>
+          <t>149865</t>
+        </is>
+      </c>
+      <c r="E140" s="8" t="inlineStr">
+        <is>
+          <t>11164319</t>
+        </is>
+      </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SII26Doodle16</t>
+          <t>SI25KeychainZoo</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>86651 C1P FL26 SS TMBLR DDLE IT 16OZ</t>
+          <t>64319 P4P S25 SLCN KEYCHAIN BEAR GIRAFFE</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8393,7 +8409,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>SII26Doodle16</t>
+          <t>SI25KeychainZoo</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8407,31 +8423,27 @@
         </is>
       </c>
       <c r="B141" s="7" t="n">
-        <v>4168</v>
+        <v>4686</v>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>17307</t>
         </is>
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>152610</t>
-        </is>
-      </c>
-      <c r="E141" s="8" t="inlineStr">
-        <is>
-          <t>11177607</t>
-        </is>
-      </c>
+          <t>156359</t>
+        </is>
+      </c>
+      <c r="E141" s="8" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Wt26ReusSiren</t>
+          <t>SII26Doodle16</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>77607 P20P SP26 PLSTC RSBCLCP WMN 24OZ</t>
+          <t>86651 C1P FL26 SS TMBLR DDLE IT 16OZ</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -8446,7 +8458,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Wt26ReusSiren</t>
+          <t>SII26Doodle16</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -8460,27 +8472,31 @@
         </is>
       </c>
       <c r="B142" s="7" t="n">
-        <v>3769</v>
+        <v>4168</v>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>13694</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>150353</t>
-        </is>
-      </c>
-      <c r="E142" s="8" t="inlineStr"/>
+          <t>152610</t>
+        </is>
+      </c>
+      <c r="E142" s="8" t="inlineStr">
+        <is>
+          <t>11177607</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Filtros Chemex</t>
+          <t>Wt26ReusSiren</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>FILTROS CUADRADOS CHEMEX CJ100PZAS</t>
+          <t>77607 P20P SP26 PLSTC RSBCLCP WMN 24OZ</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -8495,7 +8511,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Filtros Chemex</t>
+          <t>Wt26ReusSiren</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -8509,31 +8525,27 @@
         </is>
       </c>
       <c r="B143" s="7" t="n">
-        <v>2785</v>
+        <v>3769</v>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>13694</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>154149</t>
-        </is>
-      </c>
-      <c r="E143" s="8" t="inlineStr">
-        <is>
-          <t>11178964</t>
-        </is>
-      </c>
+          <t>150353</t>
+        </is>
+      </c>
+      <c r="E143" s="8" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Sp26KeychainOr</t>
+          <t>Filtros Chemex</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>78964 C4P SM26 PLSTC CLDCP DMLD KEYCHAIN</t>
+          <t>FILTROS CUADRADOS CHEMEX CJ100PZAS</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -8548,7 +8560,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Sp26KeychainOr</t>
+          <t>Filtros Chemex</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -8562,31 +8574,31 @@
         </is>
       </c>
       <c r="B144" s="7" t="n">
-        <v>2665</v>
+        <v>2785</v>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>16080</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>149786</t>
+          <t>154149</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178964</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SII25BdayStopper</t>
+          <t>Sp26KeychainOr</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>TAPON SILICON P/POPOTE CUMPLE CJ50PZAS</t>
+          <t>78964 C4P SM26 PLSTC CLDCP DMLD KEYCHAIN</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -8601,7 +8613,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>SII25BdayStopper</t>
+          <t>Sp26KeychainOr</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -8615,16 +8627,16 @@
         </is>
       </c>
       <c r="B145" s="7" t="n">
-        <v>2591</v>
+        <v>2665</v>
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>16080</t>
         </is>
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>152973</t>
+          <t>149786</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -8634,12 +8646,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Wt26VasoJacaran</t>
+          <t>SII25BdayStopper</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>VASO 470ML MORADO ALUMINIO OSO CJ25PZAS</t>
+          <t>TAPON SILICON P/POPOTE CUMPLE CJ50PZAS</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -8654,7 +8666,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Wt26VasoJacaran</t>
+          <t>SII25BdayStopper</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -8668,31 +8680,31 @@
         </is>
       </c>
       <c r="B146" s="7" t="n">
-        <v>2575</v>
+        <v>2591</v>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>154142</t>
+          <t>152973</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>11178953</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Sp26SSCC24Oran</t>
+          <t>Wt26VasoJacaran</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>78953 C2P SM26 SS VAC CLD CUP 24OZ</t>
+          <t>VASO 470ML MORADO ALUMINIO OSO CJ25PZAS</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -8707,7 +8719,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Sp26SSCC24Oran</t>
+          <t>Wt26VasoJacaran</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -8721,31 +8733,31 @@
         </is>
       </c>
       <c r="B147" s="7" t="n">
-        <v>2262</v>
+        <v>2575</v>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>154151</t>
+          <t>154142</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>11179003</t>
+          <t>11178953</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sp26CC24Teach</t>
+          <t>Sp26SSCC24Oran</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>79003 C2P SM26 PLSTC CLDCP 24OZ</t>
+          <t>78953 C2P SM26 SS VAC CLD CUP 24OZ</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -8760,7 +8772,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Sp26CC24Teach</t>
+          <t>Sp26SSCC24Oran</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -8774,31 +8786,31 @@
         </is>
       </c>
       <c r="B148" s="7" t="n">
-        <v>1977</v>
+        <v>2262</v>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>16082</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>149788</t>
+          <t>154151</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11179003</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SII25ClipGirlB</t>
+          <t>Sp26CC24Teach</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>CLIP P/TAZA SUMMER 2 CJ25PZAS</t>
+          <t>79003 C2P SM26 PLSTC CLDCP 24OZ</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -8813,7 +8825,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>SII25ClipGirlB</t>
+          <t>Sp26CC24Teach</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -8831,12 +8843,12 @@
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>149957</t>
+          <t>149788</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -8851,7 +8863,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>LLAVERO ALOHA CJ50PZAS</t>
+          <t>CLIP P/TAZA SUMMER 2 CJ25PZAS</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -8880,31 +8892,31 @@
         </is>
       </c>
       <c r="B150" s="7" t="n">
-        <v>1766</v>
+        <v>1977</v>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>16343</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>154166</t>
+          <t>149957</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>11178966</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>WC26TotePride</t>
+          <t>SII25ClipGirlB</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>78966 P2P SM26 CANVAS TOTE BAG PRIDE</t>
+          <t>LLAVERO ALOHA CJ50PZAS</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -8919,7 +8931,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>WC26TotePride</t>
+          <t>SII25ClipGirlB</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -8933,31 +8945,31 @@
         </is>
       </c>
       <c r="B151" s="7" t="n">
-        <v>1744</v>
+        <v>1766</v>
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>15191</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>150106</t>
+          <t>154166</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>11144107</t>
+          <t>11178966</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>COR23 CC24 Green</t>
+          <t>WC26TotePride</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>44107 C2P CORE COLD CUP SOFT TOUCH 24OZ</t>
+          <t>78966 P2P SM26 CANVAS TOTE BAG PRIDE</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -8972,7 +8984,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>COR23 CC24 Green</t>
+          <t>WC26TotePride</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -8986,31 +8998,31 @@
         </is>
       </c>
       <c r="B152" s="7" t="n">
-        <v>1637</v>
+        <v>1744</v>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>15191</t>
         </is>
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>152972</t>
+          <t>150106</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11144107</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Wt26VasoFresa</t>
+          <t>COR23 CC24 Green</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>VASO 470ML ROSA ALUMINIO FRESA CJ25PZAS</t>
+          <t>44107 C2P CORE COLD CUP SOFT TOUCH 24OZ</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9025,7 +9037,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Wt26VasoFresa</t>
+          <t>COR23 CC24 Green</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9039,31 +9051,31 @@
         </is>
       </c>
       <c r="B153" s="7" t="n">
-        <v>1538</v>
+        <v>1637</v>
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>16264</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>149896</t>
+          <t>152972</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>11160967</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>COR26PPBTL20S</t>
+          <t>Wt26VasoFresa</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>60967 C2P CORE RECYCL WTR BTL BEIGE 24OZ</t>
+          <t>VASO 470ML ROSA ALUMINIO FRESA CJ25PZAS</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9078,7 +9090,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>COR26PPBTL20S</t>
+          <t>Wt26VasoFresa</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9092,27 +9104,31 @@
         </is>
       </c>
       <c r="B154" s="7" t="n">
-        <v>1481</v>
+        <v>1538</v>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>16722</t>
+          <t>16264</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>152970</t>
-        </is>
-      </c>
-      <c r="E154" s="8" t="inlineStr"/>
+          <t>149896</t>
+        </is>
+      </c>
+      <c r="E154" s="8" t="inlineStr">
+        <is>
+          <t>11160967</t>
+        </is>
+      </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>BearHuggerSpring</t>
+          <t>COR26PPBTL20S</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>OSO PELUCHE PASCUA CJ32PZAS</t>
+          <t>60967 C2P CORE RECYCL WTR BTL BEIGE 24OZ</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9127,7 +9143,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>BearHuggerSpring</t>
+          <t>COR26PPBTL20S</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9141,31 +9157,27 @@
         </is>
       </c>
       <c r="B155" s="7" t="n">
-        <v>1403</v>
+        <v>1481</v>
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>154122</t>
-        </is>
-      </c>
-      <c r="E155" s="8" t="inlineStr">
-        <is>
-          <t>11176592</t>
-        </is>
-      </c>
+          <t>152970</t>
+        </is>
+      </c>
+      <c r="E155" s="8" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SII26SSTu12Pony</t>
+          <t>BearHuggerSpring</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>76592 C1P WIN TBLR PONNIES 12OZ</t>
+          <t>OSO PELUCHE PASCUA CJ32PZAS</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9180,7 +9192,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>SII26SSTu12Pony</t>
+          <t>BearHuggerSpring</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9194,31 +9206,31 @@
         </is>
       </c>
       <c r="B156" s="7" t="n">
-        <v>1311</v>
+        <v>1403</v>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>16779</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>154127</t>
+          <t>154122</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>1176593</t>
+          <t>11176592</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>SII26BTL16Pony</t>
+          <t>SII26SSTu12Pony</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>76593 C1P W26 WTBL SS PONY AND FLWR 16OZ</t>
+          <t>76592 C1P WIN TBLR PONNIES 12OZ</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9233,7 +9245,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>SII26BTL16Pony</t>
+          <t>SII26SSTu12Pony</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9247,21 +9259,33 @@
         </is>
       </c>
       <c r="B157" s="7" t="n">
-        <v>1300</v>
+        <v>1311</v>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>54192</t>
-        </is>
-      </c>
-      <c r="D157" s="8" t="inlineStr"/>
-      <c r="E157" s="8" t="inlineStr"/>
+          <t>16793</t>
+        </is>
+      </c>
+      <c r="D157" s="8" t="inlineStr">
+        <is>
+          <t>154127</t>
+        </is>
+      </c>
+      <c r="E157" s="8" t="inlineStr">
+        <is>
+          <t>1176593</t>
+        </is>
+      </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>SII26GICCColor</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr"/>
+          <t>SII26BTL16Pony</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>76593 C1P W26 WTBL SS PONY AND FLWR 16OZ</t>
+        </is>
+      </c>
       <c r="H157" t="inlineStr">
         <is>
           <t>NO</t>
@@ -9274,7 +9298,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>SII26GICCColor</t>
+          <t>SII26BTL16Pony</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -9288,33 +9312,21 @@
         </is>
       </c>
       <c r="B158" s="7" t="n">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>16081</t>
-        </is>
-      </c>
-      <c r="D158" s="8" t="inlineStr">
-        <is>
-          <t>149787</t>
-        </is>
-      </c>
-      <c r="E158" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>54192</t>
+        </is>
+      </c>
+      <c r="D158" s="8" t="inlineStr"/>
+      <c r="E158" s="8" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>SII25ClipBoyB</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>CLIP P/TAZA SUMMER 1 CJ25PZAS</t>
-        </is>
-      </c>
+          <t>SII26GICCColor</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
           <t>NO</t>
@@ -9327,7 +9339,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>SII25ClipBoyB</t>
+          <t>SII26GICCColor</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -9341,16 +9353,16 @@
         </is>
       </c>
       <c r="B159" s="7" t="n">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>16502</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t>150023</t>
+          <t>149787</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -9360,12 +9372,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Xm25Tag</t>
+          <t>SII25ClipBoyB</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>TAG MALETA OSO CJ25PZAS</t>
+          <t>CLIP P/TAZA SUMMER 1 CJ25PZAS</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -9380,7 +9392,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Xm25Tag</t>
+          <t>SII25ClipBoyB</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -9398,17 +9410,29 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>53962</t>
-        </is>
-      </c>
-      <c r="D160" s="8" t="inlineStr"/>
-      <c r="E160" s="8" t="inlineStr"/>
+          <t>16502</t>
+        </is>
+      </c>
+      <c r="D160" s="8" t="inlineStr">
+        <is>
+          <t>150023</t>
+        </is>
+      </c>
+      <c r="E160" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr">
         <is>
           <t>Xm25Tag</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>TAG MALETA OSO CJ25PZAS</t>
+        </is>
+      </c>
       <c r="H160" t="inlineStr">
         <is>
           <t>NO</t>
@@ -9435,36 +9459,24 @@
         </is>
       </c>
       <c r="B161" s="7" t="n">
-        <v>1154</v>
+        <v>1276</v>
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>16107</t>
-        </is>
-      </c>
-      <c r="D161" s="8" t="inlineStr">
-        <is>
-          <t>149810</t>
-        </is>
-      </c>
-      <c r="E161" s="8" t="inlineStr">
-        <is>
-          <t>11160768</t>
-        </is>
-      </c>
+          <t>53962</t>
+        </is>
+      </c>
+      <c r="D161" s="8" t="inlineStr"/>
+      <c r="E161" s="8" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tote bags SBX Genérico</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>60768 P5P PNTS25 JOE KIND TOTE BAG</t>
-        </is>
-      </c>
+          <t>Xm25Tag</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9474,7 +9486,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Tote bags SBX Genérico</t>
+          <t>Xm25Tag</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -9492,17 +9504,17 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>15967</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>149744</t>
+          <t>149810</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>11161004</t>
+          <t>11160768</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -9512,12 +9524,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>61004 P2P CORE REUS WTR BTL CARRYING BAG</t>
+          <t>60768 P5P PNTS25 JOE KIND TOTE BAG</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -9527,7 +9539,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Tote bags SBX Genérico, Wt25CrarryingBag</t>
+          <t>Tote bags SBX Genérico</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -9545,13 +9557,17 @@
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>12318</t>
-        </is>
-      </c>
-      <c r="D163" s="8" t="inlineStr"/>
+          <t>15967</t>
+        </is>
+      </c>
+      <c r="D163" s="8" t="inlineStr">
+        <is>
+          <t>149744</t>
+        </is>
+      </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>11101960</t>
+          <t>11161004</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -9559,10 +9575,14 @@
           <t>Tote bags SBX Genérico</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>61004 P2P CORE REUS WTR BTL CARRYING BAG</t>
+        </is>
+      </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -9572,7 +9592,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Tote bags SBX Genérico</t>
+          <t>Tote bags SBX Genérico, Wt25CrarryingBag</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -9590,13 +9610,13 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>12819</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr"/>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>11115490</t>
+          <t>11101960</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -9635,11 +9655,15 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>53842</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="D165" s="8" t="inlineStr"/>
-      <c r="E165" s="8" t="inlineStr"/>
+      <c r="E165" s="8" t="inlineStr">
+        <is>
+          <t>11115490</t>
+        </is>
+      </c>
       <c r="F165" t="inlineStr">
         <is>
           <t>Tote bags SBX Genérico</t>
@@ -9648,7 +9672,7 @@
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -9672,33 +9696,21 @@
         </is>
       </c>
       <c r="B166" s="7" t="n">
-        <v>1051</v>
+        <v>1154</v>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>16899</t>
-        </is>
-      </c>
-      <c r="D166" s="8" t="inlineStr">
-        <is>
-          <t>154160</t>
-        </is>
-      </c>
-      <c r="E166" s="8" t="inlineStr">
-        <is>
-          <t>11179004</t>
-        </is>
-      </c>
+          <t>53842</t>
+        </is>
+      </c>
+      <c r="D166" s="8" t="inlineStr"/>
+      <c r="E166" s="8" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Sp26Tu16Teach</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>79004 C2P SM26 SS VAC TMBLR TEACHER 16OZ</t>
-        </is>
-      </c>
+          <t>Tote bags SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
           <t>NO</t>
@@ -9711,7 +9723,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Sp26Tu16Teach</t>
+          <t>Tote bags SBX Genérico</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -9725,27 +9737,31 @@
         </is>
       </c>
       <c r="B167" s="7" t="n">
-        <v>976</v>
+        <v>1051</v>
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="D167" s="8" t="inlineStr">
         <is>
-          <t>154133</t>
-        </is>
-      </c>
-      <c r="E167" s="8" t="inlineStr"/>
+          <t>154160</t>
+        </is>
+      </c>
+      <c r="E167" s="8" t="inlineStr">
+        <is>
+          <t>11179004</t>
+        </is>
+      </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>BearHugWorldCup</t>
+          <t>Sp26Tu16Teach</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>OSO PELUCHE WC SBX 2026 CJ15PZAS</t>
+          <t>79004 C2P SM26 SS VAC TMBLR TEACHER 16OZ</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -9760,7 +9776,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>BearHugWorldCup</t>
+          <t>Sp26Tu16Teach</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -9774,31 +9790,27 @@
         </is>
       </c>
       <c r="B168" s="7" t="n">
-        <v>865</v>
+        <v>976</v>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>16828</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>149914</t>
-        </is>
-      </c>
-      <c r="E168" s="8" t="inlineStr">
-        <is>
-          <t>11161003</t>
-        </is>
-      </c>
+          <t>154133</t>
+        </is>
+      </c>
+      <c r="E168" s="8" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>COR26Stan30White</t>
+          <t>BearHugWorldCup</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>61003 C1P F25 CORE SS TMBLR CREAM 30OZ</t>
+          <t>OSO PELUCHE WC SBX 2026 CJ15PZAS</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -9813,7 +9825,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>COR26Stan30White</t>
+          <t>BearHugWorldCup</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -9827,31 +9839,31 @@
         </is>
       </c>
       <c r="B169" s="7" t="n">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="D169" s="8" t="inlineStr">
         <is>
-          <t>154163</t>
+          <t>149914</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>11178920</t>
+          <t>11161003</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>WC26Tu20Yellow</t>
+          <t>COR26Stan30White</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>78920 C2P SM26 PLSTC TMBLR YLLOW 20OZ</t>
+          <t>61003 C1P F25 CORE SS TMBLR CREAM 30OZ</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -9866,7 +9878,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>WC26Tu20Yellow</t>
+          <t>COR26Stan30White</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Control de fotos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de fotos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Control de fotos'!$A$7:$M$1156</definedName>
@@ -726,7 +726,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>lote-01/16807.jpeg</t>
+          <t>lote-01/16807.webp</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>lote-01/11372.jpeg</t>
+          <t>lote-01/11372.webp</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>lote-01/011178935.jpeg</t>
+          <t>lote-01/16920.webp</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>lote-01/16078.jpeg</t>
+          <t>lote-01/16078.webp</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>lote-01/011178969.jpeg</t>
+          <t>lote-01/16910.webp</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>lote-01/011178930.jpeg</t>
+          <t>lote-01/16882.webp</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>lote-01/011178928.jpeg</t>
+          <t>lote-01/16880.webp</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>lote-01/16884.jpeg</t>
+          <t>lote-01/16884.webp</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>lote-01/011178956.jpeg</t>
+          <t>lote-01/16916.webp</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>lote-01/011186659.jpeg</t>
+          <t>lote-01/16999.webp</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>lote-01/011186658.jpeg</t>
+          <t>lote-01/16998.webp</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>lote-01/14886.jpeg</t>
+          <t>lote-01/14886.webp</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>lote-01/16903.jpeg</t>
+          <t>lote-01/16903.webp</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>lote-01/14928.jpeg</t>
+          <t>lote-01/14928.webp</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>lote-01/011186646.jpeg</t>
+          <t>lote-01/16997.webp</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>lote-01/011179005.jpeg</t>
+          <t>lote-01/16906.webp</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>lote-01/15857.jpeg</t>
+          <t>lote-01/15857.webp</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>lote-01/14927.jpeg</t>
+          <t>lote-01/14927.webp</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>lote-01/011178937.jpeg</t>
+          <t>lote-01/16901.webp</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>lote-01/011178946.jpg</t>
+          <t>lote-01/16913.webp</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>lote-01/011178973.jpg</t>
+          <t>lote-01/16925.webp</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>lote-01/011178952.jpeg</t>
+          <t>lote-01/16875.webp</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>lote-01/011186650.jpeg</t>
+          <t>lote-01/16995.webp</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>lote-01/011178941.jpeg</t>
+          <t>lote-01/16900.webp</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>lote-01/011178922.jpeg</t>
+          <t>lote-01/16879.webp</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>lote-01/16923.jpeg</t>
+          <t>lote-01/16923.webp</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>lote-01/011178971.jpeg</t>
+          <t>lote-01/16911.webp</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>lote-01/16896.jpeg</t>
+          <t>lote-01/16896.webp</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>lote-01/14926.jpeg</t>
+          <t>lote-01/14926.webp</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>lote-01/16531.jpeg</t>
+          <t>lote-01/16531.webp</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>lote-01/011178943.jpeg</t>
+          <t>lote-01/16918.webp</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>lote-01/16917.jpeg</t>
+          <t>lote-01/16917.webp</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>lote-01/16921.jpeg</t>
+          <t>lote-01/16921.webp</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>lote-01/16955.jpeg</t>
+          <t>lote-01/16955.webp</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>lote-01/16909.jpeg</t>
+          <t>lote-01/16909.webp</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>lote-01/011178938.jpeg</t>
+          <t>lote-01/16898.webp</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>lote-01/011178948.jpeg</t>
+          <t>lote-01/16915.webp</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>lote-01/16919.jpeg</t>
+          <t>lote-01/16919.webp</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3160,11 +3160,7 @@
           <t>152611</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>11170174</t>
-        </is>
-      </c>
+      <c r="E46" s="8" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>DiscCC24MxPais</t>
@@ -3192,7 +3188,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>lote-01/011170174.jpeg</t>
+          <t>lote-01/16681.webp</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3202,7 +3198,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3253,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>lote-01/011178945.jpeg</t>
+          <t>lote-01/16924.webp</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3267,7 +3263,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3318,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>lote-01/16378.jpeg</t>
+          <t>lote-01/16378.webp</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3383,7 +3379,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>lote-01/16977.jpeg</t>
+          <t>lote-01/16977.webp</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3444,7 +3440,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>lote-01/17298.jpeg</t>
+          <t>lote-01/17298.webp</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3497,7 +3493,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>lote-01/54213.jpeg</t>
+          <t>lote-01/54213.webp</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3562,7 +3558,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>lote-01/16877.jpeg</t>
+          <t>lote-01/16877.webp</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3627,7 +3623,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>lote-01/011178959.jpeg</t>
+          <t>lote-01/16897.webp</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3637,7 +3633,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3684,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>lote-01/16989.jpeg</t>
+          <t>lote-01/16989.webp</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3753,7 +3749,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>lote-01/16572.jpeg</t>
+          <t>lote-01/16572.webp</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3818,7 +3814,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>lote-01/14929.jpeg</t>
+          <t>lote-01/14929.webp</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3883,7 +3879,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>lote-01/16914.jpeg</t>
+          <t>lote-01/16914.webp</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3948,7 +3944,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>lote-01/16904.jpeg</t>
+          <t>lote-01/16904.webp</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4009,7 +4005,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>lote-01/16682.jpeg</t>
+          <t>lote-01/16682.webp</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4074,7 +4070,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>lote-01/16610.jpeg</t>
+          <t>lote-01/16610.webp</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4139,7 +4135,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>lote-01/16672.jpeg</t>
+          <t>lote-01/16672.webp</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4204,7 +4200,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>lote-01/14885.jpeg</t>
+          <t>lote-01/14885.webp</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4265,7 +4261,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>lote-01/17299.jpeg</t>
+          <t>lote-01/17299.webp</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4330,7 +4326,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>lote-01/011176710.jpeg</t>
+          <t>lote-01/16664.webp</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4340,7 +4336,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4387,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>lote-01/16642.jpeg</t>
+          <t>lote-01/16642.webp</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4456,7 +4452,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>lote-01/16777.jpeg</t>
+          <t>lote-01/16777.webp</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4521,7 +4517,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>lote-01/16125.jpeg</t>
+          <t>lote-01/16125.webp</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4586,7 +4582,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>lote-01/16312.jpeg</t>
+          <t>lote-01/16312.webp</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4651,7 +4647,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>lote-01/16720.jpeg</t>
+          <t>lote-01/16720.webp</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4716,7 +4712,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>lote-01/011178919.jpeg</t>
+          <t>lote-01/16922.webp</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4726,7 +4722,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4777,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>lote-01/16719.jpeg</t>
+          <t>lote-01/16719.webp</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4846,7 +4842,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>lote-01/16438.jpeg</t>
+          <t>lote-01/16438.webp</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4911,7 +4907,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>lote-01/16902.jpeg</t>
+          <t>lote-01/16902.webp</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4944,11 +4940,7 @@
           <t>152618</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>11170147</t>
-        </is>
-      </c>
+      <c r="E74" s="8" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>Disc2ozMxPais</t>
@@ -4976,7 +4968,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>lote-01/011170147.jpeg</t>
+          <t>lote-01/16688.webp</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4986,7 +4978,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5033,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>lote-01/16311.jpeg</t>
+          <t>lote-01/16311.webp</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5106,7 +5098,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>lote-01/16550.jpeg</t>
+          <t>lote-01/16550.webp</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5171,7 +5163,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>lote-01/16532.jpeg</t>
+          <t>lote-01/16532.webp</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5204,11 +5196,7 @@
           <t>152573</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>11170102</t>
-        </is>
-      </c>
+      <c r="E78" s="8" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>DiscoveryCDMX</t>
@@ -5236,7 +5224,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>lote-01/011170102.jpeg</t>
+          <t>lote-01/16643.webp</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5246,7 +5234,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -5269,11 +5257,7 @@
           <t>152541</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>11170187</t>
-        </is>
-      </c>
+      <c r="E79" s="8" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>ToteBag MxPais</t>
@@ -5301,7 +5285,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>lote-01/011170187.jpeg</t>
+          <t>lote-01/16601.webp</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5311,7 +5295,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -5334,11 +5318,7 @@
           <t>152619</t>
         </is>
       </c>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t>11170149</t>
-        </is>
-      </c>
+      <c r="E80" s="8" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>Disc2ozCDMX</t>
@@ -5366,7 +5346,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>lote-01/011170149.jpeg</t>
+          <t>lote-01/16689.webp</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5376,7 +5356,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5411,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>lote-01/16284.jpeg</t>
+          <t>lote-01/16284.webp</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5496,7 +5476,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>lote-01/16129.jpeg</t>
+          <t>lote-01/16129.webp</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5529,11 +5509,7 @@
           <t>152614</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t>11170158</t>
-        </is>
-      </c>
+      <c r="E83" s="8" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>Disc2ozChiapas</t>
@@ -5561,7 +5537,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>lote-01/011170158.jpeg</t>
+          <t>lote-01/16684.webp</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5571,7 +5547,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5602,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>lote-01/16959.jpeg</t>
+          <t>lote-01/16959.webp</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5687,7 +5663,7 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>lote-01/16477.jpeg</t>
+          <t>lote-01/16477.webp</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5748,7 +5724,7 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>lote-01/011178933.jpeg</t>
+          <t>lote-01/16881.webp</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5758,7 +5734,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>skuIntl</t>
+          <t>codigoDia</t>
         </is>
       </c>
     </row>
@@ -5805,7 +5781,7 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>lote-01/16960.jpeg</t>
+          <t>lote-01/16960.webp</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5862,7 +5838,7 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>lote-01/017357.jpeg</t>
+          <t>lote-01/17357.webp</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5919,7 +5895,7 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>lote-01/017358.jpeg</t>
+          <t>lote-01/17358.webp</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5976,7 +5952,7 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>lote-01/017359.jpeg</t>
+          <t>lote-01/17359.webp</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de fotos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Control de fotos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Control de fotos'!$A$7:$M$1156</definedName>

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Control de fotos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de fotos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Control de fotos'!$A$7:$M$1156</definedName>

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -5367,31 +5367,31 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>88</v>
+        <v>224</v>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>149915</t>
+          <t>152548</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>11160991</t>
+          <t>11177937</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>COR25SS16Sleeve</t>
+          <t>Sp26CCup16Cherry</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>60991 C2P CORE RECYCLD SS SLEEVE SI 16OZ</t>
+          <t>77937 C1P CCUP CORGICHERRY BLSM 16OZ</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>COR25SS16Sleeve</t>
+          <t>Sp26CCup16Cherry</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>lote-01/16284.webp</t>
+          <t>lote-01/16611.webp</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5432,31 +5432,31 @@
         </is>
       </c>
       <c r="B82" s="7" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>16284</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>149827</t>
+          <t>149915</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>11164293</t>
+          <t>11160991</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SI25Tz14Glass</t>
+          <t>COR25SS16Sleeve</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>64293 C2P S25 GLASS MUG SAFARI 14OZ</t>
+          <t>60991 C2P CORE RECYCLD SS SLEEVE SI 16OZ</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>SI25Tz14Glass</t>
+          <t>COR25SS16Sleeve</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>lote-01/16129.webp</t>
+          <t>lote-01/16284.webp</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5497,27 +5497,31 @@
         </is>
       </c>
       <c r="B83" s="7" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>152614</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="inlineStr"/>
+          <t>149827</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>11164293</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Disc2ozChiapas</t>
+          <t>SI25Tz14Glass</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>70158 C4P DIS STN MUG CHIAPAS 2OZ</t>
+          <t>64293 C2P S25 GLASS MUG SAFARI 14OZ</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5532,12 +5536,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Disc2ozChiapas</t>
+          <t>SI25Tz14Glass</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>lote-01/16684.webp</t>
+          <t>lote-01/16129.webp</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5558,31 +5562,27 @@
         </is>
       </c>
       <c r="B84" s="7" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>155961</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>11187372</t>
-        </is>
-      </c>
+          <t>152614</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>WC26Tu24DW</t>
+          <t>Disc2ozChiapas</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>87372 C2P WC26 PLSTC CDCP FOOTBALL 24OZ</t>
+          <t>70158 C4P DIS STN MUG CHIAPAS 2OZ</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>WC26Tu24DW</t>
+          <t>Disc2ozChiapas</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>lote-01/16959.webp</t>
+          <t>lote-01/16684.webp</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5623,31 +5623,31 @@
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>150012</t>
+          <t>155961</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>11173043</t>
+          <t>11187372</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Xm25GlassBear</t>
+          <t>WC26Tu24DW</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>73043 C2P XM25 GLASS CLD BEARISTA 20OZ</t>
+          <t>87372 C2P WC26 PLSTC CDCP FOOTBALL 24OZ</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5657,13 +5657,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>SECUNDARIO</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr"/>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>WC26Tu24DW</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>lote-01/16477.webp</t>
+          <t>lote-01/16959.webp</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5688,27 +5692,27 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16477</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>154147</t>
+          <t>150012</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>11178933</t>
+          <t>11173043</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SII25CC24Gamer</t>
+          <t>Xm25GlassBear</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>78933 C2P SM26 PLSTC CLDCP GMR CHRM 24OZ</t>
+          <t>73043 C2P XM25 GLASS CLD BEARISTA 20OZ</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5724,7 +5728,7 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>lote-01/16881.webp</t>
+          <t>lote-01/16477.webp</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5749,23 +5753,27 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>16960</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>155962</t>
-        </is>
-      </c>
-      <c r="E87" s="8" t="inlineStr"/>
+          <t>154147</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>11178933</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>60979 C2P CORE PLSTC HTCDCP DCHRC 24OZ</t>
+          <t>SII25CC24Gamer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>60979 C2P CORE PLSTC HTCDCP DCHRC 24OZ</t>
+          <t>78933 C2P SM26 PLSTC CLDCP GMR CHRM 24OZ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5781,7 +5789,7 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>lote-01/16960.webp</t>
+          <t>lote-01/16881.webp</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5806,23 +5814,23 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>16969</t>
+          <t>16960</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>155967</t>
+          <t>155962</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>86639 C2P F26 PLSTC WTRBTL PSL 24OZ</t>
+          <t>60979 C2P CORE PLSTC HTCDCP DCHRC 24OZ</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>86639 C2P F26 PLSTC WTRBTL PSL 24OZ</t>
+          <t>60979 C2P CORE PLSTC HTCDCP DCHRC 24OZ</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5838,7 +5846,7 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>lote-01/16969.webp</t>
+          <t>lote-01/16960.webp</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5863,23 +5871,23 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>16996</t>
+          <t>16969</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>156345</t>
+          <t>155967</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>86645 C2P FL26 SS TMBLR DSKTP 12OZ</t>
+          <t>86639 C2P F26 PLSTC WTRBTL PSL 24OZ</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>86645 C2P FL26 SS TMBLR DSKTP 12OZ</t>
+          <t>86639 C2P F26 PLSTC WTRBTL PSL 24OZ</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5895,7 +5903,7 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>lote-01/16996.webp</t>
+          <t>lote-01/16969.webp</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5920,23 +5928,23 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>17297</t>
+          <t>16996</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>156349</t>
+          <t>156345</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>86652 C2P FL26 SS TMBLR CHRM PSL 16OZ</t>
+          <t>86645 C2P FL26 SS TMBLR DSKTP 12OZ</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>86652 C2P FL26 SS TMBLR CHRM PSL 16OZ</t>
+          <t>86645 C2P FL26 SS TMBLR DSKTP 12OZ</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5952,7 +5960,7 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>lote-01/17297.webp</t>
+          <t>lote-01/16996.webp</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5977,23 +5985,23 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>17303</t>
+          <t>17297</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>156355</t>
+          <t>156349</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>86638 C2P FL26 PLSTC CDCP CNFT 24OZ</t>
+          <t>86652 C2P FL26 SS TMBLR CHRM PSL 16OZ</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>86638 C2P FL26 PLSTC CDCP CNFT 24OZ</t>
+          <t>86652 C2P FL26 SS TMBLR CHRM PSL 16OZ</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6009,7 +6017,7 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>lote-01/17303.webp</t>
+          <t>lote-01/17297.webp</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6034,23 +6042,23 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>17343</t>
+          <t>17303</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>159937</t>
+          <t>156355</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>86653 C1P FL26 SS CLDCP STRW TPPR 16OZ</t>
+          <t>86638 C2P FL26 PLSTC CDCP CNFT 24OZ</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>86653 C1P FL26 SS CLDCP STRW TPPR 16OZ</t>
+          <t>86638 C2P FL26 PLSTC CDCP CNFT 24OZ</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6066,7 +6074,7 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>lote-01/17343.webp</t>
+          <t>lote-01/17303.webp</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6091,23 +6099,23 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>17343</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>159943</t>
+          <t>159937</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>VASO VDR SODA TRANSP SBX 470ML CJ1PZA</t>
+          <t>86653 C1P FL26 SS CLDCP STRW TPPR 16OZ</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>VASO VDR SODA TRANSP SBX 470ML CJ1PZA</t>
+          <t>86653 C1P FL26 SS CLDCP STRW TPPR 16OZ</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6123,7 +6131,7 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>lote-01/17357.webp</t>
+          <t>lote-01/17343.webp</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6148,23 +6156,23 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>159944</t>
+          <t>159943</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>VASO VDR SODA NARANJA SBX 470ML CJ1PZA</t>
+          <t>VASO VDR SODA TRANSP SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>VASO VDR SODA NARANJA SBX 470ML CJ1PZA</t>
+          <t>VASO VDR SODA TRANSP SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6180,7 +6188,7 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>lote-01/17358.webp</t>
+          <t>lote-01/17357.webp</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6205,23 +6213,23 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>17359</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>159945</t>
+          <t>159944</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>VASO VDR SODA ROJO SBX 470ML CJ1PZA</t>
+          <t>VASO VDR SODA NARANJA SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>VASO VDR SODA ROJO SBX 470ML CJ1PZA</t>
+          <t>VASO VDR SODA NARANJA SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6237,7 +6245,7 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>lote-01/17359.webp</t>
+          <t>lote-01/17358.webp</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6262,23 +6270,23 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>17360</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>159946</t>
+          <t>159945</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>VASO VDR SODA AZUL SBX 470ML CJ1PZA</t>
+          <t>VASO VDR SODA ROJO SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>VASO VDR SODA AZUL SBX 470ML CJ1PZA</t>
+          <t>VASO VDR SODA ROJO SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6294,7 +6302,7 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>lote-01/17360.webp</t>
+          <t>lote-01/17359.webp</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6319,23 +6327,23 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>17361</t>
+          <t>17360</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>159947</t>
+          <t>159946</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>VASO VDR SODA VERDE SBX 470ML CJ1PZA</t>
+          <t>VASO VDR SODA AZUL SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>VASO VDR SODA VERDE SBX 470ML CJ1PZA</t>
+          <t>VASO VDR SODA AZUL SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6351,7 +6359,7 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>lote-01/17361.webp</t>
+          <t>lote-01/17360.webp</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6376,23 +6384,23 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17361</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>159948</t>
+          <t>159947</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>VASO VDR SODA AMARILLO SBX 470ML CJ1PZA</t>
+          <t>VASO VDR SODA VERDE SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>VASO VDR SODA AMARILLO SBX 470ML CJ1PZA</t>
+          <t>VASO VDR SODA VERDE SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6408,7 +6416,7 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>lote-01/17362.webp</t>
+          <t>lote-01/17361.webp</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6425,55 +6433,59 @@
     <row r="99" ht="24" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FALTA FOTO</t>
+          <t>CON FOTO</t>
         </is>
       </c>
       <c r="B99" s="7" t="n">
-        <v>12340</v>
+        <v>0</v>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>15146</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>149531</t>
-        </is>
-      </c>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>159948</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stoppers SBX Genérico</t>
+          <t>VASO VDR SODA AMARILLO SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>TAPON P/VASO SOFT PVC C/DISENO CJ50PZAS</t>
+          <t>VASO VDR SODA AMARILLO SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>ACTIVO</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>Stoppers SBX Genérico</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
+          <t>SECUNDARIO</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>lote-01/17362.webp</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>lote-01</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>codigoDia</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="24" customHeight="1">
       <c r="A100" t="inlineStr">
@@ -6486,15 +6498,19 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>15146</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>150402</t>
-        </is>
-      </c>
-      <c r="E100" s="8" t="inlineStr"/>
+          <t>149531</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr">
         <is>
           <t>Stoppers SBX Genérico</t>
@@ -6502,7 +6518,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>TAPON P/POPOTE SILICONA CJ100PZAS</t>
+          <t>TAPON P/VASO SOFT PVC C/DISENO CJ50PZAS</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6535,19 +6551,15 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>149624</t>
-        </is>
-      </c>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>150402</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>Stoppers SBX Genérico</t>
@@ -6555,7 +6567,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>MANGA SILICON P/VASO CJ50PZAS</t>
+          <t>TAPON P/POPOTE SILICONA CJ100PZAS</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6588,12 +6600,12 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>15606</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>149625</t>
+          <t>149624</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
@@ -6608,7 +6620,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>TAPON P/POPOTE SILICONA CJ/50PZAS</t>
+          <t>MANGA SILICON P/VASO CJ50PZAS</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6641,12 +6653,12 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>15777</t>
+          <t>15606</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>149681</t>
+          <t>149625</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -6661,7 +6673,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>PULSERA SILICON (11VERD/10NEG) CJ21PZAS</t>
+          <t>TAPON P/POPOTE SILICONA CJ/50PZAS</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6694,12 +6706,12 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>15783</t>
+          <t>15777</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>149686</t>
+          <t>149681</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
@@ -6714,7 +6726,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>TAPON P/POPOTE SILICONA VXMC CJ50PZAS</t>
+          <t>PULSERA SILICON (11VERD/10NEG) CJ21PZAS</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6747,12 +6759,12 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>16079</t>
+          <t>15783</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>149785</t>
+          <t>149686</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -6767,7 +6779,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>TAPON SILICON P/POPOTE CELEB CJ25PZAS</t>
+          <t>TAPON P/POPOTE SILICONA VXMC CJ50PZAS</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6800,17 +6812,29 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>14527</t>
-        </is>
-      </c>
-      <c r="D106" s="8" t="inlineStr"/>
-      <c r="E106" s="8" t="inlineStr"/>
+          <t>16079</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>149785</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
           <t>Stoppers SBX Genérico</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>TAPON SILICON P/POPOTE CELEB CJ25PZAS</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>SÍ</t>
@@ -6841,7 +6865,7 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>53841</t>
+          <t>14527</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr"/>
@@ -6854,7 +6878,7 @@
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6878,36 +6902,24 @@
         </is>
       </c>
       <c r="B108" s="7" t="n">
-        <v>10598</v>
+        <v>12340</v>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>15898</t>
-        </is>
-      </c>
-      <c r="D108" s="8" t="inlineStr">
-        <is>
-          <t>149735</t>
-        </is>
-      </c>
-      <c r="E108" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>53841</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr"/>
+      <c r="E108" s="8" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>KIT NAVIDENO CJ25KITS4PZAS</t>
-        </is>
-      </c>
+          <t>Stoppers SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6917,7 +6929,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Lifestyle SBX Genérico</t>
+          <t>Stoppers SBX Genérico</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -6935,17 +6947,17 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>15898</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>149809</t>
+          <t>149735</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>11160767</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6955,7 +6967,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>60767 C40P PNTS25 JOE KIND CUP SLEEVE</t>
+          <t>KIT NAVIDENO CJ25KITS4PZAS</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -6988,17 +7000,17 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>16077</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>149783</t>
+          <t>149809</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11160767</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -7008,12 +7020,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>TAPA P/STANLEY EASTER CJ5PZAS</t>
+          <t>60767 C40P PNTS25 JOE KIND CUP SLEEVE</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7041,13 +7053,17 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>12319</t>
-        </is>
-      </c>
-      <c r="D111" s="8" t="inlineStr"/>
+          <t>16077</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>149783</t>
+        </is>
+      </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>11101964</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7055,10 +7071,14 @@
           <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>TAPA P/STANLEY EASTER CJ5PZAS</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7086,13 +7106,13 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>12395</t>
+          <t>12319</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr"/>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>11101961</t>
+          <t>11101964</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7131,13 +7151,13 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>12471</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr"/>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>11091707</t>
+          <t>11101961</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7176,13 +7196,13 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>12471</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr"/>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>11103794</t>
+          <t>11091707</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7221,13 +7241,13 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>12580</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr"/>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>11109996</t>
+          <t>11103794</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7266,13 +7286,13 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>12581</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr"/>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>11109997</t>
+          <t>11109996</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7311,13 +7331,13 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12581</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr"/>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>11111777</t>
+          <t>11109997</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7356,13 +7376,13 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>12746</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr"/>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>11113480</t>
+          <t>11111777</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -7401,13 +7421,13 @@
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>12920</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr"/>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>11117024</t>
+          <t>11113480</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7446,13 +7466,13 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>13458</t>
+          <t>12920</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr"/>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>11121555</t>
+          <t>11117024</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7491,13 +7511,13 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>13851</t>
+          <t>13458</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr"/>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>11125966</t>
+          <t>11121555</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -7536,13 +7556,13 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>13851</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr"/>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>11117063</t>
+          <t>11125966</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7581,13 +7601,13 @@
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr"/>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>11130716</t>
+          <t>11117063</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -7626,13 +7646,13 @@
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>15167</t>
+          <t>14342</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr"/>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>11146257</t>
+          <t>11130716</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -7671,13 +7691,13 @@
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>15168</t>
+          <t>15167</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr"/>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>11146258</t>
+          <t>11146257</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -7716,11 +7736,15 @@
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>53844</t>
+          <t>15168</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr"/>
-      <c r="E126" s="8" t="inlineStr"/>
+      <c r="E126" s="8" t="inlineStr">
+        <is>
+          <t>11146258</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr">
         <is>
           <t>Lifestyle SBX Genérico</t>
@@ -7729,7 +7753,7 @@
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7753,36 +7777,24 @@
         </is>
       </c>
       <c r="B127" s="7" t="n">
-        <v>6944</v>
+        <v>10598</v>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>15128</t>
-        </is>
-      </c>
-      <c r="D127" s="8" t="inlineStr">
-        <is>
-          <t>150104</t>
-        </is>
-      </c>
-      <c r="E127" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>53844</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr"/>
+      <c r="E127" s="8" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>LLAVERO OSO BEARISTA CJ50PZAS</t>
-        </is>
-      </c>
+          <t>Lifestyle SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7792,7 +7804,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Llavero SBX Genérico</t>
+          <t>Lifestyle SBX Genérico</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -7810,17 +7822,17 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>15163</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>149534</t>
+          <t>150104</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>11146255</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7830,7 +7842,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>46255 P4P XM23 ORNAMENT METALLIC RED</t>
+          <t>LLAVERO OSO BEARISTA CJ50PZAS</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -7863,17 +7875,17 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>149589</t>
+          <t>149534</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>11150774</t>
+          <t>11146255</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7883,7 +7895,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>50774 P4P S24 CLD CUP KEY CHAIN PLEATED</t>
+          <t>46255 P4P XM23 ORNAMENT METALLIC RED</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -7916,17 +7928,17 @@
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>15513</t>
+          <t>15508</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>149594</t>
+          <t>149589</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>11150776</t>
+          <t>11150774</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -7936,7 +7948,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>50776 P4P S24 CLD CUP KEY CHAIN PRISM</t>
+          <t>50774 P4P S24 CLD CUP KEY CHAIN PLEATED</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -7969,17 +7981,17 @@
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>15526</t>
+          <t>15513</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>149606</t>
+          <t>149594</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>11150777</t>
+          <t>11150776</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -7989,7 +8001,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>50777 P4P S24 COLD CUP KEY CHAIN BLING</t>
+          <t>50776 P4P S24 CLD CUP KEY CHAIN PRISM</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8022,17 +8034,17 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>149658</t>
+          <t>149606</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>11154026</t>
+          <t>11150777</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8042,7 +8054,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>54026 P4P F24 COLD CUP KEYCHAIN BLACK</t>
+          <t>50777 P4P S24 COLD CUP KEY CHAIN BLING</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8075,17 +8087,17 @@
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>15812</t>
+          <t>15715</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>149699</t>
+          <t>149658</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>11157554</t>
+          <t>11154026</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -8095,7 +8107,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>57554 P4P XM24 COLD CUP KEYCHAIN GREEN</t>
+          <t>54026 P4P F24 COLD CUP KEYCHAIN BLACK</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8128,17 +8140,17 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>15842</t>
+          <t>15812</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>149706</t>
+          <t>149699</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>11157557</t>
+          <t>11157554</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -8148,7 +8160,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>57557 P4P XM24 KEYCHAIN PLUG HOLIDAY</t>
+          <t>57554 P4P XM24 COLD CUP KEYCHAIN GREEN</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8181,17 +8193,17 @@
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>15842</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>149722</t>
+          <t>149706</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>11161850</t>
+          <t>11157557</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8201,7 +8213,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>61850 P4P WCK24 CLD CUP PRISM PVD GLINDA</t>
+          <t>57557 P4P XM24 KEYCHAIN PLUG HOLIDAY</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8234,17 +8246,17 @@
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>15875</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>149726</t>
+          <t>149722</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>11161851</t>
+          <t>11161850</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8254,7 +8266,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>61851 P4P WCK24 CLD CUP PLEATED ELPHABA</t>
+          <t>61850 P4P WCK24 CLD CUP PRISM PVD GLINDA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8287,17 +8299,17 @@
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>15883</t>
+          <t>15879</t>
         </is>
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>149730</t>
+          <t>149726</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>11161852</t>
+          <t>11161851</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -8307,7 +8319,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>61852 P4P WCK24 CLD CUP GEMSTONE</t>
+          <t>61851 P4P WCK24 CLD CUP PLEATED ELPHABA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8340,17 +8352,17 @@
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>15883</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>149811</t>
+          <t>149730</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>11160769</t>
+          <t>11161852</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -8360,7 +8372,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>60769 C16P PNTS25 KEYCHAIN JOE KIND</t>
+          <t>61852 P4P WCK24 CLD CUP GEMSTONE</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8393,17 +8405,17 @@
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>150156</t>
+          <t>149811</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11160769</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -8413,12 +8425,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>LLAVERO OSO BEARISTA ANO SERP CJ50PZAS</t>
+          <t>60769 C16P PNTS25 KEYCHAIN JOE KIND</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8446,12 +8458,12 @@
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>15998</t>
+          <t>15997</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>149752</t>
+          <t>150156</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
@@ -8466,7 +8478,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>LLAVERO OSO BEARISTA SAN VALENT CJ50PZAS</t>
+          <t>LLAVERO OSO BEARISTA ANO SERP CJ50PZAS</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8499,13 +8511,17 @@
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>12980</t>
-        </is>
-      </c>
-      <c r="D141" s="8" t="inlineStr"/>
+          <t>15998</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="inlineStr">
+        <is>
+          <t>149752</t>
+        </is>
+      </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>11118190</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8513,10 +8529,14 @@
           <t>Llavero SBX Genérico</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>LLAVERO OSO BEARISTA SAN VALENT CJ50PZAS</t>
+        </is>
+      </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8544,11 +8564,15 @@
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>14323</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr"/>
-      <c r="E142" s="8" t="inlineStr"/>
+      <c r="E142" s="8" t="inlineStr">
+        <is>
+          <t>11118190</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
           <t>Llavero SBX Genérico</t>
@@ -8585,15 +8609,11 @@
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>14323</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr"/>
-      <c r="E143" s="8" t="inlineStr">
-        <is>
-          <t>11141138</t>
-        </is>
-      </c>
+      <c r="E143" s="8" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>Llavero SBX Genérico</t>
@@ -8630,13 +8650,13 @@
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr"/>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>11144122</t>
+          <t>11141138</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -8675,13 +8695,13 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>15368</t>
+          <t>15070</t>
         </is>
       </c>
       <c r="D145" s="8" t="inlineStr"/>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>11147801</t>
+          <t>11144122</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -8720,13 +8740,13 @@
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>15784</t>
+          <t>15368</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr"/>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11147801</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8765,11 +8785,15 @@
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>53840</t>
+          <t>15784</t>
         </is>
       </c>
       <c r="D147" s="8" t="inlineStr"/>
-      <c r="E147" s="8" t="inlineStr"/>
+      <c r="E147" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr">
         <is>
           <t>Llavero SBX Genérico</t>
@@ -8778,7 +8802,7 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -8802,33 +8826,21 @@
         </is>
       </c>
       <c r="B148" s="7" t="n">
-        <v>6932</v>
+        <v>6944</v>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>16178</t>
-        </is>
-      </c>
-      <c r="D148" s="8" t="inlineStr">
-        <is>
-          <t>149865</t>
-        </is>
-      </c>
-      <c r="E148" s="8" t="inlineStr">
-        <is>
-          <t>11164319</t>
-        </is>
-      </c>
+          <t>53840</t>
+        </is>
+      </c>
+      <c r="D148" s="8" t="inlineStr"/>
+      <c r="E148" s="8" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SI25KeychainZoo</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>64319 P4P S25 SLCN KEYCHAIN BEAR GIRAFFE</t>
-        </is>
-      </c>
+          <t>Llavero SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8841,7 +8853,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>SI25KeychainZoo</t>
+          <t>Llavero SBX Genérico</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -8855,27 +8867,31 @@
         </is>
       </c>
       <c r="B149" s="7" t="n">
-        <v>4686</v>
+        <v>6932</v>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>17307</t>
+          <t>16178</t>
         </is>
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>156359</t>
-        </is>
-      </c>
-      <c r="E149" s="8" t="inlineStr"/>
+          <t>149865</t>
+        </is>
+      </c>
+      <c r="E149" s="8" t="inlineStr">
+        <is>
+          <t>11164319</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SII26Doodle16</t>
+          <t>SI25KeychainZoo</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>86651 C1P FL26 SS TMBLR DDLE IT 16OZ</t>
+          <t>64319 P4P S25 SLCN KEYCHAIN BEAR GIRAFFE</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -8890,7 +8906,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>SII26Doodle16</t>
+          <t>SI25KeychainZoo</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -8904,31 +8920,27 @@
         </is>
       </c>
       <c r="B150" s="7" t="n">
-        <v>4168</v>
+        <v>4686</v>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>17307</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>152610</t>
-        </is>
-      </c>
-      <c r="E150" s="8" t="inlineStr">
-        <is>
-          <t>11177607</t>
-        </is>
-      </c>
+          <t>156359</t>
+        </is>
+      </c>
+      <c r="E150" s="8" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Wt26ReusSiren</t>
+          <t>SII26Doodle16</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>77607 P20P SP26 PLSTC RSBCLCP WMN 24OZ</t>
+          <t>86651 C1P FL26 SS TMBLR DDLE IT 16OZ</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -8943,7 +8955,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Wt26ReusSiren</t>
+          <t>SII26Doodle16</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -8957,27 +8969,31 @@
         </is>
       </c>
       <c r="B151" s="7" t="n">
-        <v>3769</v>
+        <v>4168</v>
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>13694</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>150353</t>
-        </is>
-      </c>
-      <c r="E151" s="8" t="inlineStr"/>
+          <t>152610</t>
+        </is>
+      </c>
+      <c r="E151" s="8" t="inlineStr">
+        <is>
+          <t>11177607</t>
+        </is>
+      </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Filtros Chemex</t>
+          <t>Wt26ReusSiren</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>FILTROS CUADRADOS CHEMEX CJ100PZAS</t>
+          <t>77607 P20P SP26 PLSTC RSBCLCP WMN 24OZ</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -8992,7 +9008,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Filtros Chemex</t>
+          <t>Wt26ReusSiren</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9006,31 +9022,27 @@
         </is>
       </c>
       <c r="B152" s="7" t="n">
-        <v>2785</v>
+        <v>3769</v>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>13694</t>
         </is>
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>154149</t>
-        </is>
-      </c>
-      <c r="E152" s="8" t="inlineStr">
-        <is>
-          <t>11178964</t>
-        </is>
-      </c>
+          <t>150353</t>
+        </is>
+      </c>
+      <c r="E152" s="8" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Sp26KeychainOr</t>
+          <t>Filtros Chemex</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>78964 C4P SM26 PLSTC CLDCP DMLD KEYCHAIN</t>
+          <t>FILTROS CUADRADOS CHEMEX CJ100PZAS</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9045,7 +9057,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Sp26KeychainOr</t>
+          <t>Filtros Chemex</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9059,31 +9071,31 @@
         </is>
       </c>
       <c r="B153" s="7" t="n">
-        <v>2665</v>
+        <v>2785</v>
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>16080</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>149786</t>
+          <t>154149</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178964</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>SII25BdayStopper</t>
+          <t>Sp26KeychainOr</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>TAPON SILICON P/POPOTE CUMPLE CJ50PZAS</t>
+          <t>78964 C4P SM26 PLSTC CLDCP DMLD KEYCHAIN</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9098,7 +9110,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>SII25BdayStopper</t>
+          <t>Sp26KeychainOr</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9112,16 +9124,16 @@
         </is>
       </c>
       <c r="B154" s="7" t="n">
-        <v>2591</v>
+        <v>2665</v>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>16080</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>152973</t>
+          <t>149786</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
@@ -9131,12 +9143,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Wt26VasoJacaran</t>
+          <t>SII25BdayStopper</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>VASO 470ML MORADO ALUMINIO OSO CJ25PZAS</t>
+          <t>TAPON SILICON P/POPOTE CUMPLE CJ50PZAS</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9151,7 +9163,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Wt26VasoJacaran</t>
+          <t>SII25BdayStopper</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9165,31 +9177,31 @@
         </is>
       </c>
       <c r="B155" s="7" t="n">
-        <v>2575</v>
+        <v>2591</v>
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>154142</t>
+          <t>152973</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>11178953</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Sp26SSCC24Oran</t>
+          <t>Wt26VasoJacaran</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>78953 C2P SM26 SS VAC CLD CUP 24OZ</t>
+          <t>VASO 470ML MORADO ALUMINIO OSO CJ25PZAS</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9204,7 +9216,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Sp26SSCC24Oran</t>
+          <t>Wt26VasoJacaran</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9218,31 +9230,31 @@
         </is>
       </c>
       <c r="B156" s="7" t="n">
-        <v>2262</v>
+        <v>2575</v>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>154151</t>
+          <t>154142</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>11179003</t>
+          <t>11178953</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Sp26CC24Teach</t>
+          <t>Sp26SSCC24Oran</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>79003 C2P SM26 PLSTC CLDCP 24OZ</t>
+          <t>78953 C2P SM26 SS VAC CLD CUP 24OZ</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9257,7 +9269,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Sp26CC24Teach</t>
+          <t>Sp26SSCC24Oran</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9271,31 +9283,31 @@
         </is>
       </c>
       <c r="B157" s="7" t="n">
-        <v>1977</v>
+        <v>2262</v>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>16082</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>149788</t>
+          <t>154151</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11179003</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>SII25ClipGirlB</t>
+          <t>Sp26CC24Teach</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>CLIP P/TAZA SUMMER 2 CJ25PZAS</t>
+          <t>79003 C2P SM26 PLSTC CLDCP 24OZ</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -9310,7 +9322,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>SII25ClipGirlB</t>
+          <t>Sp26CC24Teach</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -9328,12 +9340,12 @@
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>149957</t>
+          <t>149788</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
@@ -9348,7 +9360,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>LLAVERO ALOHA CJ50PZAS</t>
+          <t>CLIP P/TAZA SUMMER 2 CJ25PZAS</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -9377,31 +9389,31 @@
         </is>
       </c>
       <c r="B159" s="7" t="n">
-        <v>1766</v>
+        <v>1977</v>
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>16343</t>
         </is>
       </c>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t>154166</t>
+          <t>149957</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>11178966</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>WC26TotePride</t>
+          <t>SII25ClipGirlB</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>78966 P2P SM26 CANVAS TOTE BAG PRIDE</t>
+          <t>LLAVERO ALOHA CJ50PZAS</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -9416,7 +9428,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>WC26TotePride</t>
+          <t>SII25ClipGirlB</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -9430,31 +9442,31 @@
         </is>
       </c>
       <c r="B160" s="7" t="n">
-        <v>1744</v>
+        <v>1766</v>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>15191</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>150106</t>
+          <t>154166</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>11144107</t>
+          <t>11178966</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>COR23 CC24 Green</t>
+          <t>WC26TotePride</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>44107 C2P CORE COLD CUP SOFT TOUCH 24OZ</t>
+          <t>78966 P2P SM26 CANVAS TOTE BAG PRIDE</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -9469,7 +9481,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>COR23 CC24 Green</t>
+          <t>WC26TotePride</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -9483,31 +9495,31 @@
         </is>
       </c>
       <c r="B161" s="7" t="n">
-        <v>1637</v>
+        <v>1744</v>
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>15191</t>
         </is>
       </c>
       <c r="D161" s="8" t="inlineStr">
         <is>
-          <t>152972</t>
+          <t>150106</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11144107</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Wt26VasoFresa</t>
+          <t>COR23 CC24 Green</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>VASO 470ML ROSA ALUMINIO FRESA CJ25PZAS</t>
+          <t>44107 C2P CORE COLD CUP SOFT TOUCH 24OZ</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -9522,7 +9534,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Wt26VasoFresa</t>
+          <t>COR23 CC24 Green</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -9536,31 +9548,31 @@
         </is>
       </c>
       <c r="B162" s="7" t="n">
-        <v>1538</v>
+        <v>1637</v>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>16264</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>149896</t>
+          <t>152972</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>11160967</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>COR26PPBTL20S</t>
+          <t>Wt26VasoFresa</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>60967 C2P CORE RECYCL WTR BTL BEIGE 24OZ</t>
+          <t>VASO 470ML ROSA ALUMINIO FRESA CJ25PZAS</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -9575,7 +9587,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>COR26PPBTL20S</t>
+          <t>Wt26VasoFresa</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -9589,27 +9601,31 @@
         </is>
       </c>
       <c r="B163" s="7" t="n">
-        <v>1481</v>
+        <v>1538</v>
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>16722</t>
+          <t>16264</t>
         </is>
       </c>
       <c r="D163" s="8" t="inlineStr">
         <is>
-          <t>152970</t>
-        </is>
-      </c>
-      <c r="E163" s="8" t="inlineStr"/>
+          <t>149896</t>
+        </is>
+      </c>
+      <c r="E163" s="8" t="inlineStr">
+        <is>
+          <t>11160967</t>
+        </is>
+      </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>BearHuggerSpring</t>
+          <t>COR26PPBTL20S</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>OSO PELUCHE PASCUA CJ32PZAS</t>
+          <t>60967 C2P CORE RECYCL WTR BTL BEIGE 24OZ</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -9624,7 +9640,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>BearHuggerSpring</t>
+          <t>COR26PPBTL20S</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -9638,31 +9654,27 @@
         </is>
       </c>
       <c r="B164" s="7" t="n">
-        <v>1403</v>
+        <v>1481</v>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>154122</t>
-        </is>
-      </c>
-      <c r="E164" s="8" t="inlineStr">
-        <is>
-          <t>11176592</t>
-        </is>
-      </c>
+          <t>152970</t>
+        </is>
+      </c>
+      <c r="E164" s="8" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>SII26SSTu12Pony</t>
+          <t>BearHuggerSpring</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>76592 C1P WIN TBLR PONNIES 12OZ</t>
+          <t>OSO PELUCHE PASCUA CJ32PZAS</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -9677,7 +9689,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>SII26SSTu12Pony</t>
+          <t>BearHuggerSpring</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -9691,31 +9703,31 @@
         </is>
       </c>
       <c r="B165" s="7" t="n">
-        <v>1311</v>
+        <v>1403</v>
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>16779</t>
         </is>
       </c>
       <c r="D165" s="8" t="inlineStr">
         <is>
-          <t>154127</t>
+          <t>154122</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>1176593</t>
+          <t>11176592</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>SII26BTL16Pony</t>
+          <t>SII26SSTu12Pony</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>76593 C1P W26 WTBL SS PONY AND FLWR 16OZ</t>
+          <t>76592 C1P WIN TBLR PONNIES 12OZ</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -9730,7 +9742,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>SII26BTL16Pony</t>
+          <t>SII26SSTu12Pony</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -9744,21 +9756,33 @@
         </is>
       </c>
       <c r="B166" s="7" t="n">
-        <v>1300</v>
+        <v>1311</v>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>54192</t>
-        </is>
-      </c>
-      <c r="D166" s="8" t="inlineStr"/>
-      <c r="E166" s="8" t="inlineStr"/>
+          <t>16793</t>
+        </is>
+      </c>
+      <c r="D166" s="8" t="inlineStr">
+        <is>
+          <t>154127</t>
+        </is>
+      </c>
+      <c r="E166" s="8" t="inlineStr">
+        <is>
+          <t>1176593</t>
+        </is>
+      </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>SII26GICCColor</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr"/>
+          <t>SII26BTL16Pony</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>76593 C1P W26 WTBL SS PONY AND FLWR 16OZ</t>
+        </is>
+      </c>
       <c r="H166" t="inlineStr">
         <is>
           <t>NO</t>
@@ -9771,7 +9795,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>SII26GICCColor</t>
+          <t>SII26BTL16Pony</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -9785,33 +9809,21 @@
         </is>
       </c>
       <c r="B167" s="7" t="n">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>16081</t>
-        </is>
-      </c>
-      <c r="D167" s="8" t="inlineStr">
-        <is>
-          <t>149787</t>
-        </is>
-      </c>
-      <c r="E167" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>54192</t>
+        </is>
+      </c>
+      <c r="D167" s="8" t="inlineStr"/>
+      <c r="E167" s="8" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>SII25ClipBoyB</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>CLIP P/TAZA SUMMER 1 CJ25PZAS</t>
-        </is>
-      </c>
+          <t>SII26GICCColor</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
           <t>NO</t>
@@ -9824,7 +9836,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>SII25ClipBoyB</t>
+          <t>SII26GICCColor</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -9838,16 +9850,16 @@
         </is>
       </c>
       <c r="B168" s="7" t="n">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>16502</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>150023</t>
+          <t>149787</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
@@ -9857,12 +9869,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Xm25Tag</t>
+          <t>SII25ClipBoyB</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>TAG MALETA OSO CJ25PZAS</t>
+          <t>CLIP P/TAZA SUMMER 1 CJ25PZAS</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -9877,7 +9889,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Xm25Tag</t>
+          <t>SII25ClipBoyB</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -9895,17 +9907,29 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>53962</t>
-        </is>
-      </c>
-      <c r="D169" s="8" t="inlineStr"/>
-      <c r="E169" s="8" t="inlineStr"/>
+          <t>16502</t>
+        </is>
+      </c>
+      <c r="D169" s="8" t="inlineStr">
+        <is>
+          <t>150023</t>
+        </is>
+      </c>
+      <c r="E169" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F169" t="inlineStr">
         <is>
           <t>Xm25Tag</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>TAG MALETA OSO CJ25PZAS</t>
+        </is>
+      </c>
       <c r="H169" t="inlineStr">
         <is>
           <t>NO</t>
@@ -9932,36 +9956,24 @@
         </is>
       </c>
       <c r="B170" s="7" t="n">
-        <v>1154</v>
+        <v>1276</v>
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>16107</t>
-        </is>
-      </c>
-      <c r="D170" s="8" t="inlineStr">
-        <is>
-          <t>149810</t>
-        </is>
-      </c>
-      <c r="E170" s="8" t="inlineStr">
-        <is>
-          <t>11160768</t>
-        </is>
-      </c>
+          <t>53962</t>
+        </is>
+      </c>
+      <c r="D170" s="8" t="inlineStr"/>
+      <c r="E170" s="8" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tote bags SBX Genérico</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>60768 P5P PNTS25 JOE KIND TOTE BAG</t>
-        </is>
-      </c>
+          <t>Xm25Tag</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -9971,7 +9983,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Tote bags SBX Genérico</t>
+          <t>Xm25Tag</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -9989,17 +10001,17 @@
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>15967</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="D171" s="8" t="inlineStr">
         <is>
-          <t>149744</t>
+          <t>149810</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>11161004</t>
+          <t>11160768</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -10009,12 +10021,12 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>61004 P2P CORE REUS WTR BTL CARRYING BAG</t>
+          <t>60768 P5P PNTS25 JOE KIND TOTE BAG</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10024,7 +10036,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Tote bags SBX Genérico, Wt25CrarryingBag</t>
+          <t>Tote bags SBX Genérico</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10042,13 +10054,17 @@
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>12318</t>
-        </is>
-      </c>
-      <c r="D172" s="8" t="inlineStr"/>
+          <t>15967</t>
+        </is>
+      </c>
+      <c r="D172" s="8" t="inlineStr">
+        <is>
+          <t>149744</t>
+        </is>
+      </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>11101960</t>
+          <t>11161004</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -10056,10 +10072,14 @@
           <t>Tote bags SBX Genérico</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>61004 P2P CORE REUS WTR BTL CARRYING BAG</t>
+        </is>
+      </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10069,7 +10089,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Tote bags SBX Genérico</t>
+          <t>Tote bags SBX Genérico, Wt25CrarryingBag</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -10087,13 +10107,13 @@
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>12819</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="D173" s="8" t="inlineStr"/>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>11115490</t>
+          <t>11101960</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -10132,11 +10152,15 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>53842</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="D174" s="8" t="inlineStr"/>
-      <c r="E174" s="8" t="inlineStr"/>
+      <c r="E174" s="8" t="inlineStr">
+        <is>
+          <t>11115490</t>
+        </is>
+      </c>
       <c r="F174" t="inlineStr">
         <is>
           <t>Tote bags SBX Genérico</t>
@@ -10145,7 +10169,7 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10169,33 +10193,21 @@
         </is>
       </c>
       <c r="B175" s="7" t="n">
-        <v>1051</v>
+        <v>1154</v>
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>16899</t>
-        </is>
-      </c>
-      <c r="D175" s="8" t="inlineStr">
-        <is>
-          <t>154160</t>
-        </is>
-      </c>
-      <c r="E175" s="8" t="inlineStr">
-        <is>
-          <t>11179004</t>
-        </is>
-      </c>
+          <t>53842</t>
+        </is>
+      </c>
+      <c r="D175" s="8" t="inlineStr"/>
+      <c r="E175" s="8" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Sp26Tu16Teach</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>79004 C2P SM26 SS VAC TMBLR TEACHER 16OZ</t>
-        </is>
-      </c>
+          <t>Tote bags SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
           <t>NO</t>
@@ -10208,7 +10220,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Sp26Tu16Teach</t>
+          <t>Tote bags SBX Genérico</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -10222,27 +10234,31 @@
         </is>
       </c>
       <c r="B176" s="7" t="n">
-        <v>976</v>
+        <v>1051</v>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>154133</t>
-        </is>
-      </c>
-      <c r="E176" s="8" t="inlineStr"/>
+          <t>154160</t>
+        </is>
+      </c>
+      <c r="E176" s="8" t="inlineStr">
+        <is>
+          <t>11179004</t>
+        </is>
+      </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>BearHugWorldCup</t>
+          <t>Sp26Tu16Teach</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>OSO PELUCHE WC SBX 2026 CJ15PZAS</t>
+          <t>79004 C2P SM26 SS VAC TMBLR TEACHER 16OZ</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -10257,7 +10273,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>BearHugWorldCup</t>
+          <t>Sp26Tu16Teach</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -10271,31 +10287,27 @@
         </is>
       </c>
       <c r="B177" s="7" t="n">
-        <v>865</v>
+        <v>976</v>
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>16828</t>
         </is>
       </c>
       <c r="D177" s="8" t="inlineStr">
         <is>
-          <t>149914</t>
-        </is>
-      </c>
-      <c r="E177" s="8" t="inlineStr">
-        <is>
-          <t>11161003</t>
-        </is>
-      </c>
+          <t>154133</t>
+        </is>
+      </c>
+      <c r="E177" s="8" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>COR26Stan30White</t>
+          <t>BearHugWorldCup</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>61003 C1P F25 CORE SS TMBLR CREAM 30OZ</t>
+          <t>OSO PELUCHE WC SBX 2026 CJ15PZAS</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -10310,7 +10322,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>COR26Stan30White</t>
+          <t>BearHugWorldCup</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -10324,31 +10336,31 @@
         </is>
       </c>
       <c r="B178" s="7" t="n">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>16503</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="D178" s="8" t="inlineStr">
         <is>
-          <t>150024</t>
+          <t>149914</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11161003</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Xm25Stopper</t>
+          <t>COR26Stan30White</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>STOPPER PINGUINO CJ25PZAS</t>
+          <t>61003 C1P F25 CORE SS TMBLR CREAM 30OZ</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -10363,7 +10375,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Xm25Stopper</t>
+          <t>COR26Stan30White</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -10377,31 +10389,31 @@
         </is>
       </c>
       <c r="B179" s="7" t="n">
-        <v>823</v>
+        <v>850</v>
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>16878</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="D179" s="8" t="inlineStr">
         <is>
-          <t>154144</t>
+          <t>150024</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>11178921</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sp26Tu16Orange</t>
+          <t>Xm25Stopper</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>78921 C2P SM26 PLSTC TMBLR SWIRL 16OZ</t>
+          <t>STOPPER PINGUINO CJ25PZAS</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -10416,7 +10428,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Sp26Tu16Orange</t>
+          <t>Xm25Stopper</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -10430,31 +10442,31 @@
         </is>
       </c>
       <c r="B180" s="7" t="n">
-        <v>796</v>
+        <v>823</v>
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>16769</t>
+          <t>16878</t>
         </is>
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>155921</t>
+          <t>154144</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178921</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Wt26VasoPistache</t>
+          <t>Sp26Tu16Orange</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>VASO 470ML VERDE ALUMINIO OSO CJ25PZAS</t>
+          <t>78921 C2P SM26 PLSTC TMBLR SWIRL 16OZ</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -10469,7 +10481,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Wt26VasoPistache</t>
+          <t>Sp26Tu16Orange</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -10483,16 +10495,16 @@
         </is>
       </c>
       <c r="B181" s="7" t="n">
-        <v>760</v>
+        <v>796</v>
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="D181" s="8" t="inlineStr">
         <is>
-          <t>149985</t>
+          <t>155921</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -10502,12 +10514,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Fl25MonederoAniv</t>
+          <t>Wt26VasoPistache</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>MONEDERO SIRENA CJ10PZAS</t>
+          <t>VASO 470ML VERDE ALUMINIO OSO CJ25PZAS</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -10522,7 +10534,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Fl25MonederoAniv</t>
+          <t>Wt26VasoPistache</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -10536,31 +10548,31 @@
         </is>
       </c>
       <c r="B182" s="7" t="n">
-        <v>659</v>
+        <v>760</v>
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>16446</t>
         </is>
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>152582</t>
+          <t>149985</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>11170108</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>DiscoveryTulum</t>
+          <t>Fl25MonederoAniv</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>70108 C4P DIS STN MUG TULUM 14OZ</t>
+          <t>MONEDERO SIRENA CJ10PZAS</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -10575,7 +10587,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>DiscoveryTulum</t>
+          <t>Fl25MonederoAniv</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -10589,36 +10601,36 @@
         </is>
       </c>
       <c r="B183" s="7" t="n">
-        <v>634</v>
+        <v>659</v>
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>15312</t>
+          <t>16652</t>
         </is>
       </c>
       <c r="D183" s="8" t="inlineStr">
         <is>
-          <t>149552</t>
+          <t>152582</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>11147705</t>
+          <t>11170108</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tazas SBX Genérico</t>
+          <t>DiscoveryTulum</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>47705 C2P W24 CERMC MUG HEART 12OZ</t>
+          <t>70108 C4P DIS STN MUG TULUM 14OZ</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -10628,7 +10640,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Tazas SBX Genérico</t>
+          <t>DiscoveryTulum</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -10646,17 +10658,17 @@
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>15490</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>150111</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>11150697</t>
+          <t>11147705</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10666,7 +10678,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>50697 C2P S24 CERMC TMBLR ANGULAR 12OZ</t>
+          <t>47705 C2P W24 CERMC MUG HEART 12OZ</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -10699,17 +10711,17 @@
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>15509</t>
+          <t>15490</t>
         </is>
       </c>
       <c r="D185" s="8" t="inlineStr">
         <is>
-          <t>149590</t>
+          <t>150111</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>11150698</t>
+          <t>11150697</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -10719,7 +10731,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>50698 C2P S24 CERMC MUG MOTHERS DAY 12OZ</t>
+          <t>50697 C2P S24 CERMC TMBLR ANGULAR 12OZ</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -10752,17 +10764,17 @@
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>15516</t>
+          <t>15509</t>
         </is>
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>149597</t>
+          <t>149590</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>11150701</t>
+          <t>11150698</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -10772,7 +10784,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>50701 C2P S24 CERMC MUG PUFFY 12OZ</t>
+          <t>50698 C2P S24 CERMC MUG MOTHERS DAY 12OZ</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -10805,17 +10817,17 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>15517</t>
+          <t>15516</t>
         </is>
       </c>
       <c r="D187" s="8" t="inlineStr">
         <is>
-          <t>149598</t>
+          <t>149597</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>11150705</t>
+          <t>11150701</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -10825,7 +10837,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>50705 C2P S24 GLASS MUG 90S 14OZ</t>
+          <t>50701 C2P S24 CERMC MUG PUFFY 12OZ</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -10858,17 +10870,17 @@
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>149659</t>
+          <t>149598</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>11153958</t>
+          <t>11150705</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -10878,7 +10890,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>53958 C2P F24 CERMC TMBLR DIAGONAL 12OZ</t>
+          <t>50705 C2P S24 GLASS MUG 90S 14OZ</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -10911,17 +10923,17 @@
       </c>
       <c r="C189" s="8" t="inlineStr">
         <is>
-          <t>15723</t>
+          <t>15718</t>
         </is>
       </c>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t>149664</t>
+          <t>149659</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>11154007</t>
+          <t>11153958</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -10931,7 +10943,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>54007 C1P F24 SS MUG SUGAR SKULL 12OZ</t>
+          <t>53958 C2P F24 CERMC TMBLR DIAGONAL 12OZ</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -10964,17 +10976,17 @@
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>15727</t>
+          <t>15723</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t>149667</t>
+          <t>149664</t>
         </is>
       </c>
       <c r="E190" s="8" t="inlineStr">
         <is>
-          <t>11153959</t>
+          <t>11154007</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -10984,7 +10996,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>53959 C2P F24 CRMC TMBLR HALLOWEEN 12OZ</t>
+          <t>54007 C1P F24 SS MUG SUGAR SKULL 12OZ</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -11017,17 +11029,17 @@
       </c>
       <c r="C191" s="8" t="inlineStr">
         <is>
-          <t>15740</t>
+          <t>15727</t>
         </is>
       </c>
       <c r="D191" s="8" t="inlineStr">
         <is>
-          <t>149672</t>
+          <t>149667</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>11153976</t>
+          <t>11153959</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -11037,7 +11049,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>53976 C2P F24 SUSTAIN RECYCLD MUG 16OZ</t>
+          <t>53959 C2P F24 CRMC TMBLR HALLOWEEN 12OZ</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -11070,17 +11082,17 @@
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>15815</t>
+          <t>15740</t>
         </is>
       </c>
       <c r="D192" s="8" t="inlineStr">
         <is>
-          <t>149701</t>
+          <t>149672</t>
         </is>
       </c>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>11157505</t>
+          <t>11153976</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -11090,7 +11102,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>57505 C1P XM24 CERMC TMBLR GROOVE 2OZ</t>
+          <t>53976 C2P F24 SUSTAIN RECYCLD MUG 16OZ</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -11123,17 +11135,17 @@
       </c>
       <c r="C193" s="8" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>15815</t>
         </is>
       </c>
       <c r="D193" s="8" t="inlineStr">
         <is>
-          <t>149702</t>
+          <t>149701</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>11157512</t>
+          <t>11157505</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -11143,7 +11155,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>57512 C2P XM24 CERMC MUG MINT GREE 14OZ</t>
+          <t>57505 C1P XM24 CERMC TMBLR GROOVE 2OZ</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -11176,17 +11188,17 @@
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="D194" s="8" t="inlineStr">
         <is>
-          <t>149703</t>
+          <t>149702</t>
         </is>
       </c>
       <c r="E194" s="8" t="inlineStr">
         <is>
-          <t>11157513</t>
+          <t>11157512</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -11196,7 +11208,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>57513 C2P XMA4 CRM MUG BEAR HOLIDAY 14OZ</t>
+          <t>57512 C2P XM24 CERMC MUG MINT GREE 14OZ</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -11229,17 +11241,17 @@
       </c>
       <c r="C195" s="8" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>15828</t>
         </is>
       </c>
       <c r="D195" s="8" t="inlineStr">
         <is>
-          <t>150130</t>
+          <t>149703</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>11157509</t>
+          <t>11157513</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -11249,7 +11261,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>57509 C2P XM24 CERMC TMBLR HOLIDAY 12OZ</t>
+          <t>57513 C2P XMA4 CRM MUG BEAR HOLIDAY 14OZ</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -11282,17 +11294,17 @@
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>15841</t>
         </is>
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>149772</t>
+          <t>150130</t>
         </is>
       </c>
       <c r="E196" s="8" t="inlineStr">
         <is>
-          <t>11162615</t>
+          <t>11157509</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -11302,7 +11314,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>62615 C2P SP25 CERMC MUG CHERRY 16OZ</t>
+          <t>57509 C2P XM24 CERMC TMBLR HOLIDAY 12OZ</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -11335,17 +11347,17 @@
       </c>
       <c r="C197" s="8" t="inlineStr">
         <is>
-          <t>16066</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="D197" s="8" t="inlineStr">
         <is>
-          <t>149773</t>
+          <t>149772</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>11162614</t>
+          <t>11162615</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -11355,7 +11367,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>62614 C2P SP25 MUG FROSTED PINK 14OZ</t>
+          <t>62615 C2P SP25 CERMC MUG CHERRY 16OZ</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -11388,17 +11400,17 @@
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>16066</t>
         </is>
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>149797</t>
+          <t>149773</t>
         </is>
       </c>
       <c r="E198" s="8" t="inlineStr">
         <is>
-          <t>11163290</t>
+          <t>11162614</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -11408,7 +11420,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>63290 C2P PNTS25 CERMC MUG YELLOW 14OZ</t>
+          <t>62614 C2P SP25 MUG FROSTED PINK 14OZ</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -11441,17 +11453,17 @@
       </c>
       <c r="C199" s="8" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16094</t>
         </is>
       </c>
       <c r="D199" s="8" t="inlineStr">
         <is>
-          <t>149807</t>
+          <t>149797</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>11160765</t>
+          <t>11163290</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -11461,7 +11473,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>60765 C1P PNTS25 CERMC MUG JOE WCAP 12OZ</t>
+          <t>63290 C2P PNTS25 CERMC MUG YELLOW 14OZ</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -11494,17 +11506,17 @@
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>15951</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>150142</t>
+          <t>149807</t>
         </is>
       </c>
       <c r="E200" s="8" t="inlineStr">
         <is>
-          <t>11160945</t>
+          <t>11160765</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -11514,12 +11526,12 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>60945 C1P W25 CERMC DW TMBLR TWIST 12OZ</t>
+          <t>60765 C1P PNTS25 CERMC MUG JOE WCAP 12OZ</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -11547,17 +11559,17 @@
       </c>
       <c r="C201" s="8" t="inlineStr">
         <is>
-          <t>15952</t>
+          <t>15951</t>
         </is>
       </c>
       <c r="D201" s="8" t="inlineStr">
         <is>
-          <t>150143</t>
+          <t>150142</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>11160946</t>
+          <t>11160945</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -11567,7 +11579,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>60946 C2P W25 CERMC MUG HEART BLUE 12OZ</t>
+          <t>60945 C1P W25 CERMC DW TMBLR TWIST 12OZ</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -11600,17 +11612,17 @@
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>16059</t>
+          <t>15952</t>
         </is>
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>149766</t>
+          <t>150143</t>
         </is>
       </c>
       <c r="E202" s="8" t="inlineStr">
         <is>
-          <t>11163341</t>
+          <t>11160946</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -11620,7 +11632,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>63341 C2P SP25 SS MUG CONTOUR MINT 12OZ</t>
+          <t>60946 C2P W25 CERMC MUG HEART BLUE 12OZ</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -11653,13 +11665,17 @@
       </c>
       <c r="C203" s="8" t="inlineStr">
         <is>
-          <t>9506</t>
-        </is>
-      </c>
-      <c r="D203" s="8" t="inlineStr"/>
+          <t>16059</t>
+        </is>
+      </c>
+      <c r="D203" s="8" t="inlineStr">
+        <is>
+          <t>149766</t>
+        </is>
+      </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>11042169</t>
+          <t>11163341</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -11667,10 +11683,14 @@
           <t>Tazas SBX Genérico</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>63341 C2P SP25 SS MUG CONTOUR MINT 12OZ</t>
+        </is>
+      </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -11698,13 +11718,13 @@
       </c>
       <c r="C204" s="8" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="D204" s="8" t="inlineStr"/>
       <c r="E204" s="8" t="inlineStr">
         <is>
-          <t>11093759</t>
+          <t>11042169</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -11743,13 +11763,13 @@
       </c>
       <c r="C205" s="8" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12031</t>
         </is>
       </c>
       <c r="D205" s="8" t="inlineStr"/>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>11091114</t>
+          <t>11093759</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -11788,13 +11808,13 @@
       </c>
       <c r="C206" s="8" t="inlineStr">
         <is>
-          <t>12035</t>
+          <t>12032</t>
         </is>
       </c>
       <c r="D206" s="8" t="inlineStr"/>
       <c r="E206" s="8" t="inlineStr">
         <is>
-          <t>11091115</t>
+          <t>11091114</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -11833,13 +11853,13 @@
       </c>
       <c r="C207" s="8" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>12035</t>
         </is>
       </c>
       <c r="D207" s="8" t="inlineStr"/>
       <c r="E207" s="8" t="inlineStr">
         <is>
-          <t>11094813</t>
+          <t>11091115</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -11878,13 +11898,13 @@
       </c>
       <c r="C208" s="8" t="inlineStr">
         <is>
-          <t>12317</t>
+          <t>12142</t>
         </is>
       </c>
       <c r="D208" s="8" t="inlineStr"/>
       <c r="E208" s="8" t="inlineStr">
         <is>
-          <t>11101957</t>
+          <t>11094813</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -11923,13 +11943,13 @@
       </c>
       <c r="C209" s="8" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="D209" s="8" t="inlineStr"/>
       <c r="E209" s="8" t="inlineStr">
         <is>
-          <t>11103793</t>
+          <t>11101957</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -11968,13 +11988,13 @@
       </c>
       <c r="C210" s="8" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12464</t>
         </is>
       </c>
       <c r="D210" s="8" t="inlineStr"/>
       <c r="E210" s="8" t="inlineStr">
         <is>
-          <t>11091825</t>
+          <t>11103793</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -12013,13 +12033,13 @@
       </c>
       <c r="C211" s="8" t="inlineStr">
         <is>
-          <t>12554</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="D211" s="8" t="inlineStr"/>
       <c r="E211" s="8" t="inlineStr">
         <is>
-          <t>11109979</t>
+          <t>11091825</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -12058,13 +12078,13 @@
       </c>
       <c r="C212" s="8" t="inlineStr">
         <is>
-          <t>12555</t>
+          <t>12554</t>
         </is>
       </c>
       <c r="D212" s="8" t="inlineStr"/>
       <c r="E212" s="8" t="inlineStr">
         <is>
-          <t>11109980</t>
+          <t>11109979</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -12103,13 +12123,13 @@
       </c>
       <c r="C213" s="8" t="inlineStr">
         <is>
-          <t>12559</t>
+          <t>12555</t>
         </is>
       </c>
       <c r="D213" s="8" t="inlineStr"/>
       <c r="E213" s="8" t="inlineStr">
         <is>
-          <t>11109994</t>
+          <t>11109980</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -12148,13 +12168,13 @@
       </c>
       <c r="C214" s="8" t="inlineStr">
         <is>
-          <t>12640</t>
+          <t>12559</t>
         </is>
       </c>
       <c r="D214" s="8" t="inlineStr"/>
       <c r="E214" s="8" t="inlineStr">
         <is>
-          <t>11111783</t>
+          <t>11109994</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -12193,13 +12213,13 @@
       </c>
       <c r="C215" s="8" t="inlineStr">
         <is>
-          <t>12696</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="D215" s="8" t="inlineStr"/>
       <c r="E215" s="8" t="inlineStr">
         <is>
-          <t>11113322</t>
+          <t>11111783</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -12238,13 +12258,13 @@
       </c>
       <c r="C216" s="8" t="inlineStr">
         <is>
-          <t>12705</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="D216" s="8" t="inlineStr"/>
       <c r="E216" s="8" t="inlineStr">
         <is>
-          <t>11113324</t>
+          <t>11113322</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -12283,13 +12303,13 @@
       </c>
       <c r="C217" s="8" t="inlineStr">
         <is>
-          <t>12711</t>
+          <t>12705</t>
         </is>
       </c>
       <c r="D217" s="8" t="inlineStr"/>
       <c r="E217" s="8" t="inlineStr">
         <is>
-          <t>11112592</t>
+          <t>11113324</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -12328,13 +12348,13 @@
       </c>
       <c r="C218" s="8" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>12711</t>
         </is>
       </c>
       <c r="D218" s="8" t="inlineStr"/>
       <c r="E218" s="8" t="inlineStr">
         <is>
-          <t>11115401</t>
+          <t>11112592</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -12373,13 +12393,13 @@
       </c>
       <c r="C219" s="8" t="inlineStr">
         <is>
-          <t>12782</t>
+          <t>12781</t>
         </is>
       </c>
       <c r="D219" s="8" t="inlineStr"/>
       <c r="E219" s="8" t="inlineStr">
         <is>
-          <t>11115527</t>
+          <t>11115401</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -12418,13 +12438,13 @@
       </c>
       <c r="C220" s="8" t="inlineStr">
         <is>
-          <t>12796</t>
+          <t>12782</t>
         </is>
       </c>
       <c r="D220" s="8" t="inlineStr"/>
       <c r="E220" s="8" t="inlineStr">
         <is>
-          <t>11115545</t>
+          <t>11115527</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -12463,13 +12483,13 @@
       </c>
       <c r="C221" s="8" t="inlineStr">
         <is>
-          <t>12910</t>
+          <t>12796</t>
         </is>
       </c>
       <c r="D221" s="8" t="inlineStr"/>
       <c r="E221" s="8" t="inlineStr">
         <is>
-          <t>11117009</t>
+          <t>11115545</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -12508,13 +12528,13 @@
       </c>
       <c r="C222" s="8" t="inlineStr">
         <is>
-          <t>12917</t>
+          <t>12910</t>
         </is>
       </c>
       <c r="D222" s="8" t="inlineStr"/>
       <c r="E222" s="8" t="inlineStr">
         <is>
-          <t>11117015</t>
+          <t>11117009</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -12553,13 +12573,13 @@
       </c>
       <c r="C223" s="8" t="inlineStr">
         <is>
-          <t>12975</t>
+          <t>12917</t>
         </is>
       </c>
       <c r="D223" s="8" t="inlineStr"/>
       <c r="E223" s="8" t="inlineStr">
         <is>
-          <t>11118175</t>
+          <t>11117015</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -12598,13 +12618,13 @@
       </c>
       <c r="C224" s="8" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>12975</t>
         </is>
       </c>
       <c r="D224" s="8" t="inlineStr"/>
       <c r="E224" s="8" t="inlineStr">
         <is>
-          <t>11113472</t>
+          <t>11118175</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -12643,13 +12663,13 @@
       </c>
       <c r="C225" s="8" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="D225" s="8" t="inlineStr"/>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>11118193</t>
+          <t>11113472</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -12688,13 +12708,13 @@
       </c>
       <c r="C226" s="8" t="inlineStr">
         <is>
-          <t>13375</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="D226" s="8" t="inlineStr"/>
       <c r="E226" s="8" t="inlineStr">
         <is>
-          <t>11118194</t>
+          <t>11118193</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -12733,13 +12753,13 @@
       </c>
       <c r="C227" s="8" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>13375</t>
         </is>
       </c>
       <c r="D227" s="8" t="inlineStr"/>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>11121186</t>
+          <t>11118194</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -12778,13 +12798,13 @@
       </c>
       <c r="C228" s="8" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="D228" s="8" t="inlineStr"/>
       <c r="E228" s="8" t="inlineStr">
         <is>
-          <t>11124278</t>
+          <t>11121186</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -12823,13 +12843,13 @@
       </c>
       <c r="C229" s="8" t="inlineStr">
         <is>
-          <t>13836</t>
+          <t>13719</t>
         </is>
       </c>
       <c r="D229" s="8" t="inlineStr"/>
       <c r="E229" s="8" t="inlineStr">
         <is>
-          <t>11126371, 11126455</t>
+          <t>11124278</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -12850,7 +12870,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Tazas SBX Genérico, Tumb Plastic SBX Genérico</t>
+          <t>Tazas SBX Genérico</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -12868,13 +12888,13 @@
       </c>
       <c r="C230" s="8" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="D230" s="8" t="inlineStr"/>
       <c r="E230" s="8" t="inlineStr">
         <is>
-          <t>11126380</t>
+          <t>11126371, 11126455</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -12895,7 +12915,7 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Tazas SBX Genérico</t>
+          <t>Tazas SBX Genérico, Tumb Plastic SBX Genérico</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -12913,13 +12933,13 @@
       </c>
       <c r="C231" s="8" t="inlineStr">
         <is>
-          <t>13846</t>
+          <t>13844</t>
         </is>
       </c>
       <c r="D231" s="8" t="inlineStr"/>
       <c r="E231" s="8" t="inlineStr">
         <is>
-          <t>11125952</t>
+          <t>11126380</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -12958,13 +12978,13 @@
       </c>
       <c r="C232" s="8" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="D232" s="8" t="inlineStr"/>
       <c r="E232" s="8" t="inlineStr">
         <is>
-          <t>11127805</t>
+          <t>11125952</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -13003,13 +13023,13 @@
       </c>
       <c r="C233" s="8" t="inlineStr">
         <is>
-          <t>14155</t>
+          <t>14032</t>
         </is>
       </c>
       <c r="D233" s="8" t="inlineStr"/>
       <c r="E233" s="8" t="inlineStr">
         <is>
-          <t>11129137</t>
+          <t>11127805</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -13048,13 +13068,13 @@
       </c>
       <c r="C234" s="8" t="inlineStr">
         <is>
-          <t>14162</t>
+          <t>14155</t>
         </is>
       </c>
       <c r="D234" s="8" t="inlineStr"/>
       <c r="E234" s="8" t="inlineStr">
         <is>
-          <t>11130180</t>
+          <t>11129137</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -13093,13 +13113,13 @@
       </c>
       <c r="C235" s="8" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="D235" s="8" t="inlineStr"/>
       <c r="E235" s="8" t="inlineStr">
         <is>
-          <t>11130181</t>
+          <t>11130180</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -13138,13 +13158,13 @@
       </c>
       <c r="C236" s="8" t="inlineStr">
         <is>
-          <t>14173</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="D236" s="8" t="inlineStr"/>
       <c r="E236" s="8" t="inlineStr">
         <is>
-          <t>11130192</t>
+          <t>11130181</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -13183,13 +13203,13 @@
       </c>
       <c r="C237" s="8" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>14173</t>
         </is>
       </c>
       <c r="D237" s="8" t="inlineStr"/>
       <c r="E237" s="8" t="inlineStr">
         <is>
-          <t>11130706</t>
+          <t>11130192</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -13228,13 +13248,13 @@
       </c>
       <c r="C238" s="8" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="D238" s="8" t="inlineStr"/>
       <c r="E238" s="8" t="inlineStr">
         <is>
-          <t>11130721</t>
+          <t>11130706</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -13273,13 +13293,13 @@
       </c>
       <c r="C239" s="8" t="inlineStr">
         <is>
-          <t>14361</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="D239" s="8" t="inlineStr"/>
       <c r="E239" s="8" t="inlineStr">
         <is>
-          <t>11133659</t>
+          <t>11130721</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -13318,13 +13338,13 @@
       </c>
       <c r="C240" s="8" t="inlineStr">
         <is>
-          <t>14441</t>
+          <t>14361</t>
         </is>
       </c>
       <c r="D240" s="8" t="inlineStr"/>
       <c r="E240" s="8" t="inlineStr">
         <is>
-          <t>11134118</t>
+          <t>11133659</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -13363,13 +13383,13 @@
       </c>
       <c r="C241" s="8" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>14441</t>
         </is>
       </c>
       <c r="D241" s="8" t="inlineStr"/>
       <c r="E241" s="8" t="inlineStr">
         <is>
-          <t>11133735</t>
+          <t>11134118</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -13408,13 +13428,13 @@
       </c>
       <c r="C242" s="8" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="D242" s="8" t="inlineStr"/>
       <c r="E242" s="8" t="inlineStr">
         <is>
-          <t>11133683</t>
+          <t>11133735</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -13453,13 +13473,13 @@
       </c>
       <c r="C243" s="8" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="D243" s="8" t="inlineStr"/>
       <c r="E243" s="8" t="inlineStr">
         <is>
-          <t>11133714</t>
+          <t>11133683</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -13498,13 +13518,13 @@
       </c>
       <c r="C244" s="8" t="inlineStr">
         <is>
-          <t>14454</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="D244" s="8" t="inlineStr"/>
       <c r="E244" s="8" t="inlineStr">
         <is>
-          <t>11133698</t>
+          <t>11133714</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -13543,13 +13563,13 @@
       </c>
       <c r="C245" s="8" t="inlineStr">
         <is>
-          <t>14595</t>
+          <t>14454</t>
         </is>
       </c>
       <c r="D245" s="8" t="inlineStr"/>
       <c r="E245" s="8" t="inlineStr">
         <is>
-          <t>11135998</t>
+          <t>11133698</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -13588,13 +13608,13 @@
       </c>
       <c r="C246" s="8" t="inlineStr">
         <is>
-          <t>14596</t>
+          <t>14595</t>
         </is>
       </c>
       <c r="D246" s="8" t="inlineStr"/>
       <c r="E246" s="8" t="inlineStr">
         <is>
-          <t>11135979</t>
+          <t>11135998</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -13633,13 +13653,13 @@
       </c>
       <c r="C247" s="8" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>14596</t>
         </is>
       </c>
       <c r="D247" s="8" t="inlineStr"/>
       <c r="E247" s="8" t="inlineStr">
         <is>
-          <t>11135981</t>
+          <t>11135979</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -13678,13 +13698,13 @@
       </c>
       <c r="C248" s="8" t="inlineStr">
         <is>
-          <t>14702</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="D248" s="8" t="inlineStr"/>
       <c r="E248" s="8" t="inlineStr">
         <is>
-          <t>11138070</t>
+          <t>11135981</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -13723,13 +13743,13 @@
       </c>
       <c r="C249" s="8" t="inlineStr">
         <is>
-          <t>14710</t>
+          <t>14702</t>
         </is>
       </c>
       <c r="D249" s="8" t="inlineStr"/>
       <c r="E249" s="8" t="inlineStr">
         <is>
-          <t>11138093</t>
+          <t>11138070</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -13768,13 +13788,13 @@
       </c>
       <c r="C250" s="8" t="inlineStr">
         <is>
-          <t>14751</t>
+          <t>14710</t>
         </is>
       </c>
       <c r="D250" s="8" t="inlineStr"/>
       <c r="E250" s="8" t="inlineStr">
         <is>
-          <t>11140064</t>
+          <t>11138093</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -13813,13 +13833,13 @@
       </c>
       <c r="C251" s="8" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>14751</t>
         </is>
       </c>
       <c r="D251" s="8" t="inlineStr"/>
       <c r="E251" s="8" t="inlineStr">
         <is>
-          <t>11140066</t>
+          <t>11140064</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -13858,13 +13878,13 @@
       </c>
       <c r="C252" s="8" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="D252" s="8" t="inlineStr"/>
       <c r="E252" s="8" t="inlineStr">
         <is>
-          <t>11140085</t>
+          <t>11140066</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -13903,13 +13923,13 @@
       </c>
       <c r="C253" s="8" t="inlineStr">
         <is>
-          <t>14766</t>
+          <t>14760</t>
         </is>
       </c>
       <c r="D253" s="8" t="inlineStr"/>
       <c r="E253" s="8" t="inlineStr">
         <is>
-          <t>11140102</t>
+          <t>11140085</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -13948,13 +13968,13 @@
       </c>
       <c r="C254" s="8" t="inlineStr">
         <is>
-          <t>14822</t>
+          <t>14766</t>
         </is>
       </c>
       <c r="D254" s="8" t="inlineStr"/>
       <c r="E254" s="8" t="inlineStr">
         <is>
-          <t>11141044</t>
+          <t>11140102</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -13993,13 +14013,13 @@
       </c>
       <c r="C255" s="8" t="inlineStr">
         <is>
-          <t>15054</t>
+          <t>14822</t>
         </is>
       </c>
       <c r="D255" s="8" t="inlineStr"/>
       <c r="E255" s="8" t="inlineStr">
         <is>
-          <t>11144058</t>
+          <t>11141044</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -14038,13 +14058,13 @@
       </c>
       <c r="C256" s="8" t="inlineStr">
         <is>
-          <t>15055</t>
+          <t>15054</t>
         </is>
       </c>
       <c r="D256" s="8" t="inlineStr"/>
       <c r="E256" s="8" t="inlineStr">
         <is>
-          <t>11144059</t>
+          <t>11144058</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -14083,13 +14103,13 @@
       </c>
       <c r="C257" s="8" t="inlineStr">
         <is>
-          <t>15065</t>
+          <t>15055</t>
         </is>
       </c>
       <c r="D257" s="8" t="inlineStr"/>
       <c r="E257" s="8" t="inlineStr">
         <is>
-          <t>11144067</t>
+          <t>11144059</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -14128,13 +14148,13 @@
       </c>
       <c r="C258" s="8" t="inlineStr">
         <is>
-          <t>15071</t>
+          <t>15065</t>
         </is>
       </c>
       <c r="D258" s="8" t="inlineStr"/>
       <c r="E258" s="8" t="inlineStr">
         <is>
-          <t>11144061</t>
+          <t>11144067</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -14173,13 +14193,13 @@
       </c>
       <c r="C259" s="8" t="inlineStr">
         <is>
-          <t>15072</t>
+          <t>15071</t>
         </is>
       </c>
       <c r="D259" s="8" t="inlineStr"/>
       <c r="E259" s="8" t="inlineStr">
         <is>
-          <t>11144062</t>
+          <t>11144061</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -14218,13 +14238,13 @@
       </c>
       <c r="C260" s="8" t="inlineStr">
         <is>
-          <t>15075</t>
+          <t>15072</t>
         </is>
       </c>
       <c r="D260" s="8" t="inlineStr"/>
       <c r="E260" s="8" t="inlineStr">
         <is>
-          <t>11144069</t>
+          <t>11144062</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -14263,13 +14283,13 @@
       </c>
       <c r="C261" s="8" t="inlineStr">
         <is>
-          <t>15076</t>
+          <t>15075</t>
         </is>
       </c>
       <c r="D261" s="8" t="inlineStr"/>
       <c r="E261" s="8" t="inlineStr">
         <is>
-          <t>11144064</t>
+          <t>11144069</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -14308,13 +14328,13 @@
       </c>
       <c r="C262" s="8" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>15076</t>
         </is>
       </c>
       <c r="D262" s="8" t="inlineStr"/>
       <c r="E262" s="8" t="inlineStr">
         <is>
-          <t>11146212</t>
+          <t>11144064</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -14353,13 +14373,13 @@
       </c>
       <c r="C263" s="8" t="inlineStr">
         <is>
-          <t>15171</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="D263" s="8" t="inlineStr"/>
       <c r="E263" s="8" t="inlineStr">
         <is>
-          <t>11146143</t>
+          <t>11146212</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -14398,13 +14418,13 @@
       </c>
       <c r="C264" s="8" t="inlineStr">
         <is>
-          <t>15172</t>
+          <t>15171</t>
         </is>
       </c>
       <c r="D264" s="8" t="inlineStr"/>
       <c r="E264" s="8" t="inlineStr">
         <is>
-          <t>11146140</t>
+          <t>11146143</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -14443,13 +14463,13 @@
       </c>
       <c r="C265" s="8" t="inlineStr">
         <is>
-          <t>15178</t>
+          <t>15172</t>
         </is>
       </c>
       <c r="D265" s="8" t="inlineStr"/>
       <c r="E265" s="8" t="inlineStr">
         <is>
-          <t>11146144</t>
+          <t>11146140</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -14488,13 +14508,13 @@
       </c>
       <c r="C266" s="8" t="inlineStr">
         <is>
-          <t>15179</t>
+          <t>15178</t>
         </is>
       </c>
       <c r="D266" s="8" t="inlineStr"/>
       <c r="E266" s="8" t="inlineStr">
         <is>
-          <t>11146145</t>
+          <t>11146144</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -14533,13 +14553,13 @@
       </c>
       <c r="C267" s="8" t="inlineStr">
         <is>
-          <t>15189</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="D267" s="8" t="inlineStr"/>
       <c r="E267" s="8" t="inlineStr">
         <is>
-          <t>11141054</t>
+          <t>11146145</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -14560,7 +14580,7 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>COR25Mug 16Sus, Tazas SBX Genérico</t>
+          <t>Tazas SBX Genérico</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
@@ -14578,13 +14598,13 @@
       </c>
       <c r="C268" s="8" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="D268" s="8" t="inlineStr"/>
       <c r="E268" s="8" t="inlineStr">
         <is>
-          <t>11147707</t>
+          <t>11141054</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -14605,7 +14625,7 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Tazas SBX Genérico</t>
+          <t>COR25Mug 16Sus, Tazas SBX Genérico</t>
         </is>
       </c>
       <c r="K268" t="inlineStr"/>
@@ -14623,13 +14643,13 @@
       </c>
       <c r="C269" s="8" t="inlineStr">
         <is>
-          <t>15460</t>
+          <t>15302</t>
         </is>
       </c>
       <c r="D269" s="8" t="inlineStr"/>
       <c r="E269" s="8" t="inlineStr">
         <is>
-          <t>11149519</t>
+          <t>11147707</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -14668,13 +14688,13 @@
       </c>
       <c r="C270" s="8" t="inlineStr">
         <is>
-          <t>15469</t>
+          <t>15460</t>
         </is>
       </c>
       <c r="D270" s="8" t="inlineStr"/>
       <c r="E270" s="8" t="inlineStr">
         <is>
-          <t>11149574</t>
+          <t>11149519</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -14713,13 +14733,13 @@
       </c>
       <c r="C271" s="8" t="inlineStr">
         <is>
-          <t>15470</t>
+          <t>15469</t>
         </is>
       </c>
       <c r="D271" s="8" t="inlineStr"/>
       <c r="E271" s="8" t="inlineStr">
         <is>
-          <t>11149571</t>
+          <t>11149574</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -14758,13 +14778,13 @@
       </c>
       <c r="C272" s="8" t="inlineStr">
         <is>
-          <t>15479</t>
+          <t>15470</t>
         </is>
       </c>
       <c r="D272" s="8" t="inlineStr"/>
       <c r="E272" s="8" t="inlineStr">
         <is>
-          <t>11149518</t>
+          <t>11149571</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -14803,13 +14823,13 @@
       </c>
       <c r="C273" s="8" t="inlineStr">
         <is>
-          <t>15480</t>
+          <t>15479</t>
         </is>
       </c>
       <c r="D273" s="8" t="inlineStr"/>
       <c r="E273" s="8" t="inlineStr">
         <is>
-          <t>11149576</t>
+          <t>11149518</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -14848,13 +14868,13 @@
       </c>
       <c r="C274" s="8" t="inlineStr">
         <is>
-          <t>15705</t>
+          <t>15480</t>
         </is>
       </c>
       <c r="D274" s="8" t="inlineStr"/>
       <c r="E274" s="8" t="inlineStr">
         <is>
-          <t>11153979</t>
+          <t>11149576</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -14893,13 +14913,13 @@
       </c>
       <c r="C275" s="8" t="inlineStr">
         <is>
-          <t>15706</t>
+          <t>15705</t>
         </is>
       </c>
       <c r="D275" s="8" t="inlineStr"/>
       <c r="E275" s="8" t="inlineStr">
         <is>
-          <t>11153962</t>
+          <t>11153979</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -14938,13 +14958,13 @@
       </c>
       <c r="C276" s="8" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>15706</t>
         </is>
       </c>
       <c r="D276" s="8" t="inlineStr"/>
       <c r="E276" s="8" t="inlineStr">
         <is>
-          <t>11153978</t>
+          <t>11153962</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -14983,13 +15003,13 @@
       </c>
       <c r="C277" s="8" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>15717</t>
         </is>
       </c>
       <c r="D277" s="8" t="inlineStr"/>
       <c r="E277" s="8" t="inlineStr">
         <is>
-          <t>11153966</t>
+          <t>11153978</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -15028,13 +15048,13 @@
       </c>
       <c r="C278" s="8" t="inlineStr">
         <is>
-          <t>15729</t>
+          <t>15728</t>
         </is>
       </c>
       <c r="D278" s="8" t="inlineStr"/>
       <c r="E278" s="8" t="inlineStr">
         <is>
-          <t>11153967</t>
+          <t>11153966</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -15073,13 +15093,13 @@
       </c>
       <c r="C279" s="8" t="inlineStr">
         <is>
-          <t>15852</t>
+          <t>15729</t>
         </is>
       </c>
       <c r="D279" s="8" t="inlineStr"/>
       <c r="E279" s="8" t="inlineStr">
         <is>
-          <t>11157527</t>
+          <t>11153967</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -15118,11 +15138,15 @@
       </c>
       <c r="C280" s="8" t="inlineStr">
         <is>
-          <t>53834</t>
+          <t>15852</t>
         </is>
       </c>
       <c r="D280" s="8" t="inlineStr"/>
-      <c r="E280" s="8" t="inlineStr"/>
+      <c r="E280" s="8" t="inlineStr">
+        <is>
+          <t>11157527</t>
+        </is>
+      </c>
       <c r="F280" t="inlineStr">
         <is>
           <t>Tazas SBX Genérico</t>
@@ -15131,7 +15155,7 @@
       <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -15155,33 +15179,21 @@
         </is>
       </c>
       <c r="B281" s="7" t="n">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="C281" s="8" t="inlineStr">
         <is>
-          <t>16490</t>
-        </is>
-      </c>
-      <c r="D281" s="8" t="inlineStr">
-        <is>
-          <t>150017</t>
-        </is>
-      </c>
-      <c r="E281" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>53834</t>
+        </is>
+      </c>
+      <c r="D281" s="8" t="inlineStr"/>
+      <c r="E281" s="8" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Fl25Manga</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>MANGA SILICON P/VASO BARBIE CJ25PZAS</t>
-        </is>
-      </c>
+          <t>Tazas SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr">
         <is>
           <t>NO</t>
@@ -15194,7 +15206,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Fl25Manga</t>
+          <t>Tazas SBX Genérico</t>
         </is>
       </c>
       <c r="K281" t="inlineStr"/>
@@ -15208,16 +15220,16 @@
         </is>
       </c>
       <c r="B282" s="7" t="n">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="C282" s="8" t="inlineStr">
         <is>
-          <t>16488</t>
+          <t>16490</t>
         </is>
       </c>
       <c r="D282" s="8" t="inlineStr">
         <is>
-          <t>150015</t>
+          <t>150017</t>
         </is>
       </c>
       <c r="E282" s="8" t="inlineStr">
@@ -15227,12 +15239,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Fl25StopperBar</t>
+          <t>Fl25Manga</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>STOPPER BARBIE CJ25PZAS</t>
+          <t>MANGA SILICON P/VASO BARBIE CJ25PZAS</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -15247,7 +15259,7 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Fl25StopperBar</t>
+          <t>Fl25Manga</t>
         </is>
       </c>
       <c r="K282" t="inlineStr"/>
@@ -15261,31 +15273,31 @@
         </is>
       </c>
       <c r="B283" s="7" t="n">
-        <v>573</v>
+        <v>615</v>
       </c>
       <c r="C283" s="8" t="inlineStr">
         <is>
-          <t>16636</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
-          <t>152566</t>
+          <t>150015</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
         <is>
-          <t>11170104</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>DiscoveryGDL</t>
+          <t>Fl25StopperBar</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>70104 C4P DIS STN MUG GUADALAJARA 14OZ</t>
+          <t>STOPPER BARBIE CJ25PZAS</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -15300,7 +15312,7 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>DiscoveryGDL</t>
+          <t>Fl25StopperBar</t>
         </is>
       </c>
       <c r="K283" t="inlineStr"/>
@@ -15314,31 +15326,31 @@
         </is>
       </c>
       <c r="B284" s="7" t="n">
-        <v>524</v>
+        <v>573</v>
       </c>
       <c r="C284" s="8" t="inlineStr">
         <is>
-          <t>16775</t>
+          <t>16636</t>
         </is>
       </c>
       <c r="D284" s="8" t="inlineStr">
         <is>
-          <t>152975</t>
+          <t>152566</t>
         </is>
       </c>
       <c r="E284" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11170104</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Wt26LlaveroSV</t>
+          <t>DiscoveryGDL</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>LLAVERO METALICO CJ22PZAS</t>
+          <t>70104 C4P DIS STN MUG GUADALAJARA 14OZ</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -15353,7 +15365,7 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Wt26LlaveroSV</t>
+          <t>DiscoveryGDL</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
@@ -15367,31 +15379,31 @@
         </is>
       </c>
       <c r="B285" s="7" t="n">
-        <v>499</v>
+        <v>524</v>
       </c>
       <c r="C285" s="8" t="inlineStr">
         <is>
-          <t>16663</t>
+          <t>16775</t>
         </is>
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>152593</t>
+          <t>152975</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
         <is>
-          <t>11176699</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Sp26Mug14Rabbit</t>
+          <t>Wt26LlaveroSV</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>76699 C2P SP26 STN MUG RBBT 14OZ</t>
+          <t>LLAVERO METALICO CJ22PZAS</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -15406,7 +15418,7 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>Sp26Mug14Rabbit</t>
+          <t>Wt26LlaveroSV</t>
         </is>
       </c>
       <c r="K285" t="inlineStr"/>
@@ -15420,36 +15432,36 @@
         </is>
       </c>
       <c r="B286" s="7" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C286" s="8" t="inlineStr">
         <is>
-          <t>14834</t>
+          <t>16663</t>
         </is>
       </c>
       <c r="D286" s="8" t="inlineStr">
         <is>
-          <t>149504</t>
+          <t>152593</t>
         </is>
       </c>
       <c r="E286" s="8" t="inlineStr">
         <is>
-          <t>11141083</t>
+          <t>11176699</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>CCupPlastic SBX Genérico</t>
+          <t>Sp26Mug14Rabbit</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>41083 C2P SUM23 COLD CUP JEWELED 24OZ</t>
+          <t>76699 C2P SP26 STN MUG RBBT 14OZ</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -15459,7 +15471,7 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>CCupPlastic SBX Genérico</t>
+          <t>Sp26Mug14Rabbit</t>
         </is>
       </c>
       <c r="K286" t="inlineStr"/>
@@ -15477,17 +15489,17 @@
       </c>
       <c r="C287" s="8" t="inlineStr">
         <is>
-          <t>15310</t>
+          <t>14834</t>
         </is>
       </c>
       <c r="D287" s="8" t="inlineStr">
         <is>
-          <t>149550</t>
+          <t>149504</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
         <is>
-          <t>11147727</t>
+          <t>11141083</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -15497,7 +15509,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>47727 C2P W24 CLD CUP GRID SOFT 24OZ</t>
+          <t>41083 C2P SUM23 COLD CUP JEWELED 24OZ</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -15530,17 +15542,17 @@
       </c>
       <c r="C288" s="8" t="inlineStr">
         <is>
-          <t>15311</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="D288" s="8" t="inlineStr">
         <is>
-          <t>149551</t>
+          <t>149550</t>
         </is>
       </c>
       <c r="E288" s="8" t="inlineStr">
         <is>
-          <t>11147728</t>
+          <t>11147727</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -15550,7 +15562,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>47728 C2P W24 CLD CUP PLEATED SOFT 24OZ</t>
+          <t>47727 C2P W24 CLD CUP GRID SOFT 24OZ</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -15583,17 +15595,17 @@
       </c>
       <c r="C289" s="8" t="inlineStr">
         <is>
-          <t>15502</t>
+          <t>15311</t>
         </is>
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>149585</t>
+          <t>149551</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
         <is>
-          <t>11150728</t>
+          <t>11147728</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -15603,7 +15615,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>50728 C2P S24 CLD CUP BLING METALLI 24OZ</t>
+          <t>47728 C2P W24 CLD CUP PLEATED SOFT 24OZ</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -15636,17 +15648,17 @@
       </c>
       <c r="C290" s="8" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>15502</t>
         </is>
       </c>
       <c r="D290" s="8" t="inlineStr">
         <is>
-          <t>149586</t>
+          <t>149585</t>
         </is>
       </c>
       <c r="E290" s="8" t="inlineStr">
         <is>
-          <t>11150733</t>
+          <t>11150728</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -15656,7 +15668,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>50733 C2P S24 CLD CUP SCALES 24OZ</t>
+          <t>50728 C2P S24 CLD CUP BLING METALLI 24OZ</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -15689,17 +15701,17 @@
       </c>
       <c r="C291" s="8" t="inlineStr">
         <is>
-          <t>15505</t>
+          <t>15504</t>
         </is>
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>149587</t>
+          <t>149586</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
         <is>
-          <t>11150734</t>
+          <t>11150733</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -15709,7 +15721,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>50734 C1P S24 CLD CUP BLUE CARRY 24OZ</t>
+          <t>50733 C2P S24 CLD CUP SCALES 24OZ</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -15742,17 +15754,17 @@
       </c>
       <c r="C292" s="8" t="inlineStr">
         <is>
-          <t>15512</t>
+          <t>15505</t>
         </is>
       </c>
       <c r="D292" s="8" t="inlineStr">
         <is>
-          <t>149593</t>
+          <t>149587</t>
         </is>
       </c>
       <c r="E292" s="8" t="inlineStr">
         <is>
-          <t>11150738</t>
+          <t>11150734</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -15762,7 +15774,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>50738 C2P S24 CLD CUP PRISM PRIDE 24OZ</t>
+          <t>50734 C1P S24 CLD CUP BLUE CARRY 24OZ</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -15795,17 +15807,17 @@
       </c>
       <c r="C293" s="8" t="inlineStr">
         <is>
-          <t>15523</t>
+          <t>15512</t>
         </is>
       </c>
       <c r="D293" s="8" t="inlineStr">
         <is>
-          <t>149604</t>
+          <t>149593</t>
         </is>
       </c>
       <c r="E293" s="8" t="inlineStr">
         <is>
-          <t>11150741</t>
+          <t>11150738</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -15815,7 +15827,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>50741 C2P S24 CLD CUP BLING PURPLE 24OZ</t>
+          <t>50738 C2P S24 CLD CUP PRISM PRIDE 24OZ</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -15848,17 +15860,17 @@
       </c>
       <c r="C294" s="8" t="inlineStr">
         <is>
-          <t>15524</t>
+          <t>15523</t>
         </is>
       </c>
       <c r="D294" s="8" t="inlineStr">
         <is>
-          <t>149605</t>
+          <t>149604</t>
         </is>
       </c>
       <c r="E294" s="8" t="inlineStr">
         <is>
-          <t>11150742</t>
+          <t>11150741</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -15868,7 +15880,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>50742 C2P S24 CLD CUP METALLIC 24OZ</t>
+          <t>50741 C2P S24 CLD CUP BLING PURPLE 24OZ</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -15901,17 +15913,17 @@
       </c>
       <c r="C295" s="8" t="inlineStr">
         <is>
-          <t>15713</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="D295" s="8" t="inlineStr">
         <is>
-          <t>149656</t>
+          <t>149605</t>
         </is>
       </c>
       <c r="E295" s="8" t="inlineStr">
         <is>
-          <t>11153992</t>
+          <t>11150742</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -15921,7 +15933,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>53992 C2P F24 CLD CUP GRADIENT 24OZ</t>
+          <t>50742 C2P S24 CLD CUP METALLIC 24OZ</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -15954,17 +15966,17 @@
       </c>
       <c r="C296" s="8" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>15713</t>
         </is>
       </c>
       <c r="D296" s="8" t="inlineStr">
         <is>
-          <t>149657</t>
+          <t>149656</t>
         </is>
       </c>
       <c r="E296" s="8" t="inlineStr">
         <is>
-          <t>11153993</t>
+          <t>11153992</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -15974,7 +15986,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>53993 C2P F24 CLD CUP BLING BLACK 24OZ</t>
+          <t>53992 C2P F24 CLD CUP GRADIENT 24OZ</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -16007,17 +16019,17 @@
       </c>
       <c r="C297" s="8" t="inlineStr">
         <is>
-          <t>15722</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="D297" s="8" t="inlineStr">
         <is>
-          <t>149663</t>
+          <t>149657</t>
         </is>
       </c>
       <c r="E297" s="8" t="inlineStr">
         <is>
-          <t>11153995</t>
+          <t>11153993</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -16027,7 +16039,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>53995 C2P F24 CLD CUP ANNIVERSARY 24OZ</t>
+          <t>53993 C2P F24 CLD CUP BLING BLACK 24OZ</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -16060,17 +16072,17 @@
       </c>
       <c r="C298" s="8" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="D298" s="8" t="inlineStr">
         <is>
-          <t>149669</t>
+          <t>149663</t>
         </is>
       </c>
       <c r="E298" s="8" t="inlineStr">
         <is>
-          <t>11154002</t>
+          <t>11153995</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -16080,7 +16092,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>54002 C2P F24 CLD CUP DRIP GID 24OZ</t>
+          <t>53995 C2P F24 CLD CUP ANNIVERSARY 24OZ</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -16113,17 +16125,17 @@
       </c>
       <c r="C299" s="8" t="inlineStr">
         <is>
-          <t>15810</t>
+          <t>15732</t>
         </is>
       </c>
       <c r="D299" s="8" t="inlineStr">
         <is>
-          <t>149697</t>
+          <t>149669</t>
         </is>
       </c>
       <c r="E299" s="8" t="inlineStr">
         <is>
-          <t>11157530</t>
+          <t>11154002</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -16133,7 +16145,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>57530 C2P XM24 CLD CUP GREEN TRASLU 24OZ</t>
+          <t>54002 C2P F24 CLD CUP DRIP GID 24OZ</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -16166,17 +16178,17 @@
       </c>
       <c r="C300" s="8" t="inlineStr">
         <is>
-          <t>15846</t>
+          <t>15810</t>
         </is>
       </c>
       <c r="D300" s="8" t="inlineStr">
         <is>
-          <t>150131</t>
+          <t>149697</t>
         </is>
       </c>
       <c r="E300" s="8" t="inlineStr">
         <is>
-          <t>11157528</t>
+          <t>11157530</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -16186,7 +16198,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>57528 C2P XM24 CLD CUP BLUE GLIT 24OZ</t>
+          <t>57530 C2P XM24 CLD CUP GREEN TRASLU 24OZ</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -16219,17 +16231,17 @@
       </c>
       <c r="C301" s="8" t="inlineStr">
         <is>
-          <t>15847</t>
+          <t>15846</t>
         </is>
       </c>
       <c r="D301" s="8" t="inlineStr">
         <is>
-          <t>149710</t>
+          <t>150131</t>
         </is>
       </c>
       <c r="E301" s="8" t="inlineStr">
         <is>
-          <t>11157529</t>
+          <t>11157528</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -16239,7 +16251,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>57529 C2P XM24 CLD CUP MET SILVER 24OZ</t>
+          <t>57528 C2P XM24 CLD CUP BLUE GLIT 24OZ</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -16272,17 +16284,17 @@
       </c>
       <c r="C302" s="8" t="inlineStr">
         <is>
-          <t>15849</t>
+          <t>15847</t>
         </is>
       </c>
       <c r="D302" s="8" t="inlineStr">
         <is>
-          <t>150133</t>
+          <t>149710</t>
         </is>
       </c>
       <c r="E302" s="8" t="inlineStr">
         <is>
-          <t>11157536</t>
+          <t>11157529</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -16292,7 +16304,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>57536 C2P XM24 CLD CUP DOME GINGER 24OZ</t>
+          <t>57529 C2P XM24 CLD CUP MET SILVER 24OZ</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -16325,17 +16337,17 @@
       </c>
       <c r="C303" s="8" t="inlineStr">
         <is>
-          <t>15874</t>
+          <t>15849</t>
         </is>
       </c>
       <c r="D303" s="8" t="inlineStr">
         <is>
-          <t>149721</t>
+          <t>150133</t>
         </is>
       </c>
       <c r="E303" s="8" t="inlineStr">
         <is>
-          <t>11161838</t>
+          <t>11157536</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -16345,7 +16357,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>61838 C4P WCK24 CLD CUP PRIS GLINDA 24OZ</t>
+          <t>57536 C2P XM24 CLD CUP DOME GINGER 24OZ</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -16378,17 +16390,17 @@
       </c>
       <c r="C304" s="8" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>15874</t>
         </is>
       </c>
       <c r="D304" s="8" t="inlineStr">
         <is>
-          <t>149723</t>
+          <t>149721</t>
         </is>
       </c>
       <c r="E304" s="8" t="inlineStr">
         <is>
-          <t>11161839</t>
+          <t>11161838</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -16398,7 +16410,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>61839 C4P WCK24 CLD CUP PINK GOLD 24OZ</t>
+          <t>61838 C4P WCK24 CLD CUP PRIS GLINDA 24OZ</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -16431,17 +16443,17 @@
       </c>
       <c r="C305" s="8" t="inlineStr">
         <is>
-          <t>15878</t>
+          <t>15876</t>
         </is>
       </c>
       <c r="D305" s="8" t="inlineStr">
         <is>
-          <t>149725</t>
+          <t>149723</t>
         </is>
       </c>
       <c r="E305" s="8" t="inlineStr">
         <is>
-          <t>11161840</t>
+          <t>11161839</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -16451,7 +16463,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>61840 C4P WCK24 CLD CUP PLEATED GID 24OZ</t>
+          <t>61839 C4P WCK24 CLD CUP PINK GOLD 24OZ</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -16484,17 +16496,17 @@
       </c>
       <c r="C306" s="8" t="inlineStr">
         <is>
-          <t>15880</t>
+          <t>15878</t>
         </is>
       </c>
       <c r="D306" s="8" t="inlineStr">
         <is>
-          <t>149727</t>
+          <t>149725</t>
         </is>
       </c>
       <c r="E306" s="8" t="inlineStr">
         <is>
-          <t>11161841</t>
+          <t>11161840</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -16504,7 +16516,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>61841 C4P WCK24 CLD CUP GID DEFY 24OZ</t>
+          <t>61840 C4P WCK24 CLD CUP PLEATED GID 24OZ</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -16537,17 +16549,17 @@
       </c>
       <c r="C307" s="8" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>15880</t>
         </is>
       </c>
       <c r="D307" s="8" t="inlineStr">
         <is>
-          <t>149729</t>
+          <t>149727</t>
         </is>
       </c>
       <c r="E307" s="8" t="inlineStr">
         <is>
-          <t>11161842</t>
+          <t>11161841</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -16557,7 +16569,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>61842 C2P WCK24 CLD CUP GEMSTONE 24OZ</t>
+          <t>61841 C4P WCK24 CLD CUP GID DEFY 24OZ</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -16590,17 +16602,17 @@
       </c>
       <c r="C308" s="8" t="inlineStr">
         <is>
-          <t>15884</t>
+          <t>15882</t>
         </is>
       </c>
       <c r="D308" s="8" t="inlineStr">
         <is>
-          <t>149731</t>
+          <t>149729</t>
         </is>
       </c>
       <c r="E308" s="8" t="inlineStr">
         <is>
-          <t>11161843</t>
+          <t>11161842</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -16610,7 +16622,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>61843 C4P WCK24 CLD CUP GREEN METAL 24OZ</t>
+          <t>61842 C2P WCK24 CLD CUP GEMSTONE 24OZ</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -16643,17 +16655,17 @@
       </c>
       <c r="C309" s="8" t="inlineStr">
         <is>
-          <t>16090</t>
+          <t>15884</t>
         </is>
       </c>
       <c r="D309" s="8" t="inlineStr">
         <is>
-          <t>149793</t>
+          <t>149731</t>
         </is>
       </c>
       <c r="E309" s="8" t="inlineStr">
         <is>
-          <t>11163286</t>
+          <t>11161843</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -16663,7 +16675,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>63286 C2P PNTS25 CLD SNOPY WOODSTCK 24OZ</t>
+          <t>61843 C4P WCK24 CLD CUP GREEN METAL 24OZ</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -16696,17 +16708,17 @@
       </c>
       <c r="C310" s="8" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>16090</t>
         </is>
       </c>
       <c r="D310" s="8" t="inlineStr">
         <is>
-          <t>149806</t>
+          <t>149793</t>
         </is>
       </c>
       <c r="E310" s="8" t="inlineStr">
         <is>
-          <t>11160764</t>
+          <t>11163286</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -16716,7 +16728,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>60764 C1P PNTS25 WTR BTL JOE KIND 16OZ</t>
+          <t>63286 C2P PNTS25 CLD SNOPY WOODSTCK 24OZ</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -16749,17 +16761,17 @@
       </c>
       <c r="C311" s="8" t="inlineStr">
         <is>
-          <t>15811</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="D311" s="8" t="inlineStr">
         <is>
-          <t>149698</t>
+          <t>149806</t>
         </is>
       </c>
       <c r="E311" s="8" t="inlineStr">
         <is>
-          <t>11157532</t>
+          <t>11160764</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -16769,12 +16781,12 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>57532 C2P XM24 HOT CLD CUP STR HOLS 24OZ</t>
+          <t>60764 C1P PNTS25 WTR BTL JOE KIND 16OZ</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -16802,17 +16814,17 @@
       </c>
       <c r="C312" s="8" t="inlineStr">
         <is>
-          <t>16050</t>
+          <t>15811</t>
         </is>
       </c>
       <c r="D312" s="8" t="inlineStr">
         <is>
-          <t>149757</t>
+          <t>149698</t>
         </is>
       </c>
       <c r="E312" s="8" t="inlineStr">
         <is>
-          <t>11162626</t>
+          <t>11157532</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -16822,7 +16834,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>62626 C2P SP25 CLD CUP PLEATED PINK 24OZ</t>
+          <t>57532 C2P XM24 HOT CLD CUP STR HOLS 24OZ</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -16855,13 +16867,17 @@
       </c>
       <c r="C313" s="8" t="inlineStr">
         <is>
-          <t>12548</t>
-        </is>
-      </c>
-      <c r="D313" s="8" t="inlineStr"/>
+          <t>16050</t>
+        </is>
+      </c>
+      <c r="D313" s="8" t="inlineStr">
+        <is>
+          <t>149757</t>
+        </is>
+      </c>
       <c r="E313" s="8" t="inlineStr">
         <is>
-          <t>11109972</t>
+          <t>11162626</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -16869,10 +16885,14 @@
           <t>CCupPlastic SBX Genérico</t>
         </is>
       </c>
-      <c r="G313" t="inlineStr"/>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>62626 C2P SP25 CLD CUP PLEATED PINK 24OZ</t>
+        </is>
+      </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -16900,13 +16920,13 @@
       </c>
       <c r="C314" s="8" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>12548</t>
         </is>
       </c>
       <c r="D314" s="8" t="inlineStr"/>
       <c r="E314" s="8" t="inlineStr">
         <is>
-          <t>11109975</t>
+          <t>11109972</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -16945,13 +16965,13 @@
       </c>
       <c r="C315" s="8" t="inlineStr">
         <is>
-          <t>12818</t>
+          <t>12550</t>
         </is>
       </c>
       <c r="D315" s="8" t="inlineStr"/>
       <c r="E315" s="8" t="inlineStr">
         <is>
-          <t>11115526</t>
+          <t>11109975</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -16990,13 +17010,13 @@
       </c>
       <c r="C316" s="8" t="inlineStr">
         <is>
-          <t>12905</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="D316" s="8" t="inlineStr"/>
       <c r="E316" s="8" t="inlineStr">
         <is>
-          <t>11117004</t>
+          <t>11115526</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -17035,13 +17055,13 @@
       </c>
       <c r="C317" s="8" t="inlineStr">
         <is>
-          <t>12983</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="D317" s="8" t="inlineStr"/>
       <c r="E317" s="8" t="inlineStr">
         <is>
-          <t>11112579</t>
+          <t>11117004</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -17080,13 +17100,13 @@
       </c>
       <c r="C318" s="8" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>12983</t>
         </is>
       </c>
       <c r="D318" s="8" t="inlineStr"/>
       <c r="E318" s="8" t="inlineStr">
         <is>
-          <t>11126377</t>
+          <t>11112579</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -17125,13 +17145,13 @@
       </c>
       <c r="C319" s="8" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="D319" s="8" t="inlineStr"/>
       <c r="E319" s="8" t="inlineStr">
         <is>
-          <t>11125961</t>
+          <t>11126377</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -17170,13 +17190,13 @@
       </c>
       <c r="C320" s="8" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>13850</t>
         </is>
       </c>
       <c r="D320" s="8" t="inlineStr"/>
       <c r="E320" s="8" t="inlineStr">
         <is>
-          <t>11128421</t>
+          <t>11125961</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -17215,13 +17235,13 @@
       </c>
       <c r="C321" s="8" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="D321" s="8" t="inlineStr"/>
       <c r="E321" s="8" t="inlineStr">
         <is>
-          <t>11128426</t>
+          <t>11128421</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -17260,13 +17280,13 @@
       </c>
       <c r="C322" s="8" t="inlineStr">
         <is>
-          <t>14044</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="D322" s="8" t="inlineStr"/>
       <c r="E322" s="8" t="inlineStr">
         <is>
-          <t>11127831</t>
+          <t>11128426</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -17305,13 +17325,13 @@
       </c>
       <c r="C323" s="8" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>14044</t>
         </is>
       </c>
       <c r="D323" s="8" t="inlineStr"/>
       <c r="E323" s="8" t="inlineStr">
         <is>
-          <t>11128425</t>
+          <t>11127831</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -17350,13 +17370,13 @@
       </c>
       <c r="C324" s="8" t="inlineStr">
         <is>
-          <t>14149</t>
+          <t>14045</t>
         </is>
       </c>
       <c r="D324" s="8" t="inlineStr"/>
       <c r="E324" s="8" t="inlineStr">
         <is>
-          <t>11129116</t>
+          <t>11128425</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -17395,13 +17415,13 @@
       </c>
       <c r="C325" s="8" t="inlineStr">
         <is>
-          <t>14152</t>
+          <t>14149</t>
         </is>
       </c>
       <c r="D325" s="8" t="inlineStr"/>
       <c r="E325" s="8" t="inlineStr">
         <is>
-          <t>11129127</t>
+          <t>11129116</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -17440,13 +17460,13 @@
       </c>
       <c r="C326" s="8" t="inlineStr">
         <is>
-          <t>14160</t>
+          <t>14152</t>
         </is>
       </c>
       <c r="D326" s="8" t="inlineStr"/>
       <c r="E326" s="8" t="inlineStr">
         <is>
-          <t>11129148</t>
+          <t>11129127</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -17485,13 +17505,13 @@
       </c>
       <c r="C327" s="8" t="inlineStr">
         <is>
-          <t>14166</t>
+          <t>14160</t>
         </is>
       </c>
       <c r="D327" s="8" t="inlineStr"/>
       <c r="E327" s="8" t="inlineStr">
         <is>
-          <t>11130184</t>
+          <t>11129148</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -17530,13 +17550,13 @@
       </c>
       <c r="C328" s="8" t="inlineStr">
         <is>
-          <t>14177</t>
+          <t>14166</t>
         </is>
       </c>
       <c r="D328" s="8" t="inlineStr"/>
       <c r="E328" s="8" t="inlineStr">
         <is>
-          <t>11130196</t>
+          <t>11130184</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -17575,13 +17595,13 @@
       </c>
       <c r="C329" s="8" t="inlineStr">
         <is>
-          <t>14344</t>
+          <t>14177</t>
         </is>
       </c>
       <c r="D329" s="8" t="inlineStr"/>
       <c r="E329" s="8" t="inlineStr">
         <is>
-          <t>11130717</t>
+          <t>11130196</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -17620,13 +17640,13 @@
       </c>
       <c r="C330" s="8" t="inlineStr">
         <is>
-          <t>14345</t>
+          <t>14344</t>
         </is>
       </c>
       <c r="D330" s="8" t="inlineStr"/>
       <c r="E330" s="8" t="inlineStr">
         <is>
-          <t>11130718</t>
+          <t>11130717</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -17665,13 +17685,13 @@
       </c>
       <c r="C331" s="8" t="inlineStr">
         <is>
-          <t>14362</t>
+          <t>14345</t>
         </is>
       </c>
       <c r="D331" s="8" t="inlineStr"/>
       <c r="E331" s="8" t="inlineStr">
         <is>
-          <t>11136365</t>
+          <t>11130718</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -17710,13 +17730,13 @@
       </c>
       <c r="C332" s="8" t="inlineStr">
         <is>
-          <t>14415</t>
+          <t>14362</t>
         </is>
       </c>
       <c r="D332" s="8" t="inlineStr"/>
       <c r="E332" s="8" t="inlineStr">
         <is>
-          <t>11133673</t>
+          <t>11136365</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -17755,13 +17775,13 @@
       </c>
       <c r="C333" s="8" t="inlineStr">
         <is>
-          <t>14438</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="D333" s="8" t="inlineStr"/>
       <c r="E333" s="8" t="inlineStr">
         <is>
-          <t>11133674</t>
+          <t>11133673</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -17800,13 +17820,13 @@
       </c>
       <c r="C334" s="8" t="inlineStr">
         <is>
-          <t>14443</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="D334" s="8" t="inlineStr"/>
       <c r="E334" s="8" t="inlineStr">
         <is>
-          <t>11134116</t>
+          <t>11133674</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -17845,13 +17865,13 @@
       </c>
       <c r="C335" s="8" t="inlineStr">
         <is>
-          <t>14445</t>
+          <t>14443</t>
         </is>
       </c>
       <c r="D335" s="8" t="inlineStr"/>
       <c r="E335" s="8" t="inlineStr">
         <is>
-          <t>11133685</t>
+          <t>11134116</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -17890,13 +17910,13 @@
       </c>
       <c r="C336" s="8" t="inlineStr">
         <is>
-          <t>14602</t>
+          <t>14445</t>
         </is>
       </c>
       <c r="D336" s="8" t="inlineStr"/>
       <c r="E336" s="8" t="inlineStr">
         <is>
-          <t>11135996</t>
+          <t>11133685</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -17935,13 +17955,13 @@
       </c>
       <c r="C337" s="8" t="inlineStr">
         <is>
-          <t>14604</t>
+          <t>14602</t>
         </is>
       </c>
       <c r="D337" s="8" t="inlineStr"/>
       <c r="E337" s="8" t="inlineStr">
         <is>
-          <t>11136489</t>
+          <t>11135996</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -17980,13 +18000,13 @@
       </c>
       <c r="C338" s="8" t="inlineStr">
         <is>
-          <t>14605</t>
+          <t>14604</t>
         </is>
       </c>
       <c r="D338" s="8" t="inlineStr"/>
       <c r="E338" s="8" t="inlineStr">
         <is>
-          <t>11136490</t>
+          <t>11136489</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -18025,13 +18045,13 @@
       </c>
       <c r="C339" s="8" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>14605</t>
         </is>
       </c>
       <c r="D339" s="8" t="inlineStr"/>
       <c r="E339" s="8" t="inlineStr">
         <is>
-          <t>11138084</t>
+          <t>11136490</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -18070,13 +18090,13 @@
       </c>
       <c r="C340" s="8" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="D340" s="8" t="inlineStr"/>
       <c r="E340" s="8" t="inlineStr">
         <is>
-          <t>11138103</t>
+          <t>11138084</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -18115,13 +18135,13 @@
       </c>
       <c r="C341" s="8" t="inlineStr">
         <is>
-          <t>14707</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="D341" s="8" t="inlineStr"/>
       <c r="E341" s="8" t="inlineStr">
         <is>
-          <t>11138105</t>
+          <t>11138103</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -18160,13 +18180,13 @@
       </c>
       <c r="C342" s="8" t="inlineStr">
         <is>
-          <t>14755</t>
+          <t>14707</t>
         </is>
       </c>
       <c r="D342" s="8" t="inlineStr"/>
       <c r="E342" s="8" t="inlineStr">
         <is>
-          <t>11140081</t>
+          <t>11138105</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -18205,13 +18225,13 @@
       </c>
       <c r="C343" s="8" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>14755</t>
         </is>
       </c>
       <c r="D343" s="8" t="inlineStr"/>
       <c r="E343" s="8" t="inlineStr">
         <is>
-          <t>11140116</t>
+          <t>11140081</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -18250,13 +18270,13 @@
       </c>
       <c r="C344" s="8" t="inlineStr">
         <is>
-          <t>14770</t>
+          <t>14756</t>
         </is>
       </c>
       <c r="D344" s="8" t="inlineStr"/>
       <c r="E344" s="8" t="inlineStr">
         <is>
-          <t>11140110</t>
+          <t>11140116</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -18295,13 +18315,13 @@
       </c>
       <c r="C345" s="8" t="inlineStr">
         <is>
-          <t>14771</t>
+          <t>14770</t>
         </is>
       </c>
       <c r="D345" s="8" t="inlineStr"/>
       <c r="E345" s="8" t="inlineStr">
         <is>
-          <t>11140117</t>
+          <t>11140110</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -18340,13 +18360,13 @@
       </c>
       <c r="C346" s="8" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>14771</t>
         </is>
       </c>
       <c r="D346" s="8" t="inlineStr"/>
       <c r="E346" s="8" t="inlineStr">
         <is>
-          <t>11141080</t>
+          <t>11140117</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -18385,13 +18405,13 @@
       </c>
       <c r="C347" s="8" t="inlineStr">
         <is>
-          <t>14840</t>
+          <t>14833</t>
         </is>
       </c>
       <c r="D347" s="8" t="inlineStr"/>
       <c r="E347" s="8" t="inlineStr">
         <is>
-          <t>11141085</t>
+          <t>11141080</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -18430,13 +18450,13 @@
       </c>
       <c r="C348" s="8" t="inlineStr">
         <is>
-          <t>15061</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="D348" s="8" t="inlineStr"/>
       <c r="E348" s="8" t="inlineStr">
         <is>
-          <t>11144094</t>
+          <t>11141085</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -18475,13 +18495,13 @@
       </c>
       <c r="C349" s="8" t="inlineStr">
         <is>
-          <t>15062</t>
+          <t>15061</t>
         </is>
       </c>
       <c r="D349" s="8" t="inlineStr"/>
       <c r="E349" s="8" t="inlineStr">
         <is>
-          <t>11144090</t>
+          <t>11144094</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -18520,13 +18540,13 @@
       </c>
       <c r="C350" s="8" t="inlineStr">
         <is>
-          <t>15063</t>
+          <t>15062</t>
         </is>
       </c>
       <c r="D350" s="8" t="inlineStr"/>
       <c r="E350" s="8" t="inlineStr">
         <is>
-          <t>11144091</t>
+          <t>11144090</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -18565,13 +18585,13 @@
       </c>
       <c r="C351" s="8" t="inlineStr">
         <is>
-          <t>15069</t>
+          <t>15063</t>
         </is>
       </c>
       <c r="D351" s="8" t="inlineStr"/>
       <c r="E351" s="8" t="inlineStr">
         <is>
-          <t>11144096</t>
+          <t>11144091</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -18610,13 +18630,13 @@
       </c>
       <c r="C352" s="8" t="inlineStr">
         <is>
-          <t>15161</t>
+          <t>15069</t>
         </is>
       </c>
       <c r="D352" s="8" t="inlineStr"/>
       <c r="E352" s="8" t="inlineStr">
         <is>
-          <t>11146167</t>
+          <t>11144096</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -18655,13 +18675,13 @@
       </c>
       <c r="C353" s="8" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>15161</t>
         </is>
       </c>
       <c r="D353" s="8" t="inlineStr"/>
       <c r="E353" s="8" t="inlineStr">
         <is>
-          <t>11146168</t>
+          <t>11146167</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -18700,13 +18720,13 @@
       </c>
       <c r="C354" s="8" t="inlineStr">
         <is>
-          <t>15184</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="D354" s="8" t="inlineStr"/>
       <c r="E354" s="8" t="inlineStr">
         <is>
-          <t>11146172</t>
+          <t>11146168</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -18745,13 +18765,13 @@
       </c>
       <c r="C355" s="8" t="inlineStr">
         <is>
-          <t>15309</t>
+          <t>15184</t>
         </is>
       </c>
       <c r="D355" s="8" t="inlineStr"/>
       <c r="E355" s="8" t="inlineStr">
         <is>
-          <t>11147723</t>
+          <t>11146172</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -18790,13 +18810,13 @@
       </c>
       <c r="C356" s="8" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>15309</t>
         </is>
       </c>
       <c r="D356" s="8" t="inlineStr"/>
       <c r="E356" s="8" t="inlineStr">
         <is>
-          <t>11149588</t>
+          <t>11147723</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -18835,13 +18855,13 @@
       </c>
       <c r="C357" s="8" t="inlineStr">
         <is>
-          <t>15467</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="D357" s="8" t="inlineStr"/>
       <c r="E357" s="8" t="inlineStr">
         <is>
-          <t>11149591</t>
+          <t>11149588</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -18880,13 +18900,13 @@
       </c>
       <c r="C358" s="8" t="inlineStr">
         <is>
-          <t>15468</t>
+          <t>15467</t>
         </is>
       </c>
       <c r="D358" s="8" t="inlineStr"/>
       <c r="E358" s="8" t="inlineStr">
         <is>
-          <t>11149592</t>
+          <t>11149591</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -18925,13 +18945,13 @@
       </c>
       <c r="C359" s="8" t="inlineStr">
         <is>
-          <t>15484</t>
+          <t>15468</t>
         </is>
       </c>
       <c r="D359" s="8" t="inlineStr"/>
       <c r="E359" s="8" t="inlineStr">
         <is>
-          <t>11149597</t>
+          <t>11149592</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -18970,13 +18990,13 @@
       </c>
       <c r="C360" s="8" t="inlineStr">
         <is>
-          <t>15726</t>
+          <t>15484</t>
         </is>
       </c>
       <c r="D360" s="8" t="inlineStr"/>
       <c r="E360" s="8" t="inlineStr">
         <is>
-          <t>11154000</t>
+          <t>11149597</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -19015,13 +19035,13 @@
       </c>
       <c r="C361" s="8" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>15726</t>
         </is>
       </c>
       <c r="D361" s="8" t="inlineStr"/>
       <c r="E361" s="8" t="inlineStr">
         <is>
-          <t>11160970</t>
+          <t>11154000</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -19032,7 +19052,7 @@
       <c r="G361" t="inlineStr"/>
       <c r="H361" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -19060,11 +19080,15 @@
       </c>
       <c r="C362" s="8" t="inlineStr">
         <is>
-          <t>53835</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="D362" s="8" t="inlineStr"/>
-      <c r="E362" s="8" t="inlineStr"/>
+      <c r="E362" s="8" t="inlineStr">
+        <is>
+          <t>11160970</t>
+        </is>
+      </c>
       <c r="F362" t="inlineStr">
         <is>
           <t>CCupPlastic SBX Genérico</t>
@@ -19097,33 +19121,21 @@
         </is>
       </c>
       <c r="B363" s="7" t="n">
-        <v>459</v>
+        <v>498</v>
       </c>
       <c r="C363" s="8" t="inlineStr">
         <is>
-          <t>16609</t>
-        </is>
-      </c>
-      <c r="D363" s="8" t="inlineStr">
-        <is>
-          <t>152546</t>
-        </is>
-      </c>
-      <c r="E363" s="8" t="inlineStr">
-        <is>
-          <t>11176610</t>
-        </is>
-      </c>
+          <t>53835</t>
+        </is>
+      </c>
+      <c r="D363" s="8" t="inlineStr"/>
+      <c r="E363" s="8" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Wt26TuSS16Duck</t>
-        </is>
-      </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>76610 C1P SS CL DUCK HEAD TO HEAD16OZ</t>
-        </is>
-      </c>
+          <t>CCupPlastic SBX Genérico</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr"/>
       <c r="H363" t="inlineStr">
         <is>
           <t>NO</t>
@@ -19136,7 +19148,7 @@
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>Wt26TuSS16Duck</t>
+          <t>CCupPlastic SBX Genérico</t>
         </is>
       </c>
       <c r="K363" t="inlineStr"/>
@@ -19150,31 +19162,31 @@
         </is>
       </c>
       <c r="B364" s="7" t="n">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="C364" s="8" t="inlineStr">
         <is>
-          <t>16416</t>
+          <t>16609</t>
         </is>
       </c>
       <c r="D364" s="8" t="inlineStr">
         <is>
-          <t>149969</t>
+          <t>152546</t>
         </is>
       </c>
       <c r="E364" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11176610</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Fl25ReusCCBa</t>
+          <t>Wt26TuSS16Duck</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>VASO/TAPA 24OZ REUS BEBF PROM1 CJ48PZAS</t>
+          <t>76610 C1P SS CL DUCK HEAD TO HEAD16OZ</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -19189,7 +19201,7 @@
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>Fl25ReusCCBa</t>
+          <t>Wt26TuSS16Duck</t>
         </is>
       </c>
       <c r="K364" t="inlineStr"/>
@@ -19207,27 +19219,27 @@
       </c>
       <c r="C365" s="8" t="inlineStr">
         <is>
-          <t>16686</t>
+          <t>16416</t>
         </is>
       </c>
       <c r="D365" s="8" t="inlineStr">
         <is>
-          <t>152616</t>
+          <t>149969</t>
         </is>
       </c>
       <c r="E365" s="8" t="inlineStr">
         <is>
-          <t>11170151</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Disc2ozGDL</t>
+          <t>Fl25ReusCCBa</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>70151 C4P DIS STN MUG GUADALAJARA 2OZ</t>
+          <t>VASO/TAPA 24OZ REUS BEBF PROM1 CJ48PZAS</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -19242,7 +19254,7 @@
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>Disc2ozGDL</t>
+          <t>Fl25ReusCCBa</t>
         </is>
       </c>
       <c r="K365" t="inlineStr"/>
@@ -19256,31 +19268,31 @@
         </is>
       </c>
       <c r="B366" s="7" t="n">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="C366" s="8" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>16686</t>
         </is>
       </c>
       <c r="D366" s="8" t="inlineStr">
         <is>
-          <t>152529</t>
+          <t>152616</t>
         </is>
       </c>
       <c r="E366" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11170151</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Xm25ReuMike</t>
+          <t>Disc2ozGDL</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>VASO/TAPA 16OZ REUSABLE PROM9IM2 CJ52PZA</t>
+          <t>70151 C4P DIS STN MUG GUADALAJARA 2OZ</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -19295,7 +19307,7 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>Xm25ReuMike</t>
+          <t>Disc2ozGDL</t>
         </is>
       </c>
       <c r="K366" t="inlineStr"/>
@@ -19313,27 +19325,27 @@
       </c>
       <c r="C367" s="8" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16589</t>
         </is>
       </c>
       <c r="D367" s="8" t="inlineStr">
         <is>
-          <t>152625</t>
+          <t>152529</t>
         </is>
       </c>
       <c r="E367" s="8" t="inlineStr">
         <is>
-          <t>11170155</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Disc2ozTulum</t>
+          <t>Xm25ReuMike</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>70155 C4P DIS STN MUG TULUM 2OZ</t>
+          <t>VASO/TAPA 16OZ REUSABLE PROM9IM2 CJ52PZA</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -19348,7 +19360,7 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>Disc2ozTulum</t>
+          <t>Xm25ReuMike</t>
         </is>
       </c>
       <c r="K367" t="inlineStr"/>
@@ -19362,21 +19374,33 @@
         </is>
       </c>
       <c r="B368" s="7" t="n">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C368" s="8" t="inlineStr">
         <is>
-          <t>54201</t>
-        </is>
-      </c>
-      <c r="D368" s="8" t="inlineStr"/>
-      <c r="E368" s="8" t="inlineStr"/>
+          <t>16695</t>
+        </is>
+      </c>
+      <c r="D368" s="8" t="inlineStr">
+        <is>
+          <t>152625</t>
+        </is>
+      </c>
+      <c r="E368" s="8" t="inlineStr">
+        <is>
+          <t>11170155</t>
+        </is>
+      </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>SII26CC24Rain</t>
-        </is>
-      </c>
-      <c r="G368" t="inlineStr"/>
+          <t>Disc2ozTulum</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>70155 C4P DIS STN MUG TULUM 2OZ</t>
+        </is>
+      </c>
       <c r="H368" t="inlineStr">
         <is>
           <t>NO</t>
@@ -19389,7 +19413,7 @@
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>SII26CC24Rain</t>
+          <t>Disc2ozTulum</t>
         </is>
       </c>
       <c r="K368" t="inlineStr"/>
@@ -19403,33 +19427,21 @@
         </is>
       </c>
       <c r="B369" s="7" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C369" s="8" t="inlineStr">
         <is>
-          <t>16593</t>
-        </is>
-      </c>
-      <c r="D369" s="8" t="inlineStr">
-        <is>
-          <t>152533</t>
-        </is>
-      </c>
-      <c r="E369" s="8" t="inlineStr">
-        <is>
-          <t>11170189</t>
-        </is>
-      </c>
+          <t>54201</t>
+        </is>
+      </c>
+      <c r="D369" s="8" t="inlineStr"/>
+      <c r="E369" s="8" t="inlineStr"/>
       <c r="F369" t="inlineStr">
         <is>
-          <t>ToteBag CDMX</t>
-        </is>
-      </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>70189 P2P TOTE BAG CDMX</t>
-        </is>
-      </c>
+          <t>SII26CC24Rain</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr"/>
       <c r="H369" t="inlineStr">
         <is>
           <t>NO</t>
@@ -19442,7 +19454,7 @@
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>ToteBag CDMX</t>
+          <t>SII26CC24Rain</t>
         </is>
       </c>
       <c r="K369" t="inlineStr"/>
@@ -19456,31 +19468,31 @@
         </is>
       </c>
       <c r="B370" s="7" t="n">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="C370" s="8" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="D370" s="8" t="inlineStr">
         <is>
-          <t>152567</t>
+          <t>152533</t>
         </is>
       </c>
       <c r="E370" s="8" t="inlineStr">
         <is>
-          <t>11170111</t>
+          <t>11170189</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>DiscoveryGTO</t>
+          <t>ToteBag CDMX</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>70111 C4P DIS STN MUG GUANAJUATO 14OZ</t>
+          <t>70189 P2P TOTE BAG CDMX</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -19495,7 +19507,7 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>DiscoveryGTO</t>
+          <t>ToteBag CDMX</t>
         </is>
       </c>
       <c r="K370" t="inlineStr"/>
@@ -19509,31 +19521,31 @@
         </is>
       </c>
       <c r="B371" s="7" t="n">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="C371" s="8" t="inlineStr">
         <is>
-          <t>16694</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="D371" s="8" t="inlineStr">
         <is>
-          <t>152624</t>
+          <t>152567</t>
         </is>
       </c>
       <c r="E371" s="8" t="inlineStr">
         <is>
-          <t>11170154</t>
+          <t>11170111</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Disc2ozPVallarta</t>
+          <t>DiscoveryGTO</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>70154 C4P DIS STN MUG PRTVALLARTA 2OZ</t>
+          <t>70111 C4P DIS STN MUG GUANAJUATO 14OZ</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -19548,7 +19560,7 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>Disc2ozPVallarta</t>
+          <t>DiscoveryGTO</t>
         </is>
       </c>
       <c r="K371" t="inlineStr"/>
@@ -19562,31 +19574,31 @@
         </is>
       </c>
       <c r="B372" s="7" t="n">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="C372" s="8" t="inlineStr">
         <is>
-          <t>16692</t>
+          <t>16694</t>
         </is>
       </c>
       <c r="D372" s="8" t="inlineStr">
         <is>
-          <t>152622</t>
+          <t>152624</t>
         </is>
       </c>
       <c r="E372" s="8" t="inlineStr">
         <is>
-          <t>11170153</t>
+          <t>11170154</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Disc2ozPlayaC</t>
+          <t>Disc2ozPVallarta</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>70153 C4P DIS STN MUG PLAYADLCARMEN 2OZ</t>
+          <t>70154 C4P DIS STN MUG PRTVALLARTA 2OZ</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -19601,7 +19613,7 @@
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>Disc2ozPlayaC</t>
+          <t>Disc2ozPVallarta</t>
         </is>
       </c>
       <c r="K372" t="inlineStr"/>
@@ -19615,31 +19627,31 @@
         </is>
       </c>
       <c r="B373" s="7" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C373" s="8" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16692</t>
         </is>
       </c>
       <c r="D373" s="8" t="inlineStr">
         <is>
-          <t>152608</t>
+          <t>152622</t>
         </is>
       </c>
       <c r="E373" s="8" t="inlineStr">
         <is>
-          <t>11176705</t>
+          <t>11170153</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Sp26ReusTierra</t>
+          <t>Disc2ozPlayaC</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>76705 P20P SP26 PLSTC RSBHTCP EARTH 16OZ</t>
+          <t>70153 C4P DIS STN MUG PLAYADLCARMEN 2OZ</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -19654,7 +19666,7 @@
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>Sp26ReusTierra</t>
+          <t>Disc2ozPlayaC</t>
         </is>
       </c>
       <c r="K373" t="inlineStr"/>
@@ -19668,31 +19680,31 @@
         </is>
       </c>
       <c r="B374" s="7" t="n">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C374" s="8" t="inlineStr">
         <is>
-          <t>16644</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="D374" s="8" t="inlineStr">
         <is>
-          <t>152574</t>
+          <t>152608</t>
         </is>
       </c>
       <c r="E374" s="8" t="inlineStr">
         <is>
-          <t>11170110</t>
+          <t>11176705</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>DiscoveryMTY</t>
+          <t>Sp26ReusTierra</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>70110 C4P DIS STN MUG MONTERREY 14OZ</t>
+          <t>76705 P20P SP26 PLSTC RSBHTCP EARTH 16OZ</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -19707,7 +19719,7 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>DiscoveryMTY</t>
+          <t>Sp26ReusTierra</t>
         </is>
       </c>
       <c r="K374" t="inlineStr"/>
@@ -19721,31 +19733,31 @@
         </is>
       </c>
       <c r="B375" s="7" t="n">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="C375" s="8" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>16644</t>
         </is>
       </c>
       <c r="D375" s="8" t="inlineStr">
         <is>
-          <t>152600</t>
+          <t>152574</t>
         </is>
       </c>
       <c r="E375" s="8" t="inlineStr">
         <is>
-          <t>11176700</t>
+          <t>11170110</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Sp26Tz14GlassC</t>
+          <t>DiscoveryMTY</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>76700 C2P SP26 GLS MUG HNDL 14OZ</t>
+          <t>70110 C4P DIS STN MUG MONTERREY 14OZ</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -19760,7 +19772,7 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>Sp26Tz14GlassC</t>
+          <t>DiscoveryMTY</t>
         </is>
       </c>
       <c r="K375" t="inlineStr"/>
@@ -19774,31 +19786,31 @@
         </is>
       </c>
       <c r="B376" s="7" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C376" s="8" t="inlineStr">
         <is>
-          <t>16647</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="D376" s="8" t="inlineStr">
         <is>
-          <t>152577</t>
+          <t>152600</t>
         </is>
       </c>
       <c r="E376" s="8" t="inlineStr">
         <is>
-          <t>11170106</t>
+          <t>11176700</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>DiscoveryPlayaC</t>
+          <t>Sp26Tz14GlassC</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>70106 C4P DIS STN MUG PLAYADLCARMEN 14OZ</t>
+          <t>76700 C2P SP26 GLS MUG HNDL 14OZ</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -19813,7 +19825,7 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>DiscoveryPlayaC</t>
+          <t>Sp26Tz14GlassC</t>
         </is>
       </c>
       <c r="K376" t="inlineStr"/>
@@ -19827,31 +19839,31 @@
         </is>
       </c>
       <c r="B377" s="7" t="n">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="C377" s="8" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="D377" s="8" t="inlineStr">
         <is>
-          <t>149897</t>
+          <t>152577</t>
         </is>
       </c>
       <c r="E377" s="8" t="inlineStr">
         <is>
-          <t>11169482</t>
+          <t>11170106</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Fl25KeyChainD</t>
+          <t>DiscoveryPlayaC</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>69482 C4P F25 COLD CUP LID SPACE BEAR</t>
+          <t>70106 C4P DIS STN MUG PLAYADLCARMEN 14OZ</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -19866,7 +19878,7 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>Fl25KeyChainD</t>
+          <t>DiscoveryPlayaC</t>
         </is>
       </c>
       <c r="K377" t="inlineStr"/>
@@ -19880,31 +19892,31 @@
         </is>
       </c>
       <c r="B378" s="7" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C378" s="8" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>16265</t>
         </is>
       </c>
       <c r="D378" s="8" t="inlineStr">
         <is>
-          <t>152617</t>
+          <t>149897</t>
         </is>
       </c>
       <c r="E378" s="8" t="inlineStr">
         <is>
-          <t>11170150</t>
+          <t>11169482</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Disc2ozCabos</t>
+          <t>Fl25KeyChainD</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>70150 C4P DIS STN MUG LOS CABOS 2OZ</t>
+          <t>69482 C4P F25 COLD CUP LID SPACE BEAR</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -19919,7 +19931,7 @@
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>Disc2ozCabos</t>
+          <t>Fl25KeyChainD</t>
         </is>
       </c>
       <c r="K378" t="inlineStr"/>
@@ -19933,31 +19945,31 @@
         </is>
       </c>
       <c r="B379" s="7" t="n">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="C379" s="8" t="inlineStr">
         <is>
-          <t>16120</t>
+          <t>16687</t>
         </is>
       </c>
       <c r="D379" s="8" t="inlineStr">
         <is>
-          <t>149819</t>
+          <t>152617</t>
         </is>
       </c>
       <c r="E379" s="8" t="inlineStr">
         <is>
-          <t>11164267</t>
+          <t>11170150</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>SI25Tu20Swimm</t>
+          <t>Disc2ozCabos</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>64267 C2P S25 TMBLR SUMMER SWIMMERS 20OZ</t>
+          <t>70150 C4P DIS STN MUG LOS CABOS 2OZ</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -19972,7 +19984,7 @@
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>SI25Tu20Swimm</t>
+          <t>Disc2ozCabos</t>
         </is>
       </c>
       <c r="K379" t="inlineStr"/>
@@ -19986,31 +19998,31 @@
         </is>
       </c>
       <c r="B380" s="7" t="n">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C380" s="8" t="inlineStr">
         <is>
-          <t>16655</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="D380" s="8" t="inlineStr">
         <is>
-          <t>152585</t>
+          <t>149819</t>
         </is>
       </c>
       <c r="E380" s="8" t="inlineStr">
         <is>
-          <t>11170101</t>
+          <t>11164267</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>DiscoveryCancun</t>
+          <t>SI25Tu20Swimm</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>70101 C4P DIS STN MUG CANCUN 14OZ</t>
+          <t>64267 C2P S25 TMBLR SUMMER SWIMMERS 20OZ</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -20025,7 +20037,7 @@
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>DiscoveryCancun</t>
+          <t>SI25Tu20Swimm</t>
         </is>
       </c>
       <c r="K380" t="inlineStr"/>
@@ -20039,31 +20051,31 @@
         </is>
       </c>
       <c r="B381" s="7" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C381" s="8" t="inlineStr">
         <is>
-          <t>16150</t>
+          <t>16655</t>
         </is>
       </c>
       <c r="D381" s="8" t="inlineStr">
         <is>
-          <t>149839</t>
+          <t>152585</t>
         </is>
       </c>
       <c r="E381" s="8" t="inlineStr">
         <is>
-          <t>11164271</t>
+          <t>11170101</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>SI25SSCC24Paddle</t>
+          <t>DiscoveryCancun</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>64271 C2P S25 TMBLR HOT CLD PADEL 24OZ</t>
+          <t>70101 C4P DIS STN MUG CANCUN 14OZ</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -20078,7 +20090,7 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>SI25SSCC24Paddle</t>
+          <t>DiscoveryCancun</t>
         </is>
       </c>
       <c r="K381" t="inlineStr"/>
@@ -20092,31 +20104,31 @@
         </is>
       </c>
       <c r="B382" s="7" t="n">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C382" s="8" t="inlineStr">
         <is>
-          <t>16594</t>
+          <t>16150</t>
         </is>
       </c>
       <c r="D382" s="8" t="inlineStr">
         <is>
-          <t>152534</t>
+          <t>149839</t>
         </is>
       </c>
       <c r="E382" s="8" t="inlineStr">
         <is>
-          <t>11170196</t>
+          <t>11164271</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>ToteBag MTY</t>
+          <t>SI25SSCC24Paddle</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>70196 P2P TOTE BAG MONTERREY</t>
+          <t>64271 C2P S25 TMBLR HOT CLD PADEL 24OZ</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -20131,7 +20143,7 @@
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>ToteBag MTY</t>
+          <t>SI25SSCC24Paddle</t>
         </is>
       </c>
       <c r="K382" t="inlineStr"/>
@@ -20149,27 +20161,27 @@
       </c>
       <c r="C383" s="8" t="inlineStr">
         <is>
-          <t>16639</t>
+          <t>16594</t>
         </is>
       </c>
       <c r="D383" s="8" t="inlineStr">
         <is>
-          <t>152569</t>
+          <t>152534</t>
         </is>
       </c>
       <c r="E383" s="8" t="inlineStr">
         <is>
-          <t>11170103</t>
+          <t>11170196</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>DiscoveryCabos</t>
+          <t>ToteBag MTY</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>70103 C4P DIS STN MUG LOS CABOS 14OZ</t>
+          <t>70196 P2P TOTE BAG MONTERREY</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -20184,7 +20196,7 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>DiscoveryCabos</t>
+          <t>ToteBag MTY</t>
         </is>
       </c>
       <c r="K383" t="inlineStr"/>
@@ -20198,31 +20210,31 @@
         </is>
       </c>
       <c r="B384" s="7" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C384" s="8" t="inlineStr">
         <is>
-          <t>16588</t>
+          <t>16639</t>
         </is>
       </c>
       <c r="D384" s="8" t="inlineStr">
         <is>
-          <t>152528</t>
+          <t>152569</t>
         </is>
       </c>
       <c r="E384" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11170103</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Xm25ReuElev</t>
+          <t>DiscoveryCabos</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>VASO/TAPA 16OZ REUSABLE PROM9IM1 CJ52PZA</t>
+          <t>70103 C4P DIS STN MUG LOS CABOS 14OZ</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -20237,7 +20249,7 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>Xm25ReuElev</t>
+          <t>DiscoveryCabos</t>
         </is>
       </c>
       <c r="K384" t="inlineStr"/>
@@ -20251,27 +20263,31 @@
         </is>
       </c>
       <c r="B385" s="7" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C385" s="8" t="inlineStr">
         <is>
-          <t>16566</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="D385" s="8" t="inlineStr">
         <is>
-          <t>150059</t>
-        </is>
-      </c>
-      <c r="E385" s="8" t="inlineStr"/>
+          <t>152528</t>
+        </is>
+      </c>
+      <c r="E385" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>BearHugger</t>
+          <t>Xm25ReuElev</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>OSO DE PELUCHE MANDIL VDE CJ32PZAS</t>
+          <t>VASO/TAPA 16OZ REUSABLE PROM9IM1 CJ52PZA</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -20286,7 +20302,7 @@
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>BearHugger</t>
+          <t>Xm25ReuElev</t>
         </is>
       </c>
       <c r="K385" t="inlineStr"/>
@@ -20300,31 +20316,27 @@
         </is>
       </c>
       <c r="B386" s="7" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C386" s="8" t="inlineStr">
         <is>
-          <t>16679</t>
+          <t>16566</t>
         </is>
       </c>
       <c r="D386" s="8" t="inlineStr">
         <is>
-          <t>152609</t>
-        </is>
-      </c>
-      <c r="E386" s="8" t="inlineStr">
-        <is>
-          <t>11176712</t>
-        </is>
-      </c>
+          <t>150059</t>
+        </is>
+      </c>
+      <c r="E386" s="8" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Sp26CCReusTierra</t>
+          <t>BearHugger</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>76712 P10P SP26 PLSTC RSBCLCP EARTH 24OZ</t>
+          <t>OSO DE PELUCHE MANDIL VDE CJ32PZAS</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -20339,7 +20351,7 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>Sp26CCReusTierra</t>
+          <t>BearHugger</t>
         </is>
       </c>
       <c r="K386" t="inlineStr"/>
@@ -20353,31 +20365,31 @@
         </is>
       </c>
       <c r="B387" s="7" t="n">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C387" s="8" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>16679</t>
         </is>
       </c>
       <c r="D387" s="8" t="inlineStr">
         <is>
-          <t>152539</t>
+          <t>152609</t>
         </is>
       </c>
       <c r="E387" s="8" t="inlineStr">
         <is>
-          <t>11170191</t>
+          <t>11176712</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>ToteBag GDL</t>
+          <t>Sp26CCReusTierra</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>70191 P2P TOTE BAG GUADALAJARA</t>
+          <t>76712 P10P SP26 PLSTC RSBCLCP EARTH 24OZ</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -20392,7 +20404,7 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>ToteBag GDL</t>
+          <t>Sp26CCReusTierra</t>
         </is>
       </c>
       <c r="K387" t="inlineStr"/>
@@ -20406,31 +20418,31 @@
         </is>
       </c>
       <c r="B388" s="7" t="n">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="C388" s="8" t="inlineStr">
         <is>
-          <t>16638</t>
+          <t>16599</t>
         </is>
       </c>
       <c r="D388" s="8" t="inlineStr">
         <is>
-          <t>152568</t>
+          <t>152539</t>
         </is>
       </c>
       <c r="E388" s="8" t="inlineStr">
         <is>
-          <t>11170118</t>
+          <t>11170191</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>DiscoveryLeon</t>
+          <t>ToteBag GDL</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>70118 C4P DIS STN MUG LEON 14OZ</t>
+          <t>70191 P2P TOTE BAG GUADALAJARA</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -20445,7 +20457,7 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>DiscoveryLeon</t>
+          <t>ToteBag GDL</t>
         </is>
       </c>
       <c r="K388" t="inlineStr"/>
@@ -20459,31 +20471,31 @@
         </is>
       </c>
       <c r="B389" s="7" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C389" s="8" t="inlineStr">
         <is>
-          <t>16635</t>
+          <t>16638</t>
         </is>
       </c>
       <c r="D389" s="8" t="inlineStr">
         <is>
-          <t>152565</t>
+          <t>152568</t>
         </is>
       </c>
       <c r="E389" s="8" t="inlineStr">
         <is>
-          <t>11170109</t>
+          <t>11170118</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>DiscoveryEnsenad</t>
+          <t>DiscoveryLeon</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>70109 C4P DIS STN MUG ENSENADA 14OZ</t>
+          <t>70118 C4P DIS STN MUG LEON 14OZ</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -20498,7 +20510,7 @@
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>DiscoveryEnsenad</t>
+          <t>DiscoveryLeon</t>
         </is>
       </c>
       <c r="K389" t="inlineStr"/>
@@ -20512,31 +20524,31 @@
         </is>
       </c>
       <c r="B390" s="7" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C390" s="8" t="inlineStr">
         <is>
-          <t>16650</t>
+          <t>16635</t>
         </is>
       </c>
       <c r="D390" s="8" t="inlineStr">
         <is>
-          <t>152580</t>
+          <t>152565</t>
         </is>
       </c>
       <c r="E390" s="8" t="inlineStr">
         <is>
-          <t>11170119</t>
+          <t>11170109</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>DiscoveryQRO</t>
+          <t>DiscoveryEnsenad</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>70119 C4P DIS STN MUG QUERETARO 14OZ</t>
+          <t>70109 C4P DIS STN MUG ENSENADA 14OZ</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -20551,7 +20563,7 @@
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>DiscoveryQRO</t>
+          <t>DiscoveryEnsenad</t>
         </is>
       </c>
       <c r="K390" t="inlineStr"/>
@@ -20565,31 +20577,31 @@
         </is>
       </c>
       <c r="B391" s="7" t="n">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C391" s="8" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="D391" s="8" t="inlineStr">
         <is>
-          <t>154172</t>
+          <t>152580</t>
         </is>
       </c>
       <c r="E391" s="8" t="inlineStr">
         <is>
-          <t>11178949</t>
+          <t>11170119</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>WC26SS20Pull</t>
+          <t>DiscoveryQRO</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>78949 C2P SM26 SS VAC TMBLR HNDL 20OZ</t>
+          <t>70119 C4P DIS STN MUG QUERETARO 14OZ</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -20604,7 +20616,7 @@
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>WC26SS20Pull</t>
+          <t>DiscoveryQRO</t>
         </is>
       </c>
       <c r="K391" t="inlineStr"/>
@@ -20618,31 +20630,31 @@
         </is>
       </c>
       <c r="B392" s="7" t="n">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C392" s="8" t="inlineStr">
         <is>
-          <t>16345</t>
+          <t>16912</t>
         </is>
       </c>
       <c r="D392" s="8" t="inlineStr">
         <is>
-          <t>149959</t>
+          <t>154172</t>
         </is>
       </c>
       <c r="E392" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11178949</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>SII25StopPSL</t>
+          <t>WC26SS20Pull</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>STOPPER PSL CJ25PZAS</t>
+          <t>78949 C2P SM26 SS VAC TMBLR HNDL 20OZ</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -20657,7 +20669,7 @@
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>SII25StopPSL</t>
+          <t>WC26SS20Pull</t>
         </is>
       </c>
       <c r="K392" t="inlineStr"/>
@@ -20671,31 +20683,31 @@
         </is>
       </c>
       <c r="B393" s="7" t="n">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C393" s="8" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>16345</t>
         </is>
       </c>
       <c r="D393" s="8" t="inlineStr">
         <is>
-          <t>152564</t>
+          <t>149959</t>
         </is>
       </c>
       <c r="E393" s="8" t="inlineStr">
         <is>
-          <t>11170105</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>DiscoveryCozumel</t>
+          <t>SII25StopPSL</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>70105 C4P DIS STN MUG COZUMEL 14OZ</t>
+          <t>STOPPER PSL CJ25PZAS</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -20710,7 +20722,7 @@
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>DiscoveryCozumel</t>
+          <t>SII25StopPSL</t>
         </is>
       </c>
       <c r="K393" t="inlineStr"/>
@@ -20724,31 +20736,31 @@
         </is>
       </c>
       <c r="B394" s="7" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C394" s="8" t="inlineStr">
         <is>
-          <t>16344</t>
+          <t>16634</t>
         </is>
       </c>
       <c r="D394" s="8" t="inlineStr">
         <is>
-          <t>149958</t>
+          <t>152564</t>
         </is>
       </c>
       <c r="E394" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11170105</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>SII25StrawLluvia</t>
+          <t>DiscoveryCozumel</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>STOPPER RAIN STRAW CJ25PZAS</t>
+          <t>70105 C4P DIS STN MUG COZUMEL 14OZ</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -20763,7 +20775,7 @@
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>SII25StrawLluvia</t>
+          <t>DiscoveryCozumel</t>
         </is>
       </c>
       <c r="K394" t="inlineStr"/>
@@ -20777,16 +20789,16 @@
         </is>
       </c>
       <c r="B395" s="7" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C395" s="8" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>16344</t>
         </is>
       </c>
       <c r="D395" s="8" t="inlineStr">
         <is>
-          <t>149955</t>
+          <t>149958</t>
         </is>
       </c>
       <c r="E395" s="8" t="inlineStr">
@@ -20796,12 +20808,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>SII25LlaveroB2S</t>
+          <t>SII25StrawLluvia</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>LLAVERO MOCHILA CJ30PZAS</t>
+          <t>STOPPER RAIN STRAW CJ25PZAS</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -20816,7 +20828,7 @@
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>SII25LlaveroB2S</t>
+          <t>SII25StrawLluvia</t>
         </is>
       </c>
       <c r="K395" t="inlineStr"/>
@@ -20830,31 +20842,31 @@
         </is>
       </c>
       <c r="B396" s="7" t="n">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="C396" s="8" t="inlineStr">
         <is>
-          <t>16596</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="D396" s="8" t="inlineStr">
         <is>
-          <t>152536</t>
+          <t>149955</t>
         </is>
       </c>
       <c r="E396" s="8" t="inlineStr">
         <is>
-          <t>11170194</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>ToteBag Pvallart</t>
+          <t>SII25LlaveroB2S</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>70194 P2P TOTE BAG PUERTO VALLARTA</t>
+          <t>LLAVERO MOCHILA CJ30PZAS</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -20869,7 +20881,7 @@
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>ToteBag Pvallart</t>
+          <t>SII25LlaveroB2S</t>
         </is>
       </c>
       <c r="K396" t="inlineStr"/>
@@ -20883,31 +20895,31 @@
         </is>
       </c>
       <c r="B397" s="7" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C397" s="8" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>16596</t>
         </is>
       </c>
       <c r="D397" s="8" t="inlineStr">
         <is>
-          <t>152548</t>
+          <t>152536</t>
         </is>
       </c>
       <c r="E397" s="8" t="inlineStr">
         <is>
-          <t>11177937</t>
+          <t>11170194</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Sp26CCup16Cherry</t>
+          <t>ToteBag Pvallart</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>77937 C1P CCUP CORGICHERRY BLSM 16OZ</t>
+          <t>70194 P2P TOTE BAG PUERTO VALLARTA</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -20922,7 +20934,7 @@
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>Sp26CCup16Cherry</t>
+          <t>ToteBag Pvallart</t>
         </is>
       </c>
       <c r="K397" t="inlineStr"/>

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de fotos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Control de fotos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Control de fotos'!$A$7:$M$1170</definedName>
@@ -5245,27 +5245,27 @@
         </is>
       </c>
       <c r="B79" s="7" t="n">
-        <v>315</v>
+        <v>437</v>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>16960</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>152541</t>
+          <t>155962</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ToteBag MxPais</t>
+          <t>SII26CC24Rain</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>70187 P2P TOTE BAG MEXICO</t>
+          <t>60979 C2P CORE PLSTC HTCDCP DCHRC 24OZ</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>ToteBag MxPais</t>
+          <t>SII26CC24Rain</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>lote-01/16601.webp</t>
+          <t>lote-01/16960.webp</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5306,27 +5306,27 @@
         </is>
       </c>
       <c r="B80" s="7" t="n">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>16689</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>152619</t>
+          <t>152541</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Disc2ozCDMX</t>
+          <t>ToteBag MxPais</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>70149 C4P DIS STN MUG CDMX 2OZ</t>
+          <t>70187 P2P TOTE BAG MEXICO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5341,12 +5341,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Disc2ozCDMX</t>
+          <t>ToteBag MxPais</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>lote-01/16689.webp</t>
+          <t>lote-01/16601.webp</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5367,31 +5367,27 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>152548</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t>11177937</t>
-        </is>
-      </c>
+          <t>152619</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sp26CCup16Cherry</t>
+          <t>Disc2ozCDMX</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>77937 C1P CCUP CORGICHERRY BLSM 16OZ</t>
+          <t>70149 C4P DIS STN MUG CDMX 2OZ</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5406,12 +5402,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Sp26CCup16Cherry</t>
+          <t>Disc2ozCDMX</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>lote-01/16611.webp</t>
+          <t>lote-01/16689.webp</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5432,31 +5428,31 @@
         </is>
       </c>
       <c r="B82" s="7" t="n">
-        <v>88</v>
+        <v>224</v>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>149915</t>
+          <t>152548</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>11160991</t>
+          <t>11177937</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>COR25SS16Sleeve</t>
+          <t>Sp26CCup16Cherry</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>60991 C2P CORE RECYCLD SS SLEEVE SI 16OZ</t>
+          <t>77937 C1P CCUP CORGICHERRY BLSM 16OZ</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5471,12 +5467,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>COR25SS16Sleeve</t>
+          <t>Sp26CCup16Cherry</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>lote-01/16284.webp</t>
+          <t>lote-01/16611.webp</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5497,31 +5493,31 @@
         </is>
       </c>
       <c r="B83" s="7" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>16284</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>149827</t>
+          <t>149915</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>11164293</t>
+          <t>11160991</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SI25Tz14Glass</t>
+          <t>COR25SS16Sleeve</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>64293 C2P S25 GLASS MUG SAFARI 14OZ</t>
+          <t>60991 C2P CORE RECYCLD SS SLEEVE SI 16OZ</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5536,12 +5532,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>SI25Tz14Glass</t>
+          <t>COR25SS16Sleeve</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>lote-01/16129.webp</t>
+          <t>lote-01/16284.webp</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5562,27 +5558,31 @@
         </is>
       </c>
       <c r="B84" s="7" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>152614</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="inlineStr"/>
+          <t>149827</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>11164293</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Disc2ozChiapas</t>
+          <t>SI25Tz14Glass</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>70158 C4P DIS STN MUG CHIAPAS 2OZ</t>
+          <t>64293 C2P S25 GLASS MUG SAFARI 14OZ</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Disc2ozChiapas</t>
+          <t>SI25Tz14Glass</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>lote-01/16684.webp</t>
+          <t>lote-01/16129.webp</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5623,31 +5623,27 @@
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>155961</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>11187372</t>
-        </is>
-      </c>
+          <t>152614</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>WC26Tu24DW</t>
+          <t>Disc2ozChiapas</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>87372 C2P WC26 PLSTC CDCP FOOTBALL 24OZ</t>
+          <t>70158 C4P DIS STN MUG CHIAPAS 2OZ</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5662,12 +5658,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>WC26Tu24DW</t>
+          <t>Disc2ozChiapas</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>lote-01/16959.webp</t>
+          <t>lote-01/16684.webp</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5688,31 +5684,31 @@
         </is>
       </c>
       <c r="B86" s="7" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>150012</t>
+          <t>155961</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>11173043</t>
+          <t>11187372</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Xm25GlassBear</t>
+          <t>WC26Tu24DW</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>73043 C2P XM25 GLASS CLD BEARISTA 20OZ</t>
+          <t>87372 C2P WC26 PLSTC CDCP FOOTBALL 24OZ</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5722,13 +5718,17 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SECUNDARIO</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>WC26Tu24DW</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>lote-01/16477.webp</t>
+          <t>lote-01/16959.webp</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5753,27 +5753,27 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16477</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>154147</t>
+          <t>150012</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>11178933</t>
+          <t>11173043</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SII25CC24Gamer</t>
+          <t>Xm25GlassBear</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>78933 C2P SM26 PLSTC CLDCP GMR CHRM 24OZ</t>
+          <t>73043 C2P XM25 GLASS CLD BEARISTA 20OZ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5789,7 +5789,7 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>lote-01/16881.webp</t>
+          <t>lote-01/16477.webp</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5814,23 +5814,27 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>16889</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>154153</t>
-        </is>
-      </c>
-      <c r="E88" s="8" t="inlineStr"/>
+          <t>154147</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>11178933</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>VASO/TAPA 16OZ REUSABLE WCUP26 CJ52PZAS</t>
+          <t>SII25CC24Gamer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>VASO/TAPA 16OZ REUSABLE WCUP26 CJ52PZAS</t>
+          <t>78933 C2P SM26 PLSTC CLDCP GMR CHRM 24OZ</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5846,7 +5850,7 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>lote-01/16889.webp</t>
+          <t>lote-01/16881.webp</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5871,23 +5875,23 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>16960</t>
+          <t>16889</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>155962</t>
+          <t>154153</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>60979 C2P CORE PLSTC HTCDCP DCHRC 24OZ</t>
+          <t>Fl26ResuAMx</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>60979 C2P CORE PLSTC HTCDCP DCHRC 24OZ</t>
+          <t>VASO/TAPA 16OZ REUSABLE WCUP26 CJ52PZAS</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5903,7 +5907,7 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>lote-01/16960.webp</t>
+          <t>lote-01/16889.webp</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5939,7 +5943,7 @@
       <c r="E90" s="8" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>86639 C2P F26 PLSTC WTRBTL PSL 24OZ</t>
+          <t>Fl26PPBTL24</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5996,7 +6000,7 @@
       <c r="E91" s="8" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>86644 C2P FL26 GLSS CDCP MTTLD LSTR 18OZ</t>
+          <t>Fl26Glass18Aniv</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6053,7 +6057,7 @@
       <c r="E92" s="8" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>86654 C2P FL26 SS TMBLR CHRM 16OZ</t>
+          <t>Fl26SS16AnivCharm</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6110,7 +6114,7 @@
       <c r="E93" s="8" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>86645 C2P FL26 SS TMBLR DSKTP 12OZ</t>
+          <t>Fl26SS12psl</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6167,7 +6171,7 @@
       <c r="E94" s="8" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>86652 C2P FL26 SS TMBLR CHRM PSL 16OZ</t>
+          <t>Fl26SS16pslCharm</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6224,7 +6228,7 @@
       <c r="E95" s="8" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>86638 C2P FL26 PLSTC CDCP CNFT 24OZ</t>
+          <t>Fl26CC24psl</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6281,7 +6285,7 @@
       <c r="E96" s="8" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>86665 C2P FL26 SS CLDCP CRRY LOOP 24OZ</t>
+          <t>Fl26SSCCBrown</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -6338,7 +6342,7 @@
       <c r="E97" s="8" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>86666 C1P FL26 SS VAC TMBLR 24OZ</t>
+          <t>Fl26ThruST16Brown</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6395,7 +6399,7 @@
       <c r="E98" s="8" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>86660 C1P FL26 SS VAC TMBLR 20OZ</t>
+          <t>Fl26SS20Hand</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6452,7 +6456,7 @@
       <c r="E99" s="8" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>86653 C1P FL26 SS CLDCP STRW TPPR 16OZ</t>
+          <t>Fl26SSCCpsl</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6509,7 +6513,7 @@
       <c r="E100" s="8" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>VASO VDR SODA TRANSP SBX 470ML CJ1PZA</t>
+          <t>SII26GlCCColor</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6566,7 +6570,7 @@
       <c r="E101" s="8" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>VASO VDR SODA NARANJA SBX 470ML CJ1PZA</t>
+          <t>SII26GlCCColor</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6623,7 +6627,7 @@
       <c r="E102" s="8" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>VASO VDR SODA ROJO SBX 470ML CJ1PZA</t>
+          <t>SII26GlCCColor</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6680,7 +6684,7 @@
       <c r="E103" s="8" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>VASO VDR SODA AZUL SBX 470ML CJ1PZA</t>
+          <t>SII26GlCCColor</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6737,7 +6741,7 @@
       <c r="E104" s="8" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>VASO VDR SODA VERDE SBX 470ML CJ1PZA</t>
+          <t>SII26GlCCColor</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6794,7 +6798,7 @@
       <c r="E105" s="8" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>VASO VDR SODA AMARILLO SBX 470ML CJ1PZA</t>
+          <t>SII26GlCCColor</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Control de fotos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de fotos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Control de fotos'!$A$7:$M$1170</definedName>
@@ -5245,27 +5245,27 @@
         </is>
       </c>
       <c r="B79" s="7" t="n">
-        <v>437</v>
+        <v>315</v>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>16960</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>155962</t>
+          <t>152541</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SII26CC24Rain</t>
+          <t>ToteBag MxPais</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>60979 C2P CORE PLSTC HTCDCP DCHRC 24OZ</t>
+          <t>70187 P2P TOTE BAG MEXICO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>SII26CC24Rain</t>
+          <t>ToteBag MxPais</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>lote-01/16960.webp</t>
+          <t>lote-01/16601.webp</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5306,27 +5306,27 @@
         </is>
       </c>
       <c r="B80" s="7" t="n">
-        <v>315</v>
+        <v>278</v>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>152541</t>
+          <t>152619</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ToteBag MxPais</t>
+          <t>Disc2ozCDMX</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>70187 P2P TOTE BAG MEXICO</t>
+          <t>70149 C4P DIS STN MUG CDMX 2OZ</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5341,12 +5341,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>ToteBag MxPais</t>
+          <t>Disc2ozCDMX</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>lote-01/16601.webp</t>
+          <t>lote-01/16689.webp</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5367,27 +5367,31 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>16689</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>152619</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="inlineStr"/>
+          <t>152548</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>11177937</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Disc2ozCDMX</t>
+          <t>Sp26CCup16Cherry</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>70149 C4P DIS STN MUG CDMX 2OZ</t>
+          <t>77937 C1P CCUP CORGICHERRY BLSM 16OZ</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5402,12 +5406,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Disc2ozCDMX</t>
+          <t>Sp26CCup16Cherry</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>lote-01/16689.webp</t>
+          <t>lote-01/16611.webp</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5428,31 +5432,31 @@
         </is>
       </c>
       <c r="B82" s="7" t="n">
-        <v>224</v>
+        <v>88</v>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>16284</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>152548</t>
+          <t>149915</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>11177937</t>
+          <t>11160991</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sp26CCup16Cherry</t>
+          <t>COR25SS16Sleeve</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>77937 C1P CCUP CORGICHERRY BLSM 16OZ</t>
+          <t>60991 C2P CORE RECYCLD SS SLEEVE SI 16OZ</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5467,12 +5471,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Sp26CCup16Cherry</t>
+          <t>COR25SS16Sleeve</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>lote-01/16611.webp</t>
+          <t>lote-01/16284.webp</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5493,31 +5497,31 @@
         </is>
       </c>
       <c r="B83" s="7" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>149915</t>
+          <t>149827</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>11160991</t>
+          <t>11164293</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>COR25SS16Sleeve</t>
+          <t>SI25Tz14Glass</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>60991 C2P CORE RECYCLD SS SLEEVE SI 16OZ</t>
+          <t>64293 C2P S25 GLASS MUG SAFARI 14OZ</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5532,12 +5536,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>COR25SS16Sleeve</t>
+          <t>SI25Tz14Glass</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>lote-01/16284.webp</t>
+          <t>lote-01/16129.webp</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5558,31 +5562,27 @@
         </is>
       </c>
       <c r="B84" s="7" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>149827</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>11164293</t>
-        </is>
-      </c>
+          <t>152614</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SI25Tz14Glass</t>
+          <t>Disc2ozChiapas</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>64293 C2P S25 GLASS MUG SAFARI 14OZ</t>
+          <t>70158 C4P DIS STN MUG CHIAPAS 2OZ</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>SI25Tz14Glass</t>
+          <t>Disc2ozChiapas</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>lote-01/16129.webp</t>
+          <t>lote-01/16684.webp</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5623,27 +5623,31 @@
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>152614</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="inlineStr"/>
+          <t>155961</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>11187372</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Disc2ozChiapas</t>
+          <t>WC26Tu24DW</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>70158 C4P DIS STN MUG CHIAPAS 2OZ</t>
+          <t>87372 C2P WC26 PLSTC CDCP FOOTBALL 24OZ</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5658,12 +5662,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Disc2ozChiapas</t>
+          <t>WC26Tu24DW</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>lote-01/16684.webp</t>
+          <t>lote-01/16959.webp</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5684,31 +5688,31 @@
         </is>
       </c>
       <c r="B86" s="7" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>16477</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>155961</t>
+          <t>150012</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>11187372</t>
+          <t>11173043</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>WC26Tu24DW</t>
+          <t>Xm25GlassBear</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>87372 C2P WC26 PLSTC CDCP FOOTBALL 24OZ</t>
+          <t>73043 C2P XM25 GLASS CLD BEARISTA 20OZ</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5718,17 +5722,13 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>ACTIVO</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>WC26Tu24DW</t>
-        </is>
-      </c>
+          <t>SECUNDARIO</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>lote-01/16959.webp</t>
+          <t>lote-01/16477.webp</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5753,27 +5753,27 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>150012</t>
+          <t>154147</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>11173043</t>
+          <t>11178933</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Xm25GlassBear</t>
+          <t>SII25CC24Gamer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>73043 C2P XM25 GLASS CLD BEARISTA 20OZ</t>
+          <t>78933 C2P SM26 PLSTC CLDCP GMR CHRM 24OZ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5789,7 +5789,7 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>lote-01/16477.webp</t>
+          <t>lote-01/16881.webp</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5814,27 +5814,23 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16889</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>154147</t>
-        </is>
-      </c>
-      <c r="E88" s="8" t="inlineStr">
-        <is>
-          <t>11178933</t>
-        </is>
-      </c>
+          <t>154153</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SII25CC24Gamer</t>
+          <t>VASO/TAPA 16OZ REUSABLE WCUP26 CJ52PZAS</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>78933 C2P SM26 PLSTC CLDCP GMR CHRM 24OZ</t>
+          <t>VASO/TAPA 16OZ REUSABLE WCUP26 CJ52PZAS</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5850,12 +5846,12 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>lote-01/16881.webp</t>
+          <t>lote-02/16889.webp</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>lote-01</t>
+          <t>lote-02</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -5875,23 +5871,23 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>16889</t>
+          <t>16960</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>154153</t>
+          <t>155962</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fl26ResuAMx</t>
+          <t>60979 C2P CORE PLSTC HTCDCP DCHRC 24OZ</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>VASO/TAPA 16OZ REUSABLE WCUP26 CJ52PZAS</t>
+          <t>60979 C2P CORE PLSTC HTCDCP DCHRC 24OZ</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5907,7 +5903,7 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>lote-01/16889.webp</t>
+          <t>lote-01/16960.webp</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5943,7 +5939,7 @@
       <c r="E90" s="8" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fl26PPBTL24</t>
+          <t>86639 C2P F26 PLSTC WTRBTL PSL 24OZ</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6000,7 +5996,7 @@
       <c r="E91" s="8" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fl26Glass18Aniv</t>
+          <t>86644 C2P FL26 GLSS CDCP MTTLD LSTR 18OZ</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6021,12 +6017,12 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>lote-01/16972.webp</t>
+          <t>lote-02/16972.webp</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>lote-01</t>
+          <t>lote-02</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -6057,7 +6053,7 @@
       <c r="E92" s="8" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fl26SS16AnivCharm</t>
+          <t>86654 C2P FL26 SS TMBLR CHRM 16OZ</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6078,12 +6074,12 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>lote-01/16990.webp</t>
+          <t>lote-02/16990.webp</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>lote-01</t>
+          <t>lote-02</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -6114,7 +6110,7 @@
       <c r="E93" s="8" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fl26SS12psl</t>
+          <t>86645 C2P FL26 SS TMBLR DSKTP 12OZ</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6171,7 +6167,7 @@
       <c r="E94" s="8" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fl26SS16pslCharm</t>
+          <t>86652 C2P FL26 SS TMBLR CHRM PSL 16OZ</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6228,7 +6224,7 @@
       <c r="E95" s="8" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fl26CC24psl</t>
+          <t>86638 C2P FL26 PLSTC CDCP CNFT 24OZ</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6285,7 +6281,7 @@
       <c r="E96" s="8" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fl26SSCCBrown</t>
+          <t>86665 C2P FL26 SS CLDCP CRRY LOOP 24OZ</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -6306,12 +6302,12 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>lote-01/17336.webp</t>
+          <t>lote-02/17336.webp</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>lote-01</t>
+          <t>lote-02</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -6342,7 +6338,7 @@
       <c r="E97" s="8" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fl26ThruST16Brown</t>
+          <t>86666 C1P FL26 SS VAC TMBLR 24OZ</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6363,12 +6359,12 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>lote-01/17337.webp</t>
+          <t>lote-02/17337.webp</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>lote-01</t>
+          <t>lote-02</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -6399,7 +6395,7 @@
       <c r="E98" s="8" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fl26SS20Hand</t>
+          <t>86660 C1P FL26 SS VAC TMBLR 20OZ</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6420,12 +6416,12 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>lote-01/17338.webp</t>
+          <t>lote-02/17338.webp</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>lote-01</t>
+          <t>lote-02</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -6456,7 +6452,7 @@
       <c r="E99" s="8" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fl26SSCCpsl</t>
+          <t>86653 C1P FL26 SS CLDCP STRW TPPR 16OZ</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6513,7 +6509,7 @@
       <c r="E100" s="8" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SII26GlCCColor</t>
+          <t>VASO VDR SODA TRANSP SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6570,7 +6566,7 @@
       <c r="E101" s="8" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SII26GlCCColor</t>
+          <t>VASO VDR SODA NARANJA SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6627,7 +6623,7 @@
       <c r="E102" s="8" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SII26GlCCColor</t>
+          <t>VASO VDR SODA ROJO SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6684,7 +6680,7 @@
       <c r="E103" s="8" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SII26GlCCColor</t>
+          <t>VASO VDR SODA AZUL SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6741,7 +6737,7 @@
       <c r="E104" s="8" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SII26GlCCColor</t>
+          <t>VASO VDR SODA VERDE SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6798,7 +6794,7 @@
       <c r="E105" s="8" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SII26GlCCColor</t>
+          <t>VASO VDR SODA AMARILLO SBX 470ML CJ1PZA</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">

--- a/Control_Fotos_CodeBrew.xlsx
+++ b/Control_Fotos_CodeBrew.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de fotos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Control de fotos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Control de fotos'!$A$7:$M$1170</definedName>
